--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-07-22 · evaluated at 0 days to election (actual: 104 days out)</t>
+          <t>Data as of 2026-07-23 · evaluated at 0 days to election (actual: 103 days out)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>231.9</v>
       </c>
       <c r="C9" t="n">
-        <v>203</v>
+        <v>203.1</v>
       </c>
       <c r="D9" t="n">
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>80.5</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-2.77</v>
+        <v>-3.18</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>59.4</v>
+        <v>60.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>44.4</v>
+        <v>44.38</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>47.6</v>
+        <v>47.62</v>
       </c>
       <c r="AD2" s="4" t="n">
         <v>8</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.44</v>
+        <v>7.46</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>88.90000000000001</v>
@@ -1253,10 +1253,10 @@
         <v>4.91</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>7.93</v>
+        <v>7.97</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q5" s="4" t="n">
         <v>6.01</v>
@@ -1277,10 +1277,10 @@
         <v>6.65</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>6534592</v>
+        <v>9827820</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>1923723</v>
+        <v>2787170</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" s="4" t="n">
@@ -1290,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>53.72</v>
+        <v>53.73</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>46.28</v>
+        <v>46.27</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26.58</v>
+        <v>26.61</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>63.29</v>
+        <v>63.31</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>36.71</v>
+        <v>36.69</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17.3</v>
+        <v>17.34</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.59999999999999</v>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>58.65</v>
+        <v>58.67</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>41.35</v>
+        <v>41.33</v>
       </c>
       <c r="AD8" s="4" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>51.52</v>
+        <v>51.51</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>48.48</v>
+        <v>48.49</v>
       </c>
       <c r="AD10" s="4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>29.03</v>
+        <v>29.05</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>64.51000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>35.49</v>
+        <v>35.47</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12.53</v>
+        <v>12.51</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>55.62</v>
+        <v>55.61</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>43.24</v>
+        <v>43.25</v>
       </c>
       <c r="AD18" s="4" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>12.37</v>
+        <v>12.38</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.37</v>
+        <v>12.36</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>56.19</v>
+        <v>56.18</v>
       </c>
       <c r="AC20" s="4" t="n">
-        <v>43.81</v>
+        <v>43.82</v>
       </c>
       <c r="AD20" s="4" t="n">
         <v>0</v>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.67</v>
+        <v>-10.69</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>44.66</v>
+        <v>44.65</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>55.34</v>
+        <v>55.35</v>
       </c>
       <c r="AD22" s="4" t="n">
         <v>0</v>
@@ -3233,13 +3233,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.02</v>
+        <v>15.01</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>99.3</v>
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.46</v>
+        <v>-3.47</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>77.90000000000001</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>52.08</v>
+        <v>52.09</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>47.92</v>
+        <v>47.91</v>
       </c>
       <c r="AD28" s="4" t="n">
         <v>0</v>
@@ -3816,10 +3816,10 @@
         <v>0</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>58.16</v>
+        <v>58.17</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>41.84</v>
+        <v>41.83</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.39</v>
+        <v>19.4</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.7</v>
@@ -3920,10 +3920,10 @@
         <v>0</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>59.69</v>
+        <v>59.7</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>40.31</v>
+        <v>40.3</v>
       </c>
       <c r="AD30" s="4" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-21.33</v>
+        <v>-21.32</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>0.2</v>
@@ -4271,13 +4271,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-8.68</v>
+        <v>-8.69</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>45.66</v>
+        <v>45.65</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>54.34</v>
+        <v>54.35</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-18.35</v>
+        <v>-18.46</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.3</v>
@@ -4436,10 +4436,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>40.82</v>
+        <v>40.77</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>59.18</v>
+        <v>59.23</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>0</v>
@@ -4486,10 +4486,10 @@
         <v>3.68</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4689,13 +4689,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.32</v>
+        <v>-3.18</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>41.8</v>
+        <v>40</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>58.2</v>
+        <v>60</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4703,16 +4703,16 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-8.369999999999999</v>
+        <v>-2.53</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-6.19</v>
+        <v>-1.45</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="Q38" s="4" t="n">
         <v>-1.67</v>
@@ -4736,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="5" t="n">
-        <v>0</v>
+        <v>5261611</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4744,16 +4744,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.84</v>
+        <v>48.41</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>41.8</v>
+        <v>40</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.16</v>
+        <v>51.59</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>-3.4</v>
+        <v>-3.41</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>25</v>
@@ -4919,10 +4919,10 @@
         <v>4.91</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-3.05</v>
+        <v>-3.07</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="Q40" s="4" t="n">
         <v>2.48</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>79</v>
@@ -5941,10 +5941,10 @@
         <v>4.91</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>-0.48</v>
+        <v>-0.5</v>
       </c>
       <c r="Q50" s="4" t="n">
         <v>0</v>
@@ -5978,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>51.26</v>
+        <v>51.25</v>
       </c>
       <c r="AC50" s="4" t="n">
-        <v>46.86</v>
+        <v>46.87</v>
       </c>
       <c r="AD50" s="4" t="n">
         <v>1.88</v>
@@ -6029,13 +6029,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-1.04</v>
+        <v>-1</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6086,10 +6086,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>49.48</v>
+        <v>49.5</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>50.52</v>
+        <v>50.5</v>
       </c>
       <c r="AD51" s="4" t="n">
         <v>0</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>46.7</v>
+        <v>46.71</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>4.91</v>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>10.54</v>
+        <v>10.55</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>4.91</v>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>-13.4</v>
+        <v>-13.39</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>0.9</v>
@@ -6351,13 +6351,13 @@
         </is>
       </c>
       <c r="M54" s="4" t="n">
-        <v>-16.36</v>
+        <v>-16.35</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>-13.4</v>
+        <v>-13.39</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>-1.75</v>
@@ -6439,13 +6439,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>4.58</v>
+        <v>4.59</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -6453,13 +6453,13 @@
         </is>
       </c>
       <c r="M55" s="4" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0.13</v>
@@ -6496,10 +6496,10 @@
         <v>0</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>51.18</v>
+        <v>51.19</v>
       </c>
       <c r="AC55" s="4" t="n">
-        <v>46.7</v>
+        <v>46.69</v>
       </c>
       <c r="AD55" s="4" t="n">
         <v>2.12</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>28.74</v>
+        <v>28.75</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>4.91</v>
@@ -6802,10 +6802,10 @@
         <v>0</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>38.37</v>
+        <v>38.38</v>
       </c>
       <c r="AC58" s="4" t="n">
-        <v>61.63</v>
+        <v>61.62</v>
       </c>
       <c r="AD58" s="4" t="n">
         <v>0</v>
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>15.4</v>
+        <v>15.41</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>4.91</v>
@@ -6904,10 +6904,10 @@
         <v>0</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>59.48</v>
+        <v>59.49</v>
       </c>
       <c r="AC59" s="4" t="n">
-        <v>40.52</v>
+        <v>40.51</v>
       </c>
       <c r="AD59" s="4" t="n">
         <v>0</v>
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>33.04</v>
+        <v>33.05</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>100</v>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.78</v>
+        <v>27.79</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33.04</v>
+        <v>33.05</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>20.85</v>
+        <v>20.86</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>99.8</v>
@@ -7077,7 +7077,7 @@
         <v>4.91</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>20.85</v>
+        <v>20.86</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>1.08</v>
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>18.23</v>
+        <v>18.24</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>26.27</v>
+        <v>26.28</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>-18.51</v>
+        <v>-18.5</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0.3</v>
@@ -7281,7 +7281,7 @@
         <v>4.91</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>-18.51</v>
+        <v>-18.5</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>-0.65</v>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12.12</v>
+        <v>12.13</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>98.90000000000001</v>
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>11.2</v>
+        <v>11.21</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12.12</v>
+        <v>12.13</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>-0.35</v>
@@ -7485,7 +7485,7 @@
         <v>4.91</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>25.14</v>
+        <v>25.15</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>39.13</v>
+        <v>39.14</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>4.91</v>
@@ -7669,7 +7669,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>30.43</v>
+        <v>30.44</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>100</v>
@@ -7689,7 +7689,7 @@
         <v>4.91</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>30.43</v>
+        <v>30.44</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>2.78</v>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>42.6</v>
+        <v>42.61</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>100</v>
@@ -7791,7 +7791,7 @@
         <v>4.91</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>42.6</v>
+        <v>42.61</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
@@ -7883,13 +7883,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>73.98999999999999</v>
+        <v>74</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>78.59</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21.32</v>
+        <v>21.33</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>99.8</v>
@@ -8093,7 +8093,7 @@
         <v>4.91</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>21.32</v>
+        <v>21.33</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0.46</v>
@@ -8185,13 +8185,13 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>40.66</v>
+        <v>40.67</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>45.69</v>
+        <v>45.7</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
         </is>
       </c>
       <c r="M74" s="4" t="n">
-        <v>52.87</v>
+        <v>52.88</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>4.91</v>
@@ -8426,10 +8426,10 @@
         <v>0</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>79.67</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="AC74" s="4" t="n">
-        <v>20.33</v>
+        <v>20.32</v>
       </c>
       <c r="AD74" s="4" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>48.7</v>
+        <v>48.71</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>100</v>
@@ -8497,7 +8497,7 @@
         <v>4.91</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>48.7</v>
+        <v>48.71</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>3.69</v>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>43.64</v>
+        <v>43.65</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>100</v>
@@ -8599,7 +8599,7 @@
         <v>4.91</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>43.64</v>
+        <v>43.65</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>2.1</v>
@@ -8695,13 +8695,13 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.6</v>
+        <v>38.61</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>49.91</v>
+        <v>49.92</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>2.46</v>
@@ -8783,7 +8783,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-28.9</v>
+        <v>-28.89</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -8797,13 +8797,13 @@
         </is>
       </c>
       <c r="M78" s="4" t="n">
-        <v>-30.37</v>
+        <v>-30.36</v>
       </c>
       <c r="N78" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-28.9</v>
+        <v>-28.89</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.51</v>
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.74</v>
+        <v>11.75</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>4.91</v>
@@ -8936,10 +8936,10 @@
         <v>0</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>60.3</v>
+        <v>60.31</v>
       </c>
       <c r="AC79" s="4" t="n">
-        <v>39.7</v>
+        <v>39.69</v>
       </c>
       <c r="AD79" s="4" t="n">
         <v>0</v>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="M80" s="4" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>4.91</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>52.59</v>
+        <v>52.6</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47.41</v>
+        <v>47.4</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -9146,10 +9146,10 @@
         <v>0</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>41.66</v>
+        <v>41.67</v>
       </c>
       <c r="AC81" s="4" t="n">
-        <v>58.34</v>
+        <v>58.33</v>
       </c>
       <c r="AD81" s="4" t="n">
         <v>0</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="M82" s="4" t="n">
-        <v>28.15</v>
+        <v>28.16</v>
       </c>
       <c r="N82" s="4" t="n">
         <v>4.91</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25.52</v>
+        <v>25.53</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>99.90000000000001</v>
@@ -9417,7 +9417,7 @@
         <v>4.91</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>25.52</v>
+        <v>25.53</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.63</v>
@@ -9550,10 +9550,10 @@
         <v>0</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>63.26</v>
+        <v>63.27</v>
       </c>
       <c r="AC85" s="4" t="n">
-        <v>36.74</v>
+        <v>36.73</v>
       </c>
       <c r="AD85" s="4" t="n">
         <v>0</v>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>39.48</v>
+        <v>39.49</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9615,13 +9615,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.74</v>
+        <v>29.75</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>39.48</v>
+        <v>39.49</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.23</v>
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.3</v>
+        <v>41.31</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>4.91</v>
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>51.38</v>
+        <v>51.39</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>100</v>
@@ -9819,13 +9819,13 @@
         </is>
       </c>
       <c r="M88" s="4" t="n">
-        <v>44.75</v>
+        <v>44.76</v>
       </c>
       <c r="N88" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>51.38</v>
+        <v>51.39</v>
       </c>
       <c r="P88" s="4" t="n">
         <v>1.57</v>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>29.86</v>
+        <v>29.87</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>4.91</v>
@@ -10111,7 +10111,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28.07</v>
+        <v>28.08</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>100</v>
@@ -10125,13 +10125,13 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>16.21</v>
+        <v>16.22</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28.07</v>
+        <v>28.08</v>
       </c>
       <c r="P91" s="4" t="n">
         <v>0</v>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.77</v>
+        <v>58.78</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>4.91</v>
@@ -10315,7 +10315,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>25.98</v>
+        <v>25.99</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>100</v>
@@ -10335,7 +10335,7 @@
         <v>4.91</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>25.98</v>
+        <v>25.99</v>
       </c>
       <c r="P93" s="4" t="n">
         <v>2.03</v>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>50.76</v>
+        <v>50.77</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>100</v>
@@ -10431,13 +10431,13 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.36</v>
+        <v>43.37</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>50.76</v>
+        <v>50.77</v>
       </c>
       <c r="P94" s="4" t="n">
         <v>2.66</v>
@@ -10539,7 +10539,7 @@
         <v>4.91</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>76.25</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>62.5</v>
+        <v>62.51</v>
       </c>
       <c r="AC97" s="4" t="n">
-        <v>37.5</v>
+        <v>37.49</v>
       </c>
       <c r="AD97" s="4" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>30.83</v>
+        <v>30.84</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -10943,7 +10943,7 @@
         <v>4.91</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>30.83</v>
+        <v>30.84</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.64</v>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>25.93</v>
+        <v>25.94</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>100</v>
@@ -11045,7 +11045,7 @@
         <v>4.91</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>25.93</v>
+        <v>25.94</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1.69</v>
@@ -11178,10 +11178,10 @@
         <v>0</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>81.56999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="AC101" s="4" t="n">
-        <v>18.43</v>
+        <v>18.42</v>
       </c>
       <c r="AD101" s="4" t="n">
         <v>0</v>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>58.58</v>
+        <v>58.59</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11243,13 +11243,13 @@
         </is>
       </c>
       <c r="M102" s="4" t="n">
-        <v>43.45</v>
+        <v>43.46</v>
       </c>
       <c r="N102" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>58.58</v>
+        <v>58.59</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>1.93</v>
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>19.96</v>
+        <v>19.97</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>99.8</v>
@@ -11351,7 +11351,7 @@
         <v>4.91</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>19.96</v>
+        <v>19.97</v>
       </c>
       <c r="P103" s="4" t="n">
         <v>1.39</v>
@@ -11433,7 +11433,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>39.08</v>
+        <v>39.09</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
@@ -11447,13 +11447,13 @@
         </is>
       </c>
       <c r="M104" s="4" t="n">
-        <v>21.91</v>
+        <v>21.92</v>
       </c>
       <c r="N104" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>39.08</v>
+        <v>39.09</v>
       </c>
       <c r="P104" s="4" t="n">
         <v>1.73</v>
@@ -11555,7 +11555,7 @@
         <v>4.91</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>22.17</v>
+        <v>22.18</v>
       </c>
       <c r="P105" s="4" t="n">
         <v>1.61</v>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>11.43</v>
+        <v>11.44</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>98.7</v>
@@ -11647,13 +11647,13 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.53</v>
+        <v>5.54</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>11.43</v>
+        <v>11.44</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>0.13</v>
@@ -11786,10 +11786,10 @@
         <v>0</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>60.81</v>
+        <v>60.82</v>
       </c>
       <c r="AC107" s="4" t="n">
-        <v>39.19</v>
+        <v>39.18</v>
       </c>
       <c r="AD107" s="4" t="n">
         <v>0</v>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>25.9</v>
+        <v>25.91</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>100</v>
@@ -11851,13 +11851,13 @@
         </is>
       </c>
       <c r="M108" s="4" t="n">
-        <v>20.69</v>
+        <v>20.7</v>
       </c>
       <c r="N108" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>25.9</v>
+        <v>25.91</v>
       </c>
       <c r="P108" s="4" t="n">
         <v>0</v>
@@ -11939,7 +11939,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27.13</v>
+        <v>27.14</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -11953,13 +11953,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.34</v>
+        <v>21.35</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>27.13</v>
+        <v>27.14</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>39.38</v>
+        <v>39.39</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>100</v>
@@ -12061,7 +12061,7 @@
         <v>4.91</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>39.38</v>
+        <v>39.39</v>
       </c>
       <c r="P110" s="4" t="n">
         <v>1.58</v>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>36.39</v>
+        <v>36.4</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>100</v>
@@ -12981,13 +12981,13 @@
         </is>
       </c>
       <c r="M119" s="4" t="n">
-        <v>25.08</v>
+        <v>25.09</v>
       </c>
       <c r="N119" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O119" s="4" t="n">
-        <v>36.39</v>
+        <v>36.4</v>
       </c>
       <c r="P119" s="4" t="n">
         <v>2.93</v>
@@ -13069,7 +13069,7 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>26.87</v>
+        <v>26.88</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>100</v>
@@ -13083,13 +13083,13 @@
         </is>
       </c>
       <c r="M120" s="4" t="n">
-        <v>9.02</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="N120" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>26.87</v>
+        <v>26.88</v>
       </c>
       <c r="P120" s="4" t="n">
         <v>1.43</v>
@@ -13120,10 +13120,10 @@
         <v>0</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>63.43</v>
+        <v>63.44</v>
       </c>
       <c r="AC120" s="4" t="n">
-        <v>36.57</v>
+        <v>36.56</v>
       </c>
       <c r="AD120" s="4" t="n">
         <v>0</v>
@@ -13171,7 +13171,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>27.91</v>
+        <v>27.92</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>100</v>
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="M121" s="4" t="n">
-        <v>16.15</v>
+        <v>16.16</v>
       </c>
       <c r="N121" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O121" s="4" t="n">
-        <v>27.91</v>
+        <v>27.92</v>
       </c>
       <c r="P121" s="4" t="n">
         <v>2.19</v>
@@ -13222,10 +13222,10 @@
         <v>0</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>63.95</v>
+        <v>63.96</v>
       </c>
       <c r="AC121" s="4" t="n">
-        <v>36.05</v>
+        <v>36.04</v>
       </c>
       <c r="AD121" s="4" t="n">
         <v>0</v>
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>34.41</v>
+        <v>34.42</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>100</v>
@@ -13287,13 +13287,13 @@
         </is>
       </c>
       <c r="M122" s="4" t="n">
-        <v>26.06</v>
+        <v>26.07</v>
       </c>
       <c r="N122" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>34.41</v>
+        <v>34.42</v>
       </c>
       <c r="P122" s="4" t="n">
         <v>2.06</v>
@@ -13324,10 +13324,10 @@
         <v>0</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>67.2</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="AC122" s="4" t="n">
-        <v>32.8</v>
+        <v>32.79</v>
       </c>
       <c r="AD122" s="4" t="n">
         <v>0</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>14.82</v>
+        <v>14.83</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>99.3</v>
@@ -13389,13 +13389,13 @@
         </is>
       </c>
       <c r="M123" s="4" t="n">
-        <v>7.3</v>
+        <v>7.31</v>
       </c>
       <c r="N123" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O123" s="4" t="n">
-        <v>14.82</v>
+        <v>14.83</v>
       </c>
       <c r="P123" s="4" t="n">
         <v>1.9</v>
@@ -13426,10 +13426,10 @@
         <v>0</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>57.41</v>
+        <v>57.42</v>
       </c>
       <c r="AC123" s="4" t="n">
-        <v>42.59</v>
+        <v>42.58</v>
       </c>
       <c r="AD123" s="4" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>27</v>
+        <v>30.39</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>100</v>
@@ -13497,10 +13497,10 @@
         <v>4.91</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>27</v>
+        <v>30.39</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q124" s="4" t="n">
         <v>4.39</v>
@@ -13515,10 +13515,10 @@
       </c>
       <c r="V124" s="4" t="n"/>
       <c r="W124" s="5" t="n">
-        <v>0</v>
+        <v>4659086</v>
       </c>
       <c r="X124" s="5" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" s="4" t="n">
@@ -13528,10 +13528,10 @@
         <v>0</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>63.5</v>
+        <v>65.2</v>
       </c>
       <c r="AC124" s="4" t="n">
-        <v>36.5</v>
+        <v>34.8</v>
       </c>
       <c r="AD124" s="4" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="M125" s="4" t="n">
-        <v>-33.82</v>
+        <v>-33.83</v>
       </c>
       <c r="N125" s="4" t="n">
         <v>4.91</v>
@@ -13677,7 +13677,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>-11.34</v>
+        <v>-11.33</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>1.3</v>
@@ -13697,10 +13697,10 @@
         <v>4.91</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>-11.34</v>
+        <v>-11.33</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>-2.33</v>
+        <v>-2.31</v>
       </c>
       <c r="Q126" s="4" t="n">
         <v>0</v>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="V126" s="4" t="n"/>
       <c r="W126" s="5" t="n">
-        <v>431261</v>
+        <v>440861</v>
       </c>
       <c r="X126" s="5" t="n">
         <v>10654949</v>
@@ -13793,7 +13793,7 @@
         </is>
       </c>
       <c r="M127" s="4" t="n">
-        <v>-16.5</v>
+        <v>-16.51</v>
       </c>
       <c r="N127" s="4" t="n">
         <v>4.91</v>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="M128" s="4" t="n">
-        <v>-7.89</v>
+        <v>-7.9</v>
       </c>
       <c r="N128" s="4" t="n">
         <v>4.91</v>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M129" s="4" t="n">
-        <v>-17.7</v>
+        <v>-17.71</v>
       </c>
       <c r="N129" s="4" t="n">
         <v>4.91</v>
@@ -14085,7 +14085,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>-22.78</v>
+        <v>-22.79</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>0.1</v>
@@ -14105,7 +14105,7 @@
         <v>4.91</v>
       </c>
       <c r="O130" s="4" t="n">
-        <v>-22.78</v>
+        <v>-22.79</v>
       </c>
       <c r="P130" s="4" t="n">
         <v>0</v>
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>-4.45</v>
+        <v>-4.47</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>21.1</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>4.9</v>
@@ -14315,7 +14315,7 @@
         <v>4.91</v>
       </c>
       <c r="O132" s="4" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="P132" s="4" t="n">
         <v>-0.65</v>
@@ -14400,10 +14400,10 @@
         <v>2.7</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>37.81</v>
+        <v>37.8</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>100</v>
@@ -14519,7 +14519,7 @@
         <v>4.91</v>
       </c>
       <c r="O134" s="4" t="n">
-        <v>37.81</v>
+        <v>37.8</v>
       </c>
       <c r="P134" s="4" t="n">
         <v>0</v>
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="M139" s="4" t="n">
-        <v>-14.62</v>
+        <v>-14.63</v>
       </c>
       <c r="N139" s="4" t="n">
         <v>4.91</v>
@@ -15160,10 +15160,10 @@
         <v>0</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>47.45</v>
+        <v>47.44</v>
       </c>
       <c r="AC140" s="4" t="n">
-        <v>52.55</v>
+        <v>52.56</v>
       </c>
       <c r="AD140" s="4" t="n">
         <v>0</v>
@@ -15662,10 +15662,10 @@
         <v>0</v>
       </c>
       <c r="AB145" s="4" t="n">
-        <v>43.45</v>
+        <v>43.44</v>
       </c>
       <c r="AC145" s="4" t="n">
-        <v>56.55</v>
+        <v>56.56</v>
       </c>
       <c r="AD145" s="4" t="n">
         <v>0</v>
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>66.2</v>
@@ -15729,7 +15729,7 @@
         <v>4.91</v>
       </c>
       <c r="O146" s="4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P146" s="4" t="n">
         <v>-0.76</v>
@@ -15909,7 +15909,7 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>55.69</v>
+        <v>55.6</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>100</v>
@@ -15923,16 +15923,16 @@
         </is>
       </c>
       <c r="M148" s="4" t="n">
-        <v>47.69</v>
+        <v>47.68</v>
       </c>
       <c r="N148" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O148" s="4" t="n">
-        <v>55.69</v>
+        <v>55.6</v>
       </c>
       <c r="P148" s="4" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Q148" s="4" t="n">
         <v>0</v>
@@ -15960,10 +15960,10 @@
         <v>0</v>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>77.84</v>
+        <v>77.8</v>
       </c>
       <c r="AC148" s="4" t="n">
-        <v>22.16</v>
+        <v>22.2</v>
       </c>
       <c r="AD148" s="4" t="n">
         <v>0</v>
@@ -16011,7 +16011,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>6.78</v>
+        <v>6.77</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>86.8</v>
@@ -16025,7 +16025,7 @@
         </is>
       </c>
       <c r="M149" s="4" t="n">
-        <v>-2.03</v>
+        <v>-2.04</v>
       </c>
       <c r="N149" s="4" t="n">
         <v>4.91</v>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="M151" s="4" t="n">
-        <v>-6.61</v>
+        <v>-6.62</v>
       </c>
       <c r="N151" s="4" t="n">
         <v>4.91</v>
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>-8.74</v>
+        <v>-8.75</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>7.4</v>
@@ -16447,13 +16447,13 @@
         </is>
       </c>
       <c r="M153" s="4" t="n">
-        <v>-11.44</v>
+        <v>-11.45</v>
       </c>
       <c r="N153" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>-8.74</v>
+        <v>-8.75</v>
       </c>
       <c r="P153" s="4" t="n">
         <v>-1.91</v>
@@ -16535,7 +16535,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>24.11</v>
+        <v>24.1</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>99.90000000000001</v>
@@ -16549,13 +16549,13 @@
         </is>
       </c>
       <c r="M154" s="4" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="N154" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>24.11</v>
+        <v>24.1</v>
       </c>
       <c r="P154" s="4" t="n">
         <v>1.36</v>
@@ -16637,7 +16637,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>-29.3</v>
+        <v>-29.31</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>0</v>
@@ -16657,7 +16657,7 @@
         <v>4.91</v>
       </c>
       <c r="O155" s="4" t="n">
-        <v>-29.3</v>
+        <v>-29.31</v>
       </c>
       <c r="P155" s="4" t="n">
         <v>-1.75</v>
@@ -16739,7 +16739,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>65.20999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>100</v>
@@ -16759,7 +16759,7 @@
         <v>4.91</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>65.20999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="P156" s="4" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>83.66</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>100</v>
@@ -16855,13 +16855,13 @@
         </is>
       </c>
       <c r="M157" s="4" t="n">
-        <v>76.81999999999999</v>
+        <v>76.81</v>
       </c>
       <c r="N157" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O157" s="4" t="n">
-        <v>83.66</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="P157" s="4" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>62.96</v>
+        <v>62.95</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>100</v>
@@ -16963,7 +16963,7 @@
         <v>4.91</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>62.96</v>
+        <v>62.95</v>
       </c>
       <c r="P158" s="4" t="n">
         <v>2.07</v>
@@ -17096,10 +17096,10 @@
         <v>0</v>
       </c>
       <c r="AB159" s="4" t="n">
-        <v>39.97</v>
+        <v>39.96</v>
       </c>
       <c r="AC159" s="4" t="n">
-        <v>60.03</v>
+        <v>60.04</v>
       </c>
       <c r="AD159" s="4" t="n">
         <v>0</v>
@@ -17147,7 +17147,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-29.92</v>
+        <v>-29.93</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>0</v>
@@ -17161,13 +17161,13 @@
         </is>
       </c>
       <c r="M160" s="4" t="n">
-        <v>-26.16</v>
+        <v>-26.17</v>
       </c>
       <c r="N160" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O160" s="4" t="n">
-        <v>-29.92</v>
+        <v>-29.93</v>
       </c>
       <c r="P160" s="4" t="n">
         <v>-2.36</v>
@@ -17263,7 +17263,7 @@
         </is>
       </c>
       <c r="M161" s="4" t="n">
-        <v>-30.48</v>
+        <v>-30.49</v>
       </c>
       <c r="N161" s="4" t="n">
         <v>4.91</v>
@@ -17361,7 +17361,7 @@
         </is>
       </c>
       <c r="M162" s="4" t="n">
-        <v>-17.42</v>
+        <v>-17.43</v>
       </c>
       <c r="N162" s="4" t="n">
         <v>4.91</v>
@@ -17398,10 +17398,10 @@
         <v>0</v>
       </c>
       <c r="AB162" s="4" t="n">
-        <v>41.81</v>
+        <v>41.8</v>
       </c>
       <c r="AC162" s="4" t="n">
-        <v>58.19</v>
+        <v>58.2</v>
       </c>
       <c r="AD162" s="4" t="n">
         <v>0</v>
@@ -17445,7 +17445,7 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>-17.48</v>
+        <v>-17.49</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>0.4</v>
@@ -17459,13 +17459,13 @@
         </is>
       </c>
       <c r="M163" s="4" t="n">
-        <v>-19.85</v>
+        <v>-19.86</v>
       </c>
       <c r="N163" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O163" s="4" t="n">
-        <v>-17.48</v>
+        <v>-17.49</v>
       </c>
       <c r="P163" s="4" t="n">
         <v>-2.21</v>
@@ -17496,10 +17496,10 @@
         <v>0</v>
       </c>
       <c r="AB163" s="4" t="n">
-        <v>41.26</v>
+        <v>41.25</v>
       </c>
       <c r="AC163" s="4" t="n">
-        <v>58.74</v>
+        <v>58.75</v>
       </c>
       <c r="AD163" s="4" t="n">
         <v>0</v>
@@ -17547,7 +17547,7 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-11.82</v>
+        <v>-11.83</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>1.2</v>
@@ -17567,7 +17567,7 @@
         <v>4.91</v>
       </c>
       <c r="O164" s="4" t="n">
-        <v>-11.82</v>
+        <v>-11.83</v>
       </c>
       <c r="P164" s="4" t="n">
         <v>-1.96</v>
@@ -17645,7 +17645,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>50.75</v>
+        <v>50.74</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>100</v>
@@ -17659,13 +17659,13 @@
         </is>
       </c>
       <c r="M165" s="4" t="n">
-        <v>45.57</v>
+        <v>45.56</v>
       </c>
       <c r="N165" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>50.75</v>
+        <v>50.74</v>
       </c>
       <c r="P165" s="4" t="n">
         <v>0</v>
@@ -17696,10 +17696,10 @@
         <v>0</v>
       </c>
       <c r="AB165" s="4" t="n">
-        <v>75.38</v>
+        <v>75.37</v>
       </c>
       <c r="AC165" s="4" t="n">
-        <v>24.62</v>
+        <v>24.63</v>
       </c>
       <c r="AD165" s="4" t="n">
         <v>0</v>
@@ -17747,7 +17747,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-21.87</v>
+        <v>-21.88</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>0.1</v>
@@ -17767,7 +17767,7 @@
         <v>4.91</v>
       </c>
       <c r="O166" s="4" t="n">
-        <v>-21.87</v>
+        <v>-21.88</v>
       </c>
       <c r="P166" s="4" t="n">
         <v>0.62</v>
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-24.38</v>
+        <v>-24.39</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>4.91</v>
@@ -18587,7 +18587,7 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-28.92</v>
+        <v>-28.93</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>4.91</v>
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>32.81</v>
+        <v>32.7</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>100</v>
@@ -21939,10 +21939,10 @@
         <v>4.91</v>
       </c>
       <c r="O207" s="4" t="n">
-        <v>32.81</v>
+        <v>32.7</v>
       </c>
       <c r="P207" s="4" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="Q207" s="4" t="n">
         <v>5.67</v>
@@ -21960,7 +21960,7 @@
         <v>1633684</v>
       </c>
       <c r="X207" s="5" t="n">
-        <v>25659</v>
+        <v>38069</v>
       </c>
       <c r="Y207" t="inlineStr"/>
       <c r="Z207" s="4" t="n">
@@ -21970,10 +21970,10 @@
         <v>0</v>
       </c>
       <c r="AB207" s="4" t="n">
-        <v>66.41</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="AC207" s="4" t="n">
-        <v>33.59</v>
+        <v>33.65</v>
       </c>
       <c r="AD207" s="4" t="n">
         <v>0</v>
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-7.67</v>
+        <v>-7.7</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>10.4</v>
@@ -22274,10 +22274,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.16</v>
+        <v>46.15</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.84</v>
+        <v>53.85</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -22933,7 +22933,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>23.71</v>
+        <v>23.72</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>99.90000000000001</v>
@@ -22947,13 +22947,13 @@
         </is>
       </c>
       <c r="M217" s="4" t="n">
-        <v>17.25</v>
+        <v>17.26</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>23.71</v>
+        <v>23.72</v>
       </c>
       <c r="P217" s="4" t="n">
         <v>0</v>
@@ -22984,10 +22984,10 @@
         <v>0</v>
       </c>
       <c r="AB217" s="4" t="n">
-        <v>61.85</v>
+        <v>61.86</v>
       </c>
       <c r="AC217" s="4" t="n">
-        <v>38.15</v>
+        <v>38.14</v>
       </c>
       <c r="AD217" s="4" t="n">
         <v>0</v>
@@ -23035,7 +23035,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>33.32</v>
+        <v>33.33</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -23049,13 +23049,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>27.2</v>
+        <v>27.21</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>33.32</v>
+        <v>33.33</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -23086,10 +23086,10 @@
         <v>0</v>
       </c>
       <c r="AB218" s="4" t="n">
-        <v>66.66</v>
+        <v>66.67</v>
       </c>
       <c r="AC218" s="4" t="n">
-        <v>33.34</v>
+        <v>33.33</v>
       </c>
       <c r="AD218" s="4" t="n">
         <v>0</v>
@@ -23137,7 +23137,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>31.88</v>
+        <v>31.89</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>100</v>
@@ -23151,13 +23151,13 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>22.7</v>
+        <v>22.71</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>31.88</v>
+        <v>31.89</v>
       </c>
       <c r="P219" s="4" t="n">
         <v>2.52</v>
@@ -23239,7 +23239,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>29.38</v>
+        <v>29.39</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>100</v>
@@ -23253,13 +23253,13 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.52</v>
+        <v>23.53</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O220" s="4" t="n">
-        <v>29.38</v>
+        <v>29.39</v>
       </c>
       <c r="P220" s="4" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>0</v>
       </c>
       <c r="AB220" s="4" t="n">
-        <v>64.69</v>
+        <v>64.7</v>
       </c>
       <c r="AC220" s="4" t="n">
-        <v>35.31</v>
+        <v>35.3</v>
       </c>
       <c r="AD220" s="4" t="n">
         <v>0</v>
@@ -23341,7 +23341,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>55</v>
+        <v>55.01</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>100</v>
@@ -23355,13 +23355,13 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>48.88</v>
+        <v>48.89</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O221" s="4" t="n">
-        <v>55</v>
+        <v>55.01</v>
       </c>
       <c r="P221" s="4" t="n">
         <v>0</v>
@@ -23439,7 +23439,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>28.14</v>
+        <v>28.15</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>100</v>
@@ -23453,13 +23453,13 @@
         </is>
       </c>
       <c r="M222" s="4" t="n">
-        <v>23.73</v>
+        <v>23.74</v>
       </c>
       <c r="N222" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O222" s="4" t="n">
-        <v>28.14</v>
+        <v>28.15</v>
       </c>
       <c r="P222" s="4" t="n">
         <v>0</v>
@@ -23541,7 +23541,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>75.79000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -23555,13 +23555,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>68.89</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>75.79000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -23643,7 +23643,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>45.11</v>
+        <v>45.12</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>100</v>
@@ -23657,13 +23657,13 @@
         </is>
       </c>
       <c r="M224" s="4" t="n">
-        <v>30.3</v>
+        <v>30.31</v>
       </c>
       <c r="N224" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O224" s="4" t="n">
-        <v>45.11</v>
+        <v>45.12</v>
       </c>
       <c r="P224" s="4" t="n">
         <v>0</v>
@@ -23694,10 +23694,10 @@
         <v>0</v>
       </c>
       <c r="AB224" s="4" t="n">
-        <v>72.55</v>
+        <v>72.56</v>
       </c>
       <c r="AC224" s="4" t="n">
-        <v>27.45</v>
+        <v>27.44</v>
       </c>
       <c r="AD224" s="4" t="n">
         <v>0</v>
@@ -23745,7 +23745,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.13</v>
+        <v>22.14</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23759,13 +23759,13 @@
         </is>
       </c>
       <c r="M225" s="4" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="N225" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.13</v>
+        <v>22.14</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.51</v>
@@ -23796,10 +23796,10 @@
         <v>0</v>
       </c>
       <c r="AB225" s="4" t="n">
-        <v>61.06</v>
+        <v>61.07</v>
       </c>
       <c r="AC225" s="4" t="n">
-        <v>38.94</v>
+        <v>38.93</v>
       </c>
       <c r="AD225" s="4" t="n">
         <v>0</v>
@@ -24655,7 +24655,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.2</v>
+        <v>30.56</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24669,13 +24669,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>22.28</v>
+        <v>22.27</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.02</v>
+        <v>31.01</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24756,10 +24756,10 @@
         <v>-3.88</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>38.5</v>
+        <v>37.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>61.5</v>
+        <v>62.4</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24767,13 +24767,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.43</v>
+        <v>-5.44</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24912,10 +24912,10 @@
         <v>0</v>
       </c>
       <c r="AB236" s="4" t="n">
-        <v>43.48</v>
+        <v>43.49</v>
       </c>
       <c r="AC236" s="4" t="n">
-        <v>56.52</v>
+        <v>56.51</v>
       </c>
       <c r="AD236" s="4" t="n">
         <v>0</v>
@@ -24963,7 +24963,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>-27.98</v>
+        <v>-27.97</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>0</v>
@@ -24983,10 +24983,10 @@
         <v>4.91</v>
       </c>
       <c r="O237" s="4" t="n">
-        <v>-27.98</v>
+        <v>-27.97</v>
       </c>
       <c r="P237" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.9</v>
       </c>
       <c r="Q237" s="4" t="n">
         <v>-4.17</v>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="V237" s="4" t="n"/>
       <c r="W237" s="5" t="n">
-        <v>83911</v>
+        <v>84011</v>
       </c>
       <c r="X237" s="5" t="n">
         <v>1648987</v>
@@ -25014,10 +25014,10 @@
         <v>0</v>
       </c>
       <c r="AB237" s="4" t="n">
-        <v>36.01</v>
+        <v>36.02</v>
       </c>
       <c r="AC237" s="4" t="n">
-        <v>63.99</v>
+        <v>63.98</v>
       </c>
       <c r="AD237" s="4" t="n">
         <v>0</v>
@@ -25065,7 +25065,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>20.45</v>
+        <v>20.46</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25079,13 +25079,13 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>11.69</v>
+        <v>11.7</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>20.45</v>
+        <v>20.46</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-1.47</v>
+        <v>-1.46</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>4.91</v>
@@ -25275,7 +25275,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-25.78</v>
+        <v>-25.77</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0</v>
@@ -25295,7 +25295,7 @@
         <v>4.91</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-25.78</v>
+        <v>-25.77</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.14</v>
@@ -25377,7 +25377,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>38.4</v>
+        <v>38.41</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -25391,13 +25391,13 @@
         </is>
       </c>
       <c r="M241" s="4" t="n">
-        <v>28.51</v>
+        <v>28.52</v>
       </c>
       <c r="N241" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>38.4</v>
+        <v>38.41</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -25479,13 +25479,13 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>4.91</v>
@@ -25502,7 +25502,7 @@
         <v>2.84</v>
       </c>
       <c r="P242" s="4" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="Q242" s="4" t="n">
         <v>-3.8</v>
@@ -25536,10 +25536,10 @@
         <v>0</v>
       </c>
       <c r="AB242" s="4" t="n">
-        <v>50.32</v>
+        <v>50.33</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.68</v>
+        <v>49.67</v>
       </c>
       <c r="AD242" s="4" t="n">
         <v>0</v>
@@ -25587,7 +25587,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>18.81</v>
+        <v>18.82</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>99.7</v>
@@ -25601,13 +25601,13 @@
         </is>
       </c>
       <c r="M243" s="4" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="N243" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>18.81</v>
+        <v>18.82</v>
       </c>
       <c r="P243" s="4" t="n">
         <v>1.52</v>
@@ -25638,10 +25638,10 @@
         <v>0</v>
       </c>
       <c r="AB243" s="4" t="n">
-        <v>59.4</v>
+        <v>59.41</v>
       </c>
       <c r="AC243" s="4" t="n">
-        <v>40.6</v>
+        <v>40.59</v>
       </c>
       <c r="AD243" s="4" t="n">
         <v>0</v>
@@ -25689,7 +25689,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-32.76</v>
+        <v>-32.75</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -25709,7 +25709,7 @@
         <v>4.91</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-32.76</v>
+        <v>-32.75</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -25787,13 +25787,13 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="J245" s="4" t="n">
-        <v>69.8</v>
+        <v>70</v>
       </c>
       <c r="K245" s="4" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -25801,16 +25801,16 @@
         </is>
       </c>
       <c r="M245" s="4" t="n">
-        <v>-1.41</v>
+        <v>-1.4</v>
       </c>
       <c r="N245" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O245" s="4" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="P245" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="Q245" s="4" t="n">
         <v>0</v>
@@ -25844,10 +25844,10 @@
         <v>0</v>
       </c>
       <c r="AB245" s="4" t="n">
-        <v>51.03</v>
+        <v>51.05</v>
       </c>
       <c r="AC245" s="4" t="n">
-        <v>48.97</v>
+        <v>48.95</v>
       </c>
       <c r="AD245" s="4" t="n">
         <v>0</v>
@@ -25891,7 +25891,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>27.5</v>
+        <v>27.52</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>100</v>
@@ -25905,16 +25905,16 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>21.13</v>
+        <v>21.14</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O246" s="4" t="n">
-        <v>27.5</v>
+        <v>27.52</v>
       </c>
       <c r="P246" s="4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q246" s="4" t="n">
         <v>0</v>
@@ -25942,10 +25942,10 @@
         <v>0</v>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>63.75</v>
+        <v>63.76</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>36.25</v>
+        <v>36.24</v>
       </c>
       <c r="AD246" s="4" t="n">
         <v>0</v>
@@ -26044,10 +26044,10 @@
         <v>0</v>
       </c>
       <c r="AB247" s="4" t="n">
-        <v>78.03</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="AC247" s="4" t="n">
-        <v>21.97</v>
+        <v>21.96</v>
       </c>
       <c r="AD247" s="4" t="n">
         <v>0</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>58.77</v>
+        <v>58.78</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -26109,13 +26109,13 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>48.67</v>
+        <v>48.68</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>58.77</v>
+        <v>58.78</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
@@ -26197,13 +26197,13 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>-6.32</v>
+        <v>-6.33</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="K249" s="4" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>4.91</v>
       </c>
       <c r="O249" s="4" t="n">
-        <v>-6.62</v>
+        <v>-6.63</v>
       </c>
       <c r="P249" s="4" t="n">
         <v>-0.02</v>
@@ -26301,7 +26301,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>13.23</v>
+        <v>13.22</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>99.09999999999999</v>
@@ -26321,7 +26321,7 @@
         <v>4.91</v>
       </c>
       <c r="O250" s="4" t="n">
-        <v>13.23</v>
+        <v>13.22</v>
       </c>
       <c r="P250" s="4" t="n">
         <v>0.47</v>
@@ -26417,7 +26417,7 @@
         </is>
       </c>
       <c r="M251" s="4" t="n">
-        <v>23.77</v>
+        <v>23.76</v>
       </c>
       <c r="N251" s="4" t="n">
         <v>4.91</v>
@@ -26454,10 +26454,10 @@
         <v>0</v>
       </c>
       <c r="AB251" s="4" t="n">
-        <v>64.81999999999999</v>
+        <v>64.81</v>
       </c>
       <c r="AC251" s="4" t="n">
-        <v>35.18</v>
+        <v>35.19</v>
       </c>
       <c r="AD251" s="4" t="n">
         <v>0</v>
@@ -26556,10 +26556,10 @@
         <v>0</v>
       </c>
       <c r="AB252" s="4" t="n">
-        <v>73.70999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="AC252" s="4" t="n">
-        <v>26.29</v>
+        <v>26.3</v>
       </c>
       <c r="AD252" s="4" t="n">
         <v>0</v>
@@ -26709,7 +26709,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-14.93</v>
+        <v>-14.94</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>0.7</v>
@@ -26723,13 +26723,13 @@
         </is>
       </c>
       <c r="M254" s="4" t="n">
-        <v>-17.32</v>
+        <v>-17.33</v>
       </c>
       <c r="N254" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-14.93</v>
+        <v>-14.94</v>
       </c>
       <c r="P254" s="4" t="n">
         <v>0</v>
@@ -26825,7 +26825,7 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-33.67</v>
+        <v>-33.68</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>4.91</v>
@@ -26862,10 +26862,10 @@
         <v>0</v>
       </c>
       <c r="AB255" s="4" t="n">
-        <v>34.37</v>
+        <v>34.36</v>
       </c>
       <c r="AC255" s="4" t="n">
-        <v>65.63</v>
+        <v>65.64</v>
       </c>
       <c r="AD255" s="4" t="n">
         <v>0</v>
@@ -26927,7 +26927,7 @@
         </is>
       </c>
       <c r="M256" s="4" t="n">
-        <v>-11.13</v>
+        <v>-11.14</v>
       </c>
       <c r="N256" s="4" t="n">
         <v>4.91</v>
@@ -26964,10 +26964,10 @@
         <v>0</v>
       </c>
       <c r="AB256" s="4" t="n">
-        <v>45.53</v>
+        <v>45.52</v>
       </c>
       <c r="AC256" s="4" t="n">
-        <v>54.47</v>
+        <v>54.48</v>
       </c>
       <c r="AD256" s="4" t="n">
         <v>0</v>
@@ -27117,13 +27117,13 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.72</v>
+        <v>-10.74</v>
       </c>
       <c r="J258" s="4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K258" s="4" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -27174,10 +27174,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.64</v>
+        <v>44.63</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.36</v>
+        <v>55.37</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -27327,7 +27327,7 @@
         </is>
       </c>
       <c r="I260" s="4" t="n">
-        <v>-21.36</v>
+        <v>-21.33</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>0.2</v>
@@ -27347,10 +27347,10 @@
         <v>4.91</v>
       </c>
       <c r="O260" s="4" t="n">
-        <v>-21.36</v>
+        <v>-21.33</v>
       </c>
       <c r="P260" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.17</v>
       </c>
       <c r="Q260" s="4" t="n">
         <v>-3.26</v>
@@ -27365,7 +27365,7 @@
       </c>
       <c r="V260" s="4" t="n"/>
       <c r="W260" s="5" t="n">
-        <v>236200</v>
+        <v>250118</v>
       </c>
       <c r="X260" s="5" t="n">
         <v>1370433</v>
@@ -27378,10 +27378,10 @@
         <v>0</v>
       </c>
       <c r="AB260" s="4" t="n">
-        <v>39.32</v>
+        <v>39.34</v>
       </c>
       <c r="AC260" s="4" t="n">
-        <v>60.68</v>
+        <v>60.66</v>
       </c>
       <c r="AD260" s="4" t="n">
         <v>0</v>
@@ -28237,13 +28237,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.12</v>
+        <v>-6.16</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28251,16 +28251,16 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-10.96</v>
+        <v>-11</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-7.18</v>
+        <v>-7.22</v>
       </c>
       <c r="P269" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="Q269" s="4" t="n">
         <v>0</v>
@@ -28294,10 +28294,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.94</v>
+        <v>46.92</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.06</v>
+        <v>53.08</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-32.91</v>
+        <v>-32.96</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28359,13 +28359,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-29.92</v>
+        <v>-29.97</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-32.91</v>
+        <v>-32.96</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28396,10 +28396,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.54</v>
+        <v>33.52</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.45999999999999</v>
+        <v>66.48</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28447,7 +28447,7 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="J271" s="4" t="n">
         <v>71.09999999999999</v>
@@ -29893,7 +29893,7 @@
         </is>
       </c>
       <c r="I285" s="4" t="n">
-        <v>-34.54</v>
+        <v>-36.04</v>
       </c>
       <c r="J285" s="4" t="n">
         <v>0</v>
@@ -29913,10 +29913,10 @@
         <v>4.91</v>
       </c>
       <c r="O285" s="4" t="n">
-        <v>-34.54</v>
+        <v>-36.04</v>
       </c>
       <c r="P285" s="4" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="Q285" s="4" t="n">
         <v>-1.67</v>
@@ -29931,10 +29931,10 @@
       </c>
       <c r="V285" s="4" t="n"/>
       <c r="W285" s="5" t="n">
-        <v>0</v>
+        <v>190064</v>
       </c>
       <c r="X285" s="5" t="n">
-        <v>0</v>
+        <v>1730663</v>
       </c>
       <c r="Y285" t="inlineStr"/>
       <c r="Z285" s="4" t="n">
@@ -29944,10 +29944,10 @@
         <v>0</v>
       </c>
       <c r="AB285" s="4" t="n">
-        <v>32.73</v>
+        <v>31.98</v>
       </c>
       <c r="AC285" s="4" t="n">
-        <v>67.27</v>
+        <v>68.02</v>
       </c>
       <c r="AD285" s="4" t="n">
         <v>0</v>
@@ -29995,13 +29995,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.91</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30009,13 +30009,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.970000000000001</v>
+        <v>-9.02</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-10.55</v>
+        <v>-10.6</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30042,7 +30042,7 @@
         <v>592233</v>
       </c>
       <c r="X286" s="5" t="n">
-        <v>2359410</v>
+        <v>2368910</v>
       </c>
       <c r="Y286" t="inlineStr"/>
       <c r="Z286" s="4" t="n">
@@ -30052,10 +30052,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.07</v>
+        <v>45.05</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.93</v>
+        <v>54.95</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30099,7 +30099,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.24</v>
+        <v>12.2</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>98.90000000000001</v>
@@ -30113,13 +30113,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>13.87</v>
+        <v>13.82</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30156,10 +30156,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.12</v>
+        <v>56.1</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.88</v>
+        <v>43.9</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30207,7 +30207,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-53.16</v>
+        <v>-53.15</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30221,16 +30221,16 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.92</v>
+        <v>-49.97</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-53.16</v>
+        <v>-53.15</v>
       </c>
       <c r="P288" s="4" t="n">
-        <v>-2.24</v>
+        <v>-2.18</v>
       </c>
       <c r="Q288" s="4" t="n">
         <v>-5.38</v>
@@ -30245,7 +30245,7 @@
       </c>
       <c r="V288" s="4" t="n"/>
       <c r="W288" s="5" t="n">
-        <v>46356</v>
+        <v>55101</v>
       </c>
       <c r="X288" s="5" t="n">
         <v>1777414</v>
@@ -30258,10 +30258,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.42</v>
+        <v>23.43</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.58</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -31133,7 +31133,7 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="J297" s="4" t="n">
         <v>78.09999999999999</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AB297" s="4" t="n">
-        <v>52.11</v>
+        <v>52.12</v>
       </c>
       <c r="AC297" s="4" t="n">
-        <v>47.89</v>
+        <v>47.88</v>
       </c>
       <c r="AD297" s="4" t="n">
         <v>0</v>
@@ -31849,7 +31849,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>14.41</v>
+        <v>14.43</v>
       </c>
       <c r="J304" s="4" t="n">
         <v>99.3</v>
@@ -31906,10 +31906,10 @@
         <v>0</v>
       </c>
       <c r="AB304" s="4" t="n">
-        <v>57.21</v>
+        <v>57.22</v>
       </c>
       <c r="AC304" s="4" t="n">
-        <v>42.79</v>
+        <v>42.78</v>
       </c>
       <c r="AD304" s="4" t="n">
         <v>0</v>
@@ -32059,7 +32059,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>16.04</v>
+        <v>16.05</v>
       </c>
       <c r="J306" s="4" t="n">
         <v>99.5</v>
@@ -32079,7 +32079,7 @@
         <v>4.91</v>
       </c>
       <c r="O306" s="4" t="n">
-        <v>16.04</v>
+        <v>16.05</v>
       </c>
       <c r="P306" s="4" t="n">
         <v>-0.16</v>
@@ -32157,13 +32157,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-3.42</v>
+        <v>-3.51</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>4.91</v>
       </c>
       <c r="O307" s="4" t="n">
-        <v>-8.77</v>
+        <v>-8.76</v>
       </c>
       <c r="P307" s="4" t="n">
         <v>-1.32</v>
@@ -32214,10 +32214,10 @@
         <v>0</v>
       </c>
       <c r="AB307" s="4" t="n">
-        <v>48.29</v>
+        <v>48.24</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>51.71</v>
+        <v>51.76</v>
       </c>
       <c r="AD307" s="4" t="n">
         <v>0</v>
@@ -32367,7 +32367,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>17.3</v>
+        <v>17.31</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>99.59999999999999</v>
@@ -32387,7 +32387,7 @@
         <v>4.91</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>17.3</v>
+        <v>17.31</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>0.97</v>
@@ -34513,7 +34513,7 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-12.6</v>
+        <v>-12.64</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>1</v>
@@ -34570,10 +34570,10 @@
         <v>0</v>
       </c>
       <c r="AB330" s="4" t="n">
-        <v>43.7</v>
+        <v>43.68</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>56.3</v>
+        <v>56.32</v>
       </c>
       <c r="AD330" s="4" t="n">
         <v>0</v>
@@ -34927,7 +34927,7 @@
         </is>
       </c>
       <c r="I334" s="4" t="n">
-        <v>27.87</v>
+        <v>27.88</v>
       </c>
       <c r="J334" s="4" t="n">
         <v>100</v>
@@ -34947,10 +34947,10 @@
         <v>4.91</v>
       </c>
       <c r="O334" s="4" t="n">
-        <v>27.87</v>
+        <v>27.88</v>
       </c>
       <c r="P334" s="4" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q334" s="4" t="n">
         <v>1.39</v>
@@ -34978,10 +34978,10 @@
         <v>0</v>
       </c>
       <c r="AB334" s="4" t="n">
-        <v>63.93</v>
+        <v>63.94</v>
       </c>
       <c r="AC334" s="4" t="n">
-        <v>36.07</v>
+        <v>36.06</v>
       </c>
       <c r="AD334" s="4" t="n">
         <v>0</v>
@@ -35131,7 +35131,7 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>11.37</v>
+        <v>11.36</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>98.7</v>
@@ -35145,13 +35145,13 @@
         </is>
       </c>
       <c r="M336" s="4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="N336" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O336" s="4" t="n">
-        <v>11.37</v>
+        <v>11.36</v>
       </c>
       <c r="P336" s="4" t="n">
         <v>0.77</v>
@@ -35182,10 +35182,10 @@
         <v>0</v>
       </c>
       <c r="AB336" s="4" t="n">
-        <v>55.69</v>
+        <v>55.68</v>
       </c>
       <c r="AC336" s="4" t="n">
-        <v>44.31</v>
+        <v>44.32</v>
       </c>
       <c r="AD336" s="4" t="n">
         <v>0</v>
@@ -35335,7 +35335,7 @@
         </is>
       </c>
       <c r="I338" s="4" t="n">
-        <v>52.32</v>
+        <v>52.31</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>100</v>
@@ -35355,7 +35355,7 @@
         <v>4.91</v>
       </c>
       <c r="O338" s="4" t="n">
-        <v>52.32</v>
+        <v>52.31</v>
       </c>
       <c r="P338" s="4" t="n">
         <v>0</v>
@@ -35437,7 +35437,7 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>-38.97</v>
+        <v>-38.98</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>0</v>
@@ -35457,7 +35457,7 @@
         <v>4.91</v>
       </c>
       <c r="O339" s="4" t="n">
-        <v>-38.97</v>
+        <v>-38.98</v>
       </c>
       <c r="P339" s="4" t="n">
         <v>-3.15</v>
@@ -35553,7 +35553,7 @@
         </is>
       </c>
       <c r="M340" s="4" t="n">
-        <v>-19.33</v>
+        <v>-19.34</v>
       </c>
       <c r="N340" s="4" t="n">
         <v>4.91</v>
@@ -35590,10 +35590,10 @@
         <v>0</v>
       </c>
       <c r="AB340" s="4" t="n">
-        <v>38.62</v>
+        <v>38.61</v>
       </c>
       <c r="AC340" s="4" t="n">
-        <v>61.38</v>
+        <v>61.39</v>
       </c>
       <c r="AD340" s="4" t="n">
         <v>0</v>
@@ -35641,7 +35641,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>-28.83</v>
+        <v>-28.84</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>0</v>
@@ -35661,7 +35661,7 @@
         <v>4.91</v>
       </c>
       <c r="O341" s="4" t="n">
-        <v>-28.83</v>
+        <v>-28.84</v>
       </c>
       <c r="P341" s="4" t="n">
         <v>-2.12</v>
@@ -35743,13 +35743,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-6.73</v>
+        <v>-6.75</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         </is>
       </c>
       <c r="M342" s="4" t="n">
-        <v>-7.08</v>
+        <v>-7.09</v>
       </c>
       <c r="N342" s="4" t="n">
         <v>4.91</v>
@@ -35800,10 +35800,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>46.64</v>
+        <v>46.62</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>53.36</v>
+        <v>53.38</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>93.09999999999999</v>
@@ -35967,13 +35967,13 @@
         </is>
       </c>
       <c r="M344" s="4" t="n">
-        <v>-5.68</v>
+        <v>-5.69</v>
       </c>
       <c r="N344" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O344" s="4" t="n">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
       <c r="P344" s="4" t="n">
         <v>0.77</v>
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M345" s="4" t="n">
-        <v>-3.68</v>
+        <v>-3.69</v>
       </c>
       <c r="N345" s="4" t="n">
         <v>4.91</v>
@@ -36163,7 +36163,7 @@
         </is>
       </c>
       <c r="I346" s="4" t="n">
-        <v>70.22</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>100</v>
@@ -36177,13 +36177,13 @@
         </is>
       </c>
       <c r="M346" s="4" t="n">
-        <v>60.37</v>
+        <v>60.36</v>
       </c>
       <c r="N346" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O346" s="4" t="n">
-        <v>70.22</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="P346" s="4" t="n">
         <v>0</v>
@@ -36265,7 +36265,7 @@
         </is>
       </c>
       <c r="I347" s="4" t="n">
-        <v>-26.15</v>
+        <v>-26.16</v>
       </c>
       <c r="J347" s="4" t="n">
         <v>0</v>
@@ -36279,13 +36279,13 @@
         </is>
       </c>
       <c r="M347" s="4" t="n">
-        <v>-26.39</v>
+        <v>-26.4</v>
       </c>
       <c r="N347" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O347" s="4" t="n">
-        <v>-26.15</v>
+        <v>-26.16</v>
       </c>
       <c r="P347" s="4" t="n">
         <v>-1.94</v>
@@ -36316,10 +36316,10 @@
         <v>0</v>
       </c>
       <c r="AB347" s="4" t="n">
-        <v>36.93</v>
+        <v>36.92</v>
       </c>
       <c r="AC347" s="4" t="n">
-        <v>63.07</v>
+        <v>63.08</v>
       </c>
       <c r="AD347" s="4" t="n">
         <v>0</v>
@@ -36367,7 +36367,7 @@
         </is>
       </c>
       <c r="I348" s="4" t="n">
-        <v>18.35</v>
+        <v>18.34</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>99.7</v>
@@ -36381,13 +36381,13 @@
         </is>
       </c>
       <c r="M348" s="4" t="n">
-        <v>7.87</v>
+        <v>7.86</v>
       </c>
       <c r="N348" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O348" s="4" t="n">
-        <v>18.35</v>
+        <v>18.34</v>
       </c>
       <c r="P348" s="4" t="n">
         <v>2.17</v>
@@ -36483,7 +36483,7 @@
         </is>
       </c>
       <c r="M349" s="4" t="n">
-        <v>-15.75</v>
+        <v>-15.76</v>
       </c>
       <c r="N349" s="4" t="n">
         <v>4.91</v>
@@ -36520,10 +36520,10 @@
         <v>0</v>
       </c>
       <c r="AB349" s="4" t="n">
-        <v>39.86</v>
+        <v>39.85</v>
       </c>
       <c r="AC349" s="4" t="n">
-        <v>60.14</v>
+        <v>60.15</v>
       </c>
       <c r="AD349" s="4" t="n">
         <v>0</v>
@@ -37179,7 +37179,7 @@
         </is>
       </c>
       <c r="I356" s="4" t="n">
-        <v>48.94</v>
+        <v>48.95</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>100</v>
@@ -37193,13 +37193,13 @@
         </is>
       </c>
       <c r="M356" s="4" t="n">
-        <v>38.48</v>
+        <v>38.49</v>
       </c>
       <c r="N356" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O356" s="4" t="n">
-        <v>48.94</v>
+        <v>48.95</v>
       </c>
       <c r="P356" s="4" t="n">
         <v>2.08</v>
@@ -37281,7 +37281,7 @@
         </is>
       </c>
       <c r="I357" s="4" t="n">
-        <v>-29.54</v>
+        <v>-29.53</v>
       </c>
       <c r="J357" s="4" t="n">
         <v>0</v>
@@ -37301,7 +37301,7 @@
         <v>4.91</v>
       </c>
       <c r="O357" s="4" t="n">
-        <v>-29.54</v>
+        <v>-29.53</v>
       </c>
       <c r="P357" s="4" t="n">
         <v>-1.49</v>
@@ -37332,10 +37332,10 @@
         <v>0</v>
       </c>
       <c r="AB357" s="4" t="n">
-        <v>35.23</v>
+        <v>35.24</v>
       </c>
       <c r="AC357" s="4" t="n">
-        <v>64.77</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="AD357" s="4" t="n">
         <v>0</v>
@@ -37397,7 +37397,7 @@
         </is>
       </c>
       <c r="M358" s="4" t="n">
-        <v>47.05</v>
+        <v>47.06</v>
       </c>
       <c r="N358" s="4" t="n">
         <v>4.91</v>
@@ -37434,10 +37434,10 @@
         <v>0</v>
       </c>
       <c r="AB358" s="4" t="n">
-        <v>77.31999999999999</v>
+        <v>77.33</v>
       </c>
       <c r="AC358" s="4" t="n">
-        <v>22.68</v>
+        <v>22.67</v>
       </c>
       <c r="AD358" s="4" t="n">
         <v>0</v>
@@ -37536,10 +37536,10 @@
         <v>0</v>
       </c>
       <c r="AB359" s="4" t="n">
-        <v>58.24</v>
+        <v>58.25</v>
       </c>
       <c r="AC359" s="4" t="n">
-        <v>41.76</v>
+        <v>41.75</v>
       </c>
       <c r="AD359" s="4" t="n">
         <v>0</v>
@@ -37587,7 +37587,7 @@
         </is>
       </c>
       <c r="I360" s="4" t="n">
-        <v>16.1</v>
+        <v>16.11</v>
       </c>
       <c r="J360" s="4" t="n">
         <v>99.5</v>
@@ -37601,13 +37601,13 @@
         </is>
       </c>
       <c r="M360" s="4" t="n">
-        <v>7.78</v>
+        <v>7.79</v>
       </c>
       <c r="N360" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O360" s="4" t="n">
-        <v>16.1</v>
+        <v>16.11</v>
       </c>
       <c r="P360" s="4" t="n">
         <v>1.57</v>
@@ -37689,7 +37689,7 @@
         </is>
       </c>
       <c r="I361" s="4" t="n">
-        <v>17.47</v>
+        <v>17.48</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>99.59999999999999</v>
@@ -37703,13 +37703,13 @@
         </is>
       </c>
       <c r="M361" s="4" t="n">
-        <v>11.01</v>
+        <v>11.02</v>
       </c>
       <c r="N361" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O361" s="4" t="n">
-        <v>17.47</v>
+        <v>17.48</v>
       </c>
       <c r="P361" s="4" t="n">
         <v>2.46</v>
@@ -37848,10 +37848,10 @@
         <v>0</v>
       </c>
       <c r="AB362" s="4" t="n">
-        <v>48.81</v>
+        <v>48.82</v>
       </c>
       <c r="AC362" s="4" t="n">
-        <v>51.19</v>
+        <v>51.18</v>
       </c>
       <c r="AD362" s="4" t="n">
         <v>0</v>
@@ -37997,7 +37997,7 @@
         </is>
       </c>
       <c r="I364" s="4" t="n">
-        <v>91.59</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="J364" s="4" t="n">
         <v>100</v>
@@ -38017,7 +38017,7 @@
         <v>4.91</v>
       </c>
       <c r="O364" s="4" t="n">
-        <v>91.59</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P364" s="4" t="n">
         <v>2.85</v>
@@ -38099,7 +38099,7 @@
         </is>
       </c>
       <c r="I365" s="4" t="n">
-        <v>29.1</v>
+        <v>29.11</v>
       </c>
       <c r="J365" s="4" t="n">
         <v>100</v>
@@ -38119,7 +38119,7 @@
         <v>4.91</v>
       </c>
       <c r="O365" s="4" t="n">
-        <v>29.1</v>
+        <v>29.11</v>
       </c>
       <c r="P365" s="4" t="n">
         <v>0</v>
@@ -38201,7 +38201,7 @@
         </is>
       </c>
       <c r="I366" s="4" t="n">
-        <v>41.9</v>
+        <v>41.91</v>
       </c>
       <c r="J366" s="4" t="n">
         <v>100</v>
@@ -38221,7 +38221,7 @@
         <v>4.91</v>
       </c>
       <c r="O366" s="4" t="n">
-        <v>41.9</v>
+        <v>41.91</v>
       </c>
       <c r="P366" s="4" t="n">
         <v>0</v>
@@ -38405,13 +38405,13 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="J368" s="4" t="n">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="K368" s="4" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         </is>
       </c>
       <c r="M368" s="4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="N368" s="4" t="n">
         <v>4.91</v>
@@ -38513,7 +38513,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>64</v>
@@ -38527,13 +38527,13 @@
         </is>
       </c>
       <c r="M369" s="4" t="n">
-        <v>-2.88</v>
+        <v>-2.87</v>
       </c>
       <c r="N369" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O369" s="4" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="P369" s="4" t="n">
         <v>-0.09</v>
@@ -38717,7 +38717,7 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>8.470000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="J371" s="4" t="n">
         <v>91.90000000000001</v>
@@ -39043,7 +39043,7 @@
         </is>
       </c>
       <c r="M374" s="4" t="n">
-        <v>-41.35</v>
+        <v>-41.34</v>
       </c>
       <c r="N374" s="4" t="n">
         <v>4.91</v>
@@ -39131,7 +39131,7 @@
         </is>
       </c>
       <c r="I375" s="4" t="n">
-        <v>-27.73</v>
+        <v>-27.72</v>
       </c>
       <c r="J375" s="4" t="n">
         <v>0</v>
@@ -39151,7 +39151,7 @@
         <v>4.91</v>
       </c>
       <c r="O375" s="4" t="n">
-        <v>-27.73</v>
+        <v>-27.72</v>
       </c>
       <c r="P375" s="4" t="n">
         <v>-2.12</v>
@@ -39233,7 +39233,7 @@
         </is>
       </c>
       <c r="I376" s="4" t="n">
-        <v>-35.25</v>
+        <v>-35.24</v>
       </c>
       <c r="J376" s="4" t="n">
         <v>0</v>
@@ -39253,7 +39253,7 @@
         <v>4.91</v>
       </c>
       <c r="O376" s="4" t="n">
-        <v>-35.25</v>
+        <v>-35.24</v>
       </c>
       <c r="P376" s="4" t="n">
         <v>-1.73</v>
@@ -39539,7 +39539,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>40.06</v>
+        <v>40.07</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -39553,13 +39553,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>27</v>
+        <v>27.01</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>40.06</v>
+        <v>40.07</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>0</v>
@@ -39590,10 +39590,10 @@
         <v>0</v>
       </c>
       <c r="AB379" s="4" t="n">
-        <v>70.03</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>29.97</v>
+        <v>29.96</v>
       </c>
       <c r="AD379" s="4" t="n">
         <v>0</v>
@@ -39641,7 +39641,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>16.77</v>
+        <v>16.78</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.5</v>
@@ -39655,13 +39655,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>11.14</v>
+        <v>11.15</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>16.77</v>
+        <v>16.78</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.61</v>
@@ -40445,7 +40445,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-24.46</v>
+        <v>-25.66</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40465,10 +40465,10 @@
         <v>4.91</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-24.46</v>
+        <v>-25.66</v>
       </c>
       <c r="P388" s="4" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="Q388" s="4" t="n">
         <v>0</v>
@@ -40483,10 +40483,10 @@
       </c>
       <c r="V388" s="4" t="n"/>
       <c r="W388" s="5" t="n">
-        <v>0</v>
+        <v>261764</v>
       </c>
       <c r="X388" s="5" t="n">
-        <v>0</v>
+        <v>1438706</v>
       </c>
       <c r="Y388" t="inlineStr"/>
       <c r="Z388" s="4" t="n">
@@ -40496,10 +40496,10 @@
         <v>0</v>
       </c>
       <c r="AB388" s="4" t="n">
-        <v>37.77</v>
+        <v>37.17</v>
       </c>
       <c r="AC388" s="4" t="n">
-        <v>62.23</v>
+        <v>62.83</v>
       </c>
       <c r="AD388" s="4" t="n">
         <v>0</v>
@@ -40751,7 +40751,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>-36.11</v>
+        <v>-36.12</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>0</v>
@@ -40771,10 +40771,10 @@
         <v>4.91</v>
       </c>
       <c r="O391" s="4" t="n">
-        <v>-36.11</v>
+        <v>-36.12</v>
       </c>
       <c r="P391" s="4" t="n">
-        <v>-2.89</v>
+        <v>-2.9</v>
       </c>
       <c r="Q391" s="4" t="n">
         <v>-3.43</v>
@@ -40792,7 +40792,7 @@
         <v>140</v>
       </c>
       <c r="X391" s="5" t="n">
-        <v>2319124</v>
+        <v>2330803</v>
       </c>
       <c r="Y391" t="inlineStr"/>
       <c r="Z391" s="4" t="n">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-13.94</v>
+        <v>-13.95</v>
       </c>
       <c r="J393" s="4" t="n">
         <v>0.8</v>
@@ -41012,10 +41012,10 @@
         <v>0</v>
       </c>
       <c r="AB393" s="4" t="n">
-        <v>43.03</v>
+        <v>43.02</v>
       </c>
       <c r="AC393" s="4" t="n">
-        <v>56.97</v>
+        <v>56.98</v>
       </c>
       <c r="AD393" s="4" t="n">
         <v>0</v>
@@ -41059,7 +41059,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-21.62</v>
+        <v>-21.56</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>0.2</v>
@@ -41079,10 +41079,10 @@
         <v>4.91</v>
       </c>
       <c r="O394" s="4" t="n">
-        <v>-21.62</v>
+        <v>-21.56</v>
       </c>
       <c r="P394" s="4" t="n">
-        <v>-1.88</v>
+        <v>-1.82</v>
       </c>
       <c r="Q394" s="4" t="n">
         <v>0</v>
@@ -41110,10 +41110,10 @@
         <v>0</v>
       </c>
       <c r="AB394" s="4" t="n">
-        <v>39.19</v>
+        <v>39.22</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>60.81</v>
+        <v>60.78</v>
       </c>
       <c r="AD394" s="4" t="n">
         <v>0</v>
@@ -41765,7 +41765,7 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>-21.77</v>
+        <v>-21.78</v>
       </c>
       <c r="J401" s="4" t="n">
         <v>0.1</v>
@@ -41785,7 +41785,7 @@
         <v>4.91</v>
       </c>
       <c r="O401" s="4" t="n">
-        <v>-21.77</v>
+        <v>-21.78</v>
       </c>
       <c r="P401" s="4" t="n">
         <v>-1.91</v>
@@ -42169,7 +42169,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-18.88</v>
+        <v>-18.89</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.3</v>
@@ -42183,13 +42183,13 @@
         </is>
       </c>
       <c r="M405" s="4" t="n">
-        <v>-21.79</v>
+        <v>-21.8</v>
       </c>
       <c r="N405" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-18.88</v>
+        <v>-18.89</v>
       </c>
       <c r="P405" s="4" t="n">
         <v>-2.83</v>
@@ -42270,10 +42270,10 @@
         <v>-7.6</v>
       </c>
       <c r="J406" s="4" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="K406" s="4" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -42518,10 +42518,10 @@
         <v>0</v>
       </c>
       <c r="AB408" s="4" t="n">
-        <v>35.83</v>
+        <v>35.82</v>
       </c>
       <c r="AC408" s="4" t="n">
-        <v>64.17</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="AD408" s="4" t="n">
         <v>0</v>
@@ -42569,7 +42569,7 @@
         </is>
       </c>
       <c r="I409" s="4" t="n">
-        <v>-19.7</v>
+        <v>-19.71</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>0.2</v>
@@ -42589,7 +42589,7 @@
         <v>4.91</v>
       </c>
       <c r="O409" s="4" t="n">
-        <v>-19.7</v>
+        <v>-19.71</v>
       </c>
       <c r="P409" s="4" t="n">
         <v>0</v>
@@ -42671,7 +42671,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-41.66</v>
+        <v>-41.65</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -42691,10 +42691,10 @@
         <v>4.91</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-41.66</v>
+        <v>-41.65</v>
       </c>
       <c r="P410" s="4" t="n">
-        <v>-2.5</v>
+        <v>-2.49</v>
       </c>
       <c r="Q410" s="4" t="n">
         <v>-1.67</v>
@@ -42709,7 +42709,7 @@
       </c>
       <c r="V410" s="4" t="n"/>
       <c r="W410" s="5" t="n">
-        <v>96024</v>
+        <v>98355</v>
       </c>
       <c r="X410" s="5" t="n">
         <v>4036265</v>
@@ -42889,7 +42889,7 @@
         </is>
       </c>
       <c r="M412" s="4" t="n">
-        <v>-8.83</v>
+        <v>-8.84</v>
       </c>
       <c r="N412" s="4" t="n">
         <v>4.91</v>
@@ -42983,7 +42983,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="n">
-        <v>35.63</v>
+        <v>35.62</v>
       </c>
       <c r="J413" s="4" t="n">
         <v>100</v>
@@ -43003,7 +43003,7 @@
         <v>4.91</v>
       </c>
       <c r="O413" s="4" t="n">
-        <v>35.63</v>
+        <v>35.62</v>
       </c>
       <c r="P413" s="4" t="n">
         <v>0</v>
@@ -43136,10 +43136,10 @@
         <v>0</v>
       </c>
       <c r="AB414" s="4" t="n">
-        <v>42.12</v>
+        <v>42.11</v>
       </c>
       <c r="AC414" s="4" t="n">
-        <v>57.88</v>
+        <v>57.89</v>
       </c>
       <c r="AD414" s="4" t="n">
         <v>0</v>
@@ -43285,7 +43285,7 @@
         </is>
       </c>
       <c r="I416" s="4" t="n">
-        <v>-43.69</v>
+        <v>-43.7</v>
       </c>
       <c r="J416" s="4" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
         <v>4.91</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>-43.69</v>
+        <v>-43.7</v>
       </c>
       <c r="P416" s="4" t="n">
         <v>-2.39</v>
@@ -43583,7 +43583,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-14.07</v>
+        <v>-13.97</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>0.8</v>
@@ -43603,10 +43603,10 @@
         <v>4.91</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-14.07</v>
+        <v>-13.97</v>
       </c>
       <c r="P419" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q419" s="4" t="n">
         <v>-0.6</v>
@@ -43621,7 +43621,7 @@
       </c>
       <c r="V419" s="4" t="n"/>
       <c r="W419" s="5" t="n">
-        <v>41012</v>
+        <v>53761</v>
       </c>
       <c r="X419" s="5" t="n">
         <v>206463</v>
@@ -43634,10 +43634,10 @@
         <v>0</v>
       </c>
       <c r="AB419" s="4" t="n">
-        <v>42.96</v>
+        <v>43.01</v>
       </c>
       <c r="AC419" s="4" t="n">
-        <v>57.04</v>
+        <v>56.99</v>
       </c>
       <c r="AD419" s="4" t="n">
         <v>0</v>
@@ -43681,7 +43681,7 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-3.26</v>
+        <v>-3.27</v>
       </c>
       <c r="J420" s="4" t="n">
         <v>25.5</v>
@@ -43701,10 +43701,10 @@
         <v>4.91</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-2.95</v>
+        <v>-2.97</v>
       </c>
       <c r="P420" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.91</v>
       </c>
       <c r="Q420" s="4" t="n">
         <v>0</v>
@@ -43725,7 +43725,7 @@
         <v>-5</v>
       </c>
       <c r="W420" s="5" t="n">
-        <v>498548</v>
+        <v>484915</v>
       </c>
       <c r="X420" s="5" t="n">
         <v>1937719</v>
@@ -43738,10 +43738,10 @@
         <v>0</v>
       </c>
       <c r="AB420" s="4" t="n">
-        <v>48.37</v>
+        <v>48.36</v>
       </c>
       <c r="AC420" s="4" t="n">
-        <v>51.63</v>
+        <v>51.64</v>
       </c>
       <c r="AD420" s="4" t="n">
         <v>0</v>
@@ -44146,10 +44146,10 @@
         <v>0</v>
       </c>
       <c r="AB424" s="4" t="n">
-        <v>42.58</v>
+        <v>42.57</v>
       </c>
       <c r="AC424" s="4" t="n">
-        <v>57.42</v>
+        <v>57.43</v>
       </c>
       <c r="AD424" s="4" t="n">
         <v>0</v>
@@ -44197,13 +44197,13 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>10.4</v>
+        <v>10.54</v>
       </c>
       <c r="J425" s="4" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K425" s="4" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -44254,10 +44254,10 @@
         <v>0</v>
       </c>
       <c r="AB425" s="4" t="n">
-        <v>55.2</v>
+        <v>55.27</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>44.8</v>
+        <v>44.73</v>
       </c>
       <c r="AD425" s="4" t="n">
         <v>0</v>
@@ -44617,7 +44617,7 @@
         </is>
       </c>
       <c r="M429" s="4" t="n">
-        <v>-12.69</v>
+        <v>-12.7</v>
       </c>
       <c r="N429" s="4" t="n">
         <v>4.91</v>
@@ -44803,7 +44803,7 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>7.37</v>
+        <v>7.4</v>
       </c>
       <c r="J431" s="4" t="n">
         <v>88.7</v>
@@ -44817,7 +44817,7 @@
         </is>
       </c>
       <c r="M431" s="4" t="n">
-        <v>-2.11</v>
+        <v>-2.12</v>
       </c>
       <c r="N431" s="4" t="n">
         <v>4.91</v>
@@ -44860,10 +44860,10 @@
         <v>0</v>
       </c>
       <c r="AB431" s="4" t="n">
-        <v>53.69</v>
+        <v>53.7</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>46.31</v>
+        <v>46.3</v>
       </c>
       <c r="AD431" s="4" t="n">
         <v>0</v>
@@ -45009,7 +45009,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-16.9</v>
+        <v>-16.91</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.5</v>
@@ -45023,13 +45023,13 @@
         </is>
       </c>
       <c r="M433" s="4" t="n">
-        <v>-19.72</v>
+        <v>-19.73</v>
       </c>
       <c r="N433" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-16.9</v>
+        <v>-16.91</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>0</v>
@@ -45111,7 +45111,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>70.25</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -45131,7 +45131,7 @@
         <v>4.91</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>70.25</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="P434" s="4" t="n">
         <v>1.49</v>
@@ -45718,10 +45718,10 @@
         <v>-3.54</v>
       </c>
       <c r="J440" s="4" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="K440" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>-4.73</v>
       </c>
       <c r="P440" s="4" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="Q440" s="4" t="n">
         <v>-5.6</v>
@@ -46560,7 +46560,7 @@
         <v>-40.5</v>
       </c>
       <c r="P448" s="4" t="n">
-        <v>-2.17</v>
+        <v>-2.18</v>
       </c>
       <c r="Q448" s="4" t="n">
         <v>-1.45</v>
@@ -46578,7 +46578,7 @@
         <v>53280</v>
       </c>
       <c r="X448" s="5" t="n">
-        <v>1825004</v>
+        <v>1828839</v>
       </c>
       <c r="Y448" t="inlineStr"/>
       <c r="Z448" s="4" t="n">
@@ -46843,7 +46843,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>35.37</v>
+        <v>36.21</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -46857,16 +46857,16 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>20.66</v>
+        <v>20.63</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>34.33</v>
+        <v>36.12</v>
       </c>
       <c r="P451" s="4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q451" s="4" t="n">
         <v>9.710000000000001</v>
@@ -46887,10 +46887,10 @@
         <v>36.29</v>
       </c>
       <c r="W451" s="5" t="n">
-        <v>0</v>
+        <v>911064</v>
       </c>
       <c r="X451" s="5" t="n">
-        <v>0</v>
+        <v>34786</v>
       </c>
       <c r="Y451" t="inlineStr"/>
       <c r="Z451" s="4" t="n">
@@ -46900,10 +46900,10 @@
         <v>0</v>
       </c>
       <c r="AB451" s="4" t="n">
-        <v>67.69</v>
+        <v>68.11</v>
       </c>
       <c r="AC451" s="4" t="n">
-        <v>32.31</v>
+        <v>31.89</v>
       </c>
       <c r="AD451" s="4" t="n">
         <v>0</v>
@@ -47155,13 +47155,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>4.79</v>
+        <v>4.84</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47212,10 +47212,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>52.39</v>
+        <v>52.42</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>47.61</v>
+        <v>47.58</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -47259,7 +47259,7 @@
         </is>
       </c>
       <c r="I455" s="4" t="n">
-        <v>-15.65</v>
+        <v>-15.69</v>
       </c>
       <c r="J455" s="4" t="n">
         <v>0.6</v>
@@ -47279,10 +47279,10 @@
         <v>4.91</v>
       </c>
       <c r="O455" s="4" t="n">
-        <v>-15.65</v>
+        <v>-15.69</v>
       </c>
       <c r="P455" s="4" t="n">
-        <v>-0.74</v>
+        <v>-0.78</v>
       </c>
       <c r="Q455" s="4" t="n">
         <v>0</v>
@@ -47297,7 +47297,7 @@
       </c>
       <c r="V455" s="4" t="n"/>
       <c r="W455" s="5" t="n">
-        <v>179804</v>
+        <v>168109</v>
       </c>
       <c r="X455" s="5" t="n">
         <v>565896</v>
@@ -47310,10 +47310,10 @@
         <v>0</v>
       </c>
       <c r="AB455" s="4" t="n">
-        <v>42.17</v>
+        <v>42.15</v>
       </c>
       <c r="AC455" s="4" t="n">
-        <v>57.83</v>
+        <v>57.85</v>
       </c>
       <c r="AD455" s="4" t="n">
         <v>0</v>
@@ -47361,7 +47361,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-22.8</v>
+        <v>-22.79</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47381,10 +47381,10 @@
         <v>4.91</v>
       </c>
       <c r="O456" s="4" t="n">
-        <v>-27.85</v>
+        <v>-27.74</v>
       </c>
       <c r="P456" s="4" t="n">
-        <v>-0.97</v>
+        <v>-0.86</v>
       </c>
       <c r="Q456" s="4" t="n">
         <v>-19.99</v>
@@ -47418,10 +47418,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>38.6</v>
+        <v>38.61</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>61.4</v>
+        <v>61.39</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -47915,7 +47915,7 @@
       </c>
       <c r="V461" s="4" t="n"/>
       <c r="W461" s="5" t="n">
-        <v>1479527</v>
+        <v>1511304</v>
       </c>
       <c r="X461" s="5" t="n">
         <v>0</v>
@@ -48189,13 +48189,13 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="J464" s="4" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K464" s="4" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -48246,10 +48246,10 @@
         <v>0</v>
       </c>
       <c r="AB464" s="4" t="n">
-        <v>51.9</v>
+        <v>51.91</v>
       </c>
       <c r="AC464" s="4" t="n">
-        <v>48.1</v>
+        <v>48.09</v>
       </c>
       <c r="AD464" s="4" t="n">
         <v>0</v>
@@ -48501,7 +48501,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-18.81</v>
+        <v>-18.8</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.3</v>
@@ -48558,10 +48558,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>40.59</v>
+        <v>40.6</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>59.41</v>
+        <v>59.4</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -49009,7 +49009,7 @@
         </is>
       </c>
       <c r="I472" s="4" t="n">
-        <v>-40.38</v>
+        <v>-42.72</v>
       </c>
       <c r="J472" s="4" t="n">
         <v>0</v>
@@ -49029,10 +49029,10 @@
         <v>4.91</v>
       </c>
       <c r="O472" s="4" t="n">
-        <v>-40.38</v>
+        <v>-42.72</v>
       </c>
       <c r="P472" s="4" t="n">
-        <v>0</v>
+        <v>-2.34</v>
       </c>
       <c r="Q472" s="4" t="n">
         <v>0</v>
@@ -49047,10 +49047,10 @@
       </c>
       <c r="V472" s="4" t="n"/>
       <c r="W472" s="5" t="n">
-        <v>0</v>
+        <v>13270</v>
       </c>
       <c r="X472" s="5" t="n">
-        <v>0</v>
+        <v>1378842</v>
       </c>
       <c r="Y472" t="inlineStr"/>
       <c r="Z472" s="4" t="n">
@@ -49060,10 +49060,10 @@
         <v>0</v>
       </c>
       <c r="AB472" s="4" t="n">
-        <v>29.81</v>
+        <v>28.64</v>
       </c>
       <c r="AC472" s="4" t="n">
-        <v>70.19</v>
+        <v>71.36</v>
       </c>
       <c r="AD472" s="4" t="n">
         <v>0</v>
@@ -49111,13 +49111,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.34</v>
+        <v>-0.72</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>49</v>
+        <v>46.9</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>51</v>
+        <v>53.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49125,13 +49125,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.51</v>
+        <v>-10.62</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.18</v>
+        <v>-2.29</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -49168,10 +49168,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.37</v>
+        <v>45.34</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.63</v>
+        <v>46.66</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49629,7 +49629,7 @@
         </is>
       </c>
       <c r="I478" s="4" t="n">
-        <v>-5.74</v>
+        <v>-5.73</v>
       </c>
       <c r="J478" s="4" t="n">
         <v>16.6</v>
@@ -49649,7 +49649,7 @@
         <v>4.91</v>
       </c>
       <c r="O478" s="4" t="n">
-        <v>-4.69</v>
+        <v>-4.7</v>
       </c>
       <c r="P478" s="4" t="n">
         <v>0.21</v>
@@ -49751,13 +49751,13 @@
         </is>
       </c>
       <c r="M479" s="4" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="N479" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O479" s="4" t="n">
-        <v>12.7</v>
+        <v>12.69</v>
       </c>
       <c r="P479" s="4" t="n">
         <v>1.71</v>
@@ -49794,10 +49794,10 @@
         <v>0</v>
       </c>
       <c r="AB479" s="4" t="n">
-        <v>56.2</v>
+        <v>56.19</v>
       </c>
       <c r="AC479" s="4" t="n">
-        <v>43.8</v>
+        <v>43.81</v>
       </c>
       <c r="AD479" s="4" t="n">
         <v>0</v>
@@ -49841,13 +49841,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-1.57</v>
+        <v>-1.59</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -49898,10 +49898,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.92</v>
+        <v>47.91</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.45</v>
+        <v>49.46</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -49949,7 +49949,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-39.52</v>
+        <v>-39.53</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0</v>
@@ -50469,7 +50469,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>29.54</v>
+        <v>29.57</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -50526,10 +50526,10 @@
         <v>0</v>
       </c>
       <c r="AB486" s="4" t="n">
-        <v>64.77</v>
+        <v>64.78</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>35.23</v>
+        <v>35.22</v>
       </c>
       <c r="AD486" s="4" t="n">
         <v>0</v>
@@ -50577,13 +50577,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50634,10 +50634,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>51.06</v>
+        <v>51.04</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>48.94</v>
+        <v>48.96</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -50681,13 +50681,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         </is>
       </c>
       <c r="M488" s="4" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="N488" s="4" t="n">
         <v>4.91</v>
@@ -50738,10 +50738,10 @@
         <v>0</v>
       </c>
       <c r="AB488" s="4" t="n">
-        <v>52.44</v>
+        <v>52.45</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>47.56</v>
+        <v>47.55</v>
       </c>
       <c r="AD488" s="4" t="n">
         <v>0</v>
@@ -50799,13 +50799,13 @@
         </is>
       </c>
       <c r="M489" s="4" t="n">
-        <v>6.84</v>
+        <v>6.83</v>
       </c>
       <c r="N489" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O489" s="4" t="n">
-        <v>10.98</v>
+        <v>10.97</v>
       </c>
       <c r="P489" s="4" t="n">
         <v>-0.05</v>
@@ -51001,30 +51001,30 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-20.57</v>
+        <v>-20.75</v>
       </c>
       <c r="J491" s="4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>Safe R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M491" s="4" t="n">
-        <v>-19.86</v>
+        <v>-13.86</v>
       </c>
       <c r="N491" s="4" t="n">
         <v>4.91</v>
       </c>
       <c r="O491" s="4" t="n">
-        <v>-16.37</v>
+        <v>-9.57</v>
       </c>
       <c r="P491" s="4" t="n">
-        <v>-0.4</v>
+        <v>0.39</v>
       </c>
       <c r="Q491" s="4" t="n">
         <v>0</v>
@@ -51056,16 +51056,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>33.03</v>
+        <v>33.04</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.6</v>
+        <v>53.78</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51112,10 +51112,10 @@
         <v>5.87</v>
       </c>
       <c r="J492" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K492" s="4" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -51166,10 +51166,10 @@
         <v>0</v>
       </c>
       <c r="AB492" s="4" t="n">
-        <v>51.95</v>
+        <v>51.94</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>46.18</v>
+        <v>46.19</v>
       </c>
       <c r="AD492" s="4" t="n">
         <v>1.87</v>
@@ -51217,13 +51217,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-6.45</v>
+        <v>-6.7</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>69.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51237,13 +51237,13 @@
         <v>4.91</v>
       </c>
       <c r="O493" s="4" t="n">
-        <v>-16.41</v>
+        <v>-6.68</v>
       </c>
       <c r="P493" s="4" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="Q493" s="4" t="n">
-        <v>-1.62</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="R493" s="4" t="n">
         <v>-20.84</v>
@@ -51272,16 +51272,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>46.78</v>
+        <v>46.65</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>53.22</v>
+        <v>53.35</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -51325,7 +51325,7 @@
         </is>
       </c>
       <c r="I494" s="4" t="n">
-        <v>6.95</v>
+        <v>6.96</v>
       </c>
       <c r="J494" s="4" t="n">
         <v>87.40000000000001</v>
@@ -51339,7 +51339,7 @@
         </is>
       </c>
       <c r="M494" s="4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="N494" s="4" t="n">
         <v>4.91</v>
@@ -51637,7 +51637,7 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="J497" s="4" t="n">
         <v>36.3</v>
@@ -51651,7 +51651,7 @@
         </is>
       </c>
       <c r="M497" s="4" t="n">
-        <v>-8.41</v>
+        <v>-8.42</v>
       </c>
       <c r="N497" s="4" t="n">
         <v>4.91</v>
@@ -51857,7 +51857,7 @@
         </is>
       </c>
       <c r="M499" s="4" t="n">
-        <v>12.5</v>
+        <v>12.51</v>
       </c>
       <c r="N499" s="4" t="n">
         <v>4.91</v>
@@ -51894,10 +51894,10 @@
         <v>0</v>
       </c>
       <c r="AB499" s="4" t="n">
-        <v>60.54</v>
+        <v>60.55</v>
       </c>
       <c r="AC499" s="4" t="n">
-        <v>39.46</v>
+        <v>39.45</v>
       </c>
       <c r="AD499" s="4" t="n">
         <v>0</v>
@@ -51945,7 +51945,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>22.45</v>
+        <v>22.5</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -52002,10 +52002,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.22</v>
+        <v>61.25</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.78</v>
+        <v>38.75</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -52361,7 +52361,7 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J504" s="4" t="n">
         <v>62.8</v>
@@ -55227,7 +55227,7 @@
         <v>31</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K47" t="n">
         <v>42</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-07-24 · evaluated at 0 days to election (actual: 102 days out)</t>
+          <t>Data as of 2026-07-25 · evaluated at 0 days to election (actual: 101 days out)</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="C8" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="C10" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="D10" t="n">
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>39.8</v>
+        <v>39.5</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.25</v>
+        <v>-3.6</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>39.7</v>
+        <v>39.1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>44.42</v>
+        <v>44.4</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>47.58</v>
+        <v>47.6</v>
       </c>
       <c r="AD2" s="4" t="n">
         <v>8</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.59</v>
+        <v>7.6</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>89.3</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26.76</v>
+        <v>26.78</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>63.38</v>
+        <v>63.39</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>36.62</v>
+        <v>36.61</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17.52</v>
+        <v>17.56</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.59999999999999</v>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>58.76</v>
+        <v>58.78</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>41.24</v>
+        <v>41.22</v>
       </c>
       <c r="AD8" s="4" t="n">
         <v>0</v>
@@ -1660,10 +1660,10 @@
         <v>-6.05</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         <v>0</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>46.98</v>
+        <v>46.97</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>53.02</v>
+        <v>53.03</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>73.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>51.45</v>
+        <v>51.44</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>48.55</v>
+        <v>48.56</v>
       </c>
       <c r="AD10" s="4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>29.21</v>
+        <v>29.24</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>64.61</v>
+        <v>64.62</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>35.39</v>
+        <v>35.38</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12.59</v>
+        <v>12.58</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>99</v>
@@ -2656,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>55.66</v>
+        <v>55.65</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>43.2</v>
+        <v>43.21</v>
       </c>
       <c r="AD18" s="4" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>12.5</v>
+        <v>12.39</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2735,16 +2735,16 @@
         <v>-1.44</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>44.9</v>
+        <v>44.76</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>35.32</v>
+        <v>35.34</v>
       </c>
       <c r="U19" t="n">
         <v>17</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>10.28</v>
+        <v>10.02</v>
       </c>
       <c r="W19" s="5" t="n">
         <v>5958887</v>
@@ -2760,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>56.25</v>
+        <v>56.2</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>43.75</v>
+        <v>43.8</v>
       </c>
       <c r="AD19" s="4" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.5</v>
+        <v>12.48</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>56.25</v>
+        <v>56.24</v>
       </c>
       <c r="AC20" s="4" t="n">
-        <v>43.75</v>
+        <v>43.76</v>
       </c>
       <c r="AD20" s="4" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.58</v>
+        <v>-10.6</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>2.8</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>44.71</v>
+        <v>44.7</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>55.29</v>
+        <v>55.3</v>
       </c>
       <c r="AD22" s="4" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>53.29</v>
+        <v>53.31</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>46.71</v>
+        <v>46.69</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>0</v>
@@ -3239,13 +3239,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>67.7</v>
+        <v>67.8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>50.75</v>
+        <v>50.76</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>49.25</v>
+        <v>49.24</v>
       </c>
       <c r="AD24" s="4" t="n">
         <v>0</v>
@@ -3350,10 +3350,10 @@
         <v>15.13</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.36</v>
+        <v>-3.37</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25.1</v>
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>52.18</v>
+        <v>52.19</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>47.82</v>
+        <v>47.81</v>
       </c>
       <c r="AD28" s="4" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.56</v>
+        <v>19.57</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.7</v>
@@ -3926,10 +3926,10 @@
         <v>0</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>59.78</v>
+        <v>59.79</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>40.22</v>
+        <v>40.21</v>
       </c>
       <c r="AD30" s="4" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-8.59</v>
+        <v>-8.6</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>7.8</v>
@@ -4334,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>45.71</v>
+        <v>45.7</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>54.29</v>
+        <v>54.3</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-18.46</v>
+        <v>-18.56</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.3</v>
@@ -4442,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>40.77</v>
+        <v>40.72</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>59.23</v>
+        <v>59.28</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>0</v>
@@ -4489,13 +4489,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4546,10 +4546,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>50.94</v>
+        <v>50.95</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>49.06</v>
+        <v>49.05</v>
       </c>
       <c r="AD36" s="4" t="n">
         <v>0</v>
@@ -4695,27 +4695,27 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.95</v>
+        <v>-3.19</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>59.1</v>
+        <v>61.1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.57</v>
+        <v>-2.71</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.27</v>
+        <v>-1.41</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.1</v>
@@ -4750,16 +4750,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.52</v>
+        <v>48.41</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>40.9</v>
+        <v>38.9</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.48</v>
+        <v>51.59</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>-3.2</v>
+        <v>-3.19</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>49.6</v>
+        <v>49.62</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>50.4</v>
+        <v>50.38</v>
       </c>
       <c r="AD51" s="4" t="n">
         <v>0</v>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>80.09999999999999</v>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19.23</v>
+        <v>19.24</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>99.7</v>
@@ -6879,7 +6879,7 @@
         <v>5.13</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>19.23</v>
+        <v>19.24</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0.21</v>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.82</v>
+        <v>27.83</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>5.13</v>
@@ -7012,10 +7012,10 @@
         <v>0</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>66.65000000000001</v>
+        <v>66.66</v>
       </c>
       <c r="AC60" s="4" t="n">
-        <v>33.35</v>
+        <v>33.34</v>
       </c>
       <c r="AD60" s="4" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>12.81</v>
+        <v>12.82</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>5.13</v>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-18.24</v>
+        <v>-18.23</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>5.13</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12.38</v>
+        <v>12.39</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>98.90000000000001</v>
@@ -7389,7 +7389,7 @@
         <v>5.13</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12.38</v>
+        <v>12.39</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>-0.35</v>
@@ -7420,10 +7420,10 @@
         <v>0</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>56.19</v>
+        <v>56.2</v>
       </c>
       <c r="AC64" s="4" t="n">
-        <v>43.81</v>
+        <v>43.8</v>
       </c>
       <c r="AD64" s="4" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>16.63</v>
+        <v>16.64</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>5.13</v>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>100</v>
@@ -7587,13 +7587,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>39.17</v>
+        <v>39.18</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>1.66</v>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>17.31</v>
+        <v>17.32</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>5.13</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="M68" s="4" t="n">
-        <v>37.48</v>
+        <v>37.49</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>5.13</v>
@@ -7828,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>71.43000000000001</v>
+        <v>71.44</v>
       </c>
       <c r="AC68" s="4" t="n">
-        <v>28.57</v>
+        <v>28.56</v>
       </c>
       <c r="AD68" s="4" t="n">
         <v>0</v>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>74.03</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>78.84999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>80.78</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>87.84</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="P70" s="4" t="n">
         <v>0</v>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="M71" s="4" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>5.13</v>
@@ -8130,10 +8130,10 @@
         <v>0</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>60.79</v>
+        <v>60.8</v>
       </c>
       <c r="AC71" s="4" t="n">
-        <v>39.21</v>
+        <v>39.2</v>
       </c>
       <c r="AD71" s="4" t="n">
         <v>0</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>58.2</v>
+        <v>58.21</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>100</v>
@@ -8293,13 +8293,13 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>53.8</v>
+        <v>53.81</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>58.2</v>
+        <v>58.21</v>
       </c>
       <c r="P73" s="4" t="n">
         <v>0</v>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>59.61</v>
+        <v>59.62</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>100</v>
@@ -8401,7 +8401,7 @@
         <v>5.13</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>59.61</v>
+        <v>59.62</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -8497,7 +8497,7 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>45.15</v>
+        <v>45.16</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>5.13</v>
@@ -8534,10 +8534,10 @@
         <v>0</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>74.48</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AC75" s="4" t="n">
-        <v>25.52</v>
+        <v>25.51</v>
       </c>
       <c r="AD75" s="4" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>43.9</v>
+        <v>43.91</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>100</v>
@@ -8599,13 +8599,13 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>35.08</v>
+        <v>35.09</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>43.9</v>
+        <v>43.91</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>2.1</v>
@@ -8636,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>71.95</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="AC76" s="4" t="n">
-        <v>28.05</v>
+        <v>28.04</v>
       </c>
       <c r="AD76" s="4" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>100</v>
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.64</v>
+        <v>38.65</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>5.13</v>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-28.64</v>
+        <v>-28.63</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
         <v>5.13</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-28.64</v>
+        <v>-28.63</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.51</v>
@@ -8840,10 +8840,10 @@
         <v>0</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>35.68</v>
+        <v>35.69</v>
       </c>
       <c r="AC78" s="4" t="n">
-        <v>64.31999999999999</v>
+        <v>64.31</v>
       </c>
       <c r="AD78" s="4" t="n">
         <v>0</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>20.87</v>
+        <v>20.88</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>99.8</v>
@@ -8905,13 +8905,13 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.78</v>
+        <v>11.79</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>20.87</v>
+        <v>20.88</v>
       </c>
       <c r="P79" s="4" t="n">
         <v>0.95</v>
@@ -8942,10 +8942,10 @@
         <v>0</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>60.43</v>
+        <v>60.44</v>
       </c>
       <c r="AC79" s="4" t="n">
-        <v>39.57</v>
+        <v>39.56</v>
       </c>
       <c r="AD79" s="4" t="n">
         <v>0</v>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.41</v>
+        <v>5.43</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>82.3</v>
@@ -9013,7 +9013,7 @@
         <v>5.13</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>7.15</v>
+        <v>7.16</v>
       </c>
       <c r="P80" s="4" t="n">
         <v>-0.32</v>
@@ -9050,10 +9050,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>52.7</v>
+        <v>52.71</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47.3</v>
+        <v>47.29</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>-16.41</v>
+        <v>-16.4</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>0.5</v>
@@ -9115,13 +9115,13 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-16.74</v>
+        <v>-16.73</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>-16.41</v>
+        <v>-16.4</v>
       </c>
       <c r="P81" s="4" t="n">
         <v>-1.89</v>
@@ -9152,10 +9152,10 @@
         <v>0</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>41.79</v>
+        <v>41.8</v>
       </c>
       <c r="AC81" s="4" t="n">
-        <v>58.21</v>
+        <v>58.2</v>
       </c>
       <c r="AD81" s="4" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>36.62</v>
+        <v>36.63</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>100</v>
@@ -9223,7 +9223,7 @@
         <v>5.13</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>36.62</v>
+        <v>36.63</v>
       </c>
       <c r="P82" s="4" t="n">
         <v>1.43</v>
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>19.72</v>
+        <v>19.73</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>99.8</v>
@@ -9319,13 +9319,13 @@
         </is>
       </c>
       <c r="M83" s="4" t="n">
-        <v>10.42</v>
+        <v>10.43</v>
       </c>
       <c r="N83" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>19.72</v>
+        <v>19.73</v>
       </c>
       <c r="P83" s="4" t="n">
         <v>0.58</v>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25.78</v>
+        <v>25.79</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>100</v>
@@ -9417,13 +9417,13 @@
         </is>
       </c>
       <c r="M84" s="4" t="n">
-        <v>19.07</v>
+        <v>19.08</v>
       </c>
       <c r="N84" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>25.78</v>
+        <v>25.79</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.63</v>
@@ -9454,10 +9454,10 @@
         <v>0</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>62.89</v>
+        <v>62.9</v>
       </c>
       <c r="AC84" s="4" t="n">
-        <v>37.11</v>
+        <v>37.1</v>
       </c>
       <c r="AD84" s="4" t="n">
         <v>0</v>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>26.79</v>
+        <v>26.8</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>100</v>
@@ -9519,13 +9519,13 @@
         </is>
       </c>
       <c r="M85" s="4" t="n">
-        <v>14.2</v>
+        <v>14.21</v>
       </c>
       <c r="N85" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>26.79</v>
+        <v>26.8</v>
       </c>
       <c r="P85" s="4" t="n">
         <v>1.74</v>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>39.74</v>
+        <v>39.75</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9621,13 +9621,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.78</v>
+        <v>29.79</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>39.74</v>
+        <v>39.75</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.23</v>
@@ -9658,10 +9658,10 @@
         <v>0</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>69.87</v>
+        <v>69.88</v>
       </c>
       <c r="AC86" s="4" t="n">
-        <v>30.13</v>
+        <v>30.12</v>
       </c>
       <c r="AD86" s="4" t="n">
         <v>0</v>
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.34</v>
+        <v>41.35</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>53.31</v>
+        <v>53.32</v>
       </c>
       <c r="P87" s="4" t="n">
         <v>0</v>
@@ -9862,10 +9862,10 @@
         <v>0</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>75.81999999999999</v>
+        <v>75.83</v>
       </c>
       <c r="AC88" s="4" t="n">
-        <v>24.18</v>
+        <v>24.17</v>
       </c>
       <c r="AD88" s="4" t="n">
         <v>0</v>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.02</v>
+        <v>16.03</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>99.5</v>
@@ -9927,13 +9927,13 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>17.88</v>
+        <v>17.89</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>16.02</v>
+        <v>16.03</v>
       </c>
       <c r="P89" s="4" t="n">
         <v>1.31</v>
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>39.5</v>
+        <v>39.51</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>100</v>
@@ -10029,13 +10029,13 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>29.9</v>
+        <v>29.91</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>39.5</v>
+        <v>39.51</v>
       </c>
       <c r="P90" s="4" t="n">
         <v>2.65</v>
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28.33</v>
+        <v>28.34</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>100</v>
@@ -10131,13 +10131,13 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>16.25</v>
+        <v>16.26</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28.33</v>
+        <v>28.34</v>
       </c>
       <c r="P91" s="4" t="n">
         <v>0</v>
@@ -10233,13 +10233,13 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.81</v>
+        <v>58.82</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>67.75</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="P92" s="4" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26.24</v>
+        <v>26.25</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>100</v>
@@ -10335,13 +10335,13 @@
         </is>
       </c>
       <c r="M93" s="4" t="n">
-        <v>14.09</v>
+        <v>14.1</v>
       </c>
       <c r="N93" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>26.24</v>
+        <v>26.25</v>
       </c>
       <c r="P93" s="4" t="n">
         <v>2.03</v>
@@ -10372,10 +10372,10 @@
         <v>0</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>63.12</v>
+        <v>63.13</v>
       </c>
       <c r="AC93" s="4" t="n">
-        <v>36.88</v>
+        <v>36.87</v>
       </c>
       <c r="AD93" s="4" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.4</v>
+        <v>43.41</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>5.13</v>
@@ -10474,10 +10474,10 @@
         <v>0</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>75.51000000000001</v>
+        <v>75.52</v>
       </c>
       <c r="AC94" s="4" t="n">
-        <v>24.49</v>
+        <v>24.48</v>
       </c>
       <c r="AD94" s="4" t="n">
         <v>0</v>
@@ -10539,13 +10539,13 @@
         </is>
       </c>
       <c r="M95" s="4" t="n">
-        <v>67.81999999999999</v>
+        <v>67.83</v>
       </c>
       <c r="N95" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>76.51000000000001</v>
+        <v>76.52</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -10623,7 +10623,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>25.96</v>
+        <v>25.97</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>100</v>
@@ -10637,13 +10637,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="n">
-        <v>18.96</v>
+        <v>18.97</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>25.96</v>
+        <v>25.97</v>
       </c>
       <c r="P96" s="4" t="n">
         <v>0</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>25.27</v>
+        <v>25.28</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>99.90000000000001</v>
@@ -10739,13 +10739,13 @@
         </is>
       </c>
       <c r="M97" s="4" t="n">
-        <v>15.98</v>
+        <v>15.99</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>25.27</v>
+        <v>25.28</v>
       </c>
       <c r="P97" s="4" t="n">
         <v>0</v>
@@ -10776,10 +10776,10 @@
         <v>0</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>62.63</v>
+        <v>62.64</v>
       </c>
       <c r="AC97" s="4" t="n">
-        <v>37.37</v>
+        <v>37.36</v>
       </c>
       <c r="AD97" s="4" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="n">
-        <v>-10.24</v>
+        <v>-10.23</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>-4.75</v>
+        <v>-4.74</v>
       </c>
       <c r="P98" s="4" t="n">
         <v>0</v>
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>31.09</v>
+        <v>31.1</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -10943,13 +10943,13 @@
         </is>
       </c>
       <c r="M99" s="4" t="n">
-        <v>19.52</v>
+        <v>19.53</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>31.09</v>
+        <v>31.1</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.64</v>
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26.19</v>
+        <v>26.2</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>100</v>
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="M100" s="4" t="n">
-        <v>16.76</v>
+        <v>16.77</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>26.19</v>
+        <v>26.2</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1.69</v>
@@ -11133,7 +11133,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>63.41</v>
+        <v>63.42</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>100</v>
@@ -11147,13 +11147,13 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>56.73</v>
+        <v>56.74</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>63.41</v>
+        <v>63.42</v>
       </c>
       <c r="P101" s="4" t="n">
         <v>0</v>
@@ -11235,7 +11235,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>58.84</v>
+        <v>58.85</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11255,7 +11255,7 @@
         <v>5.13</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>58.84</v>
+        <v>58.85</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>1.93</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>79.42</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="AC102" s="4" t="n">
-        <v>20.58</v>
+        <v>20.57</v>
       </c>
       <c r="AD102" s="4" t="n">
         <v>0</v>
@@ -11351,7 +11351,7 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N103" s="4" t="n">
         <v>5.13</v>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>60.11</v>
+        <v>60.12</v>
       </c>
       <c r="AC103" s="4" t="n">
-        <v>39.89</v>
+        <v>39.88</v>
       </c>
       <c r="AD103" s="4" t="n">
         <v>0</v>
@@ -11490,10 +11490,10 @@
         <v>0</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>69.67</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="AC104" s="4" t="n">
-        <v>30.33</v>
+        <v>30.32</v>
       </c>
       <c r="AD104" s="4" t="n">
         <v>0</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>23.16</v>
+        <v>23.17</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>99.90000000000001</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="M105" s="4" t="n">
-        <v>13.29</v>
+        <v>13.3</v>
       </c>
       <c r="N105" s="4" t="n">
         <v>5.13</v>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.57</v>
+        <v>5.58</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>5.13</v>
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>21.89</v>
+        <v>21.9</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>99.90000000000001</v>
@@ -11755,13 +11755,13 @@
         </is>
       </c>
       <c r="M107" s="4" t="n">
-        <v>14.49</v>
+        <v>14.5</v>
       </c>
       <c r="N107" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O107" s="4" t="n">
-        <v>21.89</v>
+        <v>21.9</v>
       </c>
       <c r="P107" s="4" t="n">
         <v>2.54</v>
@@ -11792,10 +11792,10 @@
         <v>0</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>60.94</v>
+        <v>60.95</v>
       </c>
       <c r="AC107" s="4" t="n">
-        <v>39.06</v>
+        <v>39.05</v>
       </c>
       <c r="AD107" s="4" t="n">
         <v>0</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>63.08</v>
+        <v>63.09</v>
       </c>
       <c r="AC108" s="4" t="n">
-        <v>36.92</v>
+        <v>36.91</v>
       </c>
       <c r="AD108" s="4" t="n">
         <v>0</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27.39</v>
+        <v>27.4</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -11959,13 +11959,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.38</v>
+        <v>21.39</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>27.39</v>
+        <v>27.4</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12061,7 +12061,7 @@
         </is>
       </c>
       <c r="M110" s="4" t="n">
-        <v>24.47</v>
+        <v>24.48</v>
       </c>
       <c r="N110" s="4" t="n">
         <v>5.13</v>
@@ -12098,10 +12098,10 @@
         <v>0</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>69.81999999999999</v>
+        <v>69.83</v>
       </c>
       <c r="AC110" s="4" t="n">
-        <v>30.18</v>
+        <v>30.17</v>
       </c>
       <c r="AD110" s="4" t="n">
         <v>0</v>
@@ -12973,7 +12973,7 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>36.67</v>
+        <v>36.68</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>100</v>
@@ -12987,13 +12987,13 @@
         </is>
       </c>
       <c r="M119" s="4" t="n">
-        <v>25.13</v>
+        <v>25.14</v>
       </c>
       <c r="N119" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O119" s="4" t="n">
-        <v>36.67</v>
+        <v>36.68</v>
       </c>
       <c r="P119" s="4" t="n">
         <v>2.93</v>
@@ -13024,10 +13024,10 @@
         <v>0</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>68.33</v>
+        <v>68.34</v>
       </c>
       <c r="AC119" s="4" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="AD119" s="4" t="n">
         <v>0</v>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>27.14</v>
+        <v>27.15</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>100</v>
@@ -13089,13 +13089,13 @@
         </is>
       </c>
       <c r="M120" s="4" t="n">
-        <v>9.07</v>
+        <v>9.08</v>
       </c>
       <c r="N120" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>27.14</v>
+        <v>27.15</v>
       </c>
       <c r="P120" s="4" t="n">
         <v>1.43</v>
@@ -13126,10 +13126,10 @@
         <v>0</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>63.57</v>
+        <v>63.58</v>
       </c>
       <c r="AC120" s="4" t="n">
-        <v>36.43</v>
+        <v>36.42</v>
       </c>
       <c r="AD120" s="4" t="n">
         <v>0</v>
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>28.18</v>
+        <v>28.19</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>100</v>
@@ -13191,13 +13191,13 @@
         </is>
       </c>
       <c r="M121" s="4" t="n">
-        <v>16.2</v>
+        <v>16.21</v>
       </c>
       <c r="N121" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O121" s="4" t="n">
-        <v>28.18</v>
+        <v>28.19</v>
       </c>
       <c r="P121" s="4" t="n">
         <v>2.19</v>
@@ -13228,10 +13228,10 @@
         <v>0</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>64.09</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AC121" s="4" t="n">
-        <v>35.91</v>
+        <v>35.9</v>
       </c>
       <c r="AD121" s="4" t="n">
         <v>0</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>34.68</v>
+        <v>34.69</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>100</v>
@@ -13293,13 +13293,13 @@
         </is>
       </c>
       <c r="M122" s="4" t="n">
-        <v>26.11</v>
+        <v>26.12</v>
       </c>
       <c r="N122" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>34.68</v>
+        <v>34.69</v>
       </c>
       <c r="P122" s="4" t="n">
         <v>2.06</v>
@@ -13330,10 +13330,10 @@
         <v>0</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>67.34</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="AC122" s="4" t="n">
-        <v>32.66</v>
+        <v>32.65</v>
       </c>
       <c r="AD122" s="4" t="n">
         <v>0</v>
@@ -13381,7 +13381,7 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>15.1</v>
+        <v>15.11</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>99.3</v>
@@ -13395,13 +13395,13 @@
         </is>
       </c>
       <c r="M123" s="4" t="n">
-        <v>7.36</v>
+        <v>7.37</v>
       </c>
       <c r="N123" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O123" s="4" t="n">
-        <v>15.1</v>
+        <v>15.11</v>
       </c>
       <c r="P123" s="4" t="n">
         <v>1.9</v>
@@ -14193,13 +14193,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>-4.27</v>
+        <v>-4.28</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -14250,10 +14250,10 @@
         <v>0</v>
       </c>
       <c r="AB131" s="4" t="n">
-        <v>47.87</v>
+        <v>47.86</v>
       </c>
       <c r="AC131" s="4" t="n">
-        <v>52.13</v>
+        <v>52.14</v>
       </c>
       <c r="AD131" s="4" t="n">
         <v>0</v>
@@ -16074,10 +16074,10 @@
         <v>0</v>
       </c>
       <c r="AB149" s="4" t="n">
-        <v>53.49</v>
+        <v>53.48</v>
       </c>
       <c r="AC149" s="4" t="n">
-        <v>46.51</v>
+        <v>46.52</v>
       </c>
       <c r="AD149" s="4" t="n">
         <v>0</v>
@@ -16439,13 +16439,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -16453,13 +16453,13 @@
         </is>
       </c>
       <c r="M153" s="4" t="n">
-        <v>-11.53</v>
+        <v>-11.54</v>
       </c>
       <c r="N153" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="P153" s="4" t="n">
         <v>-1.91</v>
@@ -16490,10 +16490,10 @@
         <v>0</v>
       </c>
       <c r="AB153" s="4" t="n">
-        <v>45.7</v>
+        <v>45.69</v>
       </c>
       <c r="AC153" s="4" t="n">
-        <v>54.3</v>
+        <v>54.31</v>
       </c>
       <c r="AD153" s="4" t="n">
         <v>0</v>
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M154" s="4" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="N154" s="4" t="n">
         <v>5.13</v>
@@ -16657,7 +16657,7 @@
         </is>
       </c>
       <c r="M155" s="4" t="n">
-        <v>-26.43</v>
+        <v>-26.44</v>
       </c>
       <c r="N155" s="4" t="n">
         <v>5.13</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB155" s="4" t="n">
-        <v>35.42</v>
+        <v>35.41</v>
       </c>
       <c r="AC155" s="4" t="n">
-        <v>64.58</v>
+        <v>64.59</v>
       </c>
       <c r="AD155" s="4" t="n">
         <v>0</v>
@@ -16745,7 +16745,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>65.34</v>
+        <v>65.33</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>100</v>
@@ -16765,7 +16765,7 @@
         <v>5.13</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>65.34</v>
+        <v>65.33</v>
       </c>
       <c r="P156" s="4" t="n">
         <v>0</v>
@@ -16861,7 +16861,7 @@
         </is>
       </c>
       <c r="M157" s="4" t="n">
-        <v>76.73</v>
+        <v>76.72</v>
       </c>
       <c r="N157" s="4" t="n">
         <v>5.13</v>
@@ -16898,10 +16898,10 @@
         <v>0</v>
       </c>
       <c r="AB157" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>91.89</v>
       </c>
       <c r="AC157" s="4" t="n">
-        <v>8.1</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AD157" s="4" t="n">
         <v>0</v>
@@ -16963,7 +16963,7 @@
         </is>
       </c>
       <c r="M158" s="4" t="n">
-        <v>53.86</v>
+        <v>53.85</v>
       </c>
       <c r="N158" s="4" t="n">
         <v>5.13</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AB158" s="4" t="n">
-        <v>81.55</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="AC158" s="4" t="n">
-        <v>18.45</v>
+        <v>18.46</v>
       </c>
       <c r="AD158" s="4" t="n">
         <v>0</v>
@@ -17153,7 +17153,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-29.79</v>
+        <v>-29.8</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>0</v>
@@ -17167,13 +17167,13 @@
         </is>
       </c>
       <c r="M160" s="4" t="n">
-        <v>-26.25</v>
+        <v>-26.26</v>
       </c>
       <c r="N160" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O160" s="4" t="n">
-        <v>-29.79</v>
+        <v>-29.8</v>
       </c>
       <c r="P160" s="4" t="n">
         <v>-2.36</v>
@@ -17204,10 +17204,10 @@
         <v>0</v>
       </c>
       <c r="AB160" s="4" t="n">
-        <v>35.11</v>
+        <v>35.1</v>
       </c>
       <c r="AC160" s="4" t="n">
-        <v>64.89</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AD160" s="4" t="n">
         <v>0</v>
@@ -17269,7 +17269,7 @@
         </is>
       </c>
       <c r="M161" s="4" t="n">
-        <v>-30.57</v>
+        <v>-30.58</v>
       </c>
       <c r="N161" s="4" t="n">
         <v>5.13</v>
@@ -17306,10 +17306,10 @@
         <v>0</v>
       </c>
       <c r="AB161" s="4" t="n">
-        <v>34.96</v>
+        <v>34.95</v>
       </c>
       <c r="AC161" s="4" t="n">
-        <v>65.04000000000001</v>
+        <v>65.05</v>
       </c>
       <c r="AD161" s="4" t="n">
         <v>0</v>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>-16.25</v>
+        <v>-16.26</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>0.5</v>
@@ -17367,13 +17367,13 @@
         </is>
       </c>
       <c r="M162" s="4" t="n">
-        <v>-17.51</v>
+        <v>-17.52</v>
       </c>
       <c r="N162" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O162" s="4" t="n">
-        <v>-16.25</v>
+        <v>-16.26</v>
       </c>
       <c r="P162" s="4" t="n">
         <v>-2.86</v>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>-17.35</v>
+        <v>-17.36</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>0.4</v>
@@ -17465,13 +17465,13 @@
         </is>
       </c>
       <c r="M163" s="4" t="n">
-        <v>-19.94</v>
+        <v>-19.95</v>
       </c>
       <c r="N163" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O163" s="4" t="n">
-        <v>-17.35</v>
+        <v>-17.36</v>
       </c>
       <c r="P163" s="4" t="n">
         <v>-2.21</v>
@@ -17567,7 +17567,7 @@
         </is>
       </c>
       <c r="M164" s="4" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="N164" s="4" t="n">
         <v>5.13</v>
@@ -17604,10 +17604,10 @@
         <v>0</v>
       </c>
       <c r="AB164" s="4" t="n">
-        <v>44.16</v>
+        <v>44.15</v>
       </c>
       <c r="AC164" s="4" t="n">
-        <v>55.84</v>
+        <v>55.85</v>
       </c>
       <c r="AD164" s="4" t="n">
         <v>0</v>
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-21.74</v>
+        <v>-21.75</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>0.1</v>
@@ -17773,7 +17773,7 @@
         <v>5.13</v>
       </c>
       <c r="O166" s="4" t="n">
-        <v>-21.74</v>
+        <v>-21.75</v>
       </c>
       <c r="P166" s="4" t="n">
         <v>0.62</v>
@@ -18163,7 +18163,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>68</v>
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>80.90000000000001</v>
@@ -18291,7 +18291,7 @@
         <v>5.13</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>6.26</v>
+        <v>6.25</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.06</v>
@@ -18375,7 +18375,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-20.91</v>
+        <v>-20.92</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.2</v>
@@ -18395,7 +18395,7 @@
         <v>5.13</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-20.91</v>
+        <v>-20.92</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-27.22</v>
+        <v>-27.53</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18534,10 +18534,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>36.39</v>
+        <v>36.23</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>63.61</v>
+        <v>63.77</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18599,7 +18599,7 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-28.84</v>
+        <v>-28.85</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.13</v>
@@ -22229,13 +22229,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-7.55</v>
+        <v>-7.57</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -22286,10 +22286,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.23</v>
+        <v>46.21</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.77</v>
+        <v>53.79</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>24</v>
+        <v>24.01</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>99.90000000000001</v>
@@ -22959,13 +22959,13 @@
         </is>
       </c>
       <c r="M217" s="4" t="n">
-        <v>17.33</v>
+        <v>17.34</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>24</v>
+        <v>24.01</v>
       </c>
       <c r="P217" s="4" t="n">
         <v>0</v>
@@ -22996,10 +22996,10 @@
         <v>0</v>
       </c>
       <c r="AB217" s="4" t="n">
-        <v>62</v>
+        <v>62.01</v>
       </c>
       <c r="AC217" s="4" t="n">
-        <v>38</v>
+        <v>37.99</v>
       </c>
       <c r="AD217" s="4" t="n">
         <v>0</v>
@@ -23047,7 +23047,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>33.62</v>
+        <v>33.63</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -23061,13 +23061,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>27.28</v>
+        <v>27.29</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>33.62</v>
+        <v>33.63</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -23098,10 +23098,10 @@
         <v>0</v>
       </c>
       <c r="AB218" s="4" t="n">
-        <v>66.81</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="AC218" s="4" t="n">
-        <v>33.19</v>
+        <v>33.18</v>
       </c>
       <c r="AD218" s="4" t="n">
         <v>0</v>
@@ -23149,7 +23149,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>32.18</v>
+        <v>32.19</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>100</v>
@@ -23163,13 +23163,13 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>22.78</v>
+        <v>22.79</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>32.18</v>
+        <v>32.19</v>
       </c>
       <c r="P219" s="4" t="n">
         <v>2.52</v>
@@ -23251,7 +23251,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>29.68</v>
+        <v>29.69</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>100</v>
@@ -23265,13 +23265,13 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.6</v>
+        <v>23.61</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O220" s="4" t="n">
-        <v>29.68</v>
+        <v>29.69</v>
       </c>
       <c r="P220" s="4" t="n">
         <v>0</v>
@@ -23353,7 +23353,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>55.3</v>
+        <v>55.31</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>100</v>
@@ -23367,13 +23367,13 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O221" s="4" t="n">
-        <v>55.3</v>
+        <v>55.31</v>
       </c>
       <c r="P221" s="4" t="n">
         <v>0</v>
@@ -23451,7 +23451,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>28.44</v>
+        <v>28.45</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>100</v>
@@ -23465,13 +23465,13 @@
         </is>
       </c>
       <c r="M222" s="4" t="n">
-        <v>23.81</v>
+        <v>23.82</v>
       </c>
       <c r="N222" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O222" s="4" t="n">
-        <v>28.44</v>
+        <v>28.45</v>
       </c>
       <c r="P222" s="4" t="n">
         <v>0</v>
@@ -23553,7 +23553,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>76.09</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -23567,13 +23567,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>68.97</v>
+        <v>68.98</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>76.09</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -23604,10 +23604,10 @@
         <v>0</v>
       </c>
       <c r="AB223" s="4" t="n">
-        <v>88.04000000000001</v>
+        <v>88.05</v>
       </c>
       <c r="AC223" s="4" t="n">
-        <v>11.96</v>
+        <v>11.95</v>
       </c>
       <c r="AD223" s="4" t="n">
         <v>0</v>
@@ -23655,7 +23655,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>45.41</v>
+        <v>45.42</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>100</v>
@@ -23669,13 +23669,13 @@
         </is>
       </c>
       <c r="M224" s="4" t="n">
-        <v>30.37</v>
+        <v>30.38</v>
       </c>
       <c r="N224" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O224" s="4" t="n">
-        <v>45.41</v>
+        <v>45.42</v>
       </c>
       <c r="P224" s="4" t="n">
         <v>0</v>
@@ -23706,10 +23706,10 @@
         <v>0</v>
       </c>
       <c r="AB224" s="4" t="n">
-        <v>72.7</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="AC224" s="4" t="n">
-        <v>27.3</v>
+        <v>27.29</v>
       </c>
       <c r="AD224" s="4" t="n">
         <v>0</v>
@@ -23757,7 +23757,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23771,13 +23771,13 @@
         </is>
       </c>
       <c r="M225" s="4" t="n">
-        <v>13.85</v>
+        <v>13.86</v>
       </c>
       <c r="N225" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.51</v>
@@ -23808,10 +23808,10 @@
         <v>0</v>
       </c>
       <c r="AB225" s="4" t="n">
-        <v>61.21</v>
+        <v>61.22</v>
       </c>
       <c r="AC225" s="4" t="n">
-        <v>38.79</v>
+        <v>38.78</v>
       </c>
       <c r="AD225" s="4" t="n">
         <v>0</v>
@@ -24667,7 +24667,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.83</v>
+        <v>30.96</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24681,13 +24681,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>22.31</v>
+        <v>22.29</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.26</v>
+        <v>31.25</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24718,10 +24718,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.35</v>
+        <v>62.34</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.65</v>
+        <v>32.66</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24765,13 +24765,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-3.65</v>
+        <v>-3.44</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>39.1</v>
+        <v>39.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>60.9</v>
+        <v>60.4</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24779,13 +24779,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-8.84</v>
+        <v>-8.85</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.19</v>
+        <v>-5.2</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24822,10 +24822,10 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>45.48</v>
+        <v>45.47</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>49.52</v>
+        <v>49.53</v>
       </c>
       <c r="AD235" s="4" t="n">
         <v>5</v>
@@ -24873,7 +24873,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>-12.75</v>
+        <v>-12.78</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>1</v>
@@ -24887,13 +24887,13 @@
         </is>
       </c>
       <c r="M236" s="4" t="n">
-        <v>-17.24</v>
+        <v>-17.27</v>
       </c>
       <c r="N236" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O236" s="4" t="n">
-        <v>-12.75</v>
+        <v>-12.78</v>
       </c>
       <c r="P236" s="4" t="n">
         <v>-0.61</v>
@@ -24924,10 +24924,10 @@
         <v>0</v>
       </c>
       <c r="AB236" s="4" t="n">
-        <v>43.62</v>
+        <v>43.61</v>
       </c>
       <c r="AC236" s="4" t="n">
-        <v>56.38</v>
+        <v>56.39</v>
       </c>
       <c r="AD236" s="4" t="n">
         <v>0</v>
@@ -24975,7 +24975,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>-27.7</v>
+        <v>-27.72</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>0</v>
@@ -24989,13 +24989,13 @@
         </is>
       </c>
       <c r="M237" s="4" t="n">
-        <v>-25.91</v>
+        <v>-25.93</v>
       </c>
       <c r="N237" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O237" s="4" t="n">
-        <v>-27.7</v>
+        <v>-27.72</v>
       </c>
       <c r="P237" s="4" t="n">
         <v>-1.9</v>
@@ -25026,10 +25026,10 @@
         <v>0</v>
       </c>
       <c r="AB237" s="4" t="n">
-        <v>36.15</v>
+        <v>36.14</v>
       </c>
       <c r="AC237" s="4" t="n">
-        <v>63.85</v>
+        <v>63.86</v>
       </c>
       <c r="AD237" s="4" t="n">
         <v>0</v>
@@ -25077,7 +25077,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>20.73</v>
+        <v>20.71</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25091,13 +25091,13 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>11.75</v>
+        <v>11.73</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>20.73</v>
+        <v>20.71</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>0</v>
@@ -25128,10 +25128,10 @@
         <v>0</v>
       </c>
       <c r="AB238" s="4" t="n">
-        <v>60.37</v>
+        <v>60.36</v>
       </c>
       <c r="AC238" s="4" t="n">
-        <v>39.63</v>
+        <v>39.64</v>
       </c>
       <c r="AD238" s="4" t="n">
         <v>0</v>
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>-1.54</v>
+        <v>-1.56</v>
       </c>
       <c r="J239" s="4" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -25193,13 +25193,13 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-1.41</v>
+        <v>-1.43</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-2.04</v>
+        <v>-2.07</v>
       </c>
       <c r="P239" s="4" t="n">
         <v>-0.31</v>
@@ -25236,10 +25236,10 @@
         <v>0</v>
       </c>
       <c r="AB239" s="4" t="n">
-        <v>49.23</v>
+        <v>49.22</v>
       </c>
       <c r="AC239" s="4" t="n">
-        <v>50.77</v>
+        <v>50.78</v>
       </c>
       <c r="AD239" s="4" t="n">
         <v>0</v>
@@ -25287,7 +25287,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-25.5</v>
+        <v>-25.52</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0.1</v>
@@ -25301,13 +25301,13 @@
         </is>
       </c>
       <c r="M240" s="4" t="n">
-        <v>-22.61</v>
+        <v>-22.64</v>
       </c>
       <c r="N240" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-25.5</v>
+        <v>-25.52</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.14</v>
@@ -25338,10 +25338,10 @@
         <v>0</v>
       </c>
       <c r="AB240" s="4" t="n">
-        <v>37.25</v>
+        <v>37.24</v>
       </c>
       <c r="AC240" s="4" t="n">
-        <v>62.75</v>
+        <v>62.76</v>
       </c>
       <c r="AD240" s="4" t="n">
         <v>0</v>
@@ -25389,7 +25389,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>38.68</v>
+        <v>38.66</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -25403,13 +25403,13 @@
         </is>
       </c>
       <c r="M241" s="4" t="n">
-        <v>28.57</v>
+        <v>28.55</v>
       </c>
       <c r="N241" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>38.68</v>
+        <v>38.66</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -25440,10 +25440,10 @@
         <v>0</v>
       </c>
       <c r="AB241" s="4" t="n">
-        <v>69.34</v>
+        <v>69.33</v>
       </c>
       <c r="AC241" s="4" t="n">
-        <v>30.66</v>
+        <v>30.67</v>
       </c>
       <c r="AD241" s="4" t="n">
         <v>0</v>
@@ -25505,13 +25505,13 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O242" s="4" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="P242" s="4" t="n">
         <v>-0.62</v>
@@ -25599,7 +25599,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>19.09</v>
+        <v>19.07</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>99.7</v>
@@ -25613,13 +25613,13 @@
         </is>
       </c>
       <c r="M243" s="4" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N243" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>19.09</v>
+        <v>19.07</v>
       </c>
       <c r="P243" s="4" t="n">
         <v>1.52</v>
@@ -25650,10 +25650,10 @@
         <v>0</v>
       </c>
       <c r="AB243" s="4" t="n">
-        <v>59.54</v>
+        <v>59.53</v>
       </c>
       <c r="AC243" s="4" t="n">
-        <v>40.46</v>
+        <v>40.47</v>
       </c>
       <c r="AD243" s="4" t="n">
         <v>0</v>
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-32.48</v>
+        <v>-32.5</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -25715,13 +25715,13 @@
         </is>
       </c>
       <c r="M244" s="4" t="n">
-        <v>-28.14</v>
+        <v>-28.17</v>
       </c>
       <c r="N244" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-32.48</v>
+        <v>-32.5</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -25752,10 +25752,10 @@
         <v>0</v>
       </c>
       <c r="AB244" s="4" t="n">
-        <v>33.76</v>
+        <v>33.75</v>
       </c>
       <c r="AC244" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="AD244" s="4" t="n">
         <v>0</v>
@@ -25799,7 +25799,7 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="J245" s="4" t="n">
         <v>70.90000000000001</v>
@@ -25813,13 +25813,13 @@
         </is>
       </c>
       <c r="M245" s="4" t="n">
-        <v>-1.35</v>
+        <v>-1.37</v>
       </c>
       <c r="N245" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O245" s="4" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="P245" s="4" t="n">
         <v>-0.11</v>
@@ -25856,10 +25856,10 @@
         <v>0</v>
       </c>
       <c r="AB245" s="4" t="n">
-        <v>51.17</v>
+        <v>51.16</v>
       </c>
       <c r="AC245" s="4" t="n">
-        <v>48.83</v>
+        <v>48.84</v>
       </c>
       <c r="AD245" s="4" t="n">
         <v>0</v>
@@ -25903,7 +25903,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>27.8</v>
+        <v>27.77</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>100</v>
@@ -25917,13 +25917,13 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>21.19</v>
+        <v>21.17</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O246" s="4" t="n">
-        <v>27.8</v>
+        <v>27.77</v>
       </c>
       <c r="P246" s="4" t="n">
         <v>2.12</v>
@@ -25954,10 +25954,10 @@
         <v>0</v>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>63.9</v>
+        <v>63.89</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>36.1</v>
+        <v>36.11</v>
       </c>
       <c r="AD246" s="4" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>56.35</v>
+        <v>56.32</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -26019,13 +26019,13 @@
         </is>
       </c>
       <c r="M247" s="4" t="n">
-        <v>46.24</v>
+        <v>46.21</v>
       </c>
       <c r="N247" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O247" s="4" t="n">
-        <v>56.35</v>
+        <v>56.32</v>
       </c>
       <c r="P247" s="4" t="n">
         <v>0</v>
@@ -26056,10 +26056,10 @@
         <v>0</v>
       </c>
       <c r="AB247" s="4" t="n">
-        <v>78.17</v>
+        <v>78.16</v>
       </c>
       <c r="AC247" s="4" t="n">
-        <v>21.83</v>
+        <v>21.84</v>
       </c>
       <c r="AD247" s="4" t="n">
         <v>0</v>
@@ -26107,7 +26107,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>59.05</v>
+        <v>59.03</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -26121,13 +26121,13 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>48.73</v>
+        <v>48.71</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>59.05</v>
+        <v>59.03</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
@@ -26158,10 +26158,10 @@
         <v>0</v>
       </c>
       <c r="AB248" s="4" t="n">
-        <v>79.52</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="AC248" s="4" t="n">
-        <v>20.48</v>
+        <v>20.49</v>
       </c>
       <c r="AD248" s="4" t="n">
         <v>0</v>
@@ -26209,13 +26209,13 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>-6.09</v>
+        <v>-6.12</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="K249" s="4" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -26223,13 +26223,13 @@
         </is>
       </c>
       <c r="M249" s="4" t="n">
-        <v>-9.08</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="N249" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O249" s="4" t="n">
-        <v>-6.34</v>
+        <v>-6.37</v>
       </c>
       <c r="P249" s="4" t="n">
         <v>-0.02</v>
@@ -26266,10 +26266,10 @@
         <v>0</v>
       </c>
       <c r="AB249" s="4" t="n">
-        <v>46.95</v>
+        <v>46.94</v>
       </c>
       <c r="AC249" s="4" t="n">
-        <v>53.05</v>
+        <v>53.06</v>
       </c>
       <c r="AD249" s="4" t="n">
         <v>0</v>
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>11.67</v>
+        <v>11.68</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>98.8</v>
@@ -26327,13 +26327,13 @@
         </is>
       </c>
       <c r="M250" s="4" t="n">
-        <v>8.550000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="N250" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O250" s="4" t="n">
-        <v>13.5</v>
+        <v>13.47</v>
       </c>
       <c r="P250" s="4" t="n">
         <v>0.47</v>
@@ -26370,10 +26370,10 @@
         <v>0</v>
       </c>
       <c r="AB250" s="4" t="n">
-        <v>55.83</v>
+        <v>55.84</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>44.17</v>
+        <v>44.16</v>
       </c>
       <c r="AD250" s="4" t="n">
         <v>0</v>
@@ -26421,7 +26421,7 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>29.91</v>
+        <v>29.88</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>100</v>
@@ -26435,13 +26435,13 @@
         </is>
       </c>
       <c r="M251" s="4" t="n">
-        <v>23.83</v>
+        <v>23.79</v>
       </c>
       <c r="N251" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O251" s="4" t="n">
-        <v>29.91</v>
+        <v>29.88</v>
       </c>
       <c r="P251" s="4" t="n">
         <v>0</v>
@@ -26472,10 +26472,10 @@
         <v>0</v>
       </c>
       <c r="AB251" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="AC251" s="4" t="n">
-        <v>35.04</v>
+        <v>35.06</v>
       </c>
       <c r="AD251" s="4" t="n">
         <v>0</v>
@@ -26523,7 +26523,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>47.7</v>
+        <v>47.66</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>100</v>
@@ -26537,13 +26537,13 @@
         </is>
       </c>
       <c r="M252" s="4" t="n">
-        <v>39.52</v>
+        <v>39.49</v>
       </c>
       <c r="N252" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O252" s="4" t="n">
-        <v>47.7</v>
+        <v>47.66</v>
       </c>
       <c r="P252" s="4" t="n">
         <v>2.14</v>
@@ -26574,10 +26574,10 @@
         <v>0</v>
       </c>
       <c r="AB252" s="4" t="n">
-        <v>73.84999999999999</v>
+        <v>73.83</v>
       </c>
       <c r="AC252" s="4" t="n">
-        <v>26.15</v>
+        <v>26.17</v>
       </c>
       <c r="AD252" s="4" t="n">
         <v>0</v>
@@ -26625,7 +26625,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>65.83</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>100</v>
@@ -26639,13 +26639,13 @@
         </is>
       </c>
       <c r="M253" s="4" t="n">
-        <v>66.34999999999999</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="N253" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O253" s="4" t="n">
-        <v>65.83</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="P253" s="4" t="n">
         <v>1.22</v>
@@ -26676,10 +26676,10 @@
         <v>0</v>
       </c>
       <c r="AB253" s="4" t="n">
-        <v>82.91</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AC253" s="4" t="n">
-        <v>17.09</v>
+        <v>17.1</v>
       </c>
       <c r="AD253" s="4" t="n">
         <v>0</v>
@@ -26727,7 +26727,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-14.65</v>
+        <v>-14.68</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>0.7</v>
@@ -26741,13 +26741,13 @@
         </is>
       </c>
       <c r="M254" s="4" t="n">
-        <v>-17.26</v>
+        <v>-17.3</v>
       </c>
       <c r="N254" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-14.65</v>
+        <v>-14.68</v>
       </c>
       <c r="P254" s="4" t="n">
         <v>0</v>
@@ -26778,10 +26778,10 @@
         <v>0</v>
       </c>
       <c r="AB254" s="4" t="n">
-        <v>42.68</v>
+        <v>42.66</v>
       </c>
       <c r="AC254" s="4" t="n">
-        <v>57.32</v>
+        <v>57.34</v>
       </c>
       <c r="AD254" s="4" t="n">
         <v>0</v>
@@ -26829,7 +26829,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>-30.99</v>
+        <v>-31.02</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>0</v>
@@ -26843,13 +26843,13 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-33.61</v>
+        <v>-33.64</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O255" s="4" t="n">
-        <v>-30.99</v>
+        <v>-31.02</v>
       </c>
       <c r="P255" s="4" t="n">
         <v>0</v>
@@ -26880,10 +26880,10 @@
         <v>0</v>
       </c>
       <c r="AB255" s="4" t="n">
-        <v>34.51</v>
+        <v>34.49</v>
       </c>
       <c r="AC255" s="4" t="n">
-        <v>65.48999999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="AD255" s="4" t="n">
         <v>0</v>
@@ -26931,13 +26931,13 @@
         </is>
       </c>
       <c r="I256" s="4" t="n">
-        <v>-8.67</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="J256" s="4" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="K256" s="4" t="n">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -26945,13 +26945,13 @@
         </is>
       </c>
       <c r="M256" s="4" t="n">
-        <v>-11.07</v>
+        <v>-11.11</v>
       </c>
       <c r="N256" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O256" s="4" t="n">
-        <v>-8.67</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P256" s="4" t="n">
         <v>0</v>
@@ -26982,10 +26982,10 @@
         <v>0</v>
       </c>
       <c r="AB256" s="4" t="n">
-        <v>45.67</v>
+        <v>45.65</v>
       </c>
       <c r="AC256" s="4" t="n">
-        <v>54.33</v>
+        <v>54.35</v>
       </c>
       <c r="AD256" s="4" t="n">
         <v>0</v>
@@ -27135,13 +27135,13 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.6</v>
+        <v>-10.61</v>
       </c>
       <c r="J258" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K258" s="4" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -27192,10 +27192,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.7</v>
+        <v>44.69</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.3</v>
+        <v>55.31</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -28255,13 +28255,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-5.98</v>
+        <v>-5.9</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28269,13 +28269,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-10.93</v>
+        <v>-11.02</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-6.93</v>
+        <v>-7.02</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28287,16 +28287,16 @@
         <v>-11.92</v>
       </c>
       <c r="S269" s="4" t="n">
-        <v>43.78</v>
+        <v>43.87</v>
       </c>
       <c r="T269" s="4" t="n">
-        <v>44.86</v>
+        <v>44.5</v>
       </c>
       <c r="U269" t="n">
         <v>2</v>
       </c>
       <c r="V269" s="4" t="n">
-        <v>-4.08</v>
+        <v>-3.63</v>
       </c>
       <c r="W269" s="5" t="n">
         <v>1382873</v>
@@ -28312,10 +28312,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>47.01</v>
+        <v>47.05</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>52.99</v>
+        <v>52.95</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28363,7 +28363,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-32.67</v>
+        <v>-32.75</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28377,13 +28377,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-29.9</v>
+        <v>-29.98</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-32.67</v>
+        <v>-32.75</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28414,10 +28414,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.67</v>
+        <v>33.62</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.33</v>
+        <v>66.38</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28465,7 +28465,7 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="J271" s="4" t="n">
         <v>71.8</v>
@@ -29497,13 +29497,13 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>-5.55</v>
+        <v>-5.02</v>
       </c>
       <c r="J281" s="4" t="n">
-        <v>17.2</v>
+        <v>19.1</v>
       </c>
       <c r="K281" s="4" t="n">
-        <v>82.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -29528,12 +29528,18 @@
       <c r="R281" s="4" t="n">
         <v>-9.609999999999999</v>
       </c>
-      <c r="S281" s="4" t="n"/>
-      <c r="T281" s="4" t="n"/>
+      <c r="S281" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T281" s="4" t="n">
+        <v>44</v>
+      </c>
       <c r="U281" t="n">
-        <v>0</v>
-      </c>
-      <c r="V281" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V281" s="4" t="n">
+        <v>-2</v>
+      </c>
       <c r="W281" s="5" t="n">
         <v>3052354</v>
       </c>
@@ -29548,10 +29554,10 @@
         <v>0</v>
       </c>
       <c r="AB281" s="4" t="n">
-        <v>47.23</v>
+        <v>47.49</v>
       </c>
       <c r="AC281" s="4" t="n">
-        <v>52.77</v>
+        <v>52.51</v>
       </c>
       <c r="AD281" s="4" t="n">
         <v>0</v>
@@ -30013,13 +30019,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.66</v>
+        <v>-9.68</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30027,13 +30033,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.92</v>
+        <v>-8.94</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-10.29</v>
+        <v>-10.3</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30070,10 +30076,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.17</v>
+        <v>45.16</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.83</v>
+        <v>54.84</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30117,7 +30123,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.47</v>
+        <v>12.45</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>98.90000000000001</v>
@@ -30131,13 +30137,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.14</v>
+        <v>14.12</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30174,10 +30180,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.23</v>
+        <v>56.22</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.77</v>
+        <v>43.78</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30225,7 +30231,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.83</v>
+        <v>-52.85</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30239,13 +30245,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.87</v>
+        <v>-49.89</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.83</v>
+        <v>-52.85</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30276,10 +30282,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.58</v>
+        <v>23.57</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.42</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -30337,7 +30343,7 @@
         </is>
       </c>
       <c r="M289" s="4" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="N289" s="4" t="n">
         <v>5.13</v>
@@ -30374,10 +30380,10 @@
         <v>0</v>
       </c>
       <c r="AB289" s="4" t="n">
-        <v>52.54</v>
+        <v>52.53</v>
       </c>
       <c r="AC289" s="4" t="n">
-        <v>47.46</v>
+        <v>47.47</v>
       </c>
       <c r="AD289" s="4" t="n">
         <v>0</v>
@@ -30425,7 +30431,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>16.05</v>
+        <v>16.04</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>99.5</v>
@@ -30439,7 +30445,7 @@
         </is>
       </c>
       <c r="M290" s="4" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="N290" s="4" t="n">
         <v>5.13</v>
@@ -30482,10 +30488,10 @@
         <v>0</v>
       </c>
       <c r="AB290" s="4" t="n">
-        <v>58.03</v>
+        <v>58.02</v>
       </c>
       <c r="AC290" s="4" t="n">
-        <v>41.97</v>
+        <v>41.98</v>
       </c>
       <c r="AD290" s="4" t="n">
         <v>0</v>
@@ -31151,13 +31157,13 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="J297" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K297" s="4" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -31208,10 +31214,10 @@
         <v>0</v>
       </c>
       <c r="AB297" s="4" t="n">
-        <v>52.23</v>
+        <v>52.24</v>
       </c>
       <c r="AC297" s="4" t="n">
-        <v>47.77</v>
+        <v>47.76</v>
       </c>
       <c r="AD297" s="4" t="n">
         <v>0</v>
@@ -31765,7 +31771,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>25.79</v>
+        <v>25.8</v>
       </c>
       <c r="J303" s="4" t="n">
         <v>100</v>
@@ -31779,13 +31785,13 @@
         </is>
       </c>
       <c r="M303" s="4" t="n">
-        <v>15.78</v>
+        <v>15.79</v>
       </c>
       <c r="N303" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O303" s="4" t="n">
-        <v>25.79</v>
+        <v>25.8</v>
       </c>
       <c r="P303" s="4" t="n">
         <v>1.68</v>
@@ -31867,7 +31873,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>14.17</v>
+        <v>14.2</v>
       </c>
       <c r="J304" s="4" t="n">
         <v>99.2</v>
@@ -31881,13 +31887,13 @@
         </is>
       </c>
       <c r="M304" s="4" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="N304" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O304" s="4" t="n">
-        <v>16.2</v>
+        <v>16.22</v>
       </c>
       <c r="P304" s="4" t="n">
         <v>0.67</v>
@@ -31924,10 +31930,10 @@
         <v>0</v>
       </c>
       <c r="AB304" s="4" t="n">
-        <v>57.08</v>
+        <v>57.1</v>
       </c>
       <c r="AC304" s="4" t="n">
-        <v>42.92</v>
+        <v>42.9</v>
       </c>
       <c r="AD304" s="4" t="n">
         <v>0</v>
@@ -31975,7 +31981,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>22.81</v>
+        <v>22.82</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>99.90000000000001</v>
@@ -31989,13 +31995,13 @@
         </is>
       </c>
       <c r="M305" s="4" t="n">
-        <v>9.539999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N305" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O305" s="4" t="n">
-        <v>22.81</v>
+        <v>22.82</v>
       </c>
       <c r="P305" s="4" t="n">
         <v>0.73</v>
@@ -32026,10 +32032,10 @@
         <v>0</v>
       </c>
       <c r="AB305" s="4" t="n">
-        <v>61.4</v>
+        <v>61.41</v>
       </c>
       <c r="AC305" s="4" t="n">
-        <v>38.6</v>
+        <v>38.59</v>
       </c>
       <c r="AD305" s="4" t="n">
         <v>0</v>
@@ -32091,7 +32097,7 @@
         </is>
       </c>
       <c r="M306" s="4" t="n">
-        <v>5.39</v>
+        <v>5.4</v>
       </c>
       <c r="N306" s="4" t="n">
         <v>5.13</v>
@@ -32175,13 +32181,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-3.54</v>
+        <v>-3.63</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>75.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -32195,7 +32201,7 @@
         <v>5.13</v>
       </c>
       <c r="O307" s="4" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="P307" s="4" t="n">
         <v>-1.32</v>
@@ -32232,10 +32238,10 @@
         <v>0</v>
       </c>
       <c r="AB307" s="4" t="n">
-        <v>48.23</v>
+        <v>48.18</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>51.77</v>
+        <v>51.82</v>
       </c>
       <c r="AD307" s="4" t="n">
         <v>0</v>
@@ -32334,10 +32340,10 @@
         <v>0</v>
       </c>
       <c r="AB308" s="4" t="n">
-        <v>55.82</v>
+        <v>55.83</v>
       </c>
       <c r="AC308" s="4" t="n">
-        <v>44.18</v>
+        <v>44.17</v>
       </c>
       <c r="AD308" s="4" t="n">
         <v>0</v>
@@ -32799,13 +32805,13 @@
         </is>
       </c>
       <c r="I313" s="4" t="n">
-        <v>15.53</v>
+        <v>15.08</v>
       </c>
       <c r="J313" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="K313" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -32840,7 +32846,7 @@
         <v>1</v>
       </c>
       <c r="V313" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W313" s="5" t="n">
         <v>5097222</v>
@@ -32856,10 +32862,10 @@
         <v>0</v>
       </c>
       <c r="AB313" s="4" t="n">
-        <v>57.76</v>
+        <v>57.54</v>
       </c>
       <c r="AC313" s="4" t="n">
-        <v>42.24</v>
+        <v>42.46</v>
       </c>
       <c r="AD313" s="4" t="n">
         <v>0</v>
@@ -34115,13 +34121,13 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="J326" s="4" t="n">
-        <v>71</v>
+        <v>70.8</v>
       </c>
       <c r="K326" s="4" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -34147,16 +34153,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="S326" s="4" t="n">
-        <v>47.21</v>
+        <v>47.26</v>
       </c>
       <c r="T326" s="4" t="n">
-        <v>47.59</v>
+        <v>47.73</v>
       </c>
       <c r="U326" t="n">
         <v>3</v>
       </c>
       <c r="V326" s="4" t="n">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="W326" s="5" t="n">
         <v>4317457</v>
@@ -34172,10 +34178,10 @@
         <v>0</v>
       </c>
       <c r="AB326" s="4" t="n">
-        <v>51.18</v>
+        <v>51.15</v>
       </c>
       <c r="AC326" s="4" t="n">
-        <v>48.82</v>
+        <v>48.85</v>
       </c>
       <c r="AD326" s="4" t="n">
         <v>0</v>
@@ -34223,13 +34229,13 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>17.1</v>
+        <v>16.65</v>
       </c>
       <c r="J327" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="K327" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -34264,7 +34270,7 @@
         <v>1</v>
       </c>
       <c r="V327" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W327" s="5" t="n">
         <v>4723627</v>
@@ -34280,10 +34286,10 @@
         <v>0</v>
       </c>
       <c r="AB327" s="4" t="n">
-        <v>58.55</v>
+        <v>58.32</v>
       </c>
       <c r="AC327" s="4" t="n">
-        <v>41.45</v>
+        <v>41.68</v>
       </c>
       <c r="AD327" s="4" t="n">
         <v>0</v>
@@ -34531,13 +34537,13 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-12.49</v>
+        <v>-12.53</v>
       </c>
       <c r="J330" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K330" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -34588,10 +34594,10 @@
         <v>0</v>
       </c>
       <c r="AB330" s="4" t="n">
-        <v>43.75</v>
+        <v>43.73</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>56.25</v>
+        <v>56.27</v>
       </c>
       <c r="AD330" s="4" t="n">
         <v>0</v>
@@ -35761,13 +35767,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-6.59</v>
+        <v>-6.61</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35818,10 +35824,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>46.7</v>
+        <v>46.69</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>53.3</v>
+        <v>53.31</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -35971,13 +35977,13 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>9.17</v>
+        <v>9.18</v>
       </c>
       <c r="J344" s="4" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="K344" s="4" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -36028,10 +36034,10 @@
         <v>0</v>
       </c>
       <c r="AB344" s="4" t="n">
-        <v>54.58</v>
+        <v>54.59</v>
       </c>
       <c r="AC344" s="4" t="n">
-        <v>45.42</v>
+        <v>45.41</v>
       </c>
       <c r="AD344" s="4" t="n">
         <v>0</v>
@@ -36079,13 +36085,13 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-7.96</v>
+        <v>-8</v>
       </c>
       <c r="J345" s="4" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="K345" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -36136,10 +36142,10 @@
         <v>0</v>
       </c>
       <c r="AB345" s="4" t="n">
-        <v>46.02</v>
+        <v>46</v>
       </c>
       <c r="AC345" s="4" t="n">
-        <v>53.98</v>
+        <v>54</v>
       </c>
       <c r="AD345" s="4" t="n">
         <v>0</v>
@@ -37254,10 +37260,10 @@
         <v>0</v>
       </c>
       <c r="AB356" s="4" t="n">
-        <v>74.62</v>
+        <v>74.63</v>
       </c>
       <c r="AC356" s="4" t="n">
-        <v>25.38</v>
+        <v>25.37</v>
       </c>
       <c r="AD356" s="4" t="n">
         <v>0</v>
@@ -37305,7 +37311,7 @@
         </is>
       </c>
       <c r="I357" s="4" t="n">
-        <v>-29.23</v>
+        <v>-29.22</v>
       </c>
       <c r="J357" s="4" t="n">
         <v>0</v>
@@ -37325,7 +37331,7 @@
         <v>5.13</v>
       </c>
       <c r="O357" s="4" t="n">
-        <v>-29.23</v>
+        <v>-29.22</v>
       </c>
       <c r="P357" s="4" t="n">
         <v>-1.49</v>
@@ -37421,7 +37427,7 @@
         </is>
       </c>
       <c r="M358" s="4" t="n">
-        <v>47.14</v>
+        <v>47.15</v>
       </c>
       <c r="N358" s="4" t="n">
         <v>5.13</v>
@@ -37611,7 +37617,7 @@
         </is>
       </c>
       <c r="I360" s="4" t="n">
-        <v>16.41</v>
+        <v>16.42</v>
       </c>
       <c r="J360" s="4" t="n">
         <v>99.5</v>
@@ -37625,13 +37631,13 @@
         </is>
       </c>
       <c r="M360" s="4" t="n">
-        <v>7.87</v>
+        <v>7.88</v>
       </c>
       <c r="N360" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O360" s="4" t="n">
-        <v>16.41</v>
+        <v>16.42</v>
       </c>
       <c r="P360" s="4" t="n">
         <v>1.57</v>
@@ -37713,7 +37719,7 @@
         </is>
       </c>
       <c r="I361" s="4" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>99.59999999999999</v>
@@ -37733,7 +37739,7 @@
         <v>5.13</v>
       </c>
       <c r="O361" s="4" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
       <c r="P361" s="4" t="n">
         <v>2.46</v>
@@ -37818,10 +37824,10 @@
         <v>-2.16</v>
       </c>
       <c r="J362" s="4" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="K362" s="4" t="n">
-        <v>70.3</v>
+        <v>70.2</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -38021,7 +38027,7 @@
         </is>
       </c>
       <c r="I364" s="4" t="n">
-        <v>91.84</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="J364" s="4" t="n">
         <v>100</v>
@@ -38041,7 +38047,7 @@
         <v>5.13</v>
       </c>
       <c r="O364" s="4" t="n">
-        <v>91.84</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P364" s="4" t="n">
         <v>2.85</v>
@@ -38123,7 +38129,7 @@
         </is>
       </c>
       <c r="I365" s="4" t="n">
-        <v>29.35</v>
+        <v>29.36</v>
       </c>
       <c r="J365" s="4" t="n">
         <v>100</v>
@@ -38143,7 +38149,7 @@
         <v>5.13</v>
       </c>
       <c r="O365" s="4" t="n">
-        <v>29.35</v>
+        <v>29.36</v>
       </c>
       <c r="P365" s="4" t="n">
         <v>0</v>
@@ -38225,7 +38231,7 @@
         </is>
       </c>
       <c r="I366" s="4" t="n">
-        <v>42.15</v>
+        <v>42.16</v>
       </c>
       <c r="J366" s="4" t="n">
         <v>100</v>
@@ -38245,7 +38251,7 @@
         <v>5.13</v>
       </c>
       <c r="O366" s="4" t="n">
-        <v>42.15</v>
+        <v>42.16</v>
       </c>
       <c r="P366" s="4" t="n">
         <v>0</v>
@@ -38378,10 +38384,10 @@
         <v>0</v>
       </c>
       <c r="AB367" s="4" t="n">
-        <v>62.82</v>
+        <v>62.83</v>
       </c>
       <c r="AC367" s="4" t="n">
-        <v>37.18</v>
+        <v>37.17</v>
       </c>
       <c r="AD367" s="4" t="n">
         <v>0</v>
@@ -38429,13 +38435,13 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="J368" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K368" s="4" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -38443,7 +38449,7 @@
         </is>
       </c>
       <c r="M368" s="4" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="N368" s="4" t="n">
         <v>5.13</v>
@@ -38486,10 +38492,10 @@
         <v>0</v>
       </c>
       <c r="AB368" s="4" t="n">
-        <v>51.12</v>
+        <v>51.13</v>
       </c>
       <c r="AC368" s="4" t="n">
-        <v>48.88</v>
+        <v>48.87</v>
       </c>
       <c r="AD368" s="4" t="n">
         <v>0</v>
@@ -38537,7 +38543,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>65</v>
@@ -38551,13 +38557,13 @@
         </is>
       </c>
       <c r="M369" s="4" t="n">
-        <v>-2.85</v>
+        <v>-2.84</v>
       </c>
       <c r="N369" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O369" s="4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="P369" s="4" t="n">
         <v>-0.09</v>
@@ -38798,10 +38804,10 @@
         <v>0</v>
       </c>
       <c r="AB371" s="4" t="n">
-        <v>54.33</v>
+        <v>54.34</v>
       </c>
       <c r="AC371" s="4" t="n">
-        <v>45.67</v>
+        <v>45.66</v>
       </c>
       <c r="AD371" s="4" t="n">
         <v>0</v>
@@ -39067,7 +39073,7 @@
         </is>
       </c>
       <c r="M374" s="4" t="n">
-        <v>-41.32</v>
+        <v>-41.31</v>
       </c>
       <c r="N374" s="4" t="n">
         <v>5.13</v>
@@ -39155,7 +39161,7 @@
         </is>
       </c>
       <c r="I375" s="4" t="n">
-        <v>-27.48</v>
+        <v>-27.47</v>
       </c>
       <c r="J375" s="4" t="n">
         <v>0</v>
@@ -39175,7 +39181,7 @@
         <v>5.13</v>
       </c>
       <c r="O375" s="4" t="n">
-        <v>-27.48</v>
+        <v>-27.47</v>
       </c>
       <c r="P375" s="4" t="n">
         <v>-2.12</v>
@@ -39257,7 +39263,7 @@
         </is>
       </c>
       <c r="I376" s="4" t="n">
-        <v>-35</v>
+        <v>-34.99</v>
       </c>
       <c r="J376" s="4" t="n">
         <v>0</v>
@@ -39277,7 +39283,7 @@
         <v>5.13</v>
       </c>
       <c r="O376" s="4" t="n">
-        <v>-35</v>
+        <v>-34.99</v>
       </c>
       <c r="P376" s="4" t="n">
         <v>-1.73</v>
@@ -39563,7 +39569,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>40.37</v>
+        <v>40.38</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -39577,13 +39583,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>27.08</v>
+        <v>27.1</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>40.37</v>
+        <v>40.38</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>0</v>
@@ -39614,10 +39620,10 @@
         <v>0</v>
       </c>
       <c r="AB379" s="4" t="n">
-        <v>70.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>29.82</v>
+        <v>29.81</v>
       </c>
       <c r="AD379" s="4" t="n">
         <v>0</v>
@@ -39665,7 +39671,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>17.08</v>
+        <v>17.09</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39679,13 +39685,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>11.22</v>
+        <v>11.24</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>17.08</v>
+        <v>17.09</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.61</v>
@@ -39716,10 +39722,10 @@
         <v>0</v>
       </c>
       <c r="AB380" s="4" t="n">
-        <v>58.54</v>
+        <v>58.55</v>
       </c>
       <c r="AC380" s="4" t="n">
-        <v>41.46</v>
+        <v>41.45</v>
       </c>
       <c r="AD380" s="4" t="n">
         <v>0</v>
@@ -40979,7 +40985,7 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-13.72</v>
+        <v>-13.73</v>
       </c>
       <c r="J393" s="4" t="n">
         <v>0.8</v>
@@ -41036,10 +41042,10 @@
         <v>0</v>
       </c>
       <c r="AB393" s="4" t="n">
-        <v>43.14</v>
+        <v>43.13</v>
       </c>
       <c r="AC393" s="4" t="n">
-        <v>56.86</v>
+        <v>56.87</v>
       </c>
       <c r="AD393" s="4" t="n">
         <v>0</v>
@@ -41585,7 +41591,7 @@
         </is>
       </c>
       <c r="I399" s="4" t="n">
-        <v>-12.99</v>
+        <v>-13</v>
       </c>
       <c r="J399" s="4" t="n">
         <v>1</v>
@@ -41599,13 +41605,13 @@
         </is>
       </c>
       <c r="M399" s="4" t="n">
-        <v>-19.47</v>
+        <v>-19.48</v>
       </c>
       <c r="N399" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O399" s="4" t="n">
-        <v>-12.99</v>
+        <v>-13</v>
       </c>
       <c r="P399" s="4" t="n">
         <v>0.88</v>
@@ -41789,7 +41795,7 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>-21.51</v>
+        <v>-21.52</v>
       </c>
       <c r="J401" s="4" t="n">
         <v>0.2</v>
@@ -41803,13 +41809,13 @@
         </is>
       </c>
       <c r="M401" s="4" t="n">
-        <v>-20.12</v>
+        <v>-20.13</v>
       </c>
       <c r="N401" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O401" s="4" t="n">
-        <v>-21.51</v>
+        <v>-21.52</v>
       </c>
       <c r="P401" s="4" t="n">
         <v>-1.91</v>
@@ -41905,7 +41911,7 @@
         </is>
       </c>
       <c r="M402" s="4" t="n">
-        <v>-16.96</v>
+        <v>-16.97</v>
       </c>
       <c r="N402" s="4" t="n">
         <v>5.13</v>
@@ -42193,7 +42199,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-18.62</v>
+        <v>-18.63</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.3</v>
@@ -42207,13 +42213,13 @@
         </is>
       </c>
       <c r="M405" s="4" t="n">
-        <v>-21.75</v>
+        <v>-21.76</v>
       </c>
       <c r="N405" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-18.62</v>
+        <v>-18.63</v>
       </c>
       <c r="P405" s="4" t="n">
         <v>-2.83</v>
@@ -42440,10 +42446,10 @@
         <v>0</v>
       </c>
       <c r="AB407" s="4" t="n">
-        <v>43.14</v>
+        <v>43.13</v>
       </c>
       <c r="AC407" s="4" t="n">
-        <v>56.86</v>
+        <v>56.87</v>
       </c>
       <c r="AD407" s="4" t="n">
         <v>0</v>
@@ -42542,10 +42548,10 @@
         <v>0</v>
       </c>
       <c r="AB408" s="4" t="n">
-        <v>35.96</v>
+        <v>35.95</v>
       </c>
       <c r="AC408" s="4" t="n">
-        <v>64.04000000000001</v>
+        <v>64.05</v>
       </c>
       <c r="AD408" s="4" t="n">
         <v>0</v>
@@ -42593,7 +42599,7 @@
         </is>
       </c>
       <c r="I409" s="4" t="n">
-        <v>-19.44</v>
+        <v>-19.45</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>0.3</v>
@@ -42613,7 +42619,7 @@
         <v>5.13</v>
       </c>
       <c r="O409" s="4" t="n">
-        <v>-19.44</v>
+        <v>-19.45</v>
       </c>
       <c r="P409" s="4" t="n">
         <v>0</v>
@@ -42811,7 +42817,7 @@
         </is>
       </c>
       <c r="M411" s="4" t="n">
-        <v>-20.1</v>
+        <v>-20.11</v>
       </c>
       <c r="N411" s="4" t="n">
         <v>5.13</v>
@@ -42913,7 +42919,7 @@
         </is>
       </c>
       <c r="M412" s="4" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="N412" s="4" t="n">
         <v>5.13</v>
@@ -43007,7 +43013,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="n">
-        <v>35.89</v>
+        <v>35.88</v>
       </c>
       <c r="J413" s="4" t="n">
         <v>100</v>
@@ -43027,7 +43033,7 @@
         <v>5.13</v>
       </c>
       <c r="O413" s="4" t="n">
-        <v>35.89</v>
+        <v>35.88</v>
       </c>
       <c r="P413" s="4" t="n">
         <v>0</v>
@@ -43160,10 +43166,10 @@
         <v>0</v>
       </c>
       <c r="AB414" s="4" t="n">
-        <v>42.25</v>
+        <v>42.24</v>
       </c>
       <c r="AC414" s="4" t="n">
-        <v>57.75</v>
+        <v>57.76</v>
       </c>
       <c r="AD414" s="4" t="n">
         <v>0</v>
@@ -43225,7 +43231,7 @@
         </is>
       </c>
       <c r="M415" s="4" t="n">
-        <v>62.35</v>
+        <v>62.34</v>
       </c>
       <c r="N415" s="4" t="n">
         <v>5.13</v>
@@ -43309,7 +43315,7 @@
         </is>
       </c>
       <c r="I416" s="4" t="n">
-        <v>-43.43</v>
+        <v>-43.44</v>
       </c>
       <c r="J416" s="4" t="n">
         <v>0</v>
@@ -43329,7 +43335,7 @@
         <v>5.13</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>-43.43</v>
+        <v>-43.44</v>
       </c>
       <c r="P416" s="4" t="n">
         <v>-2.39</v>
@@ -43719,7 +43725,7 @@
         </is>
       </c>
       <c r="M420" s="4" t="n">
-        <v>-8.960000000000001</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="N420" s="4" t="n">
         <v>5.13</v>
@@ -43915,7 +43921,7 @@
         </is>
       </c>
       <c r="I422" s="4" t="n">
-        <v>-14.58</v>
+        <v>-14.59</v>
       </c>
       <c r="J422" s="4" t="n">
         <v>0.7</v>
@@ -43935,7 +43941,7 @@
         <v>5.13</v>
       </c>
       <c r="O422" s="4" t="n">
-        <v>-14.58</v>
+        <v>-14.59</v>
       </c>
       <c r="P422" s="4" t="n">
         <v>0</v>
@@ -44133,7 +44139,7 @@
         </is>
       </c>
       <c r="M424" s="4" t="n">
-        <v>-16.88</v>
+        <v>-16.89</v>
       </c>
       <c r="N424" s="4" t="n">
         <v>5.13</v>
@@ -44170,10 +44176,10 @@
         <v>0</v>
       </c>
       <c r="AB424" s="4" t="n">
-        <v>42.71</v>
+        <v>42.7</v>
       </c>
       <c r="AC424" s="4" t="n">
-        <v>57.29</v>
+        <v>57.3</v>
       </c>
       <c r="AD424" s="4" t="n">
         <v>0</v>
@@ -44221,13 +44227,13 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>10.86</v>
+        <v>10.99</v>
       </c>
       <c r="J425" s="4" t="n">
-        <v>97.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K425" s="4" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -44235,7 +44241,7 @@
         </is>
       </c>
       <c r="M425" s="4" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="N425" s="4" t="n">
         <v>5.13</v>
@@ -44278,10 +44284,10 @@
         <v>0</v>
       </c>
       <c r="AB425" s="4" t="n">
-        <v>55.43</v>
+        <v>55.5</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>44.57</v>
+        <v>44.5</v>
       </c>
       <c r="AD425" s="4" t="n">
         <v>0</v>
@@ -44380,10 +44386,10 @@
         <v>0</v>
       </c>
       <c r="AB426" s="4" t="n">
-        <v>76.68000000000001</v>
+        <v>76.67</v>
       </c>
       <c r="AC426" s="4" t="n">
-        <v>23.32</v>
+        <v>23.33</v>
       </c>
       <c r="AD426" s="4" t="n">
         <v>0</v>
@@ -44641,7 +44647,7 @@
         </is>
       </c>
       <c r="M429" s="4" t="n">
-        <v>-12.65</v>
+        <v>-12.66</v>
       </c>
       <c r="N429" s="4" t="n">
         <v>5.13</v>
@@ -44678,10 +44684,10 @@
         <v>0</v>
       </c>
       <c r="AB429" s="4" t="n">
-        <v>45.41</v>
+        <v>45.4</v>
       </c>
       <c r="AC429" s="4" t="n">
-        <v>54.59</v>
+        <v>54.6</v>
       </c>
       <c r="AD429" s="4" t="n">
         <v>0</v>
@@ -44827,13 +44833,13 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>7.62</v>
+        <v>7.64</v>
       </c>
       <c r="J431" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="K431" s="4" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -44841,7 +44847,7 @@
         </is>
       </c>
       <c r="M431" s="4" t="n">
-        <v>-2.07</v>
+        <v>-2.08</v>
       </c>
       <c r="N431" s="4" t="n">
         <v>5.13</v>
@@ -44884,10 +44890,10 @@
         <v>0</v>
       </c>
       <c r="AB431" s="4" t="n">
-        <v>53.81</v>
+        <v>53.82</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>46.19</v>
+        <v>46.18</v>
       </c>
       <c r="AD431" s="4" t="n">
         <v>0</v>
@@ -44931,7 +44937,7 @@
         </is>
       </c>
       <c r="I432" s="4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="J432" s="4" t="n">
         <v>71.7</v>
@@ -44951,7 +44957,7 @@
         <v>5.13</v>
       </c>
       <c r="O432" s="4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="P432" s="4" t="n">
         <v>0.08</v>
@@ -45033,7 +45039,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-16.64</v>
+        <v>-16.65</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.5</v>
@@ -45047,13 +45053,13 @@
         </is>
       </c>
       <c r="M433" s="4" t="n">
-        <v>-19.68</v>
+        <v>-19.69</v>
       </c>
       <c r="N433" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-16.64</v>
+        <v>-16.65</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>0</v>
@@ -45135,7 +45141,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -45155,7 +45161,7 @@
         <v>5.13</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="P434" s="4" t="n">
         <v>1.49</v>
@@ -45233,7 +45239,7 @@
         </is>
       </c>
       <c r="I435" s="4" t="n">
-        <v>-14.72</v>
+        <v>-14.73</v>
       </c>
       <c r="J435" s="4" t="n">
         <v>0.7</v>
@@ -45247,7 +45253,7 @@
         </is>
       </c>
       <c r="M435" s="4" t="n">
-        <v>-17.12</v>
+        <v>-17.13</v>
       </c>
       <c r="N435" s="4" t="n">
         <v>5.13</v>
@@ -45847,13 +45853,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>67.5</v>
+        <v>67.8</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>32.5</v>
+        <v>32.2</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -45904,10 +45910,10 @@
         <v>0</v>
       </c>
       <c r="AB441" s="4" t="n">
-        <v>50.73</v>
+        <v>50.77</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>49.27</v>
+        <v>49.23</v>
       </c>
       <c r="AD441" s="4" t="n">
         <v>0</v>
@@ -46873,7 +46879,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>36.32</v>
+        <v>36.3</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -46887,13 +46893,13 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>20.63</v>
+        <v>20.6</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>36.34</v>
+        <v>36.32</v>
       </c>
       <c r="P451" s="4" t="n">
         <v>1.82</v>
@@ -46930,10 +46936,10 @@
         <v>0</v>
       </c>
       <c r="AB451" s="4" t="n">
-        <v>68.16</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="AC451" s="4" t="n">
-        <v>31.84</v>
+        <v>31.85</v>
       </c>
       <c r="AD451" s="4" t="n">
         <v>0</v>
@@ -47185,13 +47191,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>5.04</v>
+        <v>5.09</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47242,10 +47248,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>52.52</v>
+        <v>52.54</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>47.48</v>
+        <v>47.46</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -47391,7 +47397,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-22.68</v>
+        <v>-22.74</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47448,10 +47454,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>38.66</v>
+        <v>38.63</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>61.34</v>
+        <v>61.37</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -48009,7 +48015,7 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-4.19</v>
+        <v>-4.18</v>
       </c>
       <c r="J462" s="4" t="n">
         <v>22.1</v>
@@ -48023,13 +48029,13 @@
         </is>
       </c>
       <c r="M462" s="4" t="n">
-        <v>-3.14</v>
+        <v>-3.13</v>
       </c>
       <c r="N462" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O462" s="4" t="n">
-        <v>-4.84</v>
+        <v>-4.83</v>
       </c>
       <c r="P462" s="4" t="n">
         <v>-1.52</v>
@@ -48117,7 +48123,7 @@
         </is>
       </c>
       <c r="I463" s="4" t="n">
-        <v>50.13</v>
+        <v>50.14</v>
       </c>
       <c r="J463" s="4" t="n">
         <v>100</v>
@@ -48137,7 +48143,7 @@
         <v>5.13</v>
       </c>
       <c r="O463" s="4" t="n">
-        <v>50.13</v>
+        <v>50.14</v>
       </c>
       <c r="P463" s="4" t="n">
         <v>2.06</v>
@@ -48233,13 +48239,13 @@
         </is>
       </c>
       <c r="M464" s="4" t="n">
-        <v>-5.97</v>
+        <v>-5.96</v>
       </c>
       <c r="N464" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O464" s="4" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
       <c r="P464" s="4" t="n">
         <v>0.09</v>
@@ -48251,16 +48257,16 @@
         <v>-7.51</v>
       </c>
       <c r="S464" s="4" t="n">
-        <v>49.97</v>
+        <v>49.96</v>
       </c>
       <c r="T464" s="4" t="n">
-        <v>46.03</v>
+        <v>46.05</v>
       </c>
       <c r="U464" t="n">
         <v>5</v>
       </c>
       <c r="V464" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="W464" s="5" t="n">
         <v>8305020</v>
@@ -48341,7 +48347,7 @@
         </is>
       </c>
       <c r="M465" s="4" t="n">
-        <v>53.57</v>
+        <v>53.58</v>
       </c>
       <c r="N465" s="4" t="n">
         <v>5.13</v>
@@ -48429,7 +48435,7 @@
         </is>
       </c>
       <c r="I466" s="4" t="n">
-        <v>-24.82</v>
+        <v>-24.81</v>
       </c>
       <c r="J466" s="4" t="n">
         <v>0.1</v>
@@ -48449,7 +48455,7 @@
         <v>5.13</v>
       </c>
       <c r="O466" s="4" t="n">
-        <v>-24.82</v>
+        <v>-24.81</v>
       </c>
       <c r="P466" s="4" t="n">
         <v>-2.3</v>
@@ -48531,7 +48537,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-18.96</v>
+        <v>-18.94</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.3</v>
@@ -48588,10 +48594,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>40.52</v>
+        <v>40.53</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>59.48</v>
+        <v>59.47</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48686,10 +48692,10 @@
         <v>0</v>
       </c>
       <c r="AB468" s="4" t="n">
-        <v>40.58</v>
+        <v>40.59</v>
       </c>
       <c r="AC468" s="4" t="n">
-        <v>59.42</v>
+        <v>59.41</v>
       </c>
       <c r="AD468" s="4" t="n">
         <v>0</v>
@@ -48737,7 +48743,7 @@
         </is>
       </c>
       <c r="I469" s="4" t="n">
-        <v>-14.46</v>
+        <v>-14.45</v>
       </c>
       <c r="J469" s="4" t="n">
         <v>0.7</v>
@@ -48751,13 +48757,13 @@
         </is>
       </c>
       <c r="M469" s="4" t="n">
-        <v>-15.61</v>
+        <v>-15.6</v>
       </c>
       <c r="N469" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O469" s="4" t="n">
-        <v>-14.46</v>
+        <v>-14.45</v>
       </c>
       <c r="P469" s="4" t="n">
         <v>-1.34</v>
@@ -49141,13 +49147,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.83</v>
+        <v>-1.2</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>47.3</v>
+        <v>46.8</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49155,13 +49161,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.63</v>
+        <v>-10.72</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.08</v>
+        <v>-2.17</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -49198,10 +49204,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.39</v>
+        <v>45.37</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.61</v>
+        <v>46.63</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49659,7 +49665,7 @@
         </is>
       </c>
       <c r="I478" s="4" t="n">
-        <v>-5.6</v>
+        <v>-5.59</v>
       </c>
       <c r="J478" s="4" t="n">
         <v>17.1</v>
@@ -49787,7 +49793,7 @@
         <v>5.13</v>
       </c>
       <c r="O479" s="4" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="P479" s="4" t="n">
         <v>1.71</v>
@@ -49871,7 +49877,7 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-1.47</v>
+        <v>-1.49</v>
       </c>
       <c r="J480" s="4" t="n">
         <v>32.4</v>
@@ -49928,10 +49934,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.97</v>
+        <v>47.96</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.4</v>
+        <v>49.41</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -49979,7 +49985,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-39.34</v>
+        <v>-39.35</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0</v>
@@ -50040,10 +50046,10 @@
         <v>0</v>
       </c>
       <c r="AB481" s="4" t="n">
-        <v>28.21</v>
+        <v>28.2</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -50499,7 +50505,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>29.75</v>
+        <v>29.78</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -50513,13 +50519,13 @@
         </is>
       </c>
       <c r="M486" s="4" t="n">
-        <v>28.62</v>
+        <v>28.63</v>
       </c>
       <c r="N486" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O486" s="4" t="n">
-        <v>35.73</v>
+        <v>35.74</v>
       </c>
       <c r="P486" s="4" t="n">
         <v>0.66</v>
@@ -50556,10 +50562,10 @@
         <v>0</v>
       </c>
       <c r="AB486" s="4" t="n">
-        <v>64.88</v>
+        <v>64.89</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>35.12</v>
+        <v>35.11</v>
       </c>
       <c r="AD486" s="4" t="n">
         <v>0</v>
@@ -50607,13 +50613,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50627,7 +50633,7 @@
         <v>5.13</v>
       </c>
       <c r="O487" s="4" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="P487" s="4" t="n">
         <v>0</v>
@@ -50664,10 +50670,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>51.08</v>
+        <v>51.06</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>48.92</v>
+        <v>48.94</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -50725,13 +50731,13 @@
         </is>
       </c>
       <c r="M488" s="4" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="N488" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O488" s="4" t="n">
-        <v>7.72</v>
+        <v>7.69</v>
       </c>
       <c r="P488" s="4" t="n">
         <v>-0.28</v>
@@ -50815,17 +50821,17 @@
         </is>
       </c>
       <c r="I489" s="4" t="n">
-        <v>9.75</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J489" s="4" t="n">
-        <v>95.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="K489" s="4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>Safe D</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="M489" s="4" t="n">
@@ -50835,7 +50841,7 @@
         <v>5.13</v>
       </c>
       <c r="O489" s="4" t="n">
-        <v>11.23</v>
+        <v>11.22</v>
       </c>
       <c r="P489" s="4" t="n">
         <v>-0.05</v>
@@ -50847,16 +50853,16 @@
         <v>4.34</v>
       </c>
       <c r="S489" s="4" t="n">
-        <v>49.03</v>
+        <v>49.3</v>
       </c>
       <c r="T489" s="4" t="n">
-        <v>41.46</v>
+        <v>41.8</v>
       </c>
       <c r="U489" t="n">
         <v>6</v>
       </c>
       <c r="V489" s="4" t="n">
-        <v>7.05</v>
+        <v>6.64</v>
       </c>
       <c r="W489" s="5" t="n">
         <v>6044163</v>
@@ -50872,10 +50878,10 @@
         <v>0</v>
       </c>
       <c r="AB489" s="4" t="n">
-        <v>54.87</v>
+        <v>54.8</v>
       </c>
       <c r="AC489" s="4" t="n">
-        <v>45.13</v>
+        <v>45.2</v>
       </c>
       <c r="AD489" s="4" t="n">
         <v>0</v>
@@ -51031,7 +51037,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-20.47</v>
+        <v>-20.82</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>4.9</v>
@@ -51086,16 +51092,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>9.76</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>33.06</v>
+        <v>32.91</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.53</v>
+        <v>53.72</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51139,7 +51145,7 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>5.98</v>
+        <v>5.97</v>
       </c>
       <c r="J492" s="4" t="n">
         <v>84.2</v>
@@ -51196,10 +51202,10 @@
         <v>0</v>
       </c>
       <c r="AB492" s="4" t="n">
-        <v>52</v>
+        <v>51.99</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>46.13</v>
+        <v>46.14</v>
       </c>
       <c r="AD492" s="4" t="n">
         <v>1.87</v>
@@ -51247,13 +51253,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-6.42</v>
+        <v>-6.51</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>31.6</v>
+        <v>30.5</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51302,16 +51308,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>46.79</v>
+        <v>46.74</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>31.6</v>
+        <v>30.5</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>53.21</v>
+        <v>53.26</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -51375,7 +51381,7 @@
         <v>5.13</v>
       </c>
       <c r="O494" s="4" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="P494" s="4" t="n">
         <v>0.75</v>
@@ -51565,7 +51571,7 @@
         </is>
       </c>
       <c r="I496" s="4" t="n">
-        <v>18.6</v>
+        <v>18.61</v>
       </c>
       <c r="J496" s="4" t="n">
         <v>99.7</v>
@@ -51579,13 +51585,13 @@
         </is>
       </c>
       <c r="M496" s="4" t="n">
-        <v>7.52</v>
+        <v>7.53</v>
       </c>
       <c r="N496" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O496" s="4" t="n">
-        <v>18.6</v>
+        <v>18.61</v>
       </c>
       <c r="P496" s="4" t="n">
         <v>3.16</v>
@@ -51616,10 +51622,10 @@
         <v>0</v>
       </c>
       <c r="AB496" s="4" t="n">
-        <v>59.3</v>
+        <v>59.31</v>
       </c>
       <c r="AC496" s="4" t="n">
-        <v>40.7</v>
+        <v>40.69</v>
       </c>
       <c r="AD496" s="4" t="n">
         <v>0</v>
@@ -51667,7 +51673,7 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="J497" s="4" t="n">
         <v>36.9</v>
@@ -51724,10 +51730,10 @@
         <v>0</v>
       </c>
       <c r="AB497" s="4" t="n">
-        <v>49.05</v>
+        <v>49.04</v>
       </c>
       <c r="AC497" s="4" t="n">
-        <v>49.38</v>
+        <v>49.39</v>
       </c>
       <c r="AD497" s="4" t="n">
         <v>1.57</v>
@@ -51873,7 +51879,7 @@
         </is>
       </c>
       <c r="I499" s="4" t="n">
-        <v>21.35</v>
+        <v>21.36</v>
       </c>
       <c r="J499" s="4" t="n">
         <v>99.8</v>
@@ -51893,7 +51899,7 @@
         <v>5.13</v>
       </c>
       <c r="O499" s="4" t="n">
-        <v>21.35</v>
+        <v>21.36</v>
       </c>
       <c r="P499" s="4" t="n">
         <v>2.47</v>
@@ -51975,7 +51981,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>22.72</v>
+        <v>22.77</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -51995,7 +52001,7 @@
         <v>5.13</v>
       </c>
       <c r="O500" s="4" t="n">
-        <v>25.72</v>
+        <v>25.73</v>
       </c>
       <c r="P500" s="4" t="n">
         <v>2.03</v>
@@ -52032,10 +52038,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.36</v>
+        <v>61.39</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.64</v>
+        <v>38.61</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -52391,13 +52397,13 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="K504" s="4" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -52411,7 +52417,7 @@
         <v>5.13</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
       <c r="P504" s="4" t="n">
         <v>1.51</v>
@@ -52432,7 +52438,7 @@
         <v>19</v>
       </c>
       <c r="V504" s="4" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="W504" s="5" t="n">
         <v>68555930</v>
@@ -52448,10 +52454,10 @@
         <v>0</v>
       </c>
       <c r="AB504" s="4" t="n">
-        <v>49.19</v>
+        <v>49.18</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>48.8</v>
+        <v>48.81</v>
       </c>
       <c r="AD504" s="4" t="n">
         <v>2.01</v>
@@ -53969,7 +53975,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>86</v>
@@ -54259,7 +54265,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="K25" t="n">
         <v>19</v>
@@ -55071,7 +55077,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>84</v>
@@ -55199,7 +55205,7 @@
         <v>80</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>59.8</v>
+        <v>59.7</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -55245,7 +55251,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="K42" t="n">
         <v>22</v>
@@ -55303,7 +55309,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K43" t="n">
         <v>75</v>
@@ -55315,7 +55321,7 @@
         <v>96</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -55593,7 +55599,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="K48" t="n">
         <v>19</v>
@@ -56185,7 +56191,7 @@
         <v>15</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -56881,7 +56887,7 @@
         <v>38</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-07-25 · evaluated at 0 days to election (actual: 101 days out)</t>
+          <t>Data as of 2026-07-26 · evaluated at 0 days to election (actual: 100 days out)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>50.9</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.1</v>
+        <v>231.9</v>
       </c>
       <c r="C9" t="n">
-        <v>202.9</v>
+        <v>203.1</v>
       </c>
       <c r="D9" t="n">
         <v>230</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="C10" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="D10" t="n">
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.6</v>
+        <v>-2.86</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>39.1</v>
+        <v>41</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>60.9</v>
+        <v>59</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>44.4</v>
+        <v>44.38</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>47.6</v>
+        <v>47.62</v>
       </c>
       <c r="AD2" s="4" t="n">
         <v>8</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>63.39</v>
+        <v>63.4</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>36.61</v>
+        <v>36.6</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17.56</v>
+        <v>17.6</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.59999999999999</v>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>58.78</v>
+        <v>58.8</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>41.22</v>
+        <v>41.2</v>
       </c>
       <c r="AD8" s="4" t="n">
         <v>0</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.05</v>
+        <v>-6.06</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>15.5</v>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>73</v>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>51.44</v>
+        <v>51.43</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>48.56</v>
+        <v>48.57</v>
       </c>
       <c r="AD10" s="4" t="n">
         <v>0</v>
@@ -2024,10 +2024,10 @@
         <v>0</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>52.82</v>
+        <v>52.83</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>47.18</v>
+        <v>47.17</v>
       </c>
       <c r="AD12" s="4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>29.24</v>
+        <v>29.26</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>64.62</v>
+        <v>64.63</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>35.38</v>
+        <v>35.37</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12.58</v>
+        <v>12.56</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>99</v>
@@ -2656,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>55.65</v>
+        <v>55.64</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>43.21</v>
+        <v>43.22</v>
       </c>
       <c r="AD18" s="4" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>12.39</v>
+        <v>12.4</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.48</v>
+        <v>12.47</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>56.24</v>
+        <v>56.23</v>
       </c>
       <c r="AC20" s="4" t="n">
-        <v>43.76</v>
+        <v>43.77</v>
       </c>
       <c r="AD20" s="4" t="n">
         <v>0</v>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.6</v>
+        <v>-10.61</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>44.7</v>
+        <v>44.69</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>55.3</v>
+        <v>55.31</v>
       </c>
       <c r="AD22" s="4" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>86.3</v>
+        <v>86.5</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>53.31</v>
+        <v>53.34</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>46.69</v>
+        <v>46.66</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>67.8</v>
@@ -3296,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>50.76</v>
+        <v>50.77</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>49.24</v>
+        <v>49.23</v>
       </c>
       <c r="AD24" s="4" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.13</v>
+        <v>15.12</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>99.3</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.37</v>
+        <v>-3.38</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25.1</v>
@@ -3508,10 +3508,10 @@
         <v>0</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>48.32</v>
+        <v>48.31</v>
       </c>
       <c r="AC26" s="4" t="n">
-        <v>51.68</v>
+        <v>51.69</v>
       </c>
       <c r="AD26" s="4" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16.45</v>
+        <v>16.46</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>99.5</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.57</v>
+        <v>19.59</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.7</v>
@@ -4226,10 +4226,10 @@
         <v>0</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>39.42</v>
+        <v>39.43</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>60.58</v>
+        <v>60.57</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-8.6</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>7.8</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-18.56</v>
+        <v>-18.66</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.3</v>
@@ -4442,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>40.72</v>
+        <v>40.67</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>59.28</v>
+        <v>59.33</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>0</v>
@@ -4489,13 +4489,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>69.2</v>
+        <v>69.3</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4546,10 +4546,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>50.95</v>
+        <v>50.96</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>49.05</v>
+        <v>49.04</v>
       </c>
       <c r="AD36" s="4" t="n">
         <v>0</v>
@@ -4695,27 +4695,27 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-3.19</v>
+        <v>-2.96</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>38.9</v>
+        <v>41.1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>61.1</v>
+        <v>58.9</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.71</v>
+        <v>-2.51</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.41</v>
+        <v>-1.21</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.1</v>
@@ -4750,16 +4750,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.41</v>
+        <v>48.52</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>38.9</v>
+        <v>41.1</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.59</v>
+        <v>51.48</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -4962,10 +4962,10 @@
         <v>0</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>48.4</v>
+        <v>48.41</v>
       </c>
       <c r="AC40" s="4" t="n">
-        <v>51.6</v>
+        <v>51.59</v>
       </c>
       <c r="AD40" s="4" t="n">
         <v>0</v>
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.76</v>
+        <v>-0.72</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>49.62</v>
+        <v>49.64</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>50.38</v>
+        <v>50.36</v>
       </c>
       <c r="AD51" s="4" t="n">
         <v>0</v>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>80.09999999999999</v>
@@ -6502,10 +6502,10 @@
         <v>0</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>51.28</v>
+        <v>51.29</v>
       </c>
       <c r="AC55" s="4" t="n">
-        <v>46.6</v>
+        <v>46.59</v>
       </c>
       <c r="AD55" s="4" t="n">
         <v>2.12</v>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>15.45</v>
+        <v>15.46</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>5.13</v>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>33.31</v>
+        <v>33.32</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>100</v>
@@ -6975,13 +6975,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.83</v>
+        <v>27.84</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33.31</v>
+        <v>33.32</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>21.12</v>
+        <v>21.13</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>99.8</v>
@@ -7083,7 +7083,7 @@
         <v>5.13</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>21.12</v>
+        <v>21.13</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>1.08</v>
@@ -7179,13 +7179,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>18.28</v>
+        <v>18.29</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>26.54</v>
+        <v>26.55</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>-18.24</v>
+        <v>-18.23</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0.3</v>
@@ -7287,7 +7287,7 @@
         <v>5.13</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>-18.24</v>
+        <v>-18.23</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>-0.65</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12.39</v>
+        <v>12.4</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>98.90000000000001</v>
@@ -7383,13 +7383,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>11.25</v>
+        <v>11.26</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12.39</v>
+        <v>12.4</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>-0.35</v>
@@ -7491,7 +7491,7 @@
         <v>5.13</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>25.41</v>
+        <v>25.42</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>39.18</v>
+        <v>39.19</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>5.13</v>
@@ -7624,10 +7624,10 @@
         <v>0</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>74.48</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AC66" s="4" t="n">
-        <v>25.52</v>
+        <v>25.51</v>
       </c>
       <c r="AD66" s="4" t="n">
         <v>0</v>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>30.7</v>
+        <v>30.71</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>100</v>
@@ -7695,7 +7695,7 @@
         <v>5.13</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>30.7</v>
+        <v>30.71</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>2.78</v>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>42.87</v>
+        <v>42.88</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>100</v>
@@ -7797,7 +7797,7 @@
         <v>5.13</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>42.87</v>
+        <v>42.88</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>74.05</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>78.86</v>
+        <v>78.87</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21.59</v>
+        <v>21.6</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>99.8</v>
@@ -8099,7 +8099,7 @@
         <v>5.13</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>21.59</v>
+        <v>21.6</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0.46</v>
@@ -8191,13 +8191,13 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>40.71</v>
+        <v>40.72</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>45.96</v>
+        <v>45.97</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
@@ -8330,10 +8330,10 @@
         <v>0</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.11</v>
       </c>
       <c r="AC73" s="4" t="n">
-        <v>20.9</v>
+        <v>20.89</v>
       </c>
       <c r="AD73" s="4" t="n">
         <v>0</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="M74" s="4" t="n">
-        <v>52.92</v>
+        <v>52.93</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>5.13</v>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>48.97</v>
+        <v>48.98</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>100</v>
@@ -8503,7 +8503,7 @@
         <v>5.13</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>48.97</v>
+        <v>48.98</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>3.69</v>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>43.91</v>
+        <v>43.92</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>100</v>
@@ -8605,7 +8605,7 @@
         <v>5.13</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>43.91</v>
+        <v>43.92</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>2.1</v>
@@ -8701,13 +8701,13 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.65</v>
+        <v>38.66</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>50.18</v>
+        <v>50.19</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>2.46</v>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-28.63</v>
+        <v>-28.62</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -8803,13 +8803,13 @@
         </is>
       </c>
       <c r="M78" s="4" t="n">
-        <v>-30.32</v>
+        <v>-30.31</v>
       </c>
       <c r="N78" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-28.63</v>
+        <v>-28.62</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.51</v>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.79</v>
+        <v>11.8</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>5.13</v>
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.43</v>
+        <v>5.45</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="M80" s="4" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>5.13</v>
@@ -9050,10 +9050,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>52.71</v>
+        <v>52.72</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47.29</v>
+        <v>47.28</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="M82" s="4" t="n">
-        <v>28.2</v>
+        <v>28.21</v>
       </c>
       <c r="N82" s="4" t="n">
         <v>5.13</v>
@@ -9254,10 +9254,10 @@
         <v>0</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>68.31</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="AC82" s="4" t="n">
-        <v>31.69</v>
+        <v>31.68</v>
       </c>
       <c r="AD82" s="4" t="n">
         <v>0</v>
@@ -9356,10 +9356,10 @@
         <v>0</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>59.86</v>
+        <v>59.87</v>
       </c>
       <c r="AC83" s="4" t="n">
-        <v>40.14</v>
+        <v>40.13</v>
       </c>
       <c r="AD83" s="4" t="n">
         <v>0</v>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25.79</v>
+        <v>25.8</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>100</v>
@@ -9423,7 +9423,7 @@
         <v>5.13</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>25.79</v>
+        <v>25.8</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.63</v>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>39.75</v>
+        <v>39.76</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9621,13 +9621,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.79</v>
+        <v>29.8</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>39.75</v>
+        <v>39.76</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.23</v>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.35</v>
+        <v>41.36</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>5.13</v>
@@ -9811,7 +9811,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>51.65</v>
+        <v>51.66</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>100</v>
@@ -9825,13 +9825,13 @@
         </is>
       </c>
       <c r="M88" s="4" t="n">
-        <v>44.8</v>
+        <v>44.81</v>
       </c>
       <c r="N88" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>51.65</v>
+        <v>51.66</v>
       </c>
       <c r="P88" s="4" t="n">
         <v>1.57</v>
@@ -9964,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>58.01</v>
+        <v>58.02</v>
       </c>
       <c r="AC89" s="4" t="n">
-        <v>41.99</v>
+        <v>41.98</v>
       </c>
       <c r="AD89" s="4" t="n">
         <v>0</v>
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>29.91</v>
+        <v>29.92</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>5.13</v>
@@ -10066,10 +10066,10 @@
         <v>0</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>69.75</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="AC90" s="4" t="n">
-        <v>30.25</v>
+        <v>30.24</v>
       </c>
       <c r="AD90" s="4" t="n">
         <v>0</v>
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28.34</v>
+        <v>28.35</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>100</v>
@@ -10131,13 +10131,13 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28.34</v>
+        <v>28.35</v>
       </c>
       <c r="P91" s="4" t="n">
         <v>0</v>
@@ -10233,7 +10233,7 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.82</v>
+        <v>58.83</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>5.13</v>
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26.25</v>
+        <v>26.26</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>100</v>
@@ -10341,7 +10341,7 @@
         <v>5.13</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>26.25</v>
+        <v>26.26</v>
       </c>
       <c r="P93" s="4" t="n">
         <v>2.03</v>
@@ -10423,7 +10423,7 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>51.03</v>
+        <v>51.04</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>100</v>
@@ -10437,13 +10437,13 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.41</v>
+        <v>43.42</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>51.03</v>
+        <v>51.04</v>
       </c>
       <c r="P94" s="4" t="n">
         <v>2.66</v>
@@ -10545,7 +10545,7 @@
         <v>5.13</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>76.52</v>
+        <v>76.53</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -10674,10 +10674,10 @@
         <v>0</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>62.98</v>
+        <v>62.99</v>
       </c>
       <c r="AC96" s="4" t="n">
-        <v>37.02</v>
+        <v>37.01</v>
       </c>
       <c r="AD96" s="4" t="n">
         <v>0</v>
@@ -10929,7 +10929,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>31.1</v>
+        <v>31.11</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -10949,7 +10949,7 @@
         <v>5.13</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>31.1</v>
+        <v>31.11</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.64</v>
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26.2</v>
+        <v>26.21</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>100</v>
@@ -11051,7 +11051,7 @@
         <v>5.13</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>26.2</v>
+        <v>26.21</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1.69</v>
@@ -11235,7 +11235,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11249,13 +11249,13 @@
         </is>
       </c>
       <c r="M102" s="4" t="n">
-        <v>43.5</v>
+        <v>43.51</v>
       </c>
       <c r="N102" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>1.93</v>
@@ -11337,7 +11337,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20.23</v>
+        <v>20.24</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>99.8</v>
@@ -11357,7 +11357,7 @@
         <v>5.13</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>20.23</v>
+        <v>20.24</v>
       </c>
       <c r="P103" s="4" t="n">
         <v>1.39</v>
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>39.35</v>
+        <v>39.36</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
@@ -11453,13 +11453,13 @@
         </is>
       </c>
       <c r="M104" s="4" t="n">
-        <v>21.96</v>
+        <v>21.97</v>
       </c>
       <c r="N104" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>39.35</v>
+        <v>39.36</v>
       </c>
       <c r="P104" s="4" t="n">
         <v>1.73</v>
@@ -11561,7 +11561,7 @@
         <v>5.13</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>22.44</v>
+        <v>22.45</v>
       </c>
       <c r="P105" s="4" t="n">
         <v>1.61</v>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>98.8</v>
@@ -11653,13 +11653,13 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.58</v>
+        <v>5.59</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>0.13</v>
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>26.17</v>
+        <v>26.18</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>100</v>
@@ -11857,13 +11857,13 @@
         </is>
       </c>
       <c r="M108" s="4" t="n">
-        <v>20.74</v>
+        <v>20.75</v>
       </c>
       <c r="N108" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>26.17</v>
+        <v>26.18</v>
       </c>
       <c r="P108" s="4" t="n">
         <v>0</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27.4</v>
+        <v>27.41</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -11959,13 +11959,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.39</v>
+        <v>21.4</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>27.4</v>
+        <v>27.41</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>39.65</v>
+        <v>39.66</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>100</v>
@@ -12067,7 +12067,7 @@
         <v>5.13</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>39.65</v>
+        <v>39.66</v>
       </c>
       <c r="P110" s="4" t="n">
         <v>1.58</v>
@@ -12973,7 +12973,7 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>36.68</v>
+        <v>36.69</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>100</v>
@@ -12987,13 +12987,13 @@
         </is>
       </c>
       <c r="M119" s="4" t="n">
-        <v>25.14</v>
+        <v>25.15</v>
       </c>
       <c r="N119" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O119" s="4" t="n">
-        <v>36.68</v>
+        <v>36.69</v>
       </c>
       <c r="P119" s="4" t="n">
         <v>2.93</v>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>27.15</v>
+        <v>27.16</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>100</v>
@@ -13089,13 +13089,13 @@
         </is>
       </c>
       <c r="M120" s="4" t="n">
-        <v>9.08</v>
+        <v>9.09</v>
       </c>
       <c r="N120" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>27.15</v>
+        <v>27.16</v>
       </c>
       <c r="P120" s="4" t="n">
         <v>1.43</v>
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>28.19</v>
+        <v>28.2</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>100</v>
@@ -13191,13 +13191,13 @@
         </is>
       </c>
       <c r="M121" s="4" t="n">
-        <v>16.21</v>
+        <v>16.22</v>
       </c>
       <c r="N121" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O121" s="4" t="n">
-        <v>28.19</v>
+        <v>28.2</v>
       </c>
       <c r="P121" s="4" t="n">
         <v>2.19</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>34.69</v>
+        <v>34.7</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>100</v>
@@ -13293,13 +13293,13 @@
         </is>
       </c>
       <c r="M122" s="4" t="n">
-        <v>26.12</v>
+        <v>26.13</v>
       </c>
       <c r="N122" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>34.69</v>
+        <v>34.7</v>
       </c>
       <c r="P122" s="4" t="n">
         <v>2.06</v>
@@ -13381,7 +13381,7 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>15.11</v>
+        <v>15.12</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>99.3</v>
@@ -13395,13 +13395,13 @@
         </is>
       </c>
       <c r="M123" s="4" t="n">
-        <v>7.37</v>
+        <v>7.38</v>
       </c>
       <c r="N123" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O123" s="4" t="n">
-        <v>15.11</v>
+        <v>15.12</v>
       </c>
       <c r="P123" s="4" t="n">
         <v>1.9</v>
@@ -13432,10 +13432,10 @@
         <v>0</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>57.55</v>
+        <v>57.56</v>
       </c>
       <c r="AC123" s="4" t="n">
-        <v>42.45</v>
+        <v>42.44</v>
       </c>
       <c r="AD123" s="4" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>-4.28</v>
+        <v>-4.29</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>21.7</v>
@@ -16541,7 +16541,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>24.24</v>
+        <v>24.23</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>99.90000000000001</v>
@@ -16561,7 +16561,7 @@
         <v>5.13</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>24.24</v>
+        <v>24.23</v>
       </c>
       <c r="P154" s="4" t="n">
         <v>1.36</v>
@@ -16643,7 +16643,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>-29.17</v>
+        <v>-29.18</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>0</v>
@@ -16663,7 +16663,7 @@
         <v>5.13</v>
       </c>
       <c r="O155" s="4" t="n">
-        <v>-29.17</v>
+        <v>-29.18</v>
       </c>
       <c r="P155" s="4" t="n">
         <v>-1.75</v>
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>83.79000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>100</v>
@@ -16867,7 +16867,7 @@
         <v>5.13</v>
       </c>
       <c r="O157" s="4" t="n">
-        <v>83.79000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="P157" s="4" t="n">
         <v>0</v>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>63.09</v>
+        <v>63.08</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>100</v>
@@ -16969,7 +16969,7 @@
         <v>5.13</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>63.09</v>
+        <v>63.08</v>
       </c>
       <c r="P158" s="4" t="n">
         <v>2.07</v>
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-11.69</v>
+        <v>-11.7</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>1.2</v>
@@ -17573,7 +17573,7 @@
         <v>5.13</v>
       </c>
       <c r="O164" s="4" t="n">
-        <v>-11.69</v>
+        <v>-11.7</v>
       </c>
       <c r="P164" s="4" t="n">
         <v>-1.96</v>
@@ -17651,7 +17651,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>50.88</v>
+        <v>50.87</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>100</v>
@@ -17665,13 +17665,13 @@
         </is>
       </c>
       <c r="M165" s="4" t="n">
-        <v>45.48</v>
+        <v>45.47</v>
       </c>
       <c r="N165" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>50.88</v>
+        <v>50.87</v>
       </c>
       <c r="P165" s="4" t="n">
         <v>0</v>
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-27.53</v>
+        <v>-27.84</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18534,10 +18534,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>36.23</v>
+        <v>36.08</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>63.77</v>
+        <v>63.92</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -22229,7 +22229,7 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-7.57</v>
+        <v>-7.6</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>10.7</v>
@@ -22286,10 +22286,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.21</v>
+        <v>46.2</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.79</v>
+        <v>53.8</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>24.01</v>
+        <v>24.03</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>99.90000000000001</v>
@@ -22959,13 +22959,13 @@
         </is>
       </c>
       <c r="M217" s="4" t="n">
-        <v>17.34</v>
+        <v>17.35</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>24.01</v>
+        <v>24.03</v>
       </c>
       <c r="P217" s="4" t="n">
         <v>0</v>
@@ -23047,7 +23047,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>33.63</v>
+        <v>33.64</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -23061,13 +23061,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>27.29</v>
+        <v>27.3</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>33.63</v>
+        <v>33.64</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -23149,7 +23149,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>32.19</v>
+        <v>32.2</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>100</v>
@@ -23163,13 +23163,13 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>22.79</v>
+        <v>22.8</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>32.19</v>
+        <v>32.2</v>
       </c>
       <c r="P219" s="4" t="n">
         <v>2.52</v>
@@ -23200,10 +23200,10 @@
         <v>0</v>
       </c>
       <c r="AB219" s="4" t="n">
-        <v>66.09</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AC219" s="4" t="n">
-        <v>33.91</v>
+        <v>33.9</v>
       </c>
       <c r="AD219" s="4" t="n">
         <v>0</v>
@@ -23251,7 +23251,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>29.69</v>
+        <v>29.7</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>100</v>
@@ -23265,13 +23265,13 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.61</v>
+        <v>23.62</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O220" s="4" t="n">
-        <v>29.69</v>
+        <v>29.7</v>
       </c>
       <c r="P220" s="4" t="n">
         <v>0</v>
@@ -23302,10 +23302,10 @@
         <v>0</v>
       </c>
       <c r="AB220" s="4" t="n">
-        <v>64.84</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AC220" s="4" t="n">
-        <v>35.16</v>
+        <v>35.15</v>
       </c>
       <c r="AD220" s="4" t="n">
         <v>0</v>
@@ -23353,7 +23353,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>55.31</v>
+        <v>55.32</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>100</v>
@@ -23367,13 +23367,13 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>48.97</v>
+        <v>48.98</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O221" s="4" t="n">
-        <v>55.31</v>
+        <v>55.32</v>
       </c>
       <c r="P221" s="4" t="n">
         <v>0</v>
@@ -23404,10 +23404,10 @@
         <v>0</v>
       </c>
       <c r="AB221" s="4" t="n">
-        <v>77.65000000000001</v>
+        <v>77.66</v>
       </c>
       <c r="AC221" s="4" t="n">
-        <v>22.35</v>
+        <v>22.34</v>
       </c>
       <c r="AD221" s="4" t="n">
         <v>0</v>
@@ -23451,7 +23451,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>28.45</v>
+        <v>28.46</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>100</v>
@@ -23465,13 +23465,13 @@
         </is>
       </c>
       <c r="M222" s="4" t="n">
-        <v>23.82</v>
+        <v>23.83</v>
       </c>
       <c r="N222" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O222" s="4" t="n">
-        <v>28.45</v>
+        <v>28.46</v>
       </c>
       <c r="P222" s="4" t="n">
         <v>0</v>
@@ -23502,10 +23502,10 @@
         <v>0</v>
       </c>
       <c r="AB222" s="4" t="n">
-        <v>64.22</v>
+        <v>64.23</v>
       </c>
       <c r="AC222" s="4" t="n">
-        <v>35.78</v>
+        <v>35.77</v>
       </c>
       <c r="AD222" s="4" t="n">
         <v>0</v>
@@ -23553,7 +23553,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>76.11</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -23567,13 +23567,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>68.98</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>76.11</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -23604,10 +23604,10 @@
         <v>0</v>
       </c>
       <c r="AB223" s="4" t="n">
-        <v>88.05</v>
+        <v>88.06</v>
       </c>
       <c r="AC223" s="4" t="n">
-        <v>11.95</v>
+        <v>11.94</v>
       </c>
       <c r="AD223" s="4" t="n">
         <v>0</v>
@@ -23655,7 +23655,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>45.42</v>
+        <v>45.43</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>100</v>
@@ -23669,13 +23669,13 @@
         </is>
       </c>
       <c r="M224" s="4" t="n">
-        <v>30.38</v>
+        <v>30.4</v>
       </c>
       <c r="N224" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O224" s="4" t="n">
-        <v>45.42</v>
+        <v>45.43</v>
       </c>
       <c r="P224" s="4" t="n">
         <v>0</v>
@@ -23757,7 +23757,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.43</v>
+        <v>22.45</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23771,13 +23771,13 @@
         </is>
       </c>
       <c r="M225" s="4" t="n">
-        <v>13.86</v>
+        <v>13.87</v>
       </c>
       <c r="N225" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.43</v>
+        <v>22.45</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.51</v>
@@ -24667,7 +24667,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.96</v>
+        <v>30.9</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24681,13 +24681,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>22.29</v>
+        <v>22.28</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.25</v>
+        <v>31.24</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24765,13 +24765,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-3.44</v>
+        <v>-3.84</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24779,13 +24779,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-8.85</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.2</v>
+        <v>-5.21</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24822,10 +24822,10 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>45.47</v>
+        <v>45.46</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>49.53</v>
+        <v>49.54</v>
       </c>
       <c r="AD235" s="4" t="n">
         <v>5</v>
@@ -24873,7 +24873,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>-12.78</v>
+        <v>-12.77</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>1</v>
@@ -24887,13 +24887,13 @@
         </is>
       </c>
       <c r="M236" s="4" t="n">
-        <v>-17.27</v>
+        <v>-17.26</v>
       </c>
       <c r="N236" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O236" s="4" t="n">
-        <v>-12.78</v>
+        <v>-12.77</v>
       </c>
       <c r="P236" s="4" t="n">
         <v>-0.61</v>
@@ -25199,7 +25199,7 @@
         <v>5.13</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-2.07</v>
+        <v>-2.06</v>
       </c>
       <c r="P239" s="4" t="n">
         <v>-0.31</v>
@@ -25301,7 +25301,7 @@
         </is>
       </c>
       <c r="M240" s="4" t="n">
-        <v>-22.64</v>
+        <v>-22.63</v>
       </c>
       <c r="N240" s="4" t="n">
         <v>5.13</v>
@@ -25491,13 +25491,13 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>5.13</v>
       </c>
       <c r="O242" s="4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="P242" s="4" t="n">
         <v>-0.62</v>
@@ -25548,10 +25548,10 @@
         <v>0</v>
       </c>
       <c r="AB242" s="4" t="n">
-        <v>50.43</v>
+        <v>50.44</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.57</v>
+        <v>49.56</v>
       </c>
       <c r="AD242" s="4" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         </is>
       </c>
       <c r="M244" s="4" t="n">
-        <v>-28.17</v>
+        <v>-28.16</v>
       </c>
       <c r="N244" s="4" t="n">
         <v>5.13</v>
@@ -25799,7 +25799,7 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="J245" s="4" t="n">
         <v>70.90000000000001</v>
@@ -25903,7 +25903,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>27.77</v>
+        <v>27.78</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>100</v>
@@ -25923,7 +25923,7 @@
         <v>5.13</v>
       </c>
       <c r="O246" s="4" t="n">
-        <v>27.77</v>
+        <v>27.78</v>
       </c>
       <c r="P246" s="4" t="n">
         <v>2.12</v>
@@ -26005,7 +26005,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>56.32</v>
+        <v>56.33</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -26019,13 +26019,13 @@
         </is>
       </c>
       <c r="M247" s="4" t="n">
-        <v>46.21</v>
+        <v>46.22</v>
       </c>
       <c r="N247" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O247" s="4" t="n">
-        <v>56.32</v>
+        <v>56.33</v>
       </c>
       <c r="P247" s="4" t="n">
         <v>0</v>
@@ -26209,7 +26209,7 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>-6.12</v>
+        <v>-6.13</v>
       </c>
       <c r="J249" s="4" t="n">
         <v>15.3</v>
@@ -26229,7 +26229,7 @@
         <v>5.13</v>
       </c>
       <c r="O249" s="4" t="n">
-        <v>-6.37</v>
+        <v>-6.38</v>
       </c>
       <c r="P249" s="4" t="n">
         <v>-0.02</v>
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>11.68</v>
+        <v>11.7</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>98.8</v>
@@ -26333,7 +26333,7 @@
         <v>5.13</v>
       </c>
       <c r="O250" s="4" t="n">
-        <v>13.47</v>
+        <v>13.46</v>
       </c>
       <c r="P250" s="4" t="n">
         <v>0.47</v>
@@ -26370,10 +26370,10 @@
         <v>0</v>
       </c>
       <c r="AB250" s="4" t="n">
-        <v>55.84</v>
+        <v>55.85</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>44.16</v>
+        <v>44.15</v>
       </c>
       <c r="AD250" s="4" t="n">
         <v>0</v>
@@ -26676,10 +26676,10 @@
         <v>0</v>
       </c>
       <c r="AB253" s="4" t="n">
-        <v>82.90000000000001</v>
+        <v>82.89</v>
       </c>
       <c r="AC253" s="4" t="n">
-        <v>17.1</v>
+        <v>17.11</v>
       </c>
       <c r="AD253" s="4" t="n">
         <v>0</v>
@@ -26727,7 +26727,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-14.68</v>
+        <v>-14.69</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>0.7</v>
@@ -26747,7 +26747,7 @@
         <v>5.13</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-14.68</v>
+        <v>-14.69</v>
       </c>
       <c r="P254" s="4" t="n">
         <v>0</v>
@@ -26829,7 +26829,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>-31.02</v>
+        <v>-31.03</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>0</v>
@@ -26843,13 +26843,13 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-33.64</v>
+        <v>-33.65</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O255" s="4" t="n">
-        <v>-31.02</v>
+        <v>-31.03</v>
       </c>
       <c r="P255" s="4" t="n">
         <v>0</v>
@@ -26931,7 +26931,7 @@
         </is>
       </c>
       <c r="I256" s="4" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="J256" s="4" t="n">
         <v>7.5</v>
@@ -26951,7 +26951,7 @@
         <v>5.13</v>
       </c>
       <c r="O256" s="4" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="P256" s="4" t="n">
         <v>0</v>
@@ -27135,7 +27135,7 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.61</v>
+        <v>-10.63</v>
       </c>
       <c r="J258" s="4" t="n">
         <v>2.7</v>
@@ -27192,10 +27192,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.69</v>
+        <v>44.68</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.31</v>
+        <v>55.32</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -28255,13 +28255,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-5.9</v>
+        <v>-5.94</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28269,13 +28269,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-11.02</v>
+        <v>-11.07</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-7.02</v>
+        <v>-7.06</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28312,10 +28312,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>47.05</v>
+        <v>47.03</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>52.95</v>
+        <v>52.97</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28363,7 +28363,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-32.75</v>
+        <v>-32.8</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28377,13 +28377,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-29.98</v>
+        <v>-30.03</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-32.75</v>
+        <v>-32.8</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28414,10 +28414,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.62</v>
+        <v>33.6</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.38</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28675,7 +28675,7 @@
         </is>
       </c>
       <c r="I273" s="4" t="n">
-        <v>-8.1</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="J273" s="4" t="n">
         <v>9.199999999999999</v>
@@ -28689,13 +28689,13 @@
         </is>
       </c>
       <c r="M273" s="4" t="n">
-        <v>-9.91</v>
+        <v>-9.92</v>
       </c>
       <c r="N273" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O273" s="4" t="n">
-        <v>-8.1</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="P273" s="4" t="n">
         <v>-1.57</v>
@@ -28791,7 +28791,7 @@
         </is>
       </c>
       <c r="M274" s="4" t="n">
-        <v>48.6</v>
+        <v>48.59</v>
       </c>
       <c r="N274" s="4" t="n">
         <v>5.13</v>
@@ -29199,7 +29199,7 @@
         </is>
       </c>
       <c r="M278" s="4" t="n">
-        <v>-16.99</v>
+        <v>-17</v>
       </c>
       <c r="N278" s="4" t="n">
         <v>5.13</v>
@@ -29338,10 +29338,10 @@
         <v>0</v>
       </c>
       <c r="AB279" s="4" t="n">
-        <v>44.18</v>
+        <v>44.17</v>
       </c>
       <c r="AC279" s="4" t="n">
-        <v>55.82</v>
+        <v>55.83</v>
       </c>
       <c r="AD279" s="4" t="n">
         <v>0</v>
@@ -29511,7 +29511,7 @@
         </is>
       </c>
       <c r="M281" s="4" t="n">
-        <v>-7.93</v>
+        <v>-7.94</v>
       </c>
       <c r="N281" s="4" t="n">
         <v>5.13</v>
@@ -29727,7 +29727,7 @@
         <v>5.13</v>
       </c>
       <c r="O283" s="4" t="n">
-        <v>-13.17</v>
+        <v>-13.18</v>
       </c>
       <c r="P283" s="4" t="n">
         <v>-0.19</v>
@@ -29809,7 +29809,7 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>-13.12</v>
+        <v>-13.13</v>
       </c>
       <c r="J284" s="4" t="n">
         <v>0.9</v>
@@ -30019,13 +30019,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.68</v>
+        <v>-9.76</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30033,13 +30033,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.94</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-10.3</v>
+        <v>-10.39</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30076,10 +30076,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.16</v>
+        <v>45.12</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.84</v>
+        <v>54.88</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30123,7 +30123,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.45</v>
+        <v>12.38</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>98.90000000000001</v>
@@ -30137,13 +30137,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>8.92</v>
+        <v>8.83</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.12</v>
+        <v>14.03</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30180,10 +30180,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.22</v>
+        <v>56.19</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.78</v>
+        <v>43.81</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30231,7 +30231,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.85</v>
+        <v>-52.94</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30245,13 +30245,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.89</v>
+        <v>-49.98</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.85</v>
+        <v>-52.94</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30282,10 +30282,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.57</v>
+        <v>23.53</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.43000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -31157,7 +31157,7 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="J297" s="4" t="n">
         <v>79</v>
@@ -31771,7 +31771,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>25.8</v>
+        <v>25.81</v>
       </c>
       <c r="J303" s="4" t="n">
         <v>100</v>
@@ -31785,13 +31785,13 @@
         </is>
       </c>
       <c r="M303" s="4" t="n">
-        <v>15.79</v>
+        <v>15.8</v>
       </c>
       <c r="N303" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O303" s="4" t="n">
-        <v>25.8</v>
+        <v>25.81</v>
       </c>
       <c r="P303" s="4" t="n">
         <v>1.68</v>
@@ -31822,10 +31822,10 @@
         <v>0</v>
       </c>
       <c r="AB303" s="4" t="n">
-        <v>62.9</v>
+        <v>62.91</v>
       </c>
       <c r="AC303" s="4" t="n">
-        <v>37.1</v>
+        <v>37.09</v>
       </c>
       <c r="AD303" s="4" t="n">
         <v>0</v>
@@ -31873,7 +31873,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>14.2</v>
+        <v>14.22</v>
       </c>
       <c r="J304" s="4" t="n">
         <v>99.2</v>
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="M304" s="4" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N304" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O304" s="4" t="n">
-        <v>16.22</v>
+        <v>16.23</v>
       </c>
       <c r="P304" s="4" t="n">
         <v>0.67</v>
@@ -31930,10 +31930,10 @@
         <v>0</v>
       </c>
       <c r="AB304" s="4" t="n">
-        <v>57.1</v>
+        <v>57.11</v>
       </c>
       <c r="AC304" s="4" t="n">
-        <v>42.9</v>
+        <v>42.89</v>
       </c>
       <c r="AD304" s="4" t="n">
         <v>0</v>
@@ -31981,7 +31981,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>22.82</v>
+        <v>22.83</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>99.90000000000001</v>
@@ -31995,13 +31995,13 @@
         </is>
       </c>
       <c r="M305" s="4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="N305" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O305" s="4" t="n">
-        <v>22.82</v>
+        <v>22.83</v>
       </c>
       <c r="P305" s="4" t="n">
         <v>0.73</v>
@@ -32083,7 +32083,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>16.18</v>
+        <v>16.19</v>
       </c>
       <c r="J306" s="4" t="n">
         <v>99.5</v>
@@ -32103,7 +32103,7 @@
         <v>5.13</v>
       </c>
       <c r="O306" s="4" t="n">
-        <v>16.18</v>
+        <v>16.19</v>
       </c>
       <c r="P306" s="4" t="n">
         <v>-0.16</v>
@@ -32181,13 +32181,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-3.63</v>
+        <v>-3.72</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -32195,13 +32195,13 @@
         </is>
       </c>
       <c r="M307" s="4" t="n">
-        <v>-12.43</v>
+        <v>-12.42</v>
       </c>
       <c r="N307" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O307" s="4" t="n">
-        <v>-8.630000000000001</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="P307" s="4" t="n">
         <v>-1.32</v>
@@ -32238,10 +32238,10 @@
         <v>0</v>
       </c>
       <c r="AB307" s="4" t="n">
-        <v>48.18</v>
+        <v>48.14</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>51.82</v>
+        <v>51.86</v>
       </c>
       <c r="AD307" s="4" t="n">
         <v>0</v>
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>11.65</v>
+        <v>11.66</v>
       </c>
       <c r="J308" s="4" t="n">
         <v>98.8</v>
@@ -32303,13 +32303,13 @@
         </is>
       </c>
       <c r="M308" s="4" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="N308" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O308" s="4" t="n">
-        <v>11.65</v>
+        <v>11.66</v>
       </c>
       <c r="P308" s="4" t="n">
         <v>0.06</v>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>17.44</v>
+        <v>17.45</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>99.59999999999999</v>
@@ -32405,13 +32405,13 @@
         </is>
       </c>
       <c r="M309" s="4" t="n">
-        <v>5.43</v>
+        <v>5.44</v>
       </c>
       <c r="N309" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>17.44</v>
+        <v>17.45</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>0.97</v>
@@ -34121,13 +34121,13 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J326" s="4" t="n">
-        <v>70.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K326" s="4" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -34178,10 +34178,10 @@
         <v>0</v>
       </c>
       <c r="AB326" s="4" t="n">
-        <v>51.15</v>
+        <v>51.16</v>
       </c>
       <c r="AC326" s="4" t="n">
-        <v>48.85</v>
+        <v>48.84</v>
       </c>
       <c r="AD326" s="4" t="n">
         <v>0</v>
@@ -34537,7 +34537,7 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-12.53</v>
+        <v>-12.57</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>1</v>
@@ -34594,10 +34594,10 @@
         <v>0</v>
       </c>
       <c r="AB330" s="4" t="n">
-        <v>43.73</v>
+        <v>43.72</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>56.27</v>
+        <v>56.28</v>
       </c>
       <c r="AD330" s="4" t="n">
         <v>0</v>
@@ -35155,7 +35155,7 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>11.64</v>
+        <v>11.63</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>98.8</v>
@@ -35169,13 +35169,13 @@
         </is>
       </c>
       <c r="M336" s="4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="N336" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O336" s="4" t="n">
-        <v>11.64</v>
+        <v>11.63</v>
       </c>
       <c r="P336" s="4" t="n">
         <v>0.77</v>
@@ -35308,10 +35308,10 @@
         <v>0</v>
       </c>
       <c r="AB337" s="4" t="n">
-        <v>31.85</v>
+        <v>31.84</v>
       </c>
       <c r="AC337" s="4" t="n">
-        <v>68.15000000000001</v>
+        <v>68.16</v>
       </c>
       <c r="AD337" s="4" t="n">
         <v>0</v>
@@ -35359,7 +35359,7 @@
         </is>
       </c>
       <c r="I338" s="4" t="n">
-        <v>52.59</v>
+        <v>52.58</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>100</v>
@@ -35379,7 +35379,7 @@
         <v>5.13</v>
       </c>
       <c r="O338" s="4" t="n">
-        <v>52.59</v>
+        <v>52.58</v>
       </c>
       <c r="P338" s="4" t="n">
         <v>0</v>
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>-38.7</v>
+        <v>-38.71</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>0</v>
@@ -35481,7 +35481,7 @@
         <v>5.13</v>
       </c>
       <c r="O339" s="4" t="n">
-        <v>-38.7</v>
+        <v>-38.71</v>
       </c>
       <c r="P339" s="4" t="n">
         <v>-3.15</v>
@@ -35577,7 +35577,7 @@
         </is>
       </c>
       <c r="M340" s="4" t="n">
-        <v>-19.28</v>
+        <v>-19.29</v>
       </c>
       <c r="N340" s="4" t="n">
         <v>5.13</v>
@@ -35767,13 +35767,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-6.61</v>
+        <v>-6.63</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>86.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35824,10 +35824,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>46.69</v>
+        <v>46.68</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>53.31</v>
+        <v>53.32</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -35926,10 +35926,10 @@
         <v>0</v>
       </c>
       <c r="AB343" s="4" t="n">
-        <v>45.6</v>
+        <v>45.59</v>
       </c>
       <c r="AC343" s="4" t="n">
-        <v>54.4</v>
+        <v>54.41</v>
       </c>
       <c r="AD343" s="4" t="n">
         <v>0</v>
@@ -35977,7 +35977,7 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>9.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>93.8</v>
@@ -35991,7 +35991,7 @@
         </is>
       </c>
       <c r="M344" s="4" t="n">
-        <v>-5.63</v>
+        <v>-5.64</v>
       </c>
       <c r="N344" s="4" t="n">
         <v>5.13</v>
@@ -36034,10 +36034,10 @@
         <v>0</v>
       </c>
       <c r="AB344" s="4" t="n">
-        <v>54.59</v>
+        <v>54.6</v>
       </c>
       <c r="AC344" s="4" t="n">
-        <v>45.41</v>
+        <v>45.4</v>
       </c>
       <c r="AD344" s="4" t="n">
         <v>0</v>
@@ -36085,13 +36085,13 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-8</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="J345" s="4" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="K345" s="4" t="n">
-        <v>90.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -36142,10 +36142,10 @@
         <v>0</v>
       </c>
       <c r="AB345" s="4" t="n">
-        <v>46</v>
+        <v>45.98</v>
       </c>
       <c r="AC345" s="4" t="n">
-        <v>54</v>
+        <v>54.02</v>
       </c>
       <c r="AD345" s="4" t="n">
         <v>0</v>
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="I346" s="4" t="n">
-        <v>70.48999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>100</v>
@@ -36207,13 +36207,13 @@
         </is>
       </c>
       <c r="M346" s="4" t="n">
-        <v>60.42</v>
+        <v>60.41</v>
       </c>
       <c r="N346" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O346" s="4" t="n">
-        <v>70.48999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="P346" s="4" t="n">
         <v>0</v>
@@ -36295,7 +36295,7 @@
         </is>
       </c>
       <c r="I347" s="4" t="n">
-        <v>-25.88</v>
+        <v>-25.89</v>
       </c>
       <c r="J347" s="4" t="n">
         <v>0</v>
@@ -36309,13 +36309,13 @@
         </is>
       </c>
       <c r="M347" s="4" t="n">
-        <v>-26.34</v>
+        <v>-26.35</v>
       </c>
       <c r="N347" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O347" s="4" t="n">
-        <v>-25.88</v>
+        <v>-25.89</v>
       </c>
       <c r="P347" s="4" t="n">
         <v>-1.94</v>
@@ -36411,7 +36411,7 @@
         </is>
       </c>
       <c r="M348" s="4" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="N348" s="4" t="n">
         <v>5.13</v>
@@ -36513,7 +36513,7 @@
         </is>
       </c>
       <c r="M349" s="4" t="n">
-        <v>-15.7</v>
+        <v>-15.71</v>
       </c>
       <c r="N349" s="4" t="n">
         <v>5.13</v>
@@ -36652,10 +36652,10 @@
         <v>0</v>
       </c>
       <c r="AB350" s="4" t="n">
-        <v>47.08</v>
+        <v>47.07</v>
       </c>
       <c r="AC350" s="4" t="n">
-        <v>52.92</v>
+        <v>52.93</v>
       </c>
       <c r="AD350" s="4" t="n">
         <v>0</v>
@@ -37209,7 +37209,7 @@
         </is>
       </c>
       <c r="I356" s="4" t="n">
-        <v>49.25</v>
+        <v>49.26</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>100</v>
@@ -37223,13 +37223,13 @@
         </is>
       </c>
       <c r="M356" s="4" t="n">
-        <v>38.57</v>
+        <v>38.58</v>
       </c>
       <c r="N356" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O356" s="4" t="n">
-        <v>49.25</v>
+        <v>49.26</v>
       </c>
       <c r="P356" s="4" t="n">
         <v>2.08</v>
@@ -37325,7 +37325,7 @@
         </is>
       </c>
       <c r="M357" s="4" t="n">
-        <v>-28.25</v>
+        <v>-28.24</v>
       </c>
       <c r="N357" s="4" t="n">
         <v>5.13</v>
@@ -37413,7 +37413,7 @@
         </is>
       </c>
       <c r="I358" s="4" t="n">
-        <v>54.96</v>
+        <v>54.97</v>
       </c>
       <c r="J358" s="4" t="n">
         <v>100</v>
@@ -37433,7 +37433,7 @@
         <v>5.13</v>
       </c>
       <c r="O358" s="4" t="n">
-        <v>54.96</v>
+        <v>54.97</v>
       </c>
       <c r="P358" s="4" t="n">
         <v>0</v>
@@ -37515,7 +37515,7 @@
         </is>
       </c>
       <c r="I359" s="4" t="n">
-        <v>16.8</v>
+        <v>16.81</v>
       </c>
       <c r="J359" s="4" t="n">
         <v>99.5</v>
@@ -37529,13 +37529,13 @@
         </is>
       </c>
       <c r="M359" s="4" t="n">
-        <v>11.65</v>
+        <v>11.66</v>
       </c>
       <c r="N359" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O359" s="4" t="n">
-        <v>16.8</v>
+        <v>16.81</v>
       </c>
       <c r="P359" s="4" t="n">
         <v>0.47</v>
@@ -37733,7 +37733,7 @@
         </is>
       </c>
       <c r="M361" s="4" t="n">
-        <v>11.1</v>
+        <v>11.11</v>
       </c>
       <c r="N361" s="4" t="n">
         <v>5.13</v>
@@ -37770,10 +37770,10 @@
         <v>0</v>
       </c>
       <c r="AB361" s="4" t="n">
-        <v>58.89</v>
+        <v>58.9</v>
       </c>
       <c r="AC361" s="4" t="n">
-        <v>41.11</v>
+        <v>41.1</v>
       </c>
       <c r="AD361" s="4" t="n">
         <v>0</v>
@@ -37821,7 +37821,7 @@
         </is>
       </c>
       <c r="I362" s="4" t="n">
-        <v>-2.16</v>
+        <v>-2.15</v>
       </c>
       <c r="J362" s="4" t="n">
         <v>29.8</v>
@@ -38435,7 +38435,7 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J368" s="4" t="n">
         <v>70.7</v>
@@ -38492,10 +38492,10 @@
         <v>0</v>
       </c>
       <c r="AB368" s="4" t="n">
-        <v>51.13</v>
+        <v>51.14</v>
       </c>
       <c r="AC368" s="4" t="n">
-        <v>48.87</v>
+        <v>48.86</v>
       </c>
       <c r="AD368" s="4" t="n">
         <v>0</v>
@@ -38747,7 +38747,7 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>8.67</v>
+        <v>8.68</v>
       </c>
       <c r="J371" s="4" t="n">
         <v>92.40000000000001</v>
@@ -39569,7 +39569,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>40.38</v>
+        <v>40.39</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -39583,13 +39583,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>27.1</v>
+        <v>27.11</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>40.38</v>
+        <v>40.39</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>0</v>
@@ -39620,10 +39620,10 @@
         <v>0</v>
       </c>
       <c r="AB379" s="4" t="n">
-        <v>70.19</v>
+        <v>70.2</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>29.81</v>
+        <v>29.8</v>
       </c>
       <c r="AD379" s="4" t="n">
         <v>0</v>
@@ -39671,7 +39671,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>17.09</v>
+        <v>17.1</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39685,13 +39685,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>11.24</v>
+        <v>11.25</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>17.09</v>
+        <v>17.1</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.61</v>
@@ -40985,7 +40985,7 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-13.73</v>
+        <v>-13.74</v>
       </c>
       <c r="J393" s="4" t="n">
         <v>0.8</v>
@@ -41507,7 +41507,7 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-44.68</v>
+        <v>-44.69</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>5.13</v>
@@ -41693,7 +41693,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>0.5</v>
@@ -41707,13 +41707,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-19.28</v>
+        <v>-19.29</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -41897,7 +41897,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-14.04</v>
+        <v>-14.05</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>0.8</v>
@@ -41917,7 +41917,7 @@
         <v>5.13</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-14.04</v>
+        <v>-14.05</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.23</v>
@@ -41999,7 +41999,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-19.42</v>
+        <v>-19.43</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.3</v>
@@ -42019,7 +42019,7 @@
         <v>5.13</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-19.42</v>
+        <v>-19.43</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -42101,7 +42101,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>40.34</v>
+        <v>40.33</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -42121,7 +42121,7 @@
         <v>5.13</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>40.34</v>
+        <v>40.33</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-7.34</v>
+        <v>-7.35</v>
       </c>
       <c r="J406" s="4" t="n">
         <v>11.4</v>
@@ -42317,7 +42317,7 @@
         <v>5.13</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-7.34</v>
+        <v>-7.35</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.92</v>
@@ -42395,7 +42395,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-13.73</v>
+        <v>-13.74</v>
       </c>
       <c r="J407" s="4" t="n">
         <v>0.8</v>
@@ -42409,13 +42409,13 @@
         </is>
       </c>
       <c r="M407" s="4" t="n">
-        <v>-17.41</v>
+        <v>-17.42</v>
       </c>
       <c r="N407" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-13.73</v>
+        <v>-13.74</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -42497,7 +42497,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-28.09</v>
+        <v>-28.1</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0</v>
@@ -42511,13 +42511,13 @@
         </is>
       </c>
       <c r="M408" s="4" t="n">
-        <v>-30.1</v>
+        <v>-30.11</v>
       </c>
       <c r="N408" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-28.09</v>
+        <v>-28.1</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -42613,7 +42613,7 @@
         </is>
       </c>
       <c r="M409" s="4" t="n">
-        <v>-19.05</v>
+        <v>-19.06</v>
       </c>
       <c r="N409" s="4" t="n">
         <v>5.13</v>
@@ -42650,10 +42650,10 @@
         <v>0</v>
       </c>
       <c r="AB409" s="4" t="n">
-        <v>40.28</v>
+        <v>40.27</v>
       </c>
       <c r="AC409" s="4" t="n">
-        <v>59.72</v>
+        <v>59.73</v>
       </c>
       <c r="AD409" s="4" t="n">
         <v>0</v>
@@ -42701,7 +42701,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-41.39</v>
+        <v>-41.4</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -42721,7 +42721,7 @@
         <v>5.13</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-41.39</v>
+        <v>-41.4</v>
       </c>
       <c r="P410" s="4" t="n">
         <v>-2.49</v>
@@ -42803,7 +42803,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-20.32</v>
+        <v>-20.33</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.2</v>
@@ -42823,7 +42823,7 @@
         <v>5.13</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-20.32</v>
+        <v>-20.33</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.89</v>
@@ -42905,7 +42905,7 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>-2.56</v>
+        <v>-2.57</v>
       </c>
       <c r="J412" s="4" t="n">
         <v>28.2</v>
@@ -42925,7 +42925,7 @@
         <v>5.13</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="P412" s="4" t="n">
         <v>-0.33</v>
@@ -43027,7 +43027,7 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>26.25</v>
+        <v>26.24</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>5.13</v>
@@ -43115,7 +43115,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-15.51</v>
+        <v>-15.52</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>0.6</v>
@@ -43129,13 +43129,13 @@
         </is>
       </c>
       <c r="M414" s="4" t="n">
-        <v>-16.88</v>
+        <v>-16.89</v>
       </c>
       <c r="N414" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-15.51</v>
+        <v>-15.52</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>0</v>
@@ -43329,7 +43329,7 @@
         </is>
       </c>
       <c r="M416" s="4" t="n">
-        <v>-47.06</v>
+        <v>-47.07</v>
       </c>
       <c r="N416" s="4" t="n">
         <v>5.13</v>
@@ -43417,7 +43417,7 @@
         </is>
       </c>
       <c r="I417" s="4" t="n">
-        <v>48.56</v>
+        <v>48.55</v>
       </c>
       <c r="J417" s="4" t="n">
         <v>100</v>
@@ -43431,13 +43431,13 @@
         </is>
       </c>
       <c r="M417" s="4" t="n">
-        <v>36.09</v>
+        <v>36.08</v>
       </c>
       <c r="N417" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O417" s="4" t="n">
-        <v>48.56</v>
+        <v>48.55</v>
       </c>
       <c r="P417" s="4" t="n">
         <v>1.31</v>
@@ -43613,7 +43613,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-13.71</v>
+        <v>-13.72</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>0.8</v>
@@ -43633,7 +43633,7 @@
         <v>5.13</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-13.71</v>
+        <v>-13.72</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.8100000000000001</v>
@@ -43711,7 +43711,7 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-3.05</v>
+        <v>-3.06</v>
       </c>
       <c r="J420" s="4" t="n">
         <v>26.3</v>
@@ -43819,7 +43819,7 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-11.64</v>
+        <v>-11.65</v>
       </c>
       <c r="J421" s="4" t="n">
         <v>1.2</v>
@@ -43833,13 +43833,13 @@
         </is>
       </c>
       <c r="M421" s="4" t="n">
-        <v>-12.3</v>
+        <v>-12.31</v>
       </c>
       <c r="N421" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-11.64</v>
+        <v>-11.65</v>
       </c>
       <c r="P421" s="4" t="n">
         <v>0</v>
@@ -43935,7 +43935,7 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-18.53</v>
+        <v>-18.54</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>5.13</v>
@@ -43972,10 +43972,10 @@
         <v>0</v>
       </c>
       <c r="AB422" s="4" t="n">
-        <v>42.71</v>
+        <v>42.7</v>
       </c>
       <c r="AC422" s="4" t="n">
-        <v>57.29</v>
+        <v>57.3</v>
       </c>
       <c r="AD422" s="4" t="n">
         <v>0</v>
@@ -44023,7 +44023,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-23.32</v>
+        <v>-23.33</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.1</v>
@@ -44037,13 +44037,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-19.65</v>
+        <v>-19.66</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-23.32</v>
+        <v>-23.33</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -44125,7 +44125,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-14.59</v>
+        <v>-14.6</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>0.7</v>
@@ -44145,7 +44145,7 @@
         <v>5.13</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-14.59</v>
+        <v>-14.6</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -44227,13 +44227,13 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>10.99</v>
+        <v>11.13</v>
       </c>
       <c r="J425" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="K425" s="4" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -44284,10 +44284,10 @@
         <v>0</v>
       </c>
       <c r="AB425" s="4" t="n">
-        <v>55.5</v>
+        <v>55.56</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>44.5</v>
+        <v>44.44</v>
       </c>
       <c r="AD425" s="4" t="n">
         <v>0</v>
@@ -44335,7 +44335,7 @@
         </is>
       </c>
       <c r="I426" s="4" t="n">
-        <v>53.35</v>
+        <v>53.34</v>
       </c>
       <c r="J426" s="4" t="n">
         <v>100</v>
@@ -44349,13 +44349,13 @@
         </is>
       </c>
       <c r="M426" s="4" t="n">
-        <v>38.61</v>
+        <v>38.6</v>
       </c>
       <c r="N426" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O426" s="4" t="n">
-        <v>53.35</v>
+        <v>53.34</v>
       </c>
       <c r="P426" s="4" t="n">
         <v>0</v>
@@ -44433,7 +44433,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>60.97</v>
+        <v>60.96</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -44447,13 +44447,13 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>54.32</v>
+        <v>54.31</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>60.97</v>
+        <v>60.96</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>0.21</v>
@@ -44549,13 +44549,13 @@
         </is>
       </c>
       <c r="M428" s="4" t="n">
-        <v>-17.81</v>
+        <v>-17.82</v>
       </c>
       <c r="N428" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O428" s="4" t="n">
-        <v>-18.88</v>
+        <v>-18.89</v>
       </c>
       <c r="P428" s="4" t="n">
         <v>-1.61</v>
@@ -44633,7 +44633,7 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-9.19</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="J429" s="4" t="n">
         <v>6.2</v>
@@ -44653,7 +44653,7 @@
         <v>5.13</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-9.19</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.93</v>
@@ -44731,7 +44731,7 @@
         </is>
       </c>
       <c r="I430" s="4" t="n">
-        <v>45.44</v>
+        <v>45.43</v>
       </c>
       <c r="J430" s="4" t="n">
         <v>100</v>
@@ -44751,7 +44751,7 @@
         <v>5.13</v>
       </c>
       <c r="O430" s="4" t="n">
-        <v>45.44</v>
+        <v>45.43</v>
       </c>
       <c r="P430" s="4" t="n">
         <v>0</v>
@@ -44833,7 +44833,7 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>7.64</v>
+        <v>7.66</v>
       </c>
       <c r="J431" s="4" t="n">
         <v>89.5</v>
@@ -44853,7 +44853,7 @@
         <v>5.13</v>
       </c>
       <c r="O431" s="4" t="n">
-        <v>10.53</v>
+        <v>10.52</v>
       </c>
       <c r="P431" s="4" t="n">
         <v>0.16</v>
@@ -44890,10 +44890,10 @@
         <v>0</v>
       </c>
       <c r="AB431" s="4" t="n">
-        <v>53.82</v>
+        <v>53.83</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>46.18</v>
+        <v>46.17</v>
       </c>
       <c r="AD431" s="4" t="n">
         <v>0</v>
@@ -44940,10 +44940,10 @@
         <v>2.52</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-4.57</v>
+        <v>-4.58</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>5.13</v>
@@ -45090,10 +45090,10 @@
         <v>0</v>
       </c>
       <c r="AB433" s="4" t="n">
-        <v>41.68</v>
+        <v>41.67</v>
       </c>
       <c r="AC433" s="4" t="n">
-        <v>58.32</v>
+        <v>58.33</v>
       </c>
       <c r="AD433" s="4" t="n">
         <v>0</v>
@@ -45259,7 +45259,7 @@
         <v>5.13</v>
       </c>
       <c r="O435" s="4" t="n">
-        <v>-14.18</v>
+        <v>-14.19</v>
       </c>
       <c r="P435" s="4" t="n">
         <v>-2.01</v>
@@ -45290,10 +45290,10 @@
         <v>0</v>
       </c>
       <c r="AB435" s="4" t="n">
-        <v>41.71</v>
+        <v>41.7</v>
       </c>
       <c r="AC435" s="4" t="n">
-        <v>56.11</v>
+        <v>56.12</v>
       </c>
       <c r="AD435" s="4" t="n">
         <v>2.18</v>
@@ -45853,13 +45853,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>67.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -45910,10 +45910,10 @@
         <v>0</v>
       </c>
       <c r="AB441" s="4" t="n">
-        <v>50.77</v>
+        <v>50.8</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>49.23</v>
+        <v>49.2</v>
       </c>
       <c r="AD441" s="4" t="n">
         <v>0</v>
@@ -46879,7 +46879,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>36.3</v>
+        <v>36.29</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -46893,13 +46893,13 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>20.6</v>
+        <v>20.58</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>36.32</v>
+        <v>36.29</v>
       </c>
       <c r="P451" s="4" t="n">
         <v>1.82</v>
@@ -47191,13 +47191,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47248,10 +47248,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>52.54</v>
+        <v>52.57</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>47.46</v>
+        <v>47.43</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -47397,7 +47397,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-22.74</v>
+        <v>-22.8</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47454,10 +47454,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>38.63</v>
+        <v>38.6</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>61.37</v>
+        <v>61.4</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -48137,7 +48137,7 @@
         </is>
       </c>
       <c r="M463" s="4" t="n">
-        <v>41.85</v>
+        <v>41.86</v>
       </c>
       <c r="N463" s="4" t="n">
         <v>5.13</v>
@@ -48225,13 +48225,13 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="J464" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="K464" s="4" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -48282,10 +48282,10 @@
         <v>0</v>
       </c>
       <c r="AB464" s="4" t="n">
-        <v>51.85</v>
+        <v>51.86</v>
       </c>
       <c r="AC464" s="4" t="n">
-        <v>48.15</v>
+        <v>48.14</v>
       </c>
       <c r="AD464" s="4" t="n">
         <v>0</v>
@@ -48333,7 +48333,7 @@
         </is>
       </c>
       <c r="I465" s="4" t="n">
-        <v>62.34</v>
+        <v>62.35</v>
       </c>
       <c r="J465" s="4" t="n">
         <v>100</v>
@@ -48353,7 +48353,7 @@
         <v>5.13</v>
       </c>
       <c r="O465" s="4" t="n">
-        <v>62.34</v>
+        <v>62.35</v>
       </c>
       <c r="P465" s="4" t="n">
         <v>0</v>
@@ -48449,7 +48449,7 @@
         </is>
       </c>
       <c r="M466" s="4" t="n">
-        <v>-22.2</v>
+        <v>-22.19</v>
       </c>
       <c r="N466" s="4" t="n">
         <v>5.13</v>
@@ -48486,10 +48486,10 @@
         <v>0</v>
       </c>
       <c r="AB466" s="4" t="n">
-        <v>37.59</v>
+        <v>37.6</v>
       </c>
       <c r="AC466" s="4" t="n">
-        <v>62.41</v>
+        <v>62.4</v>
       </c>
       <c r="AD466" s="4" t="n">
         <v>0</v>
@@ -48537,7 +48537,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-18.94</v>
+        <v>-18.93</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.3</v>
@@ -48551,13 +48551,13 @@
         </is>
       </c>
       <c r="M467" s="4" t="n">
-        <v>-15.81</v>
+        <v>-15.8</v>
       </c>
       <c r="N467" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-18.03</v>
+        <v>-18.02</v>
       </c>
       <c r="P467" s="4" t="n">
         <v>-1.71</v>
@@ -48594,10 +48594,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>40.53</v>
+        <v>40.54</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>59.47</v>
+        <v>59.46</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="I468" s="4" t="n">
-        <v>-18.83</v>
+        <v>-18.82</v>
       </c>
       <c r="J468" s="4" t="n">
         <v>0.3</v>
@@ -48655,13 +48655,13 @@
         </is>
       </c>
       <c r="M468" s="4" t="n">
-        <v>-21.43</v>
+        <v>-21.42</v>
       </c>
       <c r="N468" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O468" s="4" t="n">
-        <v>-18.83</v>
+        <v>-18.82</v>
       </c>
       <c r="P468" s="4" t="n">
         <v>-1.54</v>
@@ -48794,10 +48794,10 @@
         <v>0</v>
       </c>
       <c r="AB469" s="4" t="n">
-        <v>42.77</v>
+        <v>42.78</v>
       </c>
       <c r="AC469" s="4" t="n">
-        <v>57.23</v>
+        <v>57.22</v>
       </c>
       <c r="AD469" s="4" t="n">
         <v>0</v>
@@ -49147,13 +49147,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.91</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>46.8</v>
+        <v>47.3</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>53.2</v>
+        <v>52.7</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49161,13 +49161,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.72</v>
+        <v>-10.54</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.17</v>
+        <v>-1.99</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -49204,10 +49204,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.37</v>
+        <v>45.42</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.63</v>
+        <v>46.58</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49722,10 +49722,10 @@
         <v>0</v>
       </c>
       <c r="AB478" s="4" t="n">
-        <v>47.2</v>
+        <v>47.21</v>
       </c>
       <c r="AC478" s="4" t="n">
-        <v>52.8</v>
+        <v>52.79</v>
       </c>
       <c r="AD478" s="4" t="n">
         <v>0</v>
@@ -49787,13 +49787,13 @@
         </is>
       </c>
       <c r="M479" s="4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="N479" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O479" s="4" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="P479" s="4" t="n">
         <v>1.71</v>
@@ -49877,13 +49877,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-1.49</v>
+        <v>-1.5</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-39.35</v>
+        <v>-39.36</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0</v>
@@ -50505,7 +50505,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>29.78</v>
+        <v>29.81</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -50525,7 +50525,7 @@
         <v>5.13</v>
       </c>
       <c r="O486" s="4" t="n">
-        <v>35.74</v>
+        <v>35.75</v>
       </c>
       <c r="P486" s="4" t="n">
         <v>0.66</v>
@@ -50562,10 +50562,10 @@
         <v>0</v>
       </c>
       <c r="AB486" s="4" t="n">
-        <v>64.89</v>
+        <v>64.91</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>35.11</v>
+        <v>35.09</v>
       </c>
       <c r="AD486" s="4" t="n">
         <v>0</v>
@@ -50613,13 +50613,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         </is>
       </c>
       <c r="M487" s="4" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
       <c r="N487" s="4" t="n">
         <v>5.13</v>
@@ -50670,10 +50670,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>51.06</v>
+        <v>51.04</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>48.94</v>
+        <v>48.96</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -50717,7 +50717,7 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>5.04</v>
+        <v>5.05</v>
       </c>
       <c r="J488" s="4" t="n">
         <v>81</v>
@@ -50774,10 +50774,10 @@
         <v>0</v>
       </c>
       <c r="AB488" s="4" t="n">
-        <v>52.52</v>
+        <v>52.53</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>47.48</v>
+        <v>47.47</v>
       </c>
       <c r="AD488" s="4" t="n">
         <v>0</v>
@@ -50835,7 +50835,7 @@
         </is>
       </c>
       <c r="M489" s="4" t="n">
-        <v>6.87</v>
+        <v>6.86</v>
       </c>
       <c r="N489" s="4" t="n">
         <v>5.13</v>
@@ -51037,7 +51037,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-20.82</v>
+        <v>-21</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>4.9</v>
@@ -51092,16 +51092,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>32.91</v>
+        <v>32.73</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.72</v>
+        <v>53.74</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51253,13 +51253,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-6.51</v>
+        <v>-6.95</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>30.5</v>
+        <v>29.2</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>69.5</v>
+        <v>70.8</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51308,16 +51308,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>46.74</v>
+        <v>46.52</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>30.5</v>
+        <v>29.2</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>53.26</v>
+        <v>53.48</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -51361,7 +51361,7 @@
         </is>
       </c>
       <c r="I494" s="4" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="J494" s="4" t="n">
         <v>87.8</v>
@@ -51375,7 +51375,7 @@
         </is>
       </c>
       <c r="M494" s="4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="N494" s="4" t="n">
         <v>5.13</v>
@@ -51571,7 +51571,7 @@
         </is>
       </c>
       <c r="I496" s="4" t="n">
-        <v>18.61</v>
+        <v>18.62</v>
       </c>
       <c r="J496" s="4" t="n">
         <v>99.7</v>
@@ -51585,13 +51585,13 @@
         </is>
       </c>
       <c r="M496" s="4" t="n">
-        <v>7.53</v>
+        <v>7.54</v>
       </c>
       <c r="N496" s="4" t="n">
         <v>5.13</v>
       </c>
       <c r="O496" s="4" t="n">
-        <v>18.61</v>
+        <v>18.62</v>
       </c>
       <c r="P496" s="4" t="n">
         <v>3.16</v>
@@ -51693,7 +51693,7 @@
         <v>5.13</v>
       </c>
       <c r="O497" s="4" t="n">
-        <v>-1.95</v>
+        <v>-1.96</v>
       </c>
       <c r="P497" s="4" t="n">
         <v>0.6</v>
@@ -51893,7 +51893,7 @@
         </is>
       </c>
       <c r="M499" s="4" t="n">
-        <v>12.55</v>
+        <v>12.56</v>
       </c>
       <c r="N499" s="4" t="n">
         <v>5.13</v>
@@ -51981,7 +51981,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>22.77</v>
+        <v>22.82</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -51995,7 +51995,7 @@
         </is>
       </c>
       <c r="M500" s="4" t="n">
-        <v>17.1</v>
+        <v>17.11</v>
       </c>
       <c r="N500" s="4" t="n">
         <v>5.13</v>
@@ -52038,10 +52038,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.39</v>
+        <v>61.41</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.61</v>
+        <v>38.59</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -52397,7 +52397,7 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="J504" s="4" t="n">
         <v>63.2</v>
@@ -52933,7 +52933,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -53627,7 +53627,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>121.4</v>
+        <v>121.5</v>
       </c>
       <c r="K14" t="n">
         <v>125</v>
@@ -55089,7 +55089,7 @@
         <v>112</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -55547,13 +55547,13 @@
         <v>42</v>
       </c>
       <c r="L47" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M47" t="n">
         <v>53</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.2</v>
+        <v>232.1</v>
       </c>
       <c r="C9" t="n">
-        <v>202.8</v>
+        <v>202.9</v>
       </c>
       <c r="D9" t="n">
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>80.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-2.96</v>
+        <v>-3.29</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>39.8</v>
+        <v>40.9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>60.2</v>
+        <v>59.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.95</v>
+        <v>-2.98</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>42</v>
+        <v>40.1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>58</v>
+        <v>59.9</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.49</v>
+        <v>-2.54</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.15</v>
+        <v>-1.2</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.1</v>
@@ -4750,16 +4750,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.53</v>
+        <v>48.51</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>42</v>
+        <v>40.1</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.47</v>
+        <v>51.49</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -24673,7 +24673,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>31.04</v>
+        <v>30.56</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24771,13 +24771,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.14</v>
+        <v>-4.31</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>36.4</v>
+        <v>35.3</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>63.6</v>
+        <v>64.7</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.26</v>
+        <v>-6.24</v>
       </c>
       <c r="J269" s="4" t="n">
         <v>14.9</v>
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-11.51</v>
+        <v>-11.49</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-7.47</v>
+        <v>-7.45</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28318,10 +28318,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.87</v>
+        <v>46.88</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.13</v>
+        <v>53.12</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28369,7 +28369,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.21</v>
+        <v>-33.18</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28383,13 +28383,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-30.48</v>
+        <v>-30.45</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.21</v>
+        <v>-33.18</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28420,10 +28420,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.4</v>
+        <v>33.41</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>66.59</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -30025,13 +30025,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.67</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30039,13 +30039,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.970000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-10.29</v>
+        <v>-10.25</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30082,10 +30082,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.15</v>
+        <v>45.17</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.85</v>
+        <v>54.83</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30129,7 +30129,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.46</v>
+        <v>12.49</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>98.90000000000001</v>
@@ -30143,13 +30143,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.13</v>
+        <v>14.17</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30186,10 +30186,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.23</v>
+        <v>56.25</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.77</v>
+        <v>43.75</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30237,7 +30237,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.84</v>
+        <v>-52.8</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30251,13 +30251,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.92</v>
+        <v>-49.88</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.84</v>
+        <v>-52.8</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30288,10 +30288,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.58</v>
+        <v>23.6</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.42</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -44624,7 +44624,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Alex Cornwallis</t>
+          <t>Dan Barrios</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -49153,13 +49153,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>52.6</v>
+        <v>52.2</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49167,13 +49167,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.56</v>
+        <v>-10.65</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-1.97</v>
+        <v>-2.06</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -49210,10 +49210,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.42</v>
+        <v>45.39</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.58</v>
+        <v>46.61</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -51043,13 +51043,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-22.79</v>
+        <v>-22.7</v>
       </c>
       <c r="J491" s="4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51098,16 +51098,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>11.63</v>
+        <v>11.66</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>30.96</v>
+        <v>30.99</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.75</v>
+        <v>53.69</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51259,13 +51259,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-6.69</v>
+        <v>-6.48</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>30.1</v>
+        <v>31.6</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>69.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51314,16 +51314,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>46.65</v>
+        <v>46.76</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>30.1</v>
+        <v>31.6</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>53.35</v>
+        <v>53.24</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="C8" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>80.2</v>
+        <v>80.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="C10" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="D10" t="n">
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>40.6</v>
+        <v>40.1</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.29</v>
+        <v>-3.35</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40.9</v>
+        <v>39.9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>59.1</v>
+        <v>60.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.98</v>
+        <v>-3.04</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>40.1</v>
+        <v>40.6</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>59.9</v>
+        <v>59.4</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4709,13 +4709,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.54</v>
+        <v>-2.61</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.27</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.1</v>
@@ -4750,16 +4750,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.51</v>
+        <v>48.48</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>40.1</v>
+        <v>40.6</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.49</v>
+        <v>51.52</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -22830,7 +22830,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Cleo Fields</t>
+          <t>Democratic candidate (LA-06)</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -22838,24 +22838,20 @@
           <t>Peter Williams</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
       <c r="I216" s="4" t="n">
-        <v>-20.11</v>
+        <v>-28.11</v>
       </c>
       <c r="J216" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -22869,13 +22865,13 @@
         <v>5.17</v>
       </c>
       <c r="O216" s="4" t="n">
-        <v>-20.11</v>
+        <v>-28.11</v>
       </c>
       <c r="P216" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q216" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R216" s="4" t="n">
         <v>-32.4</v>
@@ -22900,10 +22896,10 @@
         <v>0</v>
       </c>
       <c r="AB216" s="4" t="n">
-        <v>39.95</v>
+        <v>35.95</v>
       </c>
       <c r="AC216" s="4" t="n">
-        <v>60.05</v>
+        <v>64.05</v>
       </c>
       <c r="AD216" s="4" t="n">
         <v>0</v>
@@ -24673,7 +24669,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.56</v>
+        <v>30.48</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24771,13 +24767,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.31</v>
+        <v>-4.97</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>35.3</v>
+        <v>34.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>64.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -28261,13 +28257,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.24</v>
+        <v>-6.29</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28275,13 +28271,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-11.49</v>
+        <v>-11.56</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-7.45</v>
+        <v>-7.52</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28318,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.12</v>
+        <v>53.14</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28369,7 +28365,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.18</v>
+        <v>-33.25</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28383,13 +28379,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-30.45</v>
+        <v>-30.52</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.18</v>
+        <v>-33.25</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28420,10 +28416,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.41</v>
+        <v>33.37</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.59</v>
+        <v>66.63</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -30025,7 +30021,7 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.67</v>
+        <v>-9.65</v>
       </c>
       <c r="J286" s="4" t="n">
         <v>5</v>
@@ -30035,17 +30031,17 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>Safe R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.93</v>
+        <v>-8.91</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-10.25</v>
+        <v>-10.24</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30129,7 +30125,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.49</v>
+        <v>12.51</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>98.90000000000001</v>
@@ -30143,13 +30139,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.17</v>
+        <v>14.18</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30237,7 +30233,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.8</v>
+        <v>-52.78</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30251,13 +30247,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.88</v>
+        <v>-49.87</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.8</v>
+        <v>-52.78</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30288,10 +30284,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.6</v>
+        <v>23.61</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.40000000000001</v>
+        <v>76.39</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -35773,13 +35769,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-6.66</v>
+        <v>-4.86</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>13.6</v>
+        <v>19.6</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>86.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35793,13 +35789,13 @@
         <v>5.17</v>
       </c>
       <c r="O342" s="4" t="n">
-        <v>-7.82</v>
+        <v>-5.24</v>
       </c>
       <c r="P342" s="4" t="n">
         <v>-0.51</v>
       </c>
       <c r="Q342" s="4" t="n">
-        <v>-4.58</v>
+        <v>-2</v>
       </c>
       <c r="R342" s="4" t="n">
         <v>-11.15</v>
@@ -35830,10 +35826,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>46.67</v>
+        <v>47.57</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>53.33</v>
+        <v>52.43</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -49153,13 +49149,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.66</v>
+        <v>-0.95</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49167,13 +49163,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.65</v>
+        <v>-10.66</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.17</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.06</v>
+        <v>-2.07</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -51043,13 +51039,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-22.7</v>
+        <v>-22.98</v>
       </c>
       <c r="J491" s="4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51098,16 +51094,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>11.66</v>
+        <v>11.21</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>30.99</v>
+        <v>31.08</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.69</v>
+        <v>54.06</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51259,13 +51255,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-6.48</v>
+        <v>-6.41</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51314,16 +51310,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>46.76</v>
+        <v>46.79</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>53.24</v>
+        <v>53.21</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -52939,7 +52935,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -55550,7 +55546,7 @@
         <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L47" t="n">
         <v>27</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>50.4</v>
+        <v>51.9</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="C10" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="D10" t="n">
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>40.8</v>
+        <v>39.1</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.04</v>
+        <v>-3.54</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.06</v>
+        <v>-6.05</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>15.5</v>
@@ -1689,13 +1689,13 @@
         <v>-13.22</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>39.47</v>
+        <v>39.46</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>43.33</v>
       </c>
       <c r="U9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V9" s="4" t="n">
         <v>-4.22</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12.52</v>
+        <v>12.33</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2627,16 +2627,16 @@
         <v>7.09</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>53.25</v>
+        <v>52.17</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>39.65</v>
+        <v>38.68</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>13.6</v>
+        <v>13.48</v>
       </c>
       <c r="W18" s="5" t="n">
         <v>0</v>
@@ -2650,16 +2650,16 @@
         </is>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.14</v>
+        <v>3.21</v>
       </c>
       <c r="AA18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>55.62</v>
+        <v>54.36</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>43.24</v>
+        <v>42.43</v>
       </c>
       <c r="AD18" s="4" t="n">
         <v>0</v>
@@ -2735,16 +2735,16 @@
         <v>-1.44</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>44.29</v>
+        <v>44.1</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>36.81</v>
+        <v>36.73</v>
       </c>
       <c r="U19" t="n">
         <v>18</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>7.82</v>
+        <v>7.71</v>
       </c>
       <c r="W19" s="5" t="n">
         <v>5958887</v>
@@ -3382,13 +3382,13 @@
         <v>49.63</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>36.12</v>
+        <v>36.11</v>
       </c>
       <c r="U25" t="n">
         <v>15</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>14.63</v>
+        <v>14.64</v>
       </c>
       <c r="W25" s="5" t="n">
         <v>16594119</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16.49</v>
+        <v>17.15</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3797,16 +3797,16 @@
         <v>-1.75</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>52.66</v>
+        <v>52.77</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>37</v>
+        <v>35.68</v>
       </c>
       <c r="U29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>15.66</v>
+        <v>17.09</v>
       </c>
       <c r="W29" s="5" t="n">
         <v>34960533</v>
@@ -3822,10 +3822,10 @@
         <v>0</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>58.25</v>
+        <v>58.57</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>41.75</v>
+        <v>41.43</v>
       </c>
       <c r="AD29" s="4" t="n">
         <v>0</v>
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-3.26</v>
+        <v>-1.8</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>40.2</v>
+        <v>44.5</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>59.8</v>
+        <v>55.5</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4727,16 +4727,16 @@
         <v>-13.8</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>38</v>
+        <v>47.28</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>48</v>
+        <v>51.28</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>-13</v>
+        <v>-4.2</v>
       </c>
       <c r="W38" s="5" t="n">
         <v>0</v>
@@ -4750,16 +4750,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.37</v>
+        <v>49.1</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>40.2</v>
+        <v>44.5</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.63</v>
+        <v>50.9</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>-17.82</v>
+        <v>-17.81</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>0.4</v>
@@ -14015,7 +14015,7 @@
         <v>5.16</v>
       </c>
       <c r="O129" s="4" t="n">
-        <v>-17.82</v>
+        <v>-17.81</v>
       </c>
       <c r="P129" s="4" t="n">
         <v>-0.6899999999999999</v>
@@ -14219,7 +14219,7 @@
         <v>5.16</v>
       </c>
       <c r="O131" s="4" t="n">
-        <v>-5.12</v>
+        <v>-5.11</v>
       </c>
       <c r="P131" s="4" t="n">
         <v>0.25</v>
@@ -14307,21 +14307,21 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-9.41</v>
+        <v>-10.65</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="M132" s="4" t="n">
-        <v>-12.11</v>
+        <v>-12.1</v>
       </c>
       <c r="N132" s="4" t="n">
         <v>5.16</v>
@@ -14338,12 +14338,18 @@
       <c r="R132" s="4" t="n">
         <v>-16.4</v>
       </c>
-      <c r="S132" s="4" t="n"/>
-      <c r="T132" s="4" t="n"/>
+      <c r="S132" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T132" s="4" t="n">
+        <v>44</v>
+      </c>
       <c r="U132" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V132" s="4" t="n">
+        <v>-12</v>
+      </c>
       <c r="W132" s="5" t="n">
         <v>697539</v>
       </c>
@@ -14358,10 +14364,10 @@
         <v>0</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>45.3</v>
+        <v>44.68</v>
       </c>
       <c r="AC132" s="4" t="n">
-        <v>54.7</v>
+        <v>55.32</v>
       </c>
       <c r="AD132" s="4" t="n">
         <v>0</v>
@@ -14623,7 +14629,7 @@
         </is>
       </c>
       <c r="M135" s="4" t="n">
-        <v>-11.39</v>
+        <v>-11.38</v>
       </c>
       <c r="N135" s="4" t="n">
         <v>5.16</v>
@@ -14711,7 +14717,7 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>-10.8</v>
+        <v>-10.79</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>2.3</v>
@@ -14731,7 +14737,7 @@
         <v>5.16</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>-10.8</v>
+        <v>-10.79</v>
       </c>
       <c r="P136" s="4" t="n">
         <v>0</v>
@@ -14827,7 +14833,7 @@
         </is>
       </c>
       <c r="M137" s="4" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="N137" s="4" t="n">
         <v>5.16</v>
@@ -14924,10 +14930,10 @@
         <v>7.14</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -15074,10 +15080,10 @@
         <v>0</v>
       </c>
       <c r="AB139" s="4" t="n">
-        <v>43.42</v>
+        <v>43.43</v>
       </c>
       <c r="AC139" s="4" t="n">
-        <v>56.58</v>
+        <v>56.57</v>
       </c>
       <c r="AD139" s="4" t="n">
         <v>0</v>
@@ -15124,10 +15130,10 @@
         <v>-4.8</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -15223,7 +15229,7 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>-18.43</v>
+        <v>-18.42</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>0.3</v>
@@ -15243,7 +15249,7 @@
         <v>5.16</v>
       </c>
       <c r="O141" s="4" t="n">
-        <v>-18.43</v>
+        <v>-18.42</v>
       </c>
       <c r="P141" s="4" t="n">
         <v>-1.69</v>
@@ -15325,7 +15331,7 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>6.2</v>
@@ -15345,7 +15351,7 @@
         <v>5.16</v>
       </c>
       <c r="O142" s="4" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="P142" s="4" t="n">
         <v>0</v>
@@ -15437,7 +15443,7 @@
         </is>
       </c>
       <c r="M143" s="4" t="n">
-        <v>-25.38</v>
+        <v>-25.37</v>
       </c>
       <c r="N143" s="4" t="n">
         <v>5.16</v>
@@ -15637,7 +15643,7 @@
         </is>
       </c>
       <c r="M145" s="4" t="n">
-        <v>-11.44</v>
+        <v>-11.43</v>
       </c>
       <c r="N145" s="4" t="n">
         <v>5.16</v>
@@ -15735,7 +15741,7 @@
         </is>
       </c>
       <c r="M146" s="4" t="n">
-        <v>-3.79</v>
+        <v>-3.78</v>
       </c>
       <c r="N146" s="4" t="n">
         <v>5.16</v>
@@ -15823,7 +15829,7 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>29.86</v>
+        <v>29.87</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>100</v>
@@ -15837,13 +15843,13 @@
         </is>
       </c>
       <c r="M147" s="4" t="n">
-        <v>20.62</v>
+        <v>20.63</v>
       </c>
       <c r="N147" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O147" s="4" t="n">
-        <v>29.86</v>
+        <v>29.87</v>
       </c>
       <c r="P147" s="4" t="n">
         <v>0</v>
@@ -16023,7 +16029,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>6.98</v>
+        <v>6.99</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>87.5</v>
@@ -16131,7 +16137,7 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>-11.67</v>
+        <v>-11.66</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>1.2</v>
@@ -16151,7 +16157,7 @@
         <v>5.16</v>
       </c>
       <c r="O150" s="4" t="n">
-        <v>-11.67</v>
+        <v>-11.66</v>
       </c>
       <c r="P150" s="4" t="n">
         <v>-2.32</v>
@@ -16355,7 +16361,7 @@
         </is>
       </c>
       <c r="M152" s="4" t="n">
-        <v>-16.05</v>
+        <v>-16.04</v>
       </c>
       <c r="N152" s="4" t="n">
         <v>5.16</v>
@@ -16547,7 +16553,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>24.25</v>
+        <v>24.26</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>99.90000000000001</v>
@@ -16567,7 +16573,7 @@
         <v>5.16</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>24.25</v>
+        <v>24.26</v>
       </c>
       <c r="P154" s="4" t="n">
         <v>1.36</v>
@@ -16649,7 +16655,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>-29.16</v>
+        <v>-29.15</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>0</v>
@@ -16669,7 +16675,7 @@
         <v>5.16</v>
       </c>
       <c r="O155" s="4" t="n">
-        <v>-29.16</v>
+        <v>-29.15</v>
       </c>
       <c r="P155" s="4" t="n">
         <v>-1.75</v>
@@ -16853,7 +16859,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>83.8</v>
+        <v>83.81</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>100</v>
@@ -16873,7 +16879,7 @@
         <v>5.16</v>
       </c>
       <c r="O157" s="4" t="n">
-        <v>83.8</v>
+        <v>83.81</v>
       </c>
       <c r="P157" s="4" t="n">
         <v>0</v>
@@ -16955,7 +16961,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>63.1</v>
+        <v>63.11</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>100</v>
@@ -16975,7 +16981,7 @@
         <v>5.16</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>63.1</v>
+        <v>63.11</v>
       </c>
       <c r="P158" s="4" t="n">
         <v>2.07</v>
@@ -17559,7 +17565,7 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-11.68</v>
+        <v>-11.67</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>1.2</v>
@@ -17579,7 +17585,7 @@
         <v>5.16</v>
       </c>
       <c r="O164" s="4" t="n">
-        <v>-11.68</v>
+        <v>-11.67</v>
       </c>
       <c r="P164" s="4" t="n">
         <v>-1.96</v>
@@ -17657,7 +17663,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>50.89</v>
+        <v>50.9</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>100</v>
@@ -17671,13 +17677,13 @@
         </is>
       </c>
       <c r="M165" s="4" t="n">
-        <v>45.46</v>
+        <v>45.47</v>
       </c>
       <c r="N165" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>50.89</v>
+        <v>50.9</v>
       </c>
       <c r="P165" s="4" t="n">
         <v>0</v>
@@ -18483,7 +18489,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-28.06</v>
+        <v>-27.45</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18497,13 +18503,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-45.02</v>
+        <v>-43.93</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-42.56</v>
+        <v>-41.47</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18540,10 +18546,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>35.97</v>
+        <v>36.28</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>64.03</v>
+        <v>63.72</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18591,7 +18597,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-29.2</v>
+        <v>-28.1</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0</v>
@@ -18605,13 +18611,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-27.21</v>
+        <v>-26.12</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-29.2</v>
+        <v>-28.1</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -18642,10 +18648,10 @@
         <v>0</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>35.4</v>
+        <v>35.95</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>64.59999999999999</v>
+        <v>64.05</v>
       </c>
       <c r="AD174" s="4" t="n">
         <v>0</v>
@@ -24669,7 +24675,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.74</v>
+        <v>30.67</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24683,13 +24689,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>22.25</v>
+        <v>22.21</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.24</v>
+        <v>31.2</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24720,10 +24726,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.34</v>
+        <v>62.32</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.66</v>
+        <v>32.68</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24767,13 +24773,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>60.9</v>
+        <v>61.2</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24781,13 +24787,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.21</v>
+        <v>-5.25</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24824,10 +24830,10 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>45.45</v>
+        <v>45.44</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>49.55</v>
+        <v>49.56</v>
       </c>
       <c r="AD235" s="4" t="n">
         <v>5</v>
@@ -25130,10 +25136,10 @@
         <v>0</v>
       </c>
       <c r="AB238" s="4" t="n">
-        <v>60.07</v>
+        <v>60.06</v>
       </c>
       <c r="AC238" s="4" t="n">
-        <v>39.93</v>
+        <v>39.94</v>
       </c>
       <c r="AD238" s="4" t="n">
         <v>0</v>
@@ -25405,7 +25411,7 @@
         </is>
       </c>
       <c r="M241" s="4" t="n">
-        <v>27.94</v>
+        <v>27.93</v>
       </c>
       <c r="N241" s="4" t="n">
         <v>5.16</v>
@@ -25493,7 +25499,7 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="J242" s="4" t="n">
         <v>63.9</v>
@@ -25601,7 +25607,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>18.49</v>
+        <v>18.48</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>99.7</v>
@@ -25615,13 +25621,13 @@
         </is>
       </c>
       <c r="M243" s="4" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="N243" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>18.49</v>
+        <v>18.48</v>
       </c>
       <c r="P243" s="4" t="n">
         <v>1.52</v>
@@ -25703,7 +25709,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-33.08</v>
+        <v>-33.09</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -25723,7 +25729,7 @@
         <v>5.16</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-33.08</v>
+        <v>-33.09</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -25815,13 +25821,13 @@
         </is>
       </c>
       <c r="M245" s="4" t="n">
-        <v>-1.98</v>
+        <v>-1.99</v>
       </c>
       <c r="N245" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O245" s="4" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="P245" s="4" t="n">
         <v>-0.11</v>
@@ -25919,7 +25925,7 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>20.56</v>
+        <v>20.55</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.16</v>
@@ -25956,10 +25962,10 @@
         <v>0</v>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>63.6</v>
+        <v>63.59</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>36.4</v>
+        <v>36.41</v>
       </c>
       <c r="AD246" s="4" t="n">
         <v>0</v>
@@ -26109,7 +26115,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>58.45</v>
+        <v>58.44</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -26129,7 +26135,7 @@
         <v>5.16</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>58.45</v>
+        <v>58.44</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
@@ -28257,13 +28263,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.25</v>
+        <v>-6.84</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>14.9</v>
+        <v>13</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28271,13 +28277,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-11.48</v>
+        <v>-12.33</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-7.44</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28314,10 +28320,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.87</v>
+        <v>46.58</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.13</v>
+        <v>53.42</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28365,7 +28371,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.18</v>
+        <v>-34.04</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28379,13 +28385,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-30.44</v>
+        <v>-31.3</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.18</v>
+        <v>-34.04</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28416,10 +28422,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.41</v>
+        <v>32.98</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.59</v>
+        <v>67.02</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28467,13 +28473,13 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J271" s="4" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K271" s="4" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -28481,13 +28487,13 @@
         </is>
       </c>
       <c r="M271" s="4" t="n">
-        <v>-7.87</v>
+        <v>-7.82</v>
       </c>
       <c r="N271" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O271" s="4" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="P271" s="4" t="n">
         <v>0.04</v>
@@ -28524,10 +28530,10 @@
         <v>0</v>
       </c>
       <c r="AB271" s="4" t="n">
-        <v>51.3</v>
+        <v>51.32</v>
       </c>
       <c r="AC271" s="4" t="n">
-        <v>48.7</v>
+        <v>48.68</v>
       </c>
       <c r="AD271" s="4" t="n">
         <v>0</v>
@@ -28575,7 +28581,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>45.26</v>
+        <v>45.31</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -28589,13 +28595,13 @@
         </is>
       </c>
       <c r="M272" s="4" t="n">
-        <v>36.9</v>
+        <v>36.95</v>
       </c>
       <c r="N272" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O272" s="4" t="n">
-        <v>45.26</v>
+        <v>45.31</v>
       </c>
       <c r="P272" s="4" t="n">
         <v>0</v>
@@ -28626,10 +28632,10 @@
         <v>0</v>
       </c>
       <c r="AB272" s="4" t="n">
-        <v>72.63</v>
+        <v>72.66</v>
       </c>
       <c r="AC272" s="4" t="n">
-        <v>27.37</v>
+        <v>27.34</v>
       </c>
       <c r="AD272" s="4" t="n">
         <v>0</v>
@@ -28677,13 +28683,13 @@
         </is>
       </c>
       <c r="I273" s="4" t="n">
-        <v>-8.08</v>
+        <v>-8.02</v>
       </c>
       <c r="J273" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="K273" s="4" t="n">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -28691,13 +28697,13 @@
         </is>
       </c>
       <c r="M273" s="4" t="n">
-        <v>-9.92</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="N273" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O273" s="4" t="n">
-        <v>-8.08</v>
+        <v>-8.02</v>
       </c>
       <c r="P273" s="4" t="n">
         <v>-1.57</v>
@@ -28728,10 +28734,10 @@
         <v>0</v>
       </c>
       <c r="AB273" s="4" t="n">
-        <v>45.96</v>
+        <v>45.99</v>
       </c>
       <c r="AC273" s="4" t="n">
-        <v>54.04</v>
+        <v>54.01</v>
       </c>
       <c r="AD273" s="4" t="n">
         <v>0</v>
@@ -28779,7 +28785,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>58.77</v>
+        <v>58.82</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>100</v>
@@ -28793,13 +28799,13 @@
         </is>
       </c>
       <c r="M274" s="4" t="n">
-        <v>48.59</v>
+        <v>48.65</v>
       </c>
       <c r="N274" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O274" s="4" t="n">
-        <v>58.77</v>
+        <v>58.82</v>
       </c>
       <c r="P274" s="4" t="n">
         <v>1.88</v>
@@ -28830,10 +28836,10 @@
         <v>0</v>
       </c>
       <c r="AB274" s="4" t="n">
-        <v>79.39</v>
+        <v>79.41</v>
       </c>
       <c r="AC274" s="4" t="n">
-        <v>20.61</v>
+        <v>20.59</v>
       </c>
       <c r="AD274" s="4" t="n">
         <v>0</v>
@@ -28881,13 +28887,13 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>-10.92</v>
+        <v>-10.87</v>
       </c>
       <c r="J275" s="4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K275" s="4" t="n">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -28895,13 +28901,13 @@
         </is>
       </c>
       <c r="M275" s="4" t="n">
-        <v>-14.77</v>
+        <v>-14.72</v>
       </c>
       <c r="N275" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O275" s="4" t="n">
-        <v>-10.92</v>
+        <v>-10.87</v>
       </c>
       <c r="P275" s="4" t="n">
         <v>-0.98</v>
@@ -28932,10 +28938,10 @@
         <v>0</v>
       </c>
       <c r="AB275" s="4" t="n">
-        <v>44.54</v>
+        <v>44.57</v>
       </c>
       <c r="AC275" s="4" t="n">
-        <v>55.46</v>
+        <v>55.43</v>
       </c>
       <c r="AD275" s="4" t="n">
         <v>0</v>
@@ -28983,7 +28989,7 @@
         </is>
       </c>
       <c r="I276" s="4" t="n">
-        <v>-13</v>
+        <v>-12.95</v>
       </c>
       <c r="J276" s="4" t="n">
         <v>1</v>
@@ -28997,13 +29003,13 @@
         </is>
       </c>
       <c r="M276" s="4" t="n">
-        <v>-14.94</v>
+        <v>-14.89</v>
       </c>
       <c r="N276" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O276" s="4" t="n">
-        <v>-13</v>
+        <v>-12.95</v>
       </c>
       <c r="P276" s="4" t="n">
         <v>-1.22</v>
@@ -29034,10 +29040,10 @@
         <v>0</v>
       </c>
       <c r="AB276" s="4" t="n">
-        <v>43.5</v>
+        <v>43.52</v>
       </c>
       <c r="AC276" s="4" t="n">
-        <v>56.5</v>
+        <v>56.48</v>
       </c>
       <c r="AD276" s="4" t="n">
         <v>0</v>
@@ -29085,13 +29091,13 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>-10.71</v>
+        <v>-10.66</v>
       </c>
       <c r="J277" s="4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K277" s="4" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -29099,13 +29105,13 @@
         </is>
       </c>
       <c r="M277" s="4" t="n">
-        <v>-10.96</v>
+        <v>-10.91</v>
       </c>
       <c r="N277" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O277" s="4" t="n">
-        <v>-11.03</v>
+        <v>-10.98</v>
       </c>
       <c r="P277" s="4" t="n">
         <v>-1.34</v>
@@ -29136,10 +29142,10 @@
         <v>0</v>
       </c>
       <c r="AB277" s="4" t="n">
-        <v>43.92</v>
+        <v>43.95</v>
       </c>
       <c r="AC277" s="4" t="n">
-        <v>54.46</v>
+        <v>54.43</v>
       </c>
       <c r="AD277" s="4" t="n">
         <v>1.62</v>
@@ -29187,7 +29193,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-17.09</v>
+        <v>-17.04</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.4</v>
@@ -29201,13 +29207,13 @@
         </is>
       </c>
       <c r="M278" s="4" t="n">
-        <v>-17</v>
+        <v>-16.94</v>
       </c>
       <c r="N278" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-17.09</v>
+        <v>-17.04</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.86</v>
@@ -29238,10 +29244,10 @@
         <v>0</v>
       </c>
       <c r="AB278" s="4" t="n">
-        <v>41.46</v>
+        <v>41.48</v>
       </c>
       <c r="AC278" s="4" t="n">
-        <v>58.54</v>
+        <v>58.52</v>
       </c>
       <c r="AD278" s="4" t="n">
         <v>0</v>
@@ -29289,7 +29295,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>-11.62</v>
+        <v>-11.57</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>1.2</v>
@@ -29303,13 +29309,13 @@
         </is>
       </c>
       <c r="M279" s="4" t="n">
-        <v>-13.29</v>
+        <v>-13.24</v>
       </c>
       <c r="N279" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O279" s="4" t="n">
-        <v>-11.62</v>
+        <v>-11.57</v>
       </c>
       <c r="P279" s="4" t="n">
         <v>-0.26</v>
@@ -29340,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="AB279" s="4" t="n">
-        <v>44.19</v>
+        <v>44.22</v>
       </c>
       <c r="AC279" s="4" t="n">
-        <v>55.81</v>
+        <v>55.78</v>
       </c>
       <c r="AD279" s="4" t="n">
         <v>0</v>
@@ -29391,7 +29397,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>-15.69</v>
+        <v>-15.65</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>0.6</v>
@@ -29405,13 +29411,13 @@
         </is>
       </c>
       <c r="M280" s="4" t="n">
-        <v>-15.11</v>
+        <v>-15.06</v>
       </c>
       <c r="N280" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O280" s="4" t="n">
-        <v>-16.52</v>
+        <v>-16.47</v>
       </c>
       <c r="P280" s="4" t="n">
         <v>-1.6</v>
@@ -29448,10 +29454,10 @@
         <v>0</v>
       </c>
       <c r="AB280" s="4" t="n">
-        <v>42.15</v>
+        <v>42.18</v>
       </c>
       <c r="AC280" s="4" t="n">
-        <v>57.85</v>
+        <v>57.82</v>
       </c>
       <c r="AD280" s="4" t="n">
         <v>0</v>
@@ -29499,13 +29505,13 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>-4.99</v>
+        <v>-4.95</v>
       </c>
       <c r="J281" s="4" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="K281" s="4" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -29513,13 +29519,13 @@
         </is>
       </c>
       <c r="M281" s="4" t="n">
-        <v>-7.94</v>
+        <v>-7.88</v>
       </c>
       <c r="N281" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O281" s="4" t="n">
-        <v>-5.52</v>
+        <v>-5.47</v>
       </c>
       <c r="P281" s="4" t="n">
         <v>0.88</v>
@@ -29556,10 +29562,10 @@
         <v>0</v>
       </c>
       <c r="AB281" s="4" t="n">
-        <v>47.5</v>
+        <v>47.53</v>
       </c>
       <c r="AC281" s="4" t="n">
-        <v>52.5</v>
+        <v>52.47</v>
       </c>
       <c r="AD281" s="4" t="n">
         <v>0</v>
@@ -29607,7 +29613,7 @@
         </is>
       </c>
       <c r="I282" s="4" t="n">
-        <v>59.68</v>
+        <v>59.73</v>
       </c>
       <c r="J282" s="4" t="n">
         <v>100</v>
@@ -29621,13 +29627,13 @@
         </is>
       </c>
       <c r="M282" s="4" t="n">
-        <v>50.32</v>
+        <v>50.37</v>
       </c>
       <c r="N282" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O282" s="4" t="n">
-        <v>59.68</v>
+        <v>59.73</v>
       </c>
       <c r="P282" s="4" t="n">
         <v>1.26</v>
@@ -29658,10 +29664,10 @@
         <v>0</v>
       </c>
       <c r="AB282" s="4" t="n">
-        <v>79.84</v>
+        <v>79.86</v>
       </c>
       <c r="AC282" s="4" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AD282" s="4" t="n">
         <v>0</v>
@@ -29709,7 +29715,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-13.61</v>
+        <v>-13.56</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>0.9</v>
@@ -29723,13 +29729,13 @@
         </is>
       </c>
       <c r="M283" s="4" t="n">
-        <v>-14.66</v>
+        <v>-14.61</v>
       </c>
       <c r="N283" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O283" s="4" t="n">
-        <v>-13.15</v>
+        <v>-13.09</v>
       </c>
       <c r="P283" s="4" t="n">
         <v>-0.19</v>
@@ -29760,10 +29766,10 @@
         <v>0</v>
       </c>
       <c r="AB283" s="4" t="n">
-        <v>42.4</v>
+        <v>42.42</v>
       </c>
       <c r="AC283" s="4" t="n">
-        <v>55.75</v>
+        <v>55.73</v>
       </c>
       <c r="AD283" s="4" t="n">
         <v>1.85</v>
@@ -29811,13 +29817,13 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>-13.1</v>
+        <v>-13.06</v>
       </c>
       <c r="J284" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K284" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -29825,13 +29831,13 @@
         </is>
       </c>
       <c r="M284" s="4" t="n">
-        <v>-13.46</v>
+        <v>-13.41</v>
       </c>
       <c r="N284" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O284" s="4" t="n">
-        <v>-14.44</v>
+        <v>-14.39</v>
       </c>
       <c r="P284" s="4" t="n">
         <v>-2.3</v>
@@ -29868,10 +29874,10 @@
         <v>0</v>
       </c>
       <c r="AB284" s="4" t="n">
-        <v>43.45</v>
+        <v>43.47</v>
       </c>
       <c r="AC284" s="4" t="n">
-        <v>56.55</v>
+        <v>56.53</v>
       </c>
       <c r="AD284" s="4" t="n">
         <v>0</v>
@@ -30021,27 +30027,27 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.23</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>Safe R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.970000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-10.3</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30078,10 +30084,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.14</v>
+        <v>45.39</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.86</v>
+        <v>54.61</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30125,13 +30131,13 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.45</v>
+        <v>12.95</v>
       </c>
       <c r="J287" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="K287" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -30139,13 +30145,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>8.890000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.12</v>
+        <v>14.71</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30182,10 +30188,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.23</v>
+        <v>56.48</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.77</v>
+        <v>43.52</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30233,7 +30239,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.85</v>
+        <v>-52.26</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30247,13 +30253,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.92</v>
+        <v>-49.33</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.85</v>
+        <v>-52.26</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30284,10 +30290,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.58</v>
+        <v>23.87</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.42</v>
+        <v>76.13</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -37823,13 +37829,13 @@
         </is>
       </c>
       <c r="I362" s="4" t="n">
-        <v>-2.11</v>
+        <v>-1.98</v>
       </c>
       <c r="J362" s="4" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="K362" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -37837,13 +37843,13 @@
         </is>
       </c>
       <c r="M362" s="4" t="n">
-        <v>5.86</v>
+        <v>6.02</v>
       </c>
       <c r="N362" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O362" s="4" t="n">
-        <v>-0.64</v>
+        <v>-0.48</v>
       </c>
       <c r="P362" s="4" t="n">
         <v>-0.89</v>
@@ -37880,10 +37886,10 @@
         <v>0</v>
       </c>
       <c r="AB362" s="4" t="n">
-        <v>48.94</v>
+        <v>49.01</v>
       </c>
       <c r="AC362" s="4" t="n">
-        <v>51.06</v>
+        <v>50.99</v>
       </c>
       <c r="AD362" s="4" t="n">
         <v>0</v>
@@ -37931,7 +37937,7 @@
         </is>
       </c>
       <c r="I363" s="4" t="n">
-        <v>55.62</v>
+        <v>55.79</v>
       </c>
       <c r="J363" s="4" t="n">
         <v>100</v>
@@ -37945,13 +37951,13 @@
         </is>
       </c>
       <c r="M363" s="4" t="n">
-        <v>43.14</v>
+        <v>43.3</v>
       </c>
       <c r="N363" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O363" s="4" t="n">
-        <v>55.62</v>
+        <v>55.79</v>
       </c>
       <c r="P363" s="4" t="n">
         <v>0</v>
@@ -37982,10 +37988,10 @@
         <v>0</v>
       </c>
       <c r="AB363" s="4" t="n">
-        <v>77.81</v>
+        <v>77.89</v>
       </c>
       <c r="AC363" s="4" t="n">
-        <v>22.19</v>
+        <v>22.11</v>
       </c>
       <c r="AD363" s="4" t="n">
         <v>0</v>
@@ -38029,7 +38035,7 @@
         </is>
       </c>
       <c r="I364" s="4" t="n">
-        <v>91.88</v>
+        <v>92.05</v>
       </c>
       <c r="J364" s="4" t="n">
         <v>100</v>
@@ -38043,13 +38049,13 @@
         </is>
       </c>
       <c r="M364" s="4" t="n">
-        <v>83.91</v>
+        <v>84.08</v>
       </c>
       <c r="N364" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O364" s="4" t="n">
-        <v>91.88</v>
+        <v>92.05</v>
       </c>
       <c r="P364" s="4" t="n">
         <v>2.85</v>
@@ -38080,10 +38086,10 @@
         <v>0</v>
       </c>
       <c r="AB364" s="4" t="n">
-        <v>95.94</v>
+        <v>96.02</v>
       </c>
       <c r="AC364" s="4" t="n">
-        <v>4.06</v>
+        <v>3.98</v>
       </c>
       <c r="AD364" s="4" t="n">
         <v>0</v>
@@ -38131,7 +38137,7 @@
         </is>
       </c>
       <c r="I365" s="4" t="n">
-        <v>29.39</v>
+        <v>29.56</v>
       </c>
       <c r="J365" s="4" t="n">
         <v>100</v>
@@ -38145,13 +38151,13 @@
         </is>
       </c>
       <c r="M365" s="4" t="n">
-        <v>21.15</v>
+        <v>21.31</v>
       </c>
       <c r="N365" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O365" s="4" t="n">
-        <v>29.39</v>
+        <v>29.56</v>
       </c>
       <c r="P365" s="4" t="n">
         <v>0</v>
@@ -38182,10 +38188,10 @@
         <v>0</v>
       </c>
       <c r="AB365" s="4" t="n">
-        <v>64.7</v>
+        <v>64.78</v>
       </c>
       <c r="AC365" s="4" t="n">
-        <v>35.3</v>
+        <v>35.22</v>
       </c>
       <c r="AD365" s="4" t="n">
         <v>0</v>
@@ -38233,7 +38239,7 @@
         </is>
       </c>
       <c r="I366" s="4" t="n">
-        <v>42.19</v>
+        <v>42.36</v>
       </c>
       <c r="J366" s="4" t="n">
         <v>100</v>
@@ -38247,13 +38253,13 @@
         </is>
       </c>
       <c r="M366" s="4" t="n">
-        <v>34.38</v>
+        <v>34.54</v>
       </c>
       <c r="N366" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O366" s="4" t="n">
-        <v>42.19</v>
+        <v>42.36</v>
       </c>
       <c r="P366" s="4" t="n">
         <v>0</v>
@@ -38284,10 +38290,10 @@
         <v>0</v>
       </c>
       <c r="AB366" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="AC366" s="4" t="n">
-        <v>28.9</v>
+        <v>28.82</v>
       </c>
       <c r="AD366" s="4" t="n">
         <v>0</v>
@@ -38335,13 +38341,13 @@
         </is>
       </c>
       <c r="I367" s="4" t="n">
-        <v>25.69</v>
+        <v>25.85</v>
       </c>
       <c r="J367" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K367" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -38349,13 +38355,13 @@
         </is>
       </c>
       <c r="M367" s="4" t="n">
-        <v>16.68</v>
+        <v>16.84</v>
       </c>
       <c r="N367" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O367" s="4" t="n">
-        <v>25.69</v>
+        <v>25.85</v>
       </c>
       <c r="P367" s="4" t="n">
         <v>1.03</v>
@@ -38386,10 +38392,10 @@
         <v>0</v>
       </c>
       <c r="AB367" s="4" t="n">
-        <v>62.84</v>
+        <v>62.93</v>
       </c>
       <c r="AC367" s="4" t="n">
-        <v>37.16</v>
+        <v>37.07</v>
       </c>
       <c r="AD367" s="4" t="n">
         <v>0</v>
@@ -38437,13 +38443,13 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="J368" s="4" t="n">
-        <v>71</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K368" s="4" t="n">
-        <v>29</v>
+        <v>28.6</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -38451,13 +38457,13 @@
         </is>
       </c>
       <c r="M368" s="4" t="n">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="N368" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O368" s="4" t="n">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="P368" s="4" t="n">
         <v>-0.22</v>
@@ -38494,10 +38500,10 @@
         <v>0</v>
       </c>
       <c r="AB368" s="4" t="n">
-        <v>51.18</v>
+        <v>51.23</v>
       </c>
       <c r="AC368" s="4" t="n">
-        <v>48.82</v>
+        <v>48.77</v>
       </c>
       <c r="AD368" s="4" t="n">
         <v>0</v>
@@ -38545,13 +38551,13 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.86</v>
+        <v>0.18</v>
       </c>
       <c r="J369" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="K369" s="4" t="n">
-        <v>34.9</v>
+        <v>37.6</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -38559,13 +38565,13 @@
         </is>
       </c>
       <c r="M369" s="4" t="n">
-        <v>-2.84</v>
+        <v>-2.67</v>
       </c>
       <c r="N369" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O369" s="4" t="n">
-        <v>0.86</v>
+        <v>1.03</v>
       </c>
       <c r="P369" s="4" t="n">
         <v>-0.09</v>
@@ -38576,12 +38582,18 @@
       <c r="R369" s="4" t="n">
         <v>-8.58</v>
       </c>
-      <c r="S369" s="4" t="n"/>
-      <c r="T369" s="4" t="n"/>
+      <c r="S369" s="4" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="T369" s="4" t="n">
+        <v>45</v>
+      </c>
       <c r="U369" t="n">
-        <v>0</v>
-      </c>
-      <c r="V369" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="V369" s="4" t="n">
+        <v>-1.49</v>
+      </c>
       <c r="W369" s="5" t="n">
         <v>4609589</v>
       </c>
@@ -38596,10 +38608,10 @@
         <v>0</v>
       </c>
       <c r="AB369" s="4" t="n">
-        <v>50.43</v>
+        <v>50.09</v>
       </c>
       <c r="AC369" s="4" t="n">
-        <v>49.57</v>
+        <v>49.91</v>
       </c>
       <c r="AD369" s="4" t="n">
         <v>0</v>
@@ -38647,7 +38659,7 @@
         </is>
       </c>
       <c r="I370" s="4" t="n">
-        <v>-32.74</v>
+        <v>-32.57</v>
       </c>
       <c r="J370" s="4" t="n">
         <v>0</v>
@@ -38661,13 +38673,13 @@
         </is>
       </c>
       <c r="M370" s="4" t="n">
-        <v>-33.54</v>
+        <v>-33.38</v>
       </c>
       <c r="N370" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O370" s="4" t="n">
-        <v>-32.74</v>
+        <v>-32.57</v>
       </c>
       <c r="P370" s="4" t="n">
         <v>-0.72</v>
@@ -38698,10 +38710,10 @@
         <v>0</v>
       </c>
       <c r="AB370" s="4" t="n">
-        <v>33.63</v>
+        <v>33.71</v>
       </c>
       <c r="AC370" s="4" t="n">
-        <v>66.37</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="AD370" s="4" t="n">
         <v>0</v>
@@ -38749,13 +38761,13 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="J371" s="4" t="n">
-        <v>92.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K371" s="4" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -38763,13 +38775,13 @@
         </is>
       </c>
       <c r="M371" s="4" t="n">
-        <v>-0.74</v>
+        <v>-0.58</v>
       </c>
       <c r="N371" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O371" s="4" t="n">
-        <v>10.49</v>
+        <v>10.65</v>
       </c>
       <c r="P371" s="4" t="n">
         <v>0.15</v>
@@ -38806,10 +38818,10 @@
         <v>0</v>
       </c>
       <c r="AB371" s="4" t="n">
-        <v>54.36</v>
+        <v>54.42</v>
       </c>
       <c r="AC371" s="4" t="n">
-        <v>45.64</v>
+        <v>45.58</v>
       </c>
       <c r="AD371" s="4" t="n">
         <v>0</v>
@@ -38857,13 +38869,13 @@
         </is>
       </c>
       <c r="I372" s="4" t="n">
-        <v>-16.97</v>
+        <v>-16.81</v>
       </c>
       <c r="J372" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K372" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -38871,13 +38883,13 @@
         </is>
       </c>
       <c r="M372" s="4" t="n">
-        <v>-17.23</v>
+        <v>-17.06</v>
       </c>
       <c r="N372" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O372" s="4" t="n">
-        <v>-16.97</v>
+        <v>-16.81</v>
       </c>
       <c r="P372" s="4" t="n">
         <v>-1.34</v>
@@ -38908,10 +38920,10 @@
         <v>0</v>
       </c>
       <c r="AB372" s="4" t="n">
-        <v>41.51</v>
+        <v>41.6</v>
       </c>
       <c r="AC372" s="4" t="n">
-        <v>58.49</v>
+        <v>58.4</v>
       </c>
       <c r="AD372" s="4" t="n">
         <v>0</v>
@@ -38959,7 +38971,7 @@
         </is>
       </c>
       <c r="I373" s="4" t="n">
-        <v>29.65</v>
+        <v>29.81</v>
       </c>
       <c r="J373" s="4" t="n">
         <v>100</v>
@@ -38973,13 +38985,13 @@
         </is>
       </c>
       <c r="M373" s="4" t="n">
-        <v>24.14</v>
+        <v>24.31</v>
       </c>
       <c r="N373" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O373" s="4" t="n">
-        <v>29.65</v>
+        <v>29.81</v>
       </c>
       <c r="P373" s="4" t="n">
         <v>2.34</v>
@@ -39010,10 +39022,10 @@
         <v>0</v>
       </c>
       <c r="AB373" s="4" t="n">
-        <v>64.81999999999999</v>
+        <v>64.91</v>
       </c>
       <c r="AC373" s="4" t="n">
-        <v>35.18</v>
+        <v>35.09</v>
       </c>
       <c r="AD373" s="4" t="n">
         <v>0</v>
@@ -39061,7 +39073,7 @@
         </is>
       </c>
       <c r="I374" s="4" t="n">
-        <v>-40.95</v>
+        <v>-40.79</v>
       </c>
       <c r="J374" s="4" t="n">
         <v>0</v>
@@ -39075,13 +39087,13 @@
         </is>
       </c>
       <c r="M374" s="4" t="n">
-        <v>-41.31</v>
+        <v>-41.14</v>
       </c>
       <c r="N374" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O374" s="4" t="n">
-        <v>-40.95</v>
+        <v>-40.79</v>
       </c>
       <c r="P374" s="4" t="n">
         <v>-2.37</v>
@@ -39112,10 +39124,10 @@
         <v>0</v>
       </c>
       <c r="AB374" s="4" t="n">
-        <v>29.52</v>
+        <v>29.61</v>
       </c>
       <c r="AC374" s="4" t="n">
-        <v>70.48</v>
+        <v>70.39</v>
       </c>
       <c r="AD374" s="4" t="n">
         <v>0</v>
@@ -39163,7 +39175,7 @@
         </is>
       </c>
       <c r="I375" s="4" t="n">
-        <v>-27.44</v>
+        <v>-27.27</v>
       </c>
       <c r="J375" s="4" t="n">
         <v>0</v>
@@ -39177,13 +39189,13 @@
         </is>
       </c>
       <c r="M375" s="4" t="n">
-        <v>-28.52</v>
+        <v>-28.36</v>
       </c>
       <c r="N375" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O375" s="4" t="n">
-        <v>-27.44</v>
+        <v>-27.27</v>
       </c>
       <c r="P375" s="4" t="n">
         <v>-2.12</v>
@@ -39214,10 +39226,10 @@
         <v>0</v>
       </c>
       <c r="AB375" s="4" t="n">
-        <v>36.28</v>
+        <v>36.36</v>
       </c>
       <c r="AC375" s="4" t="n">
-        <v>63.72</v>
+        <v>63.64</v>
       </c>
       <c r="AD375" s="4" t="n">
         <v>0</v>
@@ -39265,7 +39277,7 @@
         </is>
       </c>
       <c r="I376" s="4" t="n">
-        <v>-34.96</v>
+        <v>-34.79</v>
       </c>
       <c r="J376" s="4" t="n">
         <v>0</v>
@@ -39279,13 +39291,13 @@
         </is>
       </c>
       <c r="M376" s="4" t="n">
-        <v>-33.4</v>
+        <v>-33.24</v>
       </c>
       <c r="N376" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O376" s="4" t="n">
-        <v>-34.96</v>
+        <v>-34.79</v>
       </c>
       <c r="P376" s="4" t="n">
         <v>-1.73</v>
@@ -39316,10 +39328,10 @@
         <v>0</v>
       </c>
       <c r="AB376" s="4" t="n">
-        <v>32.52</v>
+        <v>32.6</v>
       </c>
       <c r="AC376" s="4" t="n">
-        <v>67.48</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AD376" s="4" t="n">
         <v>0</v>
@@ -39367,13 +39379,13 @@
         </is>
       </c>
       <c r="I377" s="4" t="n">
-        <v>-18.11</v>
+        <v>-17.95</v>
       </c>
       <c r="J377" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K377" s="4" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
@@ -39381,13 +39393,13 @@
         </is>
       </c>
       <c r="M377" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.72</v>
       </c>
       <c r="N377" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O377" s="4" t="n">
-        <v>-18.11</v>
+        <v>-17.95</v>
       </c>
       <c r="P377" s="4" t="n">
         <v>-1.76</v>
@@ -39418,10 +39430,10 @@
         <v>0</v>
       </c>
       <c r="AB377" s="4" t="n">
-        <v>40.94</v>
+        <v>41.03</v>
       </c>
       <c r="AC377" s="4" t="n">
-        <v>59.06</v>
+        <v>58.97</v>
       </c>
       <c r="AD377" s="4" t="n">
         <v>0</v>
@@ -39469,13 +39481,13 @@
         </is>
       </c>
       <c r="I378" s="4" t="n">
-        <v>21.68</v>
+        <v>21.84</v>
       </c>
       <c r="J378" s="4" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K378" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -39483,13 +39495,13 @@
         </is>
       </c>
       <c r="M378" s="4" t="n">
-        <v>10.02</v>
+        <v>10.18</v>
       </c>
       <c r="N378" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O378" s="4" t="n">
-        <v>21.68</v>
+        <v>21.84</v>
       </c>
       <c r="P378" s="4" t="n">
         <v>2.76</v>
@@ -39520,10 +39532,10 @@
         <v>0</v>
       </c>
       <c r="AB378" s="4" t="n">
-        <v>60.84</v>
+        <v>60.92</v>
       </c>
       <c r="AC378" s="4" t="n">
-        <v>39.16</v>
+        <v>39.08</v>
       </c>
       <c r="AD378" s="4" t="n">
         <v>0</v>
@@ -40477,7 +40489,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-25.31</v>
+        <v>-25.65</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40491,13 +40503,13 @@
         </is>
       </c>
       <c r="M388" s="4" t="n">
-        <v>-28.25</v>
+        <v>-28.59</v>
       </c>
       <c r="N388" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-25.31</v>
+        <v>-25.65</v>
       </c>
       <c r="P388" s="4" t="n">
         <v>-1.2</v>
@@ -40528,10 +40540,10 @@
         <v>0</v>
       </c>
       <c r="AB388" s="4" t="n">
-        <v>37.35</v>
+        <v>37.18</v>
       </c>
       <c r="AC388" s="4" t="n">
-        <v>62.65</v>
+        <v>62.82</v>
       </c>
       <c r="AD388" s="4" t="n">
         <v>0</v>
@@ -49149,13 +49161,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-1.04</v>
+        <v>-0.55</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>45.8</v>
+        <v>47.5</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>54.2</v>
+        <v>52.5</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49163,13 +49175,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.58</v>
+        <v>-10.71</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2</v>
+        <v>-2.13</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -49206,10 +49218,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.41</v>
+        <v>45.37</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.59</v>
+        <v>46.63</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49775,7 +49787,7 @@
         </is>
       </c>
       <c r="I479" s="4" t="n">
-        <v>12.12</v>
+        <v>12.13</v>
       </c>
       <c r="J479" s="4" t="n">
         <v>98.90000000000001</v>
@@ -49813,7 +49825,7 @@
         <v>43.02</v>
       </c>
       <c r="U479" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V479" s="4" t="n">
         <v>11.17</v>
@@ -49987,13 +49999,13 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-31.2</v>
+        <v>-25.73</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K481" s="4" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
@@ -50018,12 +50030,18 @@
       <c r="R481" s="4" t="n">
         <v>-37.52</v>
       </c>
-      <c r="S481" s="4" t="n"/>
-      <c r="T481" s="4" t="n"/>
+      <c r="S481" s="4" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="T481" s="4" t="n">
+        <v>41.47</v>
+      </c>
       <c r="U481" t="n">
-        <v>0</v>
-      </c>
-      <c r="V481" s="4" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="V481" s="4" t="n">
+        <v>-8.84</v>
+      </c>
       <c r="W481" s="5" t="n">
         <v>8642</v>
       </c>
@@ -50036,16 +50054,16 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>34.4</v>
+        <v>37.13</v>
       </c>
       <c r="AA481" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB481" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>62.87</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -50609,13 +50627,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50623,13 +50641,13 @@
         </is>
       </c>
       <c r="M487" s="4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="N487" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O487" s="4" t="n">
-        <v>-0.64</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P487" s="4" t="n">
         <v>0</v>
@@ -50666,10 +50684,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>50.99</v>
+        <v>50.98</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>49.01</v>
+        <v>49.02</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -50713,7 +50731,7 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="J488" s="4" t="n">
         <v>73.7</v>
@@ -51033,13 +51051,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-22.65</v>
+        <v>-26.07</v>
       </c>
       <c r="J491" s="4" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>96.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51065,16 +51083,16 @@
         <v>-20.58</v>
       </c>
       <c r="S491" s="4" t="n">
-        <v>32.17</v>
+        <v>31.11</v>
       </c>
       <c r="T491" s="4" t="n">
-        <v>44.17</v>
+        <v>43.81</v>
       </c>
       <c r="U491" t="n">
         <v>6</v>
       </c>
       <c r="V491" s="4" t="n">
-        <v>-12.11</v>
+        <v>-12.97</v>
       </c>
       <c r="W491" s="5" t="n">
         <v>58829</v>
@@ -51088,16 +51106,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>11.37</v>
+        <v>13.89</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>31.16</v>
+        <v>28.19</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.81</v>
+        <v>54.26</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51141,13 +51159,13 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>5.96</v>
+        <v>6.17</v>
       </c>
       <c r="J492" s="4" t="n">
-        <v>84.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K492" s="4" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -51173,16 +51191,16 @@
         <v>-3.27</v>
       </c>
       <c r="S492" s="4" t="n">
-        <v>49.17</v>
+        <v>50.89</v>
       </c>
       <c r="T492" s="4" t="n">
-        <v>40.43</v>
+        <v>42.03</v>
       </c>
       <c r="U492" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V492" s="4" t="n">
-        <v>8.4</v>
+        <v>8.67</v>
       </c>
       <c r="W492" s="5" t="n">
         <v>34975789</v>
@@ -51198,10 +51216,10 @@
         <v>0</v>
       </c>
       <c r="AB492" s="4" t="n">
-        <v>51.99</v>
+        <v>52.09</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>46.14</v>
+        <v>46.04</v>
       </c>
       <c r="AD492" s="4" t="n">
         <v>1.87</v>
@@ -51249,13 +51267,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-6.66</v>
+        <v>-3.73</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>29.9</v>
+        <v>38.5</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51281,16 +51299,16 @@
         <v>-20.84</v>
       </c>
       <c r="S493" s="4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T493" s="4" t="n">
-        <v>49</v>
+        <v>42.31</v>
       </c>
       <c r="U493" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V493" s="4" t="n">
-        <v>-7</v>
+        <v>4.54</v>
       </c>
       <c r="W493" s="5" t="n">
         <v>0</v>
@@ -51304,16 +51322,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>46.67</v>
+        <v>48.14</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>29.9</v>
+        <v>38.5</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>53.33</v>
+        <v>51.86</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -52183,7 +52201,7 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-28.91</v>
+        <v>-30.61</v>
       </c>
       <c r="J502" s="4" t="n">
         <v>0</v>
@@ -52215,16 +52233,16 @@
         <v>-29.98</v>
       </c>
       <c r="S502" s="4" t="n">
-        <v>31.79</v>
+        <v>19.31</v>
       </c>
       <c r="T502" s="4" t="n">
-        <v>49.32</v>
+        <v>43.6</v>
       </c>
       <c r="U502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V502" s="4" t="n">
-        <v>-20.53</v>
+        <v>-27.29</v>
       </c>
       <c r="W502" s="5" t="n">
         <v>228295</v>
@@ -52238,16 +52256,16 @@
         </is>
       </c>
       <c r="Z502" s="4" t="n">
-        <v>5.06</v>
+        <v>20.81</v>
       </c>
       <c r="AA502" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB502" s="4" t="n">
-        <v>33.74</v>
+        <v>27.48</v>
       </c>
       <c r="AC502" s="4" t="n">
-        <v>61.2</v>
+        <v>51.71</v>
       </c>
       <c r="AD502" s="4" t="n">
         <v>0</v>
@@ -54319,19 +54337,19 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="K26" t="n">
         <v>11</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M26" t="n">
         <v>19</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -54377,7 +54395,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="K27" t="n">
         <v>7</v>
@@ -55085,7 +55103,7 @@
         <v>112</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -55537,10 +55555,10 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="K47" t="n">
         <v>41</v>
-      </c>
-      <c r="K47" t="n">
-        <v>42</v>
       </c>
       <c r="L47" t="n">
         <v>27</v>
@@ -55549,7 +55567,7 @@
         <v>53</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -55595,7 +55613,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="K48" t="n">
         <v>19</v>
@@ -55607,7 +55625,7 @@
         <v>23</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -55665,7 +55683,7 @@
         <v>78</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -55723,7 +55741,7 @@
         <v>31</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -56987,7 +57005,7 @@
         </is>
       </c>
       <c r="J72" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="K72" t="n">
         <v>7</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generic ballot D+5.2 · House popular vote D+7.3</t>
+          <t>Generic ballot D+5.2 · House popular vote D+7.4</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>52.6</v>
+        <v>52.9</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.2</v>
+        <v>232</v>
       </c>
       <c r="C9" t="n">
-        <v>202.8</v>
+        <v>203</v>
       </c>
       <c r="D9" t="n">
         <v>229</v>
       </c>
       <c r="E9" t="n">
-        <v>81.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>41.6</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.33</v>
+        <v>-3.56</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40.8</v>
+        <v>38</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>59.2</v>
+        <v>62</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>27.1</v>
+        <v>27.27</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1357,10 +1357,10 @@
         <v>5.24</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>29.46</v>
+        <v>29.74</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1</v>
+        <v>0.19</v>
       </c>
       <c r="Q6" s="4" t="n">
         <v>0</v>
@@ -1381,10 +1381,10 @@
         <v>23.57</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>11283904</v>
+        <v>22373949</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>12875324</v>
+        <v>17445485</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" s="4" t="n">
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>63.55</v>
+        <v>63.64</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>36.45</v>
+        <v>36.36</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.75</v>
+        <v>5.28</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>16.6</v>
+        <v>18.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         <v>5.24</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>6.11</v>
+        <v>5.32</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.86</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" s="4" t="n">
         <v>10.86</v>
@@ -2011,10 +2011,10 @@
         <v>5.22</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>9572747</v>
+        <v>19860206</v>
       </c>
       <c r="X12" s="5" t="n">
-        <v>163603</v>
+        <v>1218702</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" s="4" t="n">
@@ -2024,10 +2024,10 @@
         <v>0</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>52.87</v>
+        <v>52.64</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>47.13</v>
+        <v>47.36</v>
       </c>
       <c r="AD12" s="4" t="n">
         <v>0</v>
@@ -3451,13 +3451,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3471,10 +3471,10 @@
         <v>5.24</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-6.49</v>
+        <v>-6.31</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.66</v>
+        <v>-0.48</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>0</v>
@@ -3495,10 +3495,10 @@
         <v>0.48</v>
       </c>
       <c r="W26" s="5" t="n">
-        <v>10552470</v>
+        <v>15928993</v>
       </c>
       <c r="X26" s="5" t="n">
-        <v>25555956</v>
+        <v>30306297</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" s="4" t="n">
@@ -3508,10 +3508,10 @@
         <v>0</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>48.3</v>
+        <v>48.35</v>
       </c>
       <c r="AC26" s="4" t="n">
-        <v>51.7</v>
+        <v>51.65</v>
       </c>
       <c r="AD26" s="4" t="n">
         <v>0</v>
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.57</v>
+        <v>-2.28</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>57.2</v>
+        <v>56.8</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.61</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.04</v>
+        <v>-1.2</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.1</v>
@@ -4756,16 +4756,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.71</v>
+        <v>48.86</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.29</v>
+        <v>51.14</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-27.13</v>
+        <v>-27.1</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
@@ -4829,10 +4829,10 @@
         <v>5.24</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-27.13</v>
+        <v>-27.1</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>-1.77</v>
+        <v>-1.74</v>
       </c>
       <c r="Q39" s="4" t="n">
         <v>0</v>
@@ -4847,10 +4847,10 @@
       </c>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="5" t="n">
-        <v>55423</v>
+        <v>85968</v>
       </c>
       <c r="X39" s="5" t="n">
-        <v>1065922</v>
+        <v>1162583</v>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" s="4" t="n">
@@ -4860,10 +4860,10 @@
         <v>0</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>36.44</v>
+        <v>36.45</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>63.56</v>
+        <v>63.55</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>0</v>
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>-1.97</v>
+        <v>-2.06</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>30.5</v>
+        <v>30.1</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>69.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -4931,10 +4931,10 @@
         <v>5.24</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-1.12</v>
+        <v>-1.25</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.44</v>
       </c>
       <c r="Q40" s="4" t="n">
         <v>2.48</v>
@@ -4955,10 +4955,10 @@
         <v>-4</v>
       </c>
       <c r="W40" s="5" t="n">
-        <v>1295921</v>
+        <v>1355789</v>
       </c>
       <c r="X40" s="5" t="n">
-        <v>1300076</v>
+        <v>1318574</v>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" s="4" t="n">
@@ -4968,10 +4968,10 @@
         <v>0</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>49.02</v>
+        <v>48.97</v>
       </c>
       <c r="AC40" s="4" t="n">
-        <v>50.98</v>
+        <v>51.03</v>
       </c>
       <c r="AD40" s="4" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-28.25</v>
+        <v>-28.28</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>5.24</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-28.25</v>
+        <v>-28.28</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>-2.11</v>
+        <v>-2.14</v>
       </c>
       <c r="Q44" s="4" t="n">
         <v>-0.72</v>
@@ -5366,7 +5366,7 @@
         <v>15899</v>
       </c>
       <c r="X44" s="5" t="n">
-        <v>1011566</v>
+        <v>1053566</v>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" s="4" t="n">
@@ -5376,10 +5376,10 @@
         <v>0</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>35.87</v>
+        <v>35.86</v>
       </c>
       <c r="AC44" s="4" t="n">
-        <v>64.13</v>
+        <v>64.14</v>
       </c>
       <c r="AD44" s="4" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="V45" s="4" t="n"/>
       <c r="W45" s="5" t="n">
-        <v>1933864</v>
+        <v>1961991</v>
       </c>
       <c r="X45" s="5" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>-43.82</v>
+        <v>-43.83</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>0</v>
@@ -5549,7 +5549,7 @@
         <v>5.24</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>-43.82</v>
+        <v>-43.83</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>-1.62</v>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-13.28</v>
+        <v>-13.29</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>5.24</v>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>-26.68</v>
+        <v>-26.69</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>0</v>
@@ -5747,13 +5747,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>-23.47</v>
+        <v>-23.48</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-26.68</v>
+        <v>-26.69</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>-1.82</v>
@@ -5980,7 +5980,7 @@
         <v>1830193</v>
       </c>
       <c r="X50" s="5" t="n">
-        <v>2525520</v>
+        <v>2528497</v>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" s="4" t="n">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>37</v>
@@ -6061,10 +6061,10 @@
         <v>5.24</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>-0.7</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Q51" s="4" t="n">
         <v>7.81</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19.43</v>
+        <v>19.47</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>99.7</v>
@@ -6879,13 +6879,13 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>15.53</v>
+        <v>15.57</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>19.43</v>
+        <v>19.47</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0.21</v>
@@ -6916,10 +6916,10 @@
         <v>0</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>59.71</v>
+        <v>59.73</v>
       </c>
       <c r="AC59" s="4" t="n">
-        <v>40.29</v>
+        <v>40.27</v>
       </c>
       <c r="AD59" s="4" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>33.5</v>
+        <v>33.54</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>100</v>
@@ -6981,13 +6981,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.91</v>
+        <v>27.95</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33.5</v>
+        <v>33.54</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>66.75</v>
+        <v>66.77</v>
       </c>
       <c r="AC60" s="4" t="n">
-        <v>33.25</v>
+        <v>33.23</v>
       </c>
       <c r="AD60" s="4" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>21.31</v>
+        <v>21.35</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>99.8</v>
@@ -7083,13 +7083,13 @@
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>12.89</v>
+        <v>12.94</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>21.31</v>
+        <v>21.35</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>1.08</v>
@@ -7120,10 +7120,10 @@
         <v>0</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>60.66</v>
+        <v>60.68</v>
       </c>
       <c r="AC61" s="4" t="n">
-        <v>39.34</v>
+        <v>39.32</v>
       </c>
       <c r="AD61" s="4" t="n">
         <v>0</v>
@@ -7185,13 +7185,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>18.36</v>
+        <v>18.4</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>26.73</v>
+        <v>26.77</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>-18.05</v>
+        <v>-18.01</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0.4</v>
@@ -7287,13 +7287,13 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-18.15</v>
+        <v>-18.11</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>-18.05</v>
+        <v>-18.01</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>-0.65</v>
@@ -7324,10 +7324,10 @@
         <v>0</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>40.98</v>
+        <v>41</v>
       </c>
       <c r="AC63" s="4" t="n">
-        <v>59.02</v>
+        <v>59</v>
       </c>
       <c r="AD63" s="4" t="n">
         <v>0</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12.58</v>
+        <v>12.62</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>99</v>
@@ -7389,13 +7389,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>11.33</v>
+        <v>11.37</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12.58</v>
+        <v>12.62</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>-0.35</v>
@@ -7426,10 +7426,10 @@
         <v>0</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>56.29</v>
+        <v>56.31</v>
       </c>
       <c r="AC64" s="4" t="n">
-        <v>43.71</v>
+        <v>43.69</v>
       </c>
       <c r="AD64" s="4" t="n">
         <v>0</v>
@@ -7491,13 +7491,13 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>16.72</v>
+        <v>16.76</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>25.6</v>
+        <v>25.64</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>49.16</v>
+        <v>49.2</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>100</v>
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>39.26</v>
+        <v>39.3</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>49.16</v>
+        <v>49.2</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>1.66</v>
@@ -7630,10 +7630,10 @@
         <v>0</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>74.58</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AC66" s="4" t="n">
-        <v>25.42</v>
+        <v>25.4</v>
       </c>
       <c r="AD66" s="4" t="n">
         <v>0</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>30.89</v>
+        <v>30.93</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>100</v>
@@ -7695,13 +7695,13 @@
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>17.39</v>
+        <v>17.44</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>30.89</v>
+        <v>30.93</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>2.78</v>
@@ -7732,10 +7732,10 @@
         <v>0</v>
       </c>
       <c r="AB67" s="4" t="n">
-        <v>65.45</v>
+        <v>65.47</v>
       </c>
       <c r="AC67" s="4" t="n">
-        <v>34.55</v>
+        <v>34.53</v>
       </c>
       <c r="AD67" s="4" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>43.06</v>
+        <v>43.1</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>100</v>
@@ -7797,13 +7797,13 @@
         </is>
       </c>
       <c r="M68" s="4" t="n">
-        <v>37.56</v>
+        <v>37.61</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>43.06</v>
+        <v>43.1</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
@@ -7834,10 +7834,10 @@
         <v>0</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>71.53</v>
+        <v>71.55</v>
       </c>
       <c r="AC68" s="4" t="n">
-        <v>28.47</v>
+        <v>28.45</v>
       </c>
       <c r="AD68" s="4" t="n">
         <v>0</v>
@@ -7895,13 +7895,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>74.12</v>
+        <v>74.16</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>79.05</v>
+        <v>79.09</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -7997,13 +7997,13 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>80.87</v>
+        <v>80.91</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>88.03</v>
+        <v>88.08</v>
       </c>
       <c r="P70" s="4" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>99.90000000000001</v>
@@ -8099,13 +8099,13 @@
         </is>
       </c>
       <c r="M71" s="4" t="n">
-        <v>6.96</v>
+        <v>7.01</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0.46</v>
@@ -8136,10 +8136,10 @@
         <v>0</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>60.89</v>
+        <v>60.91</v>
       </c>
       <c r="AC71" s="4" t="n">
-        <v>39.11</v>
+        <v>39.09</v>
       </c>
       <c r="AD71" s="4" t="n">
         <v>0</v>
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>40.79</v>
+        <v>40.83</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>46.15</v>
+        <v>46.19</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>58.39</v>
+        <v>58.44</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>100</v>
@@ -8299,13 +8299,13 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>53.89</v>
+        <v>53.93</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>58.39</v>
+        <v>58.44</v>
       </c>
       <c r="P73" s="4" t="n">
         <v>0</v>
@@ -8336,10 +8336,10 @@
         <v>0</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>79.2</v>
+        <v>79.22</v>
       </c>
       <c r="AC73" s="4" t="n">
-        <v>20.8</v>
+        <v>20.78</v>
       </c>
       <c r="AD73" s="4" t="n">
         <v>0</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>59.81</v>
+        <v>59.85</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>100</v>
@@ -8401,13 +8401,13 @@
         </is>
       </c>
       <c r="M74" s="4" t="n">
-        <v>53</v>
+        <v>53.04</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>59.81</v>
+        <v>59.85</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="V74" s="4" t="n"/>
       <c r="W74" s="5" t="n">
-        <v>3489798</v>
+        <v>3489298</v>
       </c>
       <c r="X74" s="5" t="n">
         <v>0</v>
@@ -8438,10 +8438,10 @@
         <v>0</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="AC74" s="4" t="n">
-        <v>20.1</v>
+        <v>20.08</v>
       </c>
       <c r="AD74" s="4" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>49.16</v>
+        <v>49.2</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>100</v>
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>45.24</v>
+        <v>45.28</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>49.16</v>
+        <v>49.2</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>3.69</v>
@@ -8540,10 +8540,10 @@
         <v>0</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>74.58</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AC75" s="4" t="n">
-        <v>25.42</v>
+        <v>25.4</v>
       </c>
       <c r="AD75" s="4" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>44.1</v>
+        <v>44.14</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>100</v>
@@ -8605,13 +8605,13 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>35.17</v>
+        <v>35.21</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>44.1</v>
+        <v>44.14</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>2.1</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>72.05</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="AC76" s="4" t="n">
-        <v>27.95</v>
+        <v>27.93</v>
       </c>
       <c r="AD76" s="4" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>49.46</v>
+        <v>49.5</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>100</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.73</v>
+        <v>38.77</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>50.37</v>
+        <v>50.41</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>2.46</v>
@@ -8744,10 +8744,10 @@
         <v>0</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>71.98999999999999</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="AC77" s="4" t="n">
-        <v>24.35</v>
+        <v>24.33</v>
       </c>
       <c r="AD77" s="4" t="n">
         <v>3.66</v>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-28.44</v>
+        <v>-28.4</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -8809,13 +8809,13 @@
         </is>
       </c>
       <c r="M78" s="4" t="n">
-        <v>-30.24</v>
+        <v>-30.2</v>
       </c>
       <c r="N78" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-28.44</v>
+        <v>-28.4</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.51</v>
@@ -8846,10 +8846,10 @@
         <v>0</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>35.78</v>
+        <v>35.8</v>
       </c>
       <c r="AC78" s="4" t="n">
-        <v>64.22</v>
+        <v>64.2</v>
       </c>
       <c r="AD78" s="4" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>21.06</v>
+        <v>21.11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>99.8</v>
@@ -8911,13 +8911,13 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.87</v>
+        <v>11.91</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>21.06</v>
+        <v>21.11</v>
       </c>
       <c r="P79" s="4" t="n">
         <v>0.95</v>
@@ -8948,10 +8948,10 @@
         <v>0</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>60.53</v>
+        <v>60.55</v>
       </c>
       <c r="AC79" s="4" t="n">
-        <v>39.47</v>
+        <v>39.45</v>
       </c>
       <c r="AD79" s="4" t="n">
         <v>0</v>
@@ -8999,13 +8999,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -9013,13 +9013,13 @@
         </is>
       </c>
       <c r="M80" s="4" t="n">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>7.34</v>
+        <v>7.39</v>
       </c>
       <c r="P80" s="4" t="n">
         <v>-0.32</v>
@@ -9056,10 +9056,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>52.86</v>
+        <v>52.88</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47.14</v>
+        <v>47.12</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>-16.22</v>
+        <v>-16.17</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>0.5</v>
@@ -9121,13 +9121,13 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-16.65</v>
+        <v>-16.61</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>-16.22</v>
+        <v>-16.17</v>
       </c>
       <c r="P81" s="4" t="n">
         <v>-1.89</v>
@@ -9158,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>41.89</v>
+        <v>41.91</v>
       </c>
       <c r="AC81" s="4" t="n">
-        <v>58.11</v>
+        <v>58.09</v>
       </c>
       <c r="AD81" s="4" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>36.81</v>
+        <v>36.86</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>100</v>
@@ -9223,13 +9223,13 @@
         </is>
       </c>
       <c r="M82" s="4" t="n">
-        <v>28.28</v>
+        <v>28.32</v>
       </c>
       <c r="N82" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>36.81</v>
+        <v>36.86</v>
       </c>
       <c r="P82" s="4" t="n">
         <v>1.43</v>
@@ -9260,10 +9260,10 @@
         <v>0</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>68.41</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="AC82" s="4" t="n">
-        <v>31.59</v>
+        <v>31.57</v>
       </c>
       <c r="AD82" s="4" t="n">
         <v>0</v>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>19.91</v>
+        <v>19.96</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>99.8</v>
@@ -9325,13 +9325,13 @@
         </is>
       </c>
       <c r="M83" s="4" t="n">
-        <v>10.5</v>
+        <v>10.55</v>
       </c>
       <c r="N83" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>19.91</v>
+        <v>19.96</v>
       </c>
       <c r="P83" s="4" t="n">
         <v>0.58</v>
@@ -9362,10 +9362,10 @@
         <v>0</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>59.96</v>
+        <v>59.98</v>
       </c>
       <c r="AC83" s="4" t="n">
-        <v>40.04</v>
+        <v>40.02</v>
       </c>
       <c r="AD83" s="4" t="n">
         <v>0</v>
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25.98</v>
+        <v>26.02</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>100</v>
@@ -9423,13 +9423,13 @@
         </is>
       </c>
       <c r="M84" s="4" t="n">
-        <v>19.15</v>
+        <v>19.2</v>
       </c>
       <c r="N84" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>25.98</v>
+        <v>26.02</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.63</v>
@@ -9460,10 +9460,10 @@
         <v>0</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>62.99</v>
+        <v>63.01</v>
       </c>
       <c r="AC84" s="4" t="n">
-        <v>37.01</v>
+        <v>36.99</v>
       </c>
       <c r="AD84" s="4" t="n">
         <v>0</v>
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>26.99</v>
+        <v>27.03</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>100</v>
@@ -9525,13 +9525,13 @@
         </is>
       </c>
       <c r="M85" s="4" t="n">
-        <v>14.28</v>
+        <v>14.33</v>
       </c>
       <c r="N85" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>26.99</v>
+        <v>27.03</v>
       </c>
       <c r="P85" s="4" t="n">
         <v>1.74</v>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>63.49</v>
+        <v>63.51</v>
       </c>
       <c r="AC85" s="4" t="n">
-        <v>36.51</v>
+        <v>36.49</v>
       </c>
       <c r="AD85" s="4" t="n">
         <v>0</v>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>39.94</v>
+        <v>39.98</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9627,13 +9627,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.87</v>
+        <v>29.91</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>39.94</v>
+        <v>39.98</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.23</v>
@@ -9664,10 +9664,10 @@
         <v>0</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>69.97</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="AC86" s="4" t="n">
-        <v>30.03</v>
+        <v>30.01</v>
       </c>
       <c r="AD86" s="4" t="n">
         <v>0</v>
@@ -9729,13 +9729,13 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.43</v>
+        <v>41.47</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>53.51</v>
+        <v>53.55</v>
       </c>
       <c r="P87" s="4" t="n">
         <v>0</v>
@@ -9817,7 +9817,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>51.84</v>
+        <v>51.88</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>100</v>
@@ -9831,13 +9831,13 @@
         </is>
       </c>
       <c r="M88" s="4" t="n">
-        <v>44.88</v>
+        <v>44.92</v>
       </c>
       <c r="N88" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>51.84</v>
+        <v>51.88</v>
       </c>
       <c r="P88" s="4" t="n">
         <v>1.57</v>
@@ -9868,10 +9868,10 @@
         <v>0</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>75.92</v>
+        <v>75.94</v>
       </c>
       <c r="AC88" s="4" t="n">
-        <v>24.08</v>
+        <v>24.06</v>
       </c>
       <c r="AD88" s="4" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.22</v>
+        <v>16.26</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>99.5</v>
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>17.97</v>
+        <v>18.01</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>16.22</v>
+        <v>16.26</v>
       </c>
       <c r="P89" s="4" t="n">
         <v>1.31</v>
@@ -9970,10 +9970,10 @@
         <v>0</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>58.11</v>
+        <v>58.13</v>
       </c>
       <c r="AC89" s="4" t="n">
-        <v>41.89</v>
+        <v>41.87</v>
       </c>
       <c r="AD89" s="4" t="n">
         <v>0</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>39.69</v>
+        <v>39.74</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>100</v>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>29.99</v>
+        <v>30.03</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>39.69</v>
+        <v>39.74</v>
       </c>
       <c r="P90" s="4" t="n">
         <v>2.65</v>
@@ -10072,10 +10072,10 @@
         <v>0</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>69.84999999999999</v>
+        <v>69.87</v>
       </c>
       <c r="AC90" s="4" t="n">
-        <v>30.15</v>
+        <v>30.13</v>
       </c>
       <c r="AD90" s="4" t="n">
         <v>0</v>
@@ -10123,7 +10123,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28.53</v>
+        <v>28.57</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>100</v>
@@ -10137,13 +10137,13 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>16.34</v>
+        <v>16.38</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28.53</v>
+        <v>28.57</v>
       </c>
       <c r="P91" s="4" t="n">
         <v>0</v>
@@ -10174,10 +10174,10 @@
         <v>0</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>64.26000000000001</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="AC91" s="4" t="n">
-        <v>35.74</v>
+        <v>35.71</v>
       </c>
       <c r="AD91" s="4" t="n">
         <v>0</v>
@@ -10239,13 +10239,13 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.9</v>
+        <v>58.94</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>67.95</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="P92" s="4" t="n">
         <v>0</v>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26.44</v>
+        <v>26.48</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>100</v>
@@ -10341,13 +10341,13 @@
         </is>
       </c>
       <c r="M93" s="4" t="n">
-        <v>14.17</v>
+        <v>14.22</v>
       </c>
       <c r="N93" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>26.44</v>
+        <v>26.48</v>
       </c>
       <c r="P93" s="4" t="n">
         <v>2.03</v>
@@ -10378,10 +10378,10 @@
         <v>0</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>63.22</v>
+        <v>63.24</v>
       </c>
       <c r="AC93" s="4" t="n">
-        <v>36.78</v>
+        <v>36.76</v>
       </c>
       <c r="AD93" s="4" t="n">
         <v>0</v>
@@ -10429,7 +10429,7 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>51.22</v>
+        <v>51.26</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>100</v>
@@ -10443,13 +10443,13 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.49</v>
+        <v>43.53</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>51.22</v>
+        <v>51.26</v>
       </c>
       <c r="P94" s="4" t="n">
         <v>2.66</v>
@@ -10480,10 +10480,10 @@
         <v>0</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>75.61</v>
+        <v>75.63</v>
       </c>
       <c r="AC94" s="4" t="n">
-        <v>24.39</v>
+        <v>24.37</v>
       </c>
       <c r="AD94" s="4" t="n">
         <v>0</v>
@@ -10545,13 +10545,13 @@
         </is>
       </c>
       <c r="M95" s="4" t="n">
-        <v>67.90000000000001</v>
+        <v>67.95</v>
       </c>
       <c r="N95" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>76.70999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>26.16</v>
+        <v>26.2</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>100</v>
@@ -10643,13 +10643,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="n">
-        <v>19.05</v>
+        <v>19.09</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>26.16</v>
+        <v>26.2</v>
       </c>
       <c r="P96" s="4" t="n">
         <v>0</v>
@@ -10680,10 +10680,10 @@
         <v>0</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>63.08</v>
+        <v>63.1</v>
       </c>
       <c r="AC96" s="4" t="n">
-        <v>36.92</v>
+        <v>36.9</v>
       </c>
       <c r="AD96" s="4" t="n">
         <v>0</v>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>25.46</v>
+        <v>25.51</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>99.90000000000001</v>
@@ -10745,13 +10745,13 @@
         </is>
       </c>
       <c r="M97" s="4" t="n">
-        <v>16.07</v>
+        <v>16.11</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>25.46</v>
+        <v>25.51</v>
       </c>
       <c r="P97" s="4" t="n">
         <v>0</v>
@@ -10782,10 +10782,10 @@
         <v>0</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>62.73</v>
+        <v>62.75</v>
       </c>
       <c r="AC97" s="4" t="n">
-        <v>37.27</v>
+        <v>37.25</v>
       </c>
       <c r="AD97" s="4" t="n">
         <v>0</v>
@@ -10847,13 +10847,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="n">
-        <v>-10.15</v>
+        <v>-10.11</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>-4.55</v>
+        <v>-4.51</v>
       </c>
       <c r="P98" s="4" t="n">
         <v>0</v>
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>31.29</v>
+        <v>31.33</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -10949,13 +10949,13 @@
         </is>
       </c>
       <c r="M99" s="4" t="n">
-        <v>19.61</v>
+        <v>19.65</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>31.29</v>
+        <v>31.33</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.64</v>
@@ -10986,10 +10986,10 @@
         <v>0</v>
       </c>
       <c r="AB99" s="4" t="n">
-        <v>65.64</v>
+        <v>65.67</v>
       </c>
       <c r="AC99" s="4" t="n">
-        <v>34.36</v>
+        <v>34.33</v>
       </c>
       <c r="AD99" s="4" t="n">
         <v>0</v>
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26.39</v>
+        <v>26.43</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>100</v>
@@ -11051,13 +11051,13 @@
         </is>
       </c>
       <c r="M100" s="4" t="n">
-        <v>16.85</v>
+        <v>16.89</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>26.39</v>
+        <v>26.43</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1.69</v>
@@ -11088,10 +11088,10 @@
         <v>0</v>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>63.19</v>
+        <v>63.22</v>
       </c>
       <c r="AC100" s="4" t="n">
-        <v>36.81</v>
+        <v>36.78</v>
       </c>
       <c r="AD100" s="4" t="n">
         <v>0</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>63.61</v>
+        <v>63.65</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>100</v>
@@ -11153,13 +11153,13 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>56.82</v>
+        <v>56.86</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>63.61</v>
+        <v>63.65</v>
       </c>
       <c r="P101" s="4" t="n">
         <v>0</v>
@@ -11190,10 +11190,10 @@
         <v>0</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>81.8</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AC101" s="4" t="n">
-        <v>18.2</v>
+        <v>18.18</v>
       </c>
       <c r="AD101" s="4" t="n">
         <v>0</v>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>59.04</v>
+        <v>59.08</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11255,13 +11255,13 @@
         </is>
       </c>
       <c r="M102" s="4" t="n">
-        <v>43.58</v>
+        <v>43.62</v>
       </c>
       <c r="N102" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>59.04</v>
+        <v>59.08</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>1.93</v>
@@ -11292,10 +11292,10 @@
         <v>0</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>79.52</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="AC102" s="4" t="n">
-        <v>20.48</v>
+        <v>20.46</v>
       </c>
       <c r="AD102" s="4" t="n">
         <v>0</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20.42</v>
+        <v>20.46</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>99.8</v>
@@ -11357,13 +11357,13 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>8.289999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="N103" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>20.42</v>
+        <v>20.46</v>
       </c>
       <c r="P103" s="4" t="n">
         <v>1.39</v>
@@ -11394,10 +11394,10 @@
         <v>0</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>60.21</v>
+        <v>60.23</v>
       </c>
       <c r="AC103" s="4" t="n">
-        <v>39.79</v>
+        <v>39.77</v>
       </c>
       <c r="AD103" s="4" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>39.54</v>
+        <v>39.58</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
@@ -11459,13 +11459,13 @@
         </is>
       </c>
       <c r="M104" s="4" t="n">
-        <v>22.04</v>
+        <v>22.08</v>
       </c>
       <c r="N104" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>39.54</v>
+        <v>39.58</v>
       </c>
       <c r="P104" s="4" t="n">
         <v>1.73</v>
@@ -11496,10 +11496,10 @@
         <v>0</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>69.77</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="AC104" s="4" t="n">
-        <v>30.23</v>
+        <v>30.21</v>
       </c>
       <c r="AD104" s="4" t="n">
         <v>0</v>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>23.35</v>
+        <v>23.4</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>99.90000000000001</v>
@@ -11561,13 +11561,13 @@
         </is>
       </c>
       <c r="M105" s="4" t="n">
-        <v>13.37</v>
+        <v>13.42</v>
       </c>
       <c r="N105" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>22.63</v>
+        <v>22.67</v>
       </c>
       <c r="P105" s="4" t="n">
         <v>1.61</v>
@@ -11598,10 +11598,10 @@
         <v>0</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>59.45</v>
+        <v>59.47</v>
       </c>
       <c r="AC105" s="4" t="n">
-        <v>36.94</v>
+        <v>36.92</v>
       </c>
       <c r="AD105" s="4" t="n">
         <v>3.61</v>
@@ -11645,13 +11645,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6.72</v>
+        <v>6.75</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -11659,13 +11659,13 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.66</v>
+        <v>5.7</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>11.89</v>
+        <v>11.93</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>0.13</v>
@@ -11702,10 +11702,10 @@
         <v>0</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>53.36</v>
+        <v>53.38</v>
       </c>
       <c r="AC106" s="4" t="n">
-        <v>46.64</v>
+        <v>46.62</v>
       </c>
       <c r="AD106" s="4" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>22.08</v>
+        <v>22.13</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>99.90000000000001</v>
@@ -11767,13 +11767,13 @@
         </is>
       </c>
       <c r="M107" s="4" t="n">
-        <v>14.58</v>
+        <v>14.62</v>
       </c>
       <c r="N107" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O107" s="4" t="n">
-        <v>22.08</v>
+        <v>22.13</v>
       </c>
       <c r="P107" s="4" t="n">
         <v>2.54</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>61.04</v>
+        <v>61.06</v>
       </c>
       <c r="AC107" s="4" t="n">
-        <v>38.96</v>
+        <v>38.94</v>
       </c>
       <c r="AD107" s="4" t="n">
         <v>0</v>
@@ -11855,7 +11855,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>26.36</v>
+        <v>26.4</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>100</v>
@@ -11869,13 +11869,13 @@
         </is>
       </c>
       <c r="M108" s="4" t="n">
-        <v>20.82</v>
+        <v>20.86</v>
       </c>
       <c r="N108" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>26.36</v>
+        <v>26.4</v>
       </c>
       <c r="P108" s="4" t="n">
         <v>0</v>
@@ -11906,10 +11906,10 @@
         <v>0</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>63.18</v>
+        <v>63.2</v>
       </c>
       <c r="AC108" s="4" t="n">
-        <v>36.82</v>
+        <v>36.8</v>
       </c>
       <c r="AD108" s="4" t="n">
         <v>0</v>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27.59</v>
+        <v>27.63</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -11971,13 +11971,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.47</v>
+        <v>21.51</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>27.59</v>
+        <v>27.63</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12008,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>63.79</v>
+        <v>63.82</v>
       </c>
       <c r="AC109" s="4" t="n">
-        <v>36.21</v>
+        <v>36.18</v>
       </c>
       <c r="AD109" s="4" t="n">
         <v>0</v>
@@ -12059,7 +12059,7 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>39.84</v>
+        <v>39.88</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>100</v>
@@ -12073,13 +12073,13 @@
         </is>
       </c>
       <c r="M110" s="4" t="n">
-        <v>24.55</v>
+        <v>24.6</v>
       </c>
       <c r="N110" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>39.84</v>
+        <v>39.88</v>
       </c>
       <c r="P110" s="4" t="n">
         <v>1.58</v>
@@ -12110,10 +12110,10 @@
         <v>0</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>69.92</v>
+        <v>69.94</v>
       </c>
       <c r="AC110" s="4" t="n">
-        <v>30.08</v>
+        <v>30.06</v>
       </c>
       <c r="AD110" s="4" t="n">
         <v>0</v>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>89.8</v>
@@ -12903,10 +12903,10 @@
         <v>5.24</v>
       </c>
       <c r="O118" s="4" t="n">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="P118" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q118" s="4" t="n">
         <v>-1.67</v>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>37.17</v>
+        <v>36.67</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>100</v>
@@ -13005,10 +13005,10 @@
         <v>5.24</v>
       </c>
       <c r="O119" s="4" t="n">
-        <v>37.17</v>
+        <v>36.67</v>
       </c>
       <c r="P119" s="4" t="n">
-        <v>2.93</v>
+        <v>2.43</v>
       </c>
       <c r="Q119" s="4" t="n">
         <v>3.47</v>
@@ -13023,10 +13023,10 @@
       </c>
       <c r="V119" s="4" t="n"/>
       <c r="W119" s="5" t="n">
-        <v>2460386</v>
+        <v>2733260</v>
       </c>
       <c r="X119" s="5" t="n">
-        <v>840</v>
+        <v>20827</v>
       </c>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" s="4" t="n">
@@ -13036,10 +13036,10 @@
         <v>0</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>68.59</v>
+        <v>68.33</v>
       </c>
       <c r="AC119" s="4" t="n">
-        <v>31.41</v>
+        <v>31.67</v>
       </c>
       <c r="AD119" s="4" t="n">
         <v>0</v>
@@ -13291,7 +13291,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>35.18</v>
+        <v>35.15</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>100</v>
@@ -13311,10 +13311,10 @@
         <v>5.24</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>35.18</v>
+        <v>35.15</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q122" s="4" t="n">
         <v>1.17</v>
@@ -13332,7 +13332,7 @@
         <v>1379560</v>
       </c>
       <c r="X122" s="5" t="n">
-        <v>42112</v>
+        <v>46809</v>
       </c>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" s="4" t="n">
@@ -13342,10 +13342,10 @@
         <v>0</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>67.59</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="AC122" s="4" t="n">
-        <v>32.41</v>
+        <v>32.43</v>
       </c>
       <c r="AD122" s="4" t="n">
         <v>0</v>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>-13.64</v>
+        <v>-13.6</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>0.9</v>
@@ -13715,10 +13715,10 @@
         <v>5.24</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>-10.92</v>
+        <v>-10.83</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>-2.31</v>
+        <v>-2.22</v>
       </c>
       <c r="Q126" s="4" t="n">
         <v>0</v>
@@ -13752,10 +13752,10 @@
         <v>0</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>43.18</v>
+        <v>43.2</v>
       </c>
       <c r="AC126" s="4" t="n">
-        <v>56.82</v>
+        <v>56.8</v>
       </c>
       <c r="AD126" s="4" t="n">
         <v>0</v>
@@ -14211,13 +14211,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>-4.27</v>
+        <v>-4.09</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>78.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -14231,10 +14231,10 @@
         <v>5.24</v>
       </c>
       <c r="O131" s="4" t="n">
-        <v>-5.02</v>
+        <v>-4.8</v>
       </c>
       <c r="P131" s="4" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="Q131" s="4" t="n">
         <v>-2.73</v>
@@ -14268,10 +14268,10 @@
         <v>0</v>
       </c>
       <c r="AB131" s="4" t="n">
-        <v>47.87</v>
+        <v>47.95</v>
       </c>
       <c r="AC131" s="4" t="n">
-        <v>52.13</v>
+        <v>52.05</v>
       </c>
       <c r="AD131" s="4" t="n">
         <v>0</v>
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>7.24</v>
+        <v>7.13</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>88.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -14959,10 +14959,10 @@
         <v>5.24</v>
       </c>
       <c r="O138" s="4" t="n">
-        <v>7.24</v>
+        <v>7.13</v>
       </c>
       <c r="P138" s="4" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="Q138" s="4" t="n">
         <v>5.55</v>
@@ -14980,7 +14980,7 @@
         <v>1954817</v>
       </c>
       <c r="X138" s="5" t="n">
-        <v>166022</v>
+        <v>200797</v>
       </c>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" s="4" t="n">
@@ -14990,10 +14990,10 @@
         <v>0</v>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>53.62</v>
+        <v>53.56</v>
       </c>
       <c r="AC138" s="4" t="n">
-        <v>46.38</v>
+        <v>46.44</v>
       </c>
       <c r="AD138" s="4" t="n">
         <v>0</v>
@@ -15139,13 +15139,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>-4.7</v>
+        <v>-4.56</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>79.8</v>
+        <v>79.3</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -15159,10 +15159,10 @@
         <v>5.24</v>
       </c>
       <c r="O140" s="4" t="n">
-        <v>-4.7</v>
+        <v>-4.56</v>
       </c>
       <c r="P140" s="4" t="n">
-        <v>-1.15</v>
+        <v>-1.01</v>
       </c>
       <c r="Q140" s="4" t="n">
         <v>0</v>
@@ -15177,7 +15177,7 @@
       </c>
       <c r="V140" s="4" t="n"/>
       <c r="W140" s="5" t="n">
-        <v>223280</v>
+        <v>296507</v>
       </c>
       <c r="X140" s="5" t="n">
         <v>971068</v>
@@ -15190,10 +15190,10 @@
         <v>0</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>47.65</v>
+        <v>47.72</v>
       </c>
       <c r="AC140" s="4" t="n">
-        <v>52.35</v>
+        <v>52.28</v>
       </c>
       <c r="AD140" s="4" t="n">
         <v>0</v>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>51.31</v>
+        <v>51.25</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>100</v>
@@ -15559,10 +15559,10 @@
         <v>5.24</v>
       </c>
       <c r="O144" s="4" t="n">
-        <v>51.31</v>
+        <v>51.25</v>
       </c>
       <c r="P144" s="4" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Q144" s="4" t="n">
         <v>0</v>
@@ -15580,7 +15580,7 @@
         <v>955386</v>
       </c>
       <c r="X144" s="5" t="n">
-        <v>88417</v>
+        <v>98825</v>
       </c>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" s="4" t="n">
@@ -15590,10 +15590,10 @@
         <v>0</v>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>75.65000000000001</v>
+        <v>75.63</v>
       </c>
       <c r="AC144" s="4" t="n">
-        <v>24.35</v>
+        <v>24.37</v>
       </c>
       <c r="AD144" s="4" t="n">
         <v>0</v>
@@ -15759,7 +15759,7 @@
         <v>5.24</v>
       </c>
       <c r="O146" s="4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P146" s="4" t="n">
         <v>-0.76</v>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="V147" s="4" t="n"/>
       <c r="W147" s="5" t="n">
-        <v>2215066</v>
+        <v>2216116</v>
       </c>
       <c r="X147" s="5" t="n">
         <v>0</v>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>56.01</v>
+        <v>56.06</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>100</v>
@@ -15965,10 +15965,10 @@
         <v>5.24</v>
       </c>
       <c r="O148" s="4" t="n">
-        <v>56.01</v>
+        <v>56.06</v>
       </c>
       <c r="P148" s="4" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Q148" s="4" t="n">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>78.01000000000001</v>
+        <v>78.03</v>
       </c>
       <c r="AC148" s="4" t="n">
-        <v>21.99</v>
+        <v>21.97</v>
       </c>
       <c r="AD148" s="4" t="n">
         <v>0</v>
@@ -16047,13 +16047,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>87.7</v>
+        <v>87.5</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -16067,10 +16067,10 @@
         <v>5.24</v>
       </c>
       <c r="O149" s="4" t="n">
-        <v>6.72</v>
+        <v>6.66</v>
       </c>
       <c r="P149" s="4" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="Q149" s="4" t="n">
         <v>2.65</v>
@@ -16104,10 +16104,10 @@
         <v>0</v>
       </c>
       <c r="AB149" s="4" t="n">
-        <v>53.52</v>
+        <v>53.5</v>
       </c>
       <c r="AC149" s="4" t="n">
-        <v>46.48</v>
+        <v>46.5</v>
       </c>
       <c r="AD149" s="4" t="n">
         <v>0</v>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>-14.11</v>
+        <v>-14.09</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>0.8</v>
@@ -16385,10 +16385,10 @@
         <v>5.24</v>
       </c>
       <c r="O152" s="4" t="n">
-        <v>-15.89</v>
+        <v>-15.87</v>
       </c>
       <c r="P152" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="Q152" s="4" t="n">
         <v>-7.91</v>
@@ -16409,7 +16409,7 @@
         <v>-4</v>
       </c>
       <c r="W152" s="5" t="n">
-        <v>424189</v>
+        <v>438286</v>
       </c>
       <c r="X152" s="5" t="n">
         <v>567482</v>
@@ -16422,10 +16422,10 @@
         <v>0</v>
       </c>
       <c r="AB152" s="4" t="n">
-        <v>42.95</v>
+        <v>42.96</v>
       </c>
       <c r="AC152" s="4" t="n">
-        <v>57.05</v>
+        <v>57.04</v>
       </c>
       <c r="AD152" s="4" t="n">
         <v>0</v>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="V160" s="4" t="n"/>
       <c r="W160" s="5" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="X160" s="5" t="n">
         <v>1124952</v>
@@ -17923,7 +17923,7 @@
       </c>
       <c r="V167" s="4" t="n"/>
       <c r="W167" s="5" t="n">
-        <v>1038814</v>
+        <v>1093795</v>
       </c>
       <c r="X167" s="5" t="n">
         <v>0</v>
@@ -17987,7 +17987,7 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>43.58</v>
+        <v>43.6</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>100</v>
@@ -18007,10 +18007,10 @@
         <v>5.24</v>
       </c>
       <c r="O168" s="4" t="n">
-        <v>43.58</v>
+        <v>43.6</v>
       </c>
       <c r="P168" s="4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Q168" s="4" t="n">
         <v>10.72</v>
@@ -18025,10 +18025,10 @@
       </c>
       <c r="V168" s="4" t="n"/>
       <c r="W168" s="5" t="n">
-        <v>801957</v>
+        <v>820678</v>
       </c>
       <c r="X168" s="5" t="n">
-        <v>122390</v>
+        <v>122615</v>
       </c>
       <c r="Y168" t="inlineStr"/>
       <c r="Z168" s="4" t="n">
@@ -18038,10 +18038,10 @@
         <v>0</v>
       </c>
       <c r="AB168" s="4" t="n">
-        <v>71.79000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="AC168" s="4" t="n">
-        <v>28.21</v>
+        <v>28.2</v>
       </c>
       <c r="AD168" s="4" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11.39</v>
+        <v>11.32</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>98.7</v>
@@ -18103,16 +18103,16 @@
         </is>
       </c>
       <c r="M169" s="4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.91</v>
       </c>
       <c r="N169" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O169" s="4" t="n">
-        <v>13.78</v>
+        <v>13.68</v>
       </c>
       <c r="P169" s="4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="Q169" s="4" t="n">
         <v>10.1</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB169" s="4" t="n">
-        <v>55.7</v>
+        <v>55.66</v>
       </c>
       <c r="AC169" s="4" t="n">
-        <v>44.3</v>
+        <v>44.34</v>
       </c>
       <c r="AD169" s="4" t="n">
         <v>0</v>
@@ -18193,13 +18193,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -18207,16 +18207,16 @@
         </is>
       </c>
       <c r="M170" s="4" t="n">
-        <v>-2.35</v>
+        <v>-2.46</v>
       </c>
       <c r="N170" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="P170" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="Q170" s="4" t="n">
         <v>0</v>
@@ -18250,10 +18250,10 @@
         <v>0</v>
       </c>
       <c r="AB170" s="4" t="n">
-        <v>50.84</v>
+        <v>50.81</v>
       </c>
       <c r="AC170" s="4" t="n">
-        <v>49.16</v>
+        <v>49.19</v>
       </c>
       <c r="AD170" s="4" t="n">
         <v>0</v>
@@ -18301,13 +18301,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -18315,13 +18315,13 @@
         </is>
       </c>
       <c r="M171" s="4" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="N171" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>6.37</v>
+        <v>6.27</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.06</v>
@@ -18358,10 +18358,10 @@
         <v>0</v>
       </c>
       <c r="AB171" s="4" t="n">
-        <v>52.57</v>
+        <v>52.53</v>
       </c>
       <c r="AC171" s="4" t="n">
-        <v>47.43</v>
+        <v>47.47</v>
       </c>
       <c r="AD171" s="4" t="n">
         <v>0</v>
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.2</v>
@@ -18419,13 +18419,13 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-24.33</v>
+        <v>-24.44</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-20.8</v>
+        <v>-20.9</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -18456,10 +18456,10 @@
         <v>0</v>
       </c>
       <c r="AB172" s="4" t="n">
-        <v>39.6</v>
+        <v>39.55</v>
       </c>
       <c r="AC172" s="4" t="n">
-        <v>60.4</v>
+        <v>60.45</v>
       </c>
       <c r="AD172" s="4" t="n">
         <v>0</v>
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-28.8</v>
+        <v>-28.84</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18521,13 +18521,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-43.92</v>
+        <v>-43.98</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-41.37</v>
+        <v>-41.43</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18564,10 +18564,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>35.6</v>
+        <v>35.58</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>64.42</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18615,7 +18615,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-28.01</v>
+        <v>-28.07</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0</v>
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-26.1</v>
+        <v>-26.16</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-28.01</v>
+        <v>-28.07</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -18666,10 +18666,10 @@
         <v>0</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>36</v>
+        <v>35.97</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>64</v>
+        <v>64.03</v>
       </c>
       <c r="AD174" s="4" t="n">
         <v>0</v>
@@ -18717,7 +18717,7 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>46.67</v>
+        <v>46.63</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>100</v>
@@ -18737,10 +18737,10 @@
         <v>5.24</v>
       </c>
       <c r="O175" s="4" t="n">
-        <v>46.67</v>
+        <v>46.63</v>
       </c>
       <c r="P175" s="4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Q175" s="4" t="n">
         <v>0.87</v>
@@ -18758,7 +18758,7 @@
         <v>418350</v>
       </c>
       <c r="X175" s="5" t="n">
-        <v>58502</v>
+        <v>63316</v>
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" s="4" t="n">
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="AB175" s="4" t="n">
-        <v>73.33</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="AC175" s="4" t="n">
-        <v>26.67</v>
+        <v>26.68</v>
       </c>
       <c r="AD175" s="4" t="n">
         <v>0</v>
@@ -19921,7 +19921,7 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>27.13</v>
+        <v>27.02</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>100</v>
@@ -19941,10 +19941,10 @@
         <v>5.24</v>
       </c>
       <c r="O187" s="4" t="n">
-        <v>27.13</v>
+        <v>27.02</v>
       </c>
       <c r="P187" s="4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Q187" s="4" t="n">
         <v>6.25</v>
@@ -19962,7 +19962,7 @@
         <v>2885018</v>
       </c>
       <c r="X187" s="5" t="n">
-        <v>267865</v>
+        <v>317665</v>
       </c>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" s="4" t="n">
@@ -19972,10 +19972,10 @@
         <v>0</v>
       </c>
       <c r="AB187" s="4" t="n">
-        <v>63.56</v>
+        <v>63.51</v>
       </c>
       <c r="AC187" s="4" t="n">
-        <v>36.44</v>
+        <v>36.49</v>
       </c>
       <c r="AD187" s="4" t="n">
         <v>0</v>
@@ -21349,7 +21349,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-31.92</v>
+        <v>-32.32</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0</v>
@@ -21363,16 +21363,16 @@
         </is>
       </c>
       <c r="M201" s="4" t="n">
-        <v>-29.7</v>
+        <v>-29.69</v>
       </c>
       <c r="N201" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-31.92</v>
+        <v>-32.32</v>
       </c>
       <c r="P201" s="4" t="n">
-        <v>-1.71</v>
+        <v>-2.12</v>
       </c>
       <c r="Q201" s="4" t="n">
         <v>-5.4</v>
@@ -21387,10 +21387,10 @@
       </c>
       <c r="V201" s="4" t="n"/>
       <c r="W201" s="5" t="n">
-        <v>105413</v>
+        <v>40651</v>
       </c>
       <c r="X201" s="5" t="n">
-        <v>1467439</v>
+        <v>1488465</v>
       </c>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" s="4" t="n">
@@ -21400,10 +21400,10 @@
         <v>0</v>
       </c>
       <c r="AB201" s="4" t="n">
-        <v>34.04</v>
+        <v>33.84</v>
       </c>
       <c r="AC201" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>66.16</v>
       </c>
       <c r="AD201" s="4" t="n">
         <v>0</v>
@@ -21451,7 +21451,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-18.09</v>
+        <v>-18.08</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>0.4</v>
@@ -21465,13 +21465,13 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-17.27</v>
+        <v>-17.26</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>-18.09</v>
+        <v>-18.08</v>
       </c>
       <c r="P202" s="4" t="n">
         <v>-0.47</v>
@@ -21489,10 +21489,10 @@
       </c>
       <c r="V202" s="4" t="n"/>
       <c r="W202" s="5" t="n">
-        <v>727521</v>
+        <v>758823</v>
       </c>
       <c r="X202" s="5" t="n">
-        <v>1404518</v>
+        <v>1457605</v>
       </c>
       <c r="Y202" t="inlineStr"/>
       <c r="Z202" s="4" t="n">
@@ -21502,10 +21502,10 @@
         <v>0</v>
       </c>
       <c r="AB202" s="4" t="n">
-        <v>40.95</v>
+        <v>40.96</v>
       </c>
       <c r="AC202" s="4" t="n">
-        <v>59.05</v>
+        <v>59.04</v>
       </c>
       <c r="AD202" s="4" t="n">
         <v>0</v>
@@ -21553,13 +21553,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>17.68</v>
+        <v>20.69</v>
       </c>
       <c r="J203" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -21567,16 +21567,16 @@
         </is>
       </c>
       <c r="M203" s="4" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="N203" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>17.68</v>
+        <v>20.69</v>
       </c>
       <c r="P203" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q203" s="4" t="n">
         <v>7.29</v>
@@ -21591,10 +21591,10 @@
       </c>
       <c r="V203" s="4" t="n"/>
       <c r="W203" s="5" t="n">
-        <v>3594654</v>
+        <v>3690440</v>
       </c>
       <c r="X203" s="5" t="n">
-        <v>0</v>
+        <v>18916</v>
       </c>
       <c r="Y203" t="inlineStr"/>
       <c r="Z203" s="4" t="n">
@@ -21604,10 +21604,10 @@
         <v>0</v>
       </c>
       <c r="AB203" s="4" t="n">
-        <v>58.84</v>
+        <v>60.35</v>
       </c>
       <c r="AC203" s="4" t="n">
-        <v>41.16</v>
+        <v>39.65</v>
       </c>
       <c r="AD203" s="4" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-24.06</v>
+        <v>-23.54</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>0.1</v>
@@ -21669,16 +21669,16 @@
         </is>
       </c>
       <c r="M204" s="4" t="n">
-        <v>-21.66</v>
+        <v>-21.64</v>
       </c>
       <c r="N204" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>-24.06</v>
+        <v>-23.54</v>
       </c>
       <c r="P204" s="4" t="n">
-        <v>-1.94</v>
+        <v>-1.43</v>
       </c>
       <c r="Q204" s="4" t="n">
         <v>-5.29</v>
@@ -21693,10 +21693,10 @@
       </c>
       <c r="V204" s="4" t="n"/>
       <c r="W204" s="5" t="n">
-        <v>93010</v>
+        <v>234455</v>
       </c>
       <c r="X204" s="5" t="n">
-        <v>1841348</v>
+        <v>1855035</v>
       </c>
       <c r="Y204" t="inlineStr"/>
       <c r="Z204" s="4" t="n">
@@ -21706,10 +21706,10 @@
         <v>0</v>
       </c>
       <c r="AB204" s="4" t="n">
-        <v>37.97</v>
+        <v>38.23</v>
       </c>
       <c r="AC204" s="4" t="n">
-        <v>62.03</v>
+        <v>61.77</v>
       </c>
       <c r="AD204" s="4" t="n">
         <v>0</v>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="V209" s="4" t="n"/>
       <c r="W209" s="5" t="n">
-        <v>182256</v>
+        <v>182281</v>
       </c>
       <c r="X209" s="5" t="n">
         <v>849758</v>
@@ -22367,7 +22367,7 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>-47.07</v>
+        <v>-47.01</v>
       </c>
       <c r="J211" s="4" t="n">
         <v>0</v>
@@ -22387,10 +22387,10 @@
         <v>5.24</v>
       </c>
       <c r="O211" s="4" t="n">
-        <v>-47.07</v>
+        <v>-47.01</v>
       </c>
       <c r="P211" s="4" t="n">
-        <v>-3.08</v>
+        <v>-3.01</v>
       </c>
       <c r="Q211" s="4" t="n">
         <v>-9.01</v>
@@ -22405,10 +22405,10 @@
       </c>
       <c r="V211" s="4" t="n"/>
       <c r="W211" s="5" t="n">
-        <v>126085</v>
+        <v>142677</v>
       </c>
       <c r="X211" s="5" t="n">
-        <v>10590473</v>
+        <v>10638030</v>
       </c>
       <c r="Y211" t="inlineStr"/>
       <c r="Z211" s="4" t="n">
@@ -22418,10 +22418,10 @@
         <v>0</v>
       </c>
       <c r="AB211" s="4" t="n">
-        <v>26.46</v>
+        <v>26.5</v>
       </c>
       <c r="AC211" s="4" t="n">
-        <v>73.54000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="AD211" s="4" t="n">
         <v>0</v>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="V212" s="4" t="n"/>
       <c r="W212" s="5" t="n">
-        <v>1383847</v>
+        <v>1412697</v>
       </c>
       <c r="X212" s="5" t="n">
         <v>0</v>
@@ -22571,7 +22571,7 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>-36.97</v>
+        <v>-36.98</v>
       </c>
       <c r="J213" s="4" t="n">
         <v>0</v>
@@ -22591,10 +22591,10 @@
         <v>5.24</v>
       </c>
       <c r="O213" s="4" t="n">
-        <v>-36.97</v>
+        <v>-36.98</v>
       </c>
       <c r="P213" s="4" t="n">
-        <v>-2.04</v>
+        <v>-2.05</v>
       </c>
       <c r="Q213" s="4" t="n">
         <v>-3.74</v>
@@ -22612,7 +22612,7 @@
         <v>6968</v>
       </c>
       <c r="X213" s="5" t="n">
-        <v>816186</v>
+        <v>822841</v>
       </c>
       <c r="Y213" t="inlineStr"/>
       <c r="Z213" s="4" t="n">
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>-39.87</v>
+        <v>-39.8</v>
       </c>
       <c r="J214" s="4" t="n">
         <v>0</v>
@@ -22693,10 +22693,10 @@
         <v>5.24</v>
       </c>
       <c r="O214" s="4" t="n">
-        <v>-39.87</v>
+        <v>-39.8</v>
       </c>
       <c r="P214" s="4" t="n">
-        <v>-3.21</v>
+        <v>-3.14</v>
       </c>
       <c r="Q214" s="4" t="n">
         <v>-7.75</v>
@@ -22711,10 +22711,10 @@
       </c>
       <c r="V214" s="4" t="n"/>
       <c r="W214" s="5" t="n">
-        <v>234784</v>
+        <v>268772</v>
       </c>
       <c r="X214" s="5" t="n">
-        <v>20548480</v>
+        <v>20976864</v>
       </c>
       <c r="Y214" t="inlineStr"/>
       <c r="Z214" s="4" t="n">
@@ -22724,10 +22724,10 @@
         <v>0</v>
       </c>
       <c r="AB214" s="4" t="n">
-        <v>30.07</v>
+        <v>30.1</v>
       </c>
       <c r="AC214" s="4" t="n">
-        <v>69.93000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AD214" s="4" t="n">
         <v>0</v>
@@ -22771,7 +22771,7 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>-31.11</v>
+        <v>-31.09</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>0</v>
@@ -22791,10 +22791,10 @@
         <v>5.24</v>
       </c>
       <c r="O215" s="4" t="n">
-        <v>-31.11</v>
+        <v>-31.09</v>
       </c>
       <c r="P215" s="4" t="n">
-        <v>-2.6</v>
+        <v>-2.58</v>
       </c>
       <c r="Q215" s="4" t="n">
         <v>0</v>
@@ -22809,10 +22809,10 @@
       </c>
       <c r="V215" s="4" t="n"/>
       <c r="W215" s="5" t="n">
-        <v>83511</v>
+        <v>90000</v>
       </c>
       <c r="X215" s="5" t="n">
-        <v>6564561</v>
+        <v>6612410</v>
       </c>
       <c r="Y215" t="inlineStr"/>
       <c r="Z215" s="4" t="n">
@@ -22822,10 +22822,10 @@
         <v>0</v>
       </c>
       <c r="AB215" s="4" t="n">
-        <v>34.44</v>
+        <v>34.45</v>
       </c>
       <c r="AC215" s="4" t="n">
-        <v>65.56</v>
+        <v>65.55</v>
       </c>
       <c r="AD215" s="4" t="n">
         <v>0</v>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="V216" s="4" t="n"/>
       <c r="W216" s="5" t="n">
-        <v>832825</v>
+        <v>0</v>
       </c>
       <c r="X216" s="5" t="n">
         <v>0</v>
@@ -24693,7 +24693,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.79</v>
+        <v>31</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24791,13 +24791,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.45</v>
+        <v>-3.77</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>63.4</v>
+        <v>61.4</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24937,10 +24937,10 @@
       </c>
       <c r="V236" s="4" t="n"/>
       <c r="W236" s="5" t="n">
-        <v>803423</v>
+        <v>824341</v>
       </c>
       <c r="X236" s="5" t="n">
-        <v>1877392</v>
+        <v>1917574</v>
       </c>
       <c r="Y236" t="inlineStr"/>
       <c r="Z236" s="4" t="n">
@@ -25039,10 +25039,10 @@
       </c>
       <c r="V237" s="4" t="n"/>
       <c r="W237" s="5" t="n">
-        <v>84011</v>
+        <v>85094</v>
       </c>
       <c r="X237" s="5" t="n">
-        <v>1648987</v>
+        <v>1652235</v>
       </c>
       <c r="Y237" t="inlineStr"/>
       <c r="Z237" s="4" t="n">
@@ -25103,7 +25103,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>19.95</v>
+        <v>20.97</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25123,10 +25123,10 @@
         <v>5.24</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>19.95</v>
+        <v>20.97</v>
       </c>
       <c r="P238" s="4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q238" s="4" t="n">
         <v>4.28</v>
@@ -25141,10 +25141,10 @@
       </c>
       <c r="V238" s="4" t="n"/>
       <c r="W238" s="5" t="n">
-        <v>2287558</v>
+        <v>2329122</v>
       </c>
       <c r="X238" s="5" t="n">
-        <v>0</v>
+        <v>551697</v>
       </c>
       <c r="Y238" t="inlineStr"/>
       <c r="Z238" s="4" t="n">
@@ -25154,10 +25154,10 @@
         <v>0</v>
       </c>
       <c r="AB238" s="4" t="n">
-        <v>59.97</v>
+        <v>60.48</v>
       </c>
       <c r="AC238" s="4" t="n">
-        <v>40.03</v>
+        <v>39.52</v>
       </c>
       <c r="AD238" s="4" t="n">
         <v>0</v>
@@ -25225,10 +25225,10 @@
         <v>5.24</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-2.83</v>
+        <v>-2.82</v>
       </c>
       <c r="P239" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="Q239" s="4" t="n">
         <v>-4.89</v>
@@ -25249,10 +25249,10 @@
         <v>-0.13</v>
       </c>
       <c r="W239" s="5" t="n">
-        <v>2508603</v>
+        <v>2620011</v>
       </c>
       <c r="X239" s="5" t="n">
-        <v>4003831</v>
+        <v>4093991</v>
       </c>
       <c r="Y239" t="inlineStr"/>
       <c r="Z239" s="4" t="n">
@@ -25262,10 +25262,10 @@
         <v>0</v>
       </c>
       <c r="AB239" s="4" t="n">
-        <v>48.92</v>
+        <v>48.93</v>
       </c>
       <c r="AC239" s="4" t="n">
-        <v>51.08</v>
+        <v>51.07</v>
       </c>
       <c r="AD239" s="4" t="n">
         <v>0</v>
@@ -25313,7 +25313,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-26.28</v>
+        <v>-26.27</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0</v>
@@ -25333,10 +25333,10 @@
         <v>5.24</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-26.28</v>
+        <v>-26.27</v>
       </c>
       <c r="P240" s="4" t="n">
-        <v>-2.14</v>
+        <v>-2.12</v>
       </c>
       <c r="Q240" s="4" t="n">
         <v>-5.07</v>
@@ -25351,10 +25351,10 @@
       </c>
       <c r="V240" s="4" t="n"/>
       <c r="W240" s="5" t="n">
-        <v>51717</v>
+        <v>55756</v>
       </c>
       <c r="X240" s="5" t="n">
-        <v>1717295</v>
+        <v>1742399</v>
       </c>
       <c r="Y240" t="inlineStr"/>
       <c r="Z240" s="4" t="n">
@@ -25364,10 +25364,10 @@
         <v>0</v>
       </c>
       <c r="AB240" s="4" t="n">
-        <v>36.86</v>
+        <v>36.87</v>
       </c>
       <c r="AC240" s="4" t="n">
-        <v>63.14</v>
+        <v>63.13</v>
       </c>
       <c r="AD240" s="4" t="n">
         <v>0</v>
@@ -25453,7 +25453,7 @@
       </c>
       <c r="V241" s="4" t="n"/>
       <c r="W241" s="5" t="n">
-        <v>1155234</v>
+        <v>1193712</v>
       </c>
       <c r="X241" s="5" t="n">
         <v>0</v>
@@ -25517,13 +25517,13 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>1.27</v>
+        <v>0.93</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>66.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>33.2</v>
+        <v>34.6</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -25537,10 +25537,10 @@
         <v>5.24</v>
       </c>
       <c r="O242" s="4" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="P242" s="4" t="n">
-        <v>-0.62</v>
+        <v>-1.12</v>
       </c>
       <c r="Q242" s="4" t="n">
         <v>-3.8</v>
@@ -25561,10 +25561,10 @@
         <v>-1</v>
       </c>
       <c r="W242" s="5" t="n">
-        <v>2893770</v>
+        <v>1119198</v>
       </c>
       <c r="X242" s="5" t="n">
-        <v>6180398</v>
+        <v>6306828</v>
       </c>
       <c r="Y242" t="inlineStr"/>
       <c r="Z242" s="4" t="n">
@@ -25574,10 +25574,10 @@
         <v>0</v>
       </c>
       <c r="AB242" s="4" t="n">
-        <v>50.64</v>
+        <v>50.47</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.36</v>
+        <v>49.53</v>
       </c>
       <c r="AD242" s="4" t="n">
         <v>0</v>
@@ -25625,13 +25625,13 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>18.3</v>
+        <v>16.78</v>
       </c>
       <c r="J243" s="4" t="n">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
       <c r="K243" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -25645,10 +25645,10 @@
         <v>5.24</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>18.3</v>
+        <v>16.78</v>
       </c>
       <c r="P243" s="4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q243" s="4" t="n">
         <v>9.859999999999999</v>
@@ -25663,10 +25663,10 @@
       </c>
       <c r="V243" s="4" t="n"/>
       <c r="W243" s="5" t="n">
-        <v>5540175</v>
+        <v>5644876</v>
       </c>
       <c r="X243" s="5" t="n">
-        <v>687295</v>
+        <v>0</v>
       </c>
       <c r="Y243" t="inlineStr"/>
       <c r="Z243" s="4" t="n">
@@ -25676,10 +25676,10 @@
         <v>0</v>
       </c>
       <c r="AB243" s="4" t="n">
-        <v>59.15</v>
+        <v>58.39</v>
       </c>
       <c r="AC243" s="4" t="n">
-        <v>40.85</v>
+        <v>41.61</v>
       </c>
       <c r="AD243" s="4" t="n">
         <v>0</v>
@@ -25765,10 +25765,10 @@
       </c>
       <c r="V244" s="4" t="n"/>
       <c r="W244" s="5" t="n">
-        <v>7579</v>
+        <v>8084</v>
       </c>
       <c r="X244" s="5" t="n">
-        <v>5146490</v>
+        <v>5242309</v>
       </c>
       <c r="Y244" t="inlineStr"/>
       <c r="Z244" s="4" t="n">
@@ -25778,10 +25778,10 @@
         <v>0</v>
       </c>
       <c r="AB244" s="4" t="n">
-        <v>33.37</v>
+        <v>33.36</v>
       </c>
       <c r="AC244" s="4" t="n">
-        <v>66.63</v>
+        <v>66.64</v>
       </c>
       <c r="AD244" s="4" t="n">
         <v>0</v>
@@ -25825,13 +25825,13 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="J245" s="4" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="K245" s="4" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -25845,10 +25845,10 @@
         <v>5.24</v>
       </c>
       <c r="O245" s="4" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="P245" s="4" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="Q245" s="4" t="n">
         <v>0</v>
@@ -25869,10 +25869,10 @@
         <v>-1</v>
       </c>
       <c r="W245" s="5" t="n">
-        <v>1161111</v>
+        <v>1211489</v>
       </c>
       <c r="X245" s="5" t="n">
-        <v>1386621</v>
+        <v>1414724</v>
       </c>
       <c r="Y245" t="inlineStr"/>
       <c r="Z245" s="4" t="n">
@@ -25882,10 +25882,10 @@
         <v>0</v>
       </c>
       <c r="AB245" s="4" t="n">
-        <v>50.83</v>
+        <v>50.85</v>
       </c>
       <c r="AC245" s="4" t="n">
-        <v>49.17</v>
+        <v>49.15</v>
       </c>
       <c r="AD245" s="4" t="n">
         <v>0</v>
@@ -25929,7 +25929,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>27.01</v>
+        <v>26.49</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>100</v>
@@ -25949,10 +25949,10 @@
         <v>5.24</v>
       </c>
       <c r="O246" s="4" t="n">
-        <v>27.01</v>
+        <v>26.49</v>
       </c>
       <c r="P246" s="4" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="Q246" s="4" t="n">
         <v>0</v>
@@ -25967,10 +25967,10 @@
       </c>
       <c r="V246" s="4" t="n"/>
       <c r="W246" s="5" t="n">
-        <v>1235233</v>
+        <v>1485178</v>
       </c>
       <c r="X246" s="5" t="n">
-        <v>28616</v>
+        <v>141876</v>
       </c>
       <c r="Y246" t="inlineStr"/>
       <c r="Z246" s="4" t="n">
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>63.5</v>
+        <v>63.25</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>36.5</v>
+        <v>36.75</v>
       </c>
       <c r="AD246" s="4" t="n">
         <v>0</v>
@@ -26031,7 +26031,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>55.56</v>
+        <v>58.52</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -26051,10 +26051,10 @@
         <v>5.24</v>
       </c>
       <c r="O247" s="4" t="n">
-        <v>55.56</v>
+        <v>58.52</v>
       </c>
       <c r="P247" s="4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q247" s="4" t="n">
         <v>5.22</v>
@@ -26069,10 +26069,10 @@
       </c>
       <c r="V247" s="4" t="n"/>
       <c r="W247" s="5" t="n">
-        <v>2713214</v>
+        <v>2756214</v>
       </c>
       <c r="X247" s="5" t="n">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="Y247" t="inlineStr"/>
       <c r="Z247" s="4" t="n">
@@ -26082,10 +26082,10 @@
         <v>0</v>
       </c>
       <c r="AB247" s="4" t="n">
-        <v>77.78</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="AC247" s="4" t="n">
-        <v>22.22</v>
+        <v>20.74</v>
       </c>
       <c r="AD247" s="4" t="n">
         <v>0</v>
@@ -26171,7 +26171,7 @@
       </c>
       <c r="V248" s="4" t="n"/>
       <c r="W248" s="5" t="n">
-        <v>-1103507</v>
+        <v>390276</v>
       </c>
       <c r="X248" s="5" t="n">
         <v>0</v>
@@ -26249,16 +26249,16 @@
         </is>
       </c>
       <c r="M249" s="4" t="n">
-        <v>-9.039999999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="N249" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O249" s="4" t="n">
-        <v>-6.2</v>
+        <v>-6.19</v>
       </c>
       <c r="P249" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="Q249" s="4" t="n">
         <v>-1.67</v>
@@ -26279,10 +26279,10 @@
         <v>-5.01</v>
       </c>
       <c r="W249" s="5" t="n">
-        <v>1872308</v>
+        <v>2000547</v>
       </c>
       <c r="X249" s="5" t="n">
-        <v>1916146</v>
+        <v>2030569</v>
       </c>
       <c r="Y249" t="inlineStr"/>
       <c r="Z249" s="4" t="n">
@@ -26339,7 +26339,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>12.08</v>
+        <v>12.1</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>98.90000000000001</v>
@@ -26359,10 +26359,10 @@
         <v>5.24</v>
       </c>
       <c r="O250" s="4" t="n">
-        <v>13.64</v>
+        <v>13.66</v>
       </c>
       <c r="P250" s="4" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="Q250" s="4" t="n">
         <v>0</v>
@@ -26383,10 +26383,10 @@
         <v>8</v>
       </c>
       <c r="W250" s="5" t="n">
-        <v>892676</v>
+        <v>923277</v>
       </c>
       <c r="X250" s="5" t="n">
-        <v>461815</v>
+        <v>511213</v>
       </c>
       <c r="Y250" t="inlineStr"/>
       <c r="Z250" s="4" t="n">
@@ -26396,10 +26396,10 @@
         <v>0</v>
       </c>
       <c r="AB250" s="4" t="n">
-        <v>56.04</v>
+        <v>56.05</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>43.96</v>
+        <v>43.95</v>
       </c>
       <c r="AD250" s="4" t="n">
         <v>0</v>
@@ -26447,7 +26447,7 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>30.06</v>
+        <v>30.05</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>100</v>
@@ -26467,7 +26467,7 @@
         <v>5.24</v>
       </c>
       <c r="O251" s="4" t="n">
-        <v>30.06</v>
+        <v>30.05</v>
       </c>
       <c r="P251" s="4" t="n">
         <v>0</v>
@@ -26485,7 +26485,7 @@
       </c>
       <c r="V251" s="4" t="n"/>
       <c r="W251" s="5" t="n">
-        <v>1278346</v>
+        <v>1361933</v>
       </c>
       <c r="X251" s="5" t="n">
         <v>0</v>
@@ -26549,7 +26549,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>47.84</v>
+        <v>47.81</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>100</v>
@@ -26563,16 +26563,16 @@
         </is>
       </c>
       <c r="M252" s="4" t="n">
-        <v>39.56</v>
+        <v>39.55</v>
       </c>
       <c r="N252" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O252" s="4" t="n">
-        <v>47.84</v>
+        <v>47.81</v>
       </c>
       <c r="P252" s="4" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q252" s="4" t="n">
         <v>1.5</v>
@@ -26587,10 +26587,10 @@
       </c>
       <c r="V252" s="4" t="n"/>
       <c r="W252" s="5" t="n">
-        <v>1217732</v>
+        <v>1251583</v>
       </c>
       <c r="X252" s="5" t="n">
-        <v>23031</v>
+        <v>28031</v>
       </c>
       <c r="Y252" t="inlineStr"/>
       <c r="Z252" s="4" t="n">
@@ -26600,10 +26600,10 @@
         <v>0</v>
       </c>
       <c r="AB252" s="4" t="n">
-        <v>73.92</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AC252" s="4" t="n">
-        <v>26.08</v>
+        <v>26.1</v>
       </c>
       <c r="AD252" s="4" t="n">
         <v>0</v>
@@ -26651,7 +26651,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>65.97</v>
+        <v>65.95</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>100</v>
@@ -26665,16 +26665,16 @@
         </is>
       </c>
       <c r="M253" s="4" t="n">
-        <v>66.39</v>
+        <v>66.38</v>
       </c>
       <c r="N253" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O253" s="4" t="n">
-        <v>65.97</v>
+        <v>65.95</v>
       </c>
       <c r="P253" s="4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Q253" s="4" t="n">
         <v>-6.48</v>
@@ -26689,10 +26689,10 @@
       </c>
       <c r="V253" s="4" t="n"/>
       <c r="W253" s="5" t="n">
-        <v>5715729</v>
+        <v>5829715</v>
       </c>
       <c r="X253" s="5" t="n">
-        <v>1078205</v>
+        <v>1128979</v>
       </c>
       <c r="Y253" t="inlineStr"/>
       <c r="Z253" s="4" t="n">
@@ -26702,10 +26702,10 @@
         <v>0</v>
       </c>
       <c r="AB253" s="4" t="n">
-        <v>82.98</v>
+        <v>82.97</v>
       </c>
       <c r="AC253" s="4" t="n">
-        <v>17.02</v>
+        <v>17.03</v>
       </c>
       <c r="AD253" s="4" t="n">
         <v>0</v>
@@ -26794,7 +26794,7 @@
         <v>0</v>
       </c>
       <c r="X254" s="5" t="n">
-        <v>9631580</v>
+        <v>9786064</v>
       </c>
       <c r="Y254" t="inlineStr"/>
       <c r="Z254" s="4" t="n">
@@ -26896,7 +26896,7 @@
         <v>0</v>
       </c>
       <c r="X255" s="5" t="n">
-        <v>1239373</v>
+        <v>1286028</v>
       </c>
       <c r="Y255" t="inlineStr"/>
       <c r="Z255" s="4" t="n">
@@ -26998,7 +26998,7 @@
         <v>0</v>
       </c>
       <c r="X256" s="5" t="n">
-        <v>1940297</v>
+        <v>1996898</v>
       </c>
       <c r="Y256" t="inlineStr"/>
       <c r="Z256" s="4" t="n">
@@ -27097,7 +27097,7 @@
       </c>
       <c r="V257" s="4" t="n"/>
       <c r="W257" s="5" t="n">
-        <v>3295182</v>
+        <v>3561712</v>
       </c>
       <c r="X257" s="5" t="n">
         <v>0</v>
@@ -27161,13 +27161,13 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.7</v>
+        <v>-10.69</v>
       </c>
       <c r="J258" s="4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K258" s="4" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -27181,10 +27181,10 @@
         <v>5.24</v>
       </c>
       <c r="O258" s="4" t="n">
-        <v>-11.8</v>
+        <v>-11.79</v>
       </c>
       <c r="P258" s="4" t="n">
-        <v>-0.83</v>
+        <v>-0.82</v>
       </c>
       <c r="Q258" s="4" t="n">
         <v>-3.37</v>
@@ -27205,10 +27205,10 @@
         <v>-6.5</v>
       </c>
       <c r="W258" s="5" t="n">
-        <v>1119886</v>
+        <v>1155880</v>
       </c>
       <c r="X258" s="5" t="n">
-        <v>3478123</v>
+        <v>3528095</v>
       </c>
       <c r="Y258" t="inlineStr"/>
       <c r="Z258" s="4" t="n">
@@ -27218,10 +27218,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.65</v>
+        <v>44.66</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.35</v>
+        <v>55.34</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -27292,7 +27292,7 @@
         <v>-19.63</v>
       </c>
       <c r="P259" s="4" t="n">
-        <v>-1.79</v>
+        <v>-1.78</v>
       </c>
       <c r="Q259" s="4" t="n">
         <v>-2.01</v>
@@ -27307,10 +27307,10 @@
       </c>
       <c r="V259" s="4" t="n"/>
       <c r="W259" s="5" t="n">
-        <v>41591</v>
+        <v>43339</v>
       </c>
       <c r="X259" s="5" t="n">
-        <v>940192</v>
+        <v>950350</v>
       </c>
       <c r="Y259" t="inlineStr"/>
       <c r="Z259" s="4" t="n">
@@ -27320,10 +27320,10 @@
         <v>0</v>
       </c>
       <c r="AB259" s="4" t="n">
-        <v>40.18</v>
+        <v>40.19</v>
       </c>
       <c r="AC259" s="4" t="n">
-        <v>59.82</v>
+        <v>59.81</v>
       </c>
       <c r="AD259" s="4" t="n">
         <v>0</v>
@@ -27371,13 +27371,13 @@
         </is>
       </c>
       <c r="I260" s="4" t="n">
-        <v>-21</v>
+        <v>-21.91</v>
       </c>
       <c r="J260" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K260" s="4" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -27391,10 +27391,10 @@
         <v>5.24</v>
       </c>
       <c r="O260" s="4" t="n">
-        <v>-21</v>
+        <v>-21.91</v>
       </c>
       <c r="P260" s="4" t="n">
-        <v>-1.17</v>
+        <v>-2.08</v>
       </c>
       <c r="Q260" s="4" t="n">
         <v>-3.26</v>
@@ -27409,10 +27409,10 @@
       </c>
       <c r="V260" s="4" t="n"/>
       <c r="W260" s="5" t="n">
-        <v>250118</v>
+        <v>39762</v>
       </c>
       <c r="X260" s="5" t="n">
-        <v>1370433</v>
+        <v>1392968</v>
       </c>
       <c r="Y260" t="inlineStr"/>
       <c r="Z260" s="4" t="n">
@@ -27422,10 +27422,10 @@
         <v>0</v>
       </c>
       <c r="AB260" s="4" t="n">
-        <v>39.5</v>
+        <v>39.04</v>
       </c>
       <c r="AC260" s="4" t="n">
-        <v>60.5</v>
+        <v>60.96</v>
       </c>
       <c r="AD260" s="4" t="n">
         <v>0</v>
@@ -27473,13 +27473,13 @@
         </is>
       </c>
       <c r="I261" s="4" t="n">
-        <v>-7.21</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="J261" s="4" t="n">
-        <v>11.8</v>
+        <v>7</v>
       </c>
       <c r="K261" s="4" t="n">
-        <v>88.2</v>
+        <v>93</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -27493,10 +27493,10 @@
         <v>5.24</v>
       </c>
       <c r="O261" s="4" t="n">
-        <v>-7.21</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="P261" s="4" t="n">
-        <v>2.36</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q261" s="4" t="n">
         <v>3.1</v>
@@ -27511,10 +27511,10 @@
       </c>
       <c r="V261" s="4" t="n"/>
       <c r="W261" s="5" t="n">
-        <v>1298255</v>
+        <v>1336738</v>
       </c>
       <c r="X261" s="5" t="n">
-        <v>7774</v>
+        <v>331764</v>
       </c>
       <c r="Y261" t="inlineStr"/>
       <c r="Z261" s="4" t="n">
@@ -27524,10 +27524,10 @@
         <v>0</v>
       </c>
       <c r="AB261" s="4" t="n">
-        <v>46.39</v>
+        <v>45.56</v>
       </c>
       <c r="AC261" s="4" t="n">
-        <v>53.61</v>
+        <v>54.44</v>
       </c>
       <c r="AD261" s="4" t="n">
         <v>0</v>
@@ -27571,7 +27571,7 @@
         </is>
       </c>
       <c r="I262" s="4" t="n">
-        <v>-23.35</v>
+        <v>-23.33</v>
       </c>
       <c r="J262" s="4" t="n">
         <v>0.1</v>
@@ -27591,10 +27591,10 @@
         <v>5.24</v>
       </c>
       <c r="O262" s="4" t="n">
-        <v>-23.35</v>
+        <v>-23.33</v>
       </c>
       <c r="P262" s="4" t="n">
-        <v>-1.06</v>
+        <v>-1.04</v>
       </c>
       <c r="Q262" s="4" t="n">
         <v>0</v>
@@ -27609,10 +27609,10 @@
       </c>
       <c r="V262" s="4" t="n"/>
       <c r="W262" s="5" t="n">
-        <v>51046</v>
+        <v>72101</v>
       </c>
       <c r="X262" s="5" t="n">
-        <v>546096</v>
+        <v>599336</v>
       </c>
       <c r="Y262" t="inlineStr"/>
       <c r="Z262" s="4" t="n">
@@ -27622,10 +27622,10 @@
         <v>0</v>
       </c>
       <c r="AB262" s="4" t="n">
-        <v>38.32</v>
+        <v>38.33</v>
       </c>
       <c r="AC262" s="4" t="n">
-        <v>61.68</v>
+        <v>61.67</v>
       </c>
       <c r="AD262" s="4" t="n">
         <v>0</v>
@@ -27673,7 +27673,7 @@
         </is>
       </c>
       <c r="I263" s="4" t="n">
-        <v>-43.36</v>
+        <v>-43.42</v>
       </c>
       <c r="J263" s="4" t="n">
         <v>0</v>
@@ -27693,10 +27693,10 @@
         <v>5.24</v>
       </c>
       <c r="O263" s="4" t="n">
-        <v>-43.36</v>
+        <v>-43.42</v>
       </c>
       <c r="P263" s="4" t="n">
-        <v>-1.97</v>
+        <v>-2.03</v>
       </c>
       <c r="Q263" s="4" t="n">
         <v>-2.63</v>
@@ -27714,7 +27714,7 @@
         <v>50540</v>
       </c>
       <c r="X263" s="5" t="n">
-        <v>1339538</v>
+        <v>1460463</v>
       </c>
       <c r="Y263" t="inlineStr"/>
       <c r="Z263" s="4" t="n">
@@ -27724,10 +27724,10 @@
         <v>0</v>
       </c>
       <c r="AB263" s="4" t="n">
-        <v>28.32</v>
+        <v>28.29</v>
       </c>
       <c r="AC263" s="4" t="n">
-        <v>71.68000000000001</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="AD263" s="4" t="n">
         <v>0</v>
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="I264" s="4" t="n">
-        <v>-54.66</v>
+        <v>-54.65</v>
       </c>
       <c r="J264" s="4" t="n">
         <v>0</v>
@@ -27795,10 +27795,10 @@
         <v>5.24</v>
       </c>
       <c r="O264" s="4" t="n">
-        <v>-54.66</v>
+        <v>-54.65</v>
       </c>
       <c r="P264" s="4" t="n">
-        <v>-3.43</v>
+        <v>-3.42</v>
       </c>
       <c r="Q264" s="4" t="n">
         <v>-1.83</v>
@@ -27813,10 +27813,10 @@
       </c>
       <c r="V264" s="4" t="n"/>
       <c r="W264" s="5" t="n">
-        <v>4251</v>
+        <v>5674</v>
       </c>
       <c r="X264" s="5" t="n">
-        <v>5211627</v>
+        <v>5264183</v>
       </c>
       <c r="Y264" t="inlineStr"/>
       <c r="Z264" s="4" t="n">
@@ -28281,13 +28281,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.76</v>
+        <v>-6.86</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>86.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28295,13 +28295,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.17</v>
+        <v>-12.31</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.06</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28338,10 +28338,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.62</v>
+        <v>46.57</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.38</v>
+        <v>53.43</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.8</v>
+        <v>-33.93</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28403,13 +28403,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.14</v>
+        <v>-31.27</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.8</v>
+        <v>-33.93</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28440,10 +28440,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.1</v>
+        <v>33.03</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.97</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28599,7 +28599,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>45.4</v>
+        <v>45.39</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -28613,13 +28613,13 @@
         </is>
       </c>
       <c r="M272" s="4" t="n">
-        <v>36.96</v>
+        <v>36.95</v>
       </c>
       <c r="N272" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O272" s="4" t="n">
-        <v>45.4</v>
+        <v>45.39</v>
       </c>
       <c r="P272" s="4" t="n">
         <v>0</v>
@@ -28701,13 +28701,13 @@
         </is>
       </c>
       <c r="I273" s="4" t="n">
-        <v>-7.94</v>
+        <v>-7.88</v>
       </c>
       <c r="J273" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K273" s="4" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -28715,16 +28715,16 @@
         </is>
       </c>
       <c r="M273" s="4" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="N273" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O273" s="4" t="n">
-        <v>-7.94</v>
+        <v>-7.88</v>
       </c>
       <c r="P273" s="4" t="n">
-        <v>-1.57</v>
+        <v>-1.51</v>
       </c>
       <c r="Q273" s="4" t="n">
         <v>-1.67</v>
@@ -28752,10 +28752,10 @@
         <v>0</v>
       </c>
       <c r="AB273" s="4" t="n">
-        <v>46.03</v>
+        <v>46.06</v>
       </c>
       <c r="AC273" s="4" t="n">
-        <v>53.97</v>
+        <v>53.94</v>
       </c>
       <c r="AD273" s="4" t="n">
         <v>0</v>
@@ -28803,7 +28803,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>58.91</v>
+        <v>58.9</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>100</v>
@@ -28817,13 +28817,13 @@
         </is>
       </c>
       <c r="M274" s="4" t="n">
-        <v>48.65</v>
+        <v>48.64</v>
       </c>
       <c r="N274" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O274" s="4" t="n">
-        <v>58.91</v>
+        <v>58.9</v>
       </c>
       <c r="P274" s="4" t="n">
         <v>1.88</v>
@@ -28905,13 +28905,13 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>-10.78</v>
+        <v>-10.75</v>
       </c>
       <c r="J275" s="4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="K275" s="4" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -28925,10 +28925,10 @@
         <v>5.24</v>
       </c>
       <c r="O275" s="4" t="n">
-        <v>-10.78</v>
+        <v>-10.75</v>
       </c>
       <c r="P275" s="4" t="n">
-        <v>-0.98</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="Q275" s="4" t="n">
         <v>0.13</v>
@@ -28956,10 +28956,10 @@
         <v>0</v>
       </c>
       <c r="AB275" s="4" t="n">
-        <v>44.61</v>
+        <v>44.63</v>
       </c>
       <c r="AC275" s="4" t="n">
-        <v>55.39</v>
+        <v>55.37</v>
       </c>
       <c r="AD275" s="4" t="n">
         <v>0</v>
@@ -29058,10 +29058,10 @@
         <v>0</v>
       </c>
       <c r="AB276" s="4" t="n">
-        <v>43.57</v>
+        <v>43.56</v>
       </c>
       <c r="AC276" s="4" t="n">
-        <v>56.43</v>
+        <v>56.44</v>
       </c>
       <c r="AD276" s="4" t="n">
         <v>0</v>
@@ -29109,7 +29109,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>-10.57</v>
+        <v>-10.58</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>2.8</v>
@@ -29211,7 +29211,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-16.95</v>
+        <v>-16.96</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.4</v>
@@ -29225,13 +29225,13 @@
         </is>
       </c>
       <c r="M278" s="4" t="n">
-        <v>-16.94</v>
+        <v>-16.95</v>
       </c>
       <c r="N278" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-16.95</v>
+        <v>-16.96</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.86</v>
@@ -29313,7 +29313,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>-11.49</v>
+        <v>-11.48</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>1.3</v>
@@ -29333,10 +29333,10 @@
         <v>5.24</v>
       </c>
       <c r="O279" s="4" t="n">
-        <v>-11.49</v>
+        <v>-11.48</v>
       </c>
       <c r="P279" s="4" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="Q279" s="4" t="n">
         <v>-3.02</v>
@@ -29519,7 +29519,7 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>-3.36</v>
+        <v>-3.37</v>
       </c>
       <c r="J281" s="4" t="n">
         <v>25.1</v>
@@ -29533,13 +29533,13 @@
         </is>
       </c>
       <c r="M281" s="4" t="n">
-        <v>-7.88</v>
+        <v>-7.89</v>
       </c>
       <c r="N281" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O281" s="4" t="n">
-        <v>-3.36</v>
+        <v>-3.37</v>
       </c>
       <c r="P281" s="4" t="n">
         <v>0</v>
@@ -29560,7 +29560,7 @@
         <v>3052354</v>
       </c>
       <c r="X281" s="5" t="n">
-        <v>939985</v>
+        <v>0</v>
       </c>
       <c r="Y281" t="inlineStr"/>
       <c r="Z281" s="4" t="n">
@@ -29672,10 +29672,10 @@
         <v>0</v>
       </c>
       <c r="AB282" s="4" t="n">
-        <v>79.91</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AC282" s="4" t="n">
-        <v>20.09</v>
+        <v>20.1</v>
       </c>
       <c r="AD282" s="4" t="n">
         <v>0</v>
@@ -29723,7 +29723,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-13.47</v>
+        <v>-13.48</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>0.9</v>
@@ -29737,13 +29737,13 @@
         </is>
       </c>
       <c r="M283" s="4" t="n">
-        <v>-14.6</v>
+        <v>-14.61</v>
       </c>
       <c r="N283" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O283" s="4" t="n">
-        <v>-13.01</v>
+        <v>-13.02</v>
       </c>
       <c r="P283" s="4" t="n">
         <v>-0.19</v>
@@ -29839,7 +29839,7 @@
         </is>
       </c>
       <c r="M284" s="4" t="n">
-        <v>-13.4</v>
+        <v>-13.41</v>
       </c>
       <c r="N284" s="4" t="n">
         <v>5.24</v>
@@ -29882,10 +29882,10 @@
         <v>0</v>
       </c>
       <c r="AB284" s="4" t="n">
-        <v>43.51</v>
+        <v>43.5</v>
       </c>
       <c r="AC284" s="4" t="n">
-        <v>56.49</v>
+        <v>56.5</v>
       </c>
       <c r="AD284" s="4" t="n">
         <v>0</v>
@@ -30035,13 +30035,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.26</v>
+        <v>-9.19</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30049,13 +30049,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30092,10 +30092,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.37</v>
+        <v>45.4</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.63</v>
+        <v>54.6</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30139,7 +30139,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.95</v>
+        <v>13.02</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>99</v>
@@ -30153,13 +30153,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>9.390000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.7</v>
+        <v>14.78</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30196,10 +30196,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.47</v>
+        <v>56.51</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.53</v>
+        <v>43.49</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30247,7 +30247,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.26</v>
+        <v>-52.18</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30261,13 +30261,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.42</v>
+        <v>-49.34</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.26</v>
+        <v>-52.18</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30298,10 +30298,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.87</v>
+        <v>23.91</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.13</v>
+        <v>76.09</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -30345,13 +30345,13 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
       <c r="J289" s="4" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K289" s="4" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -30365,10 +30365,10 @@
         <v>5.24</v>
       </c>
       <c r="O289" s="4" t="n">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
       <c r="P289" s="4" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="Q289" s="4" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AB289" s="4" t="n">
-        <v>52.59</v>
+        <v>52.6</v>
       </c>
       <c r="AC289" s="4" t="n">
-        <v>47.41</v>
+        <v>47.4</v>
       </c>
       <c r="AD289" s="4" t="n">
         <v>0</v>
@@ -35171,7 +35171,7 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>11.74</v>
+        <v>11.76</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>98.8</v>
@@ -35185,13 +35185,13 @@
         </is>
       </c>
       <c r="M336" s="4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="N336" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O336" s="4" t="n">
-        <v>11.74</v>
+        <v>11.76</v>
       </c>
       <c r="P336" s="4" t="n">
         <v>0.77</v>
@@ -35222,10 +35222,10 @@
         <v>0</v>
       </c>
       <c r="AB336" s="4" t="n">
-        <v>55.87</v>
+        <v>55.88</v>
       </c>
       <c r="AC336" s="4" t="n">
-        <v>44.13</v>
+        <v>44.12</v>
       </c>
       <c r="AD336" s="4" t="n">
         <v>0</v>
@@ -35273,7 +35273,7 @@
         </is>
       </c>
       <c r="I337" s="4" t="n">
-        <v>-36.21</v>
+        <v>-36.18</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>0</v>
@@ -35287,13 +35287,13 @@
         </is>
       </c>
       <c r="M337" s="4" t="n">
-        <v>-37.85</v>
+        <v>-37.82</v>
       </c>
       <c r="N337" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O337" s="4" t="n">
-        <v>-36.21</v>
+        <v>-36.18</v>
       </c>
       <c r="P337" s="4" t="n">
         <v>0</v>
@@ -35324,10 +35324,10 @@
         <v>0</v>
       </c>
       <c r="AB337" s="4" t="n">
-        <v>31.9</v>
+        <v>31.91</v>
       </c>
       <c r="AC337" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>68.09</v>
       </c>
       <c r="AD337" s="4" t="n">
         <v>0</v>
@@ -35375,7 +35375,7 @@
         </is>
       </c>
       <c r="I338" s="4" t="n">
-        <v>52.69</v>
+        <v>52.71</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>100</v>
@@ -35389,13 +35389,13 @@
         </is>
       </c>
       <c r="M338" s="4" t="n">
-        <v>45.23</v>
+        <v>45.26</v>
       </c>
       <c r="N338" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O338" s="4" t="n">
-        <v>52.69</v>
+        <v>52.71</v>
       </c>
       <c r="P338" s="4" t="n">
         <v>0</v>
@@ -35426,10 +35426,10 @@
         <v>0</v>
       </c>
       <c r="AB338" s="4" t="n">
-        <v>76.34999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="AC338" s="4" t="n">
-        <v>23.65</v>
+        <v>23.64</v>
       </c>
       <c r="AD338" s="4" t="n">
         <v>0</v>
@@ -35477,7 +35477,7 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>-38.6</v>
+        <v>-38.58</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>0</v>
@@ -35491,13 +35491,13 @@
         </is>
       </c>
       <c r="M339" s="4" t="n">
-        <v>-38.61</v>
+        <v>-38.58</v>
       </c>
       <c r="N339" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O339" s="4" t="n">
-        <v>-38.6</v>
+        <v>-38.58</v>
       </c>
       <c r="P339" s="4" t="n">
         <v>-3.15</v>
@@ -35528,10 +35528,10 @@
         <v>0</v>
       </c>
       <c r="AB339" s="4" t="n">
-        <v>30.7</v>
+        <v>30.71</v>
       </c>
       <c r="AC339" s="4" t="n">
-        <v>69.3</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="AD339" s="4" t="n">
         <v>0</v>
@@ -35579,7 +35579,7 @@
         </is>
       </c>
       <c r="I340" s="4" t="n">
-        <v>-22.4</v>
+        <v>-22.37</v>
       </c>
       <c r="J340" s="4" t="n">
         <v>0.1</v>
@@ -35593,13 +35593,13 @@
         </is>
       </c>
       <c r="M340" s="4" t="n">
-        <v>-19.29</v>
+        <v>-19.27</v>
       </c>
       <c r="N340" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O340" s="4" t="n">
-        <v>-22.4</v>
+        <v>-22.37</v>
       </c>
       <c r="P340" s="4" t="n">
         <v>-2.45</v>
@@ -35630,10 +35630,10 @@
         <v>0</v>
       </c>
       <c r="AB340" s="4" t="n">
-        <v>38.8</v>
+        <v>38.81</v>
       </c>
       <c r="AC340" s="4" t="n">
-        <v>61.2</v>
+        <v>61.19</v>
       </c>
       <c r="AD340" s="4" t="n">
         <v>0</v>
@@ -35681,7 +35681,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>-28.46</v>
+        <v>-28.44</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>0</v>
@@ -35695,13 +35695,13 @@
         </is>
       </c>
       <c r="M341" s="4" t="n">
-        <v>-29.52</v>
+        <v>-29.49</v>
       </c>
       <c r="N341" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O341" s="4" t="n">
-        <v>-28.46</v>
+        <v>-28.44</v>
       </c>
       <c r="P341" s="4" t="n">
         <v>-2.12</v>
@@ -35732,10 +35732,10 @@
         <v>0</v>
       </c>
       <c r="AB341" s="4" t="n">
-        <v>35.77</v>
+        <v>35.78</v>
       </c>
       <c r="AC341" s="4" t="n">
-        <v>64.23</v>
+        <v>64.22</v>
       </c>
       <c r="AD341" s="4" t="n">
         <v>0</v>
@@ -35797,16 +35797,16 @@
         </is>
       </c>
       <c r="M342" s="4" t="n">
-        <v>-7.04</v>
+        <v>-7.02</v>
       </c>
       <c r="N342" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O342" s="4" t="n">
-        <v>-5.18</v>
+        <v>-5.17</v>
       </c>
       <c r="P342" s="4" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="Q342" s="4" t="n">
         <v>-2</v>
@@ -35840,10 +35840,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>47.57</v>
+        <v>47.58</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>52.43</v>
+        <v>52.42</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -35891,13 +35891,13 @@
         </is>
       </c>
       <c r="I343" s="4" t="n">
-        <v>-8.710000000000001</v>
+        <v>-8.68</v>
       </c>
       <c r="J343" s="4" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="K343" s="4" t="n">
-        <v>92.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -35905,13 +35905,13 @@
         </is>
       </c>
       <c r="M343" s="4" t="n">
-        <v>-12.05</v>
+        <v>-12.02</v>
       </c>
       <c r="N343" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O343" s="4" t="n">
-        <v>-8.710000000000001</v>
+        <v>-8.68</v>
       </c>
       <c r="P343" s="4" t="n">
         <v>0</v>
@@ -35942,10 +35942,10 @@
         <v>0</v>
       </c>
       <c r="AB343" s="4" t="n">
-        <v>45.65</v>
+        <v>45.66</v>
       </c>
       <c r="AC343" s="4" t="n">
-        <v>54.35</v>
+        <v>54.34</v>
       </c>
       <c r="AD343" s="4" t="n">
         <v>0</v>
@@ -35993,13 +35993,13 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>9.32</v>
+        <v>9.34</v>
       </c>
       <c r="J344" s="4" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="K344" s="4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -36007,13 +36007,13 @@
         </is>
       </c>
       <c r="M344" s="4" t="n">
-        <v>-5.64</v>
+        <v>-5.62</v>
       </c>
       <c r="N344" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O344" s="4" t="n">
-        <v>11.15</v>
+        <v>11.17</v>
       </c>
       <c r="P344" s="4" t="n">
         <v>0.77</v>
@@ -36050,10 +36050,10 @@
         <v>0</v>
       </c>
       <c r="AB344" s="4" t="n">
-        <v>54.66</v>
+        <v>54.67</v>
       </c>
       <c r="AC344" s="4" t="n">
-        <v>45.34</v>
+        <v>45.33</v>
       </c>
       <c r="AD344" s="4" t="n">
         <v>0</v>
@@ -36101,7 +36101,7 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-9.31</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>5.9</v>
@@ -36115,13 +36115,13 @@
         </is>
       </c>
       <c r="M345" s="4" t="n">
-        <v>-3.64</v>
+        <v>-3.62</v>
       </c>
       <c r="N345" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O345" s="4" t="n">
-        <v>-9.67</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="P345" s="4" t="n">
         <v>-0.62</v>
@@ -36158,10 +36158,10 @@
         <v>0</v>
       </c>
       <c r="AB345" s="4" t="n">
-        <v>45.34</v>
+        <v>45.35</v>
       </c>
       <c r="AC345" s="4" t="n">
-        <v>54.66</v>
+        <v>54.65</v>
       </c>
       <c r="AD345" s="4" t="n">
         <v>0</v>
@@ -36209,7 +36209,7 @@
         </is>
       </c>
       <c r="I346" s="4" t="n">
-        <v>70.59</v>
+        <v>70.61</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>100</v>
@@ -36223,13 +36223,13 @@
         </is>
       </c>
       <c r="M346" s="4" t="n">
-        <v>60.41</v>
+        <v>60.43</v>
       </c>
       <c r="N346" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O346" s="4" t="n">
-        <v>70.59</v>
+        <v>70.61</v>
       </c>
       <c r="P346" s="4" t="n">
         <v>0</v>
@@ -36260,10 +36260,10 @@
         <v>0</v>
       </c>
       <c r="AB346" s="4" t="n">
-        <v>85.29000000000001</v>
+        <v>85.31</v>
       </c>
       <c r="AC346" s="4" t="n">
-        <v>14.71</v>
+        <v>14.69</v>
       </c>
       <c r="AD346" s="4" t="n">
         <v>0</v>
@@ -36311,7 +36311,7 @@
         </is>
       </c>
       <c r="I347" s="4" t="n">
-        <v>-25.78</v>
+        <v>-25.76</v>
       </c>
       <c r="J347" s="4" t="n">
         <v>0</v>
@@ -36325,13 +36325,13 @@
         </is>
       </c>
       <c r="M347" s="4" t="n">
-        <v>-26.35</v>
+        <v>-26.33</v>
       </c>
       <c r="N347" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O347" s="4" t="n">
-        <v>-25.78</v>
+        <v>-25.76</v>
       </c>
       <c r="P347" s="4" t="n">
         <v>-1.94</v>
@@ -36362,10 +36362,10 @@
         <v>0</v>
       </c>
       <c r="AB347" s="4" t="n">
-        <v>37.11</v>
+        <v>37.12</v>
       </c>
       <c r="AC347" s="4" t="n">
-        <v>62.89</v>
+        <v>62.88</v>
       </c>
       <c r="AD347" s="4" t="n">
         <v>0</v>
@@ -36413,7 +36413,7 @@
         </is>
       </c>
       <c r="I348" s="4" t="n">
-        <v>18.72</v>
+        <v>18.74</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>99.7</v>
@@ -36427,13 +36427,13 @@
         </is>
       </c>
       <c r="M348" s="4" t="n">
-        <v>7.91</v>
+        <v>7.93</v>
       </c>
       <c r="N348" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O348" s="4" t="n">
-        <v>18.72</v>
+        <v>18.74</v>
       </c>
       <c r="P348" s="4" t="n">
         <v>2.17</v>
@@ -36464,10 +36464,10 @@
         <v>0</v>
       </c>
       <c r="AB348" s="4" t="n">
-        <v>59.36</v>
+        <v>59.37</v>
       </c>
       <c r="AC348" s="4" t="n">
-        <v>40.64</v>
+        <v>40.63</v>
       </c>
       <c r="AD348" s="4" t="n">
         <v>0</v>
@@ -36515,7 +36515,7 @@
         </is>
       </c>
       <c r="I349" s="4" t="n">
-        <v>-19.92</v>
+        <v>-19.89</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>0.2</v>
@@ -36529,13 +36529,13 @@
         </is>
       </c>
       <c r="M349" s="4" t="n">
-        <v>-15.71</v>
+        <v>-15.69</v>
       </c>
       <c r="N349" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O349" s="4" t="n">
-        <v>-19.92</v>
+        <v>-19.89</v>
       </c>
       <c r="P349" s="4" t="n">
         <v>-1.93</v>
@@ -36566,10 +36566,10 @@
         <v>0</v>
       </c>
       <c r="AB349" s="4" t="n">
-        <v>40.04</v>
+        <v>40.05</v>
       </c>
       <c r="AC349" s="4" t="n">
-        <v>59.96</v>
+        <v>59.95</v>
       </c>
       <c r="AD349" s="4" t="n">
         <v>0</v>
@@ -36617,13 +36617,13 @@
         </is>
       </c>
       <c r="I350" s="4" t="n">
-        <v>-5.75</v>
+        <v>-5.72</v>
       </c>
       <c r="J350" s="4" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="K350" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -36631,13 +36631,13 @@
         </is>
       </c>
       <c r="M350" s="4" t="n">
-        <v>-5.77</v>
+        <v>-5.74</v>
       </c>
       <c r="N350" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O350" s="4" t="n">
-        <v>-5.75</v>
+        <v>-5.72</v>
       </c>
       <c r="P350" s="4" t="n">
         <v>-1.22</v>
@@ -36668,10 +36668,10 @@
         <v>0</v>
       </c>
       <c r="AB350" s="4" t="n">
-        <v>47.13</v>
+        <v>47.14</v>
       </c>
       <c r="AC350" s="4" t="n">
-        <v>52.87</v>
+        <v>52.86</v>
       </c>
       <c r="AD350" s="4" t="n">
         <v>0</v>
@@ -38559,13 +38559,13 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="J369" s="4" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="K369" s="4" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -38579,10 +38579,10 @@
         <v>5.24</v>
       </c>
       <c r="O369" s="4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P369" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q369" s="4" t="n">
         <v>-1</v>
@@ -38616,10 +38616,10 @@
         <v>0</v>
       </c>
       <c r="AB369" s="4" t="n">
-        <v>50.14</v>
+        <v>50.15</v>
       </c>
       <c r="AC369" s="4" t="n">
-        <v>49.86</v>
+        <v>49.85</v>
       </c>
       <c r="AD369" s="4" t="n">
         <v>0</v>
@@ -40103,7 +40103,7 @@
         </is>
       </c>
       <c r="I384" s="4" t="n">
-        <v>-18.17</v>
+        <v>-18.16</v>
       </c>
       <c r="J384" s="4" t="n">
         <v>0.3</v>
@@ -40123,10 +40123,10 @@
         <v>5.24</v>
       </c>
       <c r="O384" s="4" t="n">
-        <v>-18.17</v>
+        <v>-18.16</v>
       </c>
       <c r="P384" s="4" t="n">
-        <v>-2.32</v>
+        <v>-2.31</v>
       </c>
       <c r="Q384" s="4" t="n">
         <v>-1.32</v>
@@ -40141,10 +40141,10 @@
       </c>
       <c r="V384" s="4" t="n"/>
       <c r="W384" s="5" t="n">
-        <v>31787</v>
+        <v>32993</v>
       </c>
       <c r="X384" s="5" t="n">
-        <v>1598225</v>
+        <v>1595725</v>
       </c>
       <c r="Y384" t="inlineStr"/>
       <c r="Z384" s="4" t="n">
@@ -40154,10 +40154,10 @@
         <v>0</v>
       </c>
       <c r="AB384" s="4" t="n">
-        <v>40.91</v>
+        <v>40.92</v>
       </c>
       <c r="AC384" s="4" t="n">
-        <v>59.09</v>
+        <v>59.08</v>
       </c>
       <c r="AD384" s="4" t="n">
         <v>0</v>
@@ -40503,7 +40503,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-25.54</v>
+        <v>-23.3</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40517,13 +40517,13 @@
         </is>
       </c>
       <c r="M388" s="4" t="n">
-        <v>-28.56</v>
+        <v>-26.32</v>
       </c>
       <c r="N388" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-25.54</v>
+        <v>-23.3</v>
       </c>
       <c r="P388" s="4" t="n">
         <v>-1.2</v>
@@ -40554,10 +40554,10 @@
         <v>0</v>
       </c>
       <c r="AB388" s="4" t="n">
-        <v>37.23</v>
+        <v>38.35</v>
       </c>
       <c r="AC388" s="4" t="n">
-        <v>62.77</v>
+        <v>61.65</v>
       </c>
       <c r="AD388" s="4" t="n">
         <v>0</v>
@@ -40605,7 +40605,7 @@
         </is>
       </c>
       <c r="I389" s="4" t="n">
-        <v>-56</v>
+        <v>-55.98</v>
       </c>
       <c r="J389" s="4" t="n">
         <v>0</v>
@@ -40625,10 +40625,10 @@
         <v>5.24</v>
       </c>
       <c r="O389" s="4" t="n">
-        <v>-56</v>
+        <v>-55.98</v>
       </c>
       <c r="P389" s="4" t="n">
-        <v>-1.65</v>
+        <v>-1.63</v>
       </c>
       <c r="Q389" s="4" t="n">
         <v>-2.51</v>
@@ -40643,10 +40643,10 @@
       </c>
       <c r="V389" s="4" t="n"/>
       <c r="W389" s="5" t="n">
-        <v>92445</v>
+        <v>101984</v>
       </c>
       <c r="X389" s="5" t="n">
-        <v>1228936</v>
+        <v>1274194</v>
       </c>
       <c r="Y389" t="inlineStr"/>
       <c r="Z389" s="4" t="n">
@@ -40656,10 +40656,10 @@
         <v>0</v>
       </c>
       <c r="AB389" s="4" t="n">
-        <v>22</v>
+        <v>22.01</v>
       </c>
       <c r="AC389" s="4" t="n">
-        <v>78</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="AD389" s="4" t="n">
         <v>0</v>
@@ -40707,7 +40707,7 @@
         </is>
       </c>
       <c r="I390" s="4" t="n">
-        <v>-33.34</v>
+        <v>-33.32</v>
       </c>
       <c r="J390" s="4" t="n">
         <v>0</v>
@@ -40727,10 +40727,10 @@
         <v>5.24</v>
       </c>
       <c r="O390" s="4" t="n">
-        <v>-33.34</v>
+        <v>-33.32</v>
       </c>
       <c r="P390" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.28</v>
       </c>
       <c r="Q390" s="4" t="n">
         <v>-4.43</v>
@@ -40745,10 +40745,10 @@
       </c>
       <c r="V390" s="4" t="n"/>
       <c r="W390" s="5" t="n">
-        <v>363437</v>
+        <v>397584</v>
       </c>
       <c r="X390" s="5" t="n">
-        <v>2302907</v>
+        <v>2428734</v>
       </c>
       <c r="Y390" t="inlineStr"/>
       <c r="Z390" s="4" t="n">
@@ -40758,10 +40758,10 @@
         <v>0</v>
       </c>
       <c r="AB390" s="4" t="n">
-        <v>33.33</v>
+        <v>33.34</v>
       </c>
       <c r="AC390" s="4" t="n">
-        <v>66.67</v>
+        <v>66.66</v>
       </c>
       <c r="AD390" s="4" t="n">
         <v>0</v>
@@ -40809,7 +40809,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>-35.65</v>
+        <v>-35.66</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>0</v>
@@ -40829,7 +40829,7 @@
         <v>5.24</v>
       </c>
       <c r="O391" s="4" t="n">
-        <v>-35.65</v>
+        <v>-35.66</v>
       </c>
       <c r="P391" s="4" t="n">
         <v>-2.9</v>
@@ -40911,7 +40911,7 @@
         </is>
       </c>
       <c r="I392" s="4" t="n">
-        <v>-17.5</v>
+        <v>-17.46</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>0.4</v>
@@ -40931,10 +40931,10 @@
         <v>5.24</v>
       </c>
       <c r="O392" s="4" t="n">
-        <v>-17.5</v>
+        <v>-17.46</v>
       </c>
       <c r="P392" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.26</v>
       </c>
       <c r="Q392" s="4" t="n">
         <v>-0.33</v>
@@ -40949,10 +40949,10 @@
       </c>
       <c r="V392" s="4" t="n"/>
       <c r="W392" s="5" t="n">
-        <v>52227</v>
+        <v>59772</v>
       </c>
       <c r="X392" s="5" t="n">
-        <v>524813</v>
+        <v>536843</v>
       </c>
       <c r="Y392" t="inlineStr"/>
       <c r="Z392" s="4" t="n">
@@ -40962,10 +40962,10 @@
         <v>0</v>
       </c>
       <c r="AB392" s="4" t="n">
-        <v>41.25</v>
+        <v>41.27</v>
       </c>
       <c r="AC392" s="4" t="n">
-        <v>58.75</v>
+        <v>58.73</v>
       </c>
       <c r="AD392" s="4" t="n">
         <v>0</v>
@@ -41013,7 +41013,7 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-13.72</v>
+        <v>-13.76</v>
       </c>
       <c r="J393" s="4" t="n">
         <v>0.8</v>
@@ -41027,16 +41027,16 @@
         </is>
       </c>
       <c r="M393" s="4" t="n">
-        <v>-18.93</v>
+        <v>-18.94</v>
       </c>
       <c r="N393" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>-14.7</v>
+        <v>-14.74</v>
       </c>
       <c r="P393" s="4" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="Q393" s="4" t="n">
         <v>-1.53</v>
@@ -41057,10 +41057,10 @@
         <v>-9</v>
       </c>
       <c r="W393" s="5" t="n">
-        <v>2490106</v>
+        <v>2599775</v>
       </c>
       <c r="X393" s="5" t="n">
-        <v>590480</v>
+        <v>613135</v>
       </c>
       <c r="Y393" t="inlineStr"/>
       <c r="Z393" s="4" t="n">
@@ -41070,10 +41070,10 @@
         <v>0</v>
       </c>
       <c r="AB393" s="4" t="n">
-        <v>43.14</v>
+        <v>43.12</v>
       </c>
       <c r="AC393" s="4" t="n">
-        <v>56.86</v>
+        <v>56.88</v>
       </c>
       <c r="AD393" s="4" t="n">
         <v>0</v>
@@ -41117,7 +41117,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-21.1</v>
+        <v>-20.91</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>0.2</v>
@@ -41137,10 +41137,10 @@
         <v>5.24</v>
       </c>
       <c r="O394" s="4" t="n">
-        <v>-21.1</v>
+        <v>-20.91</v>
       </c>
       <c r="P394" s="4" t="n">
-        <v>-1.82</v>
+        <v>-1.63</v>
       </c>
       <c r="Q394" s="4" t="n">
         <v>0</v>
@@ -41155,10 +41155,10 @@
       </c>
       <c r="V394" s="4" t="n"/>
       <c r="W394" s="5" t="n">
-        <v>77511</v>
+        <v>86869</v>
       </c>
       <c r="X394" s="5" t="n">
-        <v>1502905</v>
+        <v>1552429</v>
       </c>
       <c r="Y394" t="inlineStr"/>
       <c r="Z394" s="4" t="n">
@@ -41168,10 +41168,10 @@
         <v>0</v>
       </c>
       <c r="AB394" s="4" t="n">
-        <v>39.45</v>
+        <v>39.55</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>60.55</v>
+        <v>60.45</v>
       </c>
       <c r="AD394" s="4" t="n">
         <v>0</v>
@@ -41219,7 +41219,7 @@
         </is>
       </c>
       <c r="I395" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.86</v>
       </c>
       <c r="J395" s="4" t="n">
         <v>0.4</v>
@@ -41239,10 +41239,10 @@
         <v>5.24</v>
       </c>
       <c r="O395" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.86</v>
       </c>
       <c r="P395" s="4" t="n">
-        <v>-0.63</v>
+        <v>-0.6</v>
       </c>
       <c r="Q395" s="4" t="n">
         <v>-1.67</v>
@@ -41257,10 +41257,10 @@
       </c>
       <c r="V395" s="4" t="n"/>
       <c r="W395" s="5" t="n">
-        <v>794111</v>
+        <v>868615</v>
       </c>
       <c r="X395" s="5" t="n">
-        <v>2262074</v>
+        <v>2300690</v>
       </c>
       <c r="Y395" t="inlineStr"/>
       <c r="Z395" s="4" t="n">
@@ -41270,10 +41270,10 @@
         <v>0</v>
       </c>
       <c r="AB395" s="4" t="n">
-        <v>41.06</v>
+        <v>41.07</v>
       </c>
       <c r="AC395" s="4" t="n">
-        <v>58.94</v>
+        <v>58.93</v>
       </c>
       <c r="AD395" s="4" t="n">
         <v>0</v>
@@ -41362,7 +41362,7 @@
         <v>0</v>
       </c>
       <c r="X396" s="5" t="n">
-        <v>2220455</v>
+        <v>2232874</v>
       </c>
       <c r="Y396" t="inlineStr"/>
       <c r="Z396" s="4" t="n">
@@ -41419,7 +41419,7 @@
         </is>
       </c>
       <c r="I397" s="4" t="n">
-        <v>-11.73</v>
+        <v>-11.74</v>
       </c>
       <c r="J397" s="4" t="n">
         <v>1.2</v>
@@ -41439,7 +41439,7 @@
         <v>5.24</v>
       </c>
       <c r="O397" s="4" t="n">
-        <v>-11.73</v>
+        <v>-11.74</v>
       </c>
       <c r="P397" s="4" t="n">
         <v>0.24</v>
@@ -41457,10 +41457,10 @@
       </c>
       <c r="V397" s="4" t="n"/>
       <c r="W397" s="5" t="n">
-        <v>2201980</v>
+        <v>2344947</v>
       </c>
       <c r="X397" s="5" t="n">
-        <v>1426525</v>
+        <v>1549482</v>
       </c>
       <c r="Y397" t="inlineStr"/>
       <c r="Z397" s="4" t="n">
@@ -42933,7 +42933,7 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>-2.18</v>
+        <v>-2.17</v>
       </c>
       <c r="J412" s="4" t="n">
         <v>29.7</v>
@@ -42953,10 +42953,10 @@
         <v>5.24</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>-1.66</v>
+        <v>-1.65</v>
       </c>
       <c r="P412" s="4" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="Q412" s="4" t="n">
         <v>-1.43</v>
@@ -43739,13 +43739,13 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-2.55</v>
+        <v>-2.48</v>
       </c>
       <c r="J420" s="4" t="n">
-        <v>28.2</v>
+        <v>28.5</v>
       </c>
       <c r="K420" s="4" t="n">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -43759,10 +43759,10 @@
         <v>5.24</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-2.12</v>
+        <v>-2.04</v>
       </c>
       <c r="P420" s="4" t="n">
-        <v>-0.91</v>
+        <v>-0.83</v>
       </c>
       <c r="Q420" s="4" t="n">
         <v>0</v>
@@ -43796,10 +43796,10 @@
         <v>0</v>
       </c>
       <c r="AB420" s="4" t="n">
-        <v>48.72</v>
+        <v>48.76</v>
       </c>
       <c r="AC420" s="4" t="n">
-        <v>51.28</v>
+        <v>51.24</v>
       </c>
       <c r="AD420" s="4" t="n">
         <v>0</v>
@@ -44661,13 +44661,13 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-8.6</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="J429" s="4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="K429" s="4" t="n">
-        <v>92.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -44681,10 +44681,10 @@
         <v>5.24</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-8.6</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="P429" s="4" t="n">
-        <v>-1.93</v>
+        <v>-1.72</v>
       </c>
       <c r="Q429" s="4" t="n">
         <v>0</v>
@@ -44699,7 +44699,7 @@
       </c>
       <c r="V429" s="4" t="n"/>
       <c r="W429" s="5" t="n">
-        <v>58931</v>
+        <v>94438</v>
       </c>
       <c r="X429" s="5" t="n">
         <v>865911</v>
@@ -44712,10 +44712,10 @@
         <v>0</v>
       </c>
       <c r="AB429" s="4" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="AC429" s="4" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="AD429" s="4" t="n">
         <v>0</v>
@@ -44861,7 +44861,7 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>8.34</v>
+        <v>8.33</v>
       </c>
       <c r="J431" s="4" t="n">
         <v>91.5</v>
@@ -44881,10 +44881,10 @@
         <v>5.24</v>
       </c>
       <c r="O431" s="4" t="n">
-        <v>11.12</v>
+        <v>11.1</v>
       </c>
       <c r="P431" s="4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="Q431" s="4" t="n">
         <v>4.39</v>
@@ -45773,13 +45773,13 @@
         </is>
       </c>
       <c r="I440" s="4" t="n">
-        <v>-3.22</v>
+        <v>-3.19</v>
       </c>
       <c r="J440" s="4" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="K440" s="4" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
@@ -45787,16 +45787,16 @@
         </is>
       </c>
       <c r="M440" s="4" t="n">
-        <v>-2.88</v>
+        <v>-2.9</v>
       </c>
       <c r="N440" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O440" s="4" t="n">
-        <v>-4.31</v>
+        <v>-4.28</v>
       </c>
       <c r="P440" s="4" t="n">
-        <v>-0.44</v>
+        <v>-0.39</v>
       </c>
       <c r="Q440" s="4" t="n">
         <v>-5.6</v>
@@ -45817,10 +45817,10 @@
         <v>1.92</v>
       </c>
       <c r="W440" s="5" t="n">
-        <v>2054507</v>
+        <v>2140930</v>
       </c>
       <c r="X440" s="5" t="n">
-        <v>4016190</v>
+        <v>4053142</v>
       </c>
       <c r="Y440" t="inlineStr"/>
       <c r="Z440" s="4" t="n">
@@ -45830,10 +45830,10 @@
         <v>0</v>
       </c>
       <c r="AB440" s="4" t="n">
-        <v>48.39</v>
+        <v>48.4</v>
       </c>
       <c r="AC440" s="4" t="n">
-        <v>51.61</v>
+        <v>51.6</v>
       </c>
       <c r="AD440" s="4" t="n">
         <v>0</v>
@@ -45895,7 +45895,7 @@
         </is>
       </c>
       <c r="M441" s="4" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="N441" s="4" t="n">
         <v>5.24</v>
@@ -45904,7 +45904,7 @@
         <v>5.84</v>
       </c>
       <c r="P441" s="4" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="Q441" s="4" t="n">
         <v>-1.67</v>
@@ -45925,10 +45925,10 @@
         <v>-3</v>
       </c>
       <c r="W441" s="5" t="n">
-        <v>4443281</v>
+        <v>4659795</v>
       </c>
       <c r="X441" s="5" t="n">
-        <v>5843429</v>
+        <v>5954338</v>
       </c>
       <c r="Y441" t="inlineStr"/>
       <c r="Z441" s="4" t="n">
@@ -45989,7 +45989,7 @@
         </is>
       </c>
       <c r="I442" s="4" t="n">
-        <v>48.98</v>
+        <v>50.9</v>
       </c>
       <c r="J442" s="4" t="n">
         <v>100</v>
@@ -46003,16 +46003,16 @@
         </is>
       </c>
       <c r="M442" s="4" t="n">
-        <v>38.96</v>
+        <v>38.95</v>
       </c>
       <c r="N442" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O442" s="4" t="n">
-        <v>48.98</v>
+        <v>50.9</v>
       </c>
       <c r="P442" s="4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q442" s="4" t="n">
         <v>4.81</v>
@@ -46027,10 +46027,10 @@
       </c>
       <c r="V442" s="4" t="n"/>
       <c r="W442" s="5" t="n">
-        <v>659665</v>
+        <v>688200</v>
       </c>
       <c r="X442" s="5" t="n">
-        <v>0</v>
+        <v>6555</v>
       </c>
       <c r="Y442" t="inlineStr"/>
       <c r="Z442" s="4" t="n">
@@ -46040,10 +46040,10 @@
         <v>0</v>
       </c>
       <c r="AB442" s="4" t="n">
-        <v>74.48999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="AC442" s="4" t="n">
-        <v>25.51</v>
+        <v>24.55</v>
       </c>
       <c r="AD442" s="4" t="n">
         <v>0</v>
@@ -46091,7 +46091,7 @@
         </is>
       </c>
       <c r="I443" s="4" t="n">
-        <v>47.33</v>
+        <v>47.31</v>
       </c>
       <c r="J443" s="4" t="n">
         <v>100</v>
@@ -46105,13 +46105,13 @@
         </is>
       </c>
       <c r="M443" s="4" t="n">
-        <v>36.85</v>
+        <v>36.83</v>
       </c>
       <c r="N443" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O443" s="4" t="n">
-        <v>47.33</v>
+        <v>47.31</v>
       </c>
       <c r="P443" s="4" t="n">
         <v>0</v>
@@ -46129,7 +46129,7 @@
       </c>
       <c r="V443" s="4" t="n"/>
       <c r="W443" s="5" t="n">
-        <v>1124945</v>
+        <v>1135225</v>
       </c>
       <c r="X443" s="5" t="n">
         <v>0</v>
@@ -46193,7 +46193,7 @@
         </is>
       </c>
       <c r="I444" s="4" t="n">
-        <v>-5.38</v>
+        <v>-5.39</v>
       </c>
       <c r="J444" s="4" t="n">
         <v>17.8</v>
@@ -46207,13 +46207,13 @@
         </is>
       </c>
       <c r="M444" s="4" t="n">
-        <v>-8.52</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="N444" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O444" s="4" t="n">
-        <v>-5.38</v>
+        <v>-5.39</v>
       </c>
       <c r="P444" s="4" t="n">
         <v>0.13</v>
@@ -46231,10 +46231,10 @@
       </c>
       <c r="V444" s="4" t="n"/>
       <c r="W444" s="5" t="n">
-        <v>2095712</v>
+        <v>2140402</v>
       </c>
       <c r="X444" s="5" t="n">
-        <v>1746971</v>
+        <v>1781840</v>
       </c>
       <c r="Y444" t="inlineStr"/>
       <c r="Z444" s="4" t="n">
@@ -46244,10 +46244,10 @@
         <v>0</v>
       </c>
       <c r="AB444" s="4" t="n">
-        <v>47.31</v>
+        <v>47.3</v>
       </c>
       <c r="AC444" s="4" t="n">
-        <v>52.69</v>
+        <v>52.7</v>
       </c>
       <c r="AD444" s="4" t="n">
         <v>0</v>
@@ -46295,7 +46295,7 @@
         </is>
       </c>
       <c r="I445" s="4" t="n">
-        <v>-20.68</v>
+        <v>-20.66</v>
       </c>
       <c r="J445" s="4" t="n">
         <v>0.2</v>
@@ -46309,16 +46309,16 @@
         </is>
       </c>
       <c r="M445" s="4" t="n">
-        <v>-21.19</v>
+        <v>-21.21</v>
       </c>
       <c r="N445" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O445" s="4" t="n">
-        <v>-20.68</v>
+        <v>-20.66</v>
       </c>
       <c r="P445" s="4" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="Q445" s="4" t="n">
         <v>-4.2</v>
@@ -46333,10 +46333,10 @@
       </c>
       <c r="V445" s="4" t="n"/>
       <c r="W445" s="5" t="n">
-        <v>1590045</v>
+        <v>1686322</v>
       </c>
       <c r="X445" s="5" t="n">
-        <v>1413562</v>
+        <v>1441436</v>
       </c>
       <c r="Y445" t="inlineStr"/>
       <c r="Z445" s="4" t="n">
@@ -46346,10 +46346,10 @@
         <v>0</v>
       </c>
       <c r="AB445" s="4" t="n">
-        <v>39.66</v>
+        <v>39.67</v>
       </c>
       <c r="AC445" s="4" t="n">
-        <v>60.34</v>
+        <v>60.33</v>
       </c>
       <c r="AD445" s="4" t="n">
         <v>0</v>
@@ -46397,7 +46397,7 @@
         </is>
       </c>
       <c r="I446" s="4" t="n">
-        <v>18.22</v>
+        <v>18.48</v>
       </c>
       <c r="J446" s="4" t="n">
         <v>99.7</v>
@@ -46411,16 +46411,16 @@
         </is>
       </c>
       <c r="M446" s="4" t="n">
-        <v>6.7</v>
+        <v>6.69</v>
       </c>
       <c r="N446" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O446" s="4" t="n">
-        <v>18.22</v>
+        <v>18.48</v>
       </c>
       <c r="P446" s="4" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="Q446" s="4" t="n">
         <v>3.73</v>
@@ -46435,10 +46435,10 @@
       </c>
       <c r="V446" s="4" t="n"/>
       <c r="W446" s="5" t="n">
-        <v>12056375</v>
+        <v>12355664</v>
       </c>
       <c r="X446" s="5" t="n">
-        <v>392454</v>
+        <v>251134</v>
       </c>
       <c r="Y446" t="inlineStr"/>
       <c r="Z446" s="4" t="n">
@@ -46448,10 +46448,10 @@
         <v>0</v>
       </c>
       <c r="AB446" s="4" t="n">
-        <v>59.11</v>
+        <v>59.24</v>
       </c>
       <c r="AC446" s="4" t="n">
-        <v>40.89</v>
+        <v>40.76</v>
       </c>
       <c r="AD446" s="4" t="n">
         <v>0</v>
@@ -46499,7 +46499,7 @@
         </is>
       </c>
       <c r="I447" s="4" t="n">
-        <v>63.78</v>
+        <v>63.56</v>
       </c>
       <c r="J447" s="4" t="n">
         <v>100</v>
@@ -46513,16 +46513,16 @@
         </is>
       </c>
       <c r="M447" s="4" t="n">
-        <v>55.44</v>
+        <v>55.42</v>
       </c>
       <c r="N447" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O447" s="4" t="n">
-        <v>63.78</v>
+        <v>63.56</v>
       </c>
       <c r="P447" s="4" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="Q447" s="4" t="n">
         <v>0.24</v>
@@ -46537,10 +46537,10 @@
       </c>
       <c r="V447" s="4" t="n"/>
       <c r="W447" s="5" t="n">
-        <v>2086520</v>
+        <v>2125761</v>
       </c>
       <c r="X447" s="5" t="n">
-        <v>3300</v>
+        <v>21917</v>
       </c>
       <c r="Y447" t="inlineStr"/>
       <c r="Z447" s="4" t="n">
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AB447" s="4" t="n">
-        <v>81.89</v>
+        <v>81.78</v>
       </c>
       <c r="AC447" s="4" t="n">
-        <v>18.11</v>
+        <v>18.22</v>
       </c>
       <c r="AD447" s="4" t="n">
         <v>0</v>
@@ -46601,7 +46601,7 @@
         </is>
       </c>
       <c r="I448" s="4" t="n">
-        <v>-40.09</v>
+        <v>-39.9</v>
       </c>
       <c r="J448" s="4" t="n">
         <v>0</v>
@@ -46615,16 +46615,16 @@
         </is>
       </c>
       <c r="M448" s="4" t="n">
-        <v>-40.85</v>
+        <v>-40.87</v>
       </c>
       <c r="N448" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O448" s="4" t="n">
-        <v>-40.09</v>
+        <v>-39.9</v>
       </c>
       <c r="P448" s="4" t="n">
-        <v>-2.18</v>
+        <v>-1.97</v>
       </c>
       <c r="Q448" s="4" t="n">
         <v>-1.45</v>
@@ -46639,7 +46639,7 @@
       </c>
       <c r="V448" s="4" t="n"/>
       <c r="W448" s="5" t="n">
-        <v>53280</v>
+        <v>85335</v>
       </c>
       <c r="X448" s="5" t="n">
         <v>1828839</v>
@@ -46652,10 +46652,10 @@
         <v>0</v>
       </c>
       <c r="AB448" s="4" t="n">
-        <v>29.95</v>
+        <v>30.05</v>
       </c>
       <c r="AC448" s="4" t="n">
-        <v>70.05</v>
+        <v>69.95</v>
       </c>
       <c r="AD448" s="4" t="n">
         <v>0</v>
@@ -46703,7 +46703,7 @@
         </is>
       </c>
       <c r="I449" s="4" t="n">
-        <v>20.17</v>
+        <v>20.58</v>
       </c>
       <c r="J449" s="4" t="n">
         <v>99.8</v>
@@ -46717,16 +46717,16 @@
         </is>
       </c>
       <c r="M449" s="4" t="n">
-        <v>13.4</v>
+        <v>13.38</v>
       </c>
       <c r="N449" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O449" s="4" t="n">
-        <v>20.17</v>
+        <v>20.58</v>
       </c>
       <c r="P449" s="4" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="Q449" s="4" t="n">
         <v>0.51</v>
@@ -46741,10 +46741,10 @@
       </c>
       <c r="V449" s="4" t="n"/>
       <c r="W449" s="5" t="n">
-        <v>1153226</v>
+        <v>1170446</v>
       </c>
       <c r="X449" s="5" t="n">
-        <v>223056</v>
+        <v>107334</v>
       </c>
       <c r="Y449" t="inlineStr"/>
       <c r="Z449" s="4" t="n">
@@ -46754,10 +46754,10 @@
         <v>0</v>
       </c>
       <c r="AB449" s="4" t="n">
-        <v>60.09</v>
+        <v>60.29</v>
       </c>
       <c r="AC449" s="4" t="n">
-        <v>39.91</v>
+        <v>39.71</v>
       </c>
       <c r="AD449" s="4" t="n">
         <v>0</v>
@@ -46805,7 +46805,7 @@
         </is>
       </c>
       <c r="I450" s="4" t="n">
-        <v>48.03</v>
+        <v>49.32</v>
       </c>
       <c r="J450" s="4" t="n">
         <v>100</v>
@@ -46819,16 +46819,16 @@
         </is>
       </c>
       <c r="M450" s="4" t="n">
-        <v>39.68</v>
+        <v>39.66</v>
       </c>
       <c r="N450" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O450" s="4" t="n">
-        <v>48.03</v>
+        <v>49.32</v>
       </c>
       <c r="P450" s="4" t="n">
-        <v>1.71</v>
+        <v>3.01</v>
       </c>
       <c r="Q450" s="4" t="n">
         <v>1.67</v>
@@ -46843,10 +46843,10 @@
       </c>
       <c r="V450" s="4" t="n"/>
       <c r="W450" s="5" t="n">
-        <v>2725747</v>
+        <v>2758961</v>
       </c>
       <c r="X450" s="5" t="n">
-        <v>268077</v>
+        <v>5637</v>
       </c>
       <c r="Y450" t="inlineStr"/>
       <c r="Z450" s="4" t="n">
@@ -46856,10 +46856,10 @@
         <v>0</v>
       </c>
       <c r="AB450" s="4" t="n">
-        <v>74.01000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="AC450" s="4" t="n">
-        <v>25.99</v>
+        <v>25.34</v>
       </c>
       <c r="AD450" s="4" t="n">
         <v>0</v>
@@ -46907,7 +46907,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>36.24</v>
+        <v>36.25</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -46927,10 +46927,10 @@
         <v>5.24</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>36.2</v>
+        <v>36.23</v>
       </c>
       <c r="P451" s="4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q451" s="4" t="n">
         <v>9.710000000000001</v>
@@ -46951,10 +46951,10 @@
         <v>36.29</v>
       </c>
       <c r="W451" s="5" t="n">
-        <v>911064</v>
+        <v>956339</v>
       </c>
       <c r="X451" s="5" t="n">
-        <v>34786</v>
+        <v>36039</v>
       </c>
       <c r="Y451" t="inlineStr"/>
       <c r="Z451" s="4" t="n">
@@ -46964,10 +46964,10 @@
         <v>0</v>
       </c>
       <c r="AB451" s="4" t="n">
-        <v>68.12</v>
+        <v>68.13</v>
       </c>
       <c r="AC451" s="4" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="AD451" s="4" t="n">
         <v>0</v>
@@ -47015,7 +47015,7 @@
         </is>
       </c>
       <c r="I452" s="4" t="n">
-        <v>35.04</v>
+        <v>38.21</v>
       </c>
       <c r="J452" s="4" t="n">
         <v>100</v>
@@ -47035,10 +47035,10 @@
         <v>5.24</v>
       </c>
       <c r="O452" s="4" t="n">
-        <v>35.04</v>
+        <v>38.21</v>
       </c>
       <c r="P452" s="4" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q452" s="4" t="n">
         <v>0.33</v>
@@ -47053,10 +47053,10 @@
       </c>
       <c r="V452" s="4" t="n"/>
       <c r="W452" s="5" t="n">
-        <v>3472358</v>
+        <v>3550452</v>
       </c>
       <c r="X452" s="5" t="n">
-        <v>0</v>
+        <v>3186</v>
       </c>
       <c r="Y452" t="inlineStr"/>
       <c r="Z452" s="4" t="n">
@@ -47066,10 +47066,10 @@
         <v>0</v>
       </c>
       <c r="AB452" s="4" t="n">
-        <v>67.52</v>
+        <v>69.11</v>
       </c>
       <c r="AC452" s="4" t="n">
-        <v>32.48</v>
+        <v>30.89</v>
       </c>
       <c r="AD452" s="4" t="n">
         <v>0</v>
@@ -47155,7 +47155,7 @@
       </c>
       <c r="V453" s="4" t="n"/>
       <c r="W453" s="5" t="n">
-        <v>1992847</v>
+        <v>2038786</v>
       </c>
       <c r="X453" s="5" t="n">
         <v>0</v>
@@ -47242,7 +47242,7 @@
         <v>9.5</v>
       </c>
       <c r="P454" s="4" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="Q454" s="4" t="n">
         <v>7.75</v>
@@ -47263,10 +47263,10 @@
         <v>-3.69</v>
       </c>
       <c r="W454" s="5" t="n">
-        <v>6183270</v>
+        <v>6292683</v>
       </c>
       <c r="X454" s="5" t="n">
-        <v>1980862</v>
+        <v>2035255</v>
       </c>
       <c r="Y454" t="inlineStr"/>
       <c r="Z454" s="4" t="n">
@@ -47323,13 +47323,13 @@
         </is>
       </c>
       <c r="I455" s="4" t="n">
-        <v>-15.36</v>
+        <v>-16.1</v>
       </c>
       <c r="J455" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K455" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="L455" t="inlineStr">
         <is>
@@ -47343,10 +47343,10 @@
         <v>5.24</v>
       </c>
       <c r="O455" s="4" t="n">
-        <v>-15.36</v>
+        <v>-16.1</v>
       </c>
       <c r="P455" s="4" t="n">
-        <v>-0.78</v>
+        <v>-1.52</v>
       </c>
       <c r="Q455" s="4" t="n">
         <v>0</v>
@@ -47361,10 +47361,10 @@
       </c>
       <c r="V455" s="4" t="n"/>
       <c r="W455" s="5" t="n">
-        <v>168109</v>
+        <v>179020</v>
       </c>
       <c r="X455" s="5" t="n">
-        <v>565896</v>
+        <v>981820</v>
       </c>
       <c r="Y455" t="inlineStr"/>
       <c r="Z455" s="4" t="n">
@@ -47374,10 +47374,10 @@
         <v>0</v>
       </c>
       <c r="AB455" s="4" t="n">
-        <v>42.32</v>
+        <v>41.95</v>
       </c>
       <c r="AC455" s="4" t="n">
-        <v>57.68</v>
+        <v>58.05</v>
       </c>
       <c r="AD455" s="4" t="n">
         <v>0</v>
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-23.24</v>
+        <v>-23.15</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47445,10 +47445,10 @@
         <v>5.24</v>
       </c>
       <c r="O456" s="4" t="n">
-        <v>-27.41</v>
+        <v>-27.3</v>
       </c>
       <c r="P456" s="4" t="n">
-        <v>-0.86</v>
+        <v>-0.75</v>
       </c>
       <c r="Q456" s="4" t="n">
         <v>-19.99</v>
@@ -47469,10 +47469,10 @@
         <v>-6</v>
       </c>
       <c r="W456" s="5" t="n">
-        <v>387475</v>
+        <v>396217</v>
       </c>
       <c r="X456" s="5" t="n">
-        <v>1709514</v>
+        <v>1738226</v>
       </c>
       <c r="Y456" t="inlineStr"/>
       <c r="Z456" s="4" t="n">
@@ -47482,10 +47482,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>38.38</v>
+        <v>38.42</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>61.62</v>
+        <v>61.58</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -47533,7 +47533,7 @@
         </is>
       </c>
       <c r="I457" s="4" t="n">
-        <v>26.39</v>
+        <v>26.35</v>
       </c>
       <c r="J457" s="4" t="n">
         <v>100</v>
@@ -47553,10 +47553,10 @@
         <v>5.24</v>
       </c>
       <c r="O457" s="4" t="n">
-        <v>26.39</v>
+        <v>26.35</v>
       </c>
       <c r="P457" s="4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q457" s="4" t="n">
         <v>0.51</v>
@@ -47571,10 +47571,10 @@
       </c>
       <c r="V457" s="4" t="n"/>
       <c r="W457" s="5" t="n">
-        <v>1175421</v>
+        <v>1195247</v>
       </c>
       <c r="X457" s="5" t="n">
-        <v>22907</v>
+        <v>27615</v>
       </c>
       <c r="Y457" t="inlineStr"/>
       <c r="Z457" s="4" t="n">
@@ -47584,10 +47584,10 @@
         <v>0</v>
       </c>
       <c r="AB457" s="4" t="n">
-        <v>63.19</v>
+        <v>63.18</v>
       </c>
       <c r="AC457" s="4" t="n">
-        <v>36.81</v>
+        <v>36.82</v>
       </c>
       <c r="AD457" s="4" t="n">
         <v>0</v>
@@ -47635,7 +47635,7 @@
         </is>
       </c>
       <c r="I458" s="4" t="n">
-        <v>79.41</v>
+        <v>82.2</v>
       </c>
       <c r="J458" s="4" t="n">
         <v>100</v>
@@ -47655,10 +47655,10 @@
         <v>5.24</v>
       </c>
       <c r="O458" s="4" t="n">
-        <v>79.41</v>
+        <v>82.2</v>
       </c>
       <c r="P458" s="4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q458" s="4" t="n">
         <v>-2.85</v>
@@ -47673,10 +47673,10 @@
       </c>
       <c r="V458" s="4" t="n"/>
       <c r="W458" s="5" t="n">
-        <v>2474297</v>
+        <v>2502816</v>
       </c>
       <c r="X458" s="5" t="n">
-        <v>0</v>
+        <v>11811</v>
       </c>
       <c r="Y458" t="inlineStr"/>
       <c r="Z458" s="4" t="n">
@@ -47686,10 +47686,10 @@
         <v>0</v>
       </c>
       <c r="AB458" s="4" t="n">
-        <v>89.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AC458" s="4" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="AD458" s="4" t="n">
         <v>0</v>
@@ -47775,10 +47775,10 @@
       </c>
       <c r="V459" s="4" t="n"/>
       <c r="W459" s="5" t="n">
-        <v>2931993</v>
+        <v>3016894</v>
       </c>
       <c r="X459" s="5" t="n">
-        <v>154590</v>
+        <v>0</v>
       </c>
       <c r="Y459" t="inlineStr"/>
       <c r="Z459" s="4" t="n">
@@ -47839,7 +47839,7 @@
         </is>
       </c>
       <c r="I460" s="4" t="n">
-        <v>49.21</v>
+        <v>51.13</v>
       </c>
       <c r="J460" s="4" t="n">
         <v>100</v>
@@ -47859,10 +47859,10 @@
         <v>5.24</v>
       </c>
       <c r="O460" s="4" t="n">
-        <v>49.21</v>
+        <v>51.13</v>
       </c>
       <c r="P460" s="4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q460" s="4" t="n">
         <v>0.47</v>
@@ -47877,10 +47877,10 @@
       </c>
       <c r="V460" s="4" t="n"/>
       <c r="W460" s="5" t="n">
-        <v>1812862</v>
+        <v>1882001</v>
       </c>
       <c r="X460" s="5" t="n">
-        <v>0</v>
+        <v>99242</v>
       </c>
       <c r="Y460" t="inlineStr"/>
       <c r="Z460" s="4" t="n">
@@ -47890,10 +47890,10 @@
         <v>0</v>
       </c>
       <c r="AB460" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>75.56</v>
       </c>
       <c r="AC460" s="4" t="n">
-        <v>25.4</v>
+        <v>24.44</v>
       </c>
       <c r="AD460" s="4" t="n">
         <v>0</v>
@@ -48043,13 +48043,13 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-4.06</v>
+        <v>-4.03</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -48063,10 +48063,10 @@
         <v>5.24</v>
       </c>
       <c r="O462" s="4" t="n">
-        <v>-4.69</v>
+        <v>-4.65</v>
       </c>
       <c r="P462" s="4" t="n">
-        <v>-1.52</v>
+        <v>-1.48</v>
       </c>
       <c r="Q462" s="4" t="n">
         <v>-4.89</v>
@@ -48087,10 +48087,10 @@
         <v>-0.5</v>
       </c>
       <c r="W462" s="5" t="n">
-        <v>653922</v>
+        <v>712984</v>
       </c>
       <c r="X462" s="5" t="n">
-        <v>5302289</v>
+        <v>5467777</v>
       </c>
       <c r="Y462" t="inlineStr"/>
       <c r="Z462" s="4" t="n">
@@ -48100,10 +48100,10 @@
         <v>0</v>
       </c>
       <c r="AB462" s="4" t="n">
-        <v>47.97</v>
+        <v>47.99</v>
       </c>
       <c r="AC462" s="4" t="n">
-        <v>52.03</v>
+        <v>52.01</v>
       </c>
       <c r="AD462" s="4" t="n">
         <v>0</v>
@@ -48151,7 +48151,7 @@
         </is>
       </c>
       <c r="I463" s="4" t="n">
-        <v>50.28</v>
+        <v>50.32</v>
       </c>
       <c r="J463" s="4" t="n">
         <v>100</v>
@@ -48171,10 +48171,10 @@
         <v>5.24</v>
       </c>
       <c r="O463" s="4" t="n">
-        <v>50.28</v>
+        <v>50.32</v>
       </c>
       <c r="P463" s="4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q463" s="4" t="n">
         <v>1.79</v>
@@ -48189,7 +48189,7 @@
       </c>
       <c r="V463" s="4" t="n"/>
       <c r="W463" s="5" t="n">
-        <v>777289</v>
+        <v>814874</v>
       </c>
       <c r="X463" s="5" t="n">
         <v>2840</v>
@@ -48202,10 +48202,10 @@
         <v>0</v>
       </c>
       <c r="AB463" s="4" t="n">
-        <v>75.14</v>
+        <v>75.16</v>
       </c>
       <c r="AC463" s="4" t="n">
-        <v>24.86</v>
+        <v>24.84</v>
       </c>
       <c r="AD463" s="4" t="n">
         <v>0</v>
@@ -48297,10 +48297,10 @@
         <v>0.9</v>
       </c>
       <c r="W464" s="5" t="n">
-        <v>8305020</v>
+        <v>8601146</v>
       </c>
       <c r="X464" s="5" t="n">
-        <v>7289146</v>
+        <v>7526052</v>
       </c>
       <c r="Y464" t="inlineStr"/>
       <c r="Z464" s="4" t="n">
@@ -48361,7 +48361,7 @@
         </is>
       </c>
       <c r="I465" s="4" t="n">
-        <v>62.48</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="J465" s="4" t="n">
         <v>100</v>
@@ -48381,10 +48381,10 @@
         <v>5.24</v>
       </c>
       <c r="O465" s="4" t="n">
-        <v>62.48</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="P465" s="4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q465" s="4" t="n">
         <v>3.43</v>
@@ -48399,10 +48399,10 @@
       </c>
       <c r="V465" s="4" t="n"/>
       <c r="W465" s="5" t="n">
-        <v>1029973</v>
+        <v>1070659</v>
       </c>
       <c r="X465" s="5" t="n">
-        <v>0</v>
+        <v>1925</v>
       </c>
       <c r="Y465" t="inlineStr"/>
       <c r="Z465" s="4" t="n">
@@ -48412,10 +48412,10 @@
         <v>0</v>
       </c>
       <c r="AB465" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AC465" s="4" t="n">
-        <v>18.76</v>
+        <v>17.6</v>
       </c>
       <c r="AD465" s="4" t="n">
         <v>0</v>
@@ -48463,7 +48463,7 @@
         </is>
       </c>
       <c r="I466" s="4" t="n">
-        <v>-24.67</v>
+        <v>-24.68</v>
       </c>
       <c r="J466" s="4" t="n">
         <v>0.1</v>
@@ -48483,10 +48483,10 @@
         <v>5.24</v>
       </c>
       <c r="O466" s="4" t="n">
-        <v>-24.67</v>
+        <v>-24.68</v>
       </c>
       <c r="P466" s="4" t="n">
-        <v>-2.3</v>
+        <v>-2.32</v>
       </c>
       <c r="Q466" s="4" t="n">
         <v>-4.66</v>
@@ -48504,7 +48504,7 @@
         <v>14612</v>
       </c>
       <c r="X466" s="5" t="n">
-        <v>1345665</v>
+        <v>1376100</v>
       </c>
       <c r="Y466" t="inlineStr"/>
       <c r="Z466" s="4" t="n">
@@ -48514,10 +48514,10 @@
         <v>0</v>
       </c>
       <c r="AB466" s="4" t="n">
-        <v>37.67</v>
+        <v>37.66</v>
       </c>
       <c r="AC466" s="4" t="n">
-        <v>62.33</v>
+        <v>62.34</v>
       </c>
       <c r="AD466" s="4" t="n">
         <v>0</v>
@@ -48565,7 +48565,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-18.71</v>
+        <v>-18.75</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.3</v>
@@ -48585,10 +48585,10 @@
         <v>5.24</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.94</v>
       </c>
       <c r="P467" s="4" t="n">
-        <v>-1.71</v>
+        <v>-1.76</v>
       </c>
       <c r="Q467" s="4" t="n">
         <v>-4.83</v>
@@ -48612,7 +48612,7 @@
         <v>44015</v>
       </c>
       <c r="X467" s="5" t="n">
-        <v>865241</v>
+        <v>929020</v>
       </c>
       <c r="Y467" t="inlineStr"/>
       <c r="Z467" s="4" t="n">
@@ -48622,10 +48622,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>40.64</v>
+        <v>40.62</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>59.36</v>
+        <v>59.38</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48669,7 +48669,7 @@
         </is>
       </c>
       <c r="I468" s="4" t="n">
-        <v>-18.68</v>
+        <v>-18.63</v>
       </c>
       <c r="J468" s="4" t="n">
         <v>0.3</v>
@@ -48689,10 +48689,10 @@
         <v>5.24</v>
       </c>
       <c r="O468" s="4" t="n">
-        <v>-18.68</v>
+        <v>-18.63</v>
       </c>
       <c r="P468" s="4" t="n">
-        <v>-1.54</v>
+        <v>-1.49</v>
       </c>
       <c r="Q468" s="4" t="n">
         <v>0</v>
@@ -48707,7 +48707,7 @@
       </c>
       <c r="V468" s="4" t="n"/>
       <c r="W468" s="5" t="n">
-        <v>392760</v>
+        <v>423041</v>
       </c>
       <c r="X468" s="5" t="n">
         <v>3403946</v>
@@ -48720,10 +48720,10 @@
         <v>0</v>
       </c>
       <c r="AB468" s="4" t="n">
-        <v>40.66</v>
+        <v>40.68</v>
       </c>
       <c r="AC468" s="4" t="n">
-        <v>59.34</v>
+        <v>59.32</v>
       </c>
       <c r="AD468" s="4" t="n">
         <v>0</v>
@@ -48771,7 +48771,7 @@
         </is>
       </c>
       <c r="I469" s="4" t="n">
-        <v>-14.31</v>
+        <v>-14.32</v>
       </c>
       <c r="J469" s="4" t="n">
         <v>0.8</v>
@@ -48791,10 +48791,10 @@
         <v>5.24</v>
       </c>
       <c r="O469" s="4" t="n">
-        <v>-14.31</v>
+        <v>-14.32</v>
       </c>
       <c r="P469" s="4" t="n">
-        <v>-1.34</v>
+        <v>-1.36</v>
       </c>
       <c r="Q469" s="4" t="n">
         <v>-1.81</v>
@@ -48809,10 +48809,10 @@
       </c>
       <c r="V469" s="4" t="n"/>
       <c r="W469" s="5" t="n">
-        <v>132784</v>
+        <v>136755</v>
       </c>
       <c r="X469" s="5" t="n">
-        <v>1044881</v>
+        <v>1090216</v>
       </c>
       <c r="Y469" t="inlineStr"/>
       <c r="Z469" s="4" t="n">
@@ -48822,10 +48822,10 @@
         <v>0</v>
       </c>
       <c r="AB469" s="4" t="n">
-        <v>42.85</v>
+        <v>42.84</v>
       </c>
       <c r="AC469" s="4" t="n">
-        <v>57.15</v>
+        <v>57.16</v>
       </c>
       <c r="AD469" s="4" t="n">
         <v>0</v>
@@ -48896,7 +48896,7 @@
         <v>-41.63</v>
       </c>
       <c r="P470" s="4" t="n">
-        <v>-1.32</v>
+        <v>-1.33</v>
       </c>
       <c r="Q470" s="4" t="n">
         <v>-0.22</v>
@@ -48924,10 +48924,10 @@
         <v>0</v>
       </c>
       <c r="AB470" s="4" t="n">
-        <v>29.19</v>
+        <v>29.18</v>
       </c>
       <c r="AC470" s="4" t="n">
-        <v>70.81</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="AD470" s="4" t="n">
         <v>0</v>
@@ -49073,7 +49073,7 @@
         </is>
       </c>
       <c r="I472" s="4" t="n">
-        <v>-42.24</v>
+        <v>-42.25</v>
       </c>
       <c r="J472" s="4" t="n">
         <v>0</v>
@@ -49093,7 +49093,7 @@
         <v>5.24</v>
       </c>
       <c r="O472" s="4" t="n">
-        <v>-42.24</v>
+        <v>-42.25</v>
       </c>
       <c r="P472" s="4" t="n">
         <v>-2.34</v>
@@ -49175,13 +49175,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.7</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>50.4</v>
+        <v>47.9</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>49.6</v>
+        <v>52.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49189,13 +49189,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.65</v>
+        <v>-10.71</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-1.99</v>
+        <v>-2.05</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -49232,10 +49232,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.41</v>
+        <v>45.39</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.59</v>
+        <v>46.61</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49387,7 +49387,7 @@
         </is>
       </c>
       <c r="I475" s="4" t="n">
-        <v>-25.81</v>
+        <v>-25.83</v>
       </c>
       <c r="J475" s="4" t="n">
         <v>0</v>
@@ -49407,10 +49407,10 @@
         <v>5.24</v>
       </c>
       <c r="O475" s="4" t="n">
-        <v>-27.01</v>
+        <v>-27.03</v>
       </c>
       <c r="P475" s="4" t="n">
-        <v>-0.84</v>
+        <v>-0.87</v>
       </c>
       <c r="Q475" s="4" t="n">
         <v>-1.67</v>
@@ -49444,10 +49444,10 @@
         <v>0</v>
       </c>
       <c r="AB475" s="4" t="n">
-        <v>37.1</v>
+        <v>37.09</v>
       </c>
       <c r="AC475" s="4" t="n">
-        <v>62.9</v>
+        <v>62.91</v>
       </c>
       <c r="AD475" s="4" t="n">
         <v>0</v>
@@ -49536,7 +49536,7 @@
         <v>8119380</v>
       </c>
       <c r="X476" s="5" t="n">
-        <v>138597</v>
+        <v>138147</v>
       </c>
       <c r="Y476" t="inlineStr"/>
       <c r="Z476" s="4" t="n">
@@ -49911,13 +49911,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-1.55</v>
+        <v>-1.6</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>67.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -49925,16 +49925,16 @@
         </is>
       </c>
       <c r="M480" s="4" t="n">
-        <v>-7.33</v>
+        <v>-7.45</v>
       </c>
       <c r="N480" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O480" s="4" t="n">
-        <v>-3.83</v>
+        <v>-3.93</v>
       </c>
       <c r="P480" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="Q480" s="4" t="n">
         <v>-0.93</v>
@@ -49968,10 +49968,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.93</v>
+        <v>47.91</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.44</v>
+        <v>49.46</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -50019,13 +50019,13 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-25.74</v>
+        <v>-26.04</v>
       </c>
       <c r="J481" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="K481" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
@@ -50063,7 +50063,7 @@
         <v>-8.84</v>
       </c>
       <c r="W481" s="5" t="n">
-        <v>8642</v>
+        <v>0</v>
       </c>
       <c r="X481" s="5" t="n">
         <v>3357516</v>
@@ -50074,16 +50074,16 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>37.13</v>
+        <v>36.98</v>
       </c>
       <c r="AA481" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AB481" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>62.87</v>
+        <v>63.02</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -50229,13 +50229,13 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-11.03</v>
+        <v>-10.96</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -50249,10 +50249,10 @@
         <v>5.24</v>
       </c>
       <c r="O483" s="4" t="n">
-        <v>-11.57</v>
+        <v>-11.49</v>
       </c>
       <c r="P483" s="4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="Q483" s="4" t="n">
         <v>-1.09</v>
@@ -50273,10 +50273,10 @@
         <v>-8</v>
       </c>
       <c r="W483" s="5" t="n">
-        <v>3678710</v>
+        <v>4169078</v>
       </c>
       <c r="X483" s="5" t="n">
-        <v>3943411</v>
+        <v>4009075</v>
       </c>
       <c r="Y483" t="inlineStr"/>
       <c r="Z483" s="4" t="n">
@@ -50286,10 +50286,10 @@
         <v>0</v>
       </c>
       <c r="AB483" s="4" t="n">
-        <v>44.48</v>
+        <v>44.52</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>55.52</v>
+        <v>55.48</v>
       </c>
       <c r="AD483" s="4" t="n">
         <v>0</v>
@@ -50795,10 +50795,10 @@
         <v>-1.23</v>
       </c>
       <c r="W488" s="5" t="n">
-        <v>12222407</v>
+        <v>14528336</v>
       </c>
       <c r="X488" s="5" t="n">
-        <v>10582463</v>
+        <v>10898177</v>
       </c>
       <c r="Y488" t="inlineStr"/>
       <c r="Z488" s="4" t="n">
@@ -50858,10 +50858,10 @@
         <v>9.76</v>
       </c>
       <c r="J489" s="4" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="K489" s="4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>5.24</v>
       </c>
       <c r="O489" s="4" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
       <c r="P489" s="4" t="n">
         <v>-0.05</v>
@@ -50899,10 +50899,10 @@
         <v>6.64</v>
       </c>
       <c r="W489" s="5" t="n">
-        <v>6044163</v>
+        <v>6516273</v>
       </c>
       <c r="X489" s="5" t="n">
-        <v>4669609</v>
+        <v>5292553</v>
       </c>
       <c r="Y489" t="inlineStr"/>
       <c r="Z489" s="4" t="n">
@@ -51071,13 +51071,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-25.43</v>
+        <v>-25.98</v>
       </c>
       <c r="J491" s="4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51091,10 +51091,10 @@
         <v>5.24</v>
       </c>
       <c r="O491" s="4" t="n">
-        <v>-9.24</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="P491" s="4" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="Q491" s="4" t="n">
         <v>0</v>
@@ -51126,16 +51126,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>13.9</v>
+        <v>13.78</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>28.51</v>
+        <v>28.29</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.93</v>
+        <v>54.27</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51179,13 +51179,13 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="J492" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="K492" s="4" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -51199,10 +51199,10 @@
         <v>5.24</v>
       </c>
       <c r="O492" s="4" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="P492" s="4" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="Q492" s="4" t="n">
         <v>1.9</v>
@@ -51236,10 +51236,10 @@
         <v>0</v>
       </c>
       <c r="AB492" s="4" t="n">
-        <v>52.1</v>
+        <v>52.09</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>46.03</v>
+        <v>46.04</v>
       </c>
       <c r="AD492" s="4" t="n">
         <v>1.87</v>
@@ -51287,13 +51287,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-4.22</v>
+        <v>-3.82</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>37.7</v>
+        <v>39.3</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>62.3</v>
+        <v>60.7</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51307,10 +51307,10 @@
         <v>5.24</v>
       </c>
       <c r="O493" s="4" t="n">
-        <v>-6.28</v>
+        <v>-6.27</v>
       </c>
       <c r="P493" s="4" t="n">
-        <v>-0.53</v>
+        <v>-0.51</v>
       </c>
       <c r="Q493" s="4" t="n">
         <v>8.630000000000001</v>
@@ -51342,16 +51342,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>47.89</v>
+        <v>48.09</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>37.7</v>
+        <v>39.3</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>52.11</v>
+        <v>51.91</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -51707,13 +51707,13 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>-0.35</v>
+        <v>-0.33</v>
       </c>
       <c r="J497" s="4" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="K497" s="4" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -51721,13 +51721,13 @@
         </is>
       </c>
       <c r="M497" s="4" t="n">
-        <v>-8.4</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="N497" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O497" s="4" t="n">
-        <v>-1.85</v>
+        <v>-1.83</v>
       </c>
       <c r="P497" s="4" t="n">
         <v>0.6</v>
@@ -51764,10 +51764,10 @@
         <v>0</v>
       </c>
       <c r="AB497" s="4" t="n">
-        <v>49.04</v>
+        <v>49.05</v>
       </c>
       <c r="AC497" s="4" t="n">
-        <v>49.39</v>
+        <v>49.38</v>
       </c>
       <c r="AD497" s="4" t="n">
         <v>1.57</v>
@@ -52208,7 +52208,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Julian Beaudion</t>
+          <t>(No Democrat)</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -52227,30 +52227,30 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-30.55</v>
+        <v>-19.33</v>
       </c>
       <c r="J502" s="4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="K502" s="4" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>Safe R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M502" s="4" t="n">
-        <v>-28.21</v>
+        <v>-22.21</v>
       </c>
       <c r="N502" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O502" s="4" t="n">
-        <v>-30.26</v>
+        <v>-23.44</v>
       </c>
       <c r="P502" s="4" t="n">
-        <v>-1.88</v>
+        <v>-1.06</v>
       </c>
       <c r="Q502" s="4" t="n">
         <v>-4.39</v>
@@ -52259,16 +52259,16 @@
         <v>-29.98</v>
       </c>
       <c r="S502" s="4" t="n">
-        <v>19.31</v>
+        <v>39.47</v>
       </c>
       <c r="T502" s="4" t="n">
-        <v>43.6</v>
+        <v>44.25</v>
       </c>
       <c r="U502" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V502" s="4" t="n">
-        <v>-27.29</v>
+        <v>-7.78</v>
       </c>
       <c r="W502" s="5" t="n">
         <v>228295</v>
@@ -52282,16 +52282,16 @@
         </is>
       </c>
       <c r="Z502" s="4" t="n">
-        <v>20.81</v>
+        <v>40.34</v>
       </c>
       <c r="AA502" s="4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AB502" s="4" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="AC502" s="4" t="n">
-        <v>51.69</v>
+        <v>59.66</v>
       </c>
       <c r="AD502" s="4" t="n">
         <v>0</v>
@@ -52339,7 +52339,7 @@
         </is>
       </c>
       <c r="I503" s="4" t="n">
-        <v>-31.6</v>
+        <v>-31.61</v>
       </c>
       <c r="J503" s="4" t="n">
         <v>0</v>
@@ -52359,7 +52359,7 @@
         <v>5.24</v>
       </c>
       <c r="O503" s="4" t="n">
-        <v>-31.6</v>
+        <v>-31.61</v>
       </c>
       <c r="P503" s="4" t="n">
         <v>-3.72</v>
@@ -52377,10 +52377,10 @@
       </c>
       <c r="V503" s="4" t="n"/>
       <c r="W503" s="5" t="n">
-        <v>1502</v>
+        <v>2257</v>
       </c>
       <c r="X503" s="5" t="n">
-        <v>7010097</v>
+        <v>7162897</v>
       </c>
       <c r="Y503" t="inlineStr"/>
       <c r="Z503" s="4" t="n">
@@ -52440,10 +52440,10 @@
         <v>1.32</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K504" s="4" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         </is>
       </c>
       <c r="I505" s="4" t="n">
-        <v>17.77</v>
+        <v>17.71</v>
       </c>
       <c r="J505" s="4" t="n">
         <v>99.59999999999999</v>
@@ -52565,10 +52565,10 @@
         <v>5.24</v>
       </c>
       <c r="O505" s="4" t="n">
-        <v>17.77</v>
+        <v>17.71</v>
       </c>
       <c r="P505" s="4" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="Q505" s="4" t="n">
         <v>3.15</v>
@@ -52583,10 +52583,10 @@
       </c>
       <c r="V505" s="4" t="n"/>
       <c r="W505" s="5" t="n">
-        <v>17651762</v>
+        <v>17889335</v>
       </c>
       <c r="X505" s="5" t="n">
-        <v>341219</v>
+        <v>376213</v>
       </c>
       <c r="Y505" t="inlineStr"/>
       <c r="Z505" s="4" t="n">
@@ -52596,10 +52596,10 @@
         <v>0</v>
       </c>
       <c r="AB505" s="4" t="n">
-        <v>58.88</v>
+        <v>58.86</v>
       </c>
       <c r="AC505" s="4" t="n">
-        <v>41.12</v>
+        <v>41.14</v>
       </c>
       <c r="AD505" s="4" t="n">
         <v>0</v>
@@ -52745,7 +52745,7 @@
         </is>
       </c>
       <c r="I507" s="4" t="n">
-        <v>-42.9</v>
+        <v>-42.94</v>
       </c>
       <c r="J507" s="4" t="n">
         <v>0</v>
@@ -52765,10 +52765,10 @@
         <v>5.24</v>
       </c>
       <c r="O507" s="4" t="n">
-        <v>-42.9</v>
+        <v>-42.94</v>
       </c>
       <c r="P507" s="4" t="n">
-        <v>-2.56</v>
+        <v>-2.6</v>
       </c>
       <c r="Q507" s="4" t="n">
         <v>0</v>
@@ -52796,10 +52796,10 @@
         <v>0</v>
       </c>
       <c r="AB507" s="4" t="n">
-        <v>28.55</v>
+        <v>28.53</v>
       </c>
       <c r="AC507" s="4" t="n">
-        <v>71.45</v>
+        <v>71.47</v>
       </c>
       <c r="AD507" s="4" t="n">
         <v>0</v>
@@ -55581,7 +55581,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="K47" t="n">
         <v>41</v>
@@ -55593,7 +55593,7 @@
         <v>53</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="K48" t="n">
         <v>19</v>
@@ -56393,7 +56393,7 @@
         </is>
       </c>
       <c r="J61" s="4" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="K61" t="n">
         <v>39</v>
@@ -57031,19 +57031,19 @@
         </is>
       </c>
       <c r="J72" s="4" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="K72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         </is>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="K73" t="n">
         <v>5</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>52.9</v>
+        <v>51.6</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>232.4</v>
       </c>
       <c r="C9" t="n">
-        <v>203</v>
+        <v>202.6</v>
       </c>
       <c r="D9" t="n">
         <v>229</v>
       </c>
       <c r="E9" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.56</v>
+        <v>-3.04</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>38</v>
+        <v>40.1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>62</v>
+        <v>59.9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.28</v>
+        <v>-2.26</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.61</v>
+        <v>-2.51</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.1</v>
@@ -4756,16 +4756,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.86</v>
+        <v>48.87</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.14</v>
+        <v>51.13</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-28.84</v>
+        <v>-28.83</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18521,13 +18521,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-43.98</v>
+        <v>-43.96</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-41.43</v>
+        <v>-41.42</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18564,10 +18564,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>35.58</v>
+        <v>35.59</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>64.42</v>
+        <v>64.41</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18615,7 +18615,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-28.07</v>
+        <v>-28.06</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0</v>
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-26.16</v>
+        <v>-26.15</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-28.07</v>
+        <v>-28.06</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -24693,7 +24693,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>31</v>
+        <v>30.54</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24791,13 +24791,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-3.77</v>
+        <v>-4.24</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>38.6</v>
+        <v>37.2</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>61.4</v>
+        <v>62.8</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -28281,13 +28281,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.86</v>
+        <v>-6.84</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28295,13 +28295,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.31</v>
+        <v>-12.28</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.17</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28338,10 +28338,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.57</v>
+        <v>46.58</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.43</v>
+        <v>53.42</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.93</v>
+        <v>-33.9</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28403,13 +28403,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.27</v>
+        <v>-31.24</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.93</v>
+        <v>-33.9</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28440,10 +28440,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.03</v>
+        <v>33.05</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.97</v>
+        <v>66.95</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -30035,13 +30035,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.19</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30049,13 +30049,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-9.640000000000001</v>
+        <v>-9.56</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30092,10 +30092,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.4</v>
+        <v>45.44</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.6</v>
+        <v>54.56</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30139,7 +30139,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>13.02</v>
+        <v>13.09</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>99</v>
@@ -30153,13 +30153,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.78</v>
+        <v>14.87</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30196,10 +30196,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.51</v>
+        <v>56.54</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.49</v>
+        <v>43.46</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30247,7 +30247,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.18</v>
+        <v>-52.1</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30261,13 +30261,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.34</v>
+        <v>-49.25</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.18</v>
+        <v>-52.1</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30298,10 +30298,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.91</v>
+        <v>23.95</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.09</v>
+        <v>76.05</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -35783,17 +35783,17 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-4.85</v>
+        <v>-1.06</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>19.7</v>
+        <v>34.1</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>80.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M342" s="4" t="n">
@@ -35815,16 +35815,16 @@
         <v>-11.15</v>
       </c>
       <c r="S342" s="4" t="n">
-        <v>43</v>
+        <v>43.63</v>
       </c>
       <c r="T342" s="4" t="n">
-        <v>44</v>
+        <v>40.85</v>
       </c>
       <c r="U342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V342" s="4" t="n">
-        <v>-4</v>
+        <v>3.55</v>
       </c>
       <c r="W342" s="5" t="n">
         <v>603156</v>
@@ -35840,10 +35840,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>47.58</v>
+        <v>49.47</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>52.42</v>
+        <v>50.53</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -40503,7 +40503,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-23.3</v>
+        <v>-23.19</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40517,13 +40517,13 @@
         </is>
       </c>
       <c r="M388" s="4" t="n">
-        <v>-26.32</v>
+        <v>-26.21</v>
       </c>
       <c r="N388" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-23.3</v>
+        <v>-23.19</v>
       </c>
       <c r="P388" s="4" t="n">
         <v>-1.2</v>
@@ -40554,10 +40554,10 @@
         <v>0</v>
       </c>
       <c r="AB388" s="4" t="n">
-        <v>38.35</v>
+        <v>38.41</v>
       </c>
       <c r="AC388" s="4" t="n">
-        <v>61.65</v>
+        <v>61.59</v>
       </c>
       <c r="AD388" s="4" t="n">
         <v>0</v>
@@ -49175,7 +49175,7 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="J473" s="4" t="n">
         <v>47.9</v>
@@ -49189,13 +49189,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.71</v>
+        <v>-10.58</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.05</v>
+        <v>-1.92</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -49232,10 +49232,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.39</v>
+        <v>45.42</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.61</v>
+        <v>46.58</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -50019,13 +50019,13 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-26.04</v>
+        <v>-25.98</v>
       </c>
       <c r="J481" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K481" s="4" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
@@ -50074,16 +50074,16 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>36.98</v>
+        <v>37.01</v>
       </c>
       <c r="AA481" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AB481" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>63.02</v>
+        <v>62.99</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -51071,13 +51071,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-25.98</v>
+        <v>-25.86</v>
       </c>
       <c r="J491" s="4" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51126,16 +51126,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>13.78</v>
+        <v>13.63</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>28.29</v>
+        <v>28.42</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>54.27</v>
+        <v>54.29</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51287,13 +51287,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-3.82</v>
+        <v>-3.41</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>39.3</v>
+        <v>38.8</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51342,16 +51342,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>48.09</v>
+        <v>48.3</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>39.3</v>
+        <v>38.8</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>51.91</v>
+        <v>51.7</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -52227,13 +52227,13 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-19.33</v>
+        <v>-18.77</v>
       </c>
       <c r="J502" s="4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K502" s="4" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -52282,16 +52282,16 @@
         </is>
       </c>
       <c r="Z502" s="4" t="n">
-        <v>40.34</v>
+        <v>40.62</v>
       </c>
       <c r="AA502" s="4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AB502" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC502" s="4" t="n">
-        <v>59.66</v>
+        <v>59.38</v>
       </c>
       <c r="AD502" s="4" t="n">
         <v>0</v>
@@ -55581,7 +55581,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="K47" t="n">
         <v>41</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="C8" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>51.6</v>
+        <v>49.3</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.4</v>
+        <v>232.1</v>
       </c>
       <c r="C9" t="n">
-        <v>202.6</v>
+        <v>202.9</v>
       </c>
       <c r="D9" t="n">
         <v>229</v>
       </c>
       <c r="E9" t="n">
-        <v>80.8</v>
+        <v>81.3</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="C10" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="D10" t="n">
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>40.5</v>
+        <v>41.9</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.04</v>
+        <v>-3.19</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40.1</v>
+        <v>40.6</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>59.9</v>
+        <v>59.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4701,27 +4701,27 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.26</v>
+        <v>-2.43</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>43.1</v>
+        <v>28.7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>56.9</v>
+        <v>71.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.51</v>
+        <v>-2.54</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.13</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.1</v>
@@ -4756,16 +4756,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.87</v>
+        <v>48.79</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>43.1</v>
+        <v>28.7</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.13</v>
+        <v>51.21</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-28.83</v>
+        <v>-28.76</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18521,13 +18521,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-43.96</v>
+        <v>-43.84</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-41.42</v>
+        <v>-41.3</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18564,10 +18564,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>35.59</v>
+        <v>35.62</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>64.41</v>
+        <v>64.38</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18615,7 +18615,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-28.06</v>
+        <v>-27.94</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0</v>
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-26.15</v>
+        <v>-26.03</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-28.06</v>
+        <v>-27.94</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -18666,10 +18666,10 @@
         <v>0</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>35.97</v>
+        <v>36.03</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>64.03</v>
+        <v>63.97</v>
       </c>
       <c r="AD174" s="4" t="n">
         <v>0</v>
@@ -24693,7 +24693,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.54</v>
+        <v>30.67</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24791,13 +24791,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.24</v>
+        <v>-4.15</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -28281,13 +28281,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.84</v>
+        <v>-6.78</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>87</v>
+        <v>86.8</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28295,13 +28295,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.28</v>
+        <v>-12.2</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.17</v>
+        <v>-8.09</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28338,10 +28338,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.58</v>
+        <v>46.61</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.42</v>
+        <v>53.39</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.9</v>
+        <v>-33.82</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28403,13 +28403,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.24</v>
+        <v>-31.16</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.9</v>
+        <v>-33.82</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28440,10 +28440,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.05</v>
+        <v>33.09</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.95</v>
+        <v>66.91</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -30035,13 +30035,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.130000000000001</v>
+        <v>-9.17</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30049,13 +30049,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-9.56</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30092,10 +30092,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.44</v>
+        <v>45.41</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.56</v>
+        <v>54.59</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30139,7 +30139,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>13.09</v>
+        <v>13.04</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>99</v>
@@ -30153,13 +30153,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>9.56</v>
+        <v>9.5</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.87</v>
+        <v>14.81</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30196,10 +30196,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.54</v>
+        <v>56.52</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.46</v>
+        <v>43.48</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30247,7 +30247,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.1</v>
+        <v>-52.16</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30261,13 +30261,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.25</v>
+        <v>-49.31</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.1</v>
+        <v>-52.16</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30298,10 +30298,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.95</v>
+        <v>23.92</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.05</v>
+        <v>76.08</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -40503,7 +40503,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-23.19</v>
+        <v>-23.25</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40517,13 +40517,13 @@
         </is>
       </c>
       <c r="M388" s="4" t="n">
-        <v>-26.21</v>
+        <v>-26.27</v>
       </c>
       <c r="N388" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-23.19</v>
+        <v>-23.25</v>
       </c>
       <c r="P388" s="4" t="n">
         <v>-1.2</v>
@@ -40554,10 +40554,10 @@
         <v>0</v>
       </c>
       <c r="AB388" s="4" t="n">
-        <v>38.41</v>
+        <v>38.38</v>
       </c>
       <c r="AC388" s="4" t="n">
-        <v>61.59</v>
+        <v>61.62</v>
       </c>
       <c r="AD388" s="4" t="n">
         <v>0</v>
@@ -49175,13 +49175,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.72</v>
+        <v>-0.75</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>47.9</v>
+        <v>47.2</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>52.1</v>
+        <v>52.8</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49189,13 +49189,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.58</v>
+        <v>-10.62</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.96</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.37</v>
@@ -49232,10 +49232,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.42</v>
+        <v>45.41</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.58</v>
+        <v>46.59</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -50019,13 +50019,13 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-25.98</v>
+        <v>-25.38</v>
       </c>
       <c r="J481" s="4" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="K481" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
@@ -50074,16 +50074,16 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>37.01</v>
+        <v>37.31</v>
       </c>
       <c r="AA481" s="4" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="AB481" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>62.99</v>
+        <v>62.69</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -51071,13 +51071,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-25.86</v>
+        <v>-25.54</v>
       </c>
       <c r="J491" s="4" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>98.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51126,16 +51126,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>13.63</v>
+        <v>14.03</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>28.42</v>
+        <v>28.38</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>54.29</v>
+        <v>53.93</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51287,17 +51287,17 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-3.41</v>
+        <v>-3.68</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>38.8</v>
+        <v>24</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>61.2</v>
+        <v>76</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M493" s="4" t="n">
@@ -51342,16 +51342,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>48.3</v>
+        <v>48.16</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>38.8</v>
+        <v>24</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>51.7</v>
+        <v>51.84</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -52227,17 +52227,17 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-18.77</v>
+        <v>-19.07</v>
       </c>
       <c r="J502" s="4" t="n">
-        <v>7</v>
+        <v>0.3</v>
       </c>
       <c r="K502" s="4" t="n">
-        <v>93</v>
+        <v>99.7</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="M502" s="4" t="n">
@@ -52282,16 +52282,16 @@
         </is>
       </c>
       <c r="Z502" s="4" t="n">
-        <v>40.62</v>
+        <v>40.47</v>
       </c>
       <c r="AA502" s="4" t="n">
-        <v>7</v>
+        <v>0.3</v>
       </c>
       <c r="AB502" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC502" s="4" t="n">
-        <v>59.38</v>
+        <v>59.53</v>
       </c>
       <c r="AD502" s="4" t="n">
         <v>0</v>
@@ -55593,7 +55593,7 @@
         <v>53</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="K48" t="n">
         <v>19</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-08-05 · evaluated at 0 days to election (actual: 90 days out)</t>
+          <t>Data as of 2026-08-06 · evaluated at 0 days to election (actual: 89 days out)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.1</v>
+        <v>231.9</v>
       </c>
       <c r="C9" t="n">
-        <v>202.9</v>
+        <v>203.1</v>
       </c>
       <c r="D9" t="n">
         <v>229</v>
       </c>
       <c r="E9" t="n">
-        <v>81.3</v>
+        <v>80.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="C10" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>41.9</v>
+        <v>33.7</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.19</v>
+        <v>-3.42</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>59.4</v>
+        <v>60.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>44.23</v>
+        <v>44.21</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>47.77</v>
+        <v>47.79</v>
       </c>
       <c r="AD2" s="4" t="n">
         <v>8</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-17.37</v>
+        <v>-17.41</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.4</v>
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>41.31</v>
+        <v>41.29</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>58.69</v>
+        <v>58.71</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.67</v>
+        <v>7.98</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1265,16 +1265,16 @@
         <v>-5.59</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>42.7</v>
+        <v>48.87</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>36.79</v>
+        <v>41.57</v>
       </c>
       <c r="U5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>6.65</v>
+        <v>7.54</v>
       </c>
       <c r="W5" s="5" t="n">
         <v>9827820</v>
@@ -1290,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>53.83</v>
+        <v>53.99</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>46.17</v>
+        <v>46.01</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>27.27</v>
+        <v>27.29</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>63.64</v>
+        <v>63.65</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>36.36</v>
+        <v>36.35</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19.09</v>
+        <v>19.11</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.7</v>
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.03</v>
+        <v>-6.11</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
         <v>5.24</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.49</v>
+        <v>-7.31</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.35</v>
+        <v>-2.16</v>
       </c>
       <c r="Q9" s="4" t="n">
         <v>-0.47</v>
@@ -1689,22 +1689,22 @@
         <v>-13.22</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>39.46</v>
+        <v>38.12</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>43.33</v>
+        <v>42.8</v>
       </c>
       <c r="U9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-4.22</v>
+        <v>-4.84</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>2814312</v>
+        <v>5531882</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>65627327</v>
+        <v>99442171</v>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" s="4" t="n">
@@ -1714,10 +1714,10 @@
         <v>0</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>46.98</v>
+        <v>46.94</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>53.02</v>
+        <v>53.06</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>51.36</v>
+        <v>51.35</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>48.64</v>
+        <v>48.65</v>
       </c>
       <c r="AD10" s="4" t="n">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.28</v>
+        <v>5.39</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>81.8</v>
+        <v>82.2</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1999,16 +1999,16 @@
         <v>-13.45</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>50.38</v>
+        <v>49.43</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>45.25</v>
+        <v>44.02</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>5.22</v>
+        <v>5.45</v>
       </c>
       <c r="W12" s="5" t="n">
         <v>19860206</v>
@@ -2024,10 +2024,10 @@
         <v>0</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>52.64</v>
+        <v>52.69</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>47.36</v>
+        <v>47.31</v>
       </c>
       <c r="AD12" s="4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>29.55</v>
+        <v>29.57</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>64.77</v>
+        <v>64.78</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>35.23</v>
+        <v>35.22</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12.31</v>
+        <v>12.3</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.58</v>
+        <v>10.6</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>97.2</v>
@@ -2760,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>55.29</v>
+        <v>55.3</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>44.71</v>
+        <v>44.7</v>
       </c>
       <c r="AD19" s="4" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.65</v>
+        <v>12.76</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>99</v>
@@ -2827,10 +2827,10 @@
         <v>5.24</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>10.66</v>
+        <v>10.82</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>-0.12</v>
@@ -2851,10 +2851,10 @@
         <v>18.17</v>
       </c>
       <c r="W20" s="5" t="n">
-        <v>7053950</v>
+        <v>9312380</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>1001473</v>
+        <v>1078103</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" s="4" t="n">
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>56.33</v>
+        <v>56.38</v>
       </c>
       <c r="AC20" s="4" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="AD20" s="4" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.7</v>
+        <v>-10.71</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>2.5</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>44.65</v>
+        <v>44.64</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>55.35</v>
+        <v>55.36</v>
       </c>
       <c r="AD22" s="4" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.16</v>
+        <v>7.2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>53.58</v>
+        <v>53.6</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>46.42</v>
+        <v>46.4</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>0</v>
@@ -3239,17 +3239,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.83</v>
+        <v>-0.18</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>69</v>
+        <v>37.6</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>31</v>
+        <v>62.4</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Lean D</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M24" s="4" t="n">
@@ -3271,16 +3271,16 @@
         <v>-3.15</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>44.91</v>
+        <v>43.14</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>46.76</v>
+        <v>49.05</v>
       </c>
       <c r="U24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-3.12</v>
+        <v>-4.94</v>
       </c>
       <c r="W24" s="5" t="n">
         <v>4285307</v>
@@ -3296,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>50.91</v>
+        <v>49.91</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>49.09</v>
+        <v>50.09</v>
       </c>
       <c r="AD24" s="4" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.06</v>
+        <v>14.05</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>99.2</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.62</v>
+        <v>4.63</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>79.5</v>
@@ -3714,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>52.31</v>
+        <v>52.32</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>47.69</v>
+        <v>47.68</v>
       </c>
       <c r="AD28" s="4" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.78</v>
+        <v>19.79</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.8</v>
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-10.55</v>
+        <v>-10.54</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>2.9</v>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.13</v>
+        <v>-7.15</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>46.44</v>
+        <v>46.43</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>53.56</v>
+        <v>53.57</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-19.46</v>
+        <v>-19.54</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.3</v>
@@ -4448,10 +4448,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>40.27</v>
+        <v>40.23</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>59.73</v>
+        <v>59.77</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>0</v>
@@ -4495,13 +4495,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>51.01</v>
+        <v>51.02</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>48.99</v>
+        <v>48.98</v>
       </c>
       <c r="AD36" s="4" t="n">
         <v>0</v>
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.43</v>
+        <v>-2.48</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>71.3</v>
+        <v>71.5</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4715,16 +4715,16 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.54</v>
+        <v>-2.6</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O38" s="4" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="P38" s="4" t="n">
         <v>-1.13</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>-1.1</v>
       </c>
       <c r="Q38" s="4" t="n">
         <v>-1.67</v>
@@ -4756,16 +4756,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.79</v>
+        <v>48.76</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.21</v>
+        <v>51.24</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-27.1</v>
+        <v>-27.12</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
@@ -4823,13 +4823,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-30.04</v>
+        <v>-30.06</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-27.1</v>
+        <v>-27.12</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>-1.74</v>
@@ -4860,10 +4860,10 @@
         <v>0</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>36.45</v>
+        <v>36.44</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>63.55</v>
+        <v>63.56</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>0</v>
@@ -4925,13 +4925,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-8.25</v>
+        <v>-8.27</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-1.25</v>
+        <v>-1.27</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>-0.44</v>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-40.07</v>
+        <v>-40.09</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -5033,13 +5033,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-40.8</v>
+        <v>-40.82</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-40.07</v>
+        <v>-40.09</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>-2.23</v>
@@ -5070,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>29.97</v>
+        <v>29.96</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>70.03</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="AD41" s="4" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-60.25</v>
+        <v>-60.27</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-61.05</v>
+        <v>-61.07</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-60.25</v>
+        <v>-60.27</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>-2.1</v>
@@ -5172,10 +5172,10 @@
         <v>0</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>19.88</v>
+        <v>19.87</v>
       </c>
       <c r="AC42" s="4" t="n">
-        <v>80.12</v>
+        <v>80.13</v>
       </c>
       <c r="AD42" s="4" t="n">
         <v>0</v>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-22.17</v>
+        <v>-22.19</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0.1</v>
@@ -5237,13 +5237,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-24.6</v>
+        <v>-24.62</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-22.17</v>
+        <v>-22.19</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>-0.59</v>
@@ -5274,10 +5274,10 @@
         <v>0</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>38.91</v>
+        <v>38.9</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>61.09</v>
+        <v>61.1</v>
       </c>
       <c r="AD43" s="4" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-28.28</v>
+        <v>-28.3</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-30.12</v>
+        <v>-30.14</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-28.28</v>
+        <v>-28.3</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>-2.14</v>
@@ -5376,10 +5376,10 @@
         <v>0</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>35.86</v>
+        <v>35.85</v>
       </c>
       <c r="AC44" s="4" t="n">
-        <v>64.14</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="AD44" s="4" t="n">
         <v>0</v>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>33.55</v>
+        <v>33.53</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>100</v>
@@ -5441,13 +5441,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>24.12</v>
+        <v>24.1</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>33.55</v>
+        <v>33.53</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>0</v>
@@ -5478,10 +5478,10 @@
         <v>0</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>66.78</v>
+        <v>66.77</v>
       </c>
       <c r="AC45" s="4" t="n">
-        <v>33.22</v>
+        <v>33.23</v>
       </c>
       <c r="AD45" s="4" t="n">
         <v>0</v>
@@ -5933,13 +5933,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>4.79</v>
+        <v>4.86</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>-0.5</v>
@@ -5990,10 +5990,10 @@
         <v>0</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>51.41</v>
+        <v>51.44</v>
       </c>
       <c r="AC50" s="4" t="n">
-        <v>46.71</v>
+        <v>46.68</v>
       </c>
       <c r="AD50" s="4" t="n">
         <v>1.88</v>
@@ -6041,13 +6041,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>37</v>
+        <v>37.4</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>-10.08</v>
+        <v>-10</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="P51" s="4" t="n">
         <v>-0.6899999999999999</v>
@@ -6098,10 +6098,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>49.84</v>
+        <v>49.89</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>50.16</v>
+        <v>50.11</v>
       </c>
       <c r="AD51" s="4" t="n">
         <v>0</v>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>60.56</v>
+        <v>60.64</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>100</v>
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>46.76</v>
+        <v>46.84</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>60.56</v>
+        <v>60.64</v>
       </c>
       <c r="P52" s="4" t="n">
         <v>0</v>
@@ -6200,10 +6200,10 @@
         <v>0</v>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>80.28</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="AC52" s="4" t="n">
-        <v>19.72</v>
+        <v>19.68</v>
       </c>
       <c r="AD52" s="4" t="n">
         <v>0</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>20.06</v>
+        <v>20.14</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>99.8</v>
@@ -6265,13 +6265,13 @@
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>10.6</v>
+        <v>10.68</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>20.06</v>
+        <v>20.14</v>
       </c>
       <c r="P53" s="4" t="n">
         <v>0.99</v>
@@ -6302,10 +6302,10 @@
         <v>0</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>60.03</v>
+        <v>60.07</v>
       </c>
       <c r="AC53" s="4" t="n">
-        <v>39.97</v>
+        <v>39.93</v>
       </c>
       <c r="AD53" s="4" t="n">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>-13.01</v>
+        <v>-12.93</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>1</v>
@@ -6363,13 +6363,13 @@
         </is>
       </c>
       <c r="M54" s="4" t="n">
-        <v>-16.3</v>
+        <v>-16.22</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>-13.01</v>
+        <v>-12.93</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>-1.75</v>
@@ -6400,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>43.5</v>
+        <v>43.53</v>
       </c>
       <c r="AC54" s="4" t="n">
-        <v>56.5</v>
+        <v>56.47</v>
       </c>
       <c r="AD54" s="4" t="n">
         <v>0</v>
@@ -6451,13 +6451,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>4.96</v>
+        <v>5.02</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="M55" s="4" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>6.08</v>
+        <v>6.16</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0.13</v>
@@ -6508,10 +6508,10 @@
         <v>0</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>51.37</v>
+        <v>51.4</v>
       </c>
       <c r="AC55" s="4" t="n">
-        <v>46.51</v>
+        <v>46.48</v>
       </c>
       <c r="AD55" s="4" t="n">
         <v>2.12</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>39.48</v>
+        <v>39.56</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>100</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>28.8</v>
+        <v>28.88</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>39.48</v>
+        <v>39.56</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>1.53</v>
@@ -6610,10 +6610,10 @@
         <v>0</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>69.73999999999999</v>
+        <v>69.78</v>
       </c>
       <c r="AC56" s="4" t="n">
-        <v>30.26</v>
+        <v>30.22</v>
       </c>
       <c r="AD56" s="4" t="n">
         <v>0</v>
@@ -6661,27 +6661,27 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>-9.73</v>
+        <v>-9.66</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Safe R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>-12.79</v>
+        <v>-12.72</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>-9.73</v>
+        <v>-9.66</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>-1.18</v>
@@ -6712,10 +6712,10 @@
         <v>0</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>45.13</v>
+        <v>45.17</v>
       </c>
       <c r="AC57" s="4" t="n">
-        <v>54.87</v>
+        <v>54.83</v>
       </c>
       <c r="AD57" s="4" t="n">
         <v>0</v>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>-22.86</v>
+        <v>-22.79</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>0.1</v>
@@ -6777,13 +6777,13 @@
         </is>
       </c>
       <c r="M58" s="4" t="n">
-        <v>-26.92</v>
+        <v>-26.84</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>-22.86</v>
+        <v>-22.79</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>-0.33</v>
@@ -6814,10 +6814,10 @@
         <v>0</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>38.57</v>
+        <v>38.61</v>
       </c>
       <c r="AC58" s="4" t="n">
-        <v>61.43</v>
+        <v>61.39</v>
       </c>
       <c r="AD58" s="4" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19.47</v>
+        <v>19.48</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>99.7</v>
@@ -6879,13 +6879,13 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>15.57</v>
+        <v>15.58</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>19.47</v>
+        <v>19.48</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0.21</v>
@@ -6916,10 +6916,10 @@
         <v>0</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>59.73</v>
+        <v>59.74</v>
       </c>
       <c r="AC59" s="4" t="n">
-        <v>40.27</v>
+        <v>40.26</v>
       </c>
       <c r="AD59" s="4" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>33.54</v>
+        <v>33.55</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>100</v>
@@ -6981,13 +6981,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.95</v>
+        <v>27.96</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33.54</v>
+        <v>33.55</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>66.77</v>
+        <v>66.78</v>
       </c>
       <c r="AC60" s="4" t="n">
-        <v>33.23</v>
+        <v>33.22</v>
       </c>
       <c r="AD60" s="4" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>21.35</v>
+        <v>21.36</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>99.8</v>
@@ -7089,7 +7089,7 @@
         <v>5.24</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>21.35</v>
+        <v>21.36</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>1.08</v>
@@ -7185,13 +7185,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>18.4</v>
+        <v>18.41</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>26.77</v>
+        <v>26.78</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>-18.01</v>
+        <v>-18</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0.4</v>
@@ -7287,13 +7287,13 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-18.11</v>
+        <v>-18.1</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>-18.01</v>
+        <v>-18</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>-0.65</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12.62</v>
+        <v>12.63</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>99</v>
@@ -7389,13 +7389,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>11.37</v>
+        <v>11.38</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12.62</v>
+        <v>12.63</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>-0.35</v>
@@ -7491,13 +7491,13 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>16.76</v>
+        <v>16.77</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>25.64</v>
+        <v>25.65</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>100</v>
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>39.3</v>
+        <v>39.31</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>1.66</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>30.93</v>
+        <v>30.94</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>100</v>
@@ -7701,7 +7701,7 @@
         <v>5.24</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>30.93</v>
+        <v>30.94</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>2.78</v>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>43.1</v>
+        <v>43.11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>100</v>
@@ -7803,7 +7803,7 @@
         <v>5.24</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>43.1</v>
+        <v>43.11</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
@@ -7834,10 +7834,10 @@
         <v>0</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>71.55</v>
+        <v>71.56</v>
       </c>
       <c r="AC68" s="4" t="n">
-        <v>28.45</v>
+        <v>28.44</v>
       </c>
       <c r="AD68" s="4" t="n">
         <v>0</v>
@@ -7895,13 +7895,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>74.16</v>
+        <v>74.17</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>79.09</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>80.91</v>
+        <v>80.92</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>5.24</v>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>99.90000000000001</v>
@@ -8105,7 +8105,7 @@
         <v>5.24</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0.46</v>
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>40.83</v>
+        <v>40.84</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>46.19</v>
+        <v>46.2</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="V72" s="4" t="n"/>
       <c r="W72" s="5" t="n">
-        <v>575282</v>
+        <v>631749</v>
       </c>
       <c r="X72" s="5" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>53.93</v>
+        <v>53.94</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>5.24</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>59.85</v>
+        <v>59.86</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>100</v>
@@ -8401,13 +8401,13 @@
         </is>
       </c>
       <c r="M74" s="4" t="n">
-        <v>53.04</v>
+        <v>53.05</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>59.85</v>
+        <v>59.86</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -8438,10 +8438,10 @@
         <v>0</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>79.92</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="AC74" s="4" t="n">
-        <v>20.08</v>
+        <v>20.07</v>
       </c>
       <c r="AD74" s="4" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>100</v>
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>45.28</v>
+        <v>45.29</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>3.69</v>
@@ -8540,10 +8540,10 @@
         <v>0</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>74.61</v>
       </c>
       <c r="AC75" s="4" t="n">
-        <v>25.4</v>
+        <v>25.39</v>
       </c>
       <c r="AD75" s="4" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>44.14</v>
+        <v>44.15</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>100</v>
@@ -8605,13 +8605,13 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>35.21</v>
+        <v>35.22</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>44.14</v>
+        <v>44.15</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>2.1</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>49.5</v>
+        <v>49.51</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>100</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.77</v>
+        <v>38.78</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>50.41</v>
+        <v>50.42</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>2.46</v>
@@ -8744,10 +8744,10 @@
         <v>0</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>72.01000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="AC77" s="4" t="n">
-        <v>24.33</v>
+        <v>24.32</v>
       </c>
       <c r="AD77" s="4" t="n">
         <v>3.66</v>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-28.4</v>
+        <v>-28.39</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -8809,13 +8809,13 @@
         </is>
       </c>
       <c r="M78" s="4" t="n">
-        <v>-30.2</v>
+        <v>-30.19</v>
       </c>
       <c r="N78" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-28.4</v>
+        <v>-28.39</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.51</v>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.91</v>
+        <v>11.92</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>5.24</v>
@@ -8948,10 +8948,10 @@
         <v>0</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>60.55</v>
+        <v>60.56</v>
       </c>
       <c r="AC79" s="4" t="n">
-        <v>39.45</v>
+        <v>39.44</v>
       </c>
       <c r="AD79" s="4" t="n">
         <v>0</v>
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.76</v>
+        <v>5.77</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>83.5</v>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="M80" s="4" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>5.24</v>
@@ -9056,10 +9056,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>52.88</v>
+        <v>52.89</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47.12</v>
+        <v>47.11</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-16.61</v>
+        <v>-16.6</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>5.24</v>
@@ -9158,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>41.91</v>
+        <v>41.92</v>
       </c>
       <c r="AC81" s="4" t="n">
-        <v>58.09</v>
+        <v>58.08</v>
       </c>
       <c r="AD81" s="4" t="n">
         <v>0</v>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="M82" s="4" t="n">
-        <v>28.32</v>
+        <v>28.33</v>
       </c>
       <c r="N82" s="4" t="n">
         <v>5.24</v>
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>26.02</v>
+        <v>26.03</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>100</v>
@@ -9429,7 +9429,7 @@
         <v>5.24</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>26.02</v>
+        <v>26.03</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.63</v>
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>27.03</v>
+        <v>27.04</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>100</v>
@@ -9531,7 +9531,7 @@
         <v>5.24</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>27.03</v>
+        <v>27.04</v>
       </c>
       <c r="P85" s="4" t="n">
         <v>1.74</v>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>63.51</v>
+        <v>63.52</v>
       </c>
       <c r="AC85" s="4" t="n">
-        <v>36.49</v>
+        <v>36.48</v>
       </c>
       <c r="AD85" s="4" t="n">
         <v>0</v>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>39.98</v>
+        <v>39.99</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9627,13 +9627,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.91</v>
+        <v>29.92</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>39.98</v>
+        <v>39.99</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.23</v>
@@ -9729,13 +9729,13 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.47</v>
+        <v>41.48</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>53.55</v>
+        <v>53.56</v>
       </c>
       <c r="P87" s="4" t="n">
         <v>0</v>
@@ -9817,7 +9817,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>100</v>
@@ -9831,13 +9831,13 @@
         </is>
       </c>
       <c r="M88" s="4" t="n">
-        <v>44.92</v>
+        <v>44.93</v>
       </c>
       <c r="N88" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="P88" s="4" t="n">
         <v>1.57</v>
@@ -9868,10 +9868,10 @@
         <v>0</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>75.94</v>
+        <v>75.95</v>
       </c>
       <c r="AC88" s="4" t="n">
-        <v>24.06</v>
+        <v>24.05</v>
       </c>
       <c r="AD88" s="4" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>99.5</v>
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>18.01</v>
+        <v>18.02</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="P89" s="4" t="n">
         <v>1.31</v>
@@ -10035,7 +10035,7 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>30.03</v>
+        <v>30.04</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>5.24</v>
@@ -10123,7 +10123,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28.57</v>
+        <v>28.58</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>100</v>
@@ -10137,13 +10137,13 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>16.38</v>
+        <v>16.39</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28.57</v>
+        <v>28.58</v>
       </c>
       <c r="P91" s="4" t="n">
         <v>0</v>
@@ -10239,13 +10239,13 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.94</v>
+        <v>58.95</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>67.98999999999999</v>
+        <v>68</v>
       </c>
       <c r="P92" s="4" t="n">
         <v>0</v>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26.48</v>
+        <v>26.49</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>100</v>
@@ -10347,7 +10347,7 @@
         <v>5.24</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>26.48</v>
+        <v>26.49</v>
       </c>
       <c r="P93" s="4" t="n">
         <v>2.03</v>
@@ -10429,7 +10429,7 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>51.26</v>
+        <v>51.27</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>100</v>
@@ -10443,13 +10443,13 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.53</v>
+        <v>43.54</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>51.26</v>
+        <v>51.27</v>
       </c>
       <c r="P94" s="4" t="n">
         <v>2.66</v>
@@ -10480,10 +10480,10 @@
         <v>0</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>75.63</v>
+        <v>75.64</v>
       </c>
       <c r="AC94" s="4" t="n">
-        <v>24.37</v>
+        <v>24.36</v>
       </c>
       <c r="AD94" s="4" t="n">
         <v>0</v>
@@ -10551,7 +10551,7 @@
         <v>5.24</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>76.75</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -10629,7 +10629,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>26.2</v>
+        <v>26.21</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>100</v>
@@ -10643,13 +10643,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="n">
-        <v>19.09</v>
+        <v>19.1</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>26.2</v>
+        <v>26.21</v>
       </c>
       <c r="P96" s="4" t="n">
         <v>0</v>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="M97" s="4" t="n">
-        <v>16.11</v>
+        <v>16.12</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>5.24</v>
@@ -10782,10 +10782,10 @@
         <v>0</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>62.75</v>
+        <v>62.76</v>
       </c>
       <c r="AC97" s="4" t="n">
-        <v>37.25</v>
+        <v>37.24</v>
       </c>
       <c r="AD97" s="4" t="n">
         <v>0</v>
@@ -10847,13 +10847,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="n">
-        <v>-10.11</v>
+        <v>-10.1</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>-4.51</v>
+        <v>-4.5</v>
       </c>
       <c r="P98" s="4" t="n">
         <v>0</v>
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>31.33</v>
+        <v>31.34</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -10949,13 +10949,13 @@
         </is>
       </c>
       <c r="M99" s="4" t="n">
-        <v>19.65</v>
+        <v>19.66</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>31.33</v>
+        <v>31.34</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.64</v>
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26.43</v>
+        <v>26.44</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>100</v>
@@ -11051,13 +11051,13 @@
         </is>
       </c>
       <c r="M100" s="4" t="n">
-        <v>16.89</v>
+        <v>16.9</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>26.43</v>
+        <v>26.44</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1.69</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>63.65</v>
+        <v>63.66</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>100</v>
@@ -11153,13 +11153,13 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>56.86</v>
+        <v>56.87</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>63.65</v>
+        <v>63.66</v>
       </c>
       <c r="P101" s="4" t="n">
         <v>0</v>
@@ -11190,10 +11190,10 @@
         <v>0</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>81.81999999999999</v>
+        <v>81.83</v>
       </c>
       <c r="AC101" s="4" t="n">
-        <v>18.18</v>
+        <v>18.17</v>
       </c>
       <c r="AD101" s="4" t="n">
         <v>0</v>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>59.08</v>
+        <v>59.09</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11255,13 +11255,13 @@
         </is>
       </c>
       <c r="M102" s="4" t="n">
-        <v>43.62</v>
+        <v>43.63</v>
       </c>
       <c r="N102" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>59.08</v>
+        <v>59.09</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>1.93</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20.46</v>
+        <v>20.47</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>99.8</v>
@@ -11357,13 +11357,13 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>8.33</v>
+        <v>8.34</v>
       </c>
       <c r="N103" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>20.46</v>
+        <v>20.47</v>
       </c>
       <c r="P103" s="4" t="n">
         <v>1.39</v>
@@ -11394,10 +11394,10 @@
         <v>0</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>60.23</v>
+        <v>60.24</v>
       </c>
       <c r="AC103" s="4" t="n">
-        <v>39.77</v>
+        <v>39.76</v>
       </c>
       <c r="AD103" s="4" t="n">
         <v>0</v>
@@ -11445,7 +11445,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>39.58</v>
+        <v>39.59</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
@@ -11459,13 +11459,13 @@
         </is>
       </c>
       <c r="M104" s="4" t="n">
-        <v>22.08</v>
+        <v>22.09</v>
       </c>
       <c r="N104" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>39.58</v>
+        <v>39.59</v>
       </c>
       <c r="P104" s="4" t="n">
         <v>1.73</v>
@@ -11496,10 +11496,10 @@
         <v>0</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>69.79000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="AC104" s="4" t="n">
-        <v>30.21</v>
+        <v>30.2</v>
       </c>
       <c r="AD104" s="4" t="n">
         <v>0</v>
@@ -11567,7 +11567,7 @@
         <v>5.24</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>22.67</v>
+        <v>22.68</v>
       </c>
       <c r="P105" s="4" t="n">
         <v>1.61</v>
@@ -11645,13 +11645,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6.75</v>
+        <v>6.84</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>86.7</v>
+        <v>87</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -11659,13 +11659,13 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>11.93</v>
+        <v>11.94</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>0.13</v>
@@ -11702,10 +11702,10 @@
         <v>0</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>53.38</v>
+        <v>53.42</v>
       </c>
       <c r="AC106" s="4" t="n">
-        <v>46.62</v>
+        <v>46.58</v>
       </c>
       <c r="AD106" s="4" t="n">
         <v>0</v>
@@ -11767,7 +11767,7 @@
         </is>
       </c>
       <c r="M107" s="4" t="n">
-        <v>14.62</v>
+        <v>14.63</v>
       </c>
       <c r="N107" s="4" t="n">
         <v>5.24</v>
@@ -11804,10 +11804,10 @@
         <v>0</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>61.06</v>
+        <v>61.07</v>
       </c>
       <c r="AC107" s="4" t="n">
-        <v>38.94</v>
+        <v>38.93</v>
       </c>
       <c r="AD107" s="4" t="n">
         <v>0</v>
@@ -11855,7 +11855,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>26.4</v>
+        <v>26.41</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>100</v>
@@ -11869,13 +11869,13 @@
         </is>
       </c>
       <c r="M108" s="4" t="n">
-        <v>20.86</v>
+        <v>20.87</v>
       </c>
       <c r="N108" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>26.4</v>
+        <v>26.41</v>
       </c>
       <c r="P108" s="4" t="n">
         <v>0</v>
@@ -11906,10 +11906,10 @@
         <v>0</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>63.2</v>
+        <v>63.21</v>
       </c>
       <c r="AC108" s="4" t="n">
-        <v>36.8</v>
+        <v>36.79</v>
       </c>
       <c r="AD108" s="4" t="n">
         <v>0</v>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27.63</v>
+        <v>27.64</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -11971,13 +11971,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.51</v>
+        <v>21.52</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>27.63</v>
+        <v>27.64</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12059,7 +12059,7 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>39.88</v>
+        <v>39.89</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>100</v>
@@ -12079,7 +12079,7 @@
         <v>5.24</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>39.88</v>
+        <v>39.89</v>
       </c>
       <c r="P110" s="4" t="n">
         <v>1.58</v>
@@ -12110,10 +12110,10 @@
         <v>0</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>69.94</v>
+        <v>69.95</v>
       </c>
       <c r="AC110" s="4" t="n">
-        <v>30.06</v>
+        <v>30.05</v>
       </c>
       <c r="AD110" s="4" t="n">
         <v>0</v>
@@ -12361,13 +12361,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>-2.55</v>
+        <v>-2.54</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -12418,10 +12418,10 @@
         <v>0</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>48.72</v>
+        <v>48.73</v>
       </c>
       <c r="AC113" s="4" t="n">
-        <v>51.28</v>
+        <v>51.27</v>
       </c>
       <c r="AD113" s="4" t="n">
         <v>0</v>
@@ -12571,13 +12571,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>-6.19</v>
+        <v>-6.2</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -12628,10 +12628,10 @@
         <v>0</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>46.91</v>
+        <v>46.9</v>
       </c>
       <c r="AC115" s="4" t="n">
-        <v>53.09</v>
+        <v>53.1</v>
       </c>
       <c r="AD115" s="4" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
         </is>
       </c>
       <c r="M119" s="4" t="n">
-        <v>25.52</v>
+        <v>25.53</v>
       </c>
       <c r="N119" s="4" t="n">
         <v>5.24</v>
@@ -13036,10 +13036,10 @@
         <v>0</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>68.33</v>
+        <v>68.34</v>
       </c>
       <c r="AC119" s="4" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="AD119" s="4" t="n">
         <v>0</v>
@@ -13087,7 +13087,7 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>27.64</v>
+        <v>27.65</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>100</v>
@@ -13107,7 +13107,7 @@
         <v>5.24</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>27.64</v>
+        <v>27.65</v>
       </c>
       <c r="P120" s="4" t="n">
         <v>1.43</v>
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="M121" s="4" t="n">
-        <v>16.59</v>
+        <v>16.6</v>
       </c>
       <c r="N121" s="4" t="n">
         <v>5.24</v>
@@ -13240,10 +13240,10 @@
         <v>0</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>64.34</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="AC121" s="4" t="n">
-        <v>35.66</v>
+        <v>35.65</v>
       </c>
       <c r="AD121" s="4" t="n">
         <v>0</v>
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="M122" s="4" t="n">
-        <v>26.5</v>
+        <v>26.51</v>
       </c>
       <c r="N122" s="4" t="n">
         <v>5.24</v>
@@ -13342,10 +13342,10 @@
         <v>0</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>67.56999999999999</v>
+        <v>67.58</v>
       </c>
       <c r="AC122" s="4" t="n">
-        <v>32.43</v>
+        <v>32.42</v>
       </c>
       <c r="AD122" s="4" t="n">
         <v>0</v>
@@ -13407,7 +13407,7 @@
         </is>
       </c>
       <c r="M123" s="4" t="n">
-        <v>7.75</v>
+        <v>7.76</v>
       </c>
       <c r="N123" s="4" t="n">
         <v>5.24</v>
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>-30.71</v>
+        <v>-30.73</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>0</v>
@@ -13611,13 +13611,13 @@
         </is>
       </c>
       <c r="M125" s="4" t="n">
-        <v>-33.75</v>
+        <v>-33.76</v>
       </c>
       <c r="N125" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O125" s="4" t="n">
-        <v>-30.71</v>
+        <v>-30.73</v>
       </c>
       <c r="P125" s="4" t="n">
         <v>0</v>
@@ -13648,10 +13648,10 @@
         <v>0</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>34.64</v>
+        <v>34.63</v>
       </c>
       <c r="AC125" s="4" t="n">
-        <v>65.36</v>
+        <v>65.37</v>
       </c>
       <c r="AD125" s="4" t="n">
         <v>0</v>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>-13.6</v>
+        <v>-13.55</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>0.9</v>
@@ -13709,16 +13709,16 @@
         </is>
       </c>
       <c r="M126" s="4" t="n">
-        <v>-13.45</v>
+        <v>-13.47</v>
       </c>
       <c r="N126" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>-10.83</v>
+        <v>-10.84</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>-2.22</v>
+        <v>-2.21</v>
       </c>
       <c r="Q126" s="4" t="n">
         <v>0</v>
@@ -13739,7 +13739,7 @@
         <v>-16.4</v>
       </c>
       <c r="W126" s="5" t="n">
-        <v>440861</v>
+        <v>449913</v>
       </c>
       <c r="X126" s="5" t="n">
         <v>10654949</v>
@@ -13752,10 +13752,10 @@
         <v>0</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>43.2</v>
+        <v>43.22</v>
       </c>
       <c r="AC126" s="4" t="n">
-        <v>56.8</v>
+        <v>56.78</v>
       </c>
       <c r="AD126" s="4" t="n">
         <v>0</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>-17.25</v>
+        <v>-17.27</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>0.4</v>
@@ -13817,13 +13817,13 @@
         </is>
       </c>
       <c r="M127" s="4" t="n">
-        <v>-16.43</v>
+        <v>-16.44</v>
       </c>
       <c r="N127" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O127" s="4" t="n">
-        <v>-17.25</v>
+        <v>-17.27</v>
       </c>
       <c r="P127" s="4" t="n">
         <v>-2.37</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>41.37</v>
+        <v>41.36</v>
       </c>
       <c r="AC127" s="4" t="n">
-        <v>58.63</v>
+        <v>58.64</v>
       </c>
       <c r="AD127" s="4" t="n">
         <v>0</v>
@@ -13905,13 +13905,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>-6.79</v>
+        <v>-6.81</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -13919,13 +13919,13 @@
         </is>
       </c>
       <c r="M128" s="4" t="n">
-        <v>-7.82</v>
+        <v>-7.83</v>
       </c>
       <c r="N128" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>-6.79</v>
+        <v>-6.81</v>
       </c>
       <c r="P128" s="4" t="n">
         <v>-0.74</v>
@@ -13956,10 +13956,10 @@
         <v>0</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>46.61</v>
+        <v>46.6</v>
       </c>
       <c r="AC128" s="4" t="n">
-        <v>53.39</v>
+        <v>53.4</v>
       </c>
       <c r="AD128" s="4" t="n">
         <v>0</v>
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>-17.72</v>
+        <v>-17.76</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>0.4</v>
@@ -14021,16 +14021,16 @@
         </is>
       </c>
       <c r="M129" s="4" t="n">
-        <v>-17.63</v>
+        <v>-17.64</v>
       </c>
       <c r="N129" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O129" s="4" t="n">
-        <v>-17.72</v>
+        <v>-17.76</v>
       </c>
       <c r="P129" s="4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.72</v>
       </c>
       <c r="Q129" s="4" t="n">
         <v>-4.34</v>
@@ -14048,7 +14048,7 @@
         <v>248286</v>
       </c>
       <c r="X129" s="5" t="n">
-        <v>696207</v>
+        <v>726727</v>
       </c>
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" s="4" t="n">
@@ -14058,10 +14058,10 @@
         <v>0</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>41.14</v>
+        <v>41.12</v>
       </c>
       <c r="AC129" s="4" t="n">
-        <v>58.86</v>
+        <v>58.88</v>
       </c>
       <c r="AD129" s="4" t="n">
         <v>0</v>
@@ -14109,7 +14109,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>-22.38</v>
+        <v>-22.39</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>0.1</v>
@@ -14123,13 +14123,13 @@
         </is>
       </c>
       <c r="M130" s="4" t="n">
-        <v>-25.57</v>
+        <v>-25.59</v>
       </c>
       <c r="N130" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O130" s="4" t="n">
-        <v>-22.38</v>
+        <v>-22.39</v>
       </c>
       <c r="P130" s="4" t="n">
         <v>0</v>
@@ -14160,10 +14160,10 @@
         <v>0</v>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>38.81</v>
+        <v>38.8</v>
       </c>
       <c r="AC130" s="4" t="n">
-        <v>61.19</v>
+        <v>61.2</v>
       </c>
       <c r="AD130" s="4" t="n">
         <v>0</v>
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>-4.09</v>
+        <v>-4.1</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>22.4</v>
@@ -14225,16 +14225,16 @@
         </is>
       </c>
       <c r="M131" s="4" t="n">
-        <v>-7.88</v>
+        <v>-7.9</v>
       </c>
       <c r="N131" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O131" s="4" t="n">
-        <v>-4.8</v>
+        <v>-4.81</v>
       </c>
       <c r="P131" s="4" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="Q131" s="4" t="n">
         <v>-2.73</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-10.47</v>
+        <v>-10.45</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>3.1</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="M132" s="4" t="n">
-        <v>-12.09</v>
+        <v>-12.1</v>
       </c>
       <c r="N132" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O132" s="4" t="n">
-        <v>-9.31</v>
+        <v>-9.32</v>
       </c>
       <c r="P132" s="4" t="n">
         <v>-0.65</v>
@@ -14427,13 +14427,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -14441,13 +14441,13 @@
         </is>
       </c>
       <c r="M133" s="4" t="n">
-        <v>-11.65</v>
+        <v>-11.67</v>
       </c>
       <c r="N133" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O133" s="4" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="P133" s="4" t="n">
         <v>-0.34</v>
@@ -14529,7 +14529,7 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>38.21</v>
+        <v>38.2</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>100</v>
@@ -14543,13 +14543,13 @@
         </is>
       </c>
       <c r="M134" s="4" t="n">
-        <v>29.89</v>
+        <v>29.87</v>
       </c>
       <c r="N134" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O134" s="4" t="n">
-        <v>38.21</v>
+        <v>38.2</v>
       </c>
       <c r="P134" s="4" t="n">
         <v>0</v>
@@ -14580,10 +14580,10 @@
         <v>0</v>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>69.11</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AC134" s="4" t="n">
-        <v>30.89</v>
+        <v>30.9</v>
       </c>
       <c r="AD134" s="4" t="n">
         <v>0</v>
@@ -14627,13 +14627,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>-7.6</v>
+        <v>-7.62</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -14641,13 +14641,13 @@
         </is>
       </c>
       <c r="M135" s="4" t="n">
-        <v>-11.37</v>
+        <v>-11.38</v>
       </c>
       <c r="N135" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O135" s="4" t="n">
-        <v>-7.6</v>
+        <v>-7.62</v>
       </c>
       <c r="P135" s="4" t="n">
         <v>-0.8100000000000001</v>
@@ -14678,10 +14678,10 @@
         <v>0</v>
       </c>
       <c r="AB135" s="4" t="n">
-        <v>46.2</v>
+        <v>46.19</v>
       </c>
       <c r="AC135" s="4" t="n">
-        <v>53.8</v>
+        <v>53.81</v>
       </c>
       <c r="AD135" s="4" t="n">
         <v>0</v>
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>-10.7</v>
+        <v>-10.71</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>2.5</v>
@@ -14743,13 +14743,13 @@
         </is>
       </c>
       <c r="M136" s="4" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="N136" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>-10.7</v>
+        <v>-10.71</v>
       </c>
       <c r="P136" s="4" t="n">
         <v>0</v>
@@ -14780,10 +14780,10 @@
         <v>0</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>44.65</v>
+        <v>44.64</v>
       </c>
       <c r="AC136" s="4" t="n">
-        <v>55.35</v>
+        <v>55.36</v>
       </c>
       <c r="AD136" s="4" t="n">
         <v>0</v>
@@ -14831,13 +14831,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>-5.25</v>
+        <v>-5.27</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -14845,13 +14845,13 @@
         </is>
       </c>
       <c r="M137" s="4" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="N137" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O137" s="4" t="n">
-        <v>-5.31</v>
+        <v>-5.33</v>
       </c>
       <c r="P137" s="4" t="n">
         <v>-0.74</v>
@@ -14939,7 +14939,7 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>7.13</v>
+        <v>7.11</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>87.90000000000001</v>
@@ -14953,13 +14953,13 @@
         </is>
       </c>
       <c r="M138" s="4" t="n">
-        <v>-5.73</v>
+        <v>-5.75</v>
       </c>
       <c r="N138" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O138" s="4" t="n">
-        <v>7.13</v>
+        <v>7.11</v>
       </c>
       <c r="P138" s="4" t="n">
         <v>1.56</v>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>-13.05</v>
+        <v>-13.07</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>1</v>
@@ -15055,13 +15055,13 @@
         </is>
       </c>
       <c r="M139" s="4" t="n">
-        <v>-14.55</v>
+        <v>-14.56</v>
       </c>
       <c r="N139" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O139" s="4" t="n">
-        <v>-13.05</v>
+        <v>-13.07</v>
       </c>
       <c r="P139" s="4" t="n">
         <v>0</v>
@@ -15139,13 +15139,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>-4.56</v>
+        <v>-4.67</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -15153,16 +15153,16 @@
         </is>
       </c>
       <c r="M140" s="4" t="n">
-        <v>-8.6</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="N140" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O140" s="4" t="n">
-        <v>-4.56</v>
+        <v>-4.67</v>
       </c>
       <c r="P140" s="4" t="n">
-        <v>-1.01</v>
+        <v>-1.1</v>
       </c>
       <c r="Q140" s="4" t="n">
         <v>0</v>
@@ -15190,10 +15190,10 @@
         <v>0</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>47.72</v>
+        <v>47.67</v>
       </c>
       <c r="AC140" s="4" t="n">
-        <v>52.28</v>
+        <v>52.33</v>
       </c>
       <c r="AD140" s="4" t="n">
         <v>0</v>
@@ -15241,7 +15241,7 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>-18.33</v>
+        <v>-18.34</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>0.3</v>
@@ -15255,13 +15255,13 @@
         </is>
       </c>
       <c r="M141" s="4" t="n">
-        <v>-17.11</v>
+        <v>-17.13</v>
       </c>
       <c r="N141" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O141" s="4" t="n">
-        <v>-18.33</v>
+        <v>-18.34</v>
       </c>
       <c r="P141" s="4" t="n">
         <v>-1.69</v>
@@ -15292,10 +15292,10 @@
         <v>0</v>
       </c>
       <c r="AB141" s="4" t="n">
-        <v>40.84</v>
+        <v>40.83</v>
       </c>
       <c r="AC141" s="4" t="n">
-        <v>59.16</v>
+        <v>59.17</v>
       </c>
       <c r="AD141" s="4" t="n">
         <v>0</v>
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>-9.109999999999999</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>6.4</v>
@@ -15357,13 +15357,13 @@
         </is>
       </c>
       <c r="M142" s="4" t="n">
-        <v>-12.17</v>
+        <v>-12.19</v>
       </c>
       <c r="N142" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O142" s="4" t="n">
-        <v>-9.109999999999999</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="P142" s="4" t="n">
         <v>0</v>
@@ -15394,10 +15394,10 @@
         <v>0</v>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>45.45</v>
+        <v>45.44</v>
       </c>
       <c r="AC142" s="4" t="n">
-        <v>54.55</v>
+        <v>54.56</v>
       </c>
       <c r="AD142" s="4" t="n">
         <v>0</v>
@@ -15441,7 +15441,7 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>-21.71</v>
+        <v>-21.73</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>0.1</v>
@@ -15455,13 +15455,13 @@
         </is>
       </c>
       <c r="M143" s="4" t="n">
-        <v>-25.36</v>
+        <v>-25.37</v>
       </c>
       <c r="N143" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O143" s="4" t="n">
-        <v>-21.71</v>
+        <v>-21.73</v>
       </c>
       <c r="P143" s="4" t="n">
         <v>-1.64</v>
@@ -15492,10 +15492,10 @@
         <v>0</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>39.14</v>
+        <v>39.13</v>
       </c>
       <c r="AC143" s="4" t="n">
-        <v>60.86</v>
+        <v>60.87</v>
       </c>
       <c r="AD143" s="4" t="n">
         <v>0</v>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>51.25</v>
+        <v>51.23</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>100</v>
@@ -15553,13 +15553,13 @@
         </is>
       </c>
       <c r="M144" s="4" t="n">
-        <v>43.75</v>
+        <v>43.73</v>
       </c>
       <c r="N144" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O144" s="4" t="n">
-        <v>51.25</v>
+        <v>51.23</v>
       </c>
       <c r="P144" s="4" t="n">
         <v>1.43</v>
@@ -15590,10 +15590,10 @@
         <v>0</v>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>75.63</v>
+        <v>75.62</v>
       </c>
       <c r="AC144" s="4" t="n">
-        <v>24.37</v>
+        <v>24.38</v>
       </c>
       <c r="AD144" s="4" t="n">
         <v>0</v>
@@ -15641,7 +15641,7 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>-12.7</v>
+        <v>-12.72</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>1</v>
@@ -15655,13 +15655,13 @@
         </is>
       </c>
       <c r="M145" s="4" t="n">
-        <v>-11.42</v>
+        <v>-11.43</v>
       </c>
       <c r="N145" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O145" s="4" t="n">
-        <v>-12.7</v>
+        <v>-12.72</v>
       </c>
       <c r="P145" s="4" t="n">
         <v>0</v>
@@ -15692,10 +15692,10 @@
         <v>0</v>
       </c>
       <c r="AB145" s="4" t="n">
-        <v>43.65</v>
+        <v>43.64</v>
       </c>
       <c r="AC145" s="4" t="n">
-        <v>56.35</v>
+        <v>56.36</v>
       </c>
       <c r="AD145" s="4" t="n">
         <v>0</v>
@@ -15739,13 +15739,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>63.2</v>
+        <v>63.1</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -15753,13 +15753,13 @@
         </is>
       </c>
       <c r="M146" s="4" t="n">
-        <v>-3.77</v>
+        <v>-3.78</v>
       </c>
       <c r="N146" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O146" s="4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P146" s="4" t="n">
         <v>-0.76</v>
@@ -15796,10 +15796,10 @@
         <v>0</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>49.81</v>
+        <v>49.82</v>
       </c>
       <c r="AC146" s="4" t="n">
-        <v>50.19</v>
+        <v>50.18</v>
       </c>
       <c r="AD146" s="4" t="n">
         <v>0</v>
@@ -15847,7 +15847,7 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>29.96</v>
+        <v>29.95</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>100</v>
@@ -15861,13 +15861,13 @@
         </is>
       </c>
       <c r="M147" s="4" t="n">
-        <v>20.64</v>
+        <v>20.63</v>
       </c>
       <c r="N147" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O147" s="4" t="n">
-        <v>29.96</v>
+        <v>29.95</v>
       </c>
       <c r="P147" s="4" t="n">
         <v>0</v>
@@ -15898,10 +15898,10 @@
         <v>0</v>
       </c>
       <c r="AB147" s="4" t="n">
-        <v>64.98</v>
+        <v>64.97</v>
       </c>
       <c r="AC147" s="4" t="n">
-        <v>35.02</v>
+        <v>35.03</v>
       </c>
       <c r="AD147" s="4" t="n">
         <v>0</v>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>56.06</v>
+        <v>56.04</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>100</v>
@@ -15959,13 +15959,13 @@
         </is>
       </c>
       <c r="M148" s="4" t="n">
-        <v>47.76</v>
+        <v>47.75</v>
       </c>
       <c r="N148" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O148" s="4" t="n">
-        <v>56.06</v>
+        <v>56.04</v>
       </c>
       <c r="P148" s="4" t="n">
         <v>1.28</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>78.03</v>
+        <v>78.02</v>
       </c>
       <c r="AC148" s="4" t="n">
-        <v>21.97</v>
+        <v>21.98</v>
       </c>
       <c r="AD148" s="4" t="n">
         <v>0</v>
@@ -16061,7 +16061,7 @@
         </is>
       </c>
       <c r="M149" s="4" t="n">
-        <v>-1.96</v>
+        <v>-1.97</v>
       </c>
       <c r="N149" s="4" t="n">
         <v>5.24</v>
@@ -16070,7 +16070,7 @@
         <v>6.66</v>
       </c>
       <c r="P149" s="4" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="Q149" s="4" t="n">
         <v>2.65</v>
@@ -16155,7 +16155,7 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>-11.57</v>
+        <v>-11.58</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>1.2</v>
@@ -16169,13 +16169,13 @@
         </is>
       </c>
       <c r="M150" s="4" t="n">
-        <v>-9.380000000000001</v>
+        <v>-9.4</v>
       </c>
       <c r="N150" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O150" s="4" t="n">
-        <v>-11.57</v>
+        <v>-11.58</v>
       </c>
       <c r="P150" s="4" t="n">
         <v>-2.32</v>
@@ -16206,10 +16206,10 @@
         <v>0</v>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>44.22</v>
+        <v>44.21</v>
       </c>
       <c r="AC150" s="4" t="n">
-        <v>55.78</v>
+        <v>55.79</v>
       </c>
       <c r="AD150" s="4" t="n">
         <v>0</v>
@@ -16257,7 +16257,7 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>-6.8</v>
+        <v>-6.82</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>13.1</v>
@@ -16271,13 +16271,13 @@
         </is>
       </c>
       <c r="M151" s="4" t="n">
-        <v>-6.54</v>
+        <v>-6.55</v>
       </c>
       <c r="N151" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O151" s="4" t="n">
-        <v>-6.06</v>
+        <v>-6.08</v>
       </c>
       <c r="P151" s="4" t="n">
         <v>-0.6899999999999999</v>
@@ -16314,10 +16314,10 @@
         <v>0</v>
       </c>
       <c r="AB151" s="4" t="n">
-        <v>46.6</v>
+        <v>46.59</v>
       </c>
       <c r="AC151" s="4" t="n">
-        <v>53.4</v>
+        <v>53.41</v>
       </c>
       <c r="AD151" s="4" t="n">
         <v>0</v>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>-14.09</v>
+        <v>-14.1</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>0.8</v>
@@ -16379,13 +16379,13 @@
         </is>
       </c>
       <c r="M152" s="4" t="n">
-        <v>-16.03</v>
+        <v>-16.04</v>
       </c>
       <c r="N152" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O152" s="4" t="n">
-        <v>-15.87</v>
+        <v>-15.88</v>
       </c>
       <c r="P152" s="4" t="n">
         <v>-0.18</v>
@@ -16422,10 +16422,10 @@
         <v>0</v>
       </c>
       <c r="AB152" s="4" t="n">
-        <v>42.96</v>
+        <v>42.95</v>
       </c>
       <c r="AC152" s="4" t="n">
-        <v>57.04</v>
+        <v>57.05</v>
       </c>
       <c r="AD152" s="4" t="n">
         <v>0</v>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="M154" s="4" t="n">
-        <v>12.31</v>
+        <v>12.3</v>
       </c>
       <c r="N154" s="4" t="n">
         <v>5.24</v>
@@ -17132,10 +17132,10 @@
         <v>0</v>
       </c>
       <c r="AB159" s="4" t="n">
-        <v>40.08</v>
+        <v>40.07</v>
       </c>
       <c r="AC159" s="4" t="n">
-        <v>59.92</v>
+        <v>59.93</v>
       </c>
       <c r="AD159" s="4" t="n">
         <v>0</v>
@@ -17397,7 +17397,7 @@
         </is>
       </c>
       <c r="M162" s="4" t="n">
-        <v>-17.53</v>
+        <v>-17.54</v>
       </c>
       <c r="N162" s="4" t="n">
         <v>5.24</v>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>-17.26</v>
+        <v>-17.27</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>0.4</v>
@@ -17501,7 +17501,7 @@
         <v>5.24</v>
       </c>
       <c r="O163" s="4" t="n">
-        <v>-17.26</v>
+        <v>-17.27</v>
       </c>
       <c r="P163" s="4" t="n">
         <v>-2.21</v>
@@ -17732,10 +17732,10 @@
         <v>0</v>
       </c>
       <c r="AB165" s="4" t="n">
-        <v>75.48999999999999</v>
+        <v>75.48</v>
       </c>
       <c r="AC165" s="4" t="n">
-        <v>24.51</v>
+        <v>24.52</v>
       </c>
       <c r="AD165" s="4" t="n">
         <v>0</v>
@@ -17783,7 +17783,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-21.65</v>
+        <v>-21.66</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>0.2</v>
@@ -17803,7 +17803,7 @@
         <v>5.24</v>
       </c>
       <c r="O166" s="4" t="n">
-        <v>-21.65</v>
+        <v>-21.66</v>
       </c>
       <c r="P166" s="4" t="n">
         <v>0.62</v>
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11.32</v>
+        <v>11.3</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>98.7</v>
@@ -18103,13 +18103,13 @@
         </is>
       </c>
       <c r="M169" s="4" t="n">
-        <v>-0.91</v>
+        <v>-0.97</v>
       </c>
       <c r="N169" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O169" s="4" t="n">
-        <v>13.68</v>
+        <v>13.62</v>
       </c>
       <c r="P169" s="4" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB169" s="4" t="n">
-        <v>55.66</v>
+        <v>55.65</v>
       </c>
       <c r="AC169" s="4" t="n">
-        <v>44.34</v>
+        <v>44.35</v>
       </c>
       <c r="AD169" s="4" t="n">
         <v>0</v>
@@ -18193,13 +18193,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>31.9</v>
+        <v>34.2</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -18207,13 +18207,13 @@
         </is>
       </c>
       <c r="M170" s="4" t="n">
-        <v>-2.46</v>
+        <v>-2.51</v>
       </c>
       <c r="N170" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P170" s="4" t="n">
         <v>-0.05</v>
@@ -18225,16 +18225,16 @@
         <v>-10.13</v>
       </c>
       <c r="S170" s="4" t="n">
-        <v>36</v>
+        <v>38.62</v>
       </c>
       <c r="T170" s="4" t="n">
-        <v>33</v>
+        <v>36.14</v>
       </c>
       <c r="U170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V170" s="4" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="W170" s="5" t="n">
         <v>1628201</v>
@@ -18250,10 +18250,10 @@
         <v>0</v>
       </c>
       <c r="AB170" s="4" t="n">
-        <v>50.81</v>
+        <v>50.51</v>
       </c>
       <c r="AC170" s="4" t="n">
-        <v>49.19</v>
+        <v>49.49</v>
       </c>
       <c r="AD170" s="4" t="n">
         <v>0</v>
@@ -18301,13 +18301,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -18315,13 +18315,13 @@
         </is>
       </c>
       <c r="M171" s="4" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="N171" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>6.27</v>
+        <v>6.22</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.06</v>
@@ -18358,10 +18358,10 @@
         <v>0</v>
       </c>
       <c r="AB171" s="4" t="n">
-        <v>52.53</v>
+        <v>52.51</v>
       </c>
       <c r="AC171" s="4" t="n">
-        <v>47.47</v>
+        <v>47.49</v>
       </c>
       <c r="AD171" s="4" t="n">
         <v>0</v>
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-20.9</v>
+        <v>-20.95</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.2</v>
@@ -18419,13 +18419,13 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-24.44</v>
+        <v>-24.49</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-20.9</v>
+        <v>-20.95</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -18456,10 +18456,10 @@
         <v>0</v>
       </c>
       <c r="AB172" s="4" t="n">
-        <v>39.55</v>
+        <v>39.52</v>
       </c>
       <c r="AC172" s="4" t="n">
-        <v>60.45</v>
+        <v>60.48</v>
       </c>
       <c r="AD172" s="4" t="n">
         <v>0</v>
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-28.76</v>
+        <v>-28.98</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18521,13 +18521,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-43.84</v>
+        <v>-43.85</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-41.3</v>
+        <v>-41.31</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18564,10 +18564,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>35.62</v>
+        <v>35.51</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>64.38</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-26.03</v>
+        <v>-26.04</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.24</v>
@@ -19015,7 +19015,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>45.23</v>
+        <v>30.37</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>100</v>
@@ -19046,12 +19046,18 @@
       <c r="R178" s="4" t="n">
         <v>28.79</v>
       </c>
-      <c r="S178" s="4" t="n"/>
-      <c r="T178" s="4" t="n"/>
+      <c r="S178" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="T178" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="U178" t="n">
-        <v>0</v>
-      </c>
-      <c r="V178" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V178" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="W178" s="5" t="n">
         <v>358667</v>
       </c>
@@ -19066,10 +19072,10 @@
         <v>0</v>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>72.62</v>
+        <v>65.19</v>
       </c>
       <c r="AC178" s="4" t="n">
-        <v>27.38</v>
+        <v>34.81</v>
       </c>
       <c r="AD178" s="4" t="n">
         <v>0</v>
@@ -20839,13 +20845,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-15.52</v>
+        <v>-10.92</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -20870,12 +20876,18 @@
       <c r="R196" s="4" t="n">
         <v>-17.13</v>
       </c>
-      <c r="S196" s="4" t="n"/>
-      <c r="T196" s="4" t="n"/>
+      <c r="S196" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="T196" s="4" t="n">
+        <v>48</v>
+      </c>
       <c r="U196" t="n">
-        <v>0</v>
-      </c>
-      <c r="V196" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V196" s="4" t="n">
+        <v>-5</v>
+      </c>
       <c r="W196" s="5" t="n">
         <v>582087</v>
       </c>
@@ -20890,10 +20902,10 @@
         <v>0</v>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>42.24</v>
+        <v>44.54</v>
       </c>
       <c r="AC196" s="4" t="n">
-        <v>57.76</v>
+        <v>55.46</v>
       </c>
       <c r="AD196" s="4" t="n">
         <v>0</v>
@@ -21349,7 +21361,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-32.32</v>
+        <v>-32.26</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0</v>
@@ -21369,10 +21381,10 @@
         <v>5.24</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-32.32</v>
+        <v>-32.26</v>
       </c>
       <c r="P201" s="4" t="n">
-        <v>-2.12</v>
+        <v>-2.06</v>
       </c>
       <c r="Q201" s="4" t="n">
         <v>-5.4</v>
@@ -21387,7 +21399,7 @@
       </c>
       <c r="V201" s="4" t="n"/>
       <c r="W201" s="5" t="n">
-        <v>40651</v>
+        <v>48261</v>
       </c>
       <c r="X201" s="5" t="n">
         <v>1488465</v>
@@ -21400,10 +21412,10 @@
         <v>0</v>
       </c>
       <c r="AB201" s="4" t="n">
-        <v>33.84</v>
+        <v>33.87</v>
       </c>
       <c r="AC201" s="4" t="n">
-        <v>66.16</v>
+        <v>66.13</v>
       </c>
       <c r="AD201" s="4" t="n">
         <v>0</v>
@@ -22259,13 +22271,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-7.72</v>
+        <v>-7.74</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -22316,10 +22328,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.14</v>
+        <v>46.13</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.86</v>
+        <v>53.87</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -22971,7 +22983,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>24.26</v>
+        <v>24.27</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>99.90000000000001</v>
@@ -22985,13 +22997,13 @@
         </is>
       </c>
       <c r="M217" s="4" t="n">
-        <v>17.47</v>
+        <v>17.48</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>24.26</v>
+        <v>24.27</v>
       </c>
       <c r="P217" s="4" t="n">
         <v>0</v>
@@ -23073,7 +23085,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>33.88</v>
+        <v>33.89</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -23087,13 +23099,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>27.42</v>
+        <v>27.43</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>33.88</v>
+        <v>33.89</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -23175,7 +23187,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>32.43</v>
+        <v>32.44</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>100</v>
@@ -23189,13 +23201,13 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>22.93</v>
+        <v>22.94</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>32.43</v>
+        <v>32.44</v>
       </c>
       <c r="P219" s="4" t="n">
         <v>2.52</v>
@@ -23277,7 +23289,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>29.93</v>
+        <v>29.94</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>100</v>
@@ -23291,13 +23303,13 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.75</v>
+        <v>23.76</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O220" s="4" t="n">
-        <v>29.93</v>
+        <v>29.94</v>
       </c>
       <c r="P220" s="4" t="n">
         <v>0</v>
@@ -23379,7 +23391,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>55.55</v>
+        <v>55.56</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>100</v>
@@ -23393,13 +23405,13 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>49.11</v>
+        <v>49.12</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O221" s="4" t="n">
-        <v>55.55</v>
+        <v>55.56</v>
       </c>
       <c r="P221" s="4" t="n">
         <v>0</v>
@@ -23477,7 +23489,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>28.69</v>
+        <v>28.7</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>100</v>
@@ -23491,13 +23503,13 @@
         </is>
       </c>
       <c r="M222" s="4" t="n">
-        <v>23.95</v>
+        <v>23.96</v>
       </c>
       <c r="N222" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O222" s="4" t="n">
-        <v>28.69</v>
+        <v>28.7</v>
       </c>
       <c r="P222" s="4" t="n">
         <v>0</v>
@@ -23579,7 +23591,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>76.34999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -23593,13 +23605,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>69.12</v>
+        <v>69.13</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>76.34999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -23630,10 +23642,10 @@
         <v>0</v>
       </c>
       <c r="AB223" s="4" t="n">
-        <v>88.17</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="AC223" s="4" t="n">
-        <v>11.83</v>
+        <v>11.82</v>
       </c>
       <c r="AD223" s="4" t="n">
         <v>0</v>
@@ -23681,7 +23693,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>45.66</v>
+        <v>45.67</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>100</v>
@@ -23695,13 +23707,13 @@
         </is>
       </c>
       <c r="M224" s="4" t="n">
-        <v>30.52</v>
+        <v>30.53</v>
       </c>
       <c r="N224" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O224" s="4" t="n">
-        <v>45.66</v>
+        <v>45.67</v>
       </c>
       <c r="P224" s="4" t="n">
         <v>0</v>
@@ -23732,10 +23744,10 @@
         <v>0</v>
       </c>
       <c r="AB224" s="4" t="n">
-        <v>72.83</v>
+        <v>72.84</v>
       </c>
       <c r="AC224" s="4" t="n">
-        <v>27.17</v>
+        <v>27.16</v>
       </c>
       <c r="AD224" s="4" t="n">
         <v>0</v>
@@ -23783,7 +23795,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.68</v>
+        <v>22.69</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23797,13 +23809,13 @@
         </is>
       </c>
       <c r="M225" s="4" t="n">
-        <v>13.99</v>
+        <v>14</v>
       </c>
       <c r="N225" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.68</v>
+        <v>22.69</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.51</v>
@@ -23834,10 +23846,10 @@
         <v>0</v>
       </c>
       <c r="AB225" s="4" t="n">
-        <v>61.34</v>
+        <v>61.35</v>
       </c>
       <c r="AC225" s="4" t="n">
-        <v>38.66</v>
+        <v>38.65</v>
       </c>
       <c r="AD225" s="4" t="n">
         <v>0</v>
@@ -24693,7 +24705,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.67</v>
+        <v>30.35</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24707,13 +24719,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>22.19</v>
+        <v>22.15</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.25</v>
+        <v>31.22</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24744,10 +24756,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.35</v>
+        <v>62.33</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.65</v>
+        <v>32.67</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24791,13 +24803,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.15</v>
+        <v>-3.68</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>37.4</v>
+        <v>39.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>62.6</v>
+        <v>60.4</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24805,13 +24817,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-8.960000000000001</v>
+        <v>-8.99</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.2</v>
+        <v>-5.23</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24848,10 +24860,10 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>45.43</v>
+        <v>45.42</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>49.57</v>
+        <v>49.58</v>
       </c>
       <c r="AD235" s="4" t="n">
         <v>5</v>
@@ -24899,7 +24911,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>-13.54</v>
+        <v>-13.53</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>0.9</v>
@@ -24913,13 +24925,13 @@
         </is>
       </c>
       <c r="M236" s="4" t="n">
-        <v>-18.14</v>
+        <v>-18.13</v>
       </c>
       <c r="N236" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O236" s="4" t="n">
-        <v>-13.54</v>
+        <v>-13.53</v>
       </c>
       <c r="P236" s="4" t="n">
         <v>-0.61</v>
@@ -24950,10 +24962,10 @@
         <v>0</v>
       </c>
       <c r="AB236" s="4" t="n">
-        <v>43.23</v>
+        <v>43.24</v>
       </c>
       <c r="AC236" s="4" t="n">
-        <v>56.77</v>
+        <v>56.76</v>
       </c>
       <c r="AD236" s="4" t="n">
         <v>0</v>
@@ -25001,7 +25013,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>-28.48</v>
+        <v>-28.47</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>0</v>
@@ -25015,13 +25027,13 @@
         </is>
       </c>
       <c r="M237" s="4" t="n">
-        <v>-26.8</v>
+        <v>-26.79</v>
       </c>
       <c r="N237" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O237" s="4" t="n">
-        <v>-28.48</v>
+        <v>-28.47</v>
       </c>
       <c r="P237" s="4" t="n">
         <v>-1.9</v>
@@ -25052,10 +25064,10 @@
         <v>0</v>
       </c>
       <c r="AB237" s="4" t="n">
-        <v>35.76</v>
+        <v>35.77</v>
       </c>
       <c r="AC237" s="4" t="n">
-        <v>64.23999999999999</v>
+        <v>64.23</v>
       </c>
       <c r="AD237" s="4" t="n">
         <v>0</v>
@@ -25103,7 +25115,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>20.97</v>
+        <v>20.98</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25117,13 +25129,13 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>20.97</v>
+        <v>20.98</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>1.02</v>
@@ -25154,10 +25166,10 @@
         <v>0</v>
       </c>
       <c r="AB238" s="4" t="n">
-        <v>60.48</v>
+        <v>60.49</v>
       </c>
       <c r="AC238" s="4" t="n">
-        <v>39.52</v>
+        <v>39.51</v>
       </c>
       <c r="AD238" s="4" t="n">
         <v>0</v>
@@ -25205,13 +25217,13 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>-2.15</v>
+        <v>-2.12</v>
       </c>
       <c r="J239" s="4" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -25219,16 +25231,16 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-2.3</v>
+        <v>-2.29</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-2.82</v>
+        <v>-2.79</v>
       </c>
       <c r="P239" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="Q239" s="4" t="n">
         <v>-4.89</v>
@@ -25262,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AB239" s="4" t="n">
-        <v>48.93</v>
+        <v>48.94</v>
       </c>
       <c r="AC239" s="4" t="n">
-        <v>51.07</v>
+        <v>51.06</v>
       </c>
       <c r="AD239" s="4" t="n">
         <v>0</v>
@@ -25313,7 +25325,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-26.27</v>
+        <v>-26.25</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0</v>
@@ -25327,13 +25339,13 @@
         </is>
       </c>
       <c r="M240" s="4" t="n">
-        <v>-23.51</v>
+        <v>-23.5</v>
       </c>
       <c r="N240" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-26.27</v>
+        <v>-26.25</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.12</v>
@@ -25415,7 +25427,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>37.9</v>
+        <v>37.91</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -25429,13 +25441,13 @@
         </is>
       </c>
       <c r="M241" s="4" t="n">
-        <v>27.67</v>
+        <v>27.68</v>
       </c>
       <c r="N241" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>37.9</v>
+        <v>37.91</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -25517,13 +25529,13 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -25531,13 +25543,13 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O242" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="P242" s="4" t="n">
         <v>-1.12</v>
@@ -25574,10 +25586,10 @@
         <v>0</v>
       </c>
       <c r="AB242" s="4" t="n">
-        <v>50.47</v>
+        <v>50.48</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.53</v>
+        <v>49.52</v>
       </c>
       <c r="AD242" s="4" t="n">
         <v>0</v>
@@ -25625,7 +25637,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>99.5</v>
@@ -25639,13 +25651,13 @@
         </is>
       </c>
       <c r="M243" s="4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="N243" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="P243" s="4" t="n">
         <v>0</v>
@@ -25676,10 +25688,10 @@
         <v>0</v>
       </c>
       <c r="AB243" s="4" t="n">
-        <v>58.39</v>
+        <v>58.4</v>
       </c>
       <c r="AC243" s="4" t="n">
-        <v>41.61</v>
+        <v>41.6</v>
       </c>
       <c r="AD243" s="4" t="n">
         <v>0</v>
@@ -25727,7 +25739,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-33.27</v>
+        <v>-33.26</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -25741,13 +25753,13 @@
         </is>
       </c>
       <c r="M244" s="4" t="n">
-        <v>-29.04</v>
+        <v>-29.03</v>
       </c>
       <c r="N244" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-33.27</v>
+        <v>-33.26</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -25778,10 +25790,10 @@
         <v>0</v>
       </c>
       <c r="AB244" s="4" t="n">
-        <v>33.36</v>
+        <v>33.37</v>
       </c>
       <c r="AC244" s="4" t="n">
-        <v>66.64</v>
+        <v>66.63</v>
       </c>
       <c r="AD244" s="4" t="n">
         <v>0</v>
@@ -25825,7 +25837,7 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="J245" s="4" t="n">
         <v>68.5</v>
@@ -25839,13 +25851,13 @@
         </is>
       </c>
       <c r="M245" s="4" t="n">
-        <v>-2.25</v>
+        <v>-2.24</v>
       </c>
       <c r="N245" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O245" s="4" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="P245" s="4" t="n">
         <v>-0.05</v>
@@ -25882,10 +25894,10 @@
         <v>0</v>
       </c>
       <c r="AB245" s="4" t="n">
-        <v>50.85</v>
+        <v>50.86</v>
       </c>
       <c r="AC245" s="4" t="n">
-        <v>49.15</v>
+        <v>49.14</v>
       </c>
       <c r="AD245" s="4" t="n">
         <v>0</v>
@@ -25929,7 +25941,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>26.49</v>
+        <v>26.5</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>100</v>
@@ -25943,13 +25955,13 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>20.29</v>
+        <v>20.31</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O246" s="4" t="n">
-        <v>26.49</v>
+        <v>26.5</v>
       </c>
       <c r="P246" s="4" t="n">
         <v>1.6</v>
@@ -26031,7 +26043,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>58.52</v>
+        <v>58.53</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -26045,13 +26057,13 @@
         </is>
       </c>
       <c r="M247" s="4" t="n">
-        <v>45.34</v>
+        <v>45.35</v>
       </c>
       <c r="N247" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O247" s="4" t="n">
-        <v>58.52</v>
+        <v>58.53</v>
       </c>
       <c r="P247" s="4" t="n">
         <v>2.96</v>
@@ -26082,10 +26094,10 @@
         <v>0</v>
       </c>
       <c r="AB247" s="4" t="n">
-        <v>79.26000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="AC247" s="4" t="n">
-        <v>20.74</v>
+        <v>20.73</v>
       </c>
       <c r="AD247" s="4" t="n">
         <v>0</v>
@@ -26133,7 +26145,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>58.26</v>
+        <v>58.27</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -26147,13 +26159,13 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>47.84</v>
+        <v>47.85</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>58.26</v>
+        <v>58.27</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
@@ -26184,10 +26196,10 @@
         <v>0</v>
       </c>
       <c r="AB248" s="4" t="n">
-        <v>79.13</v>
+        <v>79.14</v>
       </c>
       <c r="AC248" s="4" t="n">
-        <v>20.87</v>
+        <v>20.86</v>
       </c>
       <c r="AD248" s="4" t="n">
         <v>0</v>
@@ -26235,13 +26247,13 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>-5.98</v>
+        <v>-5.96</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="K249" s="4" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -26249,13 +26261,13 @@
         </is>
       </c>
       <c r="M249" s="4" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.02</v>
       </c>
       <c r="N249" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O249" s="4" t="n">
-        <v>-6.19</v>
+        <v>-6.17</v>
       </c>
       <c r="P249" s="4" t="n">
         <v>-0.01</v>
@@ -26292,10 +26304,10 @@
         <v>0</v>
       </c>
       <c r="AB249" s="4" t="n">
-        <v>47.01</v>
+        <v>47.02</v>
       </c>
       <c r="AC249" s="4" t="n">
-        <v>52.99</v>
+        <v>52.98</v>
       </c>
       <c r="AD249" s="4" t="n">
         <v>0</v>
@@ -26339,7 +26351,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>12.1</v>
+        <v>12.15</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>98.90000000000001</v>
@@ -26353,16 +26365,16 @@
         </is>
       </c>
       <c r="M250" s="4" t="n">
-        <v>8.58</v>
+        <v>8.6</v>
       </c>
       <c r="N250" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O250" s="4" t="n">
-        <v>13.66</v>
+        <v>13.7</v>
       </c>
       <c r="P250" s="4" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="Q250" s="4" t="n">
         <v>0</v>
@@ -26396,10 +26408,10 @@
         <v>0</v>
       </c>
       <c r="AB250" s="4" t="n">
-        <v>56.05</v>
+        <v>56.07</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>43.95</v>
+        <v>43.93</v>
       </c>
       <c r="AD250" s="4" t="n">
         <v>0</v>
@@ -26447,7 +26459,7 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>30.05</v>
+        <v>30.08</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>100</v>
@@ -26461,13 +26473,13 @@
         </is>
       </c>
       <c r="M251" s="4" t="n">
-        <v>23.86</v>
+        <v>23.88</v>
       </c>
       <c r="N251" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O251" s="4" t="n">
-        <v>30.05</v>
+        <v>30.08</v>
       </c>
       <c r="P251" s="4" t="n">
         <v>0</v>
@@ -26498,10 +26510,10 @@
         <v>0</v>
       </c>
       <c r="AB251" s="4" t="n">
-        <v>65.03</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="AC251" s="4" t="n">
-        <v>34.97</v>
+        <v>34.96</v>
       </c>
       <c r="AD251" s="4" t="n">
         <v>0</v>
@@ -26549,7 +26561,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>100</v>
@@ -26563,13 +26575,13 @@
         </is>
       </c>
       <c r="M252" s="4" t="n">
-        <v>39.55</v>
+        <v>39.58</v>
       </c>
       <c r="N252" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O252" s="4" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="P252" s="4" t="n">
         <v>2.11</v>
@@ -26600,10 +26612,10 @@
         <v>0</v>
       </c>
       <c r="AB252" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>73.91</v>
       </c>
       <c r="AC252" s="4" t="n">
-        <v>26.1</v>
+        <v>26.09</v>
       </c>
       <c r="AD252" s="4" t="n">
         <v>0</v>
@@ -26651,7 +26663,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>65.95</v>
+        <v>65.97</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>100</v>
@@ -26665,13 +26677,13 @@
         </is>
       </c>
       <c r="M253" s="4" t="n">
-        <v>66.38</v>
+        <v>66.41</v>
       </c>
       <c r="N253" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O253" s="4" t="n">
-        <v>65.95</v>
+        <v>65.97</v>
       </c>
       <c r="P253" s="4" t="n">
         <v>1.21</v>
@@ -26702,10 +26714,10 @@
         <v>0</v>
       </c>
       <c r="AB253" s="4" t="n">
-        <v>82.97</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="AC253" s="4" t="n">
-        <v>17.03</v>
+        <v>17.01</v>
       </c>
       <c r="AD253" s="4" t="n">
         <v>0</v>
@@ -26753,7 +26765,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-14.51</v>
+        <v>-14.49</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>0.7</v>
@@ -26767,13 +26779,13 @@
         </is>
       </c>
       <c r="M254" s="4" t="n">
-        <v>-17.23</v>
+        <v>-17.21</v>
       </c>
       <c r="N254" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-14.51</v>
+        <v>-14.49</v>
       </c>
       <c r="P254" s="4" t="n">
         <v>0</v>
@@ -26804,10 +26816,10 @@
         <v>0</v>
       </c>
       <c r="AB254" s="4" t="n">
-        <v>42.75</v>
+        <v>42.76</v>
       </c>
       <c r="AC254" s="4" t="n">
-        <v>57.25</v>
+        <v>57.24</v>
       </c>
       <c r="AD254" s="4" t="n">
         <v>0</v>
@@ -26855,7 +26867,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>-30.85</v>
+        <v>-30.82</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>0</v>
@@ -26869,13 +26881,13 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-33.58</v>
+        <v>-33.56</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O255" s="4" t="n">
-        <v>-30.85</v>
+        <v>-30.82</v>
       </c>
       <c r="P255" s="4" t="n">
         <v>0</v>
@@ -26906,10 +26918,10 @@
         <v>0</v>
       </c>
       <c r="AB255" s="4" t="n">
-        <v>34.58</v>
+        <v>34.59</v>
       </c>
       <c r="AC255" s="4" t="n">
-        <v>65.42</v>
+        <v>65.41</v>
       </c>
       <c r="AD255" s="4" t="n">
         <v>0</v>
@@ -26957,13 +26969,13 @@
         </is>
       </c>
       <c r="I256" s="4" t="n">
-        <v>-8.529999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="J256" s="4" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="K256" s="4" t="n">
-        <v>92</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -26971,13 +26983,13 @@
         </is>
       </c>
       <c r="M256" s="4" t="n">
-        <v>-11.04</v>
+        <v>-11.02</v>
       </c>
       <c r="N256" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O256" s="4" t="n">
-        <v>-8.529999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="P256" s="4" t="n">
         <v>0</v>
@@ -27008,10 +27020,10 @@
         <v>0</v>
       </c>
       <c r="AB256" s="4" t="n">
-        <v>45.74</v>
+        <v>45.75</v>
       </c>
       <c r="AC256" s="4" t="n">
-        <v>54.26</v>
+        <v>54.25</v>
       </c>
       <c r="AD256" s="4" t="n">
         <v>0</v>
@@ -27161,13 +27173,13 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.69</v>
+        <v>-10.7</v>
       </c>
       <c r="J258" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K258" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -27218,10 +27230,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.66</v>
+        <v>44.65</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.34</v>
+        <v>55.35</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -28281,13 +28293,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.78</v>
+        <v>-6.81</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28295,13 +28307,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.2</v>
+        <v>-12.23</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.09</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28338,10 +28350,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.61</v>
+        <v>46.59</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.39</v>
+        <v>53.41</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28389,7 +28401,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.82</v>
+        <v>-33.85</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28403,13 +28415,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.16</v>
+        <v>-31.19</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.82</v>
+        <v>-33.85</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28440,10 +28452,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.09</v>
+        <v>33.07</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.91</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -30038,10 +30050,10 @@
         <v>-9.17</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30345,7 +30357,7 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="J289" s="4" t="n">
         <v>81.59999999999999</v>
@@ -30365,10 +30377,10 @@
         <v>5.24</v>
       </c>
       <c r="O289" s="4" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="P289" s="4" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="Q289" s="4" t="n">
         <v>0</v>
@@ -30396,10 +30408,10 @@
         <v>0</v>
       </c>
       <c r="AB289" s="4" t="n">
-        <v>52.6</v>
+        <v>52.61</v>
       </c>
       <c r="AC289" s="4" t="n">
-        <v>47.4</v>
+        <v>47.39</v>
       </c>
       <c r="AD289" s="4" t="n">
         <v>0</v>
@@ -31173,13 +31185,13 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="J297" s="4" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K297" s="4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -31787,7 +31799,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>26.07</v>
+        <v>26.08</v>
       </c>
       <c r="J303" s="4" t="n">
         <v>100</v>
@@ -31801,13 +31813,13 @@
         </is>
       </c>
       <c r="M303" s="4" t="n">
-        <v>15.95</v>
+        <v>15.96</v>
       </c>
       <c r="N303" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O303" s="4" t="n">
-        <v>26.07</v>
+        <v>26.08</v>
       </c>
       <c r="P303" s="4" t="n">
         <v>1.68</v>
@@ -31838,10 +31850,10 @@
         <v>0</v>
       </c>
       <c r="AB303" s="4" t="n">
-        <v>63.03</v>
+        <v>63.04</v>
       </c>
       <c r="AC303" s="4" t="n">
-        <v>36.97</v>
+        <v>36.96</v>
       </c>
       <c r="AD303" s="4" t="n">
         <v>0</v>
@@ -31889,7 +31901,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>14.6</v>
+        <v>14.62</v>
       </c>
       <c r="J304" s="4" t="n">
         <v>99.3</v>
@@ -31909,7 +31921,7 @@
         <v>5.24</v>
       </c>
       <c r="O304" s="4" t="n">
-        <v>16.48</v>
+        <v>16.49</v>
       </c>
       <c r="P304" s="4" t="n">
         <v>0.67</v>
@@ -31946,10 +31958,10 @@
         <v>0</v>
       </c>
       <c r="AB304" s="4" t="n">
-        <v>57.3</v>
+        <v>57.31</v>
       </c>
       <c r="AC304" s="4" t="n">
-        <v>42.7</v>
+        <v>42.69</v>
       </c>
       <c r="AD304" s="4" t="n">
         <v>0</v>
@@ -31997,7 +32009,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>23.08</v>
+        <v>23.09</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>99.90000000000001</v>
@@ -32011,13 +32023,13 @@
         </is>
       </c>
       <c r="M305" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N305" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O305" s="4" t="n">
-        <v>23.08</v>
+        <v>23.09</v>
       </c>
       <c r="P305" s="4" t="n">
         <v>0.73</v>
@@ -32048,10 +32060,10 @@
         <v>0</v>
       </c>
       <c r="AB305" s="4" t="n">
-        <v>61.54</v>
+        <v>61.55</v>
       </c>
       <c r="AC305" s="4" t="n">
-        <v>38.46</v>
+        <v>38.45</v>
       </c>
       <c r="AD305" s="4" t="n">
         <v>0</v>
@@ -32099,13 +32111,13 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>16.37</v>
+        <v>15.87</v>
       </c>
       <c r="J306" s="4" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K306" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -32113,13 +32125,13 @@
         </is>
       </c>
       <c r="M306" s="4" t="n">
-        <v>5.47</v>
+        <v>4.97</v>
       </c>
       <c r="N306" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O306" s="4" t="n">
-        <v>16.37</v>
+        <v>15.87</v>
       </c>
       <c r="P306" s="4" t="n">
         <v>-0.16</v>
@@ -32150,10 +32162,10 @@
         <v>0</v>
       </c>
       <c r="AB306" s="4" t="n">
-        <v>58.18</v>
+        <v>57.93</v>
       </c>
       <c r="AC306" s="4" t="n">
-        <v>41.82</v>
+        <v>42.07</v>
       </c>
       <c r="AD306" s="4" t="n">
         <v>0</v>
@@ -32197,13 +32209,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-4.4</v>
+        <v>-4.78</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>21.3</v>
+        <v>19.9</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>78.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -32211,13 +32223,13 @@
         </is>
       </c>
       <c r="M307" s="4" t="n">
-        <v>-12.35</v>
+        <v>-12.85</v>
       </c>
       <c r="N307" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O307" s="4" t="n">
-        <v>-8.44</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="P307" s="4" t="n">
         <v>-1.32</v>
@@ -32254,10 +32266,10 @@
         <v>0</v>
       </c>
       <c r="AB307" s="4" t="n">
-        <v>47.8</v>
+        <v>47.61</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>52.2</v>
+        <v>52.39</v>
       </c>
       <c r="AD307" s="4" t="n">
         <v>0</v>
@@ -32305,13 +32317,13 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>11.84</v>
+        <v>11.34</v>
       </c>
       <c r="J308" s="4" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="K308" s="4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -32319,13 +32331,13 @@
         </is>
       </c>
       <c r="M308" s="4" t="n">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="N308" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O308" s="4" t="n">
-        <v>11.84</v>
+        <v>11.34</v>
       </c>
       <c r="P308" s="4" t="n">
         <v>0.06</v>
@@ -32356,10 +32368,10 @@
         <v>0</v>
       </c>
       <c r="AB308" s="4" t="n">
-        <v>55.92</v>
+        <v>55.67</v>
       </c>
       <c r="AC308" s="4" t="n">
-        <v>44.08</v>
+        <v>44.33</v>
       </c>
       <c r="AD308" s="4" t="n">
         <v>0</v>
@@ -32407,7 +32419,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>17.63</v>
+        <v>17.13</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>99.59999999999999</v>
@@ -32421,13 +32433,13 @@
         </is>
       </c>
       <c r="M309" s="4" t="n">
-        <v>5.51</v>
+        <v>5.01</v>
       </c>
       <c r="N309" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>17.63</v>
+        <v>17.13</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>0.97</v>
@@ -32458,10 +32470,10 @@
         <v>0</v>
       </c>
       <c r="AB309" s="4" t="n">
-        <v>58.81</v>
+        <v>58.56</v>
       </c>
       <c r="AC309" s="4" t="n">
-        <v>41.19</v>
+        <v>41.44</v>
       </c>
       <c r="AD309" s="4" t="n">
         <v>0</v>
@@ -34137,7 +34149,7 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="J326" s="4" t="n">
         <v>71.40000000000001</v>
@@ -34194,10 +34206,10 @@
         <v>0</v>
       </c>
       <c r="AB326" s="4" t="n">
-        <v>51.22</v>
+        <v>51.23</v>
       </c>
       <c r="AC326" s="4" t="n">
-        <v>48.78</v>
+        <v>48.77</v>
       </c>
       <c r="AD326" s="4" t="n">
         <v>0</v>
@@ -34553,7 +34565,7 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-13.01</v>
+        <v>-13.04</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>1</v>
@@ -34610,10 +34622,10 @@
         <v>0</v>
       </c>
       <c r="AB330" s="4" t="n">
-        <v>43.5</v>
+        <v>43.48</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>56.5</v>
+        <v>56.52</v>
       </c>
       <c r="AD330" s="4" t="n">
         <v>0</v>
@@ -35273,7 +35285,7 @@
         </is>
       </c>
       <c r="I337" s="4" t="n">
-        <v>-36.18</v>
+        <v>-36.19</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>0</v>
@@ -35287,13 +35299,13 @@
         </is>
       </c>
       <c r="M337" s="4" t="n">
-        <v>-37.82</v>
+        <v>-37.83</v>
       </c>
       <c r="N337" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O337" s="4" t="n">
-        <v>-36.18</v>
+        <v>-36.19</v>
       </c>
       <c r="P337" s="4" t="n">
         <v>0</v>
@@ -35389,7 +35401,7 @@
         </is>
       </c>
       <c r="M338" s="4" t="n">
-        <v>45.26</v>
+        <v>45.25</v>
       </c>
       <c r="N338" s="4" t="n">
         <v>5.24</v>
@@ -35491,7 +35503,7 @@
         </is>
       </c>
       <c r="M339" s="4" t="n">
-        <v>-38.58</v>
+        <v>-38.59</v>
       </c>
       <c r="N339" s="4" t="n">
         <v>5.24</v>
@@ -35579,7 +35591,7 @@
         </is>
       </c>
       <c r="I340" s="4" t="n">
-        <v>-22.37</v>
+        <v>-22.38</v>
       </c>
       <c r="J340" s="4" t="n">
         <v>0.1</v>
@@ -35599,7 +35611,7 @@
         <v>5.24</v>
       </c>
       <c r="O340" s="4" t="n">
-        <v>-22.37</v>
+        <v>-22.38</v>
       </c>
       <c r="P340" s="4" t="n">
         <v>-2.45</v>
@@ -35695,7 +35707,7 @@
         </is>
       </c>
       <c r="M341" s="4" t="n">
-        <v>-29.49</v>
+        <v>-29.5</v>
       </c>
       <c r="N341" s="4" t="n">
         <v>5.24</v>
@@ -35783,13 +35795,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-1.06</v>
+        <v>-1.13</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35840,10 +35852,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>49.47</v>
+        <v>49.44</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>50.53</v>
+        <v>50.56</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -35891,7 +35903,7 @@
         </is>
       </c>
       <c r="I343" s="4" t="n">
-        <v>-8.68</v>
+        <v>-8.69</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>7.6</v>
@@ -35905,13 +35917,13 @@
         </is>
       </c>
       <c r="M343" s="4" t="n">
-        <v>-12.02</v>
+        <v>-12.03</v>
       </c>
       <c r="N343" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O343" s="4" t="n">
-        <v>-8.68</v>
+        <v>-8.69</v>
       </c>
       <c r="P343" s="4" t="n">
         <v>0</v>
@@ -36101,7 +36113,7 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.31</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>5.9</v>
@@ -36121,7 +36133,7 @@
         <v>5.24</v>
       </c>
       <c r="O345" s="4" t="n">
-        <v>-9.640000000000001</v>
+        <v>-9.65</v>
       </c>
       <c r="P345" s="4" t="n">
         <v>-0.62</v>
@@ -36260,10 +36272,10 @@
         <v>0</v>
       </c>
       <c r="AB346" s="4" t="n">
-        <v>85.31</v>
+        <v>85.3</v>
       </c>
       <c r="AC346" s="4" t="n">
-        <v>14.69</v>
+        <v>14.7</v>
       </c>
       <c r="AD346" s="4" t="n">
         <v>0</v>
@@ -36515,7 +36527,7 @@
         </is>
       </c>
       <c r="I349" s="4" t="n">
-        <v>-19.89</v>
+        <v>-19.9</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>0.2</v>
@@ -36535,7 +36547,7 @@
         <v>5.24</v>
       </c>
       <c r="O349" s="4" t="n">
-        <v>-19.89</v>
+        <v>-19.9</v>
       </c>
       <c r="P349" s="4" t="n">
         <v>-1.93</v>
@@ -36617,13 +36629,13 @@
         </is>
       </c>
       <c r="I350" s="4" t="n">
-        <v>-5.72</v>
+        <v>-5.73</v>
       </c>
       <c r="J350" s="4" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="K350" s="4" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -36631,13 +36643,13 @@
         </is>
       </c>
       <c r="M350" s="4" t="n">
-        <v>-5.74</v>
+        <v>-5.75</v>
       </c>
       <c r="N350" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O350" s="4" t="n">
-        <v>-5.72</v>
+        <v>-5.73</v>
       </c>
       <c r="P350" s="4" t="n">
         <v>-1.22</v>
@@ -37276,10 +37288,10 @@
         <v>0</v>
       </c>
       <c r="AB356" s="4" t="n">
-        <v>74.72</v>
+        <v>74.73</v>
       </c>
       <c r="AC356" s="4" t="n">
-        <v>25.28</v>
+        <v>25.27</v>
       </c>
       <c r="AD356" s="4" t="n">
         <v>0</v>
@@ -37327,7 +37339,7 @@
         </is>
       </c>
       <c r="I357" s="4" t="n">
-        <v>-29.03</v>
+        <v>-29.02</v>
       </c>
       <c r="J357" s="4" t="n">
         <v>0</v>
@@ -37347,7 +37359,7 @@
         <v>5.24</v>
       </c>
       <c r="O357" s="4" t="n">
-        <v>-29.03</v>
+        <v>-29.02</v>
       </c>
       <c r="P357" s="4" t="n">
         <v>-1.49</v>
@@ -37735,7 +37747,7 @@
         </is>
       </c>
       <c r="I361" s="4" t="n">
-        <v>17.98</v>
+        <v>17.99</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>99.59999999999999</v>
@@ -37755,7 +37767,7 @@
         <v>5.24</v>
       </c>
       <c r="O361" s="4" t="n">
-        <v>17.98</v>
+        <v>17.99</v>
       </c>
       <c r="P361" s="4" t="n">
         <v>2.46</v>
@@ -37851,7 +37863,7 @@
         </is>
       </c>
       <c r="M362" s="4" t="n">
-        <v>6.03</v>
+        <v>6.04</v>
       </c>
       <c r="N362" s="4" t="n">
         <v>5.24</v>
@@ -38159,7 +38171,7 @@
         </is>
       </c>
       <c r="M365" s="4" t="n">
-        <v>21.32</v>
+        <v>21.33</v>
       </c>
       <c r="N365" s="4" t="n">
         <v>5.24</v>
@@ -38196,10 +38208,10 @@
         <v>0</v>
       </c>
       <c r="AB365" s="4" t="n">
-        <v>64.81999999999999</v>
+        <v>64.83</v>
       </c>
       <c r="AC365" s="4" t="n">
-        <v>35.18</v>
+        <v>35.17</v>
       </c>
       <c r="AD365" s="4" t="n">
         <v>0</v>
@@ -38261,7 +38273,7 @@
         </is>
       </c>
       <c r="M366" s="4" t="n">
-        <v>34.55</v>
+        <v>34.56</v>
       </c>
       <c r="N366" s="4" t="n">
         <v>5.24</v>
@@ -38298,10 +38310,10 @@
         <v>0</v>
       </c>
       <c r="AB366" s="4" t="n">
-        <v>71.22</v>
+        <v>71.23</v>
       </c>
       <c r="AC366" s="4" t="n">
-        <v>28.78</v>
+        <v>28.77</v>
       </c>
       <c r="AD366" s="4" t="n">
         <v>0</v>
@@ -38349,7 +38361,7 @@
         </is>
       </c>
       <c r="I367" s="4" t="n">
-        <v>25.94</v>
+        <v>25.95</v>
       </c>
       <c r="J367" s="4" t="n">
         <v>100</v>
@@ -38363,13 +38375,13 @@
         </is>
       </c>
       <c r="M367" s="4" t="n">
-        <v>16.85</v>
+        <v>16.86</v>
       </c>
       <c r="N367" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O367" s="4" t="n">
-        <v>25.94</v>
+        <v>25.95</v>
       </c>
       <c r="P367" s="4" t="n">
         <v>1.03</v>
@@ -38451,13 +38463,13 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="J368" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="K368" s="4" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -38508,10 +38520,10 @@
         <v>0</v>
       </c>
       <c r="AB368" s="4" t="n">
-        <v>51.3</v>
+        <v>51.31</v>
       </c>
       <c r="AC368" s="4" t="n">
-        <v>48.7</v>
+        <v>48.69</v>
       </c>
       <c r="AD368" s="4" t="n">
         <v>0</v>
@@ -38559,7 +38571,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>62.9</v>
@@ -38681,7 +38693,7 @@
         </is>
       </c>
       <c r="M370" s="4" t="n">
-        <v>-33.37</v>
+        <v>-33.36</v>
       </c>
       <c r="N370" s="4" t="n">
         <v>5.24</v>
@@ -38769,7 +38781,7 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="J371" s="4" t="n">
         <v>93.09999999999999</v>
@@ -38783,7 +38795,7 @@
         </is>
       </c>
       <c r="M371" s="4" t="n">
-        <v>-0.57</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N371" s="4" t="n">
         <v>5.24</v>
@@ -39197,7 +39209,7 @@
         </is>
       </c>
       <c r="M375" s="4" t="n">
-        <v>-28.35</v>
+        <v>-28.34</v>
       </c>
       <c r="N375" s="4" t="n">
         <v>5.24</v>
@@ -39299,7 +39311,7 @@
         </is>
       </c>
       <c r="M376" s="4" t="n">
-        <v>-33.23</v>
+        <v>-33.22</v>
       </c>
       <c r="N376" s="4" t="n">
         <v>5.24</v>
@@ -39503,7 +39515,7 @@
         </is>
       </c>
       <c r="M378" s="4" t="n">
-        <v>10.19</v>
+        <v>10.2</v>
       </c>
       <c r="N378" s="4" t="n">
         <v>5.24</v>
@@ -39591,7 +39603,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>40.65</v>
+        <v>40.66</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -39605,13 +39617,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>27.25</v>
+        <v>27.26</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>40.65</v>
+        <v>40.66</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>0</v>
@@ -39642,10 +39654,10 @@
         <v>0</v>
       </c>
       <c r="AB379" s="4" t="n">
-        <v>70.31999999999999</v>
+        <v>70.33</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>29.68</v>
+        <v>29.67</v>
       </c>
       <c r="AD379" s="4" t="n">
         <v>0</v>
@@ -39693,7 +39705,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>17.36</v>
+        <v>17.37</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39707,13 +39719,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>11.39</v>
+        <v>11.4</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>17.36</v>
+        <v>17.37</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.61</v>
@@ -39791,13 +39803,13 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-3.74</v>
+        <v>-3.72</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -39805,13 +39817,13 @@
         </is>
       </c>
       <c r="M381" s="4" t="n">
-        <v>-8.98</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="N381" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O381" s="4" t="n">
-        <v>-3.47</v>
+        <v>-3.46</v>
       </c>
       <c r="P381" s="4" t="n">
         <v>0.72</v>
@@ -39848,10 +39860,10 @@
         <v>0</v>
       </c>
       <c r="AB381" s="4" t="n">
-        <v>47.08</v>
+        <v>47.09</v>
       </c>
       <c r="AC381" s="4" t="n">
-        <v>50.74</v>
+        <v>50.73</v>
       </c>
       <c r="AD381" s="4" t="n">
         <v>2.18</v>
@@ -39899,7 +39911,7 @@
         </is>
       </c>
       <c r="I382" s="4" t="n">
-        <v>-11.72</v>
+        <v>-11.71</v>
       </c>
       <c r="J382" s="4" t="n">
         <v>1.2</v>
@@ -39913,13 +39925,13 @@
         </is>
       </c>
       <c r="M382" s="4" t="n">
-        <v>-10.16</v>
+        <v>-10.15</v>
       </c>
       <c r="N382" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O382" s="4" t="n">
-        <v>-11.72</v>
+        <v>-11.71</v>
       </c>
       <c r="P382" s="4" t="n">
         <v>-2.01</v>
@@ -40015,7 +40027,7 @@
         </is>
       </c>
       <c r="M383" s="4" t="n">
-        <v>-38.62</v>
+        <v>-38.61</v>
       </c>
       <c r="N383" s="4" t="n">
         <v>5.24</v>
@@ -40215,7 +40227,7 @@
         </is>
       </c>
       <c r="M385" s="4" t="n">
-        <v>-18.44</v>
+        <v>-18.43</v>
       </c>
       <c r="N385" s="4" t="n">
         <v>5.24</v>
@@ -40303,7 +40315,7 @@
         </is>
       </c>
       <c r="I386" s="4" t="n">
-        <v>36.04</v>
+        <v>36.05</v>
       </c>
       <c r="J386" s="4" t="n">
         <v>100</v>
@@ -40317,13 +40329,13 @@
         </is>
       </c>
       <c r="M386" s="4" t="n">
-        <v>29.29</v>
+        <v>29.3</v>
       </c>
       <c r="N386" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O386" s="4" t="n">
-        <v>36.04</v>
+        <v>36.05</v>
       </c>
       <c r="P386" s="4" t="n">
         <v>0</v>
@@ -40405,13 +40417,13 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-21.61</v>
+        <v>-14.42</v>
       </c>
       <c r="J387" s="4" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="K387" s="4" t="n">
-        <v>99.8</v>
+        <v>99.3</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -40436,12 +40448,18 @@
       <c r="R387" s="4" t="n">
         <v>-26.62</v>
       </c>
-      <c r="S387" s="4" t="n"/>
-      <c r="T387" s="4" t="n"/>
+      <c r="S387" s="4" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="T387" s="4" t="n">
+        <v>41.1</v>
+      </c>
       <c r="U387" t="n">
-        <v>0</v>
-      </c>
-      <c r="V387" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V387" s="4" t="n">
+        <v>-7.4</v>
+      </c>
       <c r="W387" s="5" t="n">
         <v>297264</v>
       </c>
@@ -40456,10 +40474,10 @@
         <v>0</v>
       </c>
       <c r="AB387" s="4" t="n">
-        <v>39.19</v>
+        <v>42.79</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>60.81</v>
+        <v>57.21</v>
       </c>
       <c r="AD387" s="4" t="n">
         <v>0</v>
@@ -40503,7 +40521,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-23.25</v>
+        <v>-23.6</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40517,13 +40535,13 @@
         </is>
       </c>
       <c r="M388" s="4" t="n">
-        <v>-26.27</v>
+        <v>-26.62</v>
       </c>
       <c r="N388" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-23.25</v>
+        <v>-23.6</v>
       </c>
       <c r="P388" s="4" t="n">
         <v>-1.2</v>
@@ -40554,10 +40572,10 @@
         <v>0</v>
       </c>
       <c r="AB388" s="4" t="n">
-        <v>38.38</v>
+        <v>38.2</v>
       </c>
       <c r="AC388" s="4" t="n">
-        <v>61.62</v>
+        <v>61.8</v>
       </c>
       <c r="AD388" s="4" t="n">
         <v>0</v>
@@ -41013,7 +41031,7 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-13.76</v>
+        <v>-13.78</v>
       </c>
       <c r="J393" s="4" t="n">
         <v>0.8</v>
@@ -41033,10 +41051,10 @@
         <v>5.24</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>-14.74</v>
+        <v>-14.76</v>
       </c>
       <c r="P393" s="4" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="Q393" s="4" t="n">
         <v>-1.53</v>
@@ -41070,10 +41088,10 @@
         <v>0</v>
       </c>
       <c r="AB393" s="4" t="n">
-        <v>43.12</v>
+        <v>43.11</v>
       </c>
       <c r="AC393" s="4" t="n">
-        <v>56.88</v>
+        <v>56.89</v>
       </c>
       <c r="AD393" s="4" t="n">
         <v>0</v>
@@ -41168,10 +41186,10 @@
         <v>0</v>
       </c>
       <c r="AB394" s="4" t="n">
-        <v>39.55</v>
+        <v>39.54</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>60.45</v>
+        <v>60.46</v>
       </c>
       <c r="AD394" s="4" t="n">
         <v>0</v>
@@ -41521,7 +41539,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-40.67</v>
+        <v>-40.66</v>
       </c>
       <c r="J398" s="4" t="n">
         <v>0</v>
@@ -41535,13 +41553,13 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-44.2</v>
+        <v>-44.19</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O398" s="4" t="n">
-        <v>-40.67</v>
+        <v>-40.66</v>
       </c>
       <c r="P398" s="4" t="n">
         <v>0</v>
@@ -41619,7 +41637,7 @@
         </is>
       </c>
       <c r="I399" s="4" t="n">
-        <v>-12.41</v>
+        <v>-12.4</v>
       </c>
       <c r="J399" s="4" t="n">
         <v>1.1</v>
@@ -41633,13 +41651,13 @@
         </is>
       </c>
       <c r="M399" s="4" t="n">
-        <v>-19</v>
+        <v>-18.99</v>
       </c>
       <c r="N399" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O399" s="4" t="n">
-        <v>-12.41</v>
+        <v>-12.4</v>
       </c>
       <c r="P399" s="4" t="n">
         <v>0.88</v>
@@ -41721,7 +41739,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-15.49</v>
+        <v>-15.48</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>0.6</v>
@@ -41735,13 +41753,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-18.8</v>
+        <v>-18.79</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-15.49</v>
+        <v>-15.48</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -41823,7 +41841,7 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>-20.92</v>
+        <v>-20.91</v>
       </c>
       <c r="J401" s="4" t="n">
         <v>0.2</v>
@@ -41837,13 +41855,13 @@
         </is>
       </c>
       <c r="M401" s="4" t="n">
-        <v>-19.65</v>
+        <v>-19.64</v>
       </c>
       <c r="N401" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O401" s="4" t="n">
-        <v>-20.92</v>
+        <v>-20.91</v>
       </c>
       <c r="P401" s="4" t="n">
         <v>-1.91</v>
@@ -41925,7 +41943,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-13.45</v>
+        <v>-13.44</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>0.9</v>
@@ -41939,13 +41957,13 @@
         </is>
       </c>
       <c r="M402" s="4" t="n">
-        <v>-16.49</v>
+        <v>-16.48</v>
       </c>
       <c r="N402" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-13.45</v>
+        <v>-13.44</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.23</v>
@@ -42027,7 +42045,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-18.83</v>
+        <v>-18.82</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.3</v>
@@ -42041,13 +42059,13 @@
         </is>
       </c>
       <c r="M403" s="4" t="n">
-        <v>-18.57</v>
+        <v>-18.56</v>
       </c>
       <c r="N403" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-18.83</v>
+        <v>-18.82</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -42078,10 +42096,10 @@
         <v>0</v>
       </c>
       <c r="AB403" s="4" t="n">
-        <v>40.58</v>
+        <v>40.59</v>
       </c>
       <c r="AC403" s="4" t="n">
-        <v>59.42</v>
+        <v>59.41</v>
       </c>
       <c r="AD403" s="4" t="n">
         <v>0</v>
@@ -42129,7 +42147,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>40.93</v>
+        <v>40.94</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -42143,13 +42161,13 @@
         </is>
       </c>
       <c r="M404" s="4" t="n">
-        <v>30.76</v>
+        <v>30.77</v>
       </c>
       <c r="N404" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>40.93</v>
+        <v>40.94</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -42227,7 +42245,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-18.03</v>
+        <v>-18.02</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.4</v>
@@ -42241,13 +42259,13 @@
         </is>
       </c>
       <c r="M405" s="4" t="n">
-        <v>-21.27</v>
+        <v>-21.26</v>
       </c>
       <c r="N405" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-18.03</v>
+        <v>-18.02</v>
       </c>
       <c r="P405" s="4" t="n">
         <v>-2.83</v>
@@ -42278,10 +42296,10 @@
         <v>0</v>
       </c>
       <c r="AB405" s="4" t="n">
-        <v>40.98</v>
+        <v>40.99</v>
       </c>
       <c r="AC405" s="4" t="n">
-        <v>59.02</v>
+        <v>59.01</v>
       </c>
       <c r="AD405" s="4" t="n">
         <v>0</v>
@@ -42325,7 +42343,7 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-6.75</v>
+        <v>-6.74</v>
       </c>
       <c r="J406" s="4" t="n">
         <v>13.3</v>
@@ -42339,13 +42357,13 @@
         </is>
       </c>
       <c r="M406" s="4" t="n">
-        <v>-12.25</v>
+        <v>-12.24</v>
       </c>
       <c r="N406" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-6.75</v>
+        <v>-6.74</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.92</v>
@@ -42376,10 +42394,10 @@
         <v>0</v>
       </c>
       <c r="AB406" s="4" t="n">
-        <v>46.62</v>
+        <v>46.63</v>
       </c>
       <c r="AC406" s="4" t="n">
-        <v>53.38</v>
+        <v>53.37</v>
       </c>
       <c r="AD406" s="4" t="n">
         <v>0</v>
@@ -42423,7 +42441,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-13.14</v>
+        <v>-13.13</v>
       </c>
       <c r="J407" s="4" t="n">
         <v>0.9</v>
@@ -42437,13 +42455,13 @@
         </is>
       </c>
       <c r="M407" s="4" t="n">
-        <v>-16.93</v>
+        <v>-16.92</v>
       </c>
       <c r="N407" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-13.14</v>
+        <v>-13.13</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -42525,7 +42543,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-27.5</v>
+        <v>-27.49</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0</v>
@@ -42539,13 +42557,13 @@
         </is>
       </c>
       <c r="M408" s="4" t="n">
-        <v>-29.62</v>
+        <v>-29.61</v>
       </c>
       <c r="N408" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-27.5</v>
+        <v>-27.49</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -42576,10 +42594,10 @@
         <v>0</v>
       </c>
       <c r="AB408" s="4" t="n">
-        <v>36.25</v>
+        <v>36.26</v>
       </c>
       <c r="AC408" s="4" t="n">
-        <v>63.75</v>
+        <v>63.74</v>
       </c>
       <c r="AD408" s="4" t="n">
         <v>0</v>
@@ -42627,7 +42645,7 @@
         </is>
       </c>
       <c r="I409" s="4" t="n">
-        <v>-18.85</v>
+        <v>-18.84</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>0.3</v>
@@ -42641,13 +42659,13 @@
         </is>
       </c>
       <c r="M409" s="4" t="n">
-        <v>-18.57</v>
+        <v>-18.56</v>
       </c>
       <c r="N409" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O409" s="4" t="n">
-        <v>-18.85</v>
+        <v>-18.84</v>
       </c>
       <c r="P409" s="4" t="n">
         <v>0</v>
@@ -42678,10 +42696,10 @@
         <v>0</v>
       </c>
       <c r="AB409" s="4" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="AC409" s="4" t="n">
-        <v>59.43</v>
+        <v>59.42</v>
       </c>
       <c r="AD409" s="4" t="n">
         <v>0</v>
@@ -42729,7 +42747,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-40.8</v>
+        <v>-40.79</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -42743,13 +42761,13 @@
         </is>
       </c>
       <c r="M410" s="4" t="n">
-        <v>-42.22</v>
+        <v>-42.21</v>
       </c>
       <c r="N410" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-40.8</v>
+        <v>-40.79</v>
       </c>
       <c r="P410" s="4" t="n">
         <v>-2.49</v>
@@ -42831,7 +42849,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-19.73</v>
+        <v>-19.72</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.2</v>
@@ -42845,13 +42863,13 @@
         </is>
       </c>
       <c r="M411" s="4" t="n">
-        <v>-19.63</v>
+        <v>-19.62</v>
       </c>
       <c r="N411" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-19.73</v>
+        <v>-19.72</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.89</v>
@@ -42882,10 +42900,10 @@
         <v>0</v>
       </c>
       <c r="AB411" s="4" t="n">
-        <v>40.13</v>
+        <v>40.14</v>
       </c>
       <c r="AC411" s="4" t="n">
-        <v>59.87</v>
+        <v>59.86</v>
       </c>
       <c r="AD411" s="4" t="n">
         <v>0</v>
@@ -42933,7 +42951,7 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>-2.17</v>
+        <v>-2.16</v>
       </c>
       <c r="J412" s="4" t="n">
         <v>29.7</v>
@@ -42947,13 +42965,13 @@
         </is>
       </c>
       <c r="M412" s="4" t="n">
-        <v>-8.31</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N412" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>-1.65</v>
+        <v>-1.64</v>
       </c>
       <c r="P412" s="4" t="n">
         <v>-0.32</v>
@@ -42990,10 +43008,10 @@
         <v>0</v>
       </c>
       <c r="AB412" s="4" t="n">
-        <v>48.91</v>
+        <v>48.92</v>
       </c>
       <c r="AC412" s="4" t="n">
-        <v>51.09</v>
+        <v>51.08</v>
       </c>
       <c r="AD412" s="4" t="n">
         <v>0</v>
@@ -43041,7 +43059,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="n">
-        <v>36.48</v>
+        <v>36.49</v>
       </c>
       <c r="J413" s="4" t="n">
         <v>100</v>
@@ -43055,13 +43073,13 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>26.73</v>
+        <v>26.74</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O413" s="4" t="n">
-        <v>36.48</v>
+        <v>36.49</v>
       </c>
       <c r="P413" s="4" t="n">
         <v>0</v>
@@ -43143,7 +43161,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-14.92</v>
+        <v>-14.91</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>0.7</v>
@@ -43157,13 +43175,13 @@
         </is>
       </c>
       <c r="M414" s="4" t="n">
-        <v>-16.4</v>
+        <v>-16.39</v>
       </c>
       <c r="N414" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-14.92</v>
+        <v>-14.91</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>0</v>
@@ -43194,10 +43212,10 @@
         <v>0</v>
       </c>
       <c r="AB414" s="4" t="n">
-        <v>42.54</v>
+        <v>42.55</v>
       </c>
       <c r="AC414" s="4" t="n">
-        <v>57.46</v>
+        <v>57.45</v>
       </c>
       <c r="AD414" s="4" t="n">
         <v>0</v>
@@ -43245,7 +43263,7 @@
         </is>
       </c>
       <c r="I415" s="4" t="n">
-        <v>71.01000000000001</v>
+        <v>71.02</v>
       </c>
       <c r="J415" s="4" t="n">
         <v>100</v>
@@ -43259,13 +43277,13 @@
         </is>
       </c>
       <c r="M415" s="4" t="n">
-        <v>62.82</v>
+        <v>62.83</v>
       </c>
       <c r="N415" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>71.01000000000001</v>
+        <v>71.02</v>
       </c>
       <c r="P415" s="4" t="n">
         <v>0</v>
@@ -43343,7 +43361,7 @@
         </is>
       </c>
       <c r="I416" s="4" t="n">
-        <v>-42.84</v>
+        <v>-42.83</v>
       </c>
       <c r="J416" s="4" t="n">
         <v>0</v>
@@ -43357,13 +43375,13 @@
         </is>
       </c>
       <c r="M416" s="4" t="n">
-        <v>-46.58</v>
+        <v>-46.57</v>
       </c>
       <c r="N416" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>-42.84</v>
+        <v>-42.83</v>
       </c>
       <c r="P416" s="4" t="n">
         <v>-2.39</v>
@@ -43445,7 +43463,7 @@
         </is>
       </c>
       <c r="I417" s="4" t="n">
-        <v>49.15</v>
+        <v>49.16</v>
       </c>
       <c r="J417" s="4" t="n">
         <v>100</v>
@@ -43459,13 +43477,13 @@
         </is>
       </c>
       <c r="M417" s="4" t="n">
-        <v>36.57</v>
+        <v>36.58</v>
       </c>
       <c r="N417" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O417" s="4" t="n">
-        <v>49.15</v>
+        <v>49.16</v>
       </c>
       <c r="P417" s="4" t="n">
         <v>1.31</v>
@@ -43496,10 +43514,10 @@
         <v>0</v>
       </c>
       <c r="AB417" s="4" t="n">
-        <v>74.56999999999999</v>
+        <v>74.58</v>
       </c>
       <c r="AC417" s="4" t="n">
-        <v>25.43</v>
+        <v>25.42</v>
       </c>
       <c r="AD417" s="4" t="n">
         <v>0</v>
@@ -43543,7 +43561,7 @@
         </is>
       </c>
       <c r="I418" s="4" t="n">
-        <v>-12.41</v>
+        <v>-12.4</v>
       </c>
       <c r="J418" s="4" t="n">
         <v>1.1</v>
@@ -43557,13 +43575,13 @@
         </is>
       </c>
       <c r="M418" s="4" t="n">
-        <v>-16.91</v>
+        <v>-16.9</v>
       </c>
       <c r="N418" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O418" s="4" t="n">
-        <v>-12.41</v>
+        <v>-12.4</v>
       </c>
       <c r="P418" s="4" t="n">
         <v>-2.06</v>
@@ -43641,7 +43659,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-13.12</v>
+        <v>-13.11</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>0.9</v>
@@ -43655,13 +43673,13 @@
         </is>
       </c>
       <c r="M419" s="4" t="n">
-        <v>-17.49</v>
+        <v>-17.48</v>
       </c>
       <c r="N419" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-13.12</v>
+        <v>-13.11</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.8100000000000001</v>
@@ -43739,7 +43757,7 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-2.48</v>
+        <v>-2.47</v>
       </c>
       <c r="J420" s="4" t="n">
         <v>28.5</v>
@@ -43753,13 +43771,13 @@
         </is>
       </c>
       <c r="M420" s="4" t="n">
-        <v>-8.49</v>
+        <v>-8.48</v>
       </c>
       <c r="N420" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-2.04</v>
+        <v>-2.03</v>
       </c>
       <c r="P420" s="4" t="n">
         <v>-0.83</v>
@@ -43847,13 +43865,13 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-11.05</v>
+        <v>-11.04</v>
       </c>
       <c r="J421" s="4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K421" s="4" t="n">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -43861,13 +43879,13 @@
         </is>
       </c>
       <c r="M421" s="4" t="n">
-        <v>-11.82</v>
+        <v>-11.81</v>
       </c>
       <c r="N421" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-11.05</v>
+        <v>-11.04</v>
       </c>
       <c r="P421" s="4" t="n">
         <v>0</v>
@@ -43898,10 +43916,10 @@
         <v>0</v>
       </c>
       <c r="AB421" s="4" t="n">
-        <v>44.47</v>
+        <v>44.48</v>
       </c>
       <c r="AC421" s="4" t="n">
-        <v>55.53</v>
+        <v>55.52</v>
       </c>
       <c r="AD421" s="4" t="n">
         <v>0</v>
@@ -43949,7 +43967,7 @@
         </is>
       </c>
       <c r="I422" s="4" t="n">
-        <v>-14</v>
+        <v>-13.99</v>
       </c>
       <c r="J422" s="4" t="n">
         <v>0.8</v>
@@ -43963,13 +43981,13 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-18.05</v>
+        <v>-18.04</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O422" s="4" t="n">
-        <v>-14</v>
+        <v>-13.99</v>
       </c>
       <c r="P422" s="4" t="n">
         <v>0</v>
@@ -44000,10 +44018,10 @@
         <v>0</v>
       </c>
       <c r="AB422" s="4" t="n">
-        <v>43</v>
+        <v>43.01</v>
       </c>
       <c r="AC422" s="4" t="n">
-        <v>57</v>
+        <v>56.99</v>
       </c>
       <c r="AD422" s="4" t="n">
         <v>0</v>
@@ -44051,7 +44069,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-22.73</v>
+        <v>-22.72</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.1</v>
@@ -44065,13 +44083,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-19.17</v>
+        <v>-19.16</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-22.73</v>
+        <v>-22.72</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -44153,7 +44171,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-14</v>
+        <v>-13.99</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>0.8</v>
@@ -44167,13 +44185,13 @@
         </is>
       </c>
       <c r="M424" s="4" t="n">
-        <v>-16.41</v>
+        <v>-16.4</v>
       </c>
       <c r="N424" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-14</v>
+        <v>-13.99</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -44204,10 +44222,10 @@
         <v>0</v>
       </c>
       <c r="AB424" s="4" t="n">
-        <v>43</v>
+        <v>43.01</v>
       </c>
       <c r="AC424" s="4" t="n">
-        <v>57</v>
+        <v>56.99</v>
       </c>
       <c r="AD424" s="4" t="n">
         <v>0</v>
@@ -44255,7 +44273,7 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>12.75</v>
+        <v>12.87</v>
       </c>
       <c r="J425" s="4" t="n">
         <v>99</v>
@@ -44269,13 +44287,13 @@
         </is>
       </c>
       <c r="M425" s="4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="N425" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O425" s="4" t="n">
-        <v>20.03</v>
+        <v>20.04</v>
       </c>
       <c r="P425" s="4" t="n">
         <v>0.34</v>
@@ -44312,10 +44330,10 @@
         <v>0</v>
       </c>
       <c r="AB425" s="4" t="n">
-        <v>56.38</v>
+        <v>56.43</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>43.62</v>
+        <v>43.57</v>
       </c>
       <c r="AD425" s="4" t="n">
         <v>0</v>
@@ -44363,7 +44381,7 @@
         </is>
       </c>
       <c r="I426" s="4" t="n">
-        <v>53.94</v>
+        <v>53.95</v>
       </c>
       <c r="J426" s="4" t="n">
         <v>100</v>
@@ -44377,13 +44395,13 @@
         </is>
       </c>
       <c r="M426" s="4" t="n">
-        <v>39.09</v>
+        <v>39.1</v>
       </c>
       <c r="N426" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O426" s="4" t="n">
-        <v>53.94</v>
+        <v>53.95</v>
       </c>
       <c r="P426" s="4" t="n">
         <v>0</v>
@@ -44461,7 +44479,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>61.56</v>
+        <v>61.57</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -44475,13 +44493,13 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>54.8</v>
+        <v>54.81</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>61.56</v>
+        <v>61.57</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>0.21</v>
@@ -44563,7 +44581,7 @@
         </is>
       </c>
       <c r="I428" s="4" t="n">
-        <v>-18.88</v>
+        <v>-18.87</v>
       </c>
       <c r="J428" s="4" t="n">
         <v>0.3</v>
@@ -44577,13 +44595,13 @@
         </is>
       </c>
       <c r="M428" s="4" t="n">
-        <v>-17.33</v>
+        <v>-17.32</v>
       </c>
       <c r="N428" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O428" s="4" t="n">
-        <v>-18.29</v>
+        <v>-18.28</v>
       </c>
       <c r="P428" s="4" t="n">
         <v>-1.61</v>
@@ -44614,10 +44632,10 @@
         <v>0</v>
       </c>
       <c r="AB428" s="4" t="n">
-        <v>39.61</v>
+        <v>39.62</v>
       </c>
       <c r="AC428" s="4" t="n">
-        <v>58.05</v>
+        <v>58.04</v>
       </c>
       <c r="AD428" s="4" t="n">
         <v>2.34</v>
@@ -44661,7 +44679,7 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="J429" s="4" t="n">
         <v>8.4</v>
@@ -44675,13 +44693,13 @@
         </is>
       </c>
       <c r="M429" s="4" t="n">
-        <v>-12.17</v>
+        <v>-12.16</v>
       </c>
       <c r="N429" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.72</v>
@@ -44712,10 +44730,10 @@
         <v>0</v>
       </c>
       <c r="AB429" s="4" t="n">
-        <v>45.8</v>
+        <v>45.81</v>
       </c>
       <c r="AC429" s="4" t="n">
-        <v>54.2</v>
+        <v>54.19</v>
       </c>
       <c r="AD429" s="4" t="n">
         <v>0</v>
@@ -44759,7 +44777,7 @@
         </is>
       </c>
       <c r="I430" s="4" t="n">
-        <v>46.03</v>
+        <v>46.04</v>
       </c>
       <c r="J430" s="4" t="n">
         <v>100</v>
@@ -44773,13 +44791,13 @@
         </is>
       </c>
       <c r="M430" s="4" t="n">
-        <v>40.96</v>
+        <v>40.97</v>
       </c>
       <c r="N430" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O430" s="4" t="n">
-        <v>46.03</v>
+        <v>46.04</v>
       </c>
       <c r="P430" s="4" t="n">
         <v>0</v>
@@ -44810,10 +44828,10 @@
         <v>0</v>
       </c>
       <c r="AB430" s="4" t="n">
-        <v>73.01000000000001</v>
+        <v>73.02</v>
       </c>
       <c r="AC430" s="4" t="n">
-        <v>26.99</v>
+        <v>26.98</v>
       </c>
       <c r="AD430" s="4" t="n">
         <v>0</v>
@@ -44861,7 +44879,7 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>8.33</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="J431" s="4" t="n">
         <v>91.5</v>
@@ -44875,13 +44893,13 @@
         </is>
       </c>
       <c r="M431" s="4" t="n">
-        <v>-1.59</v>
+        <v>-1.58</v>
       </c>
       <c r="N431" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O431" s="4" t="n">
-        <v>11.1</v>
+        <v>11.11</v>
       </c>
       <c r="P431" s="4" t="n">
         <v>0.14</v>
@@ -44918,10 +44936,10 @@
         <v>0</v>
       </c>
       <c r="AB431" s="4" t="n">
-        <v>54.17</v>
+        <v>54.18</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>45.83</v>
+        <v>45.82</v>
       </c>
       <c r="AD431" s="4" t="n">
         <v>0</v>
@@ -44965,13 +44983,13 @@
         </is>
       </c>
       <c r="I432" s="4" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -44979,13 +44997,13 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-4.09</v>
+        <v>-4.08</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O432" s="4" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="P432" s="4" t="n">
         <v>0.08</v>
@@ -45067,7 +45085,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-16.05</v>
+        <v>-16.04</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.5</v>
@@ -45081,13 +45099,13 @@
         </is>
       </c>
       <c r="M433" s="4" t="n">
-        <v>-19.2</v>
+        <v>-19.19</v>
       </c>
       <c r="N433" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-16.05</v>
+        <v>-16.04</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>0</v>
@@ -45118,10 +45136,10 @@
         <v>0</v>
       </c>
       <c r="AB433" s="4" t="n">
-        <v>41.97</v>
+        <v>41.98</v>
       </c>
       <c r="AC433" s="4" t="n">
-        <v>58.03</v>
+        <v>58.02</v>
       </c>
       <c r="AD433" s="4" t="n">
         <v>0</v>
@@ -45169,7 +45187,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>71.11</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -45183,13 +45201,13 @@
         </is>
       </c>
       <c r="M434" s="4" t="n">
-        <v>63.58</v>
+        <v>63.59</v>
       </c>
       <c r="N434" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>71.11</v>
       </c>
       <c r="P434" s="4" t="n">
         <v>1.49</v>
@@ -45267,7 +45285,7 @@
         </is>
       </c>
       <c r="I435" s="4" t="n">
-        <v>-14.14</v>
+        <v>-14.13</v>
       </c>
       <c r="J435" s="4" t="n">
         <v>0.8</v>
@@ -45281,13 +45299,13 @@
         </is>
       </c>
       <c r="M435" s="4" t="n">
-        <v>-16.65</v>
+        <v>-16.64</v>
       </c>
       <c r="N435" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O435" s="4" t="n">
-        <v>-13.59</v>
+        <v>-13.58</v>
       </c>
       <c r="P435" s="4" t="n">
         <v>-2.01</v>
@@ -45773,7 +45791,7 @@
         </is>
       </c>
       <c r="I440" s="4" t="n">
-        <v>-3.19</v>
+        <v>-3.18</v>
       </c>
       <c r="J440" s="4" t="n">
         <v>25.8</v>
@@ -45793,10 +45811,10 @@
         <v>5.24</v>
       </c>
       <c r="O440" s="4" t="n">
-        <v>-4.28</v>
+        <v>-4.26</v>
       </c>
       <c r="P440" s="4" t="n">
-        <v>-0.39</v>
+        <v>-0.37</v>
       </c>
       <c r="Q440" s="4" t="n">
         <v>-5.6</v>
@@ -45830,10 +45848,10 @@
         <v>0</v>
       </c>
       <c r="AB440" s="4" t="n">
-        <v>48.4</v>
+        <v>48.41</v>
       </c>
       <c r="AC440" s="4" t="n">
-        <v>51.6</v>
+        <v>51.59</v>
       </c>
       <c r="AD440" s="4" t="n">
         <v>0</v>
@@ -45881,13 +45899,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>71</v>
+        <v>71.3</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -45938,10 +45956,10 @@
         <v>0</v>
       </c>
       <c r="AB441" s="4" t="n">
-        <v>51.18</v>
+        <v>51.21</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>48.82</v>
+        <v>48.79</v>
       </c>
       <c r="AD441" s="4" t="n">
         <v>0</v>
@@ -46907,7 +46925,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>36.25</v>
+        <v>36.24</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -46921,13 +46939,13 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>36.23</v>
+        <v>36.21</v>
       </c>
       <c r="P451" s="4" t="n">
         <v>1.84</v>
@@ -46964,10 +46982,10 @@
         <v>0</v>
       </c>
       <c r="AB451" s="4" t="n">
-        <v>68.13</v>
+        <v>68.12</v>
       </c>
       <c r="AC451" s="4" t="n">
-        <v>31.87</v>
+        <v>31.88</v>
       </c>
       <c r="AD451" s="4" t="n">
         <v>0</v>
@@ -47219,13 +47237,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>5.64</v>
+        <v>5.68</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47276,10 +47294,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>52.82</v>
+        <v>52.84</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>47.18</v>
+        <v>47.16</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -47425,7 +47443,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-23.15</v>
+        <v>-23.2</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47482,10 +47500,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>38.42</v>
+        <v>38.4</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>61.58</v>
+        <v>61.6</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -48043,13 +48061,13 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-4.03</v>
+        <v>-4.02</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -48253,7 +48271,7 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="J464" s="4" t="n">
         <v>77</v>
@@ -48267,13 +48285,13 @@
         </is>
       </c>
       <c r="M464" s="4" t="n">
-        <v>-5.93</v>
+        <v>-5.92</v>
       </c>
       <c r="N464" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O464" s="4" t="n">
-        <v>5.77</v>
+        <v>5.78</v>
       </c>
       <c r="P464" s="4" t="n">
         <v>0.09</v>
@@ -48310,10 +48328,10 @@
         <v>0</v>
       </c>
       <c r="AB464" s="4" t="n">
-        <v>51.96</v>
+        <v>51.97</v>
       </c>
       <c r="AC464" s="4" t="n">
-        <v>48.04</v>
+        <v>48.03</v>
       </c>
       <c r="AD464" s="4" t="n">
         <v>0</v>
@@ -48361,7 +48379,7 @@
         </is>
       </c>
       <c r="I465" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="J465" s="4" t="n">
         <v>100</v>
@@ -48375,13 +48393,13 @@
         </is>
       </c>
       <c r="M465" s="4" t="n">
-        <v>53.61</v>
+        <v>53.62</v>
       </c>
       <c r="N465" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O465" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="P465" s="4" t="n">
         <v>2.31</v>
@@ -48565,7 +48583,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-18.75</v>
+        <v>-18.74</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.3</v>
@@ -48585,7 +48603,7 @@
         <v>5.24</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-17.94</v>
+        <v>-17.93</v>
       </c>
       <c r="P467" s="4" t="n">
         <v>-1.76</v>
@@ -48622,10 +48640,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>40.62</v>
+        <v>40.63</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>59.38</v>
+        <v>59.37</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48720,10 +48738,10 @@
         <v>0</v>
       </c>
       <c r="AB468" s="4" t="n">
-        <v>40.68</v>
+        <v>40.69</v>
       </c>
       <c r="AC468" s="4" t="n">
-        <v>59.32</v>
+        <v>59.31</v>
       </c>
       <c r="AD468" s="4" t="n">
         <v>0</v>
@@ -48785,7 +48803,7 @@
         </is>
       </c>
       <c r="M469" s="4" t="n">
-        <v>-15.57</v>
+        <v>-15.56</v>
       </c>
       <c r="N469" s="4" t="n">
         <v>5.24</v>
@@ -49073,7 +49091,7 @@
         </is>
       </c>
       <c r="I472" s="4" t="n">
-        <v>-42.25</v>
+        <v>-42.26</v>
       </c>
       <c r="J472" s="4" t="n">
         <v>0</v>
@@ -49087,13 +49105,13 @@
         </is>
       </c>
       <c r="M472" s="4" t="n">
-        <v>-44.5</v>
+        <v>-44.52</v>
       </c>
       <c r="N472" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O472" s="4" t="n">
-        <v>-42.25</v>
+        <v>-42.26</v>
       </c>
       <c r="P472" s="4" t="n">
         <v>-2.34</v>
@@ -49124,10 +49142,10 @@
         <v>0</v>
       </c>
       <c r="AB472" s="4" t="n">
-        <v>28.88</v>
+        <v>28.87</v>
       </c>
       <c r="AC472" s="4" t="n">
-        <v>71.12</v>
+        <v>71.13</v>
       </c>
       <c r="AD472" s="4" t="n">
         <v>0</v>
@@ -49175,13 +49193,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.75</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49189,16 +49207,16 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.62</v>
+        <v>-10.68</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-1.96</v>
+        <v>-2.04</v>
       </c>
       <c r="P473" s="4" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="Q473" s="4" t="n">
         <v>4.11</v>
@@ -49232,10 +49250,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.41</v>
+        <v>45.39</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.59</v>
+        <v>46.61</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49279,7 +49297,7 @@
         </is>
       </c>
       <c r="I474" s="4" t="n">
-        <v>-20.45</v>
+        <v>-20.51</v>
       </c>
       <c r="J474" s="4" t="n">
         <v>0.2</v>
@@ -49293,13 +49311,13 @@
         </is>
       </c>
       <c r="M474" s="4" t="n">
-        <v>-26.28</v>
+        <v>-26.29</v>
       </c>
       <c r="N474" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O474" s="4" t="n">
-        <v>-23.79</v>
+        <v>-23.8</v>
       </c>
       <c r="P474" s="4" t="n">
         <v>-3.2</v>
@@ -49336,10 +49354,10 @@
         <v>0</v>
       </c>
       <c r="AB474" s="4" t="n">
-        <v>39.78</v>
+        <v>39.74</v>
       </c>
       <c r="AC474" s="4" t="n">
-        <v>60.22</v>
+        <v>60.26</v>
       </c>
       <c r="AD474" s="4" t="n">
         <v>0</v>
@@ -49713,13 +49731,13 @@
         </is>
       </c>
       <c r="M478" s="4" t="n">
-        <v>-8.630000000000001</v>
+        <v>-8.65</v>
       </c>
       <c r="N478" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O478" s="4" t="n">
-        <v>-4.33</v>
+        <v>-4.35</v>
       </c>
       <c r="P478" s="4" t="n">
         <v>0.21</v>
@@ -49756,10 +49774,10 @@
         <v>0</v>
       </c>
       <c r="AB478" s="4" t="n">
-        <v>47.27</v>
+        <v>47.26</v>
       </c>
       <c r="AC478" s="4" t="n">
-        <v>52.73</v>
+        <v>52.74</v>
       </c>
       <c r="AD478" s="4" t="n">
         <v>0</v>
@@ -49827,7 +49845,7 @@
         <v>5.24</v>
       </c>
       <c r="O479" s="4" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="P479" s="4" t="n">
         <v>1.71</v>
@@ -49911,13 +49929,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1.97</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>31.9</v>
+        <v>30.5</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -49925,13 +49943,13 @@
         </is>
       </c>
       <c r="M480" s="4" t="n">
-        <v>-7.45</v>
+        <v>-7.43</v>
       </c>
       <c r="N480" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O480" s="4" t="n">
-        <v>-3.93</v>
+        <v>-3.91</v>
       </c>
       <c r="P480" s="4" t="n">
         <v>-0.08</v>
@@ -49943,16 +49961,16 @@
         <v>-13.45</v>
       </c>
       <c r="S480" s="4" t="n">
-        <v>47.49</v>
+        <v>46.39</v>
       </c>
       <c r="T480" s="4" t="n">
-        <v>47.08</v>
+        <v>47.27</v>
       </c>
       <c r="U480" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V480" s="4" t="n">
-        <v>0.1</v>
+        <v>-1.05</v>
       </c>
       <c r="W480" s="5" t="n">
         <v>6276527</v>
@@ -49968,10 +49986,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.91</v>
+        <v>47.73</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.46</v>
+        <v>49.64</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -50019,7 +50037,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-25.38</v>
+        <v>-25.41</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0.1</v>
@@ -50074,7 +50092,7 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>37.31</v>
+        <v>37.29</v>
       </c>
       <c r="AA481" s="4" t="n">
         <v>0.1</v>
@@ -50083,7 +50101,7 @@
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>62.69</v>
+        <v>62.71</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -50539,7 +50557,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>30.15</v>
+        <v>30.17</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -50596,10 +50614,10 @@
         <v>0</v>
       </c>
       <c r="AB486" s="4" t="n">
-        <v>65.06999999999999</v>
+        <v>65.08</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>34.93</v>
+        <v>34.92</v>
       </c>
       <c r="AD486" s="4" t="n">
         <v>0</v>
@@ -50647,13 +50665,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>31</v>
+        <v>31.6</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50667,7 +50685,7 @@
         <v>5.24</v>
       </c>
       <c r="O487" s="4" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="P487" s="4" t="n">
         <v>0</v>
@@ -50679,16 +50697,16 @@
         <v>7.09</v>
       </c>
       <c r="S487" s="4" t="n">
-        <v>49.99</v>
+        <v>49.75</v>
       </c>
       <c r="T487" s="4" t="n">
-        <v>44.89</v>
+        <v>44.91</v>
       </c>
       <c r="U487" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V487" s="4" t="n">
-        <v>4.57</v>
+        <v>3.7</v>
       </c>
       <c r="W487" s="5" t="n">
         <v>0</v>
@@ -50704,10 +50722,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>50.92</v>
+        <v>50.85</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>49.08</v>
+        <v>49.15</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -50751,13 +50769,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -50771,10 +50789,10 @@
         <v>5.24</v>
       </c>
       <c r="O488" s="4" t="n">
-        <v>7.35</v>
+        <v>7.37</v>
       </c>
       <c r="P488" s="4" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="Q488" s="4" t="n">
         <v>0.44</v>
@@ -50808,10 +50826,10 @@
         <v>0</v>
       </c>
       <c r="AB488" s="4" t="n">
-        <v>51.24</v>
+        <v>51.26</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>48.76</v>
+        <v>48.74</v>
       </c>
       <c r="AD488" s="4" t="n">
         <v>0</v>
@@ -50855,13 +50873,13 @@
         </is>
       </c>
       <c r="I489" s="4" t="n">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
       <c r="J489" s="4" t="n">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="K489" s="4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
@@ -50869,16 +50887,16 @@
         </is>
       </c>
       <c r="M489" s="4" t="n">
-        <v>6.91</v>
+        <v>6.93</v>
       </c>
       <c r="N489" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O489" s="4" t="n">
-        <v>11.37</v>
+        <v>11.38</v>
       </c>
       <c r="P489" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q489" s="4" t="n">
         <v>0</v>
@@ -50912,10 +50930,10 @@
         <v>0</v>
       </c>
       <c r="AB489" s="4" t="n">
-        <v>54.88</v>
+        <v>54.89</v>
       </c>
       <c r="AC489" s="4" t="n">
-        <v>45.12</v>
+        <v>45.11</v>
       </c>
       <c r="AD489" s="4" t="n">
         <v>0</v>
@@ -51071,7 +51089,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-25.54</v>
+        <v>-25.66</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0.1</v>
@@ -51126,16 +51144,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.03</v>
+        <v>14.05</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>28.38</v>
+        <v>28.31</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.93</v>
+        <v>53.98</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51179,7 +51197,7 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>6.17</v>
+        <v>6.16</v>
       </c>
       <c r="J492" s="4" t="n">
         <v>84.8</v>
@@ -51290,10 +51308,10 @@
         <v>-3.68</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51345,7 +51363,7 @@
         <v>48.16</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
@@ -51395,7 +51413,7 @@
         </is>
       </c>
       <c r="I494" s="4" t="n">
-        <v>7.21</v>
+        <v>7.22</v>
       </c>
       <c r="J494" s="4" t="n">
         <v>88.2</v>
@@ -51415,7 +51433,7 @@
         <v>5.24</v>
       </c>
       <c r="O494" s="4" t="n">
-        <v>9.59</v>
+        <v>9.58</v>
       </c>
       <c r="P494" s="4" t="n">
         <v>0.75</v>
@@ -51707,13 +51725,13 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="J497" s="4" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="K497" s="4" t="n">
-        <v>63</v>
+        <v>63.1</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -51927,7 +51945,7 @@
         </is>
       </c>
       <c r="M499" s="4" t="n">
-        <v>12.61</v>
+        <v>12.62</v>
       </c>
       <c r="N499" s="4" t="n">
         <v>5.24</v>
@@ -51964,10 +51982,10 @@
         <v>0</v>
       </c>
       <c r="AB499" s="4" t="n">
-        <v>60.76</v>
+        <v>60.77</v>
       </c>
       <c r="AC499" s="4" t="n">
-        <v>39.24</v>
+        <v>39.23</v>
       </c>
       <c r="AD499" s="4" t="n">
         <v>0</v>
@@ -52015,7 +52033,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>23.35</v>
+        <v>23.39</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -52072,10 +52090,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.68</v>
+        <v>61.7</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.32</v>
+        <v>38.3</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -52119,13 +52137,13 @@
         </is>
       </c>
       <c r="I501" s="4" t="n">
-        <v>-8.09</v>
+        <v>-8.06</v>
       </c>
       <c r="J501" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K501" s="4" t="n">
-        <v>90.8</v>
+        <v>90.7</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -52176,10 +52194,10 @@
         <v>0</v>
       </c>
       <c r="AB501" s="4" t="n">
-        <v>45.09</v>
+        <v>45.11</v>
       </c>
       <c r="AC501" s="4" t="n">
-        <v>53.04</v>
+        <v>53.02</v>
       </c>
       <c r="AD501" s="4" t="n">
         <v>1.87</v>
@@ -52227,13 +52245,13 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-19.07</v>
+        <v>-20.84</v>
       </c>
       <c r="J502" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K502" s="4" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -52259,19 +52277,19 @@
         <v>-29.98</v>
       </c>
       <c r="S502" s="4" t="n">
-        <v>39.47</v>
+        <v>35.08</v>
       </c>
       <c r="T502" s="4" t="n">
-        <v>44.25</v>
+        <v>52.22</v>
       </c>
       <c r="U502" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V502" s="4" t="n">
-        <v>-7.78</v>
+        <v>-16.07</v>
       </c>
       <c r="W502" s="5" t="n">
-        <v>228295</v>
+        <v>0</v>
       </c>
       <c r="X502" s="5" t="n">
         <v>3176451</v>
@@ -52282,16 +52300,16 @@
         </is>
       </c>
       <c r="Z502" s="4" t="n">
-        <v>40.47</v>
+        <v>39.58</v>
       </c>
       <c r="AA502" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AB502" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC502" s="4" t="n">
-        <v>59.53</v>
+        <v>60.42</v>
       </c>
       <c r="AD502" s="4" t="n">
         <v>0</v>
@@ -52437,13 +52455,13 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="K504" s="4" t="n">
-        <v>33.1</v>
+        <v>32.7</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -52451,13 +52469,13 @@
         </is>
       </c>
       <c r="M504" s="4" t="n">
-        <v>-10.24</v>
+        <v>-10.25</v>
       </c>
       <c r="N504" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="P504" s="4" t="n">
         <v>1.51</v>
@@ -52469,16 +52487,16 @@
         <v>-13.88</v>
       </c>
       <c r="S504" s="4" t="n">
-        <v>47.39</v>
+        <v>47.44</v>
       </c>
       <c r="T504" s="4" t="n">
-        <v>45.41</v>
+        <v>45.38</v>
       </c>
       <c r="U504" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V504" s="4" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="W504" s="5" t="n">
         <v>68555930</v>
@@ -52494,10 +52512,10 @@
         <v>0</v>
       </c>
       <c r="AB504" s="4" t="n">
-        <v>49.64</v>
+        <v>49.68</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>48.35</v>
+        <v>48.31</v>
       </c>
       <c r="AD504" s="4" t="n">
         <v>2.01</v>
@@ -52745,7 +52763,7 @@
         </is>
       </c>
       <c r="I507" s="4" t="n">
-        <v>-42.94</v>
+        <v>-43</v>
       </c>
       <c r="J507" s="4" t="n">
         <v>0</v>
@@ -52765,10 +52783,10 @@
         <v>5.24</v>
       </c>
       <c r="O507" s="4" t="n">
-        <v>-42.94</v>
+        <v>-43</v>
       </c>
       <c r="P507" s="4" t="n">
-        <v>-2.6</v>
+        <v>-2.65</v>
       </c>
       <c r="Q507" s="4" t="n">
         <v>0</v>
@@ -52796,10 +52814,10 @@
         <v>0</v>
       </c>
       <c r="AB507" s="4" t="n">
-        <v>28.53</v>
+        <v>28.5</v>
       </c>
       <c r="AC507" s="4" t="n">
-        <v>71.47</v>
+        <v>71.5</v>
       </c>
       <c r="AD507" s="4" t="n">
         <v>0</v>
@@ -53331,7 +53349,7 @@
         <v>38</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -53377,7 +53395,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="K9" t="n">
         <v>16</v>
@@ -53389,7 +53407,7 @@
         <v>21</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>52</v>
+        <v>52.3</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -53667,7 +53685,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>122.1</v>
+        <v>122.2</v>
       </c>
       <c r="K14" t="n">
         <v>126</v>
@@ -54259,7 +54277,7 @@
         <v>62</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -55117,7 +55135,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>84</v>
@@ -55129,7 +55147,7 @@
         <v>112</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -55245,7 +55263,7 @@
         <v>79</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -55593,7 +55611,7 @@
         <v>53</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -56161,7 +56179,7 @@
         </is>
       </c>
       <c r="J57" s="4" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="K57" t="n">
         <v>28</v>
@@ -56173,7 +56191,7 @@
         <v>35</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>90.3</v>
+        <v>89.7</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -56219,7 +56237,7 @@
         </is>
       </c>
       <c r="J58" s="4" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="K58" t="n">
         <v>13</v>
@@ -56231,7 +56249,7 @@
         <v>15</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -56393,7 +56411,7 @@
         </is>
       </c>
       <c r="J61" s="4" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="K61" t="n">
         <v>39</v>
@@ -57031,7 +57049,7 @@
         </is>
       </c>
       <c r="J72" s="4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K72" t="n">
         <v>8</v>
@@ -57089,7 +57107,7 @@
         </is>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K73" t="n">
         <v>5</v>
@@ -57739,7 +57757,7 @@
         <v>64</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="C8" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>50.2</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.7</v>
+        <v>232.3</v>
       </c>
       <c r="C9" t="n">
-        <v>202.3</v>
+        <v>202.7</v>
       </c>
       <c r="D9" t="n">
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>82.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.4</v>
+        <v>-3.18</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>39.1</v>
+        <v>40.5</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>60.9</v>
+        <v>59.5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -4067,23 +4067,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Toby Doeden</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Larry Rhoden</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>REP</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-25.16</v>
+        <v>-25.8</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -4097,13 +4101,13 @@
         <v>5.27</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-25.16</v>
+        <v>-25.8</v>
       </c>
       <c r="P32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
       <c r="R32" s="4" t="n">
         <v>-29.98</v>
@@ -4128,10 +4132,10 @@
         <v>0</v>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>37.42</v>
+        <v>37.1</v>
       </c>
       <c r="AC32" s="4" t="n">
-        <v>62.58</v>
+        <v>62.9</v>
       </c>
       <c r="AD32" s="4" t="n">
         <v>0</v>
@@ -4701,13 +4705,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.38</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28.6</v>
+        <v>28.9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4715,13 +4719,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.6</v>
+        <v>-2.51</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.27</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.18</v>
+        <v>-1.09</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.13</v>
@@ -4756,16 +4760,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.77</v>
+        <v>48.81</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>28.6</v>
+        <v>28.9</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.23</v>
+        <v>51.19</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -24705,7 +24709,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.55</v>
+        <v>30.6</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24803,13 +24807,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-3.97</v>
+        <v>-3.85</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>37.4</v>
+        <v>37.8</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -28293,7 +28297,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.79</v>
+        <v>-6.77</v>
       </c>
       <c r="J269" s="4" t="n">
         <v>13.2</v>
@@ -28307,13 +28311,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.21</v>
+        <v>-12.18</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.27</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.07</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28350,10 +28354,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.6</v>
+        <v>46.62</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.4</v>
+        <v>53.38</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28401,7 +28405,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.8</v>
+        <v>-33.77</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28415,13 +28419,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.17</v>
+        <v>-31.14</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.27</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.8</v>
+        <v>-33.77</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28452,10 +28456,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.1</v>
+        <v>33.11</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.89</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -40521,7 +40525,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-23.56</v>
+        <v>-23.71</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40535,13 +40539,13 @@
         </is>
       </c>
       <c r="M388" s="4" t="n">
-        <v>-26.61</v>
+        <v>-26.76</v>
       </c>
       <c r="N388" s="4" t="n">
         <v>5.27</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-23.56</v>
+        <v>-23.71</v>
       </c>
       <c r="P388" s="4" t="n">
         <v>-1.2</v>
@@ -40572,10 +40576,10 @@
         <v>0</v>
       </c>
       <c r="AB388" s="4" t="n">
-        <v>38.22</v>
+        <v>38.15</v>
       </c>
       <c r="AC388" s="4" t="n">
-        <v>61.78</v>
+        <v>61.85</v>
       </c>
       <c r="AD388" s="4" t="n">
         <v>0</v>
@@ -40808,7 +40812,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Joel Hawn</t>
+          <t>Anna Golladay</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -40827,7 +40831,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>-35.61</v>
+        <v>-35.05</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>0</v>
@@ -40847,10 +40851,10 @@
         <v>5.27</v>
       </c>
       <c r="O391" s="4" t="n">
-        <v>-35.61</v>
+        <v>-35.05</v>
       </c>
       <c r="P391" s="4" t="n">
-        <v>-2.9</v>
+        <v>-2.34</v>
       </c>
       <c r="Q391" s="4" t="n">
         <v>-3.43</v>
@@ -40865,7 +40869,7 @@
       </c>
       <c r="V391" s="4" t="n"/>
       <c r="W391" s="5" t="n">
-        <v>140</v>
+        <v>55555</v>
       </c>
       <c r="X391" s="5" t="n">
         <v>2330803</v>
@@ -40878,10 +40882,10 @@
         <v>0</v>
       </c>
       <c r="AB391" s="4" t="n">
-        <v>32.19</v>
+        <v>32.47</v>
       </c>
       <c r="AC391" s="4" t="n">
-        <v>67.81</v>
+        <v>67.53</v>
       </c>
       <c r="AD391" s="4" t="n">
         <v>0</v>
@@ -41017,27 +41021,23 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Andy Ogles</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
+          <t>Charlie Hatcher</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>REP</t>
-        </is>
-      </c>
       <c r="I393" s="4" t="n">
-        <v>-13.76</v>
+        <v>-13.11</v>
       </c>
       <c r="J393" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K393" s="4" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -41051,34 +41051,28 @@
         <v>5.27</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>-14.72</v>
+        <v>-13.11</v>
       </c>
       <c r="P393" s="4" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="Q393" s="4" t="n">
-        <v>-1.53</v>
+        <v>0</v>
       </c>
       <c r="R393" s="4" t="n">
         <v>-23.39</v>
       </c>
-      <c r="S393" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="T393" s="4" t="n">
-        <v>47</v>
-      </c>
+      <c r="S393" s="4" t="n"/>
+      <c r="T393" s="4" t="n"/>
       <c r="U393" t="n">
-        <v>1</v>
-      </c>
-      <c r="V393" s="4" t="n">
-        <v>-9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V393" s="4" t="n"/>
       <c r="W393" s="5" t="n">
         <v>2599775</v>
       </c>
       <c r="X393" s="5" t="n">
-        <v>613135</v>
+        <v>719503</v>
       </c>
       <c r="Y393" t="inlineStr"/>
       <c r="Z393" s="4" t="n">
@@ -41088,10 +41082,10 @@
         <v>0</v>
       </c>
       <c r="AB393" s="4" t="n">
-        <v>43.12</v>
+        <v>43.45</v>
       </c>
       <c r="AC393" s="4" t="n">
-        <v>56.88</v>
+        <v>56.55</v>
       </c>
       <c r="AD393" s="4" t="n">
         <v>0</v>
@@ -41120,12 +41114,12 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Chaney Mosley</t>
+          <t>Mike Croley</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Van Hilleary</t>
+          <t>Johnny Garrett</t>
         </is>
       </c>
       <c r="G394" t="inlineStr"/>
@@ -41135,7 +41129,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-20.87</v>
+        <v>-21.31</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>0.2</v>
@@ -41155,10 +41149,10 @@
         <v>5.27</v>
       </c>
       <c r="O394" s="4" t="n">
-        <v>-20.87</v>
+        <v>-21.31</v>
       </c>
       <c r="P394" s="4" t="n">
-        <v>-1.63</v>
+        <v>-2.07</v>
       </c>
       <c r="Q394" s="4" t="n">
         <v>0</v>
@@ -41173,10 +41167,10 @@
       </c>
       <c r="V394" s="4" t="n"/>
       <c r="W394" s="5" t="n">
-        <v>86869</v>
+        <v>35380</v>
       </c>
       <c r="X394" s="5" t="n">
-        <v>1552429</v>
+        <v>2380327</v>
       </c>
       <c r="Y394" t="inlineStr"/>
       <c r="Z394" s="4" t="n">
@@ -41186,10 +41180,10 @@
         <v>0</v>
       </c>
       <c r="AB394" s="4" t="n">
-        <v>39.57</v>
+        <v>39.35</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>60.43</v>
+        <v>60.65</v>
       </c>
       <c r="AD394" s="4" t="n">
         <v>0</v>
@@ -41320,7 +41314,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>William Wicker</t>
+          <t>Heidi Kuhn</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -41339,13 +41333,13 @@
         </is>
       </c>
       <c r="I396" s="4" t="n">
-        <v>-18.63</v>
+        <v>-21.06</v>
       </c>
       <c r="J396" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K396" s="4" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -41359,10 +41353,10 @@
         <v>5.27</v>
       </c>
       <c r="O396" s="4" t="n">
-        <v>-18.63</v>
+        <v>-21.06</v>
       </c>
       <c r="P396" s="4" t="n">
-        <v>0</v>
+        <v>-2.43</v>
       </c>
       <c r="Q396" s="4" t="n">
         <v>-5.48</v>
@@ -41377,7 +41371,7 @@
       </c>
       <c r="V396" s="4" t="n"/>
       <c r="W396" s="5" t="n">
-        <v>0</v>
+        <v>39805</v>
       </c>
       <c r="X396" s="5" t="n">
         <v>2232874</v>
@@ -41390,10 +41384,10 @@
         <v>0</v>
       </c>
       <c r="AB396" s="4" t="n">
-        <v>40.68</v>
+        <v>39.47</v>
       </c>
       <c r="AC396" s="4" t="n">
-        <v>59.32</v>
+        <v>60.53</v>
       </c>
       <c r="AD396" s="4" t="n">
         <v>0</v>
@@ -49193,13 +49187,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>47.6</v>
+        <v>48.5</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>52.4</v>
+        <v>51.5</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49207,13 +49201,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.67</v>
+        <v>-10.62</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.27</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.95</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.34</v>
@@ -49250,10 +49244,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.4</v>
+        <v>45.42</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.6</v>
+        <v>46.58</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -51089,7 +51083,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-25.58</v>
+        <v>-25.45</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0.1</v>
@@ -51144,16 +51138,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.05</v>
+        <v>14.07</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>28.36</v>
+        <v>28.41</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.93</v>
+        <v>53.86</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -52245,7 +52239,7 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-20.83</v>
+        <v>-20.93</v>
       </c>
       <c r="J502" s="4" t="n">
         <v>0.2</v>
@@ -52259,13 +52253,13 @@
         </is>
       </c>
       <c r="M502" s="4" t="n">
-        <v>-22.2</v>
+        <v>-22.36</v>
       </c>
       <c r="N502" s="4" t="n">
         <v>5.27</v>
       </c>
       <c r="O502" s="4" t="n">
-        <v>-23.41</v>
+        <v>-23.57</v>
       </c>
       <c r="P502" s="4" t="n">
         <v>-1.06</v>
@@ -52300,7 +52294,7 @@
         </is>
       </c>
       <c r="Z502" s="4" t="n">
-        <v>39.59</v>
+        <v>39.53</v>
       </c>
       <c r="AA502" s="4" t="n">
         <v>0.2</v>
@@ -52309,7 +52303,7 @@
         <v>0</v>
       </c>
       <c r="AC502" s="4" t="n">
-        <v>60.41</v>
+        <v>60.47</v>
       </c>
       <c r="AD502" s="4" t="n">
         <v>0</v>
@@ -57049,7 +57043,7 @@
         </is>
       </c>
       <c r="J72" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K72" t="n">
         <v>8</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-08-08 · evaluated at 0 days to election (actual: 87 days out)</t>
+          <t>Data as of 2026-08-09 · evaluated at 0 days to election (actual: 86 days out)</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="C8" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.5</v>
+        <v>232.6</v>
       </c>
       <c r="C9" t="n">
-        <v>202.5</v>
+        <v>202.4</v>
       </c>
       <c r="D9" t="n">
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>81.2</v>
+        <v>81.7</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>34.1</v>
+        <v>35.4</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.72</v>
+        <v>-3.22</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>39.9</v>
+        <v>40.4</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>60.1</v>
+        <v>59.6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>44.19</v>
+        <v>44.18</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>47.81</v>
+        <v>47.82</v>
       </c>
       <c r="AD2" s="4" t="n">
         <v>8</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-17.47</v>
+        <v>-17.51</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.4</v>
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>41.26</v>
+        <v>41.24</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>58.74</v>
+        <v>58.76</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>90.5</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>27.36</v>
+        <v>27.38</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>63.68</v>
+        <v>63.69</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>36.32</v>
+        <v>36.31</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.7</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>51.34</v>
+        <v>51.33</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>48.66</v>
+        <v>48.67</v>
       </c>
       <c r="AD10" s="4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>29.63</v>
+        <v>29.65</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>64.81</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>35.19</v>
+        <v>35.18</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2656,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>54.35</v>
+        <v>54.34</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>42.44</v>
+        <v>42.45</v>
       </c>
       <c r="AD18" s="4" t="n">
         <v>0</v>
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.64</v>
+        <v>10.65</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>55.32</v>
+        <v>55.33</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>44.68</v>
+        <v>44.67</v>
       </c>
       <c r="AD19" s="4" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.77</v>
+        <v>12.76</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>99</v>
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>56.39</v>
+        <v>56.38</v>
       </c>
       <c r="AC20" s="4" t="n">
-        <v>43.61</v>
+        <v>43.62</v>
       </c>
       <c r="AD20" s="4" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.71</v>
+        <v>-10.72</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>2.5</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>44.65</v>
+        <v>44.64</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>55.35</v>
+        <v>55.36</v>
       </c>
       <c r="AD22" s="4" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.29</v>
+        <v>7.33</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>53.65</v>
+        <v>53.66</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>46.35</v>
+        <v>46.34</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>0</v>
@@ -3239,13 +3239,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>49.96</v>
+        <v>49.98</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>50.04</v>
+        <v>50.02</v>
       </c>
       <c r="AD24" s="4" t="n">
         <v>0</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.29</v>
+        <v>-3.3</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25.4</v>
@@ -3657,13 +3657,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>52.34</v>
+        <v>52.35</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>47.66</v>
+        <v>47.65</v>
       </c>
       <c r="AD28" s="4" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.83</v>
+        <v>19.84</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.8</v>
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-10.51</v>
+        <v>-10.5</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>3</v>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.94</v>
+        <v>-6.96</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>46.53</v>
+        <v>46.52</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>53.47</v>
+        <v>53.48</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-19.66</v>
+        <v>-19.73</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.2</v>
@@ -4452,10 +4452,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>40.17</v>
+        <v>40.13</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>59.83</v>
+        <v>59.87</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>70.09999999999999</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>51.05</v>
+        <v>51.06</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>48.95</v>
+        <v>48.94</v>
       </c>
       <c r="AD36" s="4" t="n">
         <v>0</v>
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.47</v>
+        <v>-2.34</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4719,13 +4719,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.71</v>
+        <v>-2.55</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.22</v>
+        <v>-1.06</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.06</v>
@@ -4760,16 +4760,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.76</v>
+        <v>48.83</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.24</v>
+        <v>51.17</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-27.11</v>
+        <v>-27.13</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-30.09</v>
+        <v>-30.11</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-27.11</v>
+        <v>-27.13</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>-1.75</v>
@@ -4864,10 +4864,10 @@
         <v>0</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>36.44</v>
+        <v>36.43</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>63.56</v>
+        <v>63.57</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>-2.03</v>
+        <v>-2.04</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>30.2</v>
@@ -4929,13 +4929,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.32</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-1.27</v>
+        <v>-1.29</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>-0.45</v>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-40.08</v>
+        <v>-40.1</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -5037,13 +5037,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-40.85</v>
+        <v>-40.87</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-40.08</v>
+        <v>-40.1</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>-2.23</v>
@@ -5074,10 +5074,10 @@
         <v>0</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>29.96</v>
+        <v>29.95</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>70.04000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="AD41" s="4" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-60.26</v>
+        <v>-60.28</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -5139,13 +5139,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-61.1</v>
+        <v>-61.12</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-60.26</v>
+        <v>-60.28</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>-2.1</v>
@@ -5176,10 +5176,10 @@
         <v>0</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>19.87</v>
+        <v>19.86</v>
       </c>
       <c r="AC42" s="4" t="n">
-        <v>80.13</v>
+        <v>80.14</v>
       </c>
       <c r="AD42" s="4" t="n">
         <v>0</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-22.18</v>
+        <v>-22.2</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0.1</v>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-24.65</v>
+        <v>-24.67</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-22.18</v>
+        <v>-22.2</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>-0.59</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>38.91</v>
+        <v>38.9</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>61.09</v>
+        <v>61.1</v>
       </c>
       <c r="AD43" s="4" t="n">
         <v>0</v>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-28.29</v>
+        <v>-28.31</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5343,13 +5343,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-30.17</v>
+        <v>-30.19</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-28.29</v>
+        <v>-28.31</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>-2.14</v>
@@ -5380,10 +5380,10 @@
         <v>0</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>35.86</v>
+        <v>35.85</v>
       </c>
       <c r="AC44" s="4" t="n">
-        <v>64.14</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="AD44" s="4" t="n">
         <v>0</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>33.54</v>
+        <v>33.52</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>100</v>
@@ -5445,13 +5445,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>24.07</v>
+        <v>24.05</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>33.54</v>
+        <v>33.52</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>0</v>
@@ -5482,10 +5482,10 @@
         <v>0</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>66.77</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="AC45" s="4" t="n">
-        <v>33.23</v>
+        <v>33.24</v>
       </c>
       <c r="AD45" s="4" t="n">
         <v>0</v>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>-42.56</v>
+        <v>-42.57</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>0</v>
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>-41.26</v>
+        <v>-41.28</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>-42.56</v>
+        <v>-42.57</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>-1.62</v>
@@ -5584,10 +5584,10 @@
         <v>0</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>28.72</v>
+        <v>28.71</v>
       </c>
       <c r="AC46" s="4" t="n">
-        <v>71.28</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="AD46" s="4" t="n">
         <v>0</v>
@@ -5635,13 +5635,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>-7.67</v>
+        <v>-7.7</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>89.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -5649,13 +5649,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-12.06</v>
+        <v>-12.07</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>-9.41</v>
+        <v>-9.43</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>-0.99</v>
@@ -5692,10 +5692,10 @@
         <v>0</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>46.17</v>
+        <v>46.15</v>
       </c>
       <c r="AC47" s="4" t="n">
-        <v>53.83</v>
+        <v>53.85</v>
       </c>
       <c r="AD47" s="4" t="n">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>-25.42</v>
+        <v>-25.43</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>0.1</v>
@@ -5757,13 +5757,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>-22.25</v>
+        <v>-22.26</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-25.42</v>
+        <v>-25.43</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>-1.82</v>
@@ -5794,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>37.29</v>
+        <v>37.28</v>
       </c>
       <c r="AC48" s="4" t="n">
-        <v>62.71</v>
+        <v>62.72</v>
       </c>
       <c r="AD48" s="4" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>-38.67</v>
+        <v>-38.69</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>0</v>
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>-35.62</v>
+        <v>-35.63</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>-38.67</v>
+        <v>-38.69</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>-2.88</v>
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6108,10 +6108,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>49.93</v>
+        <v>49.94</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>50.07</v>
+        <v>50.06</v>
       </c>
       <c r="AD51" s="4" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19.53</v>
+        <v>19.54</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>99.7</v>
@@ -6895,7 +6895,7 @@
         <v>5.28</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>19.53</v>
+        <v>19.54</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0.21</v>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.97</v>
+        <v>27.98</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>5.28</v>
@@ -7028,10 +7028,10 @@
         <v>0</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>66.8</v>
+        <v>66.81</v>
       </c>
       <c r="AC60" s="4" t="n">
-        <v>33.2</v>
+        <v>33.19</v>
       </c>
       <c r="AD60" s="4" t="n">
         <v>0</v>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-18.09</v>
+        <v>-18.08</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>5.28</v>
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12.68</v>
+        <v>12.69</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>99</v>
@@ -7405,7 +7405,7 @@
         <v>5.28</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12.68</v>
+        <v>12.69</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>-0.35</v>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>5.28</v>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>100</v>
@@ -7603,13 +7603,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>39.32</v>
+        <v>39.33</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>49.26</v>
+        <v>49.27</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>1.66</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>71.58</v>
+        <v>71.59</v>
       </c>
       <c r="AC68" s="4" t="n">
-        <v>28.42</v>
+        <v>28.41</v>
       </c>
       <c r="AD68" s="4" t="n">
         <v>0</v>
@@ -7905,13 +7905,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>74.18000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>79.15000000000001</v>
+        <v>79.16</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>80.93000000000001</v>
+        <v>80.94</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>5.28</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>99.90000000000001</v>
@@ -8115,7 +8115,7 @@
         <v>5.28</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0.46</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>53.95</v>
+        <v>53.96</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>5.28</v>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>59.91</v>
+        <v>59.92</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>100</v>
@@ -8417,7 +8417,7 @@
         <v>5.28</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>59.91</v>
+        <v>59.92</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>45.3</v>
+        <v>45.31</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>5.28</v>
@@ -8550,10 +8550,10 @@
         <v>0</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>74.63</v>
+        <v>74.64</v>
       </c>
       <c r="AC75" s="4" t="n">
-        <v>25.37</v>
+        <v>25.36</v>
       </c>
       <c r="AD75" s="4" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>44.2</v>
+        <v>44.21</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>100</v>
@@ -8615,13 +8615,13 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>35.23</v>
+        <v>35.24</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>44.2</v>
+        <v>44.21</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>2.1</v>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>49.56</v>
+        <v>49.57</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>100</v>
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.79</v>
+        <v>38.8</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>5.28</v>
@@ -8754,10 +8754,10 @@
         <v>0</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>72.04000000000001</v>
+        <v>72.05</v>
       </c>
       <c r="AC77" s="4" t="n">
-        <v>24.3</v>
+        <v>24.29</v>
       </c>
       <c r="AD77" s="4" t="n">
         <v>3.66</v>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-28.34</v>
+        <v>-28.33</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -8825,7 +8825,7 @@
         <v>5.28</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-28.34</v>
+        <v>-28.33</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.51</v>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.93</v>
+        <v>11.94</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>5.28</v>
@@ -8958,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>60.58</v>
+        <v>60.59</v>
       </c>
       <c r="AC79" s="4" t="n">
-        <v>39.42</v>
+        <v>39.41</v>
       </c>
       <c r="AD79" s="4" t="n">
         <v>0</v>
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.84</v>
+        <v>5.86</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>52.92</v>
+        <v>52.93</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47.08</v>
+        <v>47.07</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-16.59</v>
+        <v>-16.58</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>5.28</v>
@@ -9168,10 +9168,10 @@
         <v>0</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>41.94</v>
+        <v>41.95</v>
       </c>
       <c r="AC81" s="4" t="n">
-        <v>58.06</v>
+        <v>58.05</v>
       </c>
       <c r="AD81" s="4" t="n">
         <v>0</v>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>26.08</v>
+        <v>26.09</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>100</v>
@@ -9439,7 +9439,7 @@
         <v>5.28</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>26.08</v>
+        <v>26.09</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.63</v>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>27.09</v>
+        <v>27.1</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>100</v>
@@ -9541,7 +9541,7 @@
         <v>5.28</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>27.09</v>
+        <v>27.1</v>
       </c>
       <c r="P85" s="4" t="n">
         <v>1.74</v>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>40.04</v>
+        <v>40.05</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9637,13 +9637,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.93</v>
+        <v>29.94</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>40.04</v>
+        <v>40.05</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.23</v>
@@ -9739,13 +9739,13 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.49</v>
+        <v>41.5</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>53.61</v>
+        <v>53.62</v>
       </c>
       <c r="P87" s="4" t="n">
         <v>0</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>75.97</v>
+        <v>75.98</v>
       </c>
       <c r="AC88" s="4" t="n">
-        <v>24.03</v>
+        <v>24.02</v>
       </c>
       <c r="AD88" s="4" t="n">
         <v>0</v>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.32</v>
+        <v>16.33</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>99.5</v>
@@ -9943,13 +9943,13 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>18.03</v>
+        <v>18.04</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>16.32</v>
+        <v>16.33</v>
       </c>
       <c r="P89" s="4" t="n">
         <v>1.31</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>30.05</v>
+        <v>30.06</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>5.28</v>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28.63</v>
+        <v>28.64</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>100</v>
@@ -10147,13 +10147,13 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>16.4</v>
+        <v>16.41</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28.63</v>
+        <v>28.64</v>
       </c>
       <c r="P91" s="4" t="n">
         <v>0</v>
@@ -10249,13 +10249,13 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.96</v>
+        <v>58.97</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>68.05</v>
+        <v>68.06</v>
       </c>
       <c r="P92" s="4" t="n">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26.54</v>
+        <v>26.55</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>100</v>
@@ -10357,7 +10357,7 @@
         <v>5.28</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>26.54</v>
+        <v>26.55</v>
       </c>
       <c r="P93" s="4" t="n">
         <v>2.03</v>
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.55</v>
+        <v>43.56</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>5.28</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>75.66</v>
+        <v>75.67</v>
       </c>
       <c r="AC94" s="4" t="n">
-        <v>24.34</v>
+        <v>24.33</v>
       </c>
       <c r="AD94" s="4" t="n">
         <v>0</v>
@@ -10561,7 +10561,7 @@
         <v>5.28</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>76.81</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -10639,7 +10639,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>26.26</v>
+        <v>26.27</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>100</v>
@@ -10653,13 +10653,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="n">
-        <v>19.11</v>
+        <v>19.12</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>26.26</v>
+        <v>26.27</v>
       </c>
       <c r="P96" s="4" t="n">
         <v>0</v>
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="M97" s="4" t="n">
-        <v>16.13</v>
+        <v>16.14</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>5.28</v>
@@ -10792,10 +10792,10 @@
         <v>0</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>62.78</v>
+        <v>62.79</v>
       </c>
       <c r="AC97" s="4" t="n">
-        <v>37.22</v>
+        <v>37.21</v>
       </c>
       <c r="AD97" s="4" t="n">
         <v>0</v>
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="n">
-        <v>-10.09</v>
+        <v>-10.08</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>-4.45</v>
+        <v>-4.44</v>
       </c>
       <c r="P98" s="4" t="n">
         <v>0</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>31.39</v>
+        <v>31.4</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -10959,13 +10959,13 @@
         </is>
       </c>
       <c r="M99" s="4" t="n">
-        <v>19.67</v>
+        <v>19.68</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>31.39</v>
+        <v>31.4</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.64</v>
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26.49</v>
+        <v>26.5</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>100</v>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M100" s="4" t="n">
-        <v>16.91</v>
+        <v>16.92</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>26.49</v>
+        <v>26.5</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1.69</v>
@@ -11149,7 +11149,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>63.71</v>
+        <v>63.72</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>100</v>
@@ -11163,13 +11163,13 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>56.88</v>
+        <v>56.89</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>63.71</v>
+        <v>63.72</v>
       </c>
       <c r="P101" s="4" t="n">
         <v>0</v>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>59.14</v>
+        <v>59.15</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11271,7 +11271,7 @@
         <v>5.28</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>59.14</v>
+        <v>59.15</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>1.93</v>
@@ -11367,7 +11367,7 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>8.35</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N103" s="4" t="n">
         <v>5.28</v>
@@ -11404,10 +11404,10 @@
         <v>0</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>60.26</v>
+        <v>60.27</v>
       </c>
       <c r="AC103" s="4" t="n">
-        <v>39.74</v>
+        <v>39.73</v>
       </c>
       <c r="AD103" s="4" t="n">
         <v>0</v>
@@ -11506,10 +11506,10 @@
         <v>0</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>69.81999999999999</v>
+        <v>69.83</v>
       </c>
       <c r="AC104" s="4" t="n">
-        <v>30.18</v>
+        <v>30.17</v>
       </c>
       <c r="AD104" s="4" t="n">
         <v>0</v>
@@ -11655,13 +11655,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>7.05</v>
+        <v>7.14</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>87.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.72</v>
+        <v>5.73</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>5.28</v>
@@ -11712,10 +11712,10 @@
         <v>0</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>53.52</v>
+        <v>53.57</v>
       </c>
       <c r="AC106" s="4" t="n">
-        <v>46.48</v>
+        <v>46.43</v>
       </c>
       <c r="AD106" s="4" t="n">
         <v>0</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="M107" s="4" t="n">
-        <v>14.64</v>
+        <v>14.65</v>
       </c>
       <c r="N107" s="4" t="n">
         <v>5.28</v>
@@ -11814,10 +11814,10 @@
         <v>0</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>61.09</v>
+        <v>61.1</v>
       </c>
       <c r="AC107" s="4" t="n">
-        <v>38.91</v>
+        <v>38.9</v>
       </c>
       <c r="AD107" s="4" t="n">
         <v>0</v>
@@ -11916,10 +11916,10 @@
         <v>0</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>63.23</v>
+        <v>63.24</v>
       </c>
       <c r="AC108" s="4" t="n">
-        <v>36.77</v>
+        <v>36.76</v>
       </c>
       <c r="AD108" s="4" t="n">
         <v>0</v>
@@ -11967,7 +11967,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27.69</v>
+        <v>27.7</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -11981,13 +11981,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.53</v>
+        <v>21.54</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>27.69</v>
+        <v>27.7</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12120,10 +12120,10 @@
         <v>0</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>69.97</v>
+        <v>69.98</v>
       </c>
       <c r="AC110" s="4" t="n">
-        <v>30.03</v>
+        <v>30.02</v>
       </c>
       <c r="AD110" s="4" t="n">
         <v>0</v>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>-2.48</v>
+        <v>-2.47</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>28.5</v>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>-6.19</v>
+        <v>-6.2</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15.1</v>
@@ -12638,10 +12638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>46.91</v>
+        <v>46.9</v>
       </c>
       <c r="AC115" s="4" t="n">
-        <v>53.09</v>
+        <v>53.1</v>
       </c>
       <c r="AD115" s="4" t="n">
         <v>0</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="M120" s="4" t="n">
-        <v>9.48</v>
+        <v>9.49</v>
       </c>
       <c r="N120" s="4" t="n">
         <v>5.28</v>
@@ -13199,7 +13199,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>28.74</v>
+        <v>28.75</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>100</v>
@@ -13219,7 +13219,7 @@
         <v>5.28</v>
       </c>
       <c r="O121" s="4" t="n">
-        <v>28.74</v>
+        <v>28.75</v>
       </c>
       <c r="P121" s="4" t="n">
         <v>2.19</v>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>35.2</v>
+        <v>35.21</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>100</v>
@@ -13321,7 +13321,7 @@
         <v>5.28</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>35.2</v>
+        <v>35.21</v>
       </c>
       <c r="P122" s="4" t="n">
         <v>2.02</v>
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>15.65</v>
+        <v>15.66</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>99.40000000000001</v>
@@ -13423,7 +13423,7 @@
         <v>5.28</v>
       </c>
       <c r="O123" s="4" t="n">
-        <v>15.65</v>
+        <v>15.66</v>
       </c>
       <c r="P123" s="4" t="n">
         <v>1.9</v>
@@ -13705,7 +13705,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>-13.38</v>
+        <v>-13.33</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>0.9</v>
@@ -13762,10 +13762,10 @@
         <v>0</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>43.31</v>
+        <v>43.34</v>
       </c>
       <c r="AC126" s="4" t="n">
-        <v>56.69</v>
+        <v>56.66</v>
       </c>
       <c r="AD126" s="4" t="n">
         <v>0</v>
@@ -14221,7 +14221,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>-4.02</v>
+        <v>-4.03</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>22.7</v>
@@ -14329,13 +14329,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-10.39</v>
+        <v>-10.37</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -14386,10 +14386,10 @@
         <v>0</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>44.8</v>
+        <v>44.81</v>
       </c>
       <c r="AC132" s="4" t="n">
-        <v>55.2</v>
+        <v>55.19</v>
       </c>
       <c r="AD132" s="4" t="n">
         <v>0</v>
@@ -14844,10 +14844,10 @@
         <v>-5.2</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -15749,13 +15749,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>62.7</v>
+        <v>62.6</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -15806,10 +15806,10 @@
         <v>0</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>49.87</v>
+        <v>49.89</v>
       </c>
       <c r="AC146" s="4" t="n">
-        <v>50.13</v>
+        <v>50.11</v>
       </c>
       <c r="AD146" s="4" t="n">
         <v>0</v>
@@ -16057,13 +16057,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>7.05</v>
+        <v>7.04</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>-8.48</v>
+        <v>-8.49</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>8.1</v>
@@ -16493,13 +16493,13 @@
         </is>
       </c>
       <c r="M153" s="4" t="n">
-        <v>-11.55</v>
+        <v>-11.56</v>
       </c>
       <c r="N153" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>-8.48</v>
+        <v>-8.49</v>
       </c>
       <c r="P153" s="4" t="n">
         <v>-1.91</v>
@@ -16785,7 +16785,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>65.47</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>100</v>
@@ -16805,7 +16805,7 @@
         <v>5.28</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>65.47</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="P156" s="4" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="M157" s="4" t="n">
-        <v>76.70999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="N157" s="4" t="n">
         <v>5.28</v>
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-29.66</v>
+        <v>-29.67</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>0</v>
@@ -17207,13 +17207,13 @@
         </is>
       </c>
       <c r="M160" s="4" t="n">
-        <v>-26.27</v>
+        <v>-26.28</v>
       </c>
       <c r="N160" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O160" s="4" t="n">
-        <v>-29.66</v>
+        <v>-29.67</v>
       </c>
       <c r="P160" s="4" t="n">
         <v>-2.36</v>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="M161" s="4" t="n">
-        <v>-30.59</v>
+        <v>-30.6</v>
       </c>
       <c r="N161" s="4" t="n">
         <v>5.28</v>
@@ -17505,7 +17505,7 @@
         </is>
       </c>
       <c r="M163" s="4" t="n">
-        <v>-19.96</v>
+        <v>-19.97</v>
       </c>
       <c r="N163" s="4" t="n">
         <v>5.28</v>
@@ -18099,7 +18099,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11.37</v>
+        <v>11.39</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>98.7</v>
@@ -18113,7 +18113,7 @@
         </is>
       </c>
       <c r="M169" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="N169" s="4" t="n">
         <v>5.28</v>
@@ -18156,10 +18156,10 @@
         <v>0</v>
       </c>
       <c r="AB169" s="4" t="n">
-        <v>55.69</v>
+        <v>55.7</v>
       </c>
       <c r="AC169" s="4" t="n">
-        <v>44.31</v>
+        <v>44.3</v>
       </c>
       <c r="AD169" s="4" t="n">
         <v>0</v>
@@ -18203,7 +18203,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>66</v>
@@ -18325,7 +18325,7 @@
         </is>
       </c>
       <c r="M171" s="4" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="N171" s="4" t="n">
         <v>5.28</v>
@@ -18466,10 +18466,10 @@
         <v>0</v>
       </c>
       <c r="AB172" s="4" t="n">
-        <v>39.55</v>
+        <v>39.54</v>
       </c>
       <c r="AC172" s="4" t="n">
-        <v>60.45</v>
+        <v>60.46</v>
       </c>
       <c r="AD172" s="4" t="n">
         <v>0</v>
@@ -18517,7 +18517,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-29.37</v>
+        <v>-29.57</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18574,10 +18574,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>35.32</v>
+        <v>35.22</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>64.68000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-27.9</v>
+        <v>-27.91</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0</v>
@@ -18639,13 +18639,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-26.03</v>
+        <v>-26.04</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-27.9</v>
+        <v>-27.91</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>30.95</v>
+        <v>31.22</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>100</v>
@@ -19082,10 +19082,10 @@
         <v>0</v>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>65.47</v>
+        <v>65.61</v>
       </c>
       <c r="AC178" s="4" t="n">
-        <v>34.53</v>
+        <v>34.39</v>
       </c>
       <c r="AD178" s="4" t="n">
         <v>0</v>
@@ -20855,13 +20855,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-11.06</v>
+        <v>-11.13</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -20912,10 +20912,10 @@
         <v>0</v>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>44.47</v>
+        <v>44.43</v>
       </c>
       <c r="AC196" s="4" t="n">
-        <v>55.53</v>
+        <v>55.57</v>
       </c>
       <c r="AD196" s="4" t="n">
         <v>0</v>
@@ -22281,13 +22281,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-6.76</v>
+        <v>-6.79</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -22338,10 +22338,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.62</v>
+        <v>46.61</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.38</v>
+        <v>53.39</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="M217" s="4" t="n">
-        <v>17.51</v>
+        <v>17.52</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>5.28</v>
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>33.95</v>
+        <v>33.96</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -23109,13 +23109,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>27.46</v>
+        <v>27.47</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>33.95</v>
+        <v>33.96</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -23197,7 +23197,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>32.51</v>
+        <v>32.52</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>100</v>
@@ -23211,13 +23211,13 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>22.96</v>
+        <v>22.97</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>32.51</v>
+        <v>32.52</v>
       </c>
       <c r="P219" s="4" t="n">
         <v>2.52</v>
@@ -23248,10 +23248,10 @@
         <v>0</v>
       </c>
       <c r="AB219" s="4" t="n">
-        <v>66.25</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="AC219" s="4" t="n">
-        <v>33.75</v>
+        <v>33.74</v>
       </c>
       <c r="AD219" s="4" t="n">
         <v>0</v>
@@ -23299,7 +23299,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>30.01</v>
+        <v>30.02</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>100</v>
@@ -23313,13 +23313,13 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.78</v>
+        <v>23.79</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O220" s="4" t="n">
-        <v>30.01</v>
+        <v>30.02</v>
       </c>
       <c r="P220" s="4" t="n">
         <v>0</v>
@@ -23401,7 +23401,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>55.63</v>
+        <v>55.64</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>100</v>
@@ -23415,13 +23415,13 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>49.14</v>
+        <v>49.15</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O221" s="4" t="n">
-        <v>55.63</v>
+        <v>55.64</v>
       </c>
       <c r="P221" s="4" t="n">
         <v>0</v>
@@ -23452,10 +23452,10 @@
         <v>0</v>
       </c>
       <c r="AB221" s="4" t="n">
-        <v>77.81</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="AC221" s="4" t="n">
-        <v>22.19</v>
+        <v>22.18</v>
       </c>
       <c r="AD221" s="4" t="n">
         <v>0</v>
@@ -23499,7 +23499,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>28.77</v>
+        <v>28.78</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>100</v>
@@ -23513,13 +23513,13 @@
         </is>
       </c>
       <c r="M222" s="4" t="n">
-        <v>23.99</v>
+        <v>24</v>
       </c>
       <c r="N222" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O222" s="4" t="n">
-        <v>28.77</v>
+        <v>28.78</v>
       </c>
       <c r="P222" s="4" t="n">
         <v>0</v>
@@ -23550,10 +23550,10 @@
         <v>0</v>
       </c>
       <c r="AB222" s="4" t="n">
-        <v>64.38</v>
+        <v>64.39</v>
       </c>
       <c r="AC222" s="4" t="n">
-        <v>35.62</v>
+        <v>35.61</v>
       </c>
       <c r="AD222" s="4" t="n">
         <v>0</v>
@@ -23601,7 +23601,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>76.42</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -23615,13 +23615,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>69.15000000000001</v>
+        <v>69.16</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>76.42</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -23703,7 +23703,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>45.74</v>
+        <v>45.75</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>100</v>
@@ -23723,7 +23723,7 @@
         <v>5.28</v>
       </c>
       <c r="O224" s="4" t="n">
-        <v>45.74</v>
+        <v>45.75</v>
       </c>
       <c r="P224" s="4" t="n">
         <v>0</v>
@@ -23805,7 +23805,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.77</v>
+        <v>22.78</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23819,13 +23819,13 @@
         </is>
       </c>
       <c r="M225" s="4" t="n">
-        <v>14.03</v>
+        <v>14.04</v>
       </c>
       <c r="N225" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.77</v>
+        <v>22.78</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.53</v>
@@ -24715,7 +24715,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.61</v>
+        <v>30.7</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>22.15</v>
+        <v>22.14</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.28</v>
@@ -24766,10 +24766,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.35</v>
+        <v>62.34</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.65</v>
+        <v>32.66</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24813,13 +24813,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.09</v>
+        <v>-4.43</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>37</v>
+        <v>36.1</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>63</v>
+        <v>63.9</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-9</v>
+        <v>-9.01</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.28</v>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>-13.47</v>
+        <v>-13.46</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>0.9</v>
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="M236" s="4" t="n">
-        <v>-18.11</v>
+        <v>-18.1</v>
       </c>
       <c r="N236" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O236" s="4" t="n">
-        <v>-13.47</v>
+        <v>-13.46</v>
       </c>
       <c r="P236" s="4" t="n">
         <v>-0.61</v>
@@ -25023,7 +25023,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>-28.41</v>
+        <v>-28.4</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>0</v>
@@ -25037,13 +25037,13 @@
         </is>
       </c>
       <c r="M237" s="4" t="n">
-        <v>-26.77</v>
+        <v>-26.76</v>
       </c>
       <c r="N237" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O237" s="4" t="n">
-        <v>-28.41</v>
+        <v>-28.4</v>
       </c>
       <c r="P237" s="4" t="n">
         <v>-1.9</v>
@@ -25125,7 +25125,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>20.98</v>
+        <v>20.99</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25139,13 +25139,13 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>20.98</v>
+        <v>20.99</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>0.96</v>
@@ -25241,13 +25241,13 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-2.27</v>
+        <v>-2.26</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-2.73</v>
+        <v>-2.72</v>
       </c>
       <c r="P239" s="4" t="n">
         <v>-0.28</v>
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-26.19</v>
+        <v>-26.18</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0</v>
@@ -25349,13 +25349,13 @@
         </is>
       </c>
       <c r="M240" s="4" t="n">
-        <v>-23.48</v>
+        <v>-23.47</v>
       </c>
       <c r="N240" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-26.19</v>
+        <v>-26.18</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.12</v>
@@ -25386,10 +25386,10 @@
         <v>0</v>
       </c>
       <c r="AB240" s="4" t="n">
-        <v>36.9</v>
+        <v>36.91</v>
       </c>
       <c r="AC240" s="4" t="n">
-        <v>63.1</v>
+        <v>63.09</v>
       </c>
       <c r="AD240" s="4" t="n">
         <v>0</v>
@@ -25437,7 +25437,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>37.97</v>
+        <v>37.98</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -25457,7 +25457,7 @@
         <v>5.28</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>37.97</v>
+        <v>37.98</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -25488,10 +25488,10 @@
         <v>0</v>
       </c>
       <c r="AB241" s="4" t="n">
-        <v>68.98</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="AC241" s="4" t="n">
-        <v>31.02</v>
+        <v>31.01</v>
       </c>
       <c r="AD241" s="4" t="n">
         <v>0</v>
@@ -25539,13 +25539,13 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>65.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -25553,13 +25553,13 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O242" s="4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P242" s="4" t="n">
         <v>-1.12</v>
@@ -25596,10 +25596,10 @@
         <v>0</v>
       </c>
       <c r="AB242" s="4" t="n">
-        <v>50.51</v>
+        <v>50.52</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.49</v>
+        <v>49.48</v>
       </c>
       <c r="AD242" s="4" t="n">
         <v>0</v>
@@ -25749,7 +25749,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-33.2</v>
+        <v>-33.19</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -25763,13 +25763,13 @@
         </is>
       </c>
       <c r="M244" s="4" t="n">
-        <v>-29.01</v>
+        <v>-29</v>
       </c>
       <c r="N244" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-33.2</v>
+        <v>-33.19</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -25870,7 +25870,7 @@
         <v>2.26</v>
       </c>
       <c r="P245" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="Q245" s="4" t="n">
         <v>0</v>
@@ -25894,7 +25894,7 @@
         <v>1211489</v>
       </c>
       <c r="X245" s="5" t="n">
-        <v>1414724</v>
+        <v>1433728</v>
       </c>
       <c r="Y245" t="inlineStr"/>
       <c r="Z245" s="4" t="n">
@@ -25951,7 +25951,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>26.56</v>
+        <v>26.57</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>100</v>
@@ -25965,13 +25965,13 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O246" s="4" t="n">
-        <v>26.56</v>
+        <v>26.57</v>
       </c>
       <c r="P246" s="4" t="n">
         <v>1.6</v>
@@ -26002,10 +26002,10 @@
         <v>0</v>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>63.28</v>
+        <v>63.29</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>36.72</v>
+        <v>36.71</v>
       </c>
       <c r="AD246" s="4" t="n">
         <v>0</v>
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M247" s="4" t="n">
-        <v>45.37</v>
+        <v>45.38</v>
       </c>
       <c r="N247" s="4" t="n">
         <v>5.28</v>
@@ -26169,7 +26169,7 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>47.87</v>
+        <v>47.88</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>5.28</v>
@@ -26361,7 +26361,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>12.24</v>
+        <v>12.26</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>98.90000000000001</v>
@@ -26418,10 +26418,10 @@
         <v>0</v>
       </c>
       <c r="AB250" s="4" t="n">
-        <v>56.12</v>
+        <v>56.13</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>43.88</v>
+        <v>43.87</v>
       </c>
       <c r="AD250" s="4" t="n">
         <v>0</v>
@@ -26520,10 +26520,10 @@
         <v>0</v>
       </c>
       <c r="AB251" s="4" t="n">
-        <v>65.06999999999999</v>
+        <v>65.06</v>
       </c>
       <c r="AC251" s="4" t="n">
-        <v>34.93</v>
+        <v>34.94</v>
       </c>
       <c r="AD251" s="4" t="n">
         <v>0</v>
@@ -26775,7 +26775,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-14.43</v>
+        <v>-14.44</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>0.7</v>
@@ -26795,7 +26795,7 @@
         <v>5.28</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-14.43</v>
+        <v>-14.44</v>
       </c>
       <c r="P254" s="4" t="n">
         <v>0</v>
@@ -26891,7 +26891,7 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-33.54</v>
+        <v>-33.55</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>5.28</v>
@@ -27183,7 +27183,7 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.69</v>
+        <v>-10.71</v>
       </c>
       <c r="J258" s="4" t="n">
         <v>2.5</v>
@@ -28001,7 +28001,7 @@
         </is>
       </c>
       <c r="I266" s="4" t="n">
-        <v>35.59</v>
+        <v>35.6</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>100</v>
@@ -28021,7 +28021,7 @@
         <v>5.28</v>
       </c>
       <c r="O266" s="4" t="n">
-        <v>35.59</v>
+        <v>35.6</v>
       </c>
       <c r="P266" s="4" t="n">
         <v>1.61</v>
@@ -28103,7 +28103,7 @@
         </is>
       </c>
       <c r="I267" s="4" t="n">
-        <v>-23.85</v>
+        <v>-23.84</v>
       </c>
       <c r="J267" s="4" t="n">
         <v>0.1</v>
@@ -28123,7 +28123,7 @@
         <v>5.28</v>
       </c>
       <c r="O267" s="4" t="n">
-        <v>-23.85</v>
+        <v>-23.84</v>
       </c>
       <c r="P267" s="4" t="n">
         <v>-1.09</v>
@@ -28306,10 +28306,10 @@
         <v>-6.79</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28317,13 +28317,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.21</v>
+        <v>-12.19</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.050000000000001</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28360,10 +28360,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.6</v>
+        <v>46.61</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.4</v>
+        <v>53.39</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28411,7 +28411,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.79</v>
+        <v>-33.77</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28425,13 +28425,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.17</v>
+        <v>-31.15</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.79</v>
+        <v>-33.77</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28462,10 +28462,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.1</v>
+        <v>33.12</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.88</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28621,7 +28621,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>45.43</v>
+        <v>45.42</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -28635,13 +28635,13 @@
         </is>
       </c>
       <c r="M272" s="4" t="n">
-        <v>36.95</v>
+        <v>36.94</v>
       </c>
       <c r="N272" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O272" s="4" t="n">
-        <v>45.43</v>
+        <v>45.42</v>
       </c>
       <c r="P272" s="4" t="n">
         <v>0</v>
@@ -28825,7 +28825,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>58.94</v>
+        <v>58.93</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>100</v>
@@ -28845,7 +28845,7 @@
         <v>5.28</v>
       </c>
       <c r="O274" s="4" t="n">
-        <v>58.94</v>
+        <v>58.93</v>
       </c>
       <c r="P274" s="4" t="n">
         <v>1.88</v>
@@ -28927,7 +28927,7 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>-10.69</v>
+        <v>-10.7</v>
       </c>
       <c r="J275" s="4" t="n">
         <v>2.5</v>
@@ -28947,7 +28947,7 @@
         <v>5.28</v>
       </c>
       <c r="O275" s="4" t="n">
-        <v>-10.69</v>
+        <v>-10.7</v>
       </c>
       <c r="P275" s="4" t="n">
         <v>-0.92</v>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>-10.54</v>
+        <v>-10.55</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>2.9</v>
@@ -29233,7 +29233,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-16.92</v>
+        <v>-16.93</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.5</v>
@@ -29253,7 +29253,7 @@
         <v>5.28</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-16.92</v>
+        <v>-16.93</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.86</v>
@@ -29335,7 +29335,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>-11.44</v>
+        <v>-11.45</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>1.3</v>
@@ -29355,7 +29355,7 @@
         <v>5.28</v>
       </c>
       <c r="O279" s="4" t="n">
-        <v>-11.44</v>
+        <v>-11.45</v>
       </c>
       <c r="P279" s="4" t="n">
         <v>-0.25</v>
@@ -29544,10 +29544,10 @@
         <v>-3.33</v>
       </c>
       <c r="J281" s="4" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="K281" s="4" t="n">
-        <v>74.7</v>
+        <v>74.8</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-13.44</v>
+        <v>-13.45</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>0.9</v>
@@ -29759,7 +29759,7 @@
         </is>
       </c>
       <c r="M283" s="4" t="n">
-        <v>-14.61</v>
+        <v>-14.62</v>
       </c>
       <c r="N283" s="4" t="n">
         <v>5.28</v>
@@ -29861,7 +29861,7 @@
         </is>
       </c>
       <c r="M284" s="4" t="n">
-        <v>-13.41</v>
+        <v>-13.42</v>
       </c>
       <c r="N284" s="4" t="n">
         <v>5.28</v>
@@ -30161,7 +30161,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>13.09</v>
+        <v>13.08</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>99</v>
@@ -30175,13 +30175,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.87</v>
+        <v>14.86</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30283,7 +30283,7 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.29</v>
+        <v>-49.3</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.28</v>
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="J297" s="4" t="n">
         <v>80.09999999999999</v>
@@ -31252,10 +31252,10 @@
         <v>0</v>
       </c>
       <c r="AB297" s="4" t="n">
-        <v>52.39</v>
+        <v>52.4</v>
       </c>
       <c r="AC297" s="4" t="n">
-        <v>47.61</v>
+        <v>47.6</v>
       </c>
       <c r="AD297" s="4" t="n">
         <v>0</v>
@@ -31809,7 +31809,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>26.15</v>
+        <v>26.16</v>
       </c>
       <c r="J303" s="4" t="n">
         <v>100</v>
@@ -31823,13 +31823,13 @@
         </is>
       </c>
       <c r="M303" s="4" t="n">
-        <v>15.99</v>
+        <v>16</v>
       </c>
       <c r="N303" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O303" s="4" t="n">
-        <v>26.15</v>
+        <v>26.16</v>
       </c>
       <c r="P303" s="4" t="n">
         <v>1.68</v>
@@ -31860,10 +31860,10 @@
         <v>0</v>
       </c>
       <c r="AB303" s="4" t="n">
-        <v>63.07</v>
+        <v>63.08</v>
       </c>
       <c r="AC303" s="4" t="n">
-        <v>36.93</v>
+        <v>36.92</v>
       </c>
       <c r="AD303" s="4" t="n">
         <v>0</v>
@@ -31911,7 +31911,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>14.68</v>
+        <v>14.69</v>
       </c>
       <c r="J304" s="4" t="n">
         <v>99.3</v>
@@ -31925,13 +31925,13 @@
         </is>
       </c>
       <c r="M304" s="4" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="N304" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O304" s="4" t="n">
-        <v>16.56</v>
+        <v>16.57</v>
       </c>
       <c r="P304" s="4" t="n">
         <v>0.67</v>
@@ -32019,7 +32019,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>23.16</v>
+        <v>23.17</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>99.90000000000001</v>
@@ -32033,13 +32033,13 @@
         </is>
       </c>
       <c r="M305" s="4" t="n">
-        <v>9.74</v>
+        <v>9.75</v>
       </c>
       <c r="N305" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O305" s="4" t="n">
-        <v>23.16</v>
+        <v>23.17</v>
       </c>
       <c r="P305" s="4" t="n">
         <v>0.73</v>
@@ -32070,10 +32070,10 @@
         <v>0</v>
       </c>
       <c r="AB305" s="4" t="n">
-        <v>61.58</v>
+        <v>61.59</v>
       </c>
       <c r="AC305" s="4" t="n">
-        <v>38.42</v>
+        <v>38.41</v>
       </c>
       <c r="AD305" s="4" t="n">
         <v>0</v>
@@ -32121,7 +32121,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>15.93</v>
+        <v>15.94</v>
       </c>
       <c r="J306" s="4" t="n">
         <v>99.40000000000001</v>
@@ -32135,13 +32135,13 @@
         </is>
       </c>
       <c r="M306" s="4" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="N306" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O306" s="4" t="n">
-        <v>15.93</v>
+        <v>15.94</v>
       </c>
       <c r="P306" s="4" t="n">
         <v>-0.16</v>
@@ -32219,13 +32219,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-4.88</v>
+        <v>-4.94</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -32233,13 +32233,13 @@
         </is>
       </c>
       <c r="M307" s="4" t="n">
-        <v>-12.83</v>
+        <v>-12.82</v>
       </c>
       <c r="N307" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O307" s="4" t="n">
-        <v>-8.880000000000001</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="P307" s="4" t="n">
         <v>-1.32</v>
@@ -32276,10 +32276,10 @@
         <v>0</v>
       </c>
       <c r="AB307" s="4" t="n">
-        <v>47.56</v>
+        <v>47.53</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>52.44</v>
+        <v>52.47</v>
       </c>
       <c r="AD307" s="4" t="n">
         <v>0</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>11.4</v>
+        <v>11.41</v>
       </c>
       <c r="J308" s="4" t="n">
         <v>98.7</v>
@@ -32341,13 +32341,13 @@
         </is>
       </c>
       <c r="M308" s="4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="N308" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O308" s="4" t="n">
-        <v>11.4</v>
+        <v>11.41</v>
       </c>
       <c r="P308" s="4" t="n">
         <v>0.06</v>
@@ -32378,10 +32378,10 @@
         <v>0</v>
       </c>
       <c r="AB308" s="4" t="n">
-        <v>55.7</v>
+        <v>55.71</v>
       </c>
       <c r="AC308" s="4" t="n">
-        <v>44.3</v>
+        <v>44.29</v>
       </c>
       <c r="AD308" s="4" t="n">
         <v>0</v>
@@ -32429,7 +32429,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>17.19</v>
+        <v>17.2</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>99.59999999999999</v>
@@ -32443,13 +32443,13 @@
         </is>
       </c>
       <c r="M309" s="4" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="N309" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>17.19</v>
+        <v>17.2</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>0.97</v>
@@ -34159,13 +34159,13 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="J326" s="4" t="n">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="K326" s="4" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -34216,10 +34216,10 @@
         <v>0</v>
       </c>
       <c r="AB326" s="4" t="n">
-        <v>51.26</v>
+        <v>51.27</v>
       </c>
       <c r="AC326" s="4" t="n">
-        <v>48.74</v>
+        <v>48.73</v>
       </c>
       <c r="AD326" s="4" t="n">
         <v>0</v>
@@ -34575,7 +34575,7 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-13.06</v>
+        <v>-13.08</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>1</v>
@@ -34632,10 +34632,10 @@
         <v>0</v>
       </c>
       <c r="AB330" s="4" t="n">
-        <v>43.47</v>
+        <v>43.46</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>56.53</v>
+        <v>56.54</v>
       </c>
       <c r="AD330" s="4" t="n">
         <v>0</v>
@@ -35805,13 +35805,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>30.6</v>
+        <v>31</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35862,10 +35862,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>50.98</v>
+        <v>50.93</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>49.02</v>
+        <v>49.07</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -35927,7 +35927,7 @@
         </is>
       </c>
       <c r="M343" s="4" t="n">
-        <v>-12.02</v>
+        <v>-12.03</v>
       </c>
       <c r="N343" s="4" t="n">
         <v>5.28</v>
@@ -36123,7 +36123,7 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>5.9</v>
@@ -36143,7 +36143,7 @@
         <v>5.28</v>
       </c>
       <c r="O345" s="4" t="n">
-        <v>-9.6</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="P345" s="4" t="n">
         <v>-0.62</v>
@@ -36653,7 +36653,7 @@
         </is>
       </c>
       <c r="M350" s="4" t="n">
-        <v>-5.74</v>
+        <v>-5.75</v>
       </c>
       <c r="N350" s="4" t="n">
         <v>5.28</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="I356" s="4" t="n">
-        <v>49.51</v>
+        <v>49.52</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>100</v>
@@ -37261,13 +37261,13 @@
         </is>
       </c>
       <c r="M356" s="4" t="n">
-        <v>38.68</v>
+        <v>38.69</v>
       </c>
       <c r="N356" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O356" s="4" t="n">
-        <v>49.51</v>
+        <v>49.52</v>
       </c>
       <c r="P356" s="4" t="n">
         <v>2.08</v>
@@ -37363,7 +37363,7 @@
         </is>
       </c>
       <c r="M357" s="4" t="n">
-        <v>-28.14</v>
+        <v>-28.13</v>
       </c>
       <c r="N357" s="4" t="n">
         <v>5.28</v>
@@ -37567,7 +37567,7 @@
         </is>
       </c>
       <c r="M359" s="4" t="n">
-        <v>11.76</v>
+        <v>11.77</v>
       </c>
       <c r="N359" s="4" t="n">
         <v>5.28</v>
@@ -37771,7 +37771,7 @@
         </is>
       </c>
       <c r="M361" s="4" t="n">
-        <v>11.21</v>
+        <v>11.22</v>
       </c>
       <c r="N361" s="4" t="n">
         <v>5.28</v>
@@ -37808,10 +37808,10 @@
         <v>0</v>
       </c>
       <c r="AB361" s="4" t="n">
-        <v>59.02</v>
+        <v>59.03</v>
       </c>
       <c r="AC361" s="4" t="n">
-        <v>40.98</v>
+        <v>40.97</v>
       </c>
       <c r="AD361" s="4" t="n">
         <v>0</v>
@@ -38473,13 +38473,13 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="J368" s="4" t="n">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="K368" s="4" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -38530,10 +38530,10 @@
         <v>0</v>
       </c>
       <c r="AB368" s="4" t="n">
-        <v>51.33</v>
+        <v>51.34</v>
       </c>
       <c r="AC368" s="4" t="n">
-        <v>48.67</v>
+        <v>48.66</v>
       </c>
       <c r="AD368" s="4" t="n">
         <v>0</v>
@@ -38581,7 +38581,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>63.1</v>
@@ -38638,10 +38638,10 @@
         <v>0</v>
       </c>
       <c r="AB369" s="4" t="n">
-        <v>50.17</v>
+        <v>50.18</v>
       </c>
       <c r="AC369" s="4" t="n">
-        <v>49.83</v>
+        <v>49.82</v>
       </c>
       <c r="AD369" s="4" t="n">
         <v>0</v>
@@ -38791,7 +38791,7 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>8.98</v>
+        <v>8.99</v>
       </c>
       <c r="J371" s="4" t="n">
         <v>93.3</v>
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>40.73</v>
+        <v>40.74</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -39627,13 +39627,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>27.29</v>
+        <v>27.3</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>40.73</v>
+        <v>40.74</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>0</v>
@@ -39664,10 +39664,10 @@
         <v>0</v>
       </c>
       <c r="AB379" s="4" t="n">
-        <v>70.36</v>
+        <v>70.37</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>29.64</v>
+        <v>29.63</v>
       </c>
       <c r="AD379" s="4" t="n">
         <v>0</v>
@@ -39715,7 +39715,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>17.44</v>
+        <v>17.45</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39729,13 +39729,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>11.43</v>
+        <v>11.44</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>17.44</v>
+        <v>17.45</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.61</v>
@@ -39813,13 +39813,13 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-3.66</v>
+        <v>-3.64</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -39870,10 +39870,10 @@
         <v>0</v>
       </c>
       <c r="AB381" s="4" t="n">
-        <v>47.12</v>
+        <v>47.13</v>
       </c>
       <c r="AC381" s="4" t="n">
-        <v>50.7</v>
+        <v>50.69</v>
       </c>
       <c r="AD381" s="4" t="n">
         <v>2.18</v>
@@ -39921,7 +39921,7 @@
         </is>
       </c>
       <c r="I382" s="4" t="n">
-        <v>-11.65</v>
+        <v>-11.64</v>
       </c>
       <c r="J382" s="4" t="n">
         <v>1.2</v>
@@ -39941,7 +39941,7 @@
         <v>5.28</v>
       </c>
       <c r="O382" s="4" t="n">
-        <v>-11.65</v>
+        <v>-11.64</v>
       </c>
       <c r="P382" s="4" t="n">
         <v>-2.01</v>
@@ -40023,7 +40023,7 @@
         </is>
       </c>
       <c r="I383" s="4" t="n">
-        <v>-41.65</v>
+        <v>-41.64</v>
       </c>
       <c r="J383" s="4" t="n">
         <v>0</v>
@@ -40043,7 +40043,7 @@
         <v>5.28</v>
       </c>
       <c r="O383" s="4" t="n">
-        <v>-41.65</v>
+        <v>-41.64</v>
       </c>
       <c r="P383" s="4" t="n">
         <v>-1.36</v>
@@ -40125,7 +40125,7 @@
         </is>
       </c>
       <c r="I384" s="4" t="n">
-        <v>-18.09</v>
+        <v>-18.08</v>
       </c>
       <c r="J384" s="4" t="n">
         <v>0.4</v>
@@ -40139,13 +40139,13 @@
         </is>
       </c>
       <c r="M384" s="4" t="n">
-        <v>-19.43</v>
+        <v>-19.42</v>
       </c>
       <c r="N384" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O384" s="4" t="n">
-        <v>-18.09</v>
+        <v>-18.08</v>
       </c>
       <c r="P384" s="4" t="n">
         <v>-2.31</v>
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="I385" s="4" t="n">
-        <v>-14.79</v>
+        <v>-14.78</v>
       </c>
       <c r="J385" s="4" t="n">
         <v>0.7</v>
@@ -40243,7 +40243,7 @@
         <v>5.28</v>
       </c>
       <c r="O385" s="4" t="n">
-        <v>-14.79</v>
+        <v>-14.78</v>
       </c>
       <c r="P385" s="4" t="n">
         <v>-1.2</v>
@@ -40427,7 +40427,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-14.64</v>
+        <v>-14.76</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>0.7</v>
@@ -40441,13 +40441,13 @@
         </is>
       </c>
       <c r="M387" s="4" t="n">
-        <v>-21</v>
+        <v>-20.99</v>
       </c>
       <c r="N387" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O387" s="4" t="n">
-        <v>-21.54</v>
+        <v>-21.53</v>
       </c>
       <c r="P387" s="4" t="n">
         <v>-1.22</v>
@@ -40484,10 +40484,10 @@
         <v>0</v>
       </c>
       <c r="AB387" s="4" t="n">
-        <v>42.68</v>
+        <v>42.62</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>57.32</v>
+        <v>57.38</v>
       </c>
       <c r="AD387" s="4" t="n">
         <v>0</v>
@@ -41539,7 +41539,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-40.55</v>
+        <v>-40.56</v>
       </c>
       <c r="J398" s="4" t="n">
         <v>0</v>
@@ -41553,13 +41553,13 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-44.12</v>
+        <v>-44.13</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O398" s="4" t="n">
-        <v>-40.55</v>
+        <v>-40.56</v>
       </c>
       <c r="P398" s="4" t="n">
         <v>0</v>
@@ -41637,7 +41637,7 @@
         </is>
       </c>
       <c r="I399" s="4" t="n">
-        <v>-12.29</v>
+        <v>-12.3</v>
       </c>
       <c r="J399" s="4" t="n">
         <v>1.1</v>
@@ -41651,13 +41651,13 @@
         </is>
       </c>
       <c r="M399" s="4" t="n">
-        <v>-18.92</v>
+        <v>-18.93</v>
       </c>
       <c r="N399" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O399" s="4" t="n">
-        <v>-12.29</v>
+        <v>-12.3</v>
       </c>
       <c r="P399" s="4" t="n">
         <v>0.88</v>
@@ -41688,10 +41688,10 @@
         <v>0</v>
       </c>
       <c r="AB399" s="4" t="n">
-        <v>43.86</v>
+        <v>43.85</v>
       </c>
       <c r="AC399" s="4" t="n">
-        <v>56.14</v>
+        <v>56.15</v>
       </c>
       <c r="AD399" s="4" t="n">
         <v>0</v>
@@ -41739,7 +41739,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-15.37</v>
+        <v>-15.38</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>0.6</v>
@@ -41753,13 +41753,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-18.72</v>
+        <v>-18.73</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-15.37</v>
+        <v>-15.38</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -41855,7 +41855,7 @@
         </is>
       </c>
       <c r="M401" s="4" t="n">
-        <v>-19.57</v>
+        <v>-19.58</v>
       </c>
       <c r="N401" s="4" t="n">
         <v>5.28</v>
@@ -41892,10 +41892,10 @@
         <v>0</v>
       </c>
       <c r="AB401" s="4" t="n">
-        <v>39.6</v>
+        <v>39.59</v>
       </c>
       <c r="AC401" s="4" t="n">
-        <v>60.4</v>
+        <v>60.41</v>
       </c>
       <c r="AD401" s="4" t="n">
         <v>0</v>
@@ -41943,7 +41943,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-13.33</v>
+        <v>-13.34</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>0.9</v>
@@ -41957,13 +41957,13 @@
         </is>
       </c>
       <c r="M402" s="4" t="n">
-        <v>-16.41</v>
+        <v>-16.42</v>
       </c>
       <c r="N402" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-13.33</v>
+        <v>-13.34</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.23</v>
@@ -42045,7 +42045,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-18.71</v>
+        <v>-18.72</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.3</v>
@@ -42059,13 +42059,13 @@
         </is>
       </c>
       <c r="M403" s="4" t="n">
-        <v>-18.49</v>
+        <v>-18.5</v>
       </c>
       <c r="N403" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-18.71</v>
+        <v>-18.72</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -42147,7 +42147,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>41.05</v>
+        <v>41.04</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -42161,13 +42161,13 @@
         </is>
       </c>
       <c r="M404" s="4" t="n">
-        <v>30.84</v>
+        <v>30.83</v>
       </c>
       <c r="N404" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>41.05</v>
+        <v>41.04</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -42357,7 +42357,7 @@
         </is>
       </c>
       <c r="M406" s="4" t="n">
-        <v>-12.17</v>
+        <v>-12.18</v>
       </c>
       <c r="N406" s="4" t="n">
         <v>5.28</v>
@@ -42441,7 +42441,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-13.02</v>
+        <v>-13.03</v>
       </c>
       <c r="J407" s="4" t="n">
         <v>1</v>
@@ -42461,7 +42461,7 @@
         <v>5.28</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-13.02</v>
+        <v>-13.03</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -42492,10 +42492,10 @@
         <v>0</v>
       </c>
       <c r="AB407" s="4" t="n">
-        <v>43.49</v>
+        <v>43.48</v>
       </c>
       <c r="AC407" s="4" t="n">
-        <v>56.51</v>
+        <v>56.52</v>
       </c>
       <c r="AD407" s="4" t="n">
         <v>0</v>
@@ -42543,7 +42543,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-27.38</v>
+        <v>-27.39</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0</v>
@@ -42563,7 +42563,7 @@
         <v>5.28</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-27.38</v>
+        <v>-27.39</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -42761,7 +42761,7 @@
         </is>
       </c>
       <c r="M410" s="4" t="n">
-        <v>-42.14</v>
+        <v>-42.15</v>
       </c>
       <c r="N410" s="4" t="n">
         <v>5.28</v>
@@ -42798,10 +42798,10 @@
         <v>0</v>
       </c>
       <c r="AB410" s="4" t="n">
-        <v>29.66</v>
+        <v>29.65</v>
       </c>
       <c r="AC410" s="4" t="n">
-        <v>70.34</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="AD410" s="4" t="n">
         <v>0</v>
@@ -42849,7 +42849,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-19.61</v>
+        <v>-19.62</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.2</v>
@@ -42863,13 +42863,13 @@
         </is>
       </c>
       <c r="M411" s="4" t="n">
-        <v>-19.55</v>
+        <v>-19.56</v>
       </c>
       <c r="N411" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-19.61</v>
+        <v>-19.62</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.89</v>
@@ -42954,10 +42954,10 @@
         <v>-2.08</v>
       </c>
       <c r="J412" s="4" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="K412" s="4" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>26.81</v>
+        <v>26.8</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>5.28</v>
@@ -43110,10 +43110,10 @@
         <v>0</v>
       </c>
       <c r="AB413" s="4" t="n">
-        <v>68.3</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="AC413" s="4" t="n">
-        <v>31.7</v>
+        <v>31.71</v>
       </c>
       <c r="AD413" s="4" t="n">
         <v>0</v>
@@ -43161,7 +43161,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-14.8</v>
+        <v>-14.81</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>0.7</v>
@@ -43181,7 +43181,7 @@
         <v>5.28</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-14.8</v>
+        <v>-14.81</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>0</v>
@@ -43263,7 +43263,7 @@
         </is>
       </c>
       <c r="I415" s="4" t="n">
-        <v>71.13</v>
+        <v>71.12</v>
       </c>
       <c r="J415" s="4" t="n">
         <v>100</v>
@@ -43277,13 +43277,13 @@
         </is>
       </c>
       <c r="M415" s="4" t="n">
-        <v>62.9</v>
+        <v>62.89</v>
       </c>
       <c r="N415" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>71.13</v>
+        <v>71.12</v>
       </c>
       <c r="P415" s="4" t="n">
         <v>0</v>
@@ -43412,10 +43412,10 @@
         <v>0</v>
       </c>
       <c r="AB416" s="4" t="n">
-        <v>28.64</v>
+        <v>28.63</v>
       </c>
       <c r="AC416" s="4" t="n">
-        <v>71.36</v>
+        <v>71.37</v>
       </c>
       <c r="AD416" s="4" t="n">
         <v>0</v>
@@ -43561,7 +43561,7 @@
         </is>
       </c>
       <c r="I418" s="4" t="n">
-        <v>-12.29</v>
+        <v>-12.3</v>
       </c>
       <c r="J418" s="4" t="n">
         <v>1.1</v>
@@ -43575,13 +43575,13 @@
         </is>
       </c>
       <c r="M418" s="4" t="n">
-        <v>-16.83</v>
+        <v>-16.84</v>
       </c>
       <c r="N418" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O418" s="4" t="n">
-        <v>-12.29</v>
+        <v>-12.3</v>
       </c>
       <c r="P418" s="4" t="n">
         <v>-2.06</v>
@@ -43673,7 +43673,7 @@
         </is>
       </c>
       <c r="M419" s="4" t="n">
-        <v>-17.41</v>
+        <v>-17.42</v>
       </c>
       <c r="N419" s="4" t="n">
         <v>5.28</v>
@@ -43710,10 +43710,10 @@
         <v>0</v>
       </c>
       <c r="AB419" s="4" t="n">
-        <v>43.5</v>
+        <v>43.49</v>
       </c>
       <c r="AC419" s="4" t="n">
-        <v>56.5</v>
+        <v>56.51</v>
       </c>
       <c r="AD419" s="4" t="n">
         <v>0</v>
@@ -43771,13 +43771,13 @@
         </is>
       </c>
       <c r="M420" s="4" t="n">
-        <v>-8.41</v>
+        <v>-8.42</v>
       </c>
       <c r="N420" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.92</v>
       </c>
       <c r="P420" s="4" t="n">
         <v>-0.82</v>
@@ -43967,7 +43967,7 @@
         </is>
       </c>
       <c r="I422" s="4" t="n">
-        <v>-13.88</v>
+        <v>-13.89</v>
       </c>
       <c r="J422" s="4" t="n">
         <v>0.8</v>
@@ -43981,13 +43981,13 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-17.97</v>
+        <v>-17.98</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O422" s="4" t="n">
-        <v>-13.88</v>
+        <v>-13.89</v>
       </c>
       <c r="P422" s="4" t="n">
         <v>0</v>
@@ -44069,7 +44069,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-22.61</v>
+        <v>-22.62</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.1</v>
@@ -44083,13 +44083,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-19.09</v>
+        <v>-19.1</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-22.61</v>
+        <v>-22.62</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -44171,7 +44171,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-13.88</v>
+        <v>-13.89</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>0.8</v>
@@ -44185,13 +44185,13 @@
         </is>
       </c>
       <c r="M424" s="4" t="n">
-        <v>-16.33</v>
+        <v>-16.34</v>
       </c>
       <c r="N424" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-13.88</v>
+        <v>-13.89</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -44273,7 +44273,7 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>13.15</v>
+        <v>13.25</v>
       </c>
       <c r="J425" s="4" t="n">
         <v>99.09999999999999</v>
@@ -44287,13 +44287,13 @@
         </is>
       </c>
       <c r="M425" s="4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="N425" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O425" s="4" t="n">
-        <v>20.15</v>
+        <v>20.14</v>
       </c>
       <c r="P425" s="4" t="n">
         <v>0.34</v>
@@ -44330,10 +44330,10 @@
         <v>0</v>
       </c>
       <c r="AB425" s="4" t="n">
-        <v>56.58</v>
+        <v>56.62</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>43.42</v>
+        <v>43.38</v>
       </c>
       <c r="AD425" s="4" t="n">
         <v>0</v>
@@ -44432,10 +44432,10 @@
         <v>0</v>
       </c>
       <c r="AB426" s="4" t="n">
-        <v>77.03</v>
+        <v>77.02</v>
       </c>
       <c r="AC426" s="4" t="n">
-        <v>22.97</v>
+        <v>22.98</v>
       </c>
       <c r="AD426" s="4" t="n">
         <v>0</v>
@@ -44493,7 +44493,7 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>54.88</v>
+        <v>54.87</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>5.28</v>
@@ -44530,10 +44530,10 @@
         <v>0</v>
       </c>
       <c r="AB427" s="4" t="n">
-        <v>80.84</v>
+        <v>80.83</v>
       </c>
       <c r="AC427" s="4" t="n">
-        <v>19.16</v>
+        <v>19.17</v>
       </c>
       <c r="AD427" s="4" t="n">
         <v>0</v>
@@ -44581,7 +44581,7 @@
         </is>
       </c>
       <c r="I428" s="4" t="n">
-        <v>-18.76</v>
+        <v>-18.77</v>
       </c>
       <c r="J428" s="4" t="n">
         <v>0.3</v>
@@ -44679,7 +44679,7 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-8.27</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="J429" s="4" t="n">
         <v>8.699999999999999</v>
@@ -44699,7 +44699,7 @@
         <v>5.28</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-8.27</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.72</v>
@@ -44791,7 +44791,7 @@
         </is>
       </c>
       <c r="M430" s="4" t="n">
-        <v>41.04</v>
+        <v>41.03</v>
       </c>
       <c r="N430" s="4" t="n">
         <v>5.28</v>
@@ -44879,7 +44879,7 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>8.48</v>
+        <v>8.5</v>
       </c>
       <c r="J431" s="4" t="n">
         <v>91.90000000000001</v>
@@ -44899,7 +44899,7 @@
         <v>5.28</v>
       </c>
       <c r="O431" s="4" t="n">
-        <v>11.22</v>
+        <v>11.21</v>
       </c>
       <c r="P431" s="4" t="n">
         <v>0.14</v>
@@ -44936,10 +44936,10 @@
         <v>0</v>
       </c>
       <c r="AB431" s="4" t="n">
-        <v>54.24</v>
+        <v>54.25</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>45.76</v>
+        <v>45.75</v>
       </c>
       <c r="AD431" s="4" t="n">
         <v>0</v>
@@ -44983,13 +44983,13 @@
         </is>
       </c>
       <c r="I432" s="4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -44997,13 +44997,13 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-4.01</v>
+        <v>-4.02</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O432" s="4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="P432" s="4" t="n">
         <v>0.08</v>
@@ -45034,10 +45034,10 @@
         <v>0</v>
       </c>
       <c r="AB432" s="4" t="n">
-        <v>51.62</v>
+        <v>51.61</v>
       </c>
       <c r="AC432" s="4" t="n">
-        <v>48.38</v>
+        <v>48.39</v>
       </c>
       <c r="AD432" s="4" t="n">
         <v>0</v>
@@ -45201,7 +45201,7 @@
         </is>
       </c>
       <c r="M434" s="4" t="n">
-        <v>63.66</v>
+        <v>63.65</v>
       </c>
       <c r="N434" s="4" t="n">
         <v>5.28</v>
@@ -45238,10 +45238,10 @@
         <v>0</v>
       </c>
       <c r="AB434" s="4" t="n">
-        <v>85.61</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AC434" s="4" t="n">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="AD434" s="4" t="n">
         <v>0</v>
@@ -45285,7 +45285,7 @@
         </is>
       </c>
       <c r="I435" s="4" t="n">
-        <v>-14.02</v>
+        <v>-14.03</v>
       </c>
       <c r="J435" s="4" t="n">
         <v>0.8</v>
@@ -45299,7 +45299,7 @@
         </is>
       </c>
       <c r="M435" s="4" t="n">
-        <v>-16.57</v>
+        <v>-16.58</v>
       </c>
       <c r="N435" s="4" t="n">
         <v>5.28</v>
@@ -45899,13 +45899,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -45956,10 +45956,10 @@
         <v>0</v>
       </c>
       <c r="AB441" s="4" t="n">
-        <v>51.28</v>
+        <v>51.3</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>48.72</v>
+        <v>48.7</v>
       </c>
       <c r="AD441" s="4" t="n">
         <v>0</v>
@@ -46925,7 +46925,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>36.25</v>
+        <v>36.24</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -46939,13 +46939,13 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>20.33</v>
+        <v>20.31</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>36.22</v>
+        <v>36.2</v>
       </c>
       <c r="P451" s="4" t="n">
         <v>1.84</v>
@@ -47237,13 +47237,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>5.78</v>
+        <v>5.81</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>5.28</v>
       </c>
       <c r="O454" s="4" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="P454" s="4" t="n">
         <v>0.84</v>
@@ -47284,7 +47284,7 @@
         <v>6292683</v>
       </c>
       <c r="X454" s="5" t="n">
-        <v>2035255</v>
+        <v>2051284</v>
       </c>
       <c r="Y454" t="inlineStr"/>
       <c r="Z454" s="4" t="n">
@@ -47294,10 +47294,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>52.89</v>
+        <v>52.9</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>47.11</v>
+        <v>47.1</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-23.26</v>
+        <v>-23.3</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47500,10 +47500,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>38.37</v>
+        <v>38.35</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>61.63</v>
+        <v>61.65</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -48061,13 +48061,13 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-3.98</v>
+        <v>-3.97</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -48271,13 +48271,13 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="J464" s="4" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="K464" s="4" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -48285,13 +48285,13 @@
         </is>
       </c>
       <c r="M464" s="4" t="n">
-        <v>-5.91</v>
+        <v>-5.9</v>
       </c>
       <c r="N464" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O464" s="4" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="P464" s="4" t="n">
         <v>0.1</v>
@@ -48379,7 +48379,7 @@
         </is>
       </c>
       <c r="I465" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>64.86</v>
       </c>
       <c r="J465" s="4" t="n">
         <v>100</v>
@@ -48393,13 +48393,13 @@
         </is>
       </c>
       <c r="M465" s="4" t="n">
-        <v>53.63</v>
+        <v>53.64</v>
       </c>
       <c r="N465" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O465" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>64.86</v>
       </c>
       <c r="P465" s="4" t="n">
         <v>2.31</v>
@@ -48583,7 +48583,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-18.68</v>
+        <v>-18.67</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.3</v>
@@ -48603,7 +48603,7 @@
         <v>5.28</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.87</v>
       </c>
       <c r="P467" s="4" t="n">
         <v>-1.76</v>
@@ -48640,10 +48640,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>40.66</v>
+        <v>40.67</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>59.34</v>
+        <v>59.33</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48738,10 +48738,10 @@
         <v>0</v>
       </c>
       <c r="AB468" s="4" t="n">
-        <v>40.71</v>
+        <v>40.72</v>
       </c>
       <c r="AC468" s="4" t="n">
-        <v>59.29</v>
+        <v>59.28</v>
       </c>
       <c r="AD468" s="4" t="n">
         <v>0</v>
@@ -48803,7 +48803,7 @@
         </is>
       </c>
       <c r="M469" s="4" t="n">
-        <v>-15.55</v>
+        <v>-15.54</v>
       </c>
       <c r="N469" s="4" t="n">
         <v>5.28</v>
@@ -49091,7 +49091,7 @@
         </is>
       </c>
       <c r="I472" s="4" t="n">
-        <v>-41.47</v>
+        <v>-41.35</v>
       </c>
       <c r="J472" s="4" t="n">
         <v>0</v>
@@ -49111,10 +49111,10 @@
         <v>5.28</v>
       </c>
       <c r="O472" s="4" t="n">
-        <v>-41.47</v>
+        <v>-41.35</v>
       </c>
       <c r="P472" s="4" t="n">
-        <v>-1.59</v>
+        <v>-1.47</v>
       </c>
       <c r="Q472" s="4" t="n">
         <v>0</v>
@@ -49142,10 +49142,10 @@
         <v>0</v>
       </c>
       <c r="AB472" s="4" t="n">
-        <v>29.27</v>
+        <v>29.33</v>
       </c>
       <c r="AC472" s="4" t="n">
-        <v>70.73</v>
+        <v>70.67</v>
       </c>
       <c r="AD472" s="4" t="n">
         <v>0</v>
@@ -49193,13 +49193,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-1.06</v>
+        <v>-0.78</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>46.3</v>
+        <v>47.9</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>53.7</v>
+        <v>52.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49207,13 +49207,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.75</v>
+        <v>-10.63</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2</v>
+        <v>-1.88</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.42</v>
@@ -49250,10 +49250,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.4</v>
+        <v>45.43</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.6</v>
+        <v>46.57</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49297,7 +49297,7 @@
         </is>
       </c>
       <c r="I474" s="4" t="n">
-        <v>-20.6</v>
+        <v>-20.66</v>
       </c>
       <c r="J474" s="4" t="n">
         <v>0.2</v>
@@ -49311,13 +49311,13 @@
         </is>
       </c>
       <c r="M474" s="4" t="n">
-        <v>-26.31</v>
+        <v>-26.32</v>
       </c>
       <c r="N474" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O474" s="4" t="n">
-        <v>-23.78</v>
+        <v>-23.79</v>
       </c>
       <c r="P474" s="4" t="n">
         <v>-3.2</v>
@@ -49354,10 +49354,10 @@
         <v>0</v>
       </c>
       <c r="AB474" s="4" t="n">
-        <v>39.7</v>
+        <v>39.67</v>
       </c>
       <c r="AC474" s="4" t="n">
-        <v>60.3</v>
+        <v>60.33</v>
       </c>
       <c r="AD474" s="4" t="n">
         <v>0</v>
@@ -49405,7 +49405,7 @@
         </is>
       </c>
       <c r="I475" s="4" t="n">
-        <v>-19.7</v>
+        <v>-19.79</v>
       </c>
       <c r="J475" s="4" t="n">
         <v>0.2</v>
@@ -49462,10 +49462,10 @@
         <v>0</v>
       </c>
       <c r="AB475" s="4" t="n">
-        <v>40.15</v>
+        <v>40.11</v>
       </c>
       <c r="AC475" s="4" t="n">
-        <v>59.85</v>
+        <v>59.89</v>
       </c>
       <c r="AD475" s="4" t="n">
         <v>0</v>
@@ -49774,10 +49774,10 @@
         <v>0</v>
       </c>
       <c r="AB478" s="4" t="n">
-        <v>47.29</v>
+        <v>47.3</v>
       </c>
       <c r="AC478" s="4" t="n">
-        <v>52.71</v>
+        <v>52.7</v>
       </c>
       <c r="AD478" s="4" t="n">
         <v>0</v>
@@ -49839,7 +49839,7 @@
         </is>
       </c>
       <c r="M479" s="4" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="N479" s="4" t="n">
         <v>5.28</v>
@@ -49929,7 +49929,7 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-1.97</v>
+        <v>-1.98</v>
       </c>
       <c r="J480" s="4" t="n">
         <v>30.5</v>
@@ -49986,10 +49986,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.73</v>
+        <v>47.72</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.64</v>
+        <v>49.65</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -50037,7 +50037,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-25.44</v>
+        <v>-25.47</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0.1</v>
@@ -50092,7 +50092,7 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>37.28</v>
+        <v>37.27</v>
       </c>
       <c r="AA481" s="4" t="n">
         <v>0.1</v>
@@ -50101,7 +50101,7 @@
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>62.72</v>
+        <v>62.73</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -50247,13 +50247,13 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-10.3</v>
+        <v>-10.31</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>30.24</v>
+        <v>30.26</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -50614,10 +50614,10 @@
         <v>0</v>
       </c>
       <c r="AB486" s="4" t="n">
-        <v>65.12</v>
+        <v>65.13</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>34.88</v>
+        <v>34.87</v>
       </c>
       <c r="AD486" s="4" t="n">
         <v>0</v>
@@ -50665,13 +50665,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         </is>
       </c>
       <c r="M487" s="4" t="n">
-        <v>8.67</v>
+        <v>8.66</v>
       </c>
       <c r="N487" s="4" t="n">
         <v>5.28</v>
@@ -50722,10 +50722,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>50.83</v>
+        <v>50.82</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>49.17</v>
+        <v>49.18</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -50769,13 +50769,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -50826,10 +50826,10 @@
         <v>0</v>
       </c>
       <c r="AB488" s="4" t="n">
-        <v>51.29</v>
+        <v>51.31</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>48.71</v>
+        <v>48.69</v>
       </c>
       <c r="AD488" s="4" t="n">
         <v>0</v>
@@ -50873,7 +50873,7 @@
         </is>
       </c>
       <c r="I489" s="4" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="J489" s="4" t="n">
         <v>95.40000000000001</v>
@@ -50981,7 +50981,7 @@
         </is>
       </c>
       <c r="I490" s="4" t="n">
-        <v>-13.27</v>
+        <v>-13.26</v>
       </c>
       <c r="J490" s="4" t="n">
         <v>0.9</v>
@@ -51001,10 +51001,10 @@
         <v>5.28</v>
       </c>
       <c r="O490" s="4" t="n">
-        <v>-14.2</v>
+        <v>-14.19</v>
       </c>
       <c r="P490" s="4" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="Q490" s="4" t="n">
         <v>2.62</v>
@@ -51042,10 +51042,10 @@
         <v>0</v>
       </c>
       <c r="AB490" s="4" t="n">
-        <v>40.76</v>
+        <v>40.77</v>
       </c>
       <c r="AC490" s="4" t="n">
-        <v>53.24</v>
+        <v>53.23</v>
       </c>
       <c r="AD490" s="4" t="n">
         <v>0</v>
@@ -51089,7 +51089,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-25.57</v>
+        <v>-25.48</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0.1</v>
@@ -51144,16 +51144,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.06</v>
+        <v>14.08</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>28.36</v>
+        <v>28.39</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.92</v>
+        <v>53.87</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51305,7 +51305,7 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-3.65</v>
+        <v>-3.66</v>
       </c>
       <c r="J493" s="4" t="n">
         <v>24</v>
@@ -51413,7 +51413,7 @@
         </is>
       </c>
       <c r="I494" s="4" t="n">
-        <v>7.22</v>
+        <v>7.23</v>
       </c>
       <c r="J494" s="4" t="n">
         <v>88.2</v>
@@ -51623,7 +51623,7 @@
         </is>
       </c>
       <c r="I496" s="4" t="n">
-        <v>18.93</v>
+        <v>18.94</v>
       </c>
       <c r="J496" s="4" t="n">
         <v>99.7</v>
@@ -51637,13 +51637,13 @@
         </is>
       </c>
       <c r="M496" s="4" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="N496" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O496" s="4" t="n">
-        <v>18.93</v>
+        <v>18.94</v>
       </c>
       <c r="P496" s="4" t="n">
         <v>3.16</v>
@@ -51674,10 +51674,10 @@
         <v>0</v>
       </c>
       <c r="AB496" s="4" t="n">
-        <v>59.46</v>
+        <v>59.47</v>
       </c>
       <c r="AC496" s="4" t="n">
-        <v>40.54</v>
+        <v>40.53</v>
       </c>
       <c r="AD496" s="4" t="n">
         <v>0</v>
@@ -51725,7 +51725,7 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="J497" s="4" t="n">
         <v>37</v>
@@ -52033,7 +52033,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>23.5</v>
+        <v>23.54</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -52090,10 +52090,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.75</v>
+        <v>61.77</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.25</v>
+        <v>38.23</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -52137,13 +52137,13 @@
         </is>
       </c>
       <c r="I501" s="4" t="n">
-        <v>-7.97</v>
+        <v>-7.94</v>
       </c>
       <c r="J501" s="4" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K501" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -52194,10 +52194,10 @@
         <v>0</v>
       </c>
       <c r="AB501" s="4" t="n">
-        <v>45.16</v>
+        <v>45.17</v>
       </c>
       <c r="AC501" s="4" t="n">
-        <v>52.97</v>
+        <v>52.96</v>
       </c>
       <c r="AD501" s="4" t="n">
         <v>1.87</v>
@@ -52245,7 +52245,7 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-20.94</v>
+        <v>-20.95</v>
       </c>
       <c r="J502" s="4" t="n">
         <v>0.2</v>
@@ -52455,7 +52455,7 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J504" s="4" t="n">
         <v>67.7</v>
@@ -52475,7 +52475,7 @@
         <v>5.28</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="P504" s="4" t="n">
         <v>1.51</v>
@@ -52512,10 +52512,10 @@
         <v>0</v>
       </c>
       <c r="AB504" s="4" t="n">
-        <v>49.74</v>
+        <v>49.73</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>48.25</v>
+        <v>48.26</v>
       </c>
       <c r="AD504" s="4" t="n">
         <v>2.01</v>
@@ -52991,7 +52991,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>112</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -55785,7 +55785,7 @@
         <v>31</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>232.8</v>
       </c>
       <c r="C9" t="n">
-        <v>202</v>
+        <v>202.2</v>
       </c>
       <c r="D9" t="n">
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.84</v>
+        <v>-3.03</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>38.1</v>
+        <v>41.9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>61.9</v>
+        <v>58.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.53</v>
+        <v>-2.29</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>71.7</v>
+        <v>70.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4719,13 +4719,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.06</v>
@@ -4760,16 +4760,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.74</v>
+        <v>48.86</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.26</v>
+        <v>51.14</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -21487,7 +21487,7 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-17.12</v>
+        <v>-17.13</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>5.29</v>
@@ -24715,7 +24715,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.05</v>
+        <v>30.23</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24729,13 +24729,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>22.14</v>
+        <v>22.05</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.26</v>
+        <v>31.17</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24766,10 +24766,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.35</v>
+        <v>62.3</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.65</v>
+        <v>32.7</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24813,13 +24813,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.22</v>
+        <v>-3.99</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24827,13 +24827,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-9.01</v>
+        <v>-9.1</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.2</v>
+        <v>-5.28</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24870,10 +24870,10 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>45.42</v>
+        <v>45.39</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>49.58</v>
+        <v>49.61</v>
       </c>
       <c r="AD235" s="4" t="n">
         <v>5</v>
@@ -28303,13 +28303,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.78</v>
+        <v>-6.87</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>86.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28317,13 +28317,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.17</v>
+        <v>-12.29</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.01</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28360,10 +28360,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.61</v>
+        <v>46.57</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.39</v>
+        <v>53.43</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28411,7 +28411,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-33.74</v>
+        <v>-33.86</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28425,13 +28425,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.13</v>
+        <v>-31.25</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-33.74</v>
+        <v>-33.86</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28462,10 +28462,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.13</v>
+        <v>33.07</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.87</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -30057,13 +30057,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.140000000000001</v>
+        <v>-9.27</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>93.7</v>
+        <v>94</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30071,13 +30071,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.34</v>
+        <v>-8.5</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-9.550000000000001</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30114,10 +30114,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.43</v>
+        <v>45.36</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.57</v>
+        <v>54.64</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30161,13 +30161,13 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>13.09</v>
+        <v>12.96</v>
       </c>
       <c r="J287" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="K287" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -30175,13 +30175,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>9.51</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.87</v>
+        <v>14.72</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30218,10 +30218,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.55</v>
+        <v>56.48</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.45</v>
+        <v>43.52</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30269,7 +30269,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.09</v>
+        <v>-52.25</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30283,13 +30283,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.3</v>
+        <v>-49.45</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.09</v>
+        <v>-52.25</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30320,10 +30320,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.95</v>
+        <v>23.87</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.05</v>
+        <v>76.13</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -35805,13 +35805,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>68.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>31.3</v>
+        <v>30.4</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35837,16 +35837,16 @@
         <v>-11.15</v>
       </c>
       <c r="S342" s="4" t="n">
-        <v>44.77</v>
+        <v>48.25</v>
       </c>
       <c r="T342" s="4" t="n">
-        <v>38.42</v>
+        <v>41.28</v>
       </c>
       <c r="U342" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V342" s="4" t="n">
-        <v>7.44</v>
+        <v>6.52</v>
       </c>
       <c r="W342" s="5" t="n">
         <v>603156</v>
@@ -35862,10 +35862,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>50.88</v>
+        <v>51</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>49.12</v>
+        <v>49</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -47443,7 +47443,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-23.33</v>
+        <v>-23.89</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47484,7 +47484,7 @@
         <v>1</v>
       </c>
       <c r="V456" s="4" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="W456" s="5" t="n">
         <v>396217</v>
@@ -47500,10 +47500,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>38.33</v>
+        <v>38.06</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>61.67</v>
+        <v>61.94</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -48583,7 +48583,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-18.64</v>
+        <v>-19.21</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.3</v>
@@ -48624,7 +48624,7 @@
         <v>1</v>
       </c>
       <c r="V467" s="4" t="n">
-        <v>-22</v>
+        <v>-25</v>
       </c>
       <c r="W467" s="5" t="n">
         <v>44015</v>
@@ -48640,10 +48640,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>40.68</v>
+        <v>40.39</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>59.32</v>
+        <v>59.61</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -49193,13 +49193,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-1.41</v>
+        <v>-0.7</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>45.5</v>
+        <v>48.4</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>54.5</v>
+        <v>51.6</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49207,13 +49207,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.78</v>
+        <v>-10.58</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.29</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.8</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.43</v>
@@ -49250,10 +49250,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.4</v>
+        <v>45.45</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.6</v>
+        <v>46.55</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -50247,13 +50247,13 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-10.33</v>
+        <v>-10.34</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -50279,16 +50279,16 @@
         <v>-16.41</v>
       </c>
       <c r="S483" s="4" t="n">
-        <v>43.26</v>
+        <v>43.1</v>
       </c>
       <c r="T483" s="4" t="n">
-        <v>47.6</v>
+        <v>47.22</v>
       </c>
       <c r="U483" t="n">
         <v>2</v>
       </c>
       <c r="V483" s="4" t="n">
-        <v>-7.09</v>
+        <v>-7.13</v>
       </c>
       <c r="W483" s="5" t="n">
         <v>4169078</v>
@@ -50665,13 +50665,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>68.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>31.8</v>
+        <v>33.6</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>7.09</v>
       </c>
       <c r="S487" s="4" t="n">
-        <v>49.75</v>
+        <v>49.19</v>
       </c>
       <c r="T487" s="4" t="n">
         <v>44.91</v>
@@ -50706,7 +50706,7 @@
         <v>6</v>
       </c>
       <c r="V487" s="4" t="n">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="W487" s="5" t="n">
         <v>0</v>
@@ -50722,10 +50722,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>50.81</v>
+        <v>50.6</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>49.19</v>
+        <v>49.4</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -51089,13 +51089,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-25.42</v>
+        <v>-25.9</v>
       </c>
       <c r="J491" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51121,16 +51121,16 @@
         <v>-20.58</v>
       </c>
       <c r="S491" s="4" t="n">
-        <v>31.11</v>
+        <v>30.8</v>
       </c>
       <c r="T491" s="4" t="n">
-        <v>43.81</v>
+        <v>43.51</v>
       </c>
       <c r="U491" t="n">
         <v>6</v>
       </c>
       <c r="V491" s="4" t="n">
-        <v>-12.97</v>
+        <v>-13.03</v>
       </c>
       <c r="W491" s="5" t="n">
         <v>58829</v>
@@ -51144,16 +51144,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>28.41</v>
+        <v>28.02</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.83</v>
+        <v>53.92</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51305,13 +51305,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-3.66</v>
+        <v>-4.45</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>24</v>
+        <v>21.1</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>76</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51340,13 +51340,13 @@
         <v>47</v>
       </c>
       <c r="T493" s="4" t="n">
-        <v>42.31</v>
+        <v>42.8</v>
       </c>
       <c r="U493" t="n">
         <v>3</v>
       </c>
       <c r="V493" s="4" t="n">
-        <v>4.54</v>
+        <v>1.2</v>
       </c>
       <c r="W493" s="5" t="n">
         <v>0</v>
@@ -51360,16 +51360,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>48.17</v>
+        <v>47.78</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>24</v>
+        <v>21.1</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>51.83</v>
+        <v>52.22</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -52991,7 +52991,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>85</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>84</v>
@@ -55147,7 +55147,7 @@
         <v>112</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="K47" t="n">
         <v>41</v>
@@ -55611,7 +55611,7 @@
         <v>53</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-08-11 · evaluated at 0 days to election (actual: 84 days out)</t>
+          <t>Data as of 2026-08-12 · evaluated at 0 days to election (actual: 83 days out)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>48.4</v>
+        <v>49.3</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233.1</v>
+        <v>232.9</v>
       </c>
       <c r="C9" t="n">
-        <v>201.9</v>
+        <v>202.1</v>
       </c>
       <c r="D9" t="n">
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>81.2</v>
+        <v>82</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>40.4</v>
+        <v>40.9</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="18">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.66</v>
+        <v>-3.26</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>38.4</v>
+        <v>40.9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>61.6</v>
+        <v>59.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>44.16</v>
+        <v>44.15</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>47.84</v>
+        <v>47.85</v>
       </c>
       <c r="AD2" s="4" t="n">
         <v>8</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-17.55</v>
+        <v>-17.59</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.4</v>
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>41.22</v>
+        <v>41.2</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>58.78</v>
+        <v>58.8</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>27.48</v>
+        <v>27.5</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>63.74</v>
+        <v>63.75</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>36.26</v>
+        <v>36.25</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19.22</v>
+        <v>19.23</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.7</v>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>59.61</v>
+        <v>59.62</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>40.39</v>
+        <v>40.38</v>
       </c>
       <c r="AD8" s="4" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>51.48</v>
+        <v>51.47</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>48.52</v>
+        <v>48.53</v>
       </c>
       <c r="AD10" s="4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>29.71</v>
+        <v>29.73</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>64.86</v>
+        <v>64.87</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>35.14</v>
+        <v>35.13</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>98.90000000000001</v>
@@ -2656,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>54.35</v>
+        <v>54.34</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>42.44</v>
+        <v>42.45</v>
       </c>
       <c r="AD18" s="4" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.7</v>
+        <v>10.71</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>97.5</v>
@@ -2760,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>55.35</v>
+        <v>55.36</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>44.65</v>
+        <v>44.64</v>
       </c>
       <c r="AD19" s="4" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mike Lindell</t>
+          <t>Lisa Demuth</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2807,13 +2807,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.78</v>
+        <v>10.58</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>99</v>
+        <v>97.2</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
         <v>5.33</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>10.91</v>
+        <v>10.89</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>-0.12</v>
@@ -2839,22 +2839,22 @@
         <v>4.34</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>52.86</v>
+        <v>48.65</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>34.69</v>
+        <v>38.98</v>
       </c>
       <c r="U20" t="n">
         <v>3</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>18.17</v>
+        <v>9.67</v>
       </c>
       <c r="W20" s="5" t="n">
         <v>9312380</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>1078103</v>
+        <v>1102119</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" s="4" t="n">
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>56.39</v>
+        <v>55.29</v>
       </c>
       <c r="AC20" s="4" t="n">
-        <v>43.61</v>
+        <v>44.71</v>
       </c>
       <c r="AD20" s="4" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.71</v>
+        <v>-10.72</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>2.5</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.43</v>
+        <v>7.46</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>88.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>53.71</v>
+        <v>53.73</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>46.29</v>
+        <v>46.27</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>0</v>
@@ -3239,13 +3239,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>50.03</v>
+        <v>50.05</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>49.97</v>
+        <v>49.95</v>
       </c>
       <c r="AD24" s="4" t="n">
         <v>0</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.28</v>
+        <v>-3.29</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25.4</v>
@@ -3508,10 +3508,10 @@
         <v>0</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>48.36</v>
+        <v>48.35</v>
       </c>
       <c r="AC26" s="4" t="n">
-        <v>51.64</v>
+        <v>51.65</v>
       </c>
       <c r="AD26" s="4" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>80</v>
@@ -3714,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>52.38</v>
+        <v>52.39</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>47.62</v>
+        <v>47.61</v>
       </c>
       <c r="AD28" s="4" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.9</v>
+        <v>19.91</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.8</v>
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-10.46</v>
+        <v>-10.45</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>3.1</v>
@@ -4287,13 +4287,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.98</v>
+        <v>-7</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>46.51</v>
+        <v>46.5</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>53.49</v>
+        <v>53.5</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-19.84</v>
+        <v>-19.9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.2</v>
@@ -4452,10 +4452,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>40.08</v>
+        <v>40.05</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>59.92</v>
+        <v>59.95</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Francesca Hong</t>
+          <t>David Crowley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4499,17 +4499,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.19</v>
+        <v>5.56</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>29.6</v>
+        <v>17.2</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Lean D</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="M36" s="4" t="n">
@@ -4519,10 +4519,10 @@
         <v>5.33</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>4.7</v>
+        <v>4.52</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="4" t="n">
         <v>0.28</v>
@@ -4531,19 +4531,19 @@
         <v>-0.87</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>42.64</v>
+        <v>47.93</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>43.55</v>
+        <v>43.59</v>
       </c>
       <c r="U36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>-0.66</v>
+        <v>7.34</v>
       </c>
       <c r="W36" s="5" t="n">
-        <v>13951</v>
+        <v>0</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>1</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>51.1</v>
+        <v>52.78</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>48.9</v>
+        <v>47.22</v>
       </c>
       <c r="AD36" s="4" t="n">
         <v>0</v>
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-2.38</v>
+        <v>-2.28</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4719,13 +4719,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.67</v>
+        <v>-2.55</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.13</v>
+        <v>-1</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.06</v>
@@ -4760,16 +4760,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.81</v>
+        <v>48.86</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.19</v>
+        <v>51.14</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-27.11</v>
+        <v>-27.12</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-30.13</v>
+        <v>-30.15</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-27.11</v>
+        <v>-27.12</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>-1.75</v>
@@ -4864,10 +4864,10 @@
         <v>0</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>36.45</v>
+        <v>36.44</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>63.55</v>
+        <v>63.56</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>0</v>
@@ -4929,13 +4929,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-8.34</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-1.26</v>
+        <v>-1.28</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>-0.45</v>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Victor McInnis</t>
+          <t>Lee McInnis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-40.07</v>
+        <v>-40.09</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -5037,13 +5037,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-40.9</v>
+        <v>-40.92</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-40.07</v>
+        <v>-40.09</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>-2.23</v>
@@ -5074,10 +5074,10 @@
         <v>0</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>29.96</v>
+        <v>29.95</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>70.04000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="AD41" s="4" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-60.25</v>
+        <v>-60.27</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -5139,13 +5139,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-61.15</v>
+        <v>-61.17</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-60.25</v>
+        <v>-60.27</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>-2.1</v>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-22.17</v>
+        <v>-22.19</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0.1</v>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-24.69</v>
+        <v>-24.71</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-22.17</v>
+        <v>-22.19</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>-0.59</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>38.91</v>
+        <v>38.9</v>
       </c>
       <c r="AC43" s="4" t="n">
-        <v>61.09</v>
+        <v>61.1</v>
       </c>
       <c r="AD43" s="4" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elizabeth Anderson</t>
+          <t>Keith Pilkington</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-28.28</v>
+        <v>-27.63</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5343,19 +5343,19 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-30.21</v>
+        <v>-30.23</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-28.28</v>
+        <v>-27.63</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>-2.14</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>-0.72</v>
+        <v>-2.19</v>
       </c>
       <c r="R44" s="4" t="n">
         <v>-34.79</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="5" t="n">
-        <v>15899</v>
+        <v>0</v>
       </c>
       <c r="X44" s="5" t="n">
         <v>1053566</v>
@@ -5380,10 +5380,10 @@
         <v>0</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>35.86</v>
+        <v>36.18</v>
       </c>
       <c r="AC44" s="4" t="n">
-        <v>64.14</v>
+        <v>63.82</v>
       </c>
       <c r="AD44" s="4" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Republican candidate (AL-07)</t>
+          <t>Ammie Akin</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>33.55</v>
+        <v>35.26</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>100</v>
@@ -5445,16 +5445,16 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>24.03</v>
+        <v>24.01</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>33.55</v>
+        <v>35.26</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q45" s="4" t="n">
         <v>4.31</v>
@@ -5472,7 +5472,7 @@
         <v>1961991</v>
       </c>
       <c r="X45" s="5" t="n">
-        <v>0</v>
+        <v>150730</v>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" s="4" t="n">
@@ -5482,10 +5482,10 @@
         <v>0</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>66.77</v>
+        <v>67.63</v>
       </c>
       <c r="AC45" s="4" t="n">
-        <v>33.23</v>
+        <v>32.37</v>
       </c>
       <c r="AD45" s="4" t="n">
         <v>0</v>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>-42.54</v>
+        <v>-42.55</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>0</v>
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>-41.29</v>
+        <v>-41.31</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>-42.54</v>
+        <v>-42.55</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>-1.62</v>
@@ -5584,10 +5584,10 @@
         <v>0</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>28.73</v>
+        <v>28.72</v>
       </c>
       <c r="AC46" s="4" t="n">
-        <v>71.27</v>
+        <v>71.28</v>
       </c>
       <c r="AD46" s="4" t="n">
         <v>0</v>
@@ -5635,13 +5635,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>-7.7</v>
+        <v>-7.72</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -5649,13 +5649,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-12.09</v>
+        <v>-12.1</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.41</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>-0.99</v>
@@ -5692,10 +5692,10 @@
         <v>0</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>46.15</v>
+        <v>46.14</v>
       </c>
       <c r="AC47" s="4" t="n">
-        <v>53.85</v>
+        <v>53.86</v>
       </c>
       <c r="AD47" s="4" t="n">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>-25.4</v>
+        <v>-25.41</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>0.1</v>
@@ -5757,13 +5757,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>-22.28</v>
+        <v>-22.29</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-25.4</v>
+        <v>-25.41</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>-1.82</v>
@@ -5794,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>37.3</v>
+        <v>37.29</v>
       </c>
       <c r="AC48" s="4" t="n">
-        <v>62.7</v>
+        <v>62.71</v>
       </c>
       <c r="AD48" s="4" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>-38.65</v>
+        <v>-38.67</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>0</v>
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>-35.65</v>
+        <v>-35.67</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>-38.65</v>
+        <v>-38.67</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>-2.88</v>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>80.7</v>
@@ -6051,21 +6051,21 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>38.2</v>
+        <v>61.7</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>61.8</v>
+        <v>38.3</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>-9.99</v>
+        <v>-9.98</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>5.33</v>
@@ -6108,10 +6108,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>49.99</v>
+        <v>50</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>50.01</v>
+        <v>50</v>
       </c>
       <c r="AD51" s="4" t="n">
         <v>0</v>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>60.74</v>
+        <v>60.75</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>100</v>
@@ -6179,7 +6179,7 @@
         <v>5.33</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>60.74</v>
+        <v>60.75</v>
       </c>
       <c r="P52" s="4" t="n">
         <v>0</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>20.24</v>
+        <v>20.25</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>99.8</v>
@@ -6281,7 +6281,7 @@
         <v>5.33</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>20.24</v>
+        <v>20.25</v>
       </c>
       <c r="P53" s="4" t="n">
         <v>0.99</v>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>81.3</v>
@@ -6569,7 +6569,7 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>39.66</v>
+        <v>39.67</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>100</v>
@@ -6589,7 +6589,7 @@
         <v>5.33</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>39.66</v>
+        <v>39.67</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>1.53</v>
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="M58" s="4" t="n">
-        <v>-26.83</v>
+        <v>-26.82</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>5.33</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>99.8</v>
@@ -6895,7 +6895,7 @@
         <v>5.33</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0.21</v>
@@ -7028,10 +7028,10 @@
         <v>0</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>66.84</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AC60" s="4" t="n">
-        <v>33.16</v>
+        <v>33.15</v>
       </c>
       <c r="AD60" s="4" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>12.99</v>
+        <v>13</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>5.33</v>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-18.06</v>
+        <v>-18.05</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>5.33</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>56.38</v>
+        <v>56.39</v>
       </c>
       <c r="AC64" s="4" t="n">
-        <v>43.62</v>
+        <v>43.61</v>
       </c>
       <c r="AD64" s="4" t="n">
         <v>0</v>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>16.81</v>
+        <v>16.82</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>5.33</v>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>49.34</v>
+        <v>49.35</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>100</v>
@@ -7609,7 +7609,7 @@
         <v>5.33</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>49.34</v>
+        <v>49.35</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>1.66</v>
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>17.49</v>
+        <v>17.5</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>5.33</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="M68" s="4" t="n">
-        <v>37.66</v>
+        <v>37.67</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>5.33</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>71.62</v>
+        <v>71.63</v>
       </c>
       <c r="AC68" s="4" t="n">
-        <v>28.38</v>
+        <v>28.37</v>
       </c>
       <c r="AD68" s="4" t="n">
         <v>0</v>
@@ -8007,13 +8007,13 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>80.95999999999999</v>
+        <v>80.97</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>88.22</v>
+        <v>88.23</v>
       </c>
       <c r="P70" s="4" t="n">
         <v>0</v>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="M71" s="4" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>5.33</v>
@@ -8146,10 +8146,10 @@
         <v>0</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>60.98</v>
+        <v>60.99</v>
       </c>
       <c r="AC71" s="4" t="n">
-        <v>39.02</v>
+        <v>39.01</v>
       </c>
       <c r="AD71" s="4" t="n">
         <v>0</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>58.58</v>
+        <v>58.59</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>100</v>
@@ -8309,13 +8309,13 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>53.98</v>
+        <v>53.99</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>58.58</v>
+        <v>58.59</v>
       </c>
       <c r="P73" s="4" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="5" t="n">
-        <v>822012</v>
+        <v>819662</v>
       </c>
       <c r="X73" s="5" t="n">
         <v>0</v>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>59.99</v>
+        <v>60</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>100</v>
@@ -8417,7 +8417,7 @@
         <v>5.33</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>59.99</v>
+        <v>60</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>45.33</v>
+        <v>45.34</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>5.33</v>
@@ -8550,10 +8550,10 @@
         <v>0</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>74.67</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="AC75" s="4" t="n">
-        <v>25.33</v>
+        <v>25.32</v>
       </c>
       <c r="AD75" s="4" t="n">
         <v>0</v>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>35.26</v>
+        <v>35.27</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>5.33</v>
@@ -8652,10 +8652,10 @@
         <v>0</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>72.14</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="AC76" s="4" t="n">
-        <v>27.86</v>
+        <v>27.85</v>
       </c>
       <c r="AD76" s="4" t="n">
         <v>0</v>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>49.64</v>
+        <v>49.65</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>100</v>
@@ -8754,10 +8754,10 @@
         <v>0</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>72.08</v>
+        <v>72.09</v>
       </c>
       <c r="AC77" s="4" t="n">
-        <v>24.26</v>
+        <v>24.25</v>
       </c>
       <c r="AD77" s="4" t="n">
         <v>3.66</v>
@@ -8856,10 +8856,10 @@
         <v>0</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>35.87</v>
+        <v>35.88</v>
       </c>
       <c r="AC78" s="4" t="n">
-        <v>64.13</v>
+        <v>64.12</v>
       </c>
       <c r="AD78" s="4" t="n">
         <v>0</v>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>21.25</v>
+        <v>21.26</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>99.8</v>
@@ -8927,7 +8927,7 @@
         <v>5.33</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>21.25</v>
+        <v>21.26</v>
       </c>
       <c r="P79" s="4" t="n">
         <v>0.95</v>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>84.09999999999999</v>
@@ -9029,7 +9029,7 @@
         <v>5.33</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>7.53</v>
+        <v>7.54</v>
       </c>
       <c r="P80" s="4" t="n">
         <v>-0.32</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>52.97</v>
+        <v>52.98</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47.03</v>
+        <v>47.02</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>-16.03</v>
+        <v>-16.02</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>0.5</v>
@@ -9131,13 +9131,13 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-16.56</v>
+        <v>-16.55</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>-16.03</v>
+        <v>-16.02</v>
       </c>
       <c r="P81" s="4" t="n">
         <v>-1.89</v>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>37</v>
+        <v>37.01</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>100</v>
@@ -9239,7 +9239,7 @@
         <v>5.33</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>37</v>
+        <v>37.01</v>
       </c>
       <c r="P82" s="4" t="n">
         <v>1.43</v>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20.1</v>
+        <v>20.11</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>99.8</v>
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="M83" s="4" t="n">
-        <v>10.6</v>
+        <v>10.61</v>
       </c>
       <c r="N83" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>20.1</v>
+        <v>20.11</v>
       </c>
       <c r="P83" s="4" t="n">
         <v>0.58</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="M84" s="4" t="n">
-        <v>19.25</v>
+        <v>19.26</v>
       </c>
       <c r="N84" s="4" t="n">
         <v>5.33</v>
@@ -9470,10 +9470,10 @@
         <v>0</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>63.08</v>
+        <v>63.09</v>
       </c>
       <c r="AC84" s="4" t="n">
-        <v>36.92</v>
+        <v>36.91</v>
       </c>
       <c r="AD84" s="4" t="n">
         <v>0</v>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>27.17</v>
+        <v>27.18</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>100</v>
@@ -9535,13 +9535,13 @@
         </is>
       </c>
       <c r="M85" s="4" t="n">
-        <v>14.38</v>
+        <v>14.39</v>
       </c>
       <c r="N85" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>27.17</v>
+        <v>27.18</v>
       </c>
       <c r="P85" s="4" t="n">
         <v>1.74</v>
@@ -9674,10 +9674,10 @@
         <v>0</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>70.06</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="AC86" s="4" t="n">
-        <v>29.94</v>
+        <v>29.93</v>
       </c>
       <c r="AD86" s="4" t="n">
         <v>0</v>
@@ -9745,7 +9745,7 @@
         <v>5.33</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>53.69</v>
+        <v>53.7</v>
       </c>
       <c r="P87" s="4" t="n">
         <v>0</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>76.01000000000001</v>
+        <v>76.02</v>
       </c>
       <c r="AC88" s="4" t="n">
-        <v>23.99</v>
+        <v>23.98</v>
       </c>
       <c r="AD88" s="4" t="n">
         <v>0</v>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.4</v>
+        <v>16.41</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>99.5</v>
@@ -9943,13 +9943,13 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>18.06</v>
+        <v>18.07</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>16.4</v>
+        <v>16.41</v>
       </c>
       <c r="P89" s="4" t="n">
         <v>1.31</v>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>39.88</v>
+        <v>39.89</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>100</v>
@@ -10051,7 +10051,7 @@
         <v>5.33</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>39.88</v>
+        <v>39.89</v>
       </c>
       <c r="P90" s="4" t="n">
         <v>2.65</v>
@@ -10255,7 +10255,7 @@
         <v>5.33</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>68.13</v>
+        <v>68.14</v>
       </c>
       <c r="P92" s="4" t="n">
         <v>0</v>
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="M93" s="4" t="n">
-        <v>14.27</v>
+        <v>14.28</v>
       </c>
       <c r="N93" s="4" t="n">
         <v>5.33</v>
@@ -10388,10 +10388,10 @@
         <v>0</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>63.31</v>
+        <v>63.32</v>
       </c>
       <c r="AC93" s="4" t="n">
-        <v>36.69</v>
+        <v>36.68</v>
       </c>
       <c r="AD93" s="4" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>75.7</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="AC94" s="4" t="n">
-        <v>24.3</v>
+        <v>24.29</v>
       </c>
       <c r="AD94" s="4" t="n">
         <v>0</v>
@@ -10555,7 +10555,7 @@
         </is>
       </c>
       <c r="M95" s="4" t="n">
-        <v>68</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="N95" s="4" t="n">
         <v>5.33</v>
@@ -10639,7 +10639,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>26.34</v>
+        <v>26.35</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>100</v>
@@ -10653,13 +10653,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="n">
-        <v>19.14</v>
+        <v>19.15</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>26.34</v>
+        <v>26.35</v>
       </c>
       <c r="P96" s="4" t="n">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>25.65</v>
+        <v>25.66</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>99.90000000000001</v>
@@ -10755,13 +10755,13 @@
         </is>
       </c>
       <c r="M97" s="4" t="n">
-        <v>16.16</v>
+        <v>16.17</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>25.65</v>
+        <v>25.66</v>
       </c>
       <c r="P97" s="4" t="n">
         <v>0</v>
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="n">
-        <v>-10.06</v>
+        <v>-10.05</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>-4.37</v>
+        <v>-4.36</v>
       </c>
       <c r="P98" s="4" t="n">
         <v>0</v>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="M99" s="4" t="n">
-        <v>19.7</v>
+        <v>19.71</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>5.33</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M100" s="4" t="n">
-        <v>16.94</v>
+        <v>16.95</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>5.33</v>
@@ -11149,7 +11149,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>63.79</v>
+        <v>63.8</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>100</v>
@@ -11163,13 +11163,13 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>56.91</v>
+        <v>56.92</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>63.79</v>
+        <v>63.8</v>
       </c>
       <c r="P101" s="4" t="n">
         <v>0</v>
@@ -11302,10 +11302,10 @@
         <v>0</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>79.61</v>
+        <v>79.62</v>
       </c>
       <c r="AC102" s="4" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="AD102" s="4" t="n">
         <v>0</v>
@@ -11367,7 +11367,7 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>8.380000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N103" s="4" t="n">
         <v>5.33</v>
@@ -11404,10 +11404,10 @@
         <v>0</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>60.3</v>
+        <v>60.31</v>
       </c>
       <c r="AC103" s="4" t="n">
-        <v>39.7</v>
+        <v>39.69</v>
       </c>
       <c r="AD103" s="4" t="n">
         <v>0</v>
@@ -11506,10 +11506,10 @@
         <v>0</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>69.86</v>
+        <v>69.87</v>
       </c>
       <c r="AC104" s="4" t="n">
-        <v>30.14</v>
+        <v>30.13</v>
       </c>
       <c r="AD104" s="4" t="n">
         <v>0</v>
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>23.54</v>
+        <v>23.55</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>99.90000000000001</v>
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="M105" s="4" t="n">
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="N105" s="4" t="n">
         <v>5.33</v>
@@ -11655,13 +11655,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>7.35</v>
+        <v>7.43</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -11712,10 +11712,10 @@
         <v>0</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>53.67</v>
+        <v>53.71</v>
       </c>
       <c r="AC106" s="4" t="n">
-        <v>46.33</v>
+        <v>46.29</v>
       </c>
       <c r="AD106" s="4" t="n">
         <v>0</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>22.27</v>
+        <v>22.28</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>99.90000000000001</v>
@@ -11777,13 +11777,13 @@
         </is>
       </c>
       <c r="M107" s="4" t="n">
-        <v>14.67</v>
+        <v>14.68</v>
       </c>
       <c r="N107" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O107" s="4" t="n">
-        <v>22.27</v>
+        <v>22.28</v>
       </c>
       <c r="P107" s="4" t="n">
         <v>2.54</v>
@@ -11916,10 +11916,10 @@
         <v>0</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>63.27</v>
+        <v>63.28</v>
       </c>
       <c r="AC108" s="4" t="n">
-        <v>36.73</v>
+        <v>36.72</v>
       </c>
       <c r="AD108" s="4" t="n">
         <v>0</v>
@@ -12083,7 +12083,7 @@
         </is>
       </c>
       <c r="M110" s="4" t="n">
-        <v>24.65</v>
+        <v>24.66</v>
       </c>
       <c r="N110" s="4" t="n">
         <v>5.33</v>
@@ -12120,10 +12120,10 @@
         <v>0</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>70.01000000000001</v>
+        <v>70.02</v>
       </c>
       <c r="AC110" s="4" t="n">
-        <v>29.99</v>
+        <v>29.98</v>
       </c>
       <c r="AD110" s="4" t="n">
         <v>0</v>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>-2.41</v>
+        <v>-2.4</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>28.8</v>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>-6.18</v>
+        <v>-6.19</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15.1</v>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>John Larson</t>
+          <t>Luke Bronin</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -12984,18 +12984,14 @@
           <t>Amy Chai</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
       <c r="I119" s="4" t="n">
-        <v>36.72</v>
+        <v>32.49</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>100</v>
@@ -13015,13 +13011,13 @@
         <v>5.33</v>
       </c>
       <c r="O119" s="4" t="n">
-        <v>36.72</v>
+        <v>32.49</v>
       </c>
       <c r="P119" s="4" t="n">
-        <v>2.36</v>
+        <v>1.59</v>
       </c>
       <c r="Q119" s="4" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="R119" s="4" t="n">
         <v>23.27</v>
@@ -13033,7 +13029,7 @@
       </c>
       <c r="V119" s="4" t="n"/>
       <c r="W119" s="5" t="n">
-        <v>2733260</v>
+        <v>3070151</v>
       </c>
       <c r="X119" s="5" t="n">
         <v>20827</v>
@@ -13046,10 +13042,10 @@
         <v>0</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>68.36</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AC119" s="4" t="n">
-        <v>31.64</v>
+        <v>33.76</v>
       </c>
       <c r="AD119" s="4" t="n">
         <v>0</v>
@@ -13083,7 +13079,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mike France</t>
+          <t>George Austin</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -13097,13 +13093,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>27.77</v>
+        <v>22.79</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -13117,13 +13113,13 @@
         <v>5.33</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>27.77</v>
+        <v>22.79</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>1.43</v>
+        <v>0.66</v>
       </c>
       <c r="Q120" s="4" t="n">
-        <v>12.1</v>
+        <v>7.88</v>
       </c>
       <c r="R120" s="4" t="n">
         <v>7.86</v>
@@ -13138,7 +13134,7 @@
         <v>760424</v>
       </c>
       <c r="X120" s="5" t="n">
-        <v>70790</v>
+        <v>283997</v>
       </c>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" s="4" t="n">
@@ -13148,10 +13144,10 @@
         <v>0</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>63.88</v>
+        <v>61.39</v>
       </c>
       <c r="AC120" s="4" t="n">
-        <v>36.12</v>
+        <v>38.61</v>
       </c>
       <c r="AD120" s="4" t="n">
         <v>0</v>
@@ -13250,10 +13246,10 @@
         <v>0</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>64.41</v>
       </c>
       <c r="AC121" s="4" t="n">
-        <v>35.6</v>
+        <v>35.59</v>
       </c>
       <c r="AD121" s="4" t="n">
         <v>0</v>
@@ -13352,10 +13348,10 @@
         <v>0</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>67.63</v>
+        <v>67.64</v>
       </c>
       <c r="AC122" s="4" t="n">
-        <v>32.37</v>
+        <v>32.36</v>
       </c>
       <c r="AD122" s="4" t="n">
         <v>0</v>
@@ -13389,7 +13385,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Michele Botelho</t>
+          <t>Chris Shea</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -13403,13 +13399,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>15.72</v>
+        <v>14.81</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -13417,16 +13413,16 @@
         </is>
       </c>
       <c r="M123" s="4" t="n">
-        <v>7.78</v>
+        <v>7.79</v>
       </c>
       <c r="N123" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O123" s="4" t="n">
-        <v>15.72</v>
+        <v>14.81</v>
       </c>
       <c r="P123" s="4" t="n">
-        <v>1.9</v>
+        <v>0.98</v>
       </c>
       <c r="Q123" s="4" t="n">
         <v>0.67</v>
@@ -13444,7 +13440,7 @@
         <v>1290078</v>
       </c>
       <c r="X123" s="5" t="n">
-        <v>56497</v>
+        <v>311676</v>
       </c>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" s="4" t="n">
@@ -13454,10 +13450,10 @@
         <v>0</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>57.86</v>
+        <v>57.4</v>
       </c>
       <c r="AC123" s="4" t="n">
-        <v>42.14</v>
+        <v>42.6</v>
       </c>
       <c r="AD123" s="4" t="n">
         <v>0</v>
@@ -13705,7 +13701,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>-13.2</v>
+        <v>-13.16</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>0.9</v>
@@ -13762,10 +13758,10 @@
         <v>0</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>43.4</v>
+        <v>43.42</v>
       </c>
       <c r="AC126" s="4" t="n">
-        <v>56.6</v>
+        <v>56.58</v>
       </c>
       <c r="AD126" s="4" t="n">
         <v>0</v>
@@ -14221,7 +14217,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>-3.99</v>
+        <v>-4</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>22.8</v>
@@ -14278,10 +14274,10 @@
         <v>0</v>
       </c>
       <c r="AB131" s="4" t="n">
-        <v>48.01</v>
+        <v>48</v>
       </c>
       <c r="AC131" s="4" t="n">
-        <v>51.99</v>
+        <v>52</v>
       </c>
       <c r="AD131" s="4" t="n">
         <v>0</v>
@@ -14329,7 +14325,7 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-10.3</v>
+        <v>-10.28</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>3.5</v>
@@ -14386,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>44.85</v>
+        <v>44.86</v>
       </c>
       <c r="AC132" s="4" t="n">
-        <v>55.15</v>
+        <v>55.14</v>
       </c>
       <c r="AD132" s="4" t="n">
         <v>0</v>
@@ -14437,7 +14433,7 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>74.59999999999999</v>
@@ -14457,7 +14453,7 @@
         <v>5.33</v>
       </c>
       <c r="O133" s="4" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="P133" s="4" t="n">
         <v>-0.26</v>
@@ -14637,13 +14633,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>-7.86</v>
+        <v>-7.88</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -14657,10 +14653,10 @@
         <v>5.33</v>
       </c>
       <c r="O135" s="4" t="n">
-        <v>-7.86</v>
+        <v>-7.88</v>
       </c>
       <c r="P135" s="4" t="n">
-        <v>-1.17</v>
+        <v>-1.19</v>
       </c>
       <c r="Q135" s="4" t="n">
         <v>-0.83</v>
@@ -14688,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="AB135" s="4" t="n">
-        <v>46.07</v>
+        <v>46.06</v>
       </c>
       <c r="AC135" s="4" t="n">
-        <v>53.93</v>
+        <v>53.94</v>
       </c>
       <c r="AD135" s="4" t="n">
         <v>0</v>
@@ -15149,7 +15145,7 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>-4.62</v>
+        <v>-4.63</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>20.5</v>
@@ -15169,10 +15165,10 @@
         <v>5.33</v>
       </c>
       <c r="O140" s="4" t="n">
-        <v>-4.62</v>
+        <v>-4.63</v>
       </c>
       <c r="P140" s="4" t="n">
-        <v>-1.17</v>
+        <v>-1.18</v>
       </c>
       <c r="Q140" s="4" t="n">
         <v>0</v>
@@ -15749,13 +15745,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -15769,7 +15765,7 @@
         <v>5.33</v>
       </c>
       <c r="O146" s="4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P146" s="4" t="n">
         <v>-0.74</v>
@@ -15806,10 +15802,10 @@
         <v>0</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>49.94</v>
+        <v>49.95</v>
       </c>
       <c r="AC146" s="4" t="n">
-        <v>50.06</v>
+        <v>50.05</v>
       </c>
       <c r="AD146" s="4" t="n">
         <v>0</v>
@@ -15955,7 +15951,7 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>56.25</v>
+        <v>56.27</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>100</v>
@@ -15975,10 +15971,10 @@
         <v>5.33</v>
       </c>
       <c r="O148" s="4" t="n">
-        <v>56.25</v>
+        <v>56.27</v>
       </c>
       <c r="P148" s="4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q148" s="4" t="n">
         <v>0</v>
@@ -16057,7 +16053,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>87.8</v>
@@ -16479,7 +16475,7 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>-8.359999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>8.4</v>
@@ -16493,13 +16489,13 @@
         </is>
       </c>
       <c r="M153" s="4" t="n">
-        <v>-11.48</v>
+        <v>-11.49</v>
       </c>
       <c r="N153" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>-8.359999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="P153" s="4" t="n">
         <v>-1.91</v>
@@ -16581,7 +16577,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>24.49</v>
+        <v>24.48</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>99.90000000000001</v>
@@ -16601,7 +16597,7 @@
         <v>5.33</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>24.49</v>
+        <v>24.48</v>
       </c>
       <c r="P154" s="4" t="n">
         <v>1.36</v>
@@ -16683,7 +16679,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>-28.92</v>
+        <v>-28.93</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>0</v>
@@ -16703,7 +16699,7 @@
         <v>5.33</v>
       </c>
       <c r="O155" s="4" t="n">
-        <v>-28.92</v>
+        <v>-28.93</v>
       </c>
       <c r="P155" s="4" t="n">
         <v>-1.75</v>
@@ -16785,7 +16781,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>65.59</v>
+        <v>65.58</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>100</v>
@@ -16805,7 +16801,7 @@
         <v>5.33</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>65.59</v>
+        <v>65.58</v>
       </c>
       <c r="P156" s="4" t="n">
         <v>0</v>
@@ -16887,7 +16883,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>84.04000000000001</v>
+        <v>84.03</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>100</v>
@@ -16901,13 +16897,13 @@
         </is>
       </c>
       <c r="M157" s="4" t="n">
-        <v>76.78</v>
+        <v>76.77</v>
       </c>
       <c r="N157" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O157" s="4" t="n">
-        <v>84.04000000000001</v>
+        <v>84.03</v>
       </c>
       <c r="P157" s="4" t="n">
         <v>0</v>
@@ -16989,7 +16985,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>63.34</v>
+        <v>63.33</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>100</v>
@@ -17009,7 +17005,7 @@
         <v>5.33</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>63.34</v>
+        <v>63.33</v>
       </c>
       <c r="P158" s="4" t="n">
         <v>2.07</v>
@@ -17193,7 +17189,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-29.54</v>
+        <v>-29.55</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>0</v>
@@ -17207,13 +17203,13 @@
         </is>
       </c>
       <c r="M160" s="4" t="n">
-        <v>-26.2</v>
+        <v>-26.21</v>
       </c>
       <c r="N160" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O160" s="4" t="n">
-        <v>-29.54</v>
+        <v>-29.55</v>
       </c>
       <c r="P160" s="4" t="n">
         <v>-2.36</v>
@@ -17309,7 +17305,7 @@
         </is>
       </c>
       <c r="M161" s="4" t="n">
-        <v>-30.52</v>
+        <v>-30.53</v>
       </c>
       <c r="N161" s="4" t="n">
         <v>5.33</v>
@@ -17333,7 +17329,7 @@
       </c>
       <c r="V161" s="4" t="n"/>
       <c r="W161" s="5" t="n">
-        <v>155052</v>
+        <v>156067</v>
       </c>
       <c r="X161" s="5" t="n">
         <v>671072</v>
@@ -17444,10 +17440,10 @@
         <v>0</v>
       </c>
       <c r="AB162" s="4" t="n">
-        <v>42</v>
+        <v>41.99</v>
       </c>
       <c r="AC162" s="4" t="n">
-        <v>58</v>
+        <v>58.01</v>
       </c>
       <c r="AD162" s="4" t="n">
         <v>0</v>
@@ -17505,7 +17501,7 @@
         </is>
       </c>
       <c r="M163" s="4" t="n">
-        <v>-19.89</v>
+        <v>-19.9</v>
       </c>
       <c r="N163" s="4" t="n">
         <v>5.33</v>
@@ -17542,10 +17538,10 @@
         <v>0</v>
       </c>
       <c r="AB163" s="4" t="n">
-        <v>41.45</v>
+        <v>41.44</v>
       </c>
       <c r="AC163" s="4" t="n">
-        <v>58.55</v>
+        <v>58.56</v>
       </c>
       <c r="AD163" s="4" t="n">
         <v>0</v>
@@ -17593,7 +17589,7 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-11.44</v>
+        <v>-11.45</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>1.3</v>
@@ -17613,7 +17609,7 @@
         <v>5.33</v>
       </c>
       <c r="O164" s="4" t="n">
-        <v>-11.44</v>
+        <v>-11.45</v>
       </c>
       <c r="P164" s="4" t="n">
         <v>-1.96</v>
@@ -17691,7 +17687,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>51.13</v>
+        <v>51.12</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>100</v>
@@ -17705,13 +17701,13 @@
         </is>
       </c>
       <c r="M165" s="4" t="n">
-        <v>45.53</v>
+        <v>45.52</v>
       </c>
       <c r="N165" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>51.13</v>
+        <v>51.12</v>
       </c>
       <c r="P165" s="4" t="n">
         <v>0</v>
@@ -18099,13 +18095,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11.47</v>
+        <v>11.49</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -18203,13 +18199,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -18223,7 +18219,7 @@
         <v>5.33</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="P170" s="4" t="n">
         <v>-0.04</v>
@@ -18331,7 +18327,7 @@
         <v>5.33</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.06</v>
@@ -18415,7 +18411,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-20.85</v>
+        <v>-20.86</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.2</v>
@@ -18435,7 +18431,7 @@
         <v>5.33</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-20.85</v>
+        <v>-20.86</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -18517,7 +18513,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-29.92</v>
+        <v>-30.11</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18537,7 +18533,7 @@
         <v>5.33</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-41.21</v>
+        <v>-41.22</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18574,10 +18570,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>35.04</v>
+        <v>34.95</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18639,7 +18635,7 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-26.03</v>
+        <v>-26.04</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.33</v>
@@ -18676,10 +18672,10 @@
         <v>0</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>36.08</v>
+        <v>36.07</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>63.92</v>
+        <v>63.93</v>
       </c>
       <c r="AD174" s="4" t="n">
         <v>0</v>
@@ -19025,7 +19021,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>31.77</v>
+        <v>32.02</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>100</v>
@@ -19082,10 +19078,10 @@
         <v>0</v>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>65.88</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="AC178" s="4" t="n">
-        <v>34.12</v>
+        <v>33.99</v>
       </c>
       <c r="AD178" s="4" t="n">
         <v>0</v>
@@ -20855,7 +20851,7 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-11.25</v>
+        <v>-11.32</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>1.3</v>
@@ -20912,10 +20908,10 @@
         <v>0</v>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>44.37</v>
+        <v>44.34</v>
       </c>
       <c r="AC196" s="4" t="n">
-        <v>55.63</v>
+        <v>55.66</v>
       </c>
       <c r="AD196" s="4" t="n">
         <v>0</v>
@@ -21626,10 +21622,10 @@
         <v>0</v>
       </c>
       <c r="AB203" s="4" t="n">
-        <v>60.47</v>
+        <v>60.46</v>
       </c>
       <c r="AC203" s="4" t="n">
-        <v>39.53</v>
+        <v>39.54</v>
       </c>
       <c r="AD203" s="4" t="n">
         <v>0</v>
@@ -22281,13 +22277,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-6.81</v>
+        <v>-6.84</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>86.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -22338,10 +22334,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.59</v>
+        <v>46.58</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.41</v>
+        <v>53.42</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -22993,7 +22989,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>24.42</v>
+        <v>24.43</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23013,7 +23009,7 @@
         <v>5.33</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>24.42</v>
+        <v>24.43</v>
       </c>
       <c r="P217" s="4" t="n">
         <v>0</v>
@@ -23095,7 +23091,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>34.04</v>
+        <v>34.05</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -23109,13 +23105,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>27.49</v>
+        <v>27.5</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>34.04</v>
+        <v>34.05</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -23211,7 +23207,7 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>23</v>
+        <v>23.01</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>5.33</v>
@@ -23313,7 +23309,7 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.82</v>
+        <v>23.83</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>5.33</v>
@@ -23415,7 +23411,7 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>49.18</v>
+        <v>49.19</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>5.33</v>
@@ -23601,7 +23597,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>76.51000000000001</v>
+        <v>76.52</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -23615,13 +23611,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>69.19</v>
+        <v>69.2</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>76.51000000000001</v>
+        <v>76.52</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -23652,10 +23648,10 @@
         <v>0</v>
       </c>
       <c r="AB223" s="4" t="n">
-        <v>88.25</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="AC223" s="4" t="n">
-        <v>11.75</v>
+        <v>11.74</v>
       </c>
       <c r="AD223" s="4" t="n">
         <v>0</v>
@@ -23717,7 +23713,7 @@
         </is>
       </c>
       <c r="M224" s="4" t="n">
-        <v>30.59</v>
+        <v>30.6</v>
       </c>
       <c r="N224" s="4" t="n">
         <v>5.33</v>
@@ -23754,10 +23750,10 @@
         <v>0</v>
       </c>
       <c r="AB224" s="4" t="n">
-        <v>72.91</v>
+        <v>72.92</v>
       </c>
       <c r="AC224" s="4" t="n">
-        <v>27.09</v>
+        <v>27.08</v>
       </c>
       <c r="AD224" s="4" t="n">
         <v>0</v>
@@ -23805,7 +23801,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.86</v>
+        <v>22.87</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23825,7 +23821,7 @@
         <v>5.33</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.86</v>
+        <v>22.87</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.53</v>
@@ -24715,7 +24711,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.63</v>
+        <v>30.38</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24766,10 +24762,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.33</v>
+        <v>62.32</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.67</v>
+        <v>32.68</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24813,13 +24809,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-3.74</v>
+        <v>-4.09</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>38.4</v>
+        <v>37</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>61.6</v>
+        <v>63</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24827,13 +24823,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-9.09</v>
+        <v>-9.1</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.24</v>
+        <v>-5.25</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24921,7 +24917,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>-13.38</v>
+        <v>-13.37</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>0.9</v>
@@ -24935,13 +24931,13 @@
         </is>
       </c>
       <c r="M236" s="4" t="n">
-        <v>-18.07</v>
+        <v>-18.06</v>
       </c>
       <c r="N236" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O236" s="4" t="n">
-        <v>-13.38</v>
+        <v>-13.37</v>
       </c>
       <c r="P236" s="4" t="n">
         <v>-0.61</v>
@@ -25023,7 +25019,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>-28.32</v>
+        <v>-28.31</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>0</v>
@@ -25043,7 +25039,7 @@
         <v>5.33</v>
       </c>
       <c r="O237" s="4" t="n">
-        <v>-28.32</v>
+        <v>-28.31</v>
       </c>
       <c r="P237" s="4" t="n">
         <v>-1.9</v>
@@ -25125,7 +25121,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>21.06</v>
+        <v>21.07</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25139,13 +25135,13 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>10.92</v>
+        <v>10.93</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>21.06</v>
+        <v>21.07</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>0.96</v>
@@ -25176,10 +25172,10 @@
         <v>0</v>
       </c>
       <c r="AB238" s="4" t="n">
-        <v>60.53</v>
+        <v>60.54</v>
       </c>
       <c r="AC238" s="4" t="n">
-        <v>39.47</v>
+        <v>39.46</v>
       </c>
       <c r="AD238" s="4" t="n">
         <v>0</v>
@@ -25241,7 +25237,7 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-2.24</v>
+        <v>-2.23</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>5.33</v>
@@ -25335,7 +25331,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-26.11</v>
+        <v>-26.1</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0</v>
@@ -25349,13 +25345,13 @@
         </is>
       </c>
       <c r="M240" s="4" t="n">
-        <v>-23.44</v>
+        <v>-23.43</v>
       </c>
       <c r="N240" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-26.11</v>
+        <v>-26.1</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.12</v>
@@ -25437,7 +25433,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>38.05</v>
+        <v>38.06</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -25451,13 +25447,13 @@
         </is>
       </c>
       <c r="M241" s="4" t="n">
-        <v>27.74</v>
+        <v>27.75</v>
       </c>
       <c r="N241" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>38.05</v>
+        <v>38.06</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -25539,7 +25535,7 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="J242" s="4" t="n">
         <v>66.2</v>
@@ -25553,13 +25549,13 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O242" s="4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="P242" s="4" t="n">
         <v>-1.12</v>
@@ -25596,10 +25592,10 @@
         <v>0</v>
       </c>
       <c r="AB242" s="4" t="n">
-        <v>50.56</v>
+        <v>50.57</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.44</v>
+        <v>49.43</v>
       </c>
       <c r="AD242" s="4" t="n">
         <v>0</v>
@@ -25647,13 +25643,13 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>16.94</v>
+        <v>16.95</v>
       </c>
       <c r="J243" s="4" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="K243" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -25661,13 +25657,13 @@
         </is>
       </c>
       <c r="M243" s="4" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="N243" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>16.94</v>
+        <v>16.95</v>
       </c>
       <c r="P243" s="4" t="n">
         <v>0</v>
@@ -25749,7 +25745,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-33.12</v>
+        <v>-33.11</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -25763,13 +25759,13 @@
         </is>
       </c>
       <c r="M244" s="4" t="n">
-        <v>-28.97</v>
+        <v>-28.96</v>
       </c>
       <c r="N244" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-33.12</v>
+        <v>-33.11</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -25800,10 +25796,10 @@
         <v>0</v>
       </c>
       <c r="AB244" s="4" t="n">
-        <v>33.44</v>
+        <v>33.45</v>
       </c>
       <c r="AC244" s="4" t="n">
-        <v>66.56</v>
+        <v>66.55</v>
       </c>
       <c r="AD244" s="4" t="n">
         <v>0</v>
@@ -25861,7 +25857,7 @@
         </is>
       </c>
       <c r="M245" s="4" t="n">
-        <v>-2.18</v>
+        <v>-2.17</v>
       </c>
       <c r="N245" s="4" t="n">
         <v>5.33</v>
@@ -25951,7 +25947,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>26.65</v>
+        <v>26.66</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>100</v>
@@ -25965,13 +25961,13 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O246" s="4" t="n">
-        <v>26.65</v>
+        <v>26.66</v>
       </c>
       <c r="P246" s="4" t="n">
         <v>1.6</v>
@@ -26002,10 +25998,10 @@
         <v>0</v>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>63.32</v>
+        <v>63.33</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>36.68</v>
+        <v>36.67</v>
       </c>
       <c r="AD246" s="4" t="n">
         <v>0</v>
@@ -26053,7 +26049,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>58.68</v>
+        <v>58.69</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -26067,13 +26063,13 @@
         </is>
       </c>
       <c r="M247" s="4" t="n">
-        <v>45.41</v>
+        <v>45.42</v>
       </c>
       <c r="N247" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O247" s="4" t="n">
-        <v>58.68</v>
+        <v>58.69</v>
       </c>
       <c r="P247" s="4" t="n">
         <v>2.96</v>
@@ -26155,7 +26151,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>58.42</v>
+        <v>58.43</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -26169,13 +26165,13 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>47.9</v>
+        <v>47.91</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>58.42</v>
+        <v>58.43</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
@@ -26257,13 +26253,13 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>-5.87</v>
+        <v>-6.29</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>16.2</v>
+        <v>14.8</v>
       </c>
       <c r="K249" s="4" t="n">
-        <v>83.8</v>
+        <v>85.2</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -26271,13 +26267,13 @@
         </is>
       </c>
       <c r="M249" s="4" t="n">
-        <v>-9</v>
+        <v>-9.51</v>
       </c>
       <c r="N249" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O249" s="4" t="n">
-        <v>-6.05</v>
+        <v>-6.57</v>
       </c>
       <c r="P249" s="4" t="n">
         <v>-0.01</v>
@@ -26314,10 +26310,10 @@
         <v>0</v>
       </c>
       <c r="AB249" s="4" t="n">
-        <v>47.07</v>
+        <v>46.85</v>
       </c>
       <c r="AC249" s="4" t="n">
-        <v>52.93</v>
+        <v>53.15</v>
       </c>
       <c r="AD249" s="4" t="n">
         <v>0</v>
@@ -26361,13 +26357,13 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>12.35</v>
+        <v>11.99</v>
       </c>
       <c r="J250" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="K250" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -26375,13 +26371,13 @@
         </is>
       </c>
       <c r="M250" s="4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N250" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O250" s="4" t="n">
-        <v>13.83</v>
+        <v>13.32</v>
       </c>
       <c r="P250" s="4" t="n">
         <v>0.52</v>
@@ -26418,10 +26414,10 @@
         <v>0</v>
       </c>
       <c r="AB250" s="4" t="n">
-        <v>56.18</v>
+        <v>55.99</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>43.82</v>
+        <v>44.01</v>
       </c>
       <c r="AD250" s="4" t="n">
         <v>0</v>
@@ -26469,7 +26465,7 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>30.19</v>
+        <v>29.68</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>100</v>
@@ -26483,13 +26479,13 @@
         </is>
       </c>
       <c r="M251" s="4" t="n">
-        <v>23.91</v>
+        <v>23.39</v>
       </c>
       <c r="N251" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O251" s="4" t="n">
-        <v>30.19</v>
+        <v>29.68</v>
       </c>
       <c r="P251" s="4" t="n">
         <v>0</v>
@@ -26520,10 +26516,10 @@
         <v>0</v>
       </c>
       <c r="AB251" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>64.84</v>
       </c>
       <c r="AC251" s="4" t="n">
-        <v>34.9</v>
+        <v>35.16</v>
       </c>
       <c r="AD251" s="4" t="n">
         <v>0</v>
@@ -26571,7 +26567,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>47.94</v>
+        <v>47.43</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>100</v>
@@ -26585,13 +26581,13 @@
         </is>
       </c>
       <c r="M252" s="4" t="n">
-        <v>39.6</v>
+        <v>39.09</v>
       </c>
       <c r="N252" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O252" s="4" t="n">
-        <v>47.94</v>
+        <v>47.43</v>
       </c>
       <c r="P252" s="4" t="n">
         <v>2.11</v>
@@ -26622,10 +26618,10 @@
         <v>0</v>
       </c>
       <c r="AB252" s="4" t="n">
-        <v>73.97</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="AC252" s="4" t="n">
-        <v>26.03</v>
+        <v>26.29</v>
       </c>
       <c r="AD252" s="4" t="n">
         <v>0</v>
@@ -26659,7 +26655,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Dalia Al-Aqidi</t>
+          <t>John Nagel</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -26673,7 +26669,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>66.09</v>
+        <v>65.86</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>100</v>
@@ -26687,16 +26683,16 @@
         </is>
       </c>
       <c r="M253" s="4" t="n">
-        <v>66.43000000000001</v>
+        <v>65.92</v>
       </c>
       <c r="N253" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O253" s="4" t="n">
-        <v>66.09</v>
+        <v>65.86</v>
       </c>
       <c r="P253" s="4" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Q253" s="4" t="n">
         <v>-6.48</v>
@@ -26714,7 +26710,7 @@
         <v>5829715</v>
       </c>
       <c r="X253" s="5" t="n">
-        <v>1128979</v>
+        <v>747046</v>
       </c>
       <c r="Y253" t="inlineStr"/>
       <c r="Z253" s="4" t="n">
@@ -26724,10 +26720,10 @@
         <v>0</v>
       </c>
       <c r="AB253" s="4" t="n">
-        <v>83.04000000000001</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="AC253" s="4" t="n">
-        <v>16.96</v>
+        <v>17.07</v>
       </c>
       <c r="AD253" s="4" t="n">
         <v>0</v>
@@ -26756,7 +26752,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Democratic candidate (MN-06)</t>
+          <t>Doug Chapin</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -26775,13 +26771,13 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-14.37</v>
+        <v>-17.14</v>
       </c>
       <c r="J254" s="4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K254" s="4" t="n">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -26789,16 +26785,16 @@
         </is>
       </c>
       <c r="M254" s="4" t="n">
-        <v>-17.18</v>
+        <v>-17.7</v>
       </c>
       <c r="N254" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-14.37</v>
+        <v>-17.14</v>
       </c>
       <c r="P254" s="4" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="Q254" s="4" t="n">
         <v>-1.67</v>
@@ -26813,7 +26809,7 @@
       </c>
       <c r="V254" s="4" t="n"/>
       <c r="W254" s="5" t="n">
-        <v>0</v>
+        <v>438700</v>
       </c>
       <c r="X254" s="5" t="n">
         <v>9786064</v>
@@ -26826,10 +26822,10 @@
         <v>0</v>
       </c>
       <c r="AB254" s="4" t="n">
-        <v>42.81</v>
+        <v>41.43</v>
       </c>
       <c r="AC254" s="4" t="n">
-        <v>57.19</v>
+        <v>58.57</v>
       </c>
       <c r="AD254" s="4" t="n">
         <v>0</v>
@@ -26858,7 +26854,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Democratic candidate (MN-07)</t>
+          <t>Erik Osberg</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -26877,7 +26873,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>-30.71</v>
+        <v>-32.16</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>0</v>
@@ -26891,16 +26887,16 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-33.53</v>
+        <v>-34.05</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O255" s="4" t="n">
-        <v>-30.71</v>
+        <v>-32.16</v>
       </c>
       <c r="P255" s="4" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="Q255" s="4" t="n">
         <v>-1.67</v>
@@ -26915,7 +26911,7 @@
       </c>
       <c r="V255" s="4" t="n"/>
       <c r="W255" s="5" t="n">
-        <v>0</v>
+        <v>334945</v>
       </c>
       <c r="X255" s="5" t="n">
         <v>1286028</v>
@@ -26928,10 +26924,10 @@
         <v>0</v>
       </c>
       <c r="AB255" s="4" t="n">
-        <v>34.65</v>
+        <v>33.92</v>
       </c>
       <c r="AC255" s="4" t="n">
-        <v>65.34999999999999</v>
+        <v>66.08</v>
       </c>
       <c r="AD255" s="4" t="n">
         <v>0</v>
@@ -26960,7 +26956,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Democratic candidate (MN-08)</t>
+          <t>Trina Swanson</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -26979,30 +26975,30 @@
         </is>
       </c>
       <c r="I256" s="4" t="n">
-        <v>-8.390000000000001</v>
+        <v>-10.2</v>
       </c>
       <c r="J256" s="4" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="K256" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="M256" s="4" t="n">
-        <v>-10.99</v>
+        <v>-11.51</v>
       </c>
       <c r="N256" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O256" s="4" t="n">
-        <v>-8.390000000000001</v>
+        <v>-10.2</v>
       </c>
       <c r="P256" s="4" t="n">
-        <v>0</v>
+        <v>-1.29</v>
       </c>
       <c r="Q256" s="4" t="n">
         <v>-1.67</v>
@@ -27017,7 +27013,7 @@
       </c>
       <c r="V256" s="4" t="n"/>
       <c r="W256" s="5" t="n">
-        <v>0</v>
+        <v>316706</v>
       </c>
       <c r="X256" s="5" t="n">
         <v>1996898</v>
@@ -27030,10 +27026,10 @@
         <v>0</v>
       </c>
       <c r="AB256" s="4" t="n">
-        <v>45.81</v>
+        <v>44.9</v>
       </c>
       <c r="AC256" s="4" t="n">
-        <v>54.19</v>
+        <v>55.1</v>
       </c>
       <c r="AD256" s="4" t="n">
         <v>0</v>
@@ -27183,13 +27179,13 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.69</v>
+        <v>-10.7</v>
       </c>
       <c r="J258" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K258" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -27240,10 +27236,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.66</v>
+        <v>44.65</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.34</v>
+        <v>55.35</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -28303,7 +28299,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-6.83</v>
+        <v>-6.84</v>
       </c>
       <c r="J269" s="4" t="n">
         <v>13</v>
@@ -28317,13 +28313,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.26</v>
+        <v>-12.25</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.06</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28462,10 +28458,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>33.1</v>
+        <v>33.11</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.89</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28513,7 +28509,7 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="J271" s="4" t="n">
         <v>72.7</v>
@@ -28621,7 +28617,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>45.45</v>
+        <v>45.44</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -28635,13 +28631,13 @@
         </is>
       </c>
       <c r="M272" s="4" t="n">
-        <v>36.92</v>
+        <v>36.91</v>
       </c>
       <c r="N272" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O272" s="4" t="n">
-        <v>45.45</v>
+        <v>45.44</v>
       </c>
       <c r="P272" s="4" t="n">
         <v>0</v>
@@ -28825,7 +28821,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>58.96</v>
+        <v>58.95</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>100</v>
@@ -28845,7 +28841,7 @@
         <v>5.33</v>
       </c>
       <c r="O274" s="4" t="n">
-        <v>58.96</v>
+        <v>58.95</v>
       </c>
       <c r="P274" s="4" t="n">
         <v>1.88</v>
@@ -28927,7 +28923,7 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>-10.67</v>
+        <v>-10.68</v>
       </c>
       <c r="J275" s="4" t="n">
         <v>2.6</v>
@@ -28947,7 +28943,7 @@
         <v>5.33</v>
       </c>
       <c r="O275" s="4" t="n">
-        <v>-10.67</v>
+        <v>-10.68</v>
       </c>
       <c r="P275" s="4" t="n">
         <v>-0.92</v>
@@ -29131,7 +29127,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>-10.52</v>
+        <v>-10.53</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>2.9</v>
@@ -29233,7 +29229,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-16.9</v>
+        <v>-16.91</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.5</v>
@@ -29253,7 +29249,7 @@
         <v>5.33</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-16.9</v>
+        <v>-16.91</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.86</v>
@@ -29437,7 +29433,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>-15.53</v>
+        <v>-15.54</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>0.6</v>
@@ -29745,7 +29741,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-13.42</v>
+        <v>-13.43</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>0.9</v>
@@ -29759,7 +29755,7 @@
         </is>
       </c>
       <c r="M283" s="4" t="n">
-        <v>-14.64</v>
+        <v>-14.65</v>
       </c>
       <c r="N283" s="4" t="n">
         <v>5.33</v>
@@ -29847,7 +29843,7 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>-12.94</v>
+        <v>-12.95</v>
       </c>
       <c r="J284" s="4" t="n">
         <v>1</v>
@@ -29861,7 +29857,7 @@
         </is>
       </c>
       <c r="M284" s="4" t="n">
-        <v>-13.44</v>
+        <v>-13.45</v>
       </c>
       <c r="N284" s="4" t="n">
         <v>5.33</v>
@@ -30114,10 +30110,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.39</v>
+        <v>45.38</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.61</v>
+        <v>54.62</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30161,7 +30157,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>13.01</v>
+        <v>13</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>99</v>
@@ -30390,7 +30386,7 @@
         <v>5.32</v>
       </c>
       <c r="P289" s="4" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="Q289" s="4" t="n">
         <v>0</v>
@@ -30469,7 +30465,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>16.14</v>
+        <v>16.13</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>99.5</v>
@@ -31195,7 +31191,7 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="J297" s="4" t="n">
         <v>80.40000000000001</v>
@@ -31252,10 +31248,10 @@
         <v>0</v>
       </c>
       <c r="AB297" s="4" t="n">
-        <v>52.43</v>
+        <v>52.44</v>
       </c>
       <c r="AC297" s="4" t="n">
-        <v>47.57</v>
+        <v>47.56</v>
       </c>
       <c r="AD297" s="4" t="n">
         <v>0</v>
@@ -31809,7 +31805,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>26.24</v>
+        <v>26.25</v>
       </c>
       <c r="J303" s="4" t="n">
         <v>100</v>
@@ -31823,13 +31819,13 @@
         </is>
       </c>
       <c r="M303" s="4" t="n">
-        <v>16.03</v>
+        <v>16.04</v>
       </c>
       <c r="N303" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O303" s="4" t="n">
-        <v>26.24</v>
+        <v>26.25</v>
       </c>
       <c r="P303" s="4" t="n">
         <v>1.68</v>
@@ -31860,10 +31856,10 @@
         <v>0</v>
       </c>
       <c r="AB303" s="4" t="n">
-        <v>63.12</v>
+        <v>63.13</v>
       </c>
       <c r="AC303" s="4" t="n">
-        <v>36.88</v>
+        <v>36.87</v>
       </c>
       <c r="AD303" s="4" t="n">
         <v>0</v>
@@ -31925,7 +31921,7 @@
         </is>
       </c>
       <c r="M304" s="4" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="N304" s="4" t="n">
         <v>5.33</v>
@@ -32019,7 +32015,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>23.26</v>
+        <v>23.27</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>99.90000000000001</v>
@@ -32033,13 +32029,13 @@
         </is>
       </c>
       <c r="M305" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N305" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O305" s="4" t="n">
-        <v>23.26</v>
+        <v>23.27</v>
       </c>
       <c r="P305" s="4" t="n">
         <v>0.73</v>
@@ -32121,7 +32117,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>16.02</v>
+        <v>16.03</v>
       </c>
       <c r="J306" s="4" t="n">
         <v>99.5</v>
@@ -32135,13 +32131,13 @@
         </is>
       </c>
       <c r="M306" s="4" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="N306" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O306" s="4" t="n">
-        <v>16.02</v>
+        <v>16.03</v>
       </c>
       <c r="P306" s="4" t="n">
         <v>-0.16</v>
@@ -32219,13 +32215,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-5.02</v>
+        <v>-5.07</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -32233,13 +32229,13 @@
         </is>
       </c>
       <c r="M307" s="4" t="n">
-        <v>-12.79</v>
+        <v>-12.78</v>
       </c>
       <c r="N307" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O307" s="4" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="P307" s="4" t="n">
         <v>-1.32</v>
@@ -32276,10 +32272,10 @@
         <v>0</v>
       </c>
       <c r="AB307" s="4" t="n">
-        <v>47.49</v>
+        <v>47.46</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>52.51</v>
+        <v>52.54</v>
       </c>
       <c r="AD307" s="4" t="n">
         <v>0</v>
@@ -32327,7 +32323,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>11.49</v>
+        <v>11.5</v>
       </c>
       <c r="J308" s="4" t="n">
         <v>98.8</v>
@@ -32341,13 +32337,13 @@
         </is>
       </c>
       <c r="M308" s="4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="N308" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O308" s="4" t="n">
-        <v>11.49</v>
+        <v>11.5</v>
       </c>
       <c r="P308" s="4" t="n">
         <v>0.06</v>
@@ -32429,7 +32425,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>17.28</v>
+        <v>17.29</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>99.59999999999999</v>
@@ -32443,13 +32439,13 @@
         </is>
       </c>
       <c r="M309" s="4" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="N309" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>17.28</v>
+        <v>17.29</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>0.97</v>
@@ -32829,7 +32825,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Marvin Suber Williams</t>
+          <t>Jeanine Driscoll</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -32843,7 +32839,7 @@
         </is>
       </c>
       <c r="I313" s="4" t="n">
-        <v>15.03</v>
+        <v>14.7</v>
       </c>
       <c r="J313" s="4" t="n">
         <v>99.3</v>
@@ -32863,10 +32859,10 @@
         <v>5.33</v>
       </c>
       <c r="O313" s="4" t="n">
-        <v>17.33</v>
+        <v>16.94</v>
       </c>
       <c r="P313" s="4" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="Q313" s="4" t="n">
         <v>4.21</v>
@@ -32890,7 +32886,7 @@
         <v>5097222</v>
       </c>
       <c r="X313" s="5" t="n">
-        <v>137263</v>
+        <v>264824</v>
       </c>
       <c r="Y313" t="inlineStr"/>
       <c r="Z313" s="4" t="n">
@@ -32900,10 +32896,10 @@
         <v>0</v>
       </c>
       <c r="AB313" s="4" t="n">
-        <v>57.51</v>
+        <v>57.35</v>
       </c>
       <c r="AC313" s="4" t="n">
-        <v>42.49</v>
+        <v>42.65</v>
       </c>
       <c r="AD313" s="4" t="n">
         <v>0</v>
@@ -32937,7 +32933,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Aaron Cherry</t>
+          <t>George Marsh</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -33141,7 +33137,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Republican candidate (NY-07)</t>
+          <t>Melvin Rivera</t>
         </is>
       </c>
       <c r="G316" t="inlineStr"/>
@@ -33239,7 +33235,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Richard Simmons</t>
+          <t>Lewis Mizrahi</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -33341,7 +33337,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Jean Depalis</t>
+          <t>Joel Anabilah-Azumah</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -33355,7 +33351,7 @@
         </is>
       </c>
       <c r="I318" s="4" t="n">
-        <v>62.03</v>
+        <v>59.76</v>
       </c>
       <c r="J318" s="4" t="n">
         <v>100</v>
@@ -33375,10 +33371,10 @@
         <v>5.33</v>
       </c>
       <c r="O318" s="4" t="n">
-        <v>62.03</v>
+        <v>59.76</v>
       </c>
       <c r="P318" s="4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q318" s="4" t="n">
         <v>8.81</v>
@@ -33396,7 +33392,7 @@
         <v>1013953</v>
       </c>
       <c r="X318" s="5" t="n">
-        <v>6202</v>
+        <v>0</v>
       </c>
       <c r="Y318" t="inlineStr"/>
       <c r="Z318" s="4" t="n">
@@ -33406,10 +33402,10 @@
         <v>0</v>
       </c>
       <c r="AB318" s="4" t="n">
-        <v>81.01000000000001</v>
+        <v>79.88</v>
       </c>
       <c r="AC318" s="4" t="n">
-        <v>18.99</v>
+        <v>20.12</v>
       </c>
       <c r="AD318" s="4" t="n">
         <v>0</v>
@@ -33443,7 +33439,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Gavin Solomon</t>
+          <t>Jennifer Moore</t>
         </is>
       </c>
       <c r="G319" t="inlineStr"/>
@@ -33536,7 +33532,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Troy McGhie</t>
+          <t>Michael DeCillis</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -33555,7 +33551,7 @@
         </is>
       </c>
       <c r="I320" s="4" t="n">
-        <v>-19.95</v>
+        <v>-20.02</v>
       </c>
       <c r="J320" s="4" t="n">
         <v>0.2</v>
@@ -33575,10 +33571,10 @@
         <v>5.33</v>
       </c>
       <c r="O320" s="4" t="n">
-        <v>-19.95</v>
+        <v>-20.02</v>
       </c>
       <c r="P320" s="4" t="n">
-        <v>-2.3</v>
+        <v>-2.38</v>
       </c>
       <c r="Q320" s="4" t="n">
         <v>-2.82</v>
@@ -33593,7 +33589,7 @@
       </c>
       <c r="V320" s="4" t="n"/>
       <c r="W320" s="5" t="n">
-        <v>79597</v>
+        <v>67616</v>
       </c>
       <c r="X320" s="5" t="n">
         <v>2750505</v>
@@ -33606,10 +33602,10 @@
         <v>0</v>
       </c>
       <c r="AB320" s="4" t="n">
-        <v>40.03</v>
+        <v>39.99</v>
       </c>
       <c r="AC320" s="4" t="n">
-        <v>59.97</v>
+        <v>60.01</v>
       </c>
       <c r="AD320" s="4" t="n">
         <v>0</v>
@@ -33643,7 +33639,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Amy Jordan</t>
+          <t>Caroline Shinkle</t>
         </is>
       </c>
       <c r="G321" t="inlineStr"/>
@@ -33653,7 +33649,7 @@
         </is>
       </c>
       <c r="I321" s="4" t="n">
-        <v>73.68000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="J321" s="4" t="n">
         <v>100</v>
@@ -33673,10 +33669,10 @@
         <v>5.33</v>
       </c>
       <c r="O321" s="4" t="n">
-        <v>73.68000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="P321" s="4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Q321" s="4" t="n">
         <v>0</v>
@@ -33694,7 +33690,7 @@
         <v>3315975</v>
       </c>
       <c r="X321" s="5" t="n">
-        <v>58897</v>
+        <v>155145</v>
       </c>
       <c r="Y321" t="inlineStr"/>
       <c r="Z321" s="4" t="n">
@@ -33704,10 +33700,10 @@
         <v>0</v>
       </c>
       <c r="AB321" s="4" t="n">
-        <v>86.84</v>
+        <v>86.81</v>
       </c>
       <c r="AC321" s="4" t="n">
-        <v>13.16</v>
+        <v>13.19</v>
       </c>
       <c r="AD321" s="4" t="n">
         <v>0</v>
@@ -33839,7 +33835,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Tina Forte</t>
+          <t>Diamant Hysenaj</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -33853,7 +33849,7 @@
         </is>
       </c>
       <c r="I323" s="4" t="n">
-        <v>48.91</v>
+        <v>51.52</v>
       </c>
       <c r="J323" s="4" t="n">
         <v>100</v>
@@ -33873,13 +33869,13 @@
         <v>5.33</v>
       </c>
       <c r="O323" s="4" t="n">
-        <v>48.91</v>
+        <v>51.52</v>
       </c>
       <c r="P323" s="4" t="n">
-        <v>2.73</v>
+        <v>3.32</v>
       </c>
       <c r="Q323" s="4" t="n">
-        <v>-0.49</v>
+        <v>1.55</v>
       </c>
       <c r="R323" s="4" t="n">
         <v>32.37</v>
@@ -33894,7 +33890,7 @@
         <v>32607754</v>
       </c>
       <c r="X323" s="5" t="n">
-        <v>803141</v>
+        <v>342896</v>
       </c>
       <c r="Y323" t="inlineStr"/>
       <c r="Z323" s="4" t="n">
@@ -33904,10 +33900,10 @@
         <v>0</v>
       </c>
       <c r="AB323" s="4" t="n">
-        <v>74.45</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AC323" s="4" t="n">
-        <v>25.55</v>
+        <v>24.24</v>
       </c>
       <c r="AD323" s="4" t="n">
         <v>0</v>
@@ -34043,7 +34039,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Republican candidate (NY-16)</t>
+          <t>Joseph Cinquemani</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -34159,13 +34155,13 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="J326" s="4" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K326" s="4" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -34253,7 +34249,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Sharanjit Thind</t>
+          <t>Jackie Auringer</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -34267,13 +34263,13 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>16.6</v>
+        <v>18.85</v>
       </c>
       <c r="J327" s="4" t="n">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="K327" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -34287,10 +34283,10 @@
         <v>5.33</v>
       </c>
       <c r="O327" s="4" t="n">
-        <v>18.82</v>
+        <v>21.47</v>
       </c>
       <c r="P327" s="4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q327" s="4" t="n">
         <v>8.76</v>
@@ -34314,7 +34310,7 @@
         <v>4723627</v>
       </c>
       <c r="X327" s="5" t="n">
-        <v>0</v>
+        <v>89698</v>
       </c>
       <c r="Y327" t="inlineStr"/>
       <c r="Z327" s="4" t="n">
@@ -34324,10 +34320,10 @@
         <v>0</v>
       </c>
       <c r="AB327" s="4" t="n">
-        <v>58.3</v>
+        <v>59.42</v>
       </c>
       <c r="AC327" s="4" t="n">
-        <v>41.7</v>
+        <v>40.58</v>
       </c>
       <c r="AD327" s="4" t="n">
         <v>0</v>
@@ -34575,13 +34571,13 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-13.09</v>
+        <v>-13.11</v>
       </c>
       <c r="J330" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K330" s="4" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -34632,10 +34628,10 @@
         <v>0</v>
       </c>
       <c r="AB330" s="4" t="n">
-        <v>43.46</v>
+        <v>43.44</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>56.54</v>
+        <v>56.56</v>
       </c>
       <c r="AD330" s="4" t="n">
         <v>0</v>
@@ -34669,7 +34665,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>John Lemondes</t>
+          <t>Kailee Buller</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -34683,7 +34679,7 @@
         </is>
       </c>
       <c r="I331" s="4" t="n">
-        <v>24.34</v>
+        <v>23.4</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>99.90000000000001</v>
@@ -34703,10 +34699,10 @@
         <v>5.33</v>
       </c>
       <c r="O331" s="4" t="n">
-        <v>24.34</v>
+        <v>23.4</v>
       </c>
       <c r="P331" s="4" t="n">
-        <v>2.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q331" s="4" t="n">
         <v>8.35</v>
@@ -34724,7 +34720,7 @@
         <v>2694739</v>
       </c>
       <c r="X331" s="5" t="n">
-        <v>41022</v>
+        <v>267339</v>
       </c>
       <c r="Y331" t="inlineStr"/>
       <c r="Z331" s="4" t="n">
@@ -34734,10 +34730,10 @@
         <v>0</v>
       </c>
       <c r="AB331" s="4" t="n">
-        <v>62.17</v>
+        <v>61.7</v>
       </c>
       <c r="AC331" s="4" t="n">
-        <v>37.83</v>
+        <v>38.3</v>
       </c>
       <c r="AD331" s="4" t="n">
         <v>0</v>
@@ -35077,7 +35073,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Republican candidate (NY-26)</t>
+          <t>Dennis Hannon</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -35448,10 +35444,10 @@
         <v>0</v>
       </c>
       <c r="AB338" s="4" t="n">
-        <v>76.41</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AC338" s="4" t="n">
-        <v>23.59</v>
+        <v>23.6</v>
       </c>
       <c r="AD338" s="4" t="n">
         <v>0</v>
@@ -35703,7 +35699,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>-28.34</v>
+        <v>-28.35</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>0</v>
@@ -35723,7 +35719,7 @@
         <v>5.33</v>
       </c>
       <c r="O341" s="4" t="n">
-        <v>-28.34</v>
+        <v>-28.35</v>
       </c>
       <c r="P341" s="4" t="n">
         <v>-2.12</v>
@@ -35805,13 +35801,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>34.4</v>
+        <v>34.7</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35819,7 +35815,7 @@
         </is>
       </c>
       <c r="M342" s="4" t="n">
-        <v>-7.01</v>
+        <v>-7.02</v>
       </c>
       <c r="N342" s="4" t="n">
         <v>5.33</v>
@@ -35862,10 +35858,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>50.49</v>
+        <v>50.45</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>49.51</v>
+        <v>49.55</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -36015,7 +36011,7 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>94.40000000000001</v>
@@ -36035,7 +36031,7 @@
         <v>5.33</v>
       </c>
       <c r="O344" s="4" t="n">
-        <v>11.27</v>
+        <v>11.26</v>
       </c>
       <c r="P344" s="4" t="n">
         <v>0.77</v>
@@ -36137,7 +36133,7 @@
         </is>
       </c>
       <c r="M345" s="4" t="n">
-        <v>-3.61</v>
+        <v>-3.62</v>
       </c>
       <c r="N345" s="4" t="n">
         <v>5.33</v>
@@ -36435,7 +36431,7 @@
         </is>
       </c>
       <c r="I348" s="4" t="n">
-        <v>18.84</v>
+        <v>18.83</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>99.7</v>
@@ -36455,7 +36451,7 @@
         <v>5.33</v>
       </c>
       <c r="O348" s="4" t="n">
-        <v>18.84</v>
+        <v>18.83</v>
       </c>
       <c r="P348" s="4" t="n">
         <v>2.17</v>
@@ -37465,7 +37461,7 @@
         </is>
       </c>
       <c r="M358" s="4" t="n">
-        <v>47.28</v>
+        <v>47.29</v>
       </c>
       <c r="N358" s="4" t="n">
         <v>5.33</v>
@@ -37655,7 +37651,7 @@
         </is>
       </c>
       <c r="I360" s="4" t="n">
-        <v>16.75</v>
+        <v>16.76</v>
       </c>
       <c r="J360" s="4" t="n">
         <v>99.5</v>
@@ -37669,13 +37665,13 @@
         </is>
       </c>
       <c r="M360" s="4" t="n">
-        <v>8.01</v>
+        <v>8.02</v>
       </c>
       <c r="N360" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O360" s="4" t="n">
-        <v>16.75</v>
+        <v>16.76</v>
       </c>
       <c r="P360" s="4" t="n">
         <v>1.57</v>
@@ -37916,10 +37912,10 @@
         <v>0</v>
       </c>
       <c r="AB362" s="4" t="n">
-        <v>49.1</v>
+        <v>49.11</v>
       </c>
       <c r="AC362" s="4" t="n">
-        <v>50.9</v>
+        <v>50.89</v>
       </c>
       <c r="AD362" s="4" t="n">
         <v>0</v>
@@ -38473,7 +38469,7 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="J368" s="4" t="n">
         <v>72.5</v>
@@ -38530,10 +38526,10 @@
         <v>0</v>
       </c>
       <c r="AB368" s="4" t="n">
-        <v>51.37</v>
+        <v>51.38</v>
       </c>
       <c r="AC368" s="4" t="n">
-        <v>48.63</v>
+        <v>48.62</v>
       </c>
       <c r="AD368" s="4" t="n">
         <v>0</v>
@@ -38581,7 +38577,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>63.3</v>
@@ -38791,7 +38787,7 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>9.029999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="J371" s="4" t="n">
         <v>93.40000000000001</v>
@@ -39613,7 +39609,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>40.82</v>
+        <v>40.83</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -39627,13 +39623,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>27.34</v>
+        <v>27.35</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>40.82</v>
+        <v>40.83</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>0</v>
@@ -39664,10 +39660,10 @@
         <v>0</v>
       </c>
       <c r="AB379" s="4" t="n">
-        <v>70.41</v>
+        <v>70.42</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>29.59</v>
+        <v>29.58</v>
       </c>
       <c r="AD379" s="4" t="n">
         <v>0</v>
@@ -39715,7 +39711,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>17.53</v>
+        <v>17.54</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39729,13 +39725,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>11.48</v>
+        <v>11.49</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>17.53</v>
+        <v>17.54</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.61</v>
@@ -39813,13 +39809,13 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-3.57</v>
+        <v>-3.56</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -39827,13 +39823,13 @@
         </is>
       </c>
       <c r="M381" s="4" t="n">
-        <v>-8.91</v>
+        <v>-8.9</v>
       </c>
       <c r="N381" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O381" s="4" t="n">
-        <v>-3.31</v>
+        <v>-3.3</v>
       </c>
       <c r="P381" s="4" t="n">
         <v>0.72</v>
@@ -39870,10 +39866,10 @@
         <v>0</v>
       </c>
       <c r="AB381" s="4" t="n">
-        <v>47.16</v>
+        <v>47.17</v>
       </c>
       <c r="AC381" s="4" t="n">
-        <v>50.66</v>
+        <v>50.65</v>
       </c>
       <c r="AD381" s="4" t="n">
         <v>2.18</v>
@@ -39935,7 +39931,7 @@
         </is>
       </c>
       <c r="M382" s="4" t="n">
-        <v>-10.09</v>
+        <v>-10.08</v>
       </c>
       <c r="N382" s="4" t="n">
         <v>5.33</v>
@@ -40023,7 +40019,7 @@
         </is>
       </c>
       <c r="I383" s="4" t="n">
-        <v>-41.57</v>
+        <v>-41.56</v>
       </c>
       <c r="J383" s="4" t="n">
         <v>0</v>
@@ -40037,13 +40033,13 @@
         </is>
       </c>
       <c r="M383" s="4" t="n">
-        <v>-38.55</v>
+        <v>-38.54</v>
       </c>
       <c r="N383" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O383" s="4" t="n">
-        <v>-41.57</v>
+        <v>-41.56</v>
       </c>
       <c r="P383" s="4" t="n">
         <v>-1.36</v>
@@ -40237,7 +40233,7 @@
         </is>
       </c>
       <c r="M385" s="4" t="n">
-        <v>-18.37</v>
+        <v>-18.36</v>
       </c>
       <c r="N385" s="4" t="n">
         <v>5.33</v>
@@ -40311,7 +40307,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Republican candidate (SC-06)</t>
+          <t>John Peterson</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -40325,7 +40321,7 @@
         </is>
       </c>
       <c r="I386" s="4" t="n">
-        <v>36.2</v>
+        <v>36.21</v>
       </c>
       <c r="J386" s="4" t="n">
         <v>100</v>
@@ -40339,13 +40335,13 @@
         </is>
       </c>
       <c r="M386" s="4" t="n">
-        <v>29.36</v>
+        <v>29.37</v>
       </c>
       <c r="N386" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O386" s="4" t="n">
-        <v>36.2</v>
+        <v>36.21</v>
       </c>
       <c r="P386" s="4" t="n">
         <v>0</v>
@@ -40427,7 +40423,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-14.96</v>
+        <v>-15.08</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>0.7</v>
@@ -40447,7 +40443,7 @@
         <v>5.33</v>
       </c>
       <c r="O387" s="4" t="n">
-        <v>-21.46</v>
+        <v>-21.45</v>
       </c>
       <c r="P387" s="4" t="n">
         <v>-1.22</v>
@@ -40484,10 +40480,10 @@
         <v>0</v>
       </c>
       <c r="AB387" s="4" t="n">
-        <v>42.52</v>
+        <v>42.46</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>57.48</v>
+        <v>57.54</v>
       </c>
       <c r="AD387" s="4" t="n">
         <v>0</v>
@@ -41539,7 +41535,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-40.51</v>
+        <v>-40.52</v>
       </c>
       <c r="J398" s="4" t="n">
         <v>0</v>
@@ -41553,13 +41549,13 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-44.13</v>
+        <v>-44.14</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O398" s="4" t="n">
-        <v>-40.51</v>
+        <v>-40.52</v>
       </c>
       <c r="P398" s="4" t="n">
         <v>0</v>
@@ -41590,10 +41586,10 @@
         <v>0</v>
       </c>
       <c r="AB398" s="4" t="n">
-        <v>29.75</v>
+        <v>29.74</v>
       </c>
       <c r="AC398" s="4" t="n">
-        <v>70.25</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="AD398" s="4" t="n">
         <v>0</v>
@@ -41688,10 +41684,10 @@
         <v>0</v>
       </c>
       <c r="AB399" s="4" t="n">
-        <v>43.88</v>
+        <v>43.87</v>
       </c>
       <c r="AC399" s="4" t="n">
-        <v>56.12</v>
+        <v>56.13</v>
       </c>
       <c r="AD399" s="4" t="n">
         <v>0</v>
@@ -41739,7 +41735,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-15.33</v>
+        <v>-15.34</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>0.6</v>
@@ -41753,13 +41749,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-18.73</v>
+        <v>-18.74</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-15.33</v>
+        <v>-15.34</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -41892,10 +41888,10 @@
         <v>0</v>
       </c>
       <c r="AB401" s="4" t="n">
-        <v>39.62</v>
+        <v>39.61</v>
       </c>
       <c r="AC401" s="4" t="n">
-        <v>60.38</v>
+        <v>60.39</v>
       </c>
       <c r="AD401" s="4" t="n">
         <v>0</v>
@@ -41943,7 +41939,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-13.29</v>
+        <v>-13.3</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>0.9</v>
@@ -41963,7 +41959,7 @@
         <v>5.33</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-13.29</v>
+        <v>-13.3</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.23</v>
@@ -42045,7 +42041,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-18.67</v>
+        <v>-18.68</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.3</v>
@@ -42059,13 +42055,13 @@
         </is>
       </c>
       <c r="M403" s="4" t="n">
-        <v>-18.5</v>
+        <v>-18.51</v>
       </c>
       <c r="N403" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-18.67</v>
+        <v>-18.68</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -42147,7 +42143,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>41.09</v>
+        <v>41.08</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -42161,13 +42157,13 @@
         </is>
       </c>
       <c r="M404" s="4" t="n">
-        <v>30.83</v>
+        <v>30.82</v>
       </c>
       <c r="N404" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>41.09</v>
+        <v>41.08</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -42343,7 +42339,7 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-6.59</v>
+        <v>-6.6</v>
       </c>
       <c r="J406" s="4" t="n">
         <v>13.8</v>
@@ -42357,13 +42353,13 @@
         </is>
       </c>
       <c r="M406" s="4" t="n">
-        <v>-12.18</v>
+        <v>-12.19</v>
       </c>
       <c r="N406" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-6.59</v>
+        <v>-6.6</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.92</v>
@@ -42441,7 +42437,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-12.98</v>
+        <v>-12.99</v>
       </c>
       <c r="J407" s="4" t="n">
         <v>1</v>
@@ -42455,13 +42451,13 @@
         </is>
       </c>
       <c r="M407" s="4" t="n">
-        <v>-16.86</v>
+        <v>-16.87</v>
       </c>
       <c r="N407" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-12.98</v>
+        <v>-12.99</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -42543,7 +42539,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-27.34</v>
+        <v>-27.35</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0</v>
@@ -42557,13 +42553,13 @@
         </is>
       </c>
       <c r="M408" s="4" t="n">
-        <v>-29.55</v>
+        <v>-29.56</v>
       </c>
       <c r="N408" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-27.34</v>
+        <v>-27.35</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -42659,7 +42655,7 @@
         </is>
       </c>
       <c r="M409" s="4" t="n">
-        <v>-18.5</v>
+        <v>-18.51</v>
       </c>
       <c r="N409" s="4" t="n">
         <v>5.33</v>
@@ -42747,7 +42743,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-40.64</v>
+        <v>-40.65</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -42761,13 +42757,13 @@
         </is>
       </c>
       <c r="M410" s="4" t="n">
-        <v>-42.15</v>
+        <v>-42.16</v>
       </c>
       <c r="N410" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-40.64</v>
+        <v>-40.65</v>
       </c>
       <c r="P410" s="4" t="n">
         <v>-2.49</v>
@@ -42798,10 +42794,10 @@
         <v>0</v>
       </c>
       <c r="AB410" s="4" t="n">
-        <v>29.68</v>
+        <v>29.67</v>
       </c>
       <c r="AC410" s="4" t="n">
-        <v>70.31999999999999</v>
+        <v>70.33</v>
       </c>
       <c r="AD410" s="4" t="n">
         <v>0</v>
@@ -42849,7 +42845,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-19.57</v>
+        <v>-19.58</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.3</v>
@@ -42869,7 +42865,7 @@
         <v>5.33</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-19.57</v>
+        <v>-19.58</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.89</v>
@@ -43073,7 +43069,7 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>26.8</v>
+        <v>26.79</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>5.33</v>
@@ -43110,10 +43106,10 @@
         <v>0</v>
       </c>
       <c r="AB413" s="4" t="n">
-        <v>68.31999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="AC413" s="4" t="n">
-        <v>31.68</v>
+        <v>31.69</v>
       </c>
       <c r="AD413" s="4" t="n">
         <v>0</v>
@@ -43161,7 +43157,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-14.76</v>
+        <v>-14.77</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>0.7</v>
@@ -43175,13 +43171,13 @@
         </is>
       </c>
       <c r="M414" s="4" t="n">
-        <v>-16.33</v>
+        <v>-16.34</v>
       </c>
       <c r="N414" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-14.76</v>
+        <v>-14.77</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>0</v>
@@ -43263,7 +43259,7 @@
         </is>
       </c>
       <c r="I415" s="4" t="n">
-        <v>71.17</v>
+        <v>71.16</v>
       </c>
       <c r="J415" s="4" t="n">
         <v>100</v>
@@ -43283,7 +43279,7 @@
         <v>5.33</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>71.17</v>
+        <v>71.16</v>
       </c>
       <c r="P415" s="4" t="n">
         <v>0</v>
@@ -43375,7 +43371,7 @@
         </is>
       </c>
       <c r="M416" s="4" t="n">
-        <v>-46.51</v>
+        <v>-46.52</v>
       </c>
       <c r="N416" s="4" t="n">
         <v>5.33</v>
@@ -43412,10 +43408,10 @@
         <v>0</v>
       </c>
       <c r="AB416" s="4" t="n">
-        <v>28.66</v>
+        <v>28.65</v>
       </c>
       <c r="AC416" s="4" t="n">
-        <v>71.34</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="AD416" s="4" t="n">
         <v>0</v>
@@ -43463,7 +43459,7 @@
         </is>
       </c>
       <c r="I417" s="4" t="n">
-        <v>49.31</v>
+        <v>49.3</v>
       </c>
       <c r="J417" s="4" t="n">
         <v>100</v>
@@ -43477,13 +43473,13 @@
         </is>
       </c>
       <c r="M417" s="4" t="n">
-        <v>36.64</v>
+        <v>36.63</v>
       </c>
       <c r="N417" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O417" s="4" t="n">
-        <v>49.31</v>
+        <v>49.3</v>
       </c>
       <c r="P417" s="4" t="n">
         <v>1.31</v>
@@ -43561,7 +43557,7 @@
         </is>
       </c>
       <c r="I418" s="4" t="n">
-        <v>-12.25</v>
+        <v>-12.26</v>
       </c>
       <c r="J418" s="4" t="n">
         <v>1.1</v>
@@ -43575,13 +43571,13 @@
         </is>
       </c>
       <c r="M418" s="4" t="n">
-        <v>-16.84</v>
+        <v>-16.85</v>
       </c>
       <c r="N418" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O418" s="4" t="n">
-        <v>-12.25</v>
+        <v>-12.26</v>
       </c>
       <c r="P418" s="4" t="n">
         <v>-2.06</v>
@@ -43612,10 +43608,10 @@
         <v>0</v>
       </c>
       <c r="AB418" s="4" t="n">
-        <v>43.88</v>
+        <v>43.87</v>
       </c>
       <c r="AC418" s="4" t="n">
-        <v>56.12</v>
+        <v>56.13</v>
       </c>
       <c r="AD418" s="4" t="n">
         <v>0</v>
@@ -43659,7 +43655,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-12.96</v>
+        <v>-12.97</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>1</v>
@@ -43673,13 +43669,13 @@
         </is>
       </c>
       <c r="M419" s="4" t="n">
-        <v>-17.42</v>
+        <v>-17.43</v>
       </c>
       <c r="N419" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-12.96</v>
+        <v>-12.97</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.8100000000000001</v>
@@ -43710,10 +43706,10 @@
         <v>0</v>
       </c>
       <c r="AB419" s="4" t="n">
-        <v>43.52</v>
+        <v>43.51</v>
       </c>
       <c r="AC419" s="4" t="n">
-        <v>56.48</v>
+        <v>56.49</v>
       </c>
       <c r="AD419" s="4" t="n">
         <v>0</v>
@@ -43757,7 +43753,7 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-2.34</v>
+        <v>-2.35</v>
       </c>
       <c r="J420" s="4" t="n">
         <v>29</v>
@@ -43777,7 +43773,7 @@
         <v>5.33</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.88</v>
       </c>
       <c r="P420" s="4" t="n">
         <v>-0.82</v>
@@ -43865,7 +43861,7 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-10.89</v>
+        <v>-10.9</v>
       </c>
       <c r="J421" s="4" t="n">
         <v>2.1</v>
@@ -43879,13 +43875,13 @@
         </is>
       </c>
       <c r="M421" s="4" t="n">
-        <v>-11.75</v>
+        <v>-11.76</v>
       </c>
       <c r="N421" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-10.89</v>
+        <v>-10.9</v>
       </c>
       <c r="P421" s="4" t="n">
         <v>0</v>
@@ -43981,7 +43977,7 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-17.98</v>
+        <v>-17.99</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>5.33</v>
@@ -44069,7 +44065,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-22.57</v>
+        <v>-22.58</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.1</v>
@@ -44083,13 +44079,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-19.1</v>
+        <v>-19.11</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-22.57</v>
+        <v>-22.58</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -44171,7 +44167,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-13.84</v>
+        <v>-13.85</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>0.8</v>
@@ -44191,7 +44187,7 @@
         <v>5.33</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-13.84</v>
+        <v>-13.85</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -44273,7 +44269,7 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>13.48</v>
+        <v>13.57</v>
       </c>
       <c r="J425" s="4" t="n">
         <v>99.09999999999999</v>
@@ -44293,7 +44289,7 @@
         <v>5.33</v>
       </c>
       <c r="O425" s="4" t="n">
-        <v>20.19</v>
+        <v>20.18</v>
       </c>
       <c r="P425" s="4" t="n">
         <v>0.34</v>
@@ -44330,10 +44326,10 @@
         <v>0</v>
       </c>
       <c r="AB425" s="4" t="n">
-        <v>56.74</v>
+        <v>56.79</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>43.26</v>
+        <v>43.21</v>
       </c>
       <c r="AD425" s="4" t="n">
         <v>0</v>
@@ -44381,7 +44377,7 @@
         </is>
       </c>
       <c r="I426" s="4" t="n">
-        <v>54.1</v>
+        <v>54.09</v>
       </c>
       <c r="J426" s="4" t="n">
         <v>100</v>
@@ -44395,13 +44391,13 @@
         </is>
       </c>
       <c r="M426" s="4" t="n">
-        <v>39.16</v>
+        <v>39.15</v>
       </c>
       <c r="N426" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O426" s="4" t="n">
-        <v>54.1</v>
+        <v>54.09</v>
       </c>
       <c r="P426" s="4" t="n">
         <v>0</v>
@@ -44479,7 +44475,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>61.72</v>
+        <v>61.71</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -44493,13 +44489,13 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>54.87</v>
+        <v>54.86</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>61.72</v>
+        <v>61.71</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>0.21</v>
@@ -44530,10 +44526,10 @@
         <v>0</v>
       </c>
       <c r="AB427" s="4" t="n">
-        <v>80.86</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="AC427" s="4" t="n">
-        <v>19.14</v>
+        <v>19.15</v>
       </c>
       <c r="AD427" s="4" t="n">
         <v>0</v>
@@ -44581,7 +44577,7 @@
         </is>
       </c>
       <c r="I428" s="4" t="n">
-        <v>-18.72</v>
+        <v>-18.73</v>
       </c>
       <c r="J428" s="4" t="n">
         <v>0.3</v>
@@ -44595,13 +44591,13 @@
         </is>
       </c>
       <c r="M428" s="4" t="n">
-        <v>-17.26</v>
+        <v>-17.27</v>
       </c>
       <c r="N428" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O428" s="4" t="n">
-        <v>-18.13</v>
+        <v>-18.14</v>
       </c>
       <c r="P428" s="4" t="n">
         <v>-1.61</v>
@@ -44679,7 +44675,7 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-8.23</v>
+        <v>-8.24</v>
       </c>
       <c r="J429" s="4" t="n">
         <v>8.800000000000001</v>
@@ -44699,7 +44695,7 @@
         <v>5.33</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-8.23</v>
+        <v>-8.24</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.72</v>
@@ -44777,7 +44773,7 @@
         </is>
       </c>
       <c r="I430" s="4" t="n">
-        <v>46.19</v>
+        <v>46.18</v>
       </c>
       <c r="J430" s="4" t="n">
         <v>100</v>
@@ -44791,13 +44787,13 @@
         </is>
       </c>
       <c r="M430" s="4" t="n">
-        <v>41.03</v>
+        <v>41.02</v>
       </c>
       <c r="N430" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O430" s="4" t="n">
-        <v>46.19</v>
+        <v>46.18</v>
       </c>
       <c r="P430" s="4" t="n">
         <v>0</v>
@@ -44879,13 +44875,13 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>8.57</v>
+        <v>8.59</v>
       </c>
       <c r="J431" s="4" t="n">
-        <v>92.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="K431" s="4" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -44997,7 +44993,7 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-4.02</v>
+        <v>-4.03</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>5.33</v>
@@ -45034,10 +45030,10 @@
         <v>0</v>
       </c>
       <c r="AB432" s="4" t="n">
-        <v>51.64</v>
+        <v>51.63</v>
       </c>
       <c r="AC432" s="4" t="n">
-        <v>48.36</v>
+        <v>48.37</v>
       </c>
       <c r="AD432" s="4" t="n">
         <v>0</v>
@@ -45201,7 +45197,7 @@
         </is>
       </c>
       <c r="M434" s="4" t="n">
-        <v>63.65</v>
+        <v>63.64</v>
       </c>
       <c r="N434" s="4" t="n">
         <v>5.33</v>
@@ -45238,10 +45234,10 @@
         <v>0</v>
       </c>
       <c r="AB434" s="4" t="n">
-        <v>85.63</v>
+        <v>85.62</v>
       </c>
       <c r="AC434" s="4" t="n">
-        <v>14.37</v>
+        <v>14.38</v>
       </c>
       <c r="AD434" s="4" t="n">
         <v>0</v>
@@ -45305,7 +45301,7 @@
         <v>5.33</v>
       </c>
       <c r="O435" s="4" t="n">
-        <v>-13.43</v>
+        <v>-13.44</v>
       </c>
       <c r="P435" s="4" t="n">
         <v>-2.01</v>
@@ -45791,7 +45787,7 @@
         </is>
       </c>
       <c r="I440" s="4" t="n">
-        <v>-3.1</v>
+        <v>-3.11</v>
       </c>
       <c r="J440" s="4" t="n">
         <v>26.1</v>
@@ -45899,13 +45895,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -45956,10 +45952,10 @@
         <v>0</v>
       </c>
       <c r="AB441" s="4" t="n">
-        <v>51.38</v>
+        <v>51.4</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>48.62</v>
+        <v>48.6</v>
       </c>
       <c r="AD441" s="4" t="n">
         <v>0</v>
@@ -46911,7 +46907,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Mark Coester</t>
+          <t>Gerald Malloy</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -46925,7 +46921,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>36.25</v>
+        <v>35.87</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -46939,16 +46935,16 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>20.28</v>
+        <v>20.27</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>36.22</v>
+        <v>36.03</v>
       </c>
       <c r="P451" s="4" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="Q451" s="4" t="n">
         <v>9.710000000000001</v>
@@ -46957,7 +46953,7 @@
         <v>32.77</v>
       </c>
       <c r="S451" s="4" t="n">
-        <v>61.62</v>
+        <v>60.96</v>
       </c>
       <c r="T451" s="4" t="n">
         <v>25.34</v>
@@ -46966,13 +46962,13 @@
         <v>2</v>
       </c>
       <c r="V451" s="4" t="n">
-        <v>36.29</v>
+        <v>35.62</v>
       </c>
       <c r="W451" s="5" t="n">
         <v>956339</v>
       </c>
       <c r="X451" s="5" t="n">
-        <v>36039</v>
+        <v>58280</v>
       </c>
       <c r="Y451" t="inlineStr"/>
       <c r="Z451" s="4" t="n">
@@ -46982,10 +46978,10 @@
         <v>0</v>
       </c>
       <c r="AB451" s="4" t="n">
-        <v>68.12</v>
+        <v>67.94</v>
       </c>
       <c r="AC451" s="4" t="n">
-        <v>31.88</v>
+        <v>32.06</v>
       </c>
       <c r="AD451" s="4" t="n">
         <v>0</v>
@@ -47014,7 +47010,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Suzan Delbene</t>
+          <t>Suzan DelBene</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -47237,13 +47233,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>5.91</v>
+        <v>5.95</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47294,10 +47290,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>52.96</v>
+        <v>52.97</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>47.04</v>
+        <v>47.03</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -47443,7 +47439,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-23.89</v>
+        <v>-23.92</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47500,10 +47496,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>38.06</v>
+        <v>38.04</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>61.94</v>
+        <v>61.96</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -47741,7 +47737,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Republican candidate (WA-08)</t>
+          <t>Spencer Meline</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -47755,13 +47751,13 @@
         </is>
       </c>
       <c r="I459" s="4" t="n">
-        <v>14.66</v>
+        <v>16.81</v>
       </c>
       <c r="J459" s="4" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="K459" s="4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L459" t="inlineStr">
         <is>
@@ -47775,10 +47771,10 @@
         <v>5.33</v>
       </c>
       <c r="O459" s="4" t="n">
-        <v>14.66</v>
+        <v>16.81</v>
       </c>
       <c r="P459" s="4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q459" s="4" t="n">
         <v>3.8</v>
@@ -47796,7 +47792,7 @@
         <v>3016894</v>
       </c>
       <c r="X459" s="5" t="n">
-        <v>0</v>
+        <v>126517</v>
       </c>
       <c r="Y459" t="inlineStr"/>
       <c r="Z459" s="4" t="n">
@@ -47806,10 +47802,10 @@
         <v>0</v>
       </c>
       <c r="AB459" s="4" t="n">
-        <v>57.33</v>
+        <v>58.41</v>
       </c>
       <c r="AC459" s="4" t="n">
-        <v>42.67</v>
+        <v>41.59</v>
       </c>
       <c r="AD459" s="4" t="n">
         <v>0</v>
@@ -48061,27 +48057,27 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-3.92</v>
+        <v>-3.2</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>23.1</v>
+        <v>25.7</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M462" s="4" t="n">
-        <v>-3.06</v>
+        <v>-2.22</v>
       </c>
       <c r="N462" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O462" s="4" t="n">
-        <v>-4.52</v>
+        <v>-3.68</v>
       </c>
       <c r="P462" s="4" t="n">
         <v>-1.48</v>
@@ -48118,10 +48114,10 @@
         <v>0</v>
       </c>
       <c r="AB462" s="4" t="n">
-        <v>48.04</v>
+        <v>48.4</v>
       </c>
       <c r="AC462" s="4" t="n">
-        <v>51.96</v>
+        <v>51.6</v>
       </c>
       <c r="AD462" s="4" t="n">
         <v>0</v>
@@ -48155,7 +48151,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Erik Olsen</t>
+          <t>(no Republican filed)</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -48169,7 +48165,7 @@
         </is>
       </c>
       <c r="I463" s="4" t="n">
-        <v>50.45</v>
+        <v>50.05</v>
       </c>
       <c r="J463" s="4" t="n">
         <v>100</v>
@@ -48183,19 +48179,19 @@
         </is>
       </c>
       <c r="M463" s="4" t="n">
-        <v>41.93</v>
+        <v>42.77</v>
       </c>
       <c r="N463" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O463" s="4" t="n">
-        <v>50.45</v>
+        <v>50.05</v>
       </c>
       <c r="P463" s="4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q463" s="4" t="n">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="R463" s="4" t="n">
         <v>40.75</v>
@@ -48210,7 +48206,7 @@
         <v>814874</v>
       </c>
       <c r="X463" s="5" t="n">
-        <v>2840</v>
+        <v>0</v>
       </c>
       <c r="Y463" t="inlineStr"/>
       <c r="Z463" s="4" t="n">
@@ -48220,10 +48216,10 @@
         <v>0</v>
       </c>
       <c r="AB463" s="4" t="n">
-        <v>75.22</v>
+        <v>75.02</v>
       </c>
       <c r="AC463" s="4" t="n">
-        <v>24.78</v>
+        <v>24.98</v>
       </c>
       <c r="AD463" s="4" t="n">
         <v>0</v>
@@ -48271,13 +48267,13 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>4.07</v>
+        <v>4.62</v>
       </c>
       <c r="J464" s="4" t="n">
-        <v>77.5</v>
+        <v>79.5</v>
       </c>
       <c r="K464" s="4" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -48285,13 +48281,13 @@
         </is>
       </c>
       <c r="M464" s="4" t="n">
-        <v>-5.89</v>
+        <v>-5.05</v>
       </c>
       <c r="N464" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O464" s="4" t="n">
-        <v>5.9</v>
+        <v>6.74</v>
       </c>
       <c r="P464" s="4" t="n">
         <v>0.1</v>
@@ -48328,10 +48324,10 @@
         <v>0</v>
       </c>
       <c r="AB464" s="4" t="n">
-        <v>52.04</v>
+        <v>52.31</v>
       </c>
       <c r="AC464" s="4" t="n">
-        <v>47.96</v>
+        <v>47.69</v>
       </c>
       <c r="AD464" s="4" t="n">
         <v>0</v>
@@ -48365,7 +48361,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Purnima Nath</t>
+          <t>Tim Rogers</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -48379,7 +48375,7 @@
         </is>
       </c>
       <c r="I465" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>63.46</v>
       </c>
       <c r="J465" s="4" t="n">
         <v>100</v>
@@ -48393,16 +48389,16 @@
         </is>
       </c>
       <c r="M465" s="4" t="n">
-        <v>53.65</v>
+        <v>54.49</v>
       </c>
       <c r="N465" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O465" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>63.46</v>
       </c>
       <c r="P465" s="4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q465" s="4" t="n">
         <v>3.43</v>
@@ -48420,7 +48416,7 @@
         <v>1070659</v>
       </c>
       <c r="X465" s="5" t="n">
-        <v>1925</v>
+        <v>0</v>
       </c>
       <c r="Y465" t="inlineStr"/>
       <c r="Z465" s="4" t="n">
@@ -48430,10 +48426,10 @@
         <v>0</v>
       </c>
       <c r="AB465" s="4" t="n">
-        <v>82.45999999999999</v>
+        <v>81.73</v>
       </c>
       <c r="AC465" s="4" t="n">
-        <v>17.54</v>
+        <v>18.27</v>
       </c>
       <c r="AD465" s="4" t="n">
         <v>0</v>
@@ -48481,7 +48477,7 @@
         </is>
       </c>
       <c r="I466" s="4" t="n">
-        <v>-24.55</v>
+        <v>-23.71</v>
       </c>
       <c r="J466" s="4" t="n">
         <v>0.1</v>
@@ -48495,13 +48491,13 @@
         </is>
       </c>
       <c r="M466" s="4" t="n">
-        <v>-22.12</v>
+        <v>-21.28</v>
       </c>
       <c r="N466" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O466" s="4" t="n">
-        <v>-24.55</v>
+        <v>-23.71</v>
       </c>
       <c r="P466" s="4" t="n">
         <v>-2.32</v>
@@ -48532,10 +48528,10 @@
         <v>0</v>
       </c>
       <c r="AB466" s="4" t="n">
-        <v>37.72</v>
+        <v>38.14</v>
       </c>
       <c r="AC466" s="4" t="n">
-        <v>62.28</v>
+        <v>61.86</v>
       </c>
       <c r="AD466" s="4" t="n">
         <v>0</v>
@@ -48564,7 +48560,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Aaron Wojciechowski</t>
+          <t>Democratic candidate (WI-06)</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -48583,13 +48579,13 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-19.16</v>
+        <v>-17.03</v>
       </c>
       <c r="J467" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K467" s="4" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L467" t="inlineStr">
         <is>
@@ -48597,16 +48593,16 @@
         </is>
       </c>
       <c r="M467" s="4" t="n">
-        <v>-15.73</v>
+        <v>-14.89</v>
       </c>
       <c r="N467" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-17.8</v>
+        <v>-15.21</v>
       </c>
       <c r="P467" s="4" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
       <c r="Q467" s="4" t="n">
         <v>-4.83</v>
@@ -48627,7 +48623,7 @@
         <v>-25</v>
       </c>
       <c r="W467" s="5" t="n">
-        <v>44015</v>
+        <v>0</v>
       </c>
       <c r="X467" s="5" t="n">
         <v>929020</v>
@@ -48640,10 +48636,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>40.42</v>
+        <v>41.48</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>59.58</v>
+        <v>58.52</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48672,12 +48668,12 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Frederic Clark</t>
+          <t>Fred Clark</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Paul Wassgren</t>
+          <t>Michael Alfonso</t>
         </is>
       </c>
       <c r="G468" t="inlineStr"/>
@@ -48687,13 +48683,13 @@
         </is>
       </c>
       <c r="I468" s="4" t="n">
-        <v>-18.5</v>
+        <v>-17.32</v>
       </c>
       <c r="J468" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K468" s="4" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L468" t="inlineStr">
         <is>
@@ -48701,16 +48697,16 @@
         </is>
       </c>
       <c r="M468" s="4" t="n">
-        <v>-21.35</v>
+        <v>-20.51</v>
       </c>
       <c r="N468" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O468" s="4" t="n">
-        <v>-18.5</v>
+        <v>-17.32</v>
       </c>
       <c r="P468" s="4" t="n">
-        <v>-1.49</v>
+        <v>-1.15</v>
       </c>
       <c r="Q468" s="4" t="n">
         <v>0</v>
@@ -48728,7 +48724,7 @@
         <v>423041</v>
       </c>
       <c r="X468" s="5" t="n">
-        <v>3403946</v>
+        <v>1351546</v>
       </c>
       <c r="Y468" t="inlineStr"/>
       <c r="Z468" s="4" t="n">
@@ -48738,10 +48734,10 @@
         <v>0</v>
       </c>
       <c r="AB468" s="4" t="n">
-        <v>40.75</v>
+        <v>41.34</v>
       </c>
       <c r="AC468" s="4" t="n">
-        <v>59.25</v>
+        <v>58.66</v>
       </c>
       <c r="AD468" s="4" t="n">
         <v>0</v>
@@ -48770,7 +48766,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Mark Scheffler</t>
+          <t>Rick Crosson</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -48789,13 +48785,13 @@
         </is>
       </c>
       <c r="I469" s="4" t="n">
-        <v>-14.19</v>
+        <v>-13.65</v>
       </c>
       <c r="J469" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K469" s="4" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L469" t="inlineStr">
         <is>
@@ -48803,16 +48799,16 @@
         </is>
       </c>
       <c r="M469" s="4" t="n">
-        <v>-15.53</v>
+        <v>-14.69</v>
       </c>
       <c r="N469" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O469" s="4" t="n">
-        <v>-14.19</v>
+        <v>-13.65</v>
       </c>
       <c r="P469" s="4" t="n">
-        <v>-1.36</v>
+        <v>-1.66</v>
       </c>
       <c r="Q469" s="4" t="n">
         <v>-1.81</v>
@@ -48827,7 +48823,7 @@
       </c>
       <c r="V469" s="4" t="n"/>
       <c r="W469" s="5" t="n">
-        <v>136755</v>
+        <v>75430</v>
       </c>
       <c r="X469" s="5" t="n">
         <v>1090216</v>
@@ -48840,10 +48836,10 @@
         <v>0</v>
       </c>
       <c r="AB469" s="4" t="n">
-        <v>42.91</v>
+        <v>43.18</v>
       </c>
       <c r="AC469" s="4" t="n">
-        <v>57.09</v>
+        <v>56.82</v>
       </c>
       <c r="AD469" s="4" t="n">
         <v>0</v>
@@ -49091,7 +49087,7 @@
         </is>
       </c>
       <c r="I472" s="4" t="n">
-        <v>-41.27</v>
+        <v>-41.28</v>
       </c>
       <c r="J472" s="4" t="n">
         <v>0</v>
@@ -49111,7 +49107,7 @@
         <v>5.33</v>
       </c>
       <c r="O472" s="4" t="n">
-        <v>-41.27</v>
+        <v>-41.28</v>
       </c>
       <c r="P472" s="4" t="n">
         <v>-1.47</v>
@@ -49193,13 +49189,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.93</v>
+        <v>-0.71</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>46.5</v>
+        <v>47.8</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>53.5</v>
+        <v>52.2</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49207,13 +49203,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.74</v>
+        <v>-10.64</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.82</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.43</v>
@@ -49225,16 +49221,16 @@
         <v>-13.8</v>
       </c>
       <c r="S473" s="4" t="n">
-        <v>46.31</v>
+        <v>47.77</v>
       </c>
       <c r="T473" s="4" t="n">
-        <v>46.61</v>
+        <v>47.45</v>
       </c>
       <c r="U473" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V473" s="4" t="n">
-        <v>-0.31</v>
+        <v>0.32</v>
       </c>
       <c r="W473" s="5" t="n">
         <v>18545132</v>
@@ -49250,10 +49246,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.42</v>
+        <v>45.6</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.58</v>
+        <v>46.4</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49297,7 +49293,7 @@
         </is>
       </c>
       <c r="I474" s="4" t="n">
-        <v>-20.74</v>
+        <v>-20.79</v>
       </c>
       <c r="J474" s="4" t="n">
         <v>0.2</v>
@@ -49311,13 +49307,13 @@
         </is>
       </c>
       <c r="M474" s="4" t="n">
-        <v>-26.33</v>
+        <v>-26.34</v>
       </c>
       <c r="N474" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O474" s="4" t="n">
-        <v>-23.75</v>
+        <v>-23.76</v>
       </c>
       <c r="P474" s="4" t="n">
         <v>-3.2</v>
@@ -49354,10 +49350,10 @@
         <v>0</v>
       </c>
       <c r="AB474" s="4" t="n">
-        <v>39.63</v>
+        <v>39.6</v>
       </c>
       <c r="AC474" s="4" t="n">
-        <v>60.37</v>
+        <v>60.4</v>
       </c>
       <c r="AD474" s="4" t="n">
         <v>0</v>
@@ -49405,7 +49401,7 @@
         </is>
       </c>
       <c r="I475" s="4" t="n">
-        <v>-19.92</v>
+        <v>-20</v>
       </c>
       <c r="J475" s="4" t="n">
         <v>0.2</v>
@@ -49462,10 +49458,10 @@
         <v>0</v>
       </c>
       <c r="AB475" s="4" t="n">
-        <v>40.04</v>
+        <v>40</v>
       </c>
       <c r="AC475" s="4" t="n">
-        <v>59.96</v>
+        <v>60</v>
       </c>
       <c r="AD475" s="4" t="n">
         <v>0</v>
@@ -49731,7 +49727,7 @@
         </is>
       </c>
       <c r="M478" s="4" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.65</v>
       </c>
       <c r="N478" s="4" t="n">
         <v>5.33</v>
@@ -49986,10 +49982,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.73</v>
+        <v>47.72</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.64</v>
+        <v>49.65</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -50037,7 +50033,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-25.48</v>
+        <v>-25.5</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0.1</v>
@@ -50092,7 +50088,7 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>37.26</v>
+        <v>37.25</v>
       </c>
       <c r="AA481" s="4" t="n">
         <v>0.1</v>
@@ -50101,7 +50097,7 @@
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>62.74</v>
+        <v>62.75</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -50247,7 +50243,7 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-10.31</v>
+        <v>-10.32</v>
       </c>
       <c r="J483" s="4" t="n">
         <v>3.4</v>
@@ -50557,7 +50553,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>30.34</v>
+        <v>30.36</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -50614,10 +50610,10 @@
         <v>0</v>
       </c>
       <c r="AB486" s="4" t="n">
-        <v>65.17</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>34.83</v>
+        <v>34.82</v>
       </c>
       <c r="AD486" s="4" t="n">
         <v>0</v>
@@ -50665,13 +50661,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50679,7 +50675,7 @@
         </is>
       </c>
       <c r="M487" s="4" t="n">
-        <v>8.67</v>
+        <v>8.66</v>
       </c>
       <c r="N487" s="4" t="n">
         <v>5.33</v>
@@ -50722,10 +50718,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>50.6</v>
+        <v>50.59</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>49.4</v>
+        <v>49.41</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -50769,13 +50765,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -50826,10 +50822,10 @@
         <v>0</v>
       </c>
       <c r="AB488" s="4" t="n">
-        <v>51.35</v>
+        <v>51.37</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>48.65</v>
+        <v>48.63</v>
       </c>
       <c r="AD488" s="4" t="n">
         <v>0</v>
@@ -50873,27 +50869,27 @@
         </is>
       </c>
       <c r="I489" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J489" s="4" t="n">
-        <v>95.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K489" s="4" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>Safe D</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="M489" s="4" t="n">
-        <v>6.94</v>
+        <v>6.39</v>
       </c>
       <c r="N489" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O489" s="4" t="n">
-        <v>11.49</v>
+        <v>10.94</v>
       </c>
       <c r="P489" s="4" t="n">
         <v>-0.06</v>
@@ -50930,10 +50926,10 @@
         <v>0</v>
       </c>
       <c r="AB489" s="4" t="n">
-        <v>54.93</v>
+        <v>54.75</v>
       </c>
       <c r="AC489" s="4" t="n">
-        <v>45.07</v>
+        <v>45.25</v>
       </c>
       <c r="AD489" s="4" t="n">
         <v>0</v>
@@ -51089,7 +51085,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-25.78</v>
+        <v>-25.75</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0.1</v>
@@ -51144,16 +51140,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.4</v>
+        <v>14.39</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>28.08</v>
+        <v>28.1</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>53.86</v>
+        <v>53.85</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51197,7 +51193,7 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="J492" s="4" t="n">
         <v>84.3</v>
@@ -51254,10 +51250,10 @@
         <v>0</v>
       </c>
       <c r="AB492" s="4" t="n">
-        <v>52.02</v>
+        <v>52.01</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>46.11</v>
+        <v>46.12</v>
       </c>
       <c r="AD492" s="4" t="n">
         <v>1.87</v>
@@ -51305,7 +51301,7 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-4.41</v>
+        <v>-4.42</v>
       </c>
       <c r="J493" s="4" t="n">
         <v>21.2</v>
@@ -51427,13 +51423,13 @@
         </is>
       </c>
       <c r="M494" s="4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="N494" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O494" s="4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P494" s="4" t="n">
         <v>0.71</v>
@@ -51623,7 +51619,7 @@
         </is>
       </c>
       <c r="I496" s="4" t="n">
-        <v>19.01</v>
+        <v>19.02</v>
       </c>
       <c r="J496" s="4" t="n">
         <v>99.7</v>
@@ -51637,13 +51633,13 @@
         </is>
       </c>
       <c r="M496" s="4" t="n">
-        <v>7.73</v>
+        <v>7.74</v>
       </c>
       <c r="N496" s="4" t="n">
         <v>5.33</v>
       </c>
       <c r="O496" s="4" t="n">
-        <v>19.01</v>
+        <v>19.02</v>
       </c>
       <c r="P496" s="4" t="n">
         <v>3.16</v>
@@ -51725,13 +51721,13 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="J497" s="4" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="K497" s="4" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -51931,7 +51927,7 @@
         </is>
       </c>
       <c r="I499" s="4" t="n">
-        <v>21.65</v>
+        <v>21.66</v>
       </c>
       <c r="J499" s="4" t="n">
         <v>99.8</v>
@@ -51951,7 +51947,7 @@
         <v>5.33</v>
       </c>
       <c r="O499" s="4" t="n">
-        <v>21.65</v>
+        <v>21.66</v>
       </c>
       <c r="P499" s="4" t="n">
         <v>2.47</v>
@@ -52033,7 +52029,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>23.66</v>
+        <v>23.69</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -52090,10 +52086,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.83</v>
+        <v>61.85</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.17</v>
+        <v>38.15</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -52137,7 +52133,7 @@
         </is>
       </c>
       <c r="I501" s="4" t="n">
-        <v>-7.84</v>
+        <v>-7.81</v>
       </c>
       <c r="J501" s="4" t="n">
         <v>10</v>
@@ -52194,10 +52190,10 @@
         <v>0</v>
       </c>
       <c r="AB501" s="4" t="n">
-        <v>45.22</v>
+        <v>45.23</v>
       </c>
       <c r="AC501" s="4" t="n">
-        <v>52.91</v>
+        <v>52.9</v>
       </c>
       <c r="AD501" s="4" t="n">
         <v>1.87</v>
@@ -52245,7 +52241,7 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-20.93</v>
+        <v>-20.94</v>
       </c>
       <c r="J502" s="4" t="n">
         <v>0.2</v>
@@ -52455,7 +52451,7 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J504" s="4" t="n">
         <v>67.7</v>
@@ -52475,7 +52471,7 @@
         <v>5.33</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="P504" s="4" t="n">
         <v>1.51</v>
@@ -52763,7 +52759,7 @@
         </is>
       </c>
       <c r="I507" s="4" t="n">
-        <v>-42.97</v>
+        <v>-42.98</v>
       </c>
       <c r="J507" s="4" t="n">
         <v>0</v>
@@ -52783,10 +52779,10 @@
         <v>5.33</v>
       </c>
       <c r="O507" s="4" t="n">
-        <v>-42.97</v>
+        <v>-42.98</v>
       </c>
       <c r="P507" s="4" t="n">
-        <v>-2.74</v>
+        <v>-2.75</v>
       </c>
       <c r="Q507" s="4" t="n">
         <v>0</v>
@@ -55147,7 +55143,7 @@
         <v>112</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -55367,19 +55363,19 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="K43" t="n">
         <v>75</v>
       </c>
       <c r="L43" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M43" t="n">
         <v>96</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>78</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -55425,7 +55421,7 @@
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="K44" t="n">
         <v>38</v>
@@ -55437,7 +55433,7 @@
         <v>49</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -56875,7 +56871,7 @@
         </is>
       </c>
       <c r="J69" s="4" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="K69" t="n">
         <v>64</v>
@@ -56945,7 +56941,7 @@
         <v>38</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -57293,7 +57289,7 @@
         <v>93</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -57745,27 +57741,27 @@
         </is>
       </c>
       <c r="J84" s="4" t="n">
-        <v>49.9</v>
+        <v>50.4</v>
       </c>
       <c r="K84" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L84" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M84" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>49.1</v>
+        <v>51.7</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -57803,7 +57799,7 @@
         </is>
       </c>
       <c r="J85" s="4" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="K85" t="n">
         <v>17</v>
@@ -57815,7 +57811,7 @@
         <v>21</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>63</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>56.8</v>
+        <v>56.2</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>229</v>
       </c>
       <c r="E9" t="n">
-        <v>81.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="C10" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="D10" t="n">
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>40.4</v>
+        <v>39.3</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.1</v>
+        <v>-3.76</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>41</v>
+        <v>38.6</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>59</v>
+        <v>61.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-3.18</v>
+        <v>-3.34</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>74.2</v>
+        <v>74.8</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4725,13 +4725,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.43</v>
+        <v>-2.7</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.32</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-0.88</v>
+        <v>-1.14</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.04</v>
@@ -4766,16 +4766,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>48.41</v>
+        <v>48.33</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>51.59</v>
+        <v>51.67</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -24717,7 +24717,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.36</v>
+        <v>30.38</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24815,13 +24815,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.36</v>
+        <v>-3.99</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>35.7</v>
+        <v>38.8</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>64.3</v>
+        <v>61.2</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -28305,13 +28305,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-7.21</v>
+        <v>-7.2</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.71</v>
+        <v>-12.7</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.32</v>
@@ -28413,7 +28413,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-34.25</v>
+        <v>-34.24</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28427,13 +28427,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.67</v>
+        <v>-31.66</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.32</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-34.25</v>
+        <v>-34.24</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28464,10 +28464,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>32.87</v>
+        <v>32.88</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>67.13</v>
+        <v>67.12</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -35807,13 +35807,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-0.7</v>
+        <v>-1.17</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>35.5</v>
+        <v>33.6</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>64.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35839,16 +35839,16 @@
         <v>-11.15</v>
       </c>
       <c r="S342" s="4" t="n">
-        <v>46.08</v>
+        <v>45.02</v>
       </c>
       <c r="T342" s="4" t="n">
-        <v>42.69</v>
+        <v>42.25</v>
       </c>
       <c r="U342" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V342" s="4" t="n">
-        <v>1.18</v>
+        <v>0.67</v>
       </c>
       <c r="W342" s="5" t="n">
         <v>603156</v>
@@ -35864,10 +35864,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>49.65</v>
+        <v>49.41</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>50.35</v>
+        <v>50.59</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -49195,13 +49195,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.97</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>49.5</v>
+        <v>47.2</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>50.5</v>
+        <v>52.8</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.6</v>
+        <v>-10.76</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.32</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-1.82</v>
+        <v>-1.99</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.4</v>
@@ -49252,10 +49252,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.6</v>
+        <v>45.56</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.4</v>
+        <v>46.44</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -51091,7 +51091,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.57</v>
+        <v>-27.54</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51146,13 +51146,13 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.27</v>
+        <v>14.24</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>27.25</v>
+        <v>27.28</v>
       </c>
       <c r="AC491" s="4" t="n">
         <v>54.82</v>
@@ -53044,7 +53044,7 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="K3" t="n">
         <v>9</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-08-18 · evaluated at 0 days to election (actual: 77 days out)</t>
+          <t>Data as of 2026-08-19 · evaluated at 0 days to election (actual: 76 days out)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>56.3</v>
+        <v>56.7</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>233.3</v>
       </c>
       <c r="C9" t="n">
-        <v>202</v>
+        <v>201.7</v>
       </c>
       <c r="D9" t="n">
         <v>231</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>41.4</v>
+        <v>39</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-3.48</v>
+        <v>-4.38</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40</v>
+        <v>35.5</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>60</v>
+        <v>64.5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>44.09</v>
+        <v>44.07</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>47.91</v>
+        <v>47.93</v>
       </c>
       <c r="AD2" s="4" t="n">
         <v>8</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-17.76</v>
+        <v>-17.8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.4</v>
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>41.12</v>
+        <v>41.1</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>58.88</v>
+        <v>58.9</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-25.87</v>
+        <v>-14.91</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1162,12 +1162,18 @@
       <c r="R4" s="4" t="n">
         <v>-31.57</v>
       </c>
-      <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n"/>
+      <c r="S4" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>45</v>
+      </c>
       <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>-5</v>
+      </c>
       <c r="W4" s="5" t="n">
         <v>0</v>
       </c>
@@ -1182,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>37.06</v>
+        <v>42.55</v>
       </c>
       <c r="AC4" s="4" t="n">
-        <v>62.94</v>
+        <v>57.45</v>
       </c>
       <c r="AD4" s="4" t="n">
         <v>0</v>
@@ -1290,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>53.61</v>
+        <v>53.62</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>46.39</v>
+        <v>46.38</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>0</v>
@@ -1337,13 +1343,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>25.72</v>
+        <v>25.76</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1394,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>62.86</v>
+        <v>62.88</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>37.14</v>
+        <v>37.12</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1553,7 +1559,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19.33</v>
+        <v>19.34</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.7</v>
@@ -1657,13 +1663,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.08</v>
+        <v>-5.81</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>84.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1689,16 +1695,16 @@
         <v>-13.22</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>38.12</v>
+        <v>39.39</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>42.8</v>
+        <v>43.16</v>
       </c>
       <c r="U9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-4.84</v>
+        <v>-4.38</v>
       </c>
       <c r="W9" s="5" t="n">
         <v>5531882</v>
@@ -1714,10 +1720,10 @@
         <v>0</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>46.96</v>
+        <v>47.09</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>53.04</v>
+        <v>52.91</v>
       </c>
       <c r="AD9" s="4" t="n">
         <v>0</v>
@@ -1761,7 +1767,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>73.40000000000001</v>
@@ -2075,7 +2081,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-36.6</v>
+        <v>-36.75</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -2132,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>31.7</v>
+        <v>31.62</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>68.3</v>
+        <v>68.38</v>
       </c>
       <c r="AD13" s="4" t="n">
         <v>0</v>
@@ -2389,7 +2395,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>28.17</v>
+        <v>28.2</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2446,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>64.09</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>35.91</v>
+        <v>35.9</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2497,7 +2503,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>33.87</v>
+        <v>33.93</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>100</v>
@@ -2554,10 +2560,10 @@
         <v>0</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>66.94</v>
+        <v>66.97</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>33.06</v>
+        <v>33.03</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>0</v>
@@ -2601,7 +2607,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11.8</v>
+        <v>11.79</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>98.8</v>
@@ -2709,13 +2715,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.2</v>
+        <v>10.95</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>96.3</v>
+        <v>98</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2741,16 +2747,16 @@
         <v>-1.44</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>49.34</v>
+        <v>49.53</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>43.78</v>
+        <v>42.49</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>5.63</v>
+        <v>7.54</v>
       </c>
       <c r="W19" s="5" t="n">
         <v>5958887</v>
@@ -2766,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>55.1</v>
+        <v>55.48</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>44.9</v>
+        <v>44.52</v>
       </c>
       <c r="AD19" s="4" t="n">
         <v>0</v>
@@ -3033,7 +3039,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.75</v>
+        <v>-10.76</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>2.4</v>
@@ -3137,13 +3143,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.68</v>
+        <v>7.71</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3194,10 +3200,10 @@
         <v>0</v>
       </c>
       <c r="AB23" s="4" t="n">
-        <v>53.84</v>
+        <v>53.85</v>
       </c>
       <c r="AC23" s="4" t="n">
-        <v>46.16</v>
+        <v>46.15</v>
       </c>
       <c r="AD23" s="4" t="n">
         <v>0</v>
@@ -3245,13 +3251,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3302,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>50.17</v>
+        <v>50.19</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>49.83</v>
+        <v>49.81</v>
       </c>
       <c r="AD24" s="4" t="n">
         <v>0</v>
@@ -3410,10 +3416,10 @@
         <v>0</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>56.59</v>
+        <v>56.6</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>43.41</v>
+        <v>43.4</v>
       </c>
       <c r="AD25" s="4" t="n">
         <v>0</v>
@@ -3457,7 +3463,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.41</v>
+        <v>-3.43</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>24.9</v>
@@ -3663,7 +3669,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>80.40000000000001</v>
@@ -3875,7 +3881,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.99</v>
+        <v>20</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.8</v>
@@ -3979,13 +3985,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-10.39</v>
+        <v>-10.38</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -4293,7 +4299,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.77</v>
+        <v>-6.79</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>13.2</v>
@@ -4350,10 +4356,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>46.62</v>
+        <v>46.61</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>53.38</v>
+        <v>53.39</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4401,7 +4407,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-20.23</v>
+        <v>-20.29</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.2</v>
@@ -4458,10 +4464,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>39.88</v>
+        <v>39.86</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>60.12</v>
+        <v>60.14</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>0</v>
@@ -4505,17 +4511,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>4.24</v>
+        <v>3.32</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>21.9</v>
+        <v>25.3</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Likely D</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M36" s="4" t="n">
@@ -4525,10 +4531,10 @@
         <v>5.38</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>4.57</v>
+        <v>2.81</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0</v>
+        <v>-1.76</v>
       </c>
       <c r="Q36" s="4" t="n">
         <v>0.28</v>
@@ -4549,7 +4555,7 @@
         <v>3.88</v>
       </c>
       <c r="W36" s="5" t="n">
-        <v>0</v>
+        <v>1426778</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>15315779</v>
@@ -4562,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>52.12</v>
+        <v>51.66</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>47.88</v>
+        <v>48.34</v>
       </c>
       <c r="AD36" s="4" t="n">
         <v>0</v>
@@ -4599,7 +4605,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Megan Degenfelder</t>
+          <t>Eric Barlow</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4609,7 +4615,7 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>-39.52</v>
+        <v>-42.03</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>0</v>
@@ -4629,13 +4635,13 @@
         <v>5.38</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>-39.52</v>
+        <v>-42.03</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R37" s="4" t="n">
         <v>-46.96</v>
@@ -4650,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="X37" s="5" t="n">
-        <v>777833</v>
+        <v>1673103</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" s="4" t="n">
@@ -4660,10 +4666,10 @@
         <v>0</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>30.24</v>
+        <v>28.99</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>69.76000000000001</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="AD37" s="4" t="n">
         <v>0</v>
@@ -4711,13 +4717,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-5.1</v>
+        <v>-5.2</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>81.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4725,13 +4731,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.46</v>
+        <v>-2.71</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-0.84</v>
+        <v>-1.1</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.04</v>
@@ -4766,16 +4772,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>47.45</v>
+        <v>47.4</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>52.55</v>
+        <v>52.6</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -4819,7 +4825,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-27.16</v>
+        <v>-27.18</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
@@ -4833,13 +4839,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-30.24</v>
+        <v>-30.25</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-27.16</v>
+        <v>-27.18</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>-1.75</v>
@@ -4870,10 +4876,10 @@
         <v>0</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>36.42</v>
+        <v>36.41</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>63.58</v>
+        <v>63.59</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>0</v>
@@ -4935,13 +4941,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-1.32</v>
+        <v>-1.33</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>-0.45</v>
@@ -4978,10 +4984,10 @@
         <v>0</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>48.91</v>
+        <v>48.92</v>
       </c>
       <c r="AC40" s="4" t="n">
-        <v>51.09</v>
+        <v>51.08</v>
       </c>
       <c r="AD40" s="4" t="n">
         <v>0</v>
@@ -5029,7 +5035,7 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-40.13</v>
+        <v>-40.14</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -5043,13 +5049,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-41</v>
+        <v>-41.02</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-40.13</v>
+        <v>-40.14</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>-2.23</v>
@@ -5080,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>29.94</v>
+        <v>29.93</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>70.06</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="AD41" s="4" t="n">
         <v>0</v>
@@ -5131,7 +5137,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-60.31</v>
+        <v>-60.32</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -5145,13 +5151,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-61.25</v>
+        <v>-61.27</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-60.31</v>
+        <v>-60.32</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>-2.1</v>
@@ -5182,10 +5188,10 @@
         <v>0</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>19.85</v>
+        <v>19.84</v>
       </c>
       <c r="AC42" s="4" t="n">
-        <v>80.15000000000001</v>
+        <v>80.16</v>
       </c>
       <c r="AD42" s="4" t="n">
         <v>0</v>
@@ -5233,7 +5239,7 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-22.23</v>
+        <v>-22.24</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0.1</v>
@@ -5247,13 +5253,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-24.8</v>
+        <v>-24.81</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-22.23</v>
+        <v>-22.24</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>-0.59</v>
@@ -5335,7 +5341,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-27.67</v>
+        <v>-27.68</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5349,13 +5355,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-30.32</v>
+        <v>-30.33</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-27.67</v>
+        <v>-27.68</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>0</v>
@@ -5386,10 +5392,10 @@
         <v>0</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>36.17</v>
+        <v>36.16</v>
       </c>
       <c r="AC44" s="4" t="n">
-        <v>63.83</v>
+        <v>63.84</v>
       </c>
       <c r="AD44" s="4" t="n">
         <v>0</v>
@@ -5437,7 +5443,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>35.22</v>
+        <v>35.21</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>100</v>
@@ -5451,13 +5457,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>23.92</v>
+        <v>23.91</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>35.22</v>
+        <v>35.21</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>1.73</v>
@@ -5488,10 +5494,10 @@
         <v>0</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>67.61</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AC45" s="4" t="n">
-        <v>32.39</v>
+        <v>32.4</v>
       </c>
       <c r="AD45" s="4" t="n">
         <v>0</v>
@@ -5539,7 +5545,7 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>-42.58</v>
+        <v>-40.28</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>0</v>
@@ -5553,13 +5559,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>-41.38</v>
+        <v>-39.08</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>-42.58</v>
+        <v>-40.28</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>-1.62</v>
@@ -5590,10 +5596,10 @@
         <v>0</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>28.71</v>
+        <v>29.86</v>
       </c>
       <c r="AC46" s="4" t="n">
-        <v>71.29000000000001</v>
+        <v>70.14</v>
       </c>
       <c r="AD46" s="4" t="n">
         <v>0</v>
@@ -5641,13 +5647,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>-7.79</v>
+        <v>-5.84</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>10.1</v>
+        <v>16.3</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>89.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -5655,13 +5661,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-12.18</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>-9.43</v>
+        <v>-7.13</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>-0.99</v>
@@ -5698,10 +5704,10 @@
         <v>0</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>46.1</v>
+        <v>47.08</v>
       </c>
       <c r="AC47" s="4" t="n">
-        <v>53.9</v>
+        <v>52.92</v>
       </c>
       <c r="AD47" s="4" t="n">
         <v>0</v>
@@ -5749,7 +5755,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>-25.44</v>
+        <v>-23.14</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>0.1</v>
@@ -5763,13 +5769,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>-22.37</v>
+        <v>-20.07</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-25.44</v>
+        <v>-23.14</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>-1.82</v>
@@ -5800,10 +5806,10 @@
         <v>0</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>37.28</v>
+        <v>38.43</v>
       </c>
       <c r="AC48" s="4" t="n">
-        <v>62.72</v>
+        <v>61.57</v>
       </c>
       <c r="AD48" s="4" t="n">
         <v>0</v>
@@ -5851,7 +5857,7 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>-38.69</v>
+        <v>-36.4</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>0</v>
@@ -5865,13 +5871,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>-35.74</v>
+        <v>-33.44</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>-38.69</v>
+        <v>-36.4</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>-2.88</v>
@@ -5902,10 +5908,10 @@
         <v>0</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>30.65</v>
+        <v>31.8</v>
       </c>
       <c r="AC49" s="4" t="n">
-        <v>69.34999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="AD49" s="4" t="n">
         <v>0</v>
@@ -6057,7 +6063,7 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>61.8</v>
@@ -6114,10 +6120,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>50.01</v>
+        <v>50.02</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>49.99</v>
+        <v>49.98</v>
       </c>
       <c r="AD51" s="4" t="n">
         <v>0</v>
@@ -6467,7 +6473,7 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>81</v>
@@ -6881,7 +6887,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19.22</v>
+        <v>19.23</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>99.7</v>
@@ -6895,13 +6901,13 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>15.19</v>
+        <v>15.2</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>19.22</v>
+        <v>19.23</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0.21</v>
@@ -6932,10 +6938,10 @@
         <v>0</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>59.61</v>
+        <v>59.62</v>
       </c>
       <c r="AC59" s="4" t="n">
-        <v>40.39</v>
+        <v>40.38</v>
       </c>
       <c r="AD59" s="4" t="n">
         <v>0</v>
@@ -6983,7 +6989,7 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>33.3</v>
+        <v>33.31</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>100</v>
@@ -7003,7 +7009,7 @@
         <v>5.38</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33.3</v>
+        <v>33.31</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -7085,7 +7091,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>21.11</v>
+        <v>21.12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>99.8</v>
@@ -7099,13 +7105,13 @@
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>12.55</v>
+        <v>12.56</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>21.11</v>
+        <v>21.12</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>1.08</v>
@@ -7136,10 +7142,10 @@
         <v>0</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>60.55</v>
+        <v>60.56</v>
       </c>
       <c r="AC61" s="4" t="n">
-        <v>39.45</v>
+        <v>39.44</v>
       </c>
       <c r="AD61" s="4" t="n">
         <v>0</v>
@@ -7201,13 +7207,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>18.02</v>
+        <v>18.03</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>26.53</v>
+        <v>26.54</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -7289,7 +7295,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>-18.25</v>
+        <v>-18.24</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0.3</v>
@@ -7303,13 +7309,13 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-18.5</v>
+        <v>-18.49</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>-18.25</v>
+        <v>-18.24</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>-0.65</v>
@@ -7340,10 +7346,10 @@
         <v>0</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>40.87</v>
+        <v>40.88</v>
       </c>
       <c r="AC63" s="4" t="n">
-        <v>59.13</v>
+        <v>59.12</v>
       </c>
       <c r="AD63" s="4" t="n">
         <v>0</v>
@@ -7405,7 +7411,7 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>10.99</v>
+        <v>11</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>5.38</v>
@@ -7507,13 +7513,13 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>16.37</v>
+        <v>16.38</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>25.4</v>
+        <v>25.41</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -7595,7 +7601,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>48.95</v>
+        <v>48.96</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>100</v>
@@ -7615,7 +7621,7 @@
         <v>5.38</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>48.95</v>
+        <v>48.96</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>1.66</v>
@@ -7697,7 +7703,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>30.69</v>
+        <v>30.7</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>100</v>
@@ -7711,13 +7717,13 @@
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>17.05</v>
+        <v>17.06</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>30.69</v>
+        <v>30.7</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>2.78</v>
@@ -7748,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="AB67" s="4" t="n">
-        <v>65.34</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AC67" s="4" t="n">
-        <v>34.66</v>
+        <v>34.65</v>
       </c>
       <c r="AD67" s="4" t="n">
         <v>0</v>
@@ -7799,7 +7805,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>42.86</v>
+        <v>42.87</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>100</v>
@@ -7813,13 +7819,13 @@
         </is>
       </c>
       <c r="M68" s="4" t="n">
-        <v>37.22</v>
+        <v>37.23</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>42.86</v>
+        <v>42.87</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
@@ -8013,13 +8019,13 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>80.52</v>
+        <v>80.53</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>87.83</v>
+        <v>87.84</v>
       </c>
       <c r="P70" s="4" t="n">
         <v>0</v>
@@ -8115,7 +8121,7 @@
         </is>
       </c>
       <c r="M71" s="4" t="n">
-        <v>6.62</v>
+        <v>6.63</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>5.38</v>
@@ -8213,13 +8219,13 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>40.45</v>
+        <v>40.46</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>45.95</v>
+        <v>45.96</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
@@ -8301,7 +8307,7 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>58.19</v>
+        <v>58.2</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>100</v>
@@ -8315,13 +8321,13 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>53.54</v>
+        <v>53.55</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>58.19</v>
+        <v>58.2</v>
       </c>
       <c r="P73" s="4" t="n">
         <v>0</v>
@@ -8403,7 +8409,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>59.6</v>
+        <v>59.61</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>100</v>
@@ -8417,13 +8423,13 @@
         </is>
       </c>
       <c r="M74" s="4" t="n">
-        <v>52.66</v>
+        <v>52.67</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>59.6</v>
+        <v>59.61</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -8454,10 +8460,10 @@
         <v>0</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>79.8</v>
+        <v>79.81</v>
       </c>
       <c r="AC74" s="4" t="n">
-        <v>20.2</v>
+        <v>20.19</v>
       </c>
       <c r="AD74" s="4" t="n">
         <v>0</v>
@@ -8505,7 +8511,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>100</v>
@@ -8519,13 +8525,13 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>44.89</v>
+        <v>44.9</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>3.69</v>
@@ -8621,7 +8627,7 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>34.82</v>
+        <v>34.83</v>
       </c>
       <c r="N76" s="4" t="n">
         <v>5.38</v>
@@ -8709,7 +8715,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>49.25</v>
+        <v>49.26</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>100</v>
@@ -8729,7 +8735,7 @@
         <v>5.38</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>50.17</v>
+        <v>50.18</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>2.46</v>
@@ -8760,10 +8766,10 @@
         <v>0</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>71.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AC77" s="4" t="n">
-        <v>24.45</v>
+        <v>24.44</v>
       </c>
       <c r="AD77" s="4" t="n">
         <v>3.66</v>
@@ -8825,7 +8831,7 @@
         </is>
       </c>
       <c r="M78" s="4" t="n">
-        <v>-30.58</v>
+        <v>-30.57</v>
       </c>
       <c r="N78" s="4" t="n">
         <v>5.38</v>
@@ -8913,7 +8919,7 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>20.86</v>
+        <v>20.87</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>99.8</v>
@@ -8933,7 +8939,7 @@
         <v>5.38</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>20.86</v>
+        <v>20.87</v>
       </c>
       <c r="P79" s="4" t="n">
         <v>0.95</v>
@@ -9015,13 +9021,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.71</v>
+        <v>5.73</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -9029,13 +9035,13 @@
         </is>
       </c>
       <c r="M80" s="4" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>7.14</v>
+        <v>7.15</v>
       </c>
       <c r="P80" s="4" t="n">
         <v>-0.32</v>
@@ -9123,7 +9129,7 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>-16.42</v>
+        <v>-16.41</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>0.5</v>
@@ -9137,13 +9143,13 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-17</v>
+        <v>-16.99</v>
       </c>
       <c r="N81" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>-16.42</v>
+        <v>-16.41</v>
       </c>
       <c r="P81" s="4" t="n">
         <v>-1.89</v>
@@ -9225,7 +9231,7 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>36.61</v>
+        <v>36.62</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>100</v>
@@ -9239,13 +9245,13 @@
         </is>
       </c>
       <c r="M82" s="4" t="n">
-        <v>27.94</v>
+        <v>27.95</v>
       </c>
       <c r="N82" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>36.61</v>
+        <v>36.62</v>
       </c>
       <c r="P82" s="4" t="n">
         <v>1.43</v>
@@ -9327,7 +9333,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>19.71</v>
+        <v>19.72</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>99.8</v>
@@ -9341,13 +9347,13 @@
         </is>
       </c>
       <c r="M83" s="4" t="n">
-        <v>10.16</v>
+        <v>10.17</v>
       </c>
       <c r="N83" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>19.71</v>
+        <v>19.72</v>
       </c>
       <c r="P83" s="4" t="n">
         <v>0.58</v>
@@ -9439,7 +9445,7 @@
         </is>
       </c>
       <c r="M84" s="4" t="n">
-        <v>18.81</v>
+        <v>18.82</v>
       </c>
       <c r="N84" s="4" t="n">
         <v>5.38</v>
@@ -9527,7 +9533,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>100</v>
@@ -9541,13 +9547,13 @@
         </is>
       </c>
       <c r="M85" s="4" t="n">
-        <v>13.94</v>
+        <v>13.95</v>
       </c>
       <c r="N85" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="P85" s="4" t="n">
         <v>1.74</v>
@@ -9578,10 +9584,10 @@
         <v>0</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>63.39</v>
+        <v>63.4</v>
       </c>
       <c r="AC85" s="4" t="n">
-        <v>36.61</v>
+        <v>36.6</v>
       </c>
       <c r="AD85" s="4" t="n">
         <v>0</v>
@@ -9751,7 +9757,7 @@
         <v>5.38</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>53.3</v>
+        <v>53.31</v>
       </c>
       <c r="P87" s="4" t="n">
         <v>0</v>
@@ -9833,7 +9839,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>51.64</v>
+        <v>51.65</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>100</v>
@@ -9847,13 +9853,13 @@
         </is>
       </c>
       <c r="M88" s="4" t="n">
-        <v>44.54</v>
+        <v>44.55</v>
       </c>
       <c r="N88" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>51.64</v>
+        <v>51.65</v>
       </c>
       <c r="P88" s="4" t="n">
         <v>1.57</v>
@@ -9935,7 +9941,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.01</v>
+        <v>16.02</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>99.5</v>
@@ -9949,13 +9955,13 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>17.62</v>
+        <v>17.63</v>
       </c>
       <c r="N89" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>16.01</v>
+        <v>16.02</v>
       </c>
       <c r="P89" s="4" t="n">
         <v>1.31</v>
@@ -10037,7 +10043,7 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>39.49</v>
+        <v>39.5</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>100</v>
@@ -10057,7 +10063,7 @@
         <v>5.38</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>39.49</v>
+        <v>39.5</v>
       </c>
       <c r="P90" s="4" t="n">
         <v>2.65</v>
@@ -10190,10 +10196,10 @@
         <v>0</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>64.16</v>
+        <v>64.17</v>
       </c>
       <c r="AC91" s="4" t="n">
-        <v>35.84</v>
+        <v>35.83</v>
       </c>
       <c r="AD91" s="4" t="n">
         <v>0</v>
@@ -10261,7 +10267,7 @@
         <v>5.38</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P92" s="4" t="n">
         <v>0</v>
@@ -10357,7 +10363,7 @@
         </is>
       </c>
       <c r="M93" s="4" t="n">
-        <v>13.83</v>
+        <v>13.84</v>
       </c>
       <c r="N93" s="4" t="n">
         <v>5.38</v>
@@ -10445,7 +10451,7 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>51.02</v>
+        <v>51.03</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>100</v>
@@ -10465,7 +10471,7 @@
         <v>5.38</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>51.02</v>
+        <v>51.03</v>
       </c>
       <c r="P94" s="4" t="n">
         <v>2.66</v>
@@ -10561,7 +10567,7 @@
         </is>
       </c>
       <c r="M95" s="4" t="n">
-        <v>67.56</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="N95" s="4" t="n">
         <v>5.38</v>
@@ -10645,7 +10651,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>25.95</v>
+        <v>25.96</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>100</v>
@@ -10659,13 +10665,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="n">
-        <v>18.7</v>
+        <v>18.71</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>25.95</v>
+        <v>25.96</v>
       </c>
       <c r="P96" s="4" t="n">
         <v>0</v>
@@ -10747,7 +10753,7 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>25.26</v>
+        <v>25.27</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>99.90000000000001</v>
@@ -10761,13 +10767,13 @@
         </is>
       </c>
       <c r="M97" s="4" t="n">
-        <v>15.72</v>
+        <v>15.73</v>
       </c>
       <c r="N97" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>25.26</v>
+        <v>25.27</v>
       </c>
       <c r="P97" s="4" t="n">
         <v>0</v>
@@ -10863,13 +10869,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="n">
-        <v>-10.5</v>
+        <v>-10.49</v>
       </c>
       <c r="N98" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>-4.76</v>
+        <v>-4.75</v>
       </c>
       <c r="P98" s="4" t="n">
         <v>0</v>
@@ -10965,7 +10971,7 @@
         </is>
       </c>
       <c r="M99" s="4" t="n">
-        <v>19.26</v>
+        <v>19.27</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>5.38</v>
@@ -11002,10 +11008,10 @@
         <v>0</v>
       </c>
       <c r="AB99" s="4" t="n">
-        <v>65.54000000000001</v>
+        <v>65.55</v>
       </c>
       <c r="AC99" s="4" t="n">
-        <v>34.46</v>
+        <v>34.45</v>
       </c>
       <c r="AD99" s="4" t="n">
         <v>0</v>
@@ -11067,7 +11073,7 @@
         </is>
       </c>
       <c r="M100" s="4" t="n">
-        <v>16.5</v>
+        <v>16.51</v>
       </c>
       <c r="N100" s="4" t="n">
         <v>5.38</v>
@@ -11104,10 +11110,10 @@
         <v>0</v>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>63.09</v>
+        <v>63.1</v>
       </c>
       <c r="AC100" s="4" t="n">
-        <v>36.91</v>
+        <v>36.9</v>
       </c>
       <c r="AD100" s="4" t="n">
         <v>0</v>
@@ -11155,7 +11161,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>63.4</v>
+        <v>63.41</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>100</v>
@@ -11169,13 +11175,13 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>56.47</v>
+        <v>56.48</v>
       </c>
       <c r="N101" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>63.4</v>
+        <v>63.41</v>
       </c>
       <c r="P101" s="4" t="n">
         <v>0</v>
@@ -11206,10 +11212,10 @@
         <v>0</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>81.7</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="AC101" s="4" t="n">
-        <v>18.3</v>
+        <v>18.29</v>
       </c>
       <c r="AD101" s="4" t="n">
         <v>0</v>
@@ -11271,7 +11277,7 @@
         </is>
       </c>
       <c r="M102" s="4" t="n">
-        <v>43.24</v>
+        <v>43.25</v>
       </c>
       <c r="N102" s="4" t="n">
         <v>5.38</v>
@@ -11359,7 +11365,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20.22</v>
+        <v>20.23</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>99.8</v>
@@ -11373,13 +11379,13 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>7.94</v>
+        <v>7.95</v>
       </c>
       <c r="N103" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>20.22</v>
+        <v>20.23</v>
       </c>
       <c r="P103" s="4" t="n">
         <v>1.39</v>
@@ -11461,7 +11467,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>39.34</v>
+        <v>39.35</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
@@ -11475,13 +11481,13 @@
         </is>
       </c>
       <c r="M104" s="4" t="n">
-        <v>21.7</v>
+        <v>21.71</v>
       </c>
       <c r="N104" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>39.34</v>
+        <v>39.35</v>
       </c>
       <c r="P104" s="4" t="n">
         <v>1.73</v>
@@ -11563,7 +11569,7 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>23.15</v>
+        <v>23.16</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>99.90000000000001</v>
@@ -11577,13 +11583,13 @@
         </is>
       </c>
       <c r="M105" s="4" t="n">
-        <v>13.03</v>
+        <v>13.04</v>
       </c>
       <c r="N105" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>22.43</v>
+        <v>22.44</v>
       </c>
       <c r="P105" s="4" t="n">
         <v>1.61</v>
@@ -11614,10 +11620,10 @@
         <v>0</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>59.35</v>
+        <v>59.36</v>
       </c>
       <c r="AC105" s="4" t="n">
-        <v>37.04</v>
+        <v>37.03</v>
       </c>
       <c r="AD105" s="4" t="n">
         <v>3.61</v>
@@ -11661,13 +11667,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>7.59</v>
+        <v>7.66</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>89.3</v>
+        <v>89.5</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -11681,7 +11687,7 @@
         <v>5.38</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>11.69</v>
+        <v>11.7</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>0.13</v>
@@ -11718,10 +11724,10 @@
         <v>0</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>53.8</v>
+        <v>53.83</v>
       </c>
       <c r="AC106" s="4" t="n">
-        <v>46.2</v>
+        <v>46.17</v>
       </c>
       <c r="AD106" s="4" t="n">
         <v>0</v>
@@ -11769,7 +11775,7 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>99.90000000000001</v>
@@ -11783,13 +11789,13 @@
         </is>
       </c>
       <c r="M107" s="4" t="n">
-        <v>14.23</v>
+        <v>14.24</v>
       </c>
       <c r="N107" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O107" s="4" t="n">
-        <v>21.88</v>
+        <v>21.89</v>
       </c>
       <c r="P107" s="4" t="n">
         <v>2.54</v>
@@ -11871,7 +11877,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>26.16</v>
+        <v>26.17</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>100</v>
@@ -11885,13 +11891,13 @@
         </is>
       </c>
       <c r="M108" s="4" t="n">
-        <v>20.48</v>
+        <v>20.49</v>
       </c>
       <c r="N108" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>26.16</v>
+        <v>26.17</v>
       </c>
       <c r="P108" s="4" t="n">
         <v>0</v>
@@ -12024,10 +12030,10 @@
         <v>0</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>63.69</v>
+        <v>63.7</v>
       </c>
       <c r="AC109" s="4" t="n">
-        <v>36.31</v>
+        <v>36.3</v>
       </c>
       <c r="AD109" s="4" t="n">
         <v>0</v>
@@ -12075,7 +12081,7 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>39.64</v>
+        <v>39.65</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>100</v>
@@ -12089,13 +12095,13 @@
         </is>
       </c>
       <c r="M110" s="4" t="n">
-        <v>24.21</v>
+        <v>24.22</v>
       </c>
       <c r="N110" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>39.64</v>
+        <v>39.65</v>
       </c>
       <c r="P110" s="4" t="n">
         <v>1.58</v>
@@ -12377,13 +12383,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>-2.29</v>
+        <v>-2.28</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -12434,10 +12440,10 @@
         <v>0</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>48.85</v>
+        <v>48.86</v>
       </c>
       <c r="AC113" s="4" t="n">
-        <v>51.15</v>
+        <v>51.14</v>
       </c>
       <c r="AD113" s="4" t="n">
         <v>0</v>
@@ -12587,13 +12593,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>-6.2</v>
+        <v>-6.21</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -13011,7 +13017,7 @@
         </is>
       </c>
       <c r="M119" s="4" t="n">
-        <v>25.58</v>
+        <v>25.59</v>
       </c>
       <c r="N119" s="4" t="n">
         <v>5.38</v>
@@ -13215,7 +13221,7 @@
         </is>
       </c>
       <c r="M121" s="4" t="n">
-        <v>16.65</v>
+        <v>16.66</v>
       </c>
       <c r="N121" s="4" t="n">
         <v>5.38</v>
@@ -13317,7 +13323,7 @@
         </is>
       </c>
       <c r="M122" s="4" t="n">
-        <v>26.56</v>
+        <v>26.57</v>
       </c>
       <c r="N122" s="4" t="n">
         <v>5.38</v>
@@ -13590,7 +13596,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Marcel Davis</t>
+          <t>Gay Valimont</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -13609,7 +13615,7 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>-30.55</v>
+        <v>-32.97</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>0</v>
@@ -13623,16 +13629,16 @@
         </is>
       </c>
       <c r="M125" s="4" t="n">
-        <v>-33.73</v>
+        <v>-34.04</v>
       </c>
       <c r="N125" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O125" s="4" t="n">
-        <v>-30.55</v>
+        <v>-32.97</v>
       </c>
       <c r="P125" s="4" t="n">
-        <v>0</v>
+        <v>-2.11</v>
       </c>
       <c r="Q125" s="4" t="n">
         <v>-1.67</v>
@@ -13647,7 +13653,7 @@
       </c>
       <c r="V125" s="4" t="n"/>
       <c r="W125" s="5" t="n">
-        <v>0</v>
+        <v>174309</v>
       </c>
       <c r="X125" s="5" t="n">
         <v>3789738</v>
@@ -13660,10 +13666,10 @@
         <v>0</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>34.72</v>
+        <v>33.51</v>
       </c>
       <c r="AC125" s="4" t="n">
-        <v>65.28</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="AD125" s="4" t="n">
         <v>0</v>
@@ -13692,12 +13698,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Nicholas Zateslo</t>
+          <t>Amanda Green</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Keith Gross</t>
+          <t>Austin Rogers</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -13707,13 +13713,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>-12.87</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>99</v>
+        <v>95.3</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -13721,16 +13727,16 @@
         </is>
       </c>
       <c r="M126" s="4" t="n">
-        <v>-13.43</v>
+        <v>-13.74</v>
       </c>
       <c r="N126" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>-10.57</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>-2.12</v>
+        <v>-1.02</v>
       </c>
       <c r="Q126" s="4" t="n">
         <v>0</v>
@@ -13738,23 +13744,17 @@
       <c r="R126" s="4" t="n">
         <v>-18.33</v>
       </c>
-      <c r="S126" s="4" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="T126" s="4" t="n">
-        <v>58.5</v>
-      </c>
+      <c r="S126" s="4" t="n"/>
+      <c r="T126" s="4" t="n"/>
       <c r="U126" t="n">
-        <v>1</v>
-      </c>
-      <c r="V126" s="4" t="n">
-        <v>-16.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V126" s="4" t="n"/>
       <c r="W126" s="5" t="n">
-        <v>449913</v>
+        <v>348120</v>
       </c>
       <c r="X126" s="5" t="n">
-        <v>12325575</v>
+        <v>1010277</v>
       </c>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" s="4" t="n">
@@ -13764,10 +13764,10 @@
         <v>0</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>43.57</v>
+        <v>45.11</v>
       </c>
       <c r="AC126" s="4" t="n">
-        <v>56.43</v>
+        <v>54.89</v>
       </c>
       <c r="AD126" s="4" t="n">
         <v>0</v>
@@ -13815,7 +13815,7 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>-17.1</v>
+        <v>-17.42</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>0.4</v>
@@ -13829,13 +13829,13 @@
         </is>
       </c>
       <c r="M127" s="4" t="n">
-        <v>-16.41</v>
+        <v>-16.72</v>
       </c>
       <c r="N127" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O127" s="4" t="n">
-        <v>-17.1</v>
+        <v>-17.42</v>
       </c>
       <c r="P127" s="4" t="n">
         <v>-2.38</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>41.45</v>
+        <v>41.29</v>
       </c>
       <c r="AC127" s="4" t="n">
-        <v>58.55</v>
+        <v>58.71</v>
       </c>
       <c r="AD127" s="4" t="n">
         <v>0</v>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Michael Kirwan</t>
+          <t>LaShonda Holloway</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -13917,13 +13917,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>-6.66</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>13.6</v>
+        <v>7.5</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>86.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -13931,16 +13931,16 @@
         </is>
       </c>
       <c r="M128" s="4" t="n">
-        <v>-7.8</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="N128" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>-6.66</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>-0.77</v>
+        <v>-2.52</v>
       </c>
       <c r="Q128" s="4" t="n">
         <v>-3.29</v>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="V128" s="4" t="n"/>
       <c r="W128" s="5" t="n">
-        <v>742680</v>
+        <v>27348</v>
       </c>
       <c r="X128" s="5" t="n">
         <v>2163376</v>
@@ -13968,10 +13968,10 @@
         <v>0</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>46.67</v>
+        <v>45.64</v>
       </c>
       <c r="AC128" s="4" t="n">
-        <v>53.33</v>
+        <v>54.36</v>
       </c>
       <c r="AD128" s="4" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>-17.53</v>
+        <v>-17.84</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>0.4</v>
@@ -14033,13 +14033,13 @@
         </is>
       </c>
       <c r="M129" s="4" t="n">
-        <v>-17.61</v>
+        <v>-17.92</v>
       </c>
       <c r="N129" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O129" s="4" t="n">
-        <v>-17.53</v>
+        <v>-17.84</v>
       </c>
       <c r="P129" s="4" t="n">
         <v>-0.66</v>
@@ -14070,10 +14070,10 @@
         <v>0</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>41.24</v>
+        <v>41.08</v>
       </c>
       <c r="AC129" s="4" t="n">
-        <v>58.76</v>
+        <v>58.92</v>
       </c>
       <c r="AD129" s="4" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Democratic candidate (FL-06)</t>
+          <t>Eric Yonce</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14121,7 +14121,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>-22.22</v>
+        <v>-24.51</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>0.1</v>
@@ -14135,16 +14135,16 @@
         </is>
       </c>
       <c r="M130" s="4" t="n">
-        <v>-25.55</v>
+        <v>-25.86</v>
       </c>
       <c r="N130" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O130" s="4" t="n">
-        <v>-22.22</v>
+        <v>-24.51</v>
       </c>
       <c r="P130" s="4" t="n">
-        <v>0</v>
+        <v>-1.98</v>
       </c>
       <c r="Q130" s="4" t="n">
         <v>-1.67</v>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="V130" s="4" t="n"/>
       <c r="W130" s="5" t="n">
-        <v>0</v>
+        <v>325710</v>
       </c>
       <c r="X130" s="5" t="n">
         <v>4286207</v>
@@ -14172,10 +14172,10 @@
         <v>0</v>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>38.89</v>
+        <v>37.74</v>
       </c>
       <c r="AC130" s="4" t="n">
-        <v>61.11</v>
+        <v>62.26</v>
       </c>
       <c r="AD130" s="4" t="n">
         <v>0</v>
@@ -14209,68 +14209,58 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Cory Mills</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
+          <t>Ryan Elijah</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>REP</t>
-        </is>
-      </c>
       <c r="I131" s="4" t="n">
-        <v>-3.95</v>
+        <v>-1.55</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>22.9</v>
+        <v>32.1</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M131" s="4" t="n">
-        <v>-7.86</v>
+        <v>-8.18</v>
       </c>
       <c r="N131" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O131" s="4" t="n">
-        <v>-4.52</v>
+        <v>-1.55</v>
       </c>
       <c r="P131" s="4" t="n">
-        <v>0.58</v>
+        <v>1.15</v>
       </c>
       <c r="Q131" s="4" t="n">
-        <v>-2.73</v>
+        <v>0</v>
       </c>
       <c r="R131" s="4" t="n">
         <v>-12.62</v>
       </c>
-      <c r="S131" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="T131" s="4" t="n">
-        <v>39</v>
-      </c>
+      <c r="S131" s="4" t="n"/>
+      <c r="T131" s="4" t="n"/>
       <c r="U131" t="n">
-        <v>1</v>
-      </c>
-      <c r="V131" s="4" t="n">
-        <v>-1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V131" s="4" t="n"/>
       <c r="W131" s="5" t="n">
         <v>1378109</v>
       </c>
       <c r="X131" s="5" t="n">
-        <v>880711</v>
+        <v>355955</v>
       </c>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" s="4" t="n">
@@ -14280,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AB131" s="4" t="n">
-        <v>48.03</v>
+        <v>49.23</v>
       </c>
       <c r="AC131" s="4" t="n">
-        <v>51.97</v>
+        <v>50.77</v>
       </c>
       <c r="AD131" s="4" t="n">
         <v>0</v>
@@ -14331,13 +14321,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-10.14</v>
+        <v>-10.33</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -14345,13 +14335,13 @@
         </is>
       </c>
       <c r="M132" s="4" t="n">
-        <v>-12.06</v>
+        <v>-12.38</v>
       </c>
       <c r="N132" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O132" s="4" t="n">
-        <v>-9.16</v>
+        <v>-9.48</v>
       </c>
       <c r="P132" s="4" t="n">
         <v>-0.66</v>
@@ -14388,10 +14378,10 @@
         <v>0</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>44.93</v>
+        <v>44.83</v>
       </c>
       <c r="AC132" s="4" t="n">
-        <v>55.07</v>
+        <v>55.17</v>
       </c>
       <c r="AD132" s="4" t="n">
         <v>0</v>
@@ -14425,7 +14415,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Thomas Chalifoux</t>
+          <t>Dan Green</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -14439,13 +14429,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>3.35</v>
+        <v>0.49</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>74.8</v>
+        <v>63.7</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>25.2</v>
+        <v>36.3</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -14453,19 +14443,19 @@
         </is>
       </c>
       <c r="M133" s="4" t="n">
-        <v>-11.63</v>
+        <v>-11.94</v>
       </c>
       <c r="N133" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O133" s="4" t="n">
-        <v>3.35</v>
+        <v>0.49</v>
       </c>
       <c r="P133" s="4" t="n">
-        <v>-0.25</v>
+        <v>0.37</v>
       </c>
       <c r="Q133" s="4" t="n">
-        <v>8.83</v>
+        <v>5.65</v>
       </c>
       <c r="R133" s="4" t="n">
         <v>-17.93</v>
@@ -14480,7 +14470,7 @@
         <v>2157834</v>
       </c>
       <c r="X133" s="5" t="n">
-        <v>3139737</v>
+        <v>1298516</v>
       </c>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" s="4" t="n">
@@ -14490,10 +14480,10 @@
         <v>0</v>
       </c>
       <c r="AB133" s="4" t="n">
-        <v>51.68</v>
+        <v>50.25</v>
       </c>
       <c r="AC133" s="4" t="n">
-        <v>48.32</v>
+        <v>49.75</v>
       </c>
       <c r="AD133" s="4" t="n">
         <v>0</v>
@@ -14541,7 +14531,7 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>38.37</v>
+        <v>38.06</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>100</v>
@@ -14555,13 +14545,13 @@
         </is>
       </c>
       <c r="M134" s="4" t="n">
-        <v>29.91</v>
+        <v>29.6</v>
       </c>
       <c r="N134" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O134" s="4" t="n">
-        <v>38.37</v>
+        <v>38.06</v>
       </c>
       <c r="P134" s="4" t="n">
         <v>0</v>
@@ -14592,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>69.19</v>
+        <v>69.03</v>
       </c>
       <c r="AC134" s="4" t="n">
-        <v>30.81</v>
+        <v>30.97</v>
       </c>
       <c r="AD134" s="4" t="n">
         <v>0</v>
@@ -14624,12 +14614,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Barbie Harden Hall</t>
+          <t>James Pericola</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Carey Baker</t>
+          <t>Joe Strada</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -14639,13 +14629,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>-7.86</v>
+        <v>-6.46</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>9.9</v>
+        <v>14.2</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>90.09999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -14653,34 +14643,40 @@
         </is>
       </c>
       <c r="M135" s="4" t="n">
-        <v>-11.34</v>
+        <v>-11.66</v>
       </c>
       <c r="N135" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O135" s="4" t="n">
-        <v>-7.86</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="P135" s="4" t="n">
-        <v>-1.23</v>
+        <v>-2.59</v>
       </c>
       <c r="Q135" s="4" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="R135" s="4" t="n">
         <v>-15.84</v>
       </c>
-      <c r="S135" s="4" t="n"/>
-      <c r="T135" s="4" t="n"/>
+      <c r="S135" s="4" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="T135" s="4" t="n">
+        <v>42.1</v>
+      </c>
       <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V135" s="4" t="n">
+        <v>-3.3</v>
+      </c>
       <c r="W135" s="5" t="n">
-        <v>23989</v>
+        <v>119754</v>
       </c>
       <c r="X135" s="5" t="n">
-        <v>303575</v>
+        <v>5248640</v>
       </c>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" s="4" t="n">
@@ -14690,10 +14686,10 @@
         <v>0</v>
       </c>
       <c r="AB135" s="4" t="n">
-        <v>46.07</v>
+        <v>46.77</v>
       </c>
       <c r="AC135" s="4" t="n">
-        <v>53.93</v>
+        <v>53.23</v>
       </c>
       <c r="AD135" s="4" t="n">
         <v>0</v>
@@ -14722,7 +14718,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Christopher Irizarry</t>
+          <t>Kimberly Overman</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14741,13 +14737,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>-10.53</v>
+        <v>-12.3</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -14755,16 +14751,16 @@
         </is>
       </c>
       <c r="M136" s="4" t="n">
-        <v>-9.85</v>
+        <v>-10.16</v>
       </c>
       <c r="N136" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>-10.53</v>
+        <v>-12.3</v>
       </c>
       <c r="P136" s="4" t="n">
-        <v>0</v>
+        <v>-1.45</v>
       </c>
       <c r="Q136" s="4" t="n">
         <v>-6.47</v>
@@ -14779,7 +14775,7 @@
       </c>
       <c r="V136" s="4" t="n"/>
       <c r="W136" s="5" t="n">
-        <v>0</v>
+        <v>186813</v>
       </c>
       <c r="X136" s="5" t="n">
         <v>1588538</v>
@@ -14792,10 +14788,10 @@
         <v>0</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>44.73</v>
+        <v>43.85</v>
       </c>
       <c r="AC136" s="4" t="n">
-        <v>55.27</v>
+        <v>56.15</v>
       </c>
       <c r="AD136" s="4" t="n">
         <v>0</v>
@@ -14843,13 +14839,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>-5.28</v>
+        <v>-5.44</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>18.2</v>
+        <v>17.6</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>81.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -14857,13 +14853,13 @@
         </is>
       </c>
       <c r="M137" s="4" t="n">
-        <v>-9</v>
+        <v>-9.32</v>
       </c>
       <c r="N137" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O137" s="4" t="n">
-        <v>-5.12</v>
+        <v>-5.43</v>
       </c>
       <c r="P137" s="4" t="n">
         <v>-0.71</v>
@@ -14900,10 +14896,10 @@
         <v>0</v>
       </c>
       <c r="AB137" s="4" t="n">
-        <v>47.36</v>
+        <v>47.28</v>
       </c>
       <c r="AC137" s="4" t="n">
-        <v>52.64</v>
+        <v>52.72</v>
       </c>
       <c r="AD137" s="4" t="n">
         <v>0</v>
@@ -14937,7 +14933,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>John Peters</t>
+          <t>Mike Beltran</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -14951,13 +14947,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>7.42</v>
+        <v>6.53</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>88.8</v>
+        <v>86</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>11.2</v>
+        <v>14</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -14965,16 +14961,16 @@
         </is>
       </c>
       <c r="M138" s="4" t="n">
-        <v>-5.71</v>
+        <v>-6.03</v>
       </c>
       <c r="N138" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O138" s="4" t="n">
-        <v>7.42</v>
+        <v>5.5</v>
       </c>
       <c r="P138" s="4" t="n">
-        <v>1.69</v>
+        <v>0.08</v>
       </c>
       <c r="Q138" s="4" t="n">
         <v>5.55</v>
@@ -14982,17 +14978,23 @@
       <c r="R138" s="4" t="n">
         <v>-10.62</v>
       </c>
-      <c r="S138" s="4" t="n"/>
-      <c r="T138" s="4" t="n"/>
+      <c r="S138" s="4" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="T138" s="4" t="n">
+        <v>37.5</v>
+      </c>
       <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V138" s="4" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="W138" s="5" t="n">
         <v>2337125</v>
       </c>
       <c r="X138" s="5" t="n">
-        <v>200797</v>
+        <v>2116747</v>
       </c>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" s="4" t="n">
@@ -15002,10 +15004,10 @@
         <v>0</v>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>53.71</v>
+        <v>53.27</v>
       </c>
       <c r="AC138" s="4" t="n">
-        <v>46.29</v>
+        <v>46.73</v>
       </c>
       <c r="AD138" s="4" t="n">
         <v>0</v>
@@ -15034,7 +15036,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Darren McAuley</t>
+          <t>Robert People</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15053,13 +15055,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>-12.89</v>
+        <v>-15.66</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>99</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -15067,16 +15069,16 @@
         </is>
       </c>
       <c r="M139" s="4" t="n">
-        <v>-14.53</v>
+        <v>-14.84</v>
       </c>
       <c r="N139" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O139" s="4" t="n">
-        <v>-12.89</v>
+        <v>-15.66</v>
       </c>
       <c r="P139" s="4" t="n">
-        <v>0</v>
+        <v>-2.46</v>
       </c>
       <c r="Q139" s="4" t="n">
         <v>-3.69</v>
@@ -15091,7 +15093,7 @@
       </c>
       <c r="V139" s="4" t="n"/>
       <c r="W139" s="5" t="n">
-        <v>0</v>
+        <v>40108</v>
       </c>
       <c r="X139" s="5" t="n">
         <v>2346664</v>
@@ -15104,10 +15106,10 @@
         <v>0</v>
       </c>
       <c r="AB139" s="4" t="n">
-        <v>43.56</v>
+        <v>42.17</v>
       </c>
       <c r="AC139" s="4" t="n">
-        <v>56.44</v>
+        <v>57.83</v>
       </c>
       <c r="AD139" s="4" t="n">
         <v>0</v>
@@ -15151,13 +15153,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>-4.57</v>
+        <v>-4.89</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>79.3</v>
+        <v>80.5</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -15165,13 +15167,13 @@
         </is>
       </c>
       <c r="M140" s="4" t="n">
-        <v>-8.58</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="N140" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O140" s="4" t="n">
-        <v>-4.57</v>
+        <v>-4.89</v>
       </c>
       <c r="P140" s="4" t="n">
         <v>-1.19</v>
@@ -15202,10 +15204,10 @@
         <v>0</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>47.71</v>
+        <v>47.56</v>
       </c>
       <c r="AC140" s="4" t="n">
-        <v>52.29</v>
+        <v>52.44</v>
       </c>
       <c r="AD140" s="4" t="n">
         <v>0</v>
@@ -15253,7 +15255,7 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>-18.16</v>
+        <v>-18.48</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>0.3</v>
@@ -15267,13 +15269,13 @@
         </is>
       </c>
       <c r="M141" s="4" t="n">
-        <v>-17.09</v>
+        <v>-17.41</v>
       </c>
       <c r="N141" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O141" s="4" t="n">
-        <v>-18.16</v>
+        <v>-18.48</v>
       </c>
       <c r="P141" s="4" t="n">
         <v>-1.69</v>
@@ -15304,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="AB141" s="4" t="n">
-        <v>40.92</v>
+        <v>40.76</v>
       </c>
       <c r="AC141" s="4" t="n">
-        <v>59.08</v>
+        <v>59.24</v>
       </c>
       <c r="AD141" s="4" t="n">
         <v>0</v>
@@ -15336,7 +15338,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Tiffanie Luong</t>
+          <t>Curtis Gibson</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -15355,30 +15357,30 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>-8.94</v>
+        <v>-11.26</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>93.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="M142" s="4" t="n">
-        <v>-12.15</v>
+        <v>-12.46</v>
       </c>
       <c r="N142" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O142" s="4" t="n">
-        <v>-8.94</v>
+        <v>-11.26</v>
       </c>
       <c r="P142" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q142" s="4" t="n">
         <v>-2.65</v>
@@ -15393,7 +15395,7 @@
       </c>
       <c r="V142" s="4" t="n"/>
       <c r="W142" s="5" t="n">
-        <v>0</v>
+        <v>12208</v>
       </c>
       <c r="X142" s="5" t="n">
         <v>850000</v>
@@ -15406,10 +15408,10 @@
         <v>0</v>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>45.53</v>
+        <v>44.37</v>
       </c>
       <c r="AC142" s="4" t="n">
-        <v>54.47</v>
+        <v>55.63</v>
       </c>
       <c r="AD142" s="4" t="n">
         <v>0</v>
@@ -15438,12 +15440,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Howard Sapp</t>
+          <t>Victor Arias</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Madison Cawthorn</t>
+          <t>Jim Schwartzel</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -15453,13 +15455,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>-21.56</v>
+        <v>-22.46</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -15467,16 +15469,16 @@
         </is>
       </c>
       <c r="M143" s="4" t="n">
-        <v>-25.33</v>
+        <v>-25.65</v>
       </c>
       <c r="N143" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O143" s="4" t="n">
-        <v>-21.56</v>
+        <v>-22.46</v>
       </c>
       <c r="P143" s="4" t="n">
-        <v>-1.64</v>
+        <v>-2.23</v>
       </c>
       <c r="Q143" s="4" t="n">
         <v>0</v>
@@ -15491,10 +15493,10 @@
       </c>
       <c r="V143" s="4" t="n"/>
       <c r="W143" s="5" t="n">
-        <v>53596</v>
+        <v>45356</v>
       </c>
       <c r="X143" s="5" t="n">
-        <v>874630</v>
+        <v>2065485</v>
       </c>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" s="4" t="n">
@@ -15504,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>39.22</v>
+        <v>38.77</v>
       </c>
       <c r="AC143" s="4" t="n">
-        <v>60.78</v>
+        <v>61.23</v>
       </c>
       <c r="AD143" s="4" t="n">
         <v>0</v>
@@ -15536,22 +15538,26 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Elijah Manley</t>
+          <t>Debbie Wasserman Schultz</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rodenay Joseph</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr"/>
+          <t>Brent Andersen</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>DEM</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>51.5</v>
+        <v>53.76</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>100</v>
@@ -15565,19 +15571,19 @@
         </is>
       </c>
       <c r="M144" s="4" t="n">
-        <v>43.77</v>
+        <v>43.46</v>
       </c>
       <c r="N144" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O144" s="4" t="n">
-        <v>51.5</v>
+        <v>53.76</v>
       </c>
       <c r="P144" s="4" t="n">
-        <v>1.52</v>
+        <v>2.43</v>
       </c>
       <c r="Q144" s="4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R144" s="4" t="n">
         <v>37.5</v>
@@ -15589,10 +15595,10 @@
       </c>
       <c r="V144" s="4" t="n"/>
       <c r="W144" s="5" t="n">
-        <v>1068384</v>
+        <v>3300107</v>
       </c>
       <c r="X144" s="5" t="n">
-        <v>98825</v>
+        <v>63849</v>
       </c>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" s="4" t="n">
@@ -15602,10 +15608,10 @@
         <v>0</v>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>75.75</v>
+        <v>76.88</v>
       </c>
       <c r="AC144" s="4" t="n">
-        <v>24.25</v>
+        <v>23.12</v>
       </c>
       <c r="AD144" s="4" t="n">
         <v>0</v>
@@ -15634,7 +15640,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Adam Aarons</t>
+          <t>James Martin</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -15653,13 +15659,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>-12.54</v>
+        <v>-14.31</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -15667,16 +15673,16 @@
         </is>
       </c>
       <c r="M145" s="4" t="n">
-        <v>-11.39</v>
+        <v>-11.71</v>
       </c>
       <c r="N145" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O145" s="4" t="n">
-        <v>-12.54</v>
+        <v>-14.31</v>
       </c>
       <c r="P145" s="4" t="n">
-        <v>0</v>
+        <v>-1.45</v>
       </c>
       <c r="Q145" s="4" t="n">
         <v>-6.47</v>
@@ -15691,7 +15697,7 @@
       </c>
       <c r="V145" s="4" t="n"/>
       <c r="W145" s="5" t="n">
-        <v>0</v>
+        <v>579319</v>
       </c>
       <c r="X145" s="5" t="n">
         <v>4308890</v>
@@ -15704,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AB145" s="4" t="n">
-        <v>43.73</v>
+        <v>42.85</v>
       </c>
       <c r="AC145" s="4" t="n">
-        <v>56.27</v>
+        <v>57.15</v>
       </c>
       <c r="AD145" s="4" t="n">
         <v>0</v>
@@ -15741,7 +15747,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Michael Carbonara</t>
+          <t>Casey Askar</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -15751,13 +15757,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>62</v>
+        <v>63.4</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>38</v>
+        <v>36.6</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -15765,16 +15771,16 @@
         </is>
       </c>
       <c r="M146" s="4" t="n">
-        <v>-3.74</v>
+        <v>-4.06</v>
       </c>
       <c r="N146" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O146" s="4" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="P146" s="4" t="n">
-        <v>-0.75</v>
+        <v>-0.01</v>
       </c>
       <c r="Q146" s="4" t="n">
         <v>0</v>
@@ -15798,7 +15804,7 @@
         <v>2284052</v>
       </c>
       <c r="X146" s="5" t="n">
-        <v>6332573</v>
+        <v>2567760</v>
       </c>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" s="4" t="n">
@@ -15808,10 +15814,10 @@
         <v>0</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>50.04</v>
+        <v>50.21</v>
       </c>
       <c r="AC146" s="4" t="n">
-        <v>49.96</v>
+        <v>49.79</v>
       </c>
       <c r="AD146" s="4" t="n">
         <v>0</v>
@@ -15845,7 +15851,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Raven Harrison</t>
+          <t>Deborah Adeimy</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -15859,7 +15865,7 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>30.13</v>
+        <v>31.62</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>100</v>
@@ -15873,16 +15879,16 @@
         </is>
       </c>
       <c r="M147" s="4" t="n">
-        <v>20.67</v>
+        <v>20.35</v>
       </c>
       <c r="N147" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O147" s="4" t="n">
-        <v>30.13</v>
+        <v>31.62</v>
       </c>
       <c r="P147" s="4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q147" s="4" t="n">
         <v>3.42</v>
@@ -15900,7 +15906,7 @@
         <v>2276254</v>
       </c>
       <c r="X147" s="5" t="n">
-        <v>0</v>
+        <v>162515</v>
       </c>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" s="4" t="n">
@@ -15910,10 +15916,10 @@
         <v>0</v>
       </c>
       <c r="AB147" s="4" t="n">
-        <v>65.06</v>
+        <v>65.81</v>
       </c>
       <c r="AC147" s="4" t="n">
-        <v>34.94</v>
+        <v>34.19</v>
       </c>
       <c r="AD147" s="4" t="n">
         <v>0</v>
@@ -15942,12 +15948,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Shevrin Jones</t>
+          <t>Oliver Gilbert</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Patricia Gonzalez</t>
+          <t>Te Brown</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -15957,7 +15963,7 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>56.24</v>
+        <v>54.65</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>100</v>
@@ -15971,16 +15977,16 @@
         </is>
       </c>
       <c r="M148" s="4" t="n">
-        <v>47.78</v>
+        <v>47.47</v>
       </c>
       <c r="N148" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O148" s="4" t="n">
-        <v>56.24</v>
+        <v>54.65</v>
       </c>
       <c r="P148" s="4" t="n">
-        <v>1.29</v>
+        <v>0.02</v>
       </c>
       <c r="Q148" s="4" t="n">
         <v>0</v>
@@ -15995,10 +16001,10 @@
       </c>
       <c r="V148" s="4" t="n"/>
       <c r="W148" s="5" t="n">
-        <v>283695</v>
+        <v>812143</v>
       </c>
       <c r="X148" s="5" t="n">
-        <v>1333</v>
+        <v>313318</v>
       </c>
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" s="4" t="n">
@@ -16008,10 +16014,10 @@
         <v>0</v>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>78.12</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="AC148" s="4" t="n">
-        <v>21.88</v>
+        <v>22.68</v>
       </c>
       <c r="AD148" s="4" t="n">
         <v>0</v>
@@ -16059,13 +16065,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>7.12</v>
+        <v>6.87</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -16073,13 +16079,13 @@
         </is>
       </c>
       <c r="M149" s="4" t="n">
-        <v>-1.94</v>
+        <v>-2.25</v>
       </c>
       <c r="N149" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O149" s="4" t="n">
-        <v>6.84</v>
+        <v>6.53</v>
       </c>
       <c r="P149" s="4" t="n">
         <v>0.15</v>
@@ -16116,10 +16122,10 @@
         <v>0</v>
       </c>
       <c r="AB149" s="4" t="n">
-        <v>53.56</v>
+        <v>53.44</v>
       </c>
       <c r="AC149" s="4" t="n">
-        <v>46.44</v>
+        <v>46.56</v>
       </c>
       <c r="AD149" s="4" t="n">
         <v>0</v>
@@ -16148,7 +16154,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Yurina Gil</t>
+          <t>Nicole Locklin</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -16167,13 +16173,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>-11.46</v>
+        <v>-10.65</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>98.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -16181,16 +16187,16 @@
         </is>
       </c>
       <c r="M150" s="4" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.67</v>
       </c>
       <c r="N150" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O150" s="4" t="n">
-        <v>-11.46</v>
+        <v>-10.65</v>
       </c>
       <c r="P150" s="4" t="n">
-        <v>-2.38</v>
+        <v>-1.25</v>
       </c>
       <c r="Q150" s="4" t="n">
         <v>-8.17</v>
@@ -16205,7 +16211,7 @@
       </c>
       <c r="V150" s="4" t="n"/>
       <c r="W150" s="5" t="n">
-        <v>38588</v>
+        <v>347681</v>
       </c>
       <c r="X150" s="5" t="n">
         <v>2060782</v>
@@ -16218,10 +16224,10 @@
         <v>0</v>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>44.27</v>
+        <v>44.67</v>
       </c>
       <c r="AC150" s="4" t="n">
-        <v>55.73</v>
+        <v>55.33</v>
       </c>
       <c r="AD150" s="4" t="n">
         <v>0</v>
@@ -16250,7 +16256,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Richard Lamondin</t>
+          <t>Eliott Rodriguez</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -16269,13 +16275,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>-6.68</v>
+        <v>-5.82</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>13.5</v>
+        <v>16.3</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>86.5</v>
+        <v>83.7</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -16283,16 +16289,16 @@
         </is>
       </c>
       <c r="M151" s="4" t="n">
-        <v>-6.52</v>
+        <v>-6.83</v>
       </c>
       <c r="N151" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O151" s="4" t="n">
-        <v>-5.92</v>
+        <v>-6.31</v>
       </c>
       <c r="P151" s="4" t="n">
-        <v>-0.71</v>
+        <v>-0.79</v>
       </c>
       <c r="Q151" s="4" t="n">
         <v>-7.1</v>
@@ -16301,19 +16307,19 @@
         <v>-14.7</v>
       </c>
       <c r="S151" s="4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="T151" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U151" t="n">
         <v>1</v>
       </c>
       <c r="V151" s="4" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="W151" s="5" t="n">
-        <v>743712</v>
+        <v>661173</v>
       </c>
       <c r="X151" s="5" t="n">
         <v>1999399</v>
@@ -16326,10 +16332,10 @@
         <v>0</v>
       </c>
       <c r="AB151" s="4" t="n">
-        <v>46.66</v>
+        <v>47.09</v>
       </c>
       <c r="AC151" s="4" t="n">
-        <v>53.34</v>
+        <v>52.91</v>
       </c>
       <c r="AD151" s="4" t="n">
         <v>0</v>
@@ -16377,7 +16383,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>-13.98</v>
+        <v>-14.25</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>0.8</v>
@@ -16391,13 +16397,13 @@
         </is>
       </c>
       <c r="M152" s="4" t="n">
-        <v>-16</v>
+        <v>-16.32</v>
       </c>
       <c r="N152" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O152" s="4" t="n">
-        <v>-15.75</v>
+        <v>-16.06</v>
       </c>
       <c r="P152" s="4" t="n">
         <v>-0.22</v>
@@ -16434,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="AB152" s="4" t="n">
-        <v>43.01</v>
+        <v>42.87</v>
       </c>
       <c r="AC152" s="4" t="n">
-        <v>56.99</v>
+        <v>57.13</v>
       </c>
       <c r="AD152" s="4" t="n">
         <v>0</v>
@@ -16634,10 +16640,10 @@
         <v>0</v>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>62.27</v>
+        <v>62.26</v>
       </c>
       <c r="AC154" s="4" t="n">
-        <v>37.73</v>
+        <v>37.74</v>
       </c>
       <c r="AD154" s="4" t="n">
         <v>0</v>
@@ -16699,7 +16705,7 @@
         </is>
       </c>
       <c r="M155" s="4" t="n">
-        <v>-26.39</v>
+        <v>-26.4</v>
       </c>
       <c r="N155" s="4" t="n">
         <v>5.38</v>
@@ -16801,7 +16807,7 @@
         </is>
       </c>
       <c r="M156" s="4" t="n">
-        <v>58.37</v>
+        <v>58.36</v>
       </c>
       <c r="N156" s="4" t="n">
         <v>5.38</v>
@@ -16838,10 +16844,10 @@
         <v>0</v>
       </c>
       <c r="AB156" s="4" t="n">
-        <v>82.81999999999999</v>
+        <v>82.81</v>
       </c>
       <c r="AC156" s="4" t="n">
-        <v>17.18</v>
+        <v>17.19</v>
       </c>
       <c r="AD156" s="4" t="n">
         <v>0</v>
@@ -17005,7 +17011,7 @@
         </is>
       </c>
       <c r="M158" s="4" t="n">
-        <v>53.9</v>
+        <v>53.89</v>
       </c>
       <c r="N158" s="4" t="n">
         <v>5.38</v>
@@ -17093,7 +17099,7 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>-19.64</v>
+        <v>-19.65</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>0.2</v>
@@ -17107,13 +17113,13 @@
         </is>
       </c>
       <c r="M159" s="4" t="n">
-        <v>-18.37</v>
+        <v>-18.38</v>
       </c>
       <c r="N159" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O159" s="4" t="n">
-        <v>-19.64</v>
+        <v>-19.65</v>
       </c>
       <c r="P159" s="4" t="n">
         <v>0</v>
@@ -17297,7 +17303,7 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>-29.79</v>
+        <v>-29.8</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>0</v>
@@ -17317,7 +17323,7 @@
         <v>5.38</v>
       </c>
       <c r="O161" s="4" t="n">
-        <v>-29.79</v>
+        <v>-29.8</v>
       </c>
       <c r="P161" s="4" t="n">
         <v>-0.9</v>
@@ -17395,7 +17401,7 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>-15.96</v>
+        <v>-15.97</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>0.6</v>
@@ -17415,7 +17421,7 @@
         <v>5.38</v>
       </c>
       <c r="O162" s="4" t="n">
-        <v>-15.96</v>
+        <v>-15.97</v>
       </c>
       <c r="P162" s="4" t="n">
         <v>-2.86</v>
@@ -17609,7 +17615,7 @@
         </is>
       </c>
       <c r="M164" s="4" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="N164" s="4" t="n">
         <v>5.38</v>
@@ -17809,7 +17815,7 @@
         </is>
       </c>
       <c r="M166" s="4" t="n">
-        <v>-33.81</v>
+        <v>-33.82</v>
       </c>
       <c r="N166" s="4" t="n">
         <v>5.38</v>
@@ -17846,10 +17852,10 @@
         <v>0</v>
       </c>
       <c r="AB166" s="4" t="n">
-        <v>39.28</v>
+        <v>39.27</v>
       </c>
       <c r="AC166" s="4" t="n">
-        <v>60.72</v>
+        <v>60.73</v>
       </c>
       <c r="AD166" s="4" t="n">
         <v>0</v>
@@ -18101,7 +18107,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11.63</v>
+        <v>11.65</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>98.8</v>
@@ -18121,7 +18127,7 @@
         <v>5.38</v>
       </c>
       <c r="O169" s="4" t="n">
-        <v>13.78</v>
+        <v>13.77</v>
       </c>
       <c r="P169" s="4" t="n">
         <v>0</v>
@@ -18205,7 +18211,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>66.7</v>
@@ -18262,10 +18268,10 @@
         <v>0</v>
       </c>
       <c r="AB170" s="4" t="n">
-        <v>50.62</v>
+        <v>50.63</v>
       </c>
       <c r="AC170" s="4" t="n">
-        <v>49.38</v>
+        <v>49.37</v>
       </c>
       <c r="AD170" s="4" t="n">
         <v>0</v>
@@ -18333,7 +18339,7 @@
         <v>5.38</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>6.37</v>
+        <v>6.36</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.06</v>
@@ -18417,7 +18423,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-20.8</v>
+        <v>-20.81</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.2</v>
@@ -18437,7 +18443,7 @@
         <v>5.38</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-20.8</v>
+        <v>-20.81</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -18519,7 +18525,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-26.13</v>
+        <v>-26.34</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18533,13 +18539,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-41.33</v>
+        <v>-41.37</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-38.64</v>
+        <v>-38.69</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18576,10 +18582,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>36.93</v>
+        <v>36.83</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>63.07</v>
+        <v>63.17</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18627,7 +18633,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-25.28</v>
+        <v>-25.33</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0.1</v>
@@ -18641,13 +18647,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-23.51</v>
+        <v>-23.56</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-25.28</v>
+        <v>-25.33</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -18678,10 +18684,10 @@
         <v>0</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>37.36</v>
+        <v>37.34</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>62.64</v>
+        <v>62.66</v>
       </c>
       <c r="AD174" s="4" t="n">
         <v>0</v>
@@ -19027,7 +19033,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>33.44</v>
+        <v>33.66</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>100</v>
@@ -19084,10 +19090,10 @@
         <v>0</v>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>66.72</v>
+        <v>66.83</v>
       </c>
       <c r="AC178" s="4" t="n">
-        <v>33.28</v>
+        <v>33.17</v>
       </c>
       <c r="AD178" s="4" t="n">
         <v>0</v>
@@ -20857,7 +20863,7 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-11.69</v>
+        <v>-11.75</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>1.2</v>
@@ -20914,10 +20920,10 @@
         <v>0</v>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>44.16</v>
+        <v>44.13</v>
       </c>
       <c r="AC196" s="4" t="n">
-        <v>55.84</v>
+        <v>55.87</v>
       </c>
       <c r="AD196" s="4" t="n">
         <v>0</v>
@@ -21489,7 +21495,7 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-16.98</v>
+        <v>-16.99</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>5.38</v>
@@ -22283,13 +22289,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-6.97</v>
+        <v>-6.99</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -22340,10 +22346,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.52</v>
+        <v>46.5</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.48</v>
+        <v>53.5</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -22995,7 +23001,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>23.98</v>
+        <v>23.99</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23009,13 +23015,13 @@
         </is>
       </c>
       <c r="M217" s="4" t="n">
-        <v>17.05</v>
+        <v>17.07</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>23.98</v>
+        <v>23.99</v>
       </c>
       <c r="P217" s="4" t="n">
         <v>0</v>
@@ -23046,10 +23052,10 @@
         <v>0</v>
       </c>
       <c r="AB217" s="4" t="n">
-        <v>61.99</v>
+        <v>62</v>
       </c>
       <c r="AC217" s="4" t="n">
-        <v>38.01</v>
+        <v>38</v>
       </c>
       <c r="AD217" s="4" t="n">
         <v>0</v>
@@ -23097,7 +23103,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>33.6</v>
+        <v>33.61</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -23111,13 +23117,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>27</v>
+        <v>27.02</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>33.6</v>
+        <v>33.61</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -23148,10 +23154,10 @@
         <v>0</v>
       </c>
       <c r="AB218" s="4" t="n">
-        <v>66.8</v>
+        <v>66.81</v>
       </c>
       <c r="AC218" s="4" t="n">
-        <v>33.2</v>
+        <v>33.19</v>
       </c>
       <c r="AD218" s="4" t="n">
         <v>0</v>
@@ -23199,7 +23205,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>32.15</v>
+        <v>32.17</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>100</v>
@@ -23213,13 +23219,13 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>22.51</v>
+        <v>22.52</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>32.15</v>
+        <v>32.17</v>
       </c>
       <c r="P219" s="4" t="n">
         <v>2.52</v>
@@ -23301,7 +23307,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>29.65</v>
+        <v>29.67</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>100</v>
@@ -23315,13 +23321,13 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.33</v>
+        <v>23.34</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O220" s="4" t="n">
-        <v>29.65</v>
+        <v>29.67</v>
       </c>
       <c r="P220" s="4" t="n">
         <v>0</v>
@@ -23403,7 +23409,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>55.27</v>
+        <v>55.29</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>100</v>
@@ -23417,13 +23423,13 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>48.69</v>
+        <v>48.7</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O221" s="4" t="n">
-        <v>55.27</v>
+        <v>55.29</v>
       </c>
       <c r="P221" s="4" t="n">
         <v>0</v>
@@ -23501,7 +23507,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>28.41</v>
+        <v>28.43</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>100</v>
@@ -23515,13 +23521,13 @@
         </is>
       </c>
       <c r="M222" s="4" t="n">
-        <v>23.53</v>
+        <v>23.55</v>
       </c>
       <c r="N222" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O222" s="4" t="n">
-        <v>28.41</v>
+        <v>28.43</v>
       </c>
       <c r="P222" s="4" t="n">
         <v>0</v>
@@ -23603,7 +23609,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>76.06999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -23617,13 +23623,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>68.7</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>76.06999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -23654,10 +23660,10 @@
         <v>0</v>
       </c>
       <c r="AB223" s="4" t="n">
-        <v>88.03</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="AC223" s="4" t="n">
-        <v>11.97</v>
+        <v>11.96</v>
       </c>
       <c r="AD223" s="4" t="n">
         <v>0</v>
@@ -23705,7 +23711,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>45.38</v>
+        <v>45.4</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>100</v>
@@ -23719,13 +23725,13 @@
         </is>
       </c>
       <c r="M224" s="4" t="n">
-        <v>30.1</v>
+        <v>30.11</v>
       </c>
       <c r="N224" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O224" s="4" t="n">
-        <v>45.38</v>
+        <v>45.4</v>
       </c>
       <c r="P224" s="4" t="n">
         <v>0</v>
@@ -23756,10 +23762,10 @@
         <v>0</v>
       </c>
       <c r="AB224" s="4" t="n">
-        <v>72.69</v>
+        <v>72.7</v>
       </c>
       <c r="AC224" s="4" t="n">
-        <v>27.31</v>
+        <v>27.3</v>
       </c>
       <c r="AD224" s="4" t="n">
         <v>0</v>
@@ -23807,7 +23813,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23821,13 +23827,13 @@
         </is>
       </c>
       <c r="M225" s="4" t="n">
-        <v>13.57</v>
+        <v>13.59</v>
       </c>
       <c r="N225" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.53</v>
@@ -23858,10 +23864,10 @@
         <v>0</v>
       </c>
       <c r="AB225" s="4" t="n">
-        <v>61.21</v>
+        <v>61.22</v>
       </c>
       <c r="AC225" s="4" t="n">
-        <v>38.79</v>
+        <v>38.78</v>
       </c>
       <c r="AD225" s="4" t="n">
         <v>0</v>
@@ -23909,7 +23915,7 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>-15.81</v>
+        <v>-15.8</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>0.6</v>
@@ -23923,13 +23929,13 @@
         </is>
       </c>
       <c r="M226" s="4" t="n">
-        <v>-16.15</v>
+        <v>-16.13</v>
       </c>
       <c r="N226" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O226" s="4" t="n">
-        <v>-15.81</v>
+        <v>-15.8</v>
       </c>
       <c r="P226" s="4" t="n">
         <v>-0.86</v>
@@ -23960,10 +23966,10 @@
         <v>0</v>
       </c>
       <c r="AB226" s="4" t="n">
-        <v>42.09</v>
+        <v>42.1</v>
       </c>
       <c r="AC226" s="4" t="n">
-        <v>57.91</v>
+        <v>57.9</v>
       </c>
       <c r="AD226" s="4" t="n">
         <v>0</v>
@@ -24011,7 +24017,7 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>31.3</v>
+        <v>31.32</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>100</v>
@@ -24025,13 +24031,13 @@
         </is>
       </c>
       <c r="M227" s="4" t="n">
-        <v>20.08</v>
+        <v>20.1</v>
       </c>
       <c r="N227" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O227" s="4" t="n">
-        <v>31.3</v>
+        <v>31.32</v>
       </c>
       <c r="P227" s="4" t="n">
         <v>2.06</v>
@@ -24062,10 +24068,10 @@
         <v>0</v>
       </c>
       <c r="AB227" s="4" t="n">
-        <v>65.65000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="AC227" s="4" t="n">
-        <v>34.35</v>
+        <v>34.34</v>
       </c>
       <c r="AD227" s="4" t="n">
         <v>0</v>
@@ -24113,7 +24119,7 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>32.85</v>
+        <v>32.87</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>100</v>
@@ -24127,13 +24133,13 @@
         </is>
       </c>
       <c r="M228" s="4" t="n">
-        <v>25.3</v>
+        <v>25.31</v>
       </c>
       <c r="N228" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O228" s="4" t="n">
-        <v>32.85</v>
+        <v>32.87</v>
       </c>
       <c r="P228" s="4" t="n">
         <v>0</v>
@@ -24164,10 +24170,10 @@
         <v>0</v>
       </c>
       <c r="AB228" s="4" t="n">
-        <v>66.43000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="AC228" s="4" t="n">
-        <v>33.57</v>
+        <v>33.56</v>
       </c>
       <c r="AD228" s="4" t="n">
         <v>0</v>
@@ -24211,7 +24217,7 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>85.09</v>
+        <v>85.11</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>100</v>
@@ -24225,13 +24231,13 @@
         </is>
       </c>
       <c r="M229" s="4" t="n">
-        <v>78.78</v>
+        <v>78.8</v>
       </c>
       <c r="N229" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O229" s="4" t="n">
-        <v>85.09</v>
+        <v>85.11</v>
       </c>
       <c r="P229" s="4" t="n">
         <v>0</v>
@@ -24262,10 +24268,10 @@
         <v>0</v>
       </c>
       <c r="AB229" s="4" t="n">
-        <v>92.54000000000001</v>
+        <v>92.55</v>
       </c>
       <c r="AC229" s="4" t="n">
-        <v>7.46</v>
+        <v>7.45</v>
       </c>
       <c r="AD229" s="4" t="n">
         <v>0</v>
@@ -24309,7 +24315,7 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>39.99</v>
+        <v>40.01</v>
       </c>
       <c r="J230" s="4" t="n">
         <v>100</v>
@@ -24323,13 +24329,13 @@
         </is>
       </c>
       <c r="M230" s="4" t="n">
-        <v>35.19</v>
+        <v>35.21</v>
       </c>
       <c r="N230" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O230" s="4" t="n">
-        <v>39.99</v>
+        <v>40.01</v>
       </c>
       <c r="P230" s="4" t="n">
         <v>0</v>
@@ -24411,7 +24417,7 @@
         </is>
       </c>
       <c r="I231" s="4" t="n">
-        <v>19.32</v>
+        <v>19.34</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>99.7</v>
@@ -24425,13 +24431,13 @@
         </is>
       </c>
       <c r="M231" s="4" t="n">
-        <v>7.56</v>
+        <v>7.58</v>
       </c>
       <c r="N231" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O231" s="4" t="n">
-        <v>19.32</v>
+        <v>19.34</v>
       </c>
       <c r="P231" s="4" t="n">
         <v>2.47</v>
@@ -24462,10 +24468,10 @@
         <v>0</v>
       </c>
       <c r="AB231" s="4" t="n">
-        <v>59.66</v>
+        <v>59.67</v>
       </c>
       <c r="AC231" s="4" t="n">
-        <v>40.34</v>
+        <v>40.33</v>
       </c>
       <c r="AD231" s="4" t="n">
         <v>0</v>
@@ -24513,7 +24519,7 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>72.06</v>
+        <v>72.08</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>100</v>
@@ -24527,13 +24533,13 @@
         </is>
       </c>
       <c r="M232" s="4" t="n">
-        <v>62.66</v>
+        <v>62.68</v>
       </c>
       <c r="N232" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O232" s="4" t="n">
-        <v>72.06</v>
+        <v>72.08</v>
       </c>
       <c r="P232" s="4" t="n">
         <v>0</v>
@@ -24564,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="AB232" s="4" t="n">
-        <v>86.03</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="AC232" s="4" t="n">
-        <v>13.97</v>
+        <v>13.96</v>
       </c>
       <c r="AD232" s="4" t="n">
         <v>0</v>
@@ -24615,7 +24621,7 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>69.55</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="J233" s="4" t="n">
         <v>100</v>
@@ -24629,13 +24635,13 @@
         </is>
       </c>
       <c r="M233" s="4" t="n">
-        <v>60.51</v>
+        <v>60.53</v>
       </c>
       <c r="N233" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O233" s="4" t="n">
-        <v>69.55</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="P233" s="4" t="n">
         <v>3.54</v>
@@ -24666,10 +24672,10 @@
         <v>0</v>
       </c>
       <c r="AB233" s="4" t="n">
-        <v>84.77</v>
+        <v>84.78</v>
       </c>
       <c r="AC233" s="4" t="n">
-        <v>15.23</v>
+        <v>15.22</v>
       </c>
       <c r="AD233" s="4" t="n">
         <v>0</v>
@@ -24717,7 +24723,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.12</v>
+        <v>31.01</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24731,13 +24737,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>21.9</v>
+        <v>21.89</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.11</v>
+        <v>31.1</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24768,10 +24774,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.28</v>
+        <v>62.27</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.72</v>
+        <v>32.73</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24815,13 +24821,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.25</v>
+        <v>-3.97</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>37.1</v>
+        <v>36.2</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>62.9</v>
+        <v>63.8</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24835,7 +24841,7 @@
         <v>5.38</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.34</v>
+        <v>-5.35</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24923,7 +24929,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>-13.59</v>
+        <v>-13.34</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>0.9</v>
@@ -24937,13 +24943,13 @@
         </is>
       </c>
       <c r="M236" s="4" t="n">
-        <v>-18.33</v>
+        <v>-18.08</v>
       </c>
       <c r="N236" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O236" s="4" t="n">
-        <v>-13.59</v>
+        <v>-13.34</v>
       </c>
       <c r="P236" s="4" t="n">
         <v>-0.61</v>
@@ -24974,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AB236" s="4" t="n">
-        <v>43.21</v>
+        <v>43.33</v>
       </c>
       <c r="AC236" s="4" t="n">
-        <v>56.79</v>
+        <v>56.67</v>
       </c>
       <c r="AD236" s="4" t="n">
         <v>0</v>
@@ -25025,7 +25031,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>-28.53</v>
+        <v>-28.28</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>0</v>
@@ -25039,13 +25045,13 @@
         </is>
       </c>
       <c r="M237" s="4" t="n">
-        <v>-26.99</v>
+        <v>-26.74</v>
       </c>
       <c r="N237" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O237" s="4" t="n">
-        <v>-28.53</v>
+        <v>-28.28</v>
       </c>
       <c r="P237" s="4" t="n">
         <v>-1.9</v>
@@ -25076,10 +25082,10 @@
         <v>0</v>
       </c>
       <c r="AB237" s="4" t="n">
-        <v>35.74</v>
+        <v>35.86</v>
       </c>
       <c r="AC237" s="4" t="n">
-        <v>64.26000000000001</v>
+        <v>64.14</v>
       </c>
       <c r="AD237" s="4" t="n">
         <v>0</v>
@@ -25127,7 +25133,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>20.85</v>
+        <v>21.1</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25141,13 +25147,13 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>10.67</v>
+        <v>10.92</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>20.85</v>
+        <v>21.1</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>0.95</v>
@@ -25178,10 +25184,10 @@
         <v>0</v>
       </c>
       <c r="AB238" s="4" t="n">
-        <v>60.42</v>
+        <v>60.55</v>
       </c>
       <c r="AC238" s="4" t="n">
-        <v>39.58</v>
+        <v>39.45</v>
       </c>
       <c r="AD238" s="4" t="n">
         <v>0</v>
@@ -25229,13 +25235,13 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>-2.19</v>
+        <v>-2</v>
       </c>
       <c r="J239" s="4" t="n">
-        <v>29.6</v>
+        <v>30.4</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -25243,13 +25249,13 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-2.49</v>
+        <v>-2.24</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-2.85</v>
+        <v>-2.6</v>
       </c>
       <c r="P239" s="4" t="n">
         <v>-0.28</v>
@@ -25286,10 +25292,10 @@
         <v>0</v>
       </c>
       <c r="AB239" s="4" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="AC239" s="4" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="AD239" s="4" t="n">
         <v>0</v>
@@ -25337,7 +25343,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-26.31</v>
+        <v>-26.06</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0</v>
@@ -25351,13 +25357,13 @@
         </is>
       </c>
       <c r="M240" s="4" t="n">
-        <v>-23.7</v>
+        <v>-23.45</v>
       </c>
       <c r="N240" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-26.31</v>
+        <v>-26.06</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.12</v>
@@ -25388,10 +25394,10 @@
         <v>0</v>
       </c>
       <c r="AB240" s="4" t="n">
-        <v>36.84</v>
+        <v>36.97</v>
       </c>
       <c r="AC240" s="4" t="n">
-        <v>63.16</v>
+        <v>63.03</v>
       </c>
       <c r="AD240" s="4" t="n">
         <v>0</v>
@@ -25439,7 +25445,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>37.85</v>
+        <v>38.1</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -25453,13 +25459,13 @@
         </is>
       </c>
       <c r="M241" s="4" t="n">
-        <v>27.49</v>
+        <v>27.73</v>
       </c>
       <c r="N241" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>37.85</v>
+        <v>38.1</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -25490,10 +25496,10 @@
         <v>0</v>
       </c>
       <c r="AB241" s="4" t="n">
-        <v>68.92</v>
+        <v>69.05</v>
       </c>
       <c r="AC241" s="4" t="n">
-        <v>31.08</v>
+        <v>30.95</v>
       </c>
       <c r="AD241" s="4" t="n">
         <v>0</v>
@@ -25541,13 +25547,13 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>34.1</v>
+        <v>33.3</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -25555,13 +25561,13 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O242" s="4" t="n">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="P242" s="4" t="n">
         <v>-1.12</v>
@@ -25598,10 +25604,10 @@
         <v>0</v>
       </c>
       <c r="AB242" s="4" t="n">
-        <v>50.53</v>
+        <v>50.63</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.47</v>
+        <v>49.37</v>
       </c>
       <c r="AD242" s="4" t="n">
         <v>0</v>
@@ -25649,7 +25655,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>19.87</v>
+        <v>20.12</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>99.8</v>
@@ -25663,13 +25669,13 @@
         </is>
       </c>
       <c r="M243" s="4" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="N243" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>19.87</v>
+        <v>20.12</v>
       </c>
       <c r="P243" s="4" t="n">
         <v>3.13</v>
@@ -25700,10 +25706,10 @@
         <v>0</v>
       </c>
       <c r="AB243" s="4" t="n">
-        <v>59.93</v>
+        <v>60.06</v>
       </c>
       <c r="AC243" s="4" t="n">
-        <v>40.07</v>
+        <v>39.94</v>
       </c>
       <c r="AD243" s="4" t="n">
         <v>0</v>
@@ -25751,7 +25757,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-33.32</v>
+        <v>-33.07</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -25765,13 +25771,13 @@
         </is>
       </c>
       <c r="M244" s="4" t="n">
-        <v>-29.23</v>
+        <v>-28.98</v>
       </c>
       <c r="N244" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-33.32</v>
+        <v>-33.07</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -25802,10 +25808,10 @@
         <v>0</v>
       </c>
       <c r="AB244" s="4" t="n">
-        <v>33.34</v>
+        <v>33.46</v>
       </c>
       <c r="AC244" s="4" t="n">
-        <v>66.66</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="AD244" s="4" t="n">
         <v>0</v>
@@ -25849,13 +25855,13 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="J245" s="4" t="n">
-        <v>68.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K245" s="4" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -25863,13 +25869,13 @@
         </is>
       </c>
       <c r="M245" s="4" t="n">
-        <v>-2.43</v>
+        <v>-2.19</v>
       </c>
       <c r="N245" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O245" s="4" t="n">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="P245" s="4" t="n">
         <v>-0.08</v>
@@ -25906,10 +25912,10 @@
         <v>0</v>
       </c>
       <c r="AB245" s="4" t="n">
-        <v>50.82</v>
+        <v>50.93</v>
       </c>
       <c r="AC245" s="4" t="n">
-        <v>49.18</v>
+        <v>49.07</v>
       </c>
       <c r="AD245" s="4" t="n">
         <v>0</v>
@@ -25953,7 +25959,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>26.44</v>
+        <v>26.69</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>100</v>
@@ -25967,13 +25973,13 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>20.11</v>
+        <v>20.36</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O246" s="4" t="n">
-        <v>26.44</v>
+        <v>26.69</v>
       </c>
       <c r="P246" s="4" t="n">
         <v>1.6</v>
@@ -26004,10 +26010,10 @@
         <v>0</v>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>63.22</v>
+        <v>63.35</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>36.78</v>
+        <v>36.65</v>
       </c>
       <c r="AD246" s="4" t="n">
         <v>0</v>
@@ -26055,7 +26061,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>58.48</v>
+        <v>58.72</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -26069,13 +26075,13 @@
         </is>
       </c>
       <c r="M247" s="4" t="n">
-        <v>45.15</v>
+        <v>45.4</v>
       </c>
       <c r="N247" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O247" s="4" t="n">
-        <v>58.48</v>
+        <v>58.72</v>
       </c>
       <c r="P247" s="4" t="n">
         <v>2.96</v>
@@ -26106,10 +26112,10 @@
         <v>0</v>
       </c>
       <c r="AB247" s="4" t="n">
-        <v>79.23999999999999</v>
+        <v>79.36</v>
       </c>
       <c r="AC247" s="4" t="n">
-        <v>20.76</v>
+        <v>20.64</v>
       </c>
       <c r="AD247" s="4" t="n">
         <v>0</v>
@@ -26157,7 +26163,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>58.22</v>
+        <v>58.46</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -26171,13 +26177,13 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>47.65</v>
+        <v>47.9</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>58.22</v>
+        <v>58.46</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
@@ -26208,10 +26214,10 @@
         <v>0</v>
       </c>
       <c r="AB248" s="4" t="n">
-        <v>79.11</v>
+        <v>79.23</v>
       </c>
       <c r="AC248" s="4" t="n">
-        <v>20.89</v>
+        <v>20.77</v>
       </c>
       <c r="AD248" s="4" t="n">
         <v>0</v>
@@ -26363,7 +26369,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>12.14</v>
+        <v>12.16</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>98.90000000000001</v>
@@ -26420,10 +26426,10 @@
         <v>0</v>
       </c>
       <c r="AB250" s="4" t="n">
-        <v>56.07</v>
+        <v>56.08</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>43.93</v>
+        <v>43.92</v>
       </c>
       <c r="AD250" s="4" t="n">
         <v>0</v>
@@ -26522,10 +26528,10 @@
         <v>0</v>
       </c>
       <c r="AB251" s="4" t="n">
-        <v>64.87</v>
+        <v>64.88</v>
       </c>
       <c r="AC251" s="4" t="n">
-        <v>35.13</v>
+        <v>35.12</v>
       </c>
       <c r="AD251" s="4" t="n">
         <v>0</v>
@@ -26777,7 +26783,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-17.07</v>
+        <v>-17.06</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>0.4</v>
@@ -26797,7 +26803,7 @@
         <v>5.38</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-17.07</v>
+        <v>-17.06</v>
       </c>
       <c r="P254" s="4" t="n">
         <v>-2.25</v>
@@ -26879,7 +26885,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>-32.09</v>
+        <v>-32.08</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>0</v>
@@ -26893,13 +26899,13 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-34.03</v>
+        <v>-34.02</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O255" s="4" t="n">
-        <v>-32.09</v>
+        <v>-32.08</v>
       </c>
       <c r="P255" s="4" t="n">
         <v>-0.93</v>
@@ -27185,7 +27191,7 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.72</v>
+        <v>-10.73</v>
       </c>
       <c r="J258" s="4" t="n">
         <v>2.5</v>
@@ -27242,10 +27248,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.64</v>
+        <v>44.63</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.36</v>
+        <v>55.37</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -28305,13 +28311,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-7.19</v>
+        <v>-7.17</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>88.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28319,13 +28325,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.7</v>
+        <v>-12.66</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.44</v>
+        <v>-8.4</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28362,10 +28368,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.41</v>
+        <v>46.42</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.59</v>
+        <v>53.58</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28413,7 +28419,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-34.18</v>
+        <v>-34.14</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28427,13 +28433,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.66</v>
+        <v>-31.62</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-34.18</v>
+        <v>-34.14</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28464,10 +28470,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>32.91</v>
+        <v>32.93</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>67.09</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28535,7 +28541,7 @@
         <v>5.38</v>
       </c>
       <c r="O271" s="4" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="P271" s="4" t="n">
         <v>0.04</v>
@@ -28623,7 +28629,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>45.9</v>
+        <v>45.89</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -28637,13 +28643,13 @@
         </is>
       </c>
       <c r="M272" s="4" t="n">
-        <v>37.32</v>
+        <v>37.31</v>
       </c>
       <c r="N272" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O272" s="4" t="n">
-        <v>45.9</v>
+        <v>45.89</v>
       </c>
       <c r="P272" s="4" t="n">
         <v>0</v>
@@ -28739,7 +28745,7 @@
         </is>
       </c>
       <c r="M273" s="4" t="n">
-        <v>-9.5</v>
+        <v>-9.51</v>
       </c>
       <c r="N273" s="4" t="n">
         <v>5.38</v>
@@ -28827,7 +28833,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>59.41</v>
+        <v>59.4</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>100</v>
@@ -28841,13 +28847,13 @@
         </is>
       </c>
       <c r="M274" s="4" t="n">
-        <v>49.01</v>
+        <v>49</v>
       </c>
       <c r="N274" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O274" s="4" t="n">
-        <v>59.41</v>
+        <v>59.4</v>
       </c>
       <c r="P274" s="4" t="n">
         <v>1.88</v>
@@ -28929,7 +28935,7 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>-10.2</v>
+        <v>-10.21</v>
       </c>
       <c r="J275" s="4" t="n">
         <v>3.7</v>
@@ -28949,7 +28955,7 @@
         <v>5.38</v>
       </c>
       <c r="O275" s="4" t="n">
-        <v>-10.2</v>
+        <v>-10.21</v>
       </c>
       <c r="P275" s="4" t="n">
         <v>-0.9</v>
@@ -29082,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="AB276" s="4" t="n">
-        <v>43.82</v>
+        <v>43.81</v>
       </c>
       <c r="AC276" s="4" t="n">
-        <v>56.18</v>
+        <v>56.19</v>
       </c>
       <c r="AD276" s="4" t="n">
         <v>0</v>
@@ -29133,7 +29139,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>-10.07</v>
+        <v>-10.08</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>4</v>
@@ -29235,7 +29241,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-16.45</v>
+        <v>-16.46</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.5</v>
@@ -29249,13 +29255,13 @@
         </is>
       </c>
       <c r="M278" s="4" t="n">
-        <v>-16.58</v>
+        <v>-16.59</v>
       </c>
       <c r="N278" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-16.45</v>
+        <v>-16.46</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.86</v>
@@ -29388,10 +29394,10 @@
         <v>0</v>
       </c>
       <c r="AB279" s="4" t="n">
-        <v>44.52</v>
+        <v>44.51</v>
       </c>
       <c r="AC279" s="4" t="n">
-        <v>55.48</v>
+        <v>55.49</v>
       </c>
       <c r="AD279" s="4" t="n">
         <v>0</v>
@@ -29439,7 +29445,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>-15.15</v>
+        <v>-15.16</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>0.6</v>
@@ -29533,7 +29539,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Generic Republican</t>
+          <t>Jennifer Balkcom</t>
         </is>
       </c>
       <c r="G281" t="inlineStr"/>
@@ -29543,7 +29549,7 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>-2.86</v>
+        <v>-2.87</v>
       </c>
       <c r="J281" s="4" t="n">
         <v>27</v>
@@ -29557,13 +29563,13 @@
         </is>
       </c>
       <c r="M281" s="4" t="n">
-        <v>-7.52</v>
+        <v>-7.53</v>
       </c>
       <c r="N281" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O281" s="4" t="n">
-        <v>-2.86</v>
+        <v>-2.87</v>
       </c>
       <c r="P281" s="4" t="n">
         <v>0</v>
@@ -29696,10 +29702,10 @@
         <v>0</v>
       </c>
       <c r="AB282" s="4" t="n">
-        <v>80.16</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="AC282" s="4" t="n">
-        <v>19.84</v>
+        <v>19.85</v>
       </c>
       <c r="AD282" s="4" t="n">
         <v>0</v>
@@ -29747,7 +29753,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-12.97</v>
+        <v>-12.98</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>1</v>
@@ -29761,13 +29767,13 @@
         </is>
       </c>
       <c r="M283" s="4" t="n">
-        <v>-14.24</v>
+        <v>-14.25</v>
       </c>
       <c r="N283" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O283" s="4" t="n">
-        <v>-12.51</v>
+        <v>-12.52</v>
       </c>
       <c r="P283" s="4" t="n">
         <v>-0.19</v>
@@ -29849,7 +29855,7 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>-12.56</v>
+        <v>-12.57</v>
       </c>
       <c r="J284" s="4" t="n">
         <v>1</v>
@@ -29863,7 +29869,7 @@
         </is>
       </c>
       <c r="M284" s="4" t="n">
-        <v>-13.04</v>
+        <v>-13.05</v>
       </c>
       <c r="N284" s="4" t="n">
         <v>5.38</v>
@@ -31197,7 +31203,7 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="J297" s="4" t="n">
         <v>80.8</v>
@@ -31862,10 +31868,10 @@
         <v>0</v>
       </c>
       <c r="AB303" s="4" t="n">
-        <v>63.18</v>
+        <v>63.19</v>
       </c>
       <c r="AC303" s="4" t="n">
-        <v>36.82</v>
+        <v>36.81</v>
       </c>
       <c r="AD303" s="4" t="n">
         <v>0</v>
@@ -31913,7 +31919,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>14.86</v>
+        <v>14.87</v>
       </c>
       <c r="J304" s="4" t="n">
         <v>99.3</v>
@@ -31927,7 +31933,7 @@
         </is>
       </c>
       <c r="M304" s="4" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N304" s="4" t="n">
         <v>5.38</v>
@@ -32021,7 +32027,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>23.38</v>
+        <v>23.39</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>99.90000000000001</v>
@@ -32035,13 +32041,13 @@
         </is>
       </c>
       <c r="M305" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N305" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O305" s="4" t="n">
-        <v>23.38</v>
+        <v>23.39</v>
       </c>
       <c r="P305" s="4" t="n">
         <v>0.73</v>
@@ -32123,7 +32129,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>16.14</v>
+        <v>16.15</v>
       </c>
       <c r="J306" s="4" t="n">
         <v>99.5</v>
@@ -32137,13 +32143,13 @@
         </is>
       </c>
       <c r="M306" s="4" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="N306" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O306" s="4" t="n">
-        <v>16.14</v>
+        <v>16.15</v>
       </c>
       <c r="P306" s="4" t="n">
         <v>-0.16</v>
@@ -32221,13 +32227,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-5.34</v>
+        <v>-5.38</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -32235,13 +32241,13 @@
         </is>
       </c>
       <c r="M307" s="4" t="n">
-        <v>-12.72</v>
+        <v>-12.71</v>
       </c>
       <c r="N307" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O307" s="4" t="n">
-        <v>-8.68</v>
+        <v>-8.67</v>
       </c>
       <c r="P307" s="4" t="n">
         <v>-1.32</v>
@@ -32278,10 +32284,10 @@
         <v>0</v>
       </c>
       <c r="AB307" s="4" t="n">
-        <v>47.33</v>
+        <v>47.31</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>52.67</v>
+        <v>52.69</v>
       </c>
       <c r="AD307" s="4" t="n">
         <v>0</v>
@@ -32329,7 +32335,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="J308" s="4" t="n">
         <v>98.8</v>
@@ -32343,13 +32349,13 @@
         </is>
       </c>
       <c r="M308" s="4" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="N308" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O308" s="4" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="P308" s="4" t="n">
         <v>0.06</v>
@@ -32380,10 +32386,10 @@
         <v>0</v>
       </c>
       <c r="AB308" s="4" t="n">
-        <v>55.8</v>
+        <v>55.81</v>
       </c>
       <c r="AC308" s="4" t="n">
-        <v>44.2</v>
+        <v>44.19</v>
       </c>
       <c r="AD308" s="4" t="n">
         <v>0</v>
@@ -32431,7 +32437,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>17.4</v>
+        <v>17.41</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>99.59999999999999</v>
@@ -32445,13 +32451,13 @@
         </is>
       </c>
       <c r="M309" s="4" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
       <c r="N309" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>17.4</v>
+        <v>17.41</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>0.97</v>
@@ -32536,10 +32542,10 @@
         <v>-3.07</v>
       </c>
       <c r="J310" s="4" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="K310" s="4" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -32757,7 +32763,7 @@
         </is>
       </c>
       <c r="M312" s="4" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="N312" s="4" t="n">
         <v>5.38</v>
@@ -32953,7 +32959,7 @@
         </is>
       </c>
       <c r="I314" s="4" t="n">
-        <v>58.62</v>
+        <v>58.63</v>
       </c>
       <c r="J314" s="4" t="n">
         <v>100</v>
@@ -32973,7 +32979,7 @@
         <v>5.38</v>
       </c>
       <c r="O314" s="4" t="n">
-        <v>58.62</v>
+        <v>58.63</v>
       </c>
       <c r="P314" s="4" t="n">
         <v>0</v>
@@ -33069,7 +33075,7 @@
         </is>
       </c>
       <c r="M315" s="4" t="n">
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="N315" s="4" t="n">
         <v>5.38</v>
@@ -33455,7 +33461,7 @@
         </is>
       </c>
       <c r="I319" s="4" t="n">
-        <v>70.38</v>
+        <v>70.39</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>100</v>
@@ -33469,13 +33475,13 @@
         </is>
       </c>
       <c r="M319" s="4" t="n">
-        <v>64.98999999999999</v>
+        <v>65</v>
       </c>
       <c r="N319" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O319" s="4" t="n">
-        <v>70.38</v>
+        <v>70.39</v>
       </c>
       <c r="P319" s="4" t="n">
         <v>0</v>
@@ -33557,7 +33563,7 @@
         </is>
       </c>
       <c r="I320" s="4" t="n">
-        <v>-20.2</v>
+        <v>-20.19</v>
       </c>
       <c r="J320" s="4" t="n">
         <v>0.2</v>
@@ -33577,7 +33583,7 @@
         <v>5.38</v>
       </c>
       <c r="O320" s="4" t="n">
-        <v>-20.2</v>
+        <v>-20.19</v>
       </c>
       <c r="P320" s="4" t="n">
         <v>-2.38</v>
@@ -33869,7 +33875,7 @@
         </is>
       </c>
       <c r="M323" s="4" t="n">
-        <v>39.37</v>
+        <v>39.38</v>
       </c>
       <c r="N323" s="4" t="n">
         <v>5.38</v>
@@ -33971,7 +33977,7 @@
         </is>
       </c>
       <c r="M324" s="4" t="n">
-        <v>55.59</v>
+        <v>55.6</v>
       </c>
       <c r="N324" s="4" t="n">
         <v>5.38</v>
@@ -34073,7 +34079,7 @@
         </is>
       </c>
       <c r="M325" s="4" t="n">
-        <v>36.56</v>
+        <v>36.57</v>
       </c>
       <c r="N325" s="4" t="n">
         <v>5.38</v>
@@ -34110,10 +34116,10 @@
         <v>0</v>
       </c>
       <c r="AB325" s="4" t="n">
-        <v>75.08</v>
+        <v>75.09</v>
       </c>
       <c r="AC325" s="4" t="n">
-        <v>24.92</v>
+        <v>24.91</v>
       </c>
       <c r="AD325" s="4" t="n">
         <v>0</v>
@@ -34161,7 +34167,7 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="J326" s="4" t="n">
         <v>72</v>
@@ -34218,10 +34224,10 @@
         <v>0</v>
       </c>
       <c r="AB326" s="4" t="n">
-        <v>51.3</v>
+        <v>51.31</v>
       </c>
       <c r="AC326" s="4" t="n">
-        <v>48.7</v>
+        <v>48.69</v>
       </c>
       <c r="AD326" s="4" t="n">
         <v>0</v>
@@ -34269,7 +34275,7 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>15.88</v>
+        <v>15.95</v>
       </c>
       <c r="J327" s="4" t="n">
         <v>99.40000000000001</v>
@@ -34283,7 +34289,7 @@
         </is>
       </c>
       <c r="M327" s="4" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="N327" s="4" t="n">
         <v>5.38</v>
@@ -34326,10 +34332,10 @@
         <v>0</v>
       </c>
       <c r="AB327" s="4" t="n">
-        <v>57.94</v>
+        <v>57.97</v>
       </c>
       <c r="AC327" s="4" t="n">
-        <v>42.06</v>
+        <v>42.03</v>
       </c>
       <c r="AD327" s="4" t="n">
         <v>0</v>
@@ -34391,7 +34397,7 @@
         </is>
       </c>
       <c r="M328" s="4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="N328" s="4" t="n">
         <v>5.38</v>
@@ -34428,10 +34434,10 @@
         <v>0</v>
       </c>
       <c r="AB328" s="4" t="n">
-        <v>56.73</v>
+        <v>56.74</v>
       </c>
       <c r="AC328" s="4" t="n">
-        <v>43.27</v>
+        <v>43.26</v>
       </c>
       <c r="AD328" s="4" t="n">
         <v>0</v>
@@ -34479,7 +34485,7 @@
         </is>
       </c>
       <c r="I329" s="4" t="n">
-        <v>29.44</v>
+        <v>29.45</v>
       </c>
       <c r="J329" s="4" t="n">
         <v>100</v>
@@ -34493,13 +34499,13 @@
         </is>
       </c>
       <c r="M329" s="4" t="n">
-        <v>15.41</v>
+        <v>15.42</v>
       </c>
       <c r="N329" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O329" s="4" t="n">
-        <v>29.44</v>
+        <v>29.45</v>
       </c>
       <c r="P329" s="4" t="n">
         <v>1.91</v>
@@ -34577,13 +34583,13 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-7.69</v>
+        <v>-7.79</v>
       </c>
       <c r="J330" s="4" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="K330" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -34634,10 +34640,10 @@
         <v>0</v>
       </c>
       <c r="AB330" s="4" t="n">
-        <v>46.16</v>
+        <v>46.1</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>53.84</v>
+        <v>53.9</v>
       </c>
       <c r="AD330" s="4" t="n">
         <v>0</v>
@@ -34787,7 +34793,7 @@
         </is>
       </c>
       <c r="I332" s="4" t="n">
-        <v>-21.74</v>
+        <v>-21.73</v>
       </c>
       <c r="J332" s="4" t="n">
         <v>0.1</v>
@@ -34801,13 +34807,13 @@
         </is>
       </c>
       <c r="M332" s="4" t="n">
-        <v>-20.85</v>
+        <v>-20.84</v>
       </c>
       <c r="N332" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O332" s="4" t="n">
-        <v>-21.74</v>
+        <v>-21.73</v>
       </c>
       <c r="P332" s="4" t="n">
         <v>-1.61</v>
@@ -35107,7 +35113,7 @@
         </is>
       </c>
       <c r="M335" s="4" t="n">
-        <v>20.83</v>
+        <v>20.84</v>
       </c>
       <c r="N335" s="4" t="n">
         <v>5.38</v>
@@ -35144,10 +35150,10 @@
         <v>0</v>
       </c>
       <c r="AB335" s="4" t="n">
-        <v>68.33</v>
+        <v>68.34</v>
       </c>
       <c r="AC335" s="4" t="n">
-        <v>31.67</v>
+        <v>31.66</v>
       </c>
       <c r="AD335" s="4" t="n">
         <v>0</v>
@@ -35195,7 +35201,7 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>12.32</v>
+        <v>12.31</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>98.90000000000001</v>
@@ -35215,7 +35221,7 @@
         <v>5.38</v>
       </c>
       <c r="O336" s="4" t="n">
-        <v>12.32</v>
+        <v>12.31</v>
       </c>
       <c r="P336" s="4" t="n">
         <v>0.77</v>
@@ -35399,7 +35405,7 @@
         </is>
       </c>
       <c r="I338" s="4" t="n">
-        <v>53.27</v>
+        <v>53.26</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>100</v>
@@ -35419,7 +35425,7 @@
         <v>5.38</v>
       </c>
       <c r="O338" s="4" t="n">
-        <v>53.27</v>
+        <v>53.26</v>
       </c>
       <c r="P338" s="4" t="n">
         <v>0</v>
@@ -35617,7 +35623,7 @@
         </is>
       </c>
       <c r="M340" s="4" t="n">
-        <v>-18.85</v>
+        <v>-18.86</v>
       </c>
       <c r="N340" s="4" t="n">
         <v>5.38</v>
@@ -35807,13 +35813,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-1.29</v>
+        <v>-1.33</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>66.8</v>
+        <v>67</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35827,7 +35833,7 @@
         <v>5.38</v>
       </c>
       <c r="O342" s="4" t="n">
-        <v>-4.58</v>
+        <v>-4.59</v>
       </c>
       <c r="P342" s="4" t="n">
         <v>-0.49</v>
@@ -35864,10 +35870,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>49.36</v>
+        <v>49.34</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>50.64</v>
+        <v>50.66</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -35929,7 +35935,7 @@
         </is>
       </c>
       <c r="M343" s="4" t="n">
-        <v>-11.61</v>
+        <v>-11.62</v>
       </c>
       <c r="N343" s="4" t="n">
         <v>5.38</v>
@@ -35966,10 +35972,10 @@
         <v>0</v>
       </c>
       <c r="AB343" s="4" t="n">
-        <v>45.94</v>
+        <v>45.93</v>
       </c>
       <c r="AC343" s="4" t="n">
-        <v>54.06</v>
+        <v>54.07</v>
       </c>
       <c r="AD343" s="4" t="n">
         <v>0</v>
@@ -36031,7 +36037,7 @@
         </is>
       </c>
       <c r="M344" s="4" t="n">
-        <v>-5.2</v>
+        <v>-5.21</v>
       </c>
       <c r="N344" s="4" t="n">
         <v>5.38</v>
@@ -36125,7 +36131,7 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>6.6</v>
@@ -36145,7 +36151,7 @@
         <v>5.38</v>
       </c>
       <c r="O345" s="4" t="n">
-        <v>-9.09</v>
+        <v>-9.1</v>
       </c>
       <c r="P345" s="4" t="n">
         <v>-0.62</v>
@@ -36233,7 +36239,7 @@
         </is>
       </c>
       <c r="I346" s="4" t="n">
-        <v>71.17</v>
+        <v>71.16</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>100</v>
@@ -36247,13 +36253,13 @@
         </is>
       </c>
       <c r="M346" s="4" t="n">
-        <v>60.85</v>
+        <v>60.84</v>
       </c>
       <c r="N346" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O346" s="4" t="n">
-        <v>71.17</v>
+        <v>71.16</v>
       </c>
       <c r="P346" s="4" t="n">
         <v>0</v>
@@ -36335,7 +36341,7 @@
         </is>
       </c>
       <c r="I347" s="4" t="n">
-        <v>-25.2</v>
+        <v>-25.21</v>
       </c>
       <c r="J347" s="4" t="n">
         <v>0.1</v>
@@ -36355,7 +36361,7 @@
         <v>5.38</v>
       </c>
       <c r="O347" s="4" t="n">
-        <v>-25.2</v>
+        <v>-25.21</v>
       </c>
       <c r="P347" s="4" t="n">
         <v>-1.94</v>
@@ -36451,7 +36457,7 @@
         </is>
       </c>
       <c r="M348" s="4" t="n">
-        <v>8.35</v>
+        <v>8.34</v>
       </c>
       <c r="N348" s="4" t="n">
         <v>5.38</v>
@@ -36488,10 +36494,10 @@
         <v>0</v>
       </c>
       <c r="AB348" s="4" t="n">
-        <v>59.65</v>
+        <v>59.64</v>
       </c>
       <c r="AC348" s="4" t="n">
-        <v>40.35</v>
+        <v>40.36</v>
       </c>
       <c r="AD348" s="4" t="n">
         <v>0</v>
@@ -36553,7 +36559,7 @@
         </is>
       </c>
       <c r="M349" s="4" t="n">
-        <v>-15.27</v>
+        <v>-15.28</v>
       </c>
       <c r="N349" s="4" t="n">
         <v>5.38</v>
@@ -36644,10 +36650,10 @@
         <v>-5.17</v>
       </c>
       <c r="J350" s="4" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="K350" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -36655,7 +36661,7 @@
         </is>
       </c>
       <c r="M350" s="4" t="n">
-        <v>-5.33</v>
+        <v>-5.34</v>
       </c>
       <c r="N350" s="4" t="n">
         <v>5.38</v>
@@ -37351,7 +37357,7 @@
         </is>
       </c>
       <c r="I357" s="4" t="n">
-        <v>-28.8</v>
+        <v>-28.79</v>
       </c>
       <c r="J357" s="4" t="n">
         <v>0</v>
@@ -37371,7 +37377,7 @@
         <v>5.38</v>
       </c>
       <c r="O357" s="4" t="n">
-        <v>-28.8</v>
+        <v>-28.79</v>
       </c>
       <c r="P357" s="4" t="n">
         <v>-1.49</v>
@@ -37759,7 +37765,7 @@
         </is>
       </c>
       <c r="I361" s="4" t="n">
-        <v>18.21</v>
+        <v>18.22</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>99.7</v>
@@ -37779,7 +37785,7 @@
         <v>5.38</v>
       </c>
       <c r="O361" s="4" t="n">
-        <v>18.21</v>
+        <v>18.22</v>
       </c>
       <c r="P361" s="4" t="n">
         <v>2.46</v>
@@ -37918,10 +37924,10 @@
         <v>0</v>
       </c>
       <c r="AB362" s="4" t="n">
-        <v>49.13</v>
+        <v>49.14</v>
       </c>
       <c r="AC362" s="4" t="n">
-        <v>50.87</v>
+        <v>50.86</v>
       </c>
       <c r="AD362" s="4" t="n">
         <v>0</v>
@@ -38475,13 +38481,13 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="J368" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K368" s="4" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -38583,13 +38589,13 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="J369" s="4" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
       <c r="K369" s="4" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -38796,10 +38802,10 @@
         <v>9.1</v>
       </c>
       <c r="J371" s="4" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="K371" s="4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -39666,10 +39672,10 @@
         <v>0</v>
       </c>
       <c r="AB379" s="4" t="n">
-        <v>70.45999999999999</v>
+        <v>70.47</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>29.54</v>
+        <v>29.53</v>
       </c>
       <c r="AD379" s="4" t="n">
         <v>0</v>
@@ -39717,7 +39723,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>17.64</v>
+        <v>17.65</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39737,7 +39743,7 @@
         <v>5.38</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>17.64</v>
+        <v>17.65</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.61</v>
@@ -39815,7 +39821,7 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-3.42</v>
+        <v>-3.41</v>
       </c>
       <c r="J381" s="4" t="n">
         <v>24.9</v>
@@ -39829,13 +39835,13 @@
         </is>
       </c>
       <c r="M381" s="4" t="n">
-        <v>-8.85</v>
+        <v>-8.84</v>
       </c>
       <c r="N381" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O381" s="4" t="n">
-        <v>-3.2</v>
+        <v>-3.19</v>
       </c>
       <c r="P381" s="4" t="n">
         <v>0.72</v>
@@ -39937,7 +39943,7 @@
         </is>
       </c>
       <c r="M382" s="4" t="n">
-        <v>-10.03</v>
+        <v>-10.02</v>
       </c>
       <c r="N382" s="4" t="n">
         <v>5.38</v>
@@ -40039,7 +40045,7 @@
         </is>
       </c>
       <c r="M383" s="4" t="n">
-        <v>-38.49</v>
+        <v>-38.48</v>
       </c>
       <c r="N383" s="4" t="n">
         <v>5.38</v>
@@ -40076,10 +40082,10 @@
         <v>0</v>
       </c>
       <c r="AB383" s="4" t="n">
-        <v>29.27</v>
+        <v>29.28</v>
       </c>
       <c r="AC383" s="4" t="n">
-        <v>70.73</v>
+        <v>70.72</v>
       </c>
       <c r="AD383" s="4" t="n">
         <v>0</v>
@@ -40178,10 +40184,10 @@
         <v>0</v>
       </c>
       <c r="AB384" s="4" t="n">
-        <v>41.05</v>
+        <v>41.06</v>
       </c>
       <c r="AC384" s="4" t="n">
-        <v>58.95</v>
+        <v>58.94</v>
       </c>
       <c r="AD384" s="4" t="n">
         <v>0</v>
@@ -40239,7 +40245,7 @@
         </is>
       </c>
       <c r="M385" s="4" t="n">
-        <v>-18.31</v>
+        <v>-18.3</v>
       </c>
       <c r="N385" s="4" t="n">
         <v>5.38</v>
@@ -40276,10 +40282,10 @@
         <v>0</v>
       </c>
       <c r="AB385" s="4" t="n">
-        <v>42.7</v>
+        <v>42.71</v>
       </c>
       <c r="AC385" s="4" t="n">
-        <v>57.3</v>
+        <v>57.29</v>
       </c>
       <c r="AD385" s="4" t="n">
         <v>0</v>
@@ -40327,7 +40333,7 @@
         </is>
       </c>
       <c r="I386" s="4" t="n">
-        <v>36.31</v>
+        <v>36.32</v>
       </c>
       <c r="J386" s="4" t="n">
         <v>100</v>
@@ -40341,13 +40347,13 @@
         </is>
       </c>
       <c r="M386" s="4" t="n">
-        <v>29.42</v>
+        <v>29.43</v>
       </c>
       <c r="N386" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O386" s="4" t="n">
-        <v>36.31</v>
+        <v>36.32</v>
       </c>
       <c r="P386" s="4" t="n">
         <v>0</v>
@@ -40429,7 +40435,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-15.66</v>
+        <v>-15.75</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>0.6</v>
@@ -40486,10 +40492,10 @@
         <v>0</v>
       </c>
       <c r="AB387" s="4" t="n">
-        <v>42.17</v>
+        <v>42.12</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>57.83</v>
+        <v>57.88</v>
       </c>
       <c r="AD387" s="4" t="n">
         <v>0</v>
@@ -40533,7 +40539,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-23.58</v>
+        <v>-23.59</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40553,7 +40559,7 @@
         <v>5.38</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-23.58</v>
+        <v>-23.59</v>
       </c>
       <c r="P388" s="4" t="n">
         <v>-1.2</v>
@@ -41555,7 +41561,7 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-44.18</v>
+        <v>-44.19</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>5.38</v>
@@ -41592,10 +41598,10 @@
         <v>0</v>
       </c>
       <c r="AB398" s="4" t="n">
-        <v>29.75</v>
+        <v>29.74</v>
       </c>
       <c r="AC398" s="4" t="n">
-        <v>70.25</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="AD398" s="4" t="n">
         <v>0</v>
@@ -41690,10 +41696,10 @@
         <v>0</v>
       </c>
       <c r="AB399" s="4" t="n">
-        <v>43.88</v>
+        <v>43.87</v>
       </c>
       <c r="AC399" s="4" t="n">
-        <v>56.12</v>
+        <v>56.13</v>
       </c>
       <c r="AD399" s="4" t="n">
         <v>0</v>
@@ -41741,7 +41747,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-15.33</v>
+        <v>-15.34</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>0.6</v>
@@ -41755,13 +41761,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-18.78</v>
+        <v>-18.79</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-15.33</v>
+        <v>-15.34</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -41792,10 +41798,10 @@
         <v>0</v>
       </c>
       <c r="AB400" s="4" t="n">
-        <v>42.34</v>
+        <v>42.33</v>
       </c>
       <c r="AC400" s="4" t="n">
-        <v>57.66</v>
+        <v>57.67</v>
       </c>
       <c r="AD400" s="4" t="n">
         <v>0</v>
@@ -41843,7 +41849,7 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>-20.76</v>
+        <v>-20.77</v>
       </c>
       <c r="J401" s="4" t="n">
         <v>0.2</v>
@@ -41863,7 +41869,7 @@
         <v>5.38</v>
       </c>
       <c r="O401" s="4" t="n">
-        <v>-20.76</v>
+        <v>-20.77</v>
       </c>
       <c r="P401" s="4" t="n">
         <v>-1.91</v>
@@ -41894,10 +41900,10 @@
         <v>0</v>
       </c>
       <c r="AB401" s="4" t="n">
-        <v>39.62</v>
+        <v>39.61</v>
       </c>
       <c r="AC401" s="4" t="n">
-        <v>60.38</v>
+        <v>60.39</v>
       </c>
       <c r="AD401" s="4" t="n">
         <v>0</v>
@@ -41945,7 +41951,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-13.29</v>
+        <v>-13.3</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>0.9</v>
@@ -41965,7 +41971,7 @@
         <v>5.38</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-13.29</v>
+        <v>-13.3</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.23</v>
@@ -41996,10 +42002,10 @@
         <v>0</v>
       </c>
       <c r="AB402" s="4" t="n">
-        <v>43.36</v>
+        <v>43.35</v>
       </c>
       <c r="AC402" s="4" t="n">
-        <v>56.64</v>
+        <v>56.65</v>
       </c>
       <c r="AD402" s="4" t="n">
         <v>0</v>
@@ -42047,7 +42053,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-18.67</v>
+        <v>-18.68</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.3</v>
@@ -42067,7 +42073,7 @@
         <v>5.38</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-18.67</v>
+        <v>-18.68</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -42149,7 +42155,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>41.09</v>
+        <v>41.08</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -42169,7 +42175,7 @@
         <v>5.38</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>41.09</v>
+        <v>41.08</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -42200,10 +42206,10 @@
         <v>0</v>
       </c>
       <c r="AB404" s="4" t="n">
-        <v>70.55</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="AC404" s="4" t="n">
-        <v>29.45</v>
+        <v>29.46</v>
       </c>
       <c r="AD404" s="4" t="n">
         <v>0</v>
@@ -42247,7 +42253,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-17.87</v>
+        <v>-17.88</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.4</v>
@@ -42261,13 +42267,13 @@
         </is>
       </c>
       <c r="M405" s="4" t="n">
-        <v>-21.25</v>
+        <v>-21.26</v>
       </c>
       <c r="N405" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-17.87</v>
+        <v>-17.88</v>
       </c>
       <c r="P405" s="4" t="n">
         <v>-2.83</v>
@@ -42345,7 +42351,7 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-6.59</v>
+        <v>-6.6</v>
       </c>
       <c r="J406" s="4" t="n">
         <v>13.8</v>
@@ -42365,7 +42371,7 @@
         <v>5.38</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-6.59</v>
+        <v>-6.6</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.92</v>
@@ -42443,7 +42449,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-12.98</v>
+        <v>-12.99</v>
       </c>
       <c r="J407" s="4" t="n">
         <v>1</v>
@@ -42457,13 +42463,13 @@
         </is>
       </c>
       <c r="M407" s="4" t="n">
-        <v>-16.91</v>
+        <v>-16.92</v>
       </c>
       <c r="N407" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-12.98</v>
+        <v>-12.99</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -42545,7 +42551,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-27.34</v>
+        <v>-27.35</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0</v>
@@ -42559,13 +42565,13 @@
         </is>
       </c>
       <c r="M408" s="4" t="n">
-        <v>-29.6</v>
+        <v>-29.61</v>
       </c>
       <c r="N408" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-27.34</v>
+        <v>-27.35</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -42647,7 +42653,7 @@
         </is>
       </c>
       <c r="I409" s="4" t="n">
-        <v>-18.69</v>
+        <v>-18.7</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>0.3</v>
@@ -42661,13 +42667,13 @@
         </is>
       </c>
       <c r="M409" s="4" t="n">
-        <v>-18.55</v>
+        <v>-18.56</v>
       </c>
       <c r="N409" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O409" s="4" t="n">
-        <v>-18.69</v>
+        <v>-18.7</v>
       </c>
       <c r="P409" s="4" t="n">
         <v>0</v>
@@ -42749,7 +42755,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-40.64</v>
+        <v>-40.65</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -42769,7 +42775,7 @@
         <v>5.38</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-40.64</v>
+        <v>-40.65</v>
       </c>
       <c r="P410" s="4" t="n">
         <v>-2.49</v>
@@ -42851,7 +42857,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-19.57</v>
+        <v>-19.58</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.3</v>
@@ -42871,7 +42877,7 @@
         <v>5.38</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-19.57</v>
+        <v>-19.58</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.89</v>
@@ -42967,13 +42973,13 @@
         </is>
       </c>
       <c r="M412" s="4" t="n">
-        <v>-8.289999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N412" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>-1.48</v>
+        <v>-1.49</v>
       </c>
       <c r="P412" s="4" t="n">
         <v>-0.32</v>
@@ -43061,7 +43067,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="n">
-        <v>36.64</v>
+        <v>36.63</v>
       </c>
       <c r="J413" s="4" t="n">
         <v>100</v>
@@ -43075,13 +43081,13 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>26.75</v>
+        <v>26.74</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O413" s="4" t="n">
-        <v>36.64</v>
+        <v>36.63</v>
       </c>
       <c r="P413" s="4" t="n">
         <v>0</v>
@@ -43163,7 +43169,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-14.76</v>
+        <v>-14.77</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>0.7</v>
@@ -43177,13 +43183,13 @@
         </is>
       </c>
       <c r="M414" s="4" t="n">
-        <v>-16.38</v>
+        <v>-16.39</v>
       </c>
       <c r="N414" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-14.76</v>
+        <v>-14.77</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>0</v>
@@ -43316,10 +43322,10 @@
         <v>0</v>
       </c>
       <c r="AB415" s="4" t="n">
-        <v>85.59</v>
+        <v>85.58</v>
       </c>
       <c r="AC415" s="4" t="n">
-        <v>14.41</v>
+        <v>14.42</v>
       </c>
       <c r="AD415" s="4" t="n">
         <v>0</v>
@@ -43363,7 +43369,7 @@
         </is>
       </c>
       <c r="I416" s="4" t="n">
-        <v>-42.68</v>
+        <v>-42.69</v>
       </c>
       <c r="J416" s="4" t="n">
         <v>0</v>
@@ -43377,13 +43383,13 @@
         </is>
       </c>
       <c r="M416" s="4" t="n">
-        <v>-46.56</v>
+        <v>-46.57</v>
       </c>
       <c r="N416" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>-42.68</v>
+        <v>-42.69</v>
       </c>
       <c r="P416" s="4" t="n">
         <v>-2.39</v>
@@ -43465,7 +43471,7 @@
         </is>
       </c>
       <c r="I417" s="4" t="n">
-        <v>49.31</v>
+        <v>49.3</v>
       </c>
       <c r="J417" s="4" t="n">
         <v>100</v>
@@ -43479,13 +43485,13 @@
         </is>
       </c>
       <c r="M417" s="4" t="n">
-        <v>36.59</v>
+        <v>36.58</v>
       </c>
       <c r="N417" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O417" s="4" t="n">
-        <v>49.31</v>
+        <v>49.3</v>
       </c>
       <c r="P417" s="4" t="n">
         <v>1.31</v>
@@ -43614,10 +43620,10 @@
         <v>0</v>
       </c>
       <c r="AB418" s="4" t="n">
-        <v>43.88</v>
+        <v>43.87</v>
       </c>
       <c r="AC418" s="4" t="n">
-        <v>56.12</v>
+        <v>56.13</v>
       </c>
       <c r="AD418" s="4" t="n">
         <v>0</v>
@@ -43661,7 +43667,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-12.96</v>
+        <v>-12.97</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>1</v>
@@ -43681,7 +43687,7 @@
         <v>5.38</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-12.96</v>
+        <v>-12.97</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.8100000000000001</v>
@@ -43759,7 +43765,7 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-2.33</v>
+        <v>-2.34</v>
       </c>
       <c r="J420" s="4" t="n">
         <v>29.1</v>
@@ -43779,7 +43785,7 @@
         <v>5.38</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-1.86</v>
+        <v>-1.87</v>
       </c>
       <c r="P420" s="4" t="n">
         <v>-0.82</v>
@@ -43867,7 +43873,7 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-10.89</v>
+        <v>-10.9</v>
       </c>
       <c r="J421" s="4" t="n">
         <v>2.1</v>
@@ -43881,13 +43887,13 @@
         </is>
       </c>
       <c r="M421" s="4" t="n">
-        <v>-11.8</v>
+        <v>-11.81</v>
       </c>
       <c r="N421" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-10.89</v>
+        <v>-10.9</v>
       </c>
       <c r="P421" s="4" t="n">
         <v>0</v>
@@ -43983,7 +43989,7 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-18.03</v>
+        <v>-18.04</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>5.38</v>
@@ -44071,7 +44077,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-22.57</v>
+        <v>-22.58</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.1</v>
@@ -44085,13 +44091,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-19.15</v>
+        <v>-19.16</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-22.57</v>
+        <v>-22.58</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -44122,10 +44128,10 @@
         <v>0</v>
       </c>
       <c r="AB423" s="4" t="n">
-        <v>38.72</v>
+        <v>38.71</v>
       </c>
       <c r="AC423" s="4" t="n">
-        <v>61.28</v>
+        <v>61.29</v>
       </c>
       <c r="AD423" s="4" t="n">
         <v>0</v>
@@ -44173,7 +44179,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-13.84</v>
+        <v>-13.85</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>0.8</v>
@@ -44193,7 +44199,7 @@
         <v>5.38</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-13.84</v>
+        <v>-13.85</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -44275,7 +44281,7 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>14.1</v>
+        <v>14.18</v>
       </c>
       <c r="J425" s="4" t="n">
         <v>99.2</v>
@@ -44332,10 +44338,10 @@
         <v>0</v>
       </c>
       <c r="AB425" s="4" t="n">
-        <v>57.05</v>
+        <v>57.09</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>42.95</v>
+        <v>42.91</v>
       </c>
       <c r="AD425" s="4" t="n">
         <v>0</v>
@@ -44383,7 +44389,7 @@
         </is>
       </c>
       <c r="I426" s="4" t="n">
-        <v>54.1</v>
+        <v>54.09</v>
       </c>
       <c r="J426" s="4" t="n">
         <v>100</v>
@@ -44397,13 +44403,13 @@
         </is>
       </c>
       <c r="M426" s="4" t="n">
-        <v>39.11</v>
+        <v>39.1</v>
       </c>
       <c r="N426" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O426" s="4" t="n">
-        <v>54.1</v>
+        <v>54.09</v>
       </c>
       <c r="P426" s="4" t="n">
         <v>0</v>
@@ -44481,7 +44487,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>61.72</v>
+        <v>61.71</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -44495,13 +44501,13 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>54.82</v>
+        <v>54.81</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>61.72</v>
+        <v>61.71</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>0.21</v>
@@ -44597,13 +44603,13 @@
         </is>
       </c>
       <c r="M428" s="4" t="n">
-        <v>-17.31</v>
+        <v>-17.32</v>
       </c>
       <c r="N428" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O428" s="4" t="n">
-        <v>-18.13</v>
+        <v>-18.14</v>
       </c>
       <c r="P428" s="4" t="n">
         <v>-1.61</v>
@@ -44681,7 +44687,7 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-8.23</v>
+        <v>-8.24</v>
       </c>
       <c r="J429" s="4" t="n">
         <v>8.800000000000001</v>
@@ -44695,13 +44701,13 @@
         </is>
       </c>
       <c r="M429" s="4" t="n">
-        <v>-12.15</v>
+        <v>-12.16</v>
       </c>
       <c r="N429" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-8.23</v>
+        <v>-8.24</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.72</v>
@@ -44779,7 +44785,7 @@
         </is>
       </c>
       <c r="I430" s="4" t="n">
-        <v>46.19</v>
+        <v>46.18</v>
       </c>
       <c r="J430" s="4" t="n">
         <v>100</v>
@@ -44799,7 +44805,7 @@
         <v>5.38</v>
       </c>
       <c r="O430" s="4" t="n">
-        <v>46.19</v>
+        <v>46.18</v>
       </c>
       <c r="P430" s="4" t="n">
         <v>0</v>
@@ -44881,7 +44887,7 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="J431" s="4" t="n">
         <v>92.5</v>
@@ -44895,7 +44901,7 @@
         </is>
       </c>
       <c r="M431" s="4" t="n">
-        <v>-1.57</v>
+        <v>-1.58</v>
       </c>
       <c r="N431" s="4" t="n">
         <v>5.38</v>
@@ -44938,10 +44944,10 @@
         <v>0</v>
       </c>
       <c r="AB431" s="4" t="n">
-        <v>54.35</v>
+        <v>54.36</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>45.65</v>
+        <v>45.64</v>
       </c>
       <c r="AD431" s="4" t="n">
         <v>0</v>
@@ -44999,7 +45005,7 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-4.07</v>
+        <v>-4.08</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>5.38</v>
@@ -45036,10 +45042,10 @@
         <v>0</v>
       </c>
       <c r="AB432" s="4" t="n">
-        <v>51.64</v>
+        <v>51.63</v>
       </c>
       <c r="AC432" s="4" t="n">
-        <v>48.36</v>
+        <v>48.37</v>
       </c>
       <c r="AD432" s="4" t="n">
         <v>0</v>
@@ -45087,7 +45093,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-15.89</v>
+        <v>-15.9</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.6</v>
@@ -45101,13 +45107,13 @@
         </is>
       </c>
       <c r="M433" s="4" t="n">
-        <v>-19.18</v>
+        <v>-19.19</v>
       </c>
       <c r="N433" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-15.89</v>
+        <v>-15.9</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>0</v>
@@ -45189,7 +45195,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>71.26000000000001</v>
+        <v>71.25</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -45209,7 +45215,7 @@
         <v>5.38</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>71.26000000000001</v>
+        <v>71.25</v>
       </c>
       <c r="P434" s="4" t="n">
         <v>1.49</v>
@@ -45240,10 +45246,10 @@
         <v>0</v>
       </c>
       <c r="AB434" s="4" t="n">
-        <v>85.63</v>
+        <v>85.62</v>
       </c>
       <c r="AC434" s="4" t="n">
-        <v>14.37</v>
+        <v>14.38</v>
       </c>
       <c r="AD434" s="4" t="n">
         <v>0</v>
@@ -45307,7 +45313,7 @@
         <v>5.38</v>
       </c>
       <c r="O435" s="4" t="n">
-        <v>-13.43</v>
+        <v>-13.44</v>
       </c>
       <c r="P435" s="4" t="n">
         <v>-2.01</v>
@@ -45901,13 +45907,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>74</v>
+        <v>74.2</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -45958,10 +45964,10 @@
         <v>0</v>
       </c>
       <c r="AB441" s="4" t="n">
-        <v>51.57</v>
+        <v>51.59</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>48.43</v>
+        <v>48.41</v>
       </c>
       <c r="AD441" s="4" t="n">
         <v>0</v>
@@ -46213,7 +46219,7 @@
         </is>
       </c>
       <c r="I444" s="4" t="n">
-        <v>-5.56</v>
+        <v>-5.55</v>
       </c>
       <c r="J444" s="4" t="n">
         <v>17.2</v>
@@ -46933,7 +46939,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>35.86</v>
+        <v>35.85</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -46947,13 +46953,13 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>20.19</v>
+        <v>20.17</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>36</v>
+        <v>35.99</v>
       </c>
       <c r="P451" s="4" t="n">
         <v>1.67</v>
@@ -47245,13 +47251,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>6.17</v>
+        <v>6.2</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47302,10 +47308,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>53.08</v>
+        <v>53.1</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>46.92</v>
+        <v>46.9</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -47451,7 +47457,7 @@
         </is>
       </c>
       <c r="I456" s="4" t="n">
-        <v>-24.07</v>
+        <v>-24.1</v>
       </c>
       <c r="J456" s="4" t="n">
         <v>0.1</v>
@@ -47508,10 +47514,10 @@
         <v>0</v>
       </c>
       <c r="AB456" s="4" t="n">
-        <v>37.96</v>
+        <v>37.95</v>
       </c>
       <c r="AC456" s="4" t="n">
-        <v>62.04</v>
+        <v>62.05</v>
       </c>
       <c r="AD456" s="4" t="n">
         <v>0</v>
@@ -48069,13 +48075,13 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-3.77</v>
+        <v>-3.91</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>76.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -48083,13 +48089,13 @@
         </is>
       </c>
       <c r="M462" s="4" t="n">
-        <v>-2.55</v>
+        <v>-2.78</v>
       </c>
       <c r="N462" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O462" s="4" t="n">
-        <v>-3.96</v>
+        <v>-4.19</v>
       </c>
       <c r="P462" s="4" t="n">
         <v>-1.48</v>
@@ -48126,10 +48132,10 @@
         <v>0</v>
       </c>
       <c r="AB462" s="4" t="n">
-        <v>48.12</v>
+        <v>48.04</v>
       </c>
       <c r="AC462" s="4" t="n">
-        <v>51.88</v>
+        <v>51.96</v>
       </c>
       <c r="AD462" s="4" t="n">
         <v>0</v>
@@ -48177,7 +48183,7 @@
         </is>
       </c>
       <c r="I463" s="4" t="n">
-        <v>49.77</v>
+        <v>49.54</v>
       </c>
       <c r="J463" s="4" t="n">
         <v>100</v>
@@ -48191,13 +48197,13 @@
         </is>
       </c>
       <c r="M463" s="4" t="n">
-        <v>42.44</v>
+        <v>42.21</v>
       </c>
       <c r="N463" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O463" s="4" t="n">
-        <v>49.77</v>
+        <v>49.54</v>
       </c>
       <c r="P463" s="4" t="n">
         <v>0</v>
@@ -48228,10 +48234,10 @@
         <v>0</v>
       </c>
       <c r="AB463" s="4" t="n">
-        <v>74.88</v>
+        <v>74.77</v>
       </c>
       <c r="AC463" s="4" t="n">
-        <v>25.12</v>
+        <v>25.23</v>
       </c>
       <c r="AD463" s="4" t="n">
         <v>0</v>
@@ -48279,13 +48285,13 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="J464" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K464" s="4" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -48293,13 +48299,13 @@
         </is>
       </c>
       <c r="M464" s="4" t="n">
-        <v>-5.38</v>
+        <v>-5.61</v>
       </c>
       <c r="N464" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O464" s="4" t="n">
-        <v>6.46</v>
+        <v>6.23</v>
       </c>
       <c r="P464" s="4" t="n">
         <v>0.1</v>
@@ -48336,10 +48342,10 @@
         <v>0</v>
       </c>
       <c r="AB464" s="4" t="n">
-        <v>52.25</v>
+        <v>52.18</v>
       </c>
       <c r="AC464" s="4" t="n">
-        <v>47.75</v>
+        <v>47.82</v>
       </c>
       <c r="AD464" s="4" t="n">
         <v>0</v>
@@ -48387,7 +48393,7 @@
         </is>
       </c>
       <c r="I465" s="4" t="n">
-        <v>63.18</v>
+        <v>62.95</v>
       </c>
       <c r="J465" s="4" t="n">
         <v>100</v>
@@ -48401,13 +48407,13 @@
         </is>
       </c>
       <c r="M465" s="4" t="n">
-        <v>54.16</v>
+        <v>53.93</v>
       </c>
       <c r="N465" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O465" s="4" t="n">
-        <v>63.18</v>
+        <v>62.95</v>
       </c>
       <c r="P465" s="4" t="n">
         <v>0</v>
@@ -48438,10 +48444,10 @@
         <v>0</v>
       </c>
       <c r="AB465" s="4" t="n">
-        <v>81.59</v>
+        <v>81.47</v>
       </c>
       <c r="AC465" s="4" t="n">
-        <v>18.41</v>
+        <v>18.53</v>
       </c>
       <c r="AD465" s="4" t="n">
         <v>0</v>
@@ -48489,7 +48495,7 @@
         </is>
       </c>
       <c r="I466" s="4" t="n">
-        <v>-23.99</v>
+        <v>-24.22</v>
       </c>
       <c r="J466" s="4" t="n">
         <v>0.1</v>
@@ -48503,13 +48509,13 @@
         </is>
       </c>
       <c r="M466" s="4" t="n">
-        <v>-21.61</v>
+        <v>-21.84</v>
       </c>
       <c r="N466" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O466" s="4" t="n">
-        <v>-23.99</v>
+        <v>-24.22</v>
       </c>
       <c r="P466" s="4" t="n">
         <v>-2.32</v>
@@ -48540,10 +48546,10 @@
         <v>0</v>
       </c>
       <c r="AB466" s="4" t="n">
-        <v>38</v>
+        <v>37.89</v>
       </c>
       <c r="AC466" s="4" t="n">
-        <v>62</v>
+        <v>62.11</v>
       </c>
       <c r="AD466" s="4" t="n">
         <v>0</v>
@@ -48591,7 +48597,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-17.15</v>
+        <v>-17.33</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.4</v>
@@ -48605,13 +48611,13 @@
         </is>
       </c>
       <c r="M467" s="4" t="n">
-        <v>-15.22</v>
+        <v>-15.45</v>
       </c>
       <c r="N467" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-15.49</v>
+        <v>-15.72</v>
       </c>
       <c r="P467" s="4" t="n">
         <v>0</v>
@@ -48648,10 +48654,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>41.42</v>
+        <v>41.34</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>58.58</v>
+        <v>58.66</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48695,7 +48701,7 @@
         </is>
       </c>
       <c r="I468" s="4" t="n">
-        <v>-17.6</v>
+        <v>-17.83</v>
       </c>
       <c r="J468" s="4" t="n">
         <v>0.4</v>
@@ -48709,13 +48715,13 @@
         </is>
       </c>
       <c r="M468" s="4" t="n">
-        <v>-20.84</v>
+        <v>-21.07</v>
       </c>
       <c r="N468" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O468" s="4" t="n">
-        <v>-17.6</v>
+        <v>-17.83</v>
       </c>
       <c r="P468" s="4" t="n">
         <v>-1.15</v>
@@ -48746,10 +48752,10 @@
         <v>0</v>
       </c>
       <c r="AB468" s="4" t="n">
-        <v>41.2</v>
+        <v>41.08</v>
       </c>
       <c r="AC468" s="4" t="n">
-        <v>58.8</v>
+        <v>58.92</v>
       </c>
       <c r="AD468" s="4" t="n">
         <v>0</v>
@@ -48797,7 +48803,7 @@
         </is>
       </c>
       <c r="I469" s="4" t="n">
-        <v>-13.93</v>
+        <v>-14.16</v>
       </c>
       <c r="J469" s="4" t="n">
         <v>0.8</v>
@@ -48811,13 +48817,13 @@
         </is>
       </c>
       <c r="M469" s="4" t="n">
-        <v>-15.02</v>
+        <v>-15.25</v>
       </c>
       <c r="N469" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O469" s="4" t="n">
-        <v>-13.93</v>
+        <v>-14.16</v>
       </c>
       <c r="P469" s="4" t="n">
         <v>-1.66</v>
@@ -48848,10 +48854,10 @@
         <v>0</v>
       </c>
       <c r="AB469" s="4" t="n">
-        <v>43.04</v>
+        <v>42.92</v>
       </c>
       <c r="AC469" s="4" t="n">
-        <v>56.96</v>
+        <v>57.08</v>
       </c>
       <c r="AD469" s="4" t="n">
         <v>0</v>
@@ -49099,7 +49105,7 @@
         </is>
       </c>
       <c r="I472" s="4" t="n">
-        <v>-41</v>
+        <v>-41.63</v>
       </c>
       <c r="J472" s="4" t="n">
         <v>0</v>
@@ -49113,13 +49119,13 @@
         </is>
       </c>
       <c r="M472" s="4" t="n">
-        <v>-44.47</v>
+        <v>-45.1</v>
       </c>
       <c r="N472" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O472" s="4" t="n">
-        <v>-41</v>
+        <v>-41.63</v>
       </c>
       <c r="P472" s="4" t="n">
         <v>-1.27</v>
@@ -49150,10 +49156,10 @@
         <v>0</v>
       </c>
       <c r="AB472" s="4" t="n">
-        <v>29.5</v>
+        <v>29.19</v>
       </c>
       <c r="AC472" s="4" t="n">
-        <v>70.5</v>
+        <v>70.81</v>
       </c>
       <c r="AD472" s="4" t="n">
         <v>0</v>
@@ -49201,13 +49207,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.43</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>49.9</v>
+        <v>49</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>50.1</v>
+        <v>51</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49215,13 +49221,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.69</v>
+        <v>-10.92</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-1.84</v>
+        <v>-2.07</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.42</v>
@@ -49258,10 +49264,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.69</v>
+        <v>45.64</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.31</v>
+        <v>46.36</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49305,7 +49311,7 @@
         </is>
       </c>
       <c r="I474" s="4" t="n">
-        <v>-21.06</v>
+        <v>-21.11</v>
       </c>
       <c r="J474" s="4" t="n">
         <v>0.2</v>
@@ -49319,13 +49325,13 @@
         </is>
       </c>
       <c r="M474" s="4" t="n">
-        <v>-26.38</v>
+        <v>-26.39</v>
       </c>
       <c r="N474" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O474" s="4" t="n">
-        <v>-23.75</v>
+        <v>-23.76</v>
       </c>
       <c r="P474" s="4" t="n">
         <v>-3.2</v>
@@ -49362,10 +49368,10 @@
         <v>0</v>
       </c>
       <c r="AB474" s="4" t="n">
-        <v>39.47</v>
+        <v>39.45</v>
       </c>
       <c r="AC474" s="4" t="n">
-        <v>60.53</v>
+        <v>60.55</v>
       </c>
       <c r="AD474" s="4" t="n">
         <v>0</v>
@@ -49413,7 +49419,7 @@
         </is>
       </c>
       <c r="I475" s="4" t="n">
-        <v>-20.41</v>
+        <v>-19.89</v>
       </c>
       <c r="J475" s="4" t="n">
         <v>0.2</v>
@@ -49427,13 +49433,13 @@
         </is>
       </c>
       <c r="M475" s="4" t="n">
-        <v>-29.19</v>
+        <v>-26.45</v>
       </c>
       <c r="N475" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O475" s="4" t="n">
-        <v>-26.86</v>
+        <v>-24.11</v>
       </c>
       <c r="P475" s="4" t="n">
         <v>-0.87</v>
@@ -49445,16 +49451,16 @@
         <v>-31.57</v>
       </c>
       <c r="S475" s="4" t="n">
-        <v>42.86</v>
+        <v>35.66</v>
       </c>
       <c r="T475" s="4" t="n">
-        <v>46.25</v>
+        <v>50.6</v>
       </c>
       <c r="U475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V475" s="4" t="n">
-        <v>-6.27</v>
+        <v>-15.18</v>
       </c>
       <c r="W475" s="5" t="n">
         <v>2269114</v>
@@ -49470,10 +49476,10 @@
         <v>0</v>
       </c>
       <c r="AB475" s="4" t="n">
-        <v>39.8</v>
+        <v>40.05</v>
       </c>
       <c r="AC475" s="4" t="n">
-        <v>60.2</v>
+        <v>59.95</v>
       </c>
       <c r="AD475" s="4" t="n">
         <v>0</v>
@@ -49706,7 +49712,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Alexander Vindman</t>
+          <t>Angie Nixon</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -49725,13 +49731,13 @@
         </is>
       </c>
       <c r="I478" s="4" t="n">
-        <v>-5.31</v>
+        <v>-7.15</v>
       </c>
       <c r="J478" s="4" t="n">
-        <v>18.1</v>
+        <v>12</v>
       </c>
       <c r="K478" s="4" t="n">
-        <v>81.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="L478" t="inlineStr">
         <is>
@@ -49739,16 +49745,16 @@
         </is>
       </c>
       <c r="M478" s="4" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.58</v>
       </c>
       <c r="N478" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O478" s="4" t="n">
-        <v>-4.16</v>
+        <v>-6.15</v>
       </c>
       <c r="P478" s="4" t="n">
-        <v>0.26</v>
+        <v>-1.8</v>
       </c>
       <c r="Q478" s="4" t="n">
         <v>-1.67</v>
@@ -49757,19 +49763,19 @@
         <v>-13.22</v>
       </c>
       <c r="S478" s="4" t="n">
-        <v>41.56</v>
+        <v>40.04</v>
       </c>
       <c r="T478" s="4" t="n">
-        <v>47.23</v>
+        <v>49.3</v>
       </c>
       <c r="U478" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="V478" s="4" t="n">
-        <v>-6.85</v>
+        <v>-9.25</v>
       </c>
       <c r="W478" s="5" t="n">
-        <v>16273862</v>
+        <v>974845</v>
       </c>
       <c r="X478" s="5" t="n">
         <v>11259074</v>
@@ -49782,10 +49788,10 @@
         <v>0</v>
       </c>
       <c r="AB478" s="4" t="n">
-        <v>47.34</v>
+        <v>46.42</v>
       </c>
       <c r="AC478" s="4" t="n">
-        <v>52.66</v>
+        <v>53.58</v>
       </c>
       <c r="AD478" s="4" t="n">
         <v>0</v>
@@ -49994,10 +50000,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.72</v>
+        <v>47.71</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.65</v>
+        <v>49.66</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -50045,7 +50051,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-21.9</v>
+        <v>-21.98</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0.1</v>
@@ -50059,13 +50065,13 @@
         </is>
       </c>
       <c r="M481" s="4" t="n">
-        <v>-30.04</v>
+        <v>-30.08</v>
       </c>
       <c r="N481" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O481" s="4" t="n">
-        <v>-27.96</v>
+        <v>-28</v>
       </c>
       <c r="P481" s="4" t="n">
         <v>-1.14</v>
@@ -50100,7 +50106,7 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>39.05</v>
+        <v>39.01</v>
       </c>
       <c r="AA481" s="4" t="n">
         <v>0.1</v>
@@ -50109,7 +50115,7 @@
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>60.95</v>
+        <v>60.99</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -50255,13 +50261,13 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.73</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -50312,10 +50318,10 @@
         <v>0</v>
       </c>
       <c r="AB483" s="4" t="n">
-        <v>45.14</v>
+        <v>45.13</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>54.86</v>
+        <v>54.87</v>
       </c>
       <c r="AD483" s="4" t="n">
         <v>0</v>
@@ -50565,7 +50571,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>29.42</v>
+        <v>29.46</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -50579,7 +50585,7 @@
         </is>
       </c>
       <c r="M486" s="4" t="n">
-        <v>28.36</v>
+        <v>28.37</v>
       </c>
       <c r="N486" s="4" t="n">
         <v>5.38</v>
@@ -50622,10 +50628,10 @@
         <v>0</v>
       </c>
       <c r="AB486" s="4" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>35.29</v>
+        <v>35.27</v>
       </c>
       <c r="AD486" s="4" t="n">
         <v>0</v>
@@ -50673,13 +50679,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50777,13 +50783,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>30.6</v>
+        <v>28.7</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -50791,13 +50797,13 @@
         </is>
       </c>
       <c r="M488" s="4" t="n">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="N488" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O488" s="4" t="n">
-        <v>7.37</v>
+        <v>7.55</v>
       </c>
       <c r="P488" s="4" t="n">
         <v>-0.31</v>
@@ -50809,16 +50815,16 @@
         <v>-1.44</v>
       </c>
       <c r="S488" s="4" t="n">
-        <v>45.71</v>
+        <v>45.47</v>
       </c>
       <c r="T488" s="4" t="n">
-        <v>47.84</v>
+        <v>46.93</v>
       </c>
       <c r="U488" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V488" s="4" t="n">
-        <v>-2.29</v>
+        <v>-1.22</v>
       </c>
       <c r="W488" s="5" t="n">
         <v>14514336</v>
@@ -50834,10 +50840,10 @@
         <v>0</v>
       </c>
       <c r="AB488" s="4" t="n">
-        <v>50.97</v>
+        <v>51.21</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>49.03</v>
+        <v>48.79</v>
       </c>
       <c r="AD488" s="4" t="n">
         <v>0</v>
@@ -51097,7 +51103,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.52</v>
+        <v>-27.36</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51152,16 +51158,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.29</v>
+        <v>14.39</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>27.27</v>
+        <v>27.29</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>54.79</v>
+        <v>54.65</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51205,7 +51211,7 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>7.62</v>
+        <v>7.6</v>
       </c>
       <c r="J492" s="4" t="n">
         <v>89.40000000000001</v>
@@ -51368,7 +51374,7 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>47.81</v>
+        <v>47.8</v>
       </c>
       <c r="AA493" s="4" t="n">
         <v>21.3</v>
@@ -51377,7 +51383,7 @@
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>52.19</v>
+        <v>52.2</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -51435,13 +51441,13 @@
         </is>
       </c>
       <c r="M494" s="4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="N494" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O494" s="4" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="P494" s="4" t="n">
         <v>0.71</v>
@@ -51682,10 +51688,10 @@
         <v>0</v>
       </c>
       <c r="AB496" s="4" t="n">
-        <v>59.56</v>
+        <v>59.57</v>
       </c>
       <c r="AC496" s="4" t="n">
-        <v>40.44</v>
+        <v>40.43</v>
       </c>
       <c r="AD496" s="4" t="n">
         <v>0</v>
@@ -51733,7 +51739,7 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J497" s="4" t="n">
         <v>69</v>
@@ -52041,7 +52047,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>23.85</v>
+        <v>23.87</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -52098,10 +52104,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.92</v>
+        <v>61.93</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.08</v>
+        <v>38.07</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -52145,13 +52151,13 @@
         </is>
       </c>
       <c r="I501" s="4" t="n">
-        <v>-7.61</v>
+        <v>-7.58</v>
       </c>
       <c r="J501" s="4" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="K501" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -52202,10 +52208,10 @@
         <v>0</v>
       </c>
       <c r="AB501" s="4" t="n">
-        <v>45.33</v>
+        <v>45.35</v>
       </c>
       <c r="AC501" s="4" t="n">
-        <v>52.8</v>
+        <v>52.78</v>
       </c>
       <c r="AD501" s="4" t="n">
         <v>1.87</v>
@@ -52253,7 +52259,7 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-20.96</v>
+        <v>-20.97</v>
       </c>
       <c r="J502" s="4" t="n">
         <v>0.2</v>
@@ -52308,7 +52314,7 @@
         </is>
       </c>
       <c r="Z502" s="4" t="n">
-        <v>39.52</v>
+        <v>39.51</v>
       </c>
       <c r="AA502" s="4" t="n">
         <v>0.2</v>
@@ -52317,7 +52323,7 @@
         <v>0</v>
       </c>
       <c r="AC502" s="4" t="n">
-        <v>60.48</v>
+        <v>60.49</v>
       </c>
       <c r="AD502" s="4" t="n">
         <v>0</v>
@@ -52477,7 +52483,7 @@
         </is>
       </c>
       <c r="M504" s="4" t="n">
-        <v>-10.15</v>
+        <v>-10.16</v>
       </c>
       <c r="N504" s="4" t="n">
         <v>5.38</v>
@@ -52520,10 +52526,10 @@
         <v>0</v>
       </c>
       <c r="AB504" s="4" t="n">
-        <v>49.52</v>
+        <v>49.51</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>48.47</v>
+        <v>48.48</v>
       </c>
       <c r="AD504" s="4" t="n">
         <v>2.01</v>
@@ -52771,7 +52777,7 @@
         </is>
       </c>
       <c r="I507" s="4" t="n">
-        <v>-42.91</v>
+        <v>-43.54</v>
       </c>
       <c r="J507" s="4" t="n">
         <v>0</v>
@@ -52785,13 +52791,13 @@
         </is>
       </c>
       <c r="M507" s="4" t="n">
-        <v>-44.91</v>
+        <v>-45.54</v>
       </c>
       <c r="N507" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O507" s="4" t="n">
-        <v>-42.91</v>
+        <v>-43.54</v>
       </c>
       <c r="P507" s="4" t="n">
         <v>-2.75</v>
@@ -52822,10 +52828,10 @@
         <v>0</v>
       </c>
       <c r="AB507" s="4" t="n">
-        <v>28.54</v>
+        <v>28.23</v>
       </c>
       <c r="AC507" s="4" t="n">
-        <v>71.45999999999999</v>
+        <v>71.77</v>
       </c>
       <c r="AD507" s="4" t="n">
         <v>0</v>
@@ -53050,7 +53056,7 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="K3" t="n">
         <v>9</v>
@@ -53229,19 +53235,19 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
         <v>16</v>
       </c>
       <c r="M6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -53287,7 +53293,7 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="K7" t="n">
         <v>7</v>
@@ -53473,7 +53479,7 @@
         <v>71</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -53522,7 +53528,7 @@
         <v>31.3</v>
       </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
         <v>27</v>
@@ -53925,7 +53931,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="K18" t="n">
         <v>47</v>
@@ -53937,7 +53943,7 @@
         <v>75</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>19.2</v>
+        <v>18.4</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -53995,7 +54001,7 @@
         <v>19</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -55259,7 +55265,7 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>58.5</v>
+        <v>58.7</v>
       </c>
       <c r="K41" t="n">
         <v>57</v>
@@ -55271,7 +55277,7 @@
         <v>79</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>57.7</v>
+        <v>58.5</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -55317,7 +55323,7 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="K42" t="n">
         <v>22</v>
@@ -55326,10 +55332,10 @@
         <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>70</v>
+        <v>70.7</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -55607,7 +55613,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="K47" t="n">
         <v>41</v>
@@ -55616,7 +55622,7 @@
         <v>26</v>
       </c>
       <c r="M47" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>7.8</v>
@@ -57753,7 +57759,7 @@
         </is>
       </c>
       <c r="J84" s="4" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="K84" t="n">
         <v>50</v>
@@ -57762,10 +57768,10 @@
         <v>37</v>
       </c>
       <c r="M84" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>50.9</v>
+        <v>50.3</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -57823,7 +57829,7 @@
         <v>21</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>64.3</v>
+        <v>63.8</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -57985,7 +57991,7 @@
         </is>
       </c>
       <c r="J88" s="4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="K88" t="n">
         <v>7</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>56.7</v>
+        <v>56.3</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233.3</v>
+        <v>233.1</v>
       </c>
       <c r="C9" t="n">
-        <v>201.7</v>
+        <v>201.9</v>
       </c>
       <c r="D9" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>82.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="C10" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="D10" t="n">
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>39.4</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-4.38</v>
+        <v>-4.13</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>35.5</v>
+        <v>37</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>64.5</v>
+        <v>63</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>88.2</v>
+        <v>88.3</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
         <v>42.01</v>
       </c>
       <c r="U5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>5.86</v>
+        <v>5.87</v>
       </c>
       <c r="W5" s="5" t="n">
         <v>9827820</v>
@@ -1666,10 +1666,10 @@
         <v>-5.81</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>43.16</v>
       </c>
       <c r="U9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V9" s="4" t="n">
         <v>-4.38</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-36.75</v>
+        <v>-36.82</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -2113,16 +2113,16 @@
         <v>-37.52</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>29.67</v>
+        <v>29</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-24.33</v>
+        <v>-24.5</v>
       </c>
       <c r="W13" s="5" t="n">
         <v>136953</v>
@@ -2138,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>31.62</v>
+        <v>31.59</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>68.38</v>
+        <v>68.41</v>
       </c>
       <c r="AD13" s="4" t="n">
         <v>0</v>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>33.93</v>
+        <v>32.37</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>100</v>
@@ -2535,16 +2535,16 @@
         <v>29.51</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>57.82</v>
+        <v>58</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>30.93</v>
+        <v>31</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>23.95</v>
+        <v>24</v>
       </c>
       <c r="W17" s="5" t="n">
         <v>0</v>
@@ -2560,10 +2560,10 @@
         <v>0</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>66.97</v>
+        <v>66.19</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>33.03</v>
+        <v>33.81</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.95</v>
+        <v>10.93</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>98</v>
@@ -2753,7 +2753,7 @@
         <v>42.49</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V19" s="4" t="n">
         <v>7.54</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>55.48</v>
+        <v>55.47</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>44.52</v>
+        <v>44.53</v>
       </c>
       <c r="AD19" s="4" t="n">
         <v>0</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-10.76</v>
+        <v>-10.84</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>97.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44.73</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V22" s="4" t="n">
         <v>-6.56</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>44.62</v>
+        <v>44.58</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>55.38</v>
+        <v>55.42</v>
       </c>
       <c r="AD22" s="4" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>16</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>12.55</v>
+        <v>12.56</v>
       </c>
       <c r="W25" s="5" t="n">
         <v>16594119</v>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-20.92</v>
+        <v>-20.76</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>0.2</v>
@@ -4223,16 +4223,16 @@
         <v>-30.12</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>27.01</v>
+        <v>27</v>
       </c>
       <c r="T33" s="4" t="n">
         <v>51</v>
       </c>
       <c r="U33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-23.99</v>
+        <v>-24</v>
       </c>
       <c r="W33" s="5" t="n">
         <v>0</v>
@@ -4248,10 +4248,10 @@
         <v>0</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>39.54</v>
+        <v>39.62</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>60.46</v>
+        <v>60.38</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.79</v>
+        <v>-6.76</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>13.2</v>
@@ -4337,7 +4337,7 @@
         <v>48.73</v>
       </c>
       <c r="U34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V34" s="4" t="n">
         <v>-3.97</v>
@@ -4356,10 +4356,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>46.61</v>
+        <v>46.62</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>53.39</v>
+        <v>53.38</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4511,13 +4511,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>3.32</v>
+        <v>2.92</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>74.7</v>
+        <v>73.2</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>25.3</v>
+        <v>26.8</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4543,16 +4543,16 @@
         <v>-0.87</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>47.71</v>
+        <v>47.21</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>43.88</v>
+        <v>43.73</v>
       </c>
       <c r="U36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>3.88</v>
+        <v>3.05</v>
       </c>
       <c r="W36" s="5" t="n">
         <v>1426778</v>
@@ -4568,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>51.66</v>
+        <v>51.46</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>48.34</v>
+        <v>48.54</v>
       </c>
       <c r="AD36" s="4" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-5.2</v>
+        <v>-5.22</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>18.4</v>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.71</v>
+        <v>-2.74</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.13</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.04</v>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>47.4</v>
+        <v>47.39</v>
       </c>
       <c r="AA38" s="4" t="n">
         <v>18.4</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>52.6</v>
+        <v>52.61</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -6012,10 +6012,10 @@
         <v>0</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>51.42</v>
+        <v>51.43</v>
       </c>
       <c r="AC50" s="4" t="n">
-        <v>46.7</v>
+        <v>46.69</v>
       </c>
       <c r="AD50" s="4" t="n">
         <v>1.88</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>61.8</v>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>-10.19</v>
+        <v>-10.18</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>5.38</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>60.59</v>
+        <v>60.6</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>100</v>
@@ -6191,7 +6191,7 @@
         <v>5.38</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>60.59</v>
+        <v>60.6</v>
       </c>
       <c r="P52" s="4" t="n">
         <v>0</v>
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>20.09</v>
+        <v>20.1</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>99.8</v>
@@ -6293,7 +6293,7 @@
         <v>5.38</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>20.09</v>
+        <v>20.1</v>
       </c>
       <c r="P53" s="4" t="n">
         <v>0.99</v>
@@ -6473,13 +6473,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5.06</v>
+        <v>4.92</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>81</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>5.38</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>6.11</v>
+        <v>6.12</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0.13</v>
@@ -6505,16 +6505,16 @@
         <v>-0.76</v>
       </c>
       <c r="S55" s="4" t="n">
-        <v>46.6</v>
+        <v>46.96</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>44.6</v>
+        <v>44.87</v>
       </c>
       <c r="U55" t="n">
         <v>3</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>0.1</v>
+        <v>-0.29</v>
       </c>
       <c r="W55" s="5" t="n">
         <v>7354599</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>51.41</v>
+        <v>51.35</v>
       </c>
       <c r="AC55" s="4" t="n">
-        <v>46.47</v>
+        <v>46.53</v>
       </c>
       <c r="AD55" s="4" t="n">
         <v>2.12</v>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>39.51</v>
+        <v>39.52</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>100</v>
@@ -6601,7 +6601,7 @@
         <v>5.38</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>39.51</v>
+        <v>39.52</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>1.53</v>
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="M58" s="4" t="n">
-        <v>-27.03</v>
+        <v>-27.02</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>5.38</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>5.73</v>
+        <v>5.75</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>83.40000000000001</v>
@@ -9059,7 +9059,7 @@
         <v>44</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V80" s="4" t="n">
         <v>1</v>
@@ -9078,10 +9078,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>52.86</v>
+        <v>52.87</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47.14</v>
+        <v>47.13</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -12383,13 +12383,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>-2.28</v>
+        <v>-2.4</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>29.3</v>
+        <v>28.8</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>70.7</v>
+        <v>71.2</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -12415,16 +12415,16 @@
         <v>-9.98</v>
       </c>
       <c r="S113" s="4" t="n">
-        <v>44.68</v>
+        <v>45</v>
       </c>
       <c r="T113" s="4" t="n">
-        <v>46.04</v>
+        <v>46</v>
       </c>
       <c r="U113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V113" s="4" t="n">
-        <v>-4.12</v>
+        <v>-4</v>
       </c>
       <c r="W113" s="5" t="n">
         <v>716276</v>
@@ -12440,10 +12440,10 @@
         <v>0</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>48.86</v>
+        <v>48.8</v>
       </c>
       <c r="AC113" s="4" t="n">
-        <v>51.14</v>
+        <v>51.2</v>
       </c>
       <c r="AD113" s="4" t="n">
         <v>0</v>
@@ -16065,13 +16065,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>6.87</v>
+        <v>6.63</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -16097,16 +16097,16 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="S149" s="4" t="n">
-        <v>47.36</v>
+        <v>42.9</v>
       </c>
       <c r="T149" s="4" t="n">
-        <v>36.17</v>
+        <v>32.7</v>
       </c>
       <c r="U149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V149" s="4" t="n">
-        <v>8.19</v>
+        <v>7.2</v>
       </c>
       <c r="W149" s="5" t="n">
         <v>2998428</v>
@@ -16122,10 +16122,10 @@
         <v>0</v>
       </c>
       <c r="AB149" s="4" t="n">
-        <v>53.44</v>
+        <v>53.31</v>
       </c>
       <c r="AC149" s="4" t="n">
-        <v>46.56</v>
+        <v>46.69</v>
       </c>
       <c r="AD149" s="4" t="n">
         <v>0</v>
@@ -18107,13 +18107,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11.65</v>
+        <v>11.32</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -18121,13 +18121,13 @@
         </is>
       </c>
       <c r="M169" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="N169" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O169" s="4" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="P169" s="4" t="n">
         <v>0</v>
@@ -18164,10 +18164,10 @@
         <v>0</v>
       </c>
       <c r="AB169" s="4" t="n">
-        <v>55.82</v>
+        <v>55.66</v>
       </c>
       <c r="AC169" s="4" t="n">
-        <v>44.18</v>
+        <v>44.34</v>
       </c>
       <c r="AD169" s="4" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>66.7</v>
@@ -18225,13 +18225,13 @@
         </is>
       </c>
       <c r="M170" s="4" t="n">
-        <v>-2.5</v>
+        <v>-2.49</v>
       </c>
       <c r="N170" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="P170" s="4" t="n">
         <v>-0.03</v>
@@ -18319,13 +18319,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>5.16</v>
+        <v>4.97</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>18.6</v>
+        <v>19.3</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -18333,13 +18333,13 @@
         </is>
       </c>
       <c r="M171" s="4" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="N171" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>6.36</v>
+        <v>6.37</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.06</v>
@@ -18351,16 +18351,16 @@
         <v>-4.46</v>
       </c>
       <c r="S171" s="4" t="n">
-        <v>42.61</v>
+        <v>42</v>
       </c>
       <c r="T171" s="4" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="U171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V171" s="4" t="n">
-        <v>-0.48</v>
+        <v>-3</v>
       </c>
       <c r="W171" s="5" t="n">
         <v>5293773</v>
@@ -18376,10 +18376,10 @@
         <v>0</v>
       </c>
       <c r="AB171" s="4" t="n">
-        <v>52.58</v>
+        <v>52.48</v>
       </c>
       <c r="AC171" s="4" t="n">
-        <v>47.42</v>
+        <v>47.52</v>
       </c>
       <c r="AD171" s="4" t="n">
         <v>0</v>
@@ -18423,7 +18423,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-20.81</v>
+        <v>-20.8</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.2</v>
@@ -18437,13 +18437,13 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-24.48</v>
+        <v>-24.47</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-20.81</v>
+        <v>-20.8</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -18525,7 +18525,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-26.34</v>
+        <v>-26.35</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18539,13 +18539,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-41.37</v>
+        <v>-41.39</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-38.69</v>
+        <v>-38.71</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-25.33</v>
+        <v>-25.34</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0.1</v>
@@ -18647,13 +18647,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-23.56</v>
+        <v>-23.58</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-25.33</v>
+        <v>-25.34</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -18684,10 +18684,10 @@
         <v>0</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>37.34</v>
+        <v>37.33</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>62.66</v>
+        <v>62.67</v>
       </c>
       <c r="AD174" s="4" t="n">
         <v>0</v>
@@ -21379,7 +21379,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-31.84</v>
+        <v>-31.8</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0</v>
@@ -21393,13 +21393,13 @@
         </is>
       </c>
       <c r="M201" s="4" t="n">
-        <v>-29.41</v>
+        <v>-29.36</v>
       </c>
       <c r="N201" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-31.84</v>
+        <v>-31.8</v>
       </c>
       <c r="P201" s="4" t="n">
         <v>-2.06</v>
@@ -21430,10 +21430,10 @@
         <v>0</v>
       </c>
       <c r="AB201" s="4" t="n">
-        <v>34.08</v>
+        <v>34.1</v>
       </c>
       <c r="AC201" s="4" t="n">
-        <v>65.92</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AD201" s="4" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-17.66</v>
+        <v>-17.61</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>0.4</v>
@@ -21495,13 +21495,13 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-16.99</v>
+        <v>-16.94</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>-17.66</v>
+        <v>-17.61</v>
       </c>
       <c r="P202" s="4" t="n">
         <v>-0.47</v>
@@ -21532,10 +21532,10 @@
         <v>0</v>
       </c>
       <c r="AB202" s="4" t="n">
-        <v>41.17</v>
+        <v>41.19</v>
       </c>
       <c r="AC202" s="4" t="n">
-        <v>58.83</v>
+        <v>58.81</v>
       </c>
       <c r="AD202" s="4" t="n">
         <v>0</v>
@@ -21583,7 +21583,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>21.11</v>
+        <v>21.15</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>99.8</v>
@@ -21597,13 +21597,13 @@
         </is>
       </c>
       <c r="M203" s="4" t="n">
-        <v>5.99</v>
+        <v>6.04</v>
       </c>
       <c r="N203" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>21.11</v>
+        <v>21.15</v>
       </c>
       <c r="P203" s="4" t="n">
         <v>3</v>
@@ -21634,10 +21634,10 @@
         <v>0</v>
       </c>
       <c r="AB203" s="4" t="n">
-        <v>60.55</v>
+        <v>60.58</v>
       </c>
       <c r="AC203" s="4" t="n">
-        <v>39.45</v>
+        <v>39.42</v>
       </c>
       <c r="AD203" s="4" t="n">
         <v>0</v>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-23.12</v>
+        <v>-23.07</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>0.1</v>
@@ -21699,13 +21699,13 @@
         </is>
       </c>
       <c r="M204" s="4" t="n">
-        <v>-21.37</v>
+        <v>-21.32</v>
       </c>
       <c r="N204" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>-23.12</v>
+        <v>-23.07</v>
       </c>
       <c r="P204" s="4" t="n">
         <v>-1.43</v>
@@ -21736,10 +21736,10 @@
         <v>0</v>
       </c>
       <c r="AB204" s="4" t="n">
-        <v>38.44</v>
+        <v>38.46</v>
       </c>
       <c r="AC204" s="4" t="n">
-        <v>61.56</v>
+        <v>61.54</v>
       </c>
       <c r="AD204" s="4" t="n">
         <v>0</v>
@@ -21787,7 +21787,7 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>-46.01</v>
+        <v>-45.96</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>0</v>
@@ -21801,13 +21801,13 @@
         </is>
       </c>
       <c r="M205" s="4" t="n">
-        <v>-46.26</v>
+        <v>-46.2</v>
       </c>
       <c r="N205" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O205" s="4" t="n">
-        <v>-46.01</v>
+        <v>-45.96</v>
       </c>
       <c r="P205" s="4" t="n">
         <v>-1.84</v>
@@ -21838,10 +21838,10 @@
         <v>0</v>
       </c>
       <c r="AB205" s="4" t="n">
-        <v>26.99</v>
+        <v>27.02</v>
       </c>
       <c r="AC205" s="4" t="n">
-        <v>73.01000000000001</v>
+        <v>72.98</v>
       </c>
       <c r="AD205" s="4" t="n">
         <v>0</v>
@@ -21889,7 +21889,7 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>-43.69</v>
+        <v>-43.63</v>
       </c>
       <c r="J206" s="4" t="n">
         <v>0</v>
@@ -21903,13 +21903,13 @@
         </is>
       </c>
       <c r="M206" s="4" t="n">
-        <v>-40.36</v>
+        <v>-40.31</v>
       </c>
       <c r="N206" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O206" s="4" t="n">
-        <v>-43.69</v>
+        <v>-43.63</v>
       </c>
       <c r="P206" s="4" t="n">
         <v>-3.32</v>
@@ -21940,10 +21940,10 @@
         <v>0</v>
       </c>
       <c r="AB206" s="4" t="n">
-        <v>28.16</v>
+        <v>28.18</v>
       </c>
       <c r="AC206" s="4" t="n">
-        <v>71.84</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="AD206" s="4" t="n">
         <v>0</v>
@@ -21991,7 +21991,7 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>33.27</v>
+        <v>33.32</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>100</v>
@@ -22005,13 +22005,13 @@
         </is>
       </c>
       <c r="M207" s="4" t="n">
-        <v>20.39</v>
+        <v>20.44</v>
       </c>
       <c r="N207" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O207" s="4" t="n">
-        <v>33.27</v>
+        <v>33.32</v>
       </c>
       <c r="P207" s="4" t="n">
         <v>2.21</v>
@@ -22042,10 +22042,10 @@
         <v>0</v>
       </c>
       <c r="AB207" s="4" t="n">
-        <v>66.63</v>
+        <v>66.66</v>
       </c>
       <c r="AC207" s="4" t="n">
-        <v>33.37</v>
+        <v>33.34</v>
       </c>
       <c r="AD207" s="4" t="n">
         <v>0</v>
@@ -22089,7 +22089,7 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>-31.05</v>
+        <v>-31</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>0</v>
@@ -22103,13 +22103,13 @@
         </is>
       </c>
       <c r="M208" s="4" t="n">
-        <v>-35.14</v>
+        <v>-35.08</v>
       </c>
       <c r="N208" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O208" s="4" t="n">
-        <v>-31.05</v>
+        <v>-31</v>
       </c>
       <c r="P208" s="4" t="n">
         <v>-0.46</v>
@@ -22140,10 +22140,10 @@
         <v>0</v>
       </c>
       <c r="AB208" s="4" t="n">
-        <v>34.47</v>
+        <v>34.5</v>
       </c>
       <c r="AC208" s="4" t="n">
-        <v>65.53</v>
+        <v>65.5</v>
       </c>
       <c r="AD208" s="4" t="n">
         <v>0</v>
@@ -22191,7 +22191,7 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>-61.21</v>
+        <v>-61.15</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>0</v>
@@ -22205,13 +22205,13 @@
         </is>
       </c>
       <c r="M209" s="4" t="n">
-        <v>-62.92</v>
+        <v>-62.87</v>
       </c>
       <c r="N209" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O209" s="4" t="n">
-        <v>-61.21</v>
+        <v>-61.15</v>
       </c>
       <c r="P209" s="4" t="n">
         <v>-1.02</v>
@@ -22242,10 +22242,10 @@
         <v>0</v>
       </c>
       <c r="AB209" s="4" t="n">
-        <v>19.4</v>
+        <v>19.42</v>
       </c>
       <c r="AC209" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>80.58</v>
       </c>
       <c r="AD209" s="4" t="n">
         <v>0</v>
@@ -22289,13 +22289,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-6.99</v>
+        <v>-6.96</v>
       </c>
       <c r="J210" s="4" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -22303,13 +22303,13 @@
         </is>
       </c>
       <c r="M210" s="4" t="n">
-        <v>-14.12</v>
+        <v>-14.06</v>
       </c>
       <c r="N210" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O210" s="4" t="n">
-        <v>-9.42</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="P210" s="4" t="n">
         <v>-0.01</v>
@@ -22346,10 +22346,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.5</v>
+        <v>46.52</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.5</v>
+        <v>53.48</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -23915,13 +23915,13 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>-15.8</v>
+        <v>-16.19</v>
       </c>
       <c r="J226" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K226" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -23929,13 +23929,13 @@
         </is>
       </c>
       <c r="M226" s="4" t="n">
-        <v>-16.13</v>
+        <v>-16.52</v>
       </c>
       <c r="N226" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O226" s="4" t="n">
-        <v>-15.8</v>
+        <v>-16.19</v>
       </c>
       <c r="P226" s="4" t="n">
         <v>-0.86</v>
@@ -23966,10 +23966,10 @@
         <v>0</v>
       </c>
       <c r="AB226" s="4" t="n">
-        <v>42.1</v>
+        <v>41.91</v>
       </c>
       <c r="AC226" s="4" t="n">
-        <v>57.9</v>
+        <v>58.09</v>
       </c>
       <c r="AD226" s="4" t="n">
         <v>0</v>
@@ -24017,7 +24017,7 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>31.32</v>
+        <v>30.92</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>100</v>
@@ -24031,13 +24031,13 @@
         </is>
       </c>
       <c r="M227" s="4" t="n">
-        <v>20.1</v>
+        <v>19.71</v>
       </c>
       <c r="N227" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O227" s="4" t="n">
-        <v>31.32</v>
+        <v>30.92</v>
       </c>
       <c r="P227" s="4" t="n">
         <v>2.06</v>
@@ -24068,10 +24068,10 @@
         <v>0</v>
       </c>
       <c r="AB227" s="4" t="n">
-        <v>65.66</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="AC227" s="4" t="n">
-        <v>34.34</v>
+        <v>34.54</v>
       </c>
       <c r="AD227" s="4" t="n">
         <v>0</v>
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>32.87</v>
+        <v>32.48</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>100</v>
@@ -24133,13 +24133,13 @@
         </is>
       </c>
       <c r="M228" s="4" t="n">
-        <v>25.31</v>
+        <v>24.92</v>
       </c>
       <c r="N228" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O228" s="4" t="n">
-        <v>32.87</v>
+        <v>32.48</v>
       </c>
       <c r="P228" s="4" t="n">
         <v>0</v>
@@ -24170,10 +24170,10 @@
         <v>0</v>
       </c>
       <c r="AB228" s="4" t="n">
-        <v>66.44</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AC228" s="4" t="n">
-        <v>33.56</v>
+        <v>33.76</v>
       </c>
       <c r="AD228" s="4" t="n">
         <v>0</v>
@@ -24217,7 +24217,7 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>85.11</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>100</v>
@@ -24231,13 +24231,13 @@
         </is>
       </c>
       <c r="M229" s="4" t="n">
-        <v>78.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="N229" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O229" s="4" t="n">
-        <v>85.11</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="P229" s="4" t="n">
         <v>0</v>
@@ -24268,10 +24268,10 @@
         <v>0</v>
       </c>
       <c r="AB229" s="4" t="n">
-        <v>92.55</v>
+        <v>92.36</v>
       </c>
       <c r="AC229" s="4" t="n">
-        <v>7.45</v>
+        <v>7.64</v>
       </c>
       <c r="AD229" s="4" t="n">
         <v>0</v>
@@ -24315,7 +24315,7 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>40.01</v>
+        <v>39.62</v>
       </c>
       <c r="J230" s="4" t="n">
         <v>100</v>
@@ -24329,13 +24329,13 @@
         </is>
       </c>
       <c r="M230" s="4" t="n">
-        <v>35.21</v>
+        <v>34.81</v>
       </c>
       <c r="N230" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O230" s="4" t="n">
-        <v>40.01</v>
+        <v>39.62</v>
       </c>
       <c r="P230" s="4" t="n">
         <v>0</v>
@@ -24366,10 +24366,10 @@
         <v>0</v>
       </c>
       <c r="AB230" s="4" t="n">
-        <v>70</v>
+        <v>69.81</v>
       </c>
       <c r="AC230" s="4" t="n">
-        <v>30</v>
+        <v>30.19</v>
       </c>
       <c r="AD230" s="4" t="n">
         <v>0</v>
@@ -24417,7 +24417,7 @@
         </is>
       </c>
       <c r="I231" s="4" t="n">
-        <v>19.34</v>
+        <v>18.95</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>99.7</v>
@@ -24431,13 +24431,13 @@
         </is>
       </c>
       <c r="M231" s="4" t="n">
-        <v>7.58</v>
+        <v>7.19</v>
       </c>
       <c r="N231" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O231" s="4" t="n">
-        <v>19.34</v>
+        <v>18.95</v>
       </c>
       <c r="P231" s="4" t="n">
         <v>2.47</v>
@@ -24468,10 +24468,10 @@
         <v>0</v>
       </c>
       <c r="AB231" s="4" t="n">
-        <v>59.67</v>
+        <v>59.47</v>
       </c>
       <c r="AC231" s="4" t="n">
-        <v>40.33</v>
+        <v>40.53</v>
       </c>
       <c r="AD231" s="4" t="n">
         <v>0</v>
@@ -24519,7 +24519,7 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>72.08</v>
+        <v>71.69</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>100</v>
@@ -24533,13 +24533,13 @@
         </is>
       </c>
       <c r="M232" s="4" t="n">
-        <v>62.68</v>
+        <v>62.29</v>
       </c>
       <c r="N232" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O232" s="4" t="n">
-        <v>72.08</v>
+        <v>71.69</v>
       </c>
       <c r="P232" s="4" t="n">
         <v>0</v>
@@ -24570,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="AB232" s="4" t="n">
-        <v>86.04000000000001</v>
+        <v>85.84</v>
       </c>
       <c r="AC232" s="4" t="n">
-        <v>13.96</v>
+        <v>14.16</v>
       </c>
       <c r="AD232" s="4" t="n">
         <v>0</v>
@@ -24621,7 +24621,7 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>69.56999999999999</v>
+        <v>69.17</v>
       </c>
       <c r="J233" s="4" t="n">
         <v>100</v>
@@ -24635,13 +24635,13 @@
         </is>
       </c>
       <c r="M233" s="4" t="n">
-        <v>60.53</v>
+        <v>60.13</v>
       </c>
       <c r="N233" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O233" s="4" t="n">
-        <v>69.56999999999999</v>
+        <v>69.17</v>
       </c>
       <c r="P233" s="4" t="n">
         <v>3.54</v>
@@ -24672,10 +24672,10 @@
         <v>0</v>
       </c>
       <c r="AB233" s="4" t="n">
-        <v>84.78</v>
+        <v>84.59</v>
       </c>
       <c r="AC233" s="4" t="n">
-        <v>15.22</v>
+        <v>15.41</v>
       </c>
       <c r="AD233" s="4" t="n">
         <v>0</v>
@@ -24723,7 +24723,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>31.01</v>
+        <v>30.06</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24737,13 +24737,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>21.89</v>
+        <v>21.9</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>31.1</v>
+        <v>31.11</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24774,10 +24774,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.27</v>
+        <v>62.28</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.73</v>
+        <v>32.72</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24821,13 +24821,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-3.97</v>
+        <v>-3.66</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>36.2</v>
+        <v>39.1</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>63.8</v>
+        <v>60.9</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24853,16 +24853,16 @@
         <v>-9.720000000000001</v>
       </c>
       <c r="S235" s="4" t="n">
-        <v>47.29</v>
+        <v>47.91</v>
       </c>
       <c r="T235" s="4" t="n">
-        <v>48.12</v>
+        <v>48.13</v>
       </c>
       <c r="U235" t="n">
         <v>3</v>
       </c>
       <c r="V235" s="4" t="n">
-        <v>-2.56</v>
+        <v>-2.42</v>
       </c>
       <c r="W235" s="5" t="n">
         <v>1205432</v>
@@ -24878,10 +24878,10 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>45.35</v>
+        <v>45.38</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>49.65</v>
+        <v>49.62</v>
       </c>
       <c r="AD235" s="4" t="n">
         <v>5</v>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="M237" s="4" t="n">
-        <v>-26.74</v>
+        <v>-26.75</v>
       </c>
       <c r="N237" s="4" t="n">
         <v>5.38</v>
@@ -25133,7 +25133,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>21.1</v>
+        <v>21.09</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25147,13 +25147,13 @@
         </is>
       </c>
       <c r="M238" s="4" t="n">
-        <v>10.92</v>
+        <v>10.91</v>
       </c>
       <c r="N238" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>21.1</v>
+        <v>21.09</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>0.95</v>
@@ -25235,13 +25235,13 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>-2</v>
+        <v>-2.04</v>
       </c>
       <c r="J239" s="4" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -25249,13 +25249,13 @@
         </is>
       </c>
       <c r="M239" s="4" t="n">
-        <v>-2.24</v>
+        <v>-2.25</v>
       </c>
       <c r="N239" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-2.6</v>
+        <v>-2.61</v>
       </c>
       <c r="P239" s="4" t="n">
         <v>-0.28</v>
@@ -25267,16 +25267,16 @@
         <v>-5.61</v>
       </c>
       <c r="S239" s="4" t="n">
-        <v>47.07</v>
+        <v>47.46</v>
       </c>
       <c r="T239" s="4" t="n">
-        <v>45.06</v>
+        <v>45.22</v>
       </c>
       <c r="U239" t="n">
         <v>3</v>
       </c>
       <c r="V239" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="W239" s="5" t="n">
         <v>2620011</v>
@@ -25292,10 +25292,10 @@
         <v>0</v>
       </c>
       <c r="AB239" s="4" t="n">
-        <v>49</v>
+        <v>48.98</v>
       </c>
       <c r="AC239" s="4" t="n">
-        <v>51</v>
+        <v>51.02</v>
       </c>
       <c r="AD239" s="4" t="n">
         <v>0</v>
@@ -25343,7 +25343,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-26.06</v>
+        <v>-26.07</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0</v>
@@ -25363,7 +25363,7 @@
         <v>5.38</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-26.06</v>
+        <v>-26.07</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.12</v>
@@ -25445,7 +25445,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>38.1</v>
+        <v>38.09</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>100</v>
@@ -25465,7 +25465,7 @@
         <v>5.38</v>
       </c>
       <c r="O241" s="4" t="n">
-        <v>38.1</v>
+        <v>38.09</v>
       </c>
       <c r="P241" s="4" t="n">
         <v>0</v>
@@ -25561,7 +25561,7 @@
         </is>
       </c>
       <c r="M242" s="4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="N242" s="4" t="n">
         <v>5.38</v>
@@ -25604,10 +25604,10 @@
         <v>0</v>
       </c>
       <c r="AB242" s="4" t="n">
-        <v>50.63</v>
+        <v>50.62</v>
       </c>
       <c r="AC242" s="4" t="n">
-        <v>49.37</v>
+        <v>49.38</v>
       </c>
       <c r="AD242" s="4" t="n">
         <v>0</v>
@@ -25655,7 +25655,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>20.12</v>
+        <v>20.11</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>99.8</v>
@@ -25675,7 +25675,7 @@
         <v>5.38</v>
       </c>
       <c r="O243" s="4" t="n">
-        <v>20.12</v>
+        <v>20.11</v>
       </c>
       <c r="P243" s="4" t="n">
         <v>3.13</v>
@@ -25757,7 +25757,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>-33.07</v>
+        <v>-33.08</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>0</v>
@@ -25777,7 +25777,7 @@
         <v>5.38</v>
       </c>
       <c r="O244" s="4" t="n">
-        <v>-33.07</v>
+        <v>-33.08</v>
       </c>
       <c r="P244" s="4" t="n">
         <v>-3.38</v>
@@ -25855,7 +25855,7 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J245" s="4" t="n">
         <v>69.09999999999999</v>
@@ -25973,7 +25973,7 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>20.36</v>
+        <v>20.35</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.38</v>
@@ -26010,10 +26010,10 @@
         <v>0</v>
       </c>
       <c r="AB246" s="4" t="n">
-        <v>63.35</v>
+        <v>63.34</v>
       </c>
       <c r="AC246" s="4" t="n">
-        <v>36.65</v>
+        <v>36.66</v>
       </c>
       <c r="AD246" s="4" t="n">
         <v>0</v>
@@ -26177,7 +26177,7 @@
         </is>
       </c>
       <c r="M248" s="4" t="n">
-        <v>47.9</v>
+        <v>47.89</v>
       </c>
       <c r="N248" s="4" t="n">
         <v>5.38</v>
@@ -26265,13 +26265,13 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>-6.23</v>
+        <v>-6.53</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="K249" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -26279,13 +26279,13 @@
         </is>
       </c>
       <c r="M249" s="4" t="n">
-        <v>-9.49</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="N249" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O249" s="4" t="n">
-        <v>-6.5</v>
+        <v>-6.54</v>
       </c>
       <c r="P249" s="4" t="n">
         <v>-0.01</v>
@@ -26297,16 +26297,16 @@
         <v>-12.23</v>
       </c>
       <c r="S249" s="4" t="n">
-        <v>41</v>
+        <v>41.49</v>
       </c>
       <c r="T249" s="4" t="n">
-        <v>46.96</v>
+        <v>47.93</v>
       </c>
       <c r="U249" t="n">
         <v>2</v>
       </c>
       <c r="V249" s="4" t="n">
-        <v>-5.01</v>
+        <v>-6.49</v>
       </c>
       <c r="W249" s="5" t="n">
         <v>2000547</v>
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="AB249" s="4" t="n">
-        <v>46.88</v>
+        <v>46.73</v>
       </c>
       <c r="AC249" s="4" t="n">
-        <v>53.12</v>
+        <v>53.27</v>
       </c>
       <c r="AD249" s="4" t="n">
         <v>0</v>
@@ -26369,7 +26369,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>12.16</v>
+        <v>12.13</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>98.90000000000001</v>
@@ -26383,13 +26383,13 @@
         </is>
       </c>
       <c r="M250" s="4" t="n">
-        <v>8.130000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="N250" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O250" s="4" t="n">
-        <v>13.39</v>
+        <v>13.35</v>
       </c>
       <c r="P250" s="4" t="n">
         <v>0.52</v>
@@ -26426,10 +26426,10 @@
         <v>0</v>
       </c>
       <c r="AB250" s="4" t="n">
-        <v>56.08</v>
+        <v>56.06</v>
       </c>
       <c r="AC250" s="4" t="n">
-        <v>43.92</v>
+        <v>43.94</v>
       </c>
       <c r="AD250" s="4" t="n">
         <v>0</v>
@@ -26477,7 +26477,7 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>29.75</v>
+        <v>29.7</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>100</v>
@@ -26491,13 +26491,13 @@
         </is>
       </c>
       <c r="M251" s="4" t="n">
-        <v>23.41</v>
+        <v>23.37</v>
       </c>
       <c r="N251" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O251" s="4" t="n">
-        <v>29.75</v>
+        <v>29.7</v>
       </c>
       <c r="P251" s="4" t="n">
         <v>0</v>
@@ -26528,10 +26528,10 @@
         <v>0</v>
       </c>
       <c r="AB251" s="4" t="n">
-        <v>64.88</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AC251" s="4" t="n">
-        <v>35.12</v>
+        <v>35.15</v>
       </c>
       <c r="AD251" s="4" t="n">
         <v>0</v>
@@ -26579,7 +26579,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>47.5</v>
+        <v>47.46</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>100</v>
@@ -26593,13 +26593,13 @@
         </is>
       </c>
       <c r="M252" s="4" t="n">
-        <v>39.11</v>
+        <v>39.06</v>
       </c>
       <c r="N252" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O252" s="4" t="n">
-        <v>47.5</v>
+        <v>47.46</v>
       </c>
       <c r="P252" s="4" t="n">
         <v>2.11</v>
@@ -26630,10 +26630,10 @@
         <v>0</v>
       </c>
       <c r="AB252" s="4" t="n">
-        <v>73.75</v>
+        <v>73.73</v>
       </c>
       <c r="AC252" s="4" t="n">
-        <v>26.25</v>
+        <v>26.27</v>
       </c>
       <c r="AD252" s="4" t="n">
         <v>0</v>
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>65.94</v>
+        <v>65.89</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>100</v>
@@ -26695,13 +26695,13 @@
         </is>
       </c>
       <c r="M253" s="4" t="n">
-        <v>65.94</v>
+        <v>65.89</v>
       </c>
       <c r="N253" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O253" s="4" t="n">
-        <v>65.94</v>
+        <v>65.89</v>
       </c>
       <c r="P253" s="4" t="n">
         <v>1.5</v>
@@ -26732,10 +26732,10 @@
         <v>0</v>
       </c>
       <c r="AB253" s="4" t="n">
-        <v>82.97</v>
+        <v>82.95</v>
       </c>
       <c r="AC253" s="4" t="n">
-        <v>17.03</v>
+        <v>17.05</v>
       </c>
       <c r="AD253" s="4" t="n">
         <v>0</v>
@@ -26783,7 +26783,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>-17.06</v>
+        <v>-17.11</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>0.4</v>
@@ -26797,13 +26797,13 @@
         </is>
       </c>
       <c r="M254" s="4" t="n">
-        <v>-17.68</v>
+        <v>-17.72</v>
       </c>
       <c r="N254" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O254" s="4" t="n">
-        <v>-17.06</v>
+        <v>-17.11</v>
       </c>
       <c r="P254" s="4" t="n">
         <v>-2.25</v>
@@ -26834,10 +26834,10 @@
         <v>0</v>
       </c>
       <c r="AB254" s="4" t="n">
-        <v>41.47</v>
+        <v>41.44</v>
       </c>
       <c r="AC254" s="4" t="n">
-        <v>58.53</v>
+        <v>58.56</v>
       </c>
       <c r="AD254" s="4" t="n">
         <v>0</v>
@@ -26885,7 +26885,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>-32.08</v>
+        <v>-32.13</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>0</v>
@@ -26899,13 +26899,13 @@
         </is>
       </c>
       <c r="M255" s="4" t="n">
-        <v>-34.02</v>
+        <v>-34.07</v>
       </c>
       <c r="N255" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O255" s="4" t="n">
-        <v>-32.08</v>
+        <v>-32.13</v>
       </c>
       <c r="P255" s="4" t="n">
         <v>-0.93</v>
@@ -26936,10 +26936,10 @@
         <v>0</v>
       </c>
       <c r="AB255" s="4" t="n">
-        <v>33.96</v>
+        <v>33.93</v>
       </c>
       <c r="AC255" s="4" t="n">
-        <v>66.04000000000001</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="AD255" s="4" t="n">
         <v>0</v>
@@ -26987,13 +26987,13 @@
         </is>
       </c>
       <c r="I256" s="4" t="n">
-        <v>-10.12</v>
+        <v>-10.17</v>
       </c>
       <c r="J256" s="4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K256" s="4" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -27001,13 +27001,13 @@
         </is>
       </c>
       <c r="M256" s="4" t="n">
-        <v>-11.49</v>
+        <v>-11.53</v>
       </c>
       <c r="N256" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O256" s="4" t="n">
-        <v>-10.12</v>
+        <v>-10.17</v>
       </c>
       <c r="P256" s="4" t="n">
         <v>-1.29</v>
@@ -27038,10 +27038,10 @@
         <v>0</v>
       </c>
       <c r="AB256" s="4" t="n">
-        <v>44.94</v>
+        <v>44.92</v>
       </c>
       <c r="AC256" s="4" t="n">
-        <v>55.06</v>
+        <v>55.08</v>
       </c>
       <c r="AD256" s="4" t="n">
         <v>0</v>
@@ -27191,13 +27191,13 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.73</v>
+        <v>-10.64</v>
       </c>
       <c r="J258" s="4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K258" s="4" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -27223,16 +27223,16 @@
         <v>-11.57</v>
       </c>
       <c r="S258" s="4" t="n">
-        <v>42.5</v>
+        <v>41</v>
       </c>
       <c r="T258" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="U258" t="n">
         <v>1</v>
       </c>
       <c r="V258" s="4" t="n">
-        <v>-6.5</v>
+        <v>-6</v>
       </c>
       <c r="W258" s="5" t="n">
         <v>1155880</v>
@@ -27248,10 +27248,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.63</v>
+        <v>44.68</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.37</v>
+        <v>55.32</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -28311,13 +28311,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-7.17</v>
+        <v>-7.19</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28325,13 +28325,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.66</v>
+        <v>-12.68</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.4</v>
+        <v>-8.43</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28368,10 +28368,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.42</v>
+        <v>46.41</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.58</v>
+        <v>53.59</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28419,7 +28419,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-34.14</v>
+        <v>-34.16</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28433,13 +28433,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.62</v>
+        <v>-31.64</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-34.14</v>
+        <v>-34.16</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28470,10 +28470,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>32.93</v>
+        <v>32.92</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>67.06999999999999</v>
+        <v>67.08</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28521,13 +28521,13 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="J271" s="4" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="K271" s="4" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -28553,16 +28553,16 @@
         <v>-11.71</v>
       </c>
       <c r="S271" s="4" t="n">
-        <v>43.96</v>
+        <v>44.29</v>
       </c>
       <c r="T271" s="4" t="n">
-        <v>41.76</v>
+        <v>40.94</v>
       </c>
       <c r="U271" t="n">
         <v>3</v>
       </c>
       <c r="V271" s="4" t="n">
-        <v>0.79</v>
+        <v>1.29</v>
       </c>
       <c r="W271" s="5" t="n">
         <v>4287386</v>
@@ -28578,10 +28578,10 @@
         <v>0</v>
       </c>
       <c r="AB271" s="4" t="n">
-        <v>51.57</v>
+        <v>51.61</v>
       </c>
       <c r="AC271" s="4" t="n">
-        <v>48.43</v>
+        <v>48.39</v>
       </c>
       <c r="AD271" s="4" t="n">
         <v>0</v>
@@ -29445,7 +29445,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>-15.16</v>
+        <v>-15.31</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>0.6</v>
@@ -29477,16 +29477,16 @@
         <v>-17.89</v>
       </c>
       <c r="S280" s="4" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="T280" s="4" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="U280" t="n">
         <v>1</v>
       </c>
       <c r="V280" s="4" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="W280" s="5" t="n">
         <v>84024</v>
@@ -29502,10 +29502,10 @@
         <v>0</v>
       </c>
       <c r="AB280" s="4" t="n">
-        <v>42.42</v>
+        <v>42.35</v>
       </c>
       <c r="AC280" s="4" t="n">
-        <v>57.58</v>
+        <v>57.65</v>
       </c>
       <c r="AD280" s="4" t="n">
         <v>0</v>
@@ -29855,13 +29855,13 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>-12.57</v>
+        <v>-12.49</v>
       </c>
       <c r="J284" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K284" s="4" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -29887,16 +29887,16 @@
         <v>-15.22</v>
       </c>
       <c r="S284" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T284" s="4" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="U284" t="n">
         <v>1</v>
       </c>
       <c r="V284" s="4" t="n">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
       <c r="W284" s="5" t="n">
         <v>24888</v>
@@ -29912,10 +29912,10 @@
         <v>0</v>
       </c>
       <c r="AB284" s="4" t="n">
-        <v>43.72</v>
+        <v>43.75</v>
       </c>
       <c r="AC284" s="4" t="n">
-        <v>56.28</v>
+        <v>56.25</v>
       </c>
       <c r="AD284" s="4" t="n">
         <v>0</v>
@@ -30375,13 +30375,13 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="J289" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K289" s="4" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -30389,13 +30389,13 @@
         </is>
       </c>
       <c r="M289" s="4" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="N289" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O289" s="4" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="P289" s="4" t="n">
         <v>0.12</v>
@@ -30426,10 +30426,10 @@
         <v>0</v>
       </c>
       <c r="AB289" s="4" t="n">
-        <v>52.72</v>
+        <v>52.71</v>
       </c>
       <c r="AC289" s="4" t="n">
-        <v>47.28</v>
+        <v>47.29</v>
       </c>
       <c r="AD289" s="4" t="n">
         <v>0</v>
@@ -30477,7 +30477,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>16.15</v>
+        <v>16.14</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>99.5</v>
@@ -30491,13 +30491,13 @@
         </is>
       </c>
       <c r="M290" s="4" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="N290" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O290" s="4" t="n">
-        <v>15.18</v>
+        <v>15.16</v>
       </c>
       <c r="P290" s="4" t="n">
         <v>0.88</v>
@@ -30534,10 +30534,10 @@
         <v>0</v>
       </c>
       <c r="AB290" s="4" t="n">
-        <v>58.08</v>
+        <v>58.07</v>
       </c>
       <c r="AC290" s="4" t="n">
-        <v>41.92</v>
+        <v>41.93</v>
       </c>
       <c r="AD290" s="4" t="n">
         <v>0</v>
@@ -31919,7 +31919,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>14.87</v>
+        <v>15.02</v>
       </c>
       <c r="J304" s="4" t="n">
         <v>99.3</v>
@@ -31951,16 +31951,16 @@
         <v>-1.84</v>
       </c>
       <c r="S304" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T304" s="4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U304" t="n">
         <v>1</v>
       </c>
       <c r="V304" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W304" s="5" t="n">
         <v>3784102</v>
@@ -31976,10 +31976,10 @@
         <v>0</v>
       </c>
       <c r="AB304" s="4" t="n">
-        <v>57.43</v>
+        <v>57.51</v>
       </c>
       <c r="AC304" s="4" t="n">
-        <v>42.57</v>
+        <v>42.49</v>
       </c>
       <c r="AD304" s="4" t="n">
         <v>0</v>
@@ -34167,13 +34167,13 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="J326" s="4" t="n">
-        <v>72</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K326" s="4" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -34199,16 +34199,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="S326" s="4" t="n">
-        <v>47.26</v>
+        <v>47.37</v>
       </c>
       <c r="T326" s="4" t="n">
-        <v>47.73</v>
+        <v>48.02</v>
       </c>
       <c r="U326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V326" s="4" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="W326" s="5" t="n">
         <v>4317457</v>
@@ -34224,10 +34224,10 @@
         <v>0</v>
       </c>
       <c r="AB326" s="4" t="n">
-        <v>51.31</v>
+        <v>51.26</v>
       </c>
       <c r="AC326" s="4" t="n">
-        <v>48.69</v>
+        <v>48.74</v>
       </c>
       <c r="AD326" s="4" t="n">
         <v>0</v>
@@ -34275,13 +34275,13 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>15.95</v>
+        <v>17.31</v>
       </c>
       <c r="J327" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="K327" s="4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -34307,16 +34307,16 @@
         <v>3.35</v>
       </c>
       <c r="S327" s="4" t="n">
-        <v>49.41</v>
+        <v>53</v>
       </c>
       <c r="T327" s="4" t="n">
-        <v>39.94</v>
+        <v>39</v>
       </c>
       <c r="U327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V327" s="4" t="n">
-        <v>6.47</v>
+        <v>11</v>
       </c>
       <c r="W327" s="5" t="n">
         <v>4723627</v>
@@ -34332,10 +34332,10 @@
         <v>0</v>
       </c>
       <c r="AB327" s="4" t="n">
-        <v>57.97</v>
+        <v>58.65</v>
       </c>
       <c r="AC327" s="4" t="n">
-        <v>42.03</v>
+        <v>41.35</v>
       </c>
       <c r="AD327" s="4" t="n">
         <v>0</v>
@@ -35813,17 +35813,17 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>-1.33</v>
+        <v>1.69</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>67</v>
+        <v>31.6</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M342" s="4" t="n">
@@ -35845,16 +35845,16 @@
         <v>-11.15</v>
       </c>
       <c r="S342" s="4" t="n">
-        <v>45.02</v>
+        <v>46.47</v>
       </c>
       <c r="T342" s="4" t="n">
-        <v>42.25</v>
+        <v>39.16</v>
       </c>
       <c r="U342" t="n">
         <v>5</v>
       </c>
       <c r="V342" s="4" t="n">
-        <v>0.67</v>
+        <v>6.02</v>
       </c>
       <c r="W342" s="5" t="n">
         <v>603156</v>
@@ -35870,10 +35870,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>49.34</v>
+        <v>50.85</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>50.66</v>
+        <v>49.15</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -36131,13 +36131,13 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-9.039999999999999</v>
+        <v>-9.06</v>
       </c>
       <c r="J345" s="4" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="K345" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>-7.86</v>
       </c>
       <c r="S345" s="4" t="n">
-        <v>41.05</v>
+        <v>41</v>
       </c>
       <c r="T345" s="4" t="n">
         <v>47.01</v>
@@ -36172,7 +36172,7 @@
         <v>2</v>
       </c>
       <c r="V345" s="4" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="W345" s="5" t="n">
         <v>362666</v>
@@ -36188,10 +36188,10 @@
         <v>0</v>
       </c>
       <c r="AB345" s="4" t="n">
-        <v>45.48</v>
+        <v>45.47</v>
       </c>
       <c r="AC345" s="4" t="n">
-        <v>54.52</v>
+        <v>54.53</v>
       </c>
       <c r="AD345" s="4" t="n">
         <v>0</v>
@@ -40641,7 +40641,7 @@
         </is>
       </c>
       <c r="I389" s="4" t="n">
-        <v>-55.78</v>
+        <v>-55.74</v>
       </c>
       <c r="J389" s="4" t="n">
         <v>0</v>
@@ -40655,13 +40655,13 @@
         </is>
       </c>
       <c r="M389" s="4" t="n">
-        <v>-56.17</v>
+        <v>-56.13</v>
       </c>
       <c r="N389" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O389" s="4" t="n">
-        <v>-55.78</v>
+        <v>-55.74</v>
       </c>
       <c r="P389" s="4" t="n">
         <v>-1.63</v>
@@ -40692,10 +40692,10 @@
         <v>0</v>
       </c>
       <c r="AB389" s="4" t="n">
-        <v>22.11</v>
+        <v>22.13</v>
       </c>
       <c r="AC389" s="4" t="n">
-        <v>77.89</v>
+        <v>77.87</v>
       </c>
       <c r="AD389" s="4" t="n">
         <v>0</v>
@@ -40743,7 +40743,7 @@
         </is>
       </c>
       <c r="I390" s="4" t="n">
-        <v>-33.11</v>
+        <v>-33.07</v>
       </c>
       <c r="J390" s="4" t="n">
         <v>0</v>
@@ -40757,13 +40757,13 @@
         </is>
       </c>
       <c r="M390" s="4" t="n">
-        <v>-32.01</v>
+        <v>-31.97</v>
       </c>
       <c r="N390" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O390" s="4" t="n">
-        <v>-33.11</v>
+        <v>-33.07</v>
       </c>
       <c r="P390" s="4" t="n">
         <v>-1.28</v>
@@ -40794,10 +40794,10 @@
         <v>0</v>
       </c>
       <c r="AB390" s="4" t="n">
-        <v>33.44</v>
+        <v>33.46</v>
       </c>
       <c r="AC390" s="4" t="n">
-        <v>66.56</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="AD390" s="4" t="n">
         <v>0</v>
@@ -40845,7 +40845,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>-34.9</v>
+        <v>-34.86</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>0</v>
@@ -40859,13 +40859,13 @@
         </is>
       </c>
       <c r="M391" s="4" t="n">
-        <v>-33.82</v>
+        <v>-33.78</v>
       </c>
       <c r="N391" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O391" s="4" t="n">
-        <v>-34.9</v>
+        <v>-34.86</v>
       </c>
       <c r="P391" s="4" t="n">
         <v>-2.34</v>
@@ -40896,10 +40896,10 @@
         <v>0</v>
       </c>
       <c r="AB391" s="4" t="n">
-        <v>32.55</v>
+        <v>32.57</v>
       </c>
       <c r="AC391" s="4" t="n">
-        <v>67.45</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="AD391" s="4" t="n">
         <v>0</v>
@@ -40947,7 +40947,7 @@
         </is>
       </c>
       <c r="I392" s="4" t="n">
-        <v>-17.26</v>
+        <v>-17.22</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>0.4</v>
@@ -40961,13 +40961,13 @@
         </is>
       </c>
       <c r="M392" s="4" t="n">
-        <v>-20.79</v>
+        <v>-20.75</v>
       </c>
       <c r="N392" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O392" s="4" t="n">
-        <v>-17.26</v>
+        <v>-17.22</v>
       </c>
       <c r="P392" s="4" t="n">
         <v>-1.26</v>
@@ -40998,10 +40998,10 @@
         <v>0</v>
       </c>
       <c r="AB392" s="4" t="n">
-        <v>41.37</v>
+        <v>41.39</v>
       </c>
       <c r="AC392" s="4" t="n">
-        <v>58.63</v>
+        <v>58.61</v>
       </c>
       <c r="AD392" s="4" t="n">
         <v>0</v>
@@ -41045,7 +41045,7 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-12.95</v>
+        <v>-12.91</v>
       </c>
       <c r="J393" s="4" t="n">
         <v>1</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="M393" s="4" t="n">
-        <v>-18.87</v>
+        <v>-18.83</v>
       </c>
       <c r="N393" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>-12.95</v>
+        <v>-12.91</v>
       </c>
       <c r="P393" s="4" t="n">
         <v>0.96</v>
@@ -41096,10 +41096,10 @@
         <v>0</v>
       </c>
       <c r="AB393" s="4" t="n">
-        <v>43.53</v>
+        <v>43.55</v>
       </c>
       <c r="AC393" s="4" t="n">
-        <v>56.47</v>
+        <v>56.45</v>
       </c>
       <c r="AD393" s="4" t="n">
         <v>0</v>
@@ -41143,7 +41143,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-21.13</v>
+        <v>-21.09</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>0.2</v>
@@ -41157,13 +41157,13 @@
         </is>
       </c>
       <c r="M394" s="4" t="n">
-        <v>-23.83</v>
+        <v>-23.79</v>
       </c>
       <c r="N394" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O394" s="4" t="n">
-        <v>-21.13</v>
+        <v>-21.09</v>
       </c>
       <c r="P394" s="4" t="n">
         <v>-2.06</v>
@@ -41194,10 +41194,10 @@
         <v>0</v>
       </c>
       <c r="AB394" s="4" t="n">
-        <v>39.43</v>
+        <v>39.45</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>60.57</v>
+        <v>60.55</v>
       </c>
       <c r="AD394" s="4" t="n">
         <v>0</v>
@@ -41245,7 +41245,7 @@
         </is>
       </c>
       <c r="I395" s="4" t="n">
-        <v>-17.65</v>
+        <v>-17.61</v>
       </c>
       <c r="J395" s="4" t="n">
         <v>0.4</v>
@@ -41259,13 +41259,13 @@
         </is>
       </c>
       <c r="M395" s="4" t="n">
-        <v>-20.21</v>
+        <v>-20.17</v>
       </c>
       <c r="N395" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O395" s="4" t="n">
-        <v>-17.65</v>
+        <v>-17.61</v>
       </c>
       <c r="P395" s="4" t="n">
         <v>-0.6</v>
@@ -41296,10 +41296,10 @@
         <v>0</v>
       </c>
       <c r="AB395" s="4" t="n">
-        <v>41.17</v>
+        <v>41.19</v>
       </c>
       <c r="AC395" s="4" t="n">
-        <v>58.83</v>
+        <v>58.81</v>
       </c>
       <c r="AD395" s="4" t="n">
         <v>0</v>
@@ -41347,7 +41347,7 @@
         </is>
       </c>
       <c r="I396" s="4" t="n">
-        <v>-20.9</v>
+        <v>-20.86</v>
       </c>
       <c r="J396" s="4" t="n">
         <v>0.2</v>
@@ -41361,13 +41361,13 @@
         </is>
       </c>
       <c r="M396" s="4" t="n">
-        <v>-18.01</v>
+        <v>-17.97</v>
       </c>
       <c r="N396" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O396" s="4" t="n">
-        <v>-20.9</v>
+        <v>-20.86</v>
       </c>
       <c r="P396" s="4" t="n">
         <v>-2.43</v>
@@ -41398,10 +41398,10 @@
         <v>0</v>
       </c>
       <c r="AB396" s="4" t="n">
-        <v>39.55</v>
+        <v>39.57</v>
       </c>
       <c r="AC396" s="4" t="n">
-        <v>60.45</v>
+        <v>60.43</v>
       </c>
       <c r="AD396" s="4" t="n">
         <v>0</v>
@@ -41445,7 +41445,7 @@
         </is>
       </c>
       <c r="I397" s="4" t="n">
-        <v>-11.54</v>
+        <v>-11.5</v>
       </c>
       <c r="J397" s="4" t="n">
         <v>1.2</v>
@@ -41459,13 +41459,13 @@
         </is>
       </c>
       <c r="M397" s="4" t="n">
-        <v>-16.86</v>
+        <v>-16.82</v>
       </c>
       <c r="N397" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O397" s="4" t="n">
-        <v>-11.54</v>
+        <v>-11.5</v>
       </c>
       <c r="P397" s="4" t="n">
         <v>0.24</v>
@@ -41496,10 +41496,10 @@
         <v>0</v>
       </c>
       <c r="AB397" s="4" t="n">
-        <v>44.23</v>
+        <v>44.25</v>
       </c>
       <c r="AC397" s="4" t="n">
-        <v>55.77</v>
+        <v>55.75</v>
       </c>
       <c r="AD397" s="4" t="n">
         <v>0</v>
@@ -41561,7 +41561,7 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-44.19</v>
+        <v>-44.18</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>5.38</v>
@@ -41598,10 +41598,10 @@
         <v>0</v>
       </c>
       <c r="AB398" s="4" t="n">
-        <v>29.74</v>
+        <v>29.75</v>
       </c>
       <c r="AC398" s="4" t="n">
-        <v>70.26000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="AD398" s="4" t="n">
         <v>0</v>
@@ -41696,10 +41696,10 @@
         <v>0</v>
       </c>
       <c r="AB399" s="4" t="n">
-        <v>43.87</v>
+        <v>43.88</v>
       </c>
       <c r="AC399" s="4" t="n">
-        <v>56.13</v>
+        <v>56.12</v>
       </c>
       <c r="AD399" s="4" t="n">
         <v>0</v>
@@ -41747,7 +41747,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-15.34</v>
+        <v>-15.33</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>0.6</v>
@@ -41761,13 +41761,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-18.79</v>
+        <v>-18.78</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-15.34</v>
+        <v>-15.33</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -41798,10 +41798,10 @@
         <v>0</v>
       </c>
       <c r="AB400" s="4" t="n">
-        <v>42.33</v>
+        <v>42.34</v>
       </c>
       <c r="AC400" s="4" t="n">
-        <v>57.67</v>
+        <v>57.66</v>
       </c>
       <c r="AD400" s="4" t="n">
         <v>0</v>
@@ -41849,7 +41849,7 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>-20.77</v>
+        <v>-20.76</v>
       </c>
       <c r="J401" s="4" t="n">
         <v>0.2</v>
@@ -41869,7 +41869,7 @@
         <v>5.38</v>
       </c>
       <c r="O401" s="4" t="n">
-        <v>-20.77</v>
+        <v>-20.76</v>
       </c>
       <c r="P401" s="4" t="n">
         <v>-1.91</v>
@@ -41900,10 +41900,10 @@
         <v>0</v>
       </c>
       <c r="AB401" s="4" t="n">
-        <v>39.61</v>
+        <v>39.62</v>
       </c>
       <c r="AC401" s="4" t="n">
-        <v>60.39</v>
+        <v>60.38</v>
       </c>
       <c r="AD401" s="4" t="n">
         <v>0</v>
@@ -41951,7 +41951,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-13.3</v>
+        <v>-13.29</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>0.9</v>
@@ -41971,7 +41971,7 @@
         <v>5.38</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-13.3</v>
+        <v>-13.29</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.23</v>
@@ -42002,10 +42002,10 @@
         <v>0</v>
       </c>
       <c r="AB402" s="4" t="n">
-        <v>43.35</v>
+        <v>43.36</v>
       </c>
       <c r="AC402" s="4" t="n">
-        <v>56.65</v>
+        <v>56.64</v>
       </c>
       <c r="AD402" s="4" t="n">
         <v>0</v>
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-18.68</v>
+        <v>-18.67</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.3</v>
@@ -42073,7 +42073,7 @@
         <v>5.38</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-18.68</v>
+        <v>-18.67</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -42155,7 +42155,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>41.08</v>
+        <v>41.09</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -42175,7 +42175,7 @@
         <v>5.38</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>41.08</v>
+        <v>41.09</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -42206,10 +42206,10 @@
         <v>0</v>
       </c>
       <c r="AB404" s="4" t="n">
-        <v>70.54000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="AC404" s="4" t="n">
-        <v>29.46</v>
+        <v>29.45</v>
       </c>
       <c r="AD404" s="4" t="n">
         <v>0</v>
@@ -42253,7 +42253,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.87</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.4</v>
@@ -42267,13 +42267,13 @@
         </is>
       </c>
       <c r="M405" s="4" t="n">
-        <v>-21.26</v>
+        <v>-21.25</v>
       </c>
       <c r="N405" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.87</v>
       </c>
       <c r="P405" s="4" t="n">
         <v>-2.83</v>
@@ -42351,7 +42351,7 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-6.6</v>
+        <v>-6.59</v>
       </c>
       <c r="J406" s="4" t="n">
         <v>13.8</v>
@@ -42371,7 +42371,7 @@
         <v>5.38</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-6.6</v>
+        <v>-6.59</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.92</v>
@@ -42449,7 +42449,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-12.99</v>
+        <v>-12.98</v>
       </c>
       <c r="J407" s="4" t="n">
         <v>1</v>
@@ -42463,13 +42463,13 @@
         </is>
       </c>
       <c r="M407" s="4" t="n">
-        <v>-16.92</v>
+        <v>-16.91</v>
       </c>
       <c r="N407" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-12.99</v>
+        <v>-12.98</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -42551,7 +42551,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-27.35</v>
+        <v>-27.34</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0</v>
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="M408" s="4" t="n">
-        <v>-29.61</v>
+        <v>-29.6</v>
       </c>
       <c r="N408" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-27.35</v>
+        <v>-27.34</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -42653,7 +42653,7 @@
         </is>
       </c>
       <c r="I409" s="4" t="n">
-        <v>-18.7</v>
+        <v>-18.69</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>0.3</v>
@@ -42667,13 +42667,13 @@
         </is>
       </c>
       <c r="M409" s="4" t="n">
-        <v>-18.56</v>
+        <v>-18.55</v>
       </c>
       <c r="N409" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O409" s="4" t="n">
-        <v>-18.7</v>
+        <v>-18.69</v>
       </c>
       <c r="P409" s="4" t="n">
         <v>0</v>
@@ -42755,7 +42755,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-40.65</v>
+        <v>-40.64</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -42775,7 +42775,7 @@
         <v>5.38</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-40.65</v>
+        <v>-40.64</v>
       </c>
       <c r="P410" s="4" t="n">
         <v>-2.49</v>
@@ -42857,7 +42857,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-19.58</v>
+        <v>-19.57</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.3</v>
@@ -42877,7 +42877,7 @@
         <v>5.38</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-19.58</v>
+        <v>-19.57</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.89</v>
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>-2</v>
+        <v>-1.15</v>
       </c>
       <c r="J412" s="4" t="n">
-        <v>30.4</v>
+        <v>33.7</v>
       </c>
       <c r="K412" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -42973,13 +42973,13 @@
         </is>
       </c>
       <c r="M412" s="4" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="N412" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>-1.49</v>
+        <v>-1.48</v>
       </c>
       <c r="P412" s="4" t="n">
         <v>-0.32</v>
@@ -42991,16 +42991,16 @@
         <v>-18.02</v>
       </c>
       <c r="S412" s="4" t="n">
-        <v>47.31</v>
+        <v>48.36</v>
       </c>
       <c r="T412" s="4" t="n">
-        <v>47.23</v>
+        <v>45.85</v>
       </c>
       <c r="U412" t="n">
         <v>3</v>
       </c>
       <c r="V412" s="4" t="n">
-        <v>-2.91</v>
+        <v>-0.49</v>
       </c>
       <c r="W412" s="5" t="n">
         <v>2960462</v>
@@ -43016,10 +43016,10 @@
         <v>0</v>
       </c>
       <c r="AB412" s="4" t="n">
-        <v>49</v>
+        <v>49.42</v>
       </c>
       <c r="AC412" s="4" t="n">
-        <v>51</v>
+        <v>50.58</v>
       </c>
       <c r="AD412" s="4" t="n">
         <v>0</v>
@@ -43067,7 +43067,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="n">
-        <v>36.63</v>
+        <v>36.64</v>
       </c>
       <c r="J413" s="4" t="n">
         <v>100</v>
@@ -43081,13 +43081,13 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>26.74</v>
+        <v>26.75</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O413" s="4" t="n">
-        <v>36.63</v>
+        <v>36.64</v>
       </c>
       <c r="P413" s="4" t="n">
         <v>0</v>
@@ -43169,7 +43169,7 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-14.77</v>
+        <v>-14.76</v>
       </c>
       <c r="J414" s="4" t="n">
         <v>0.7</v>
@@ -43183,13 +43183,13 @@
         </is>
       </c>
       <c r="M414" s="4" t="n">
-        <v>-16.39</v>
+        <v>-16.38</v>
       </c>
       <c r="N414" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-14.77</v>
+        <v>-14.76</v>
       </c>
       <c r="P414" s="4" t="n">
         <v>0</v>
@@ -43322,10 +43322,10 @@
         <v>0</v>
       </c>
       <c r="AB415" s="4" t="n">
-        <v>85.58</v>
+        <v>85.59</v>
       </c>
       <c r="AC415" s="4" t="n">
-        <v>14.42</v>
+        <v>14.41</v>
       </c>
       <c r="AD415" s="4" t="n">
         <v>0</v>
@@ -43369,7 +43369,7 @@
         </is>
       </c>
       <c r="I416" s="4" t="n">
-        <v>-42.69</v>
+        <v>-42.68</v>
       </c>
       <c r="J416" s="4" t="n">
         <v>0</v>
@@ -43383,13 +43383,13 @@
         </is>
       </c>
       <c r="M416" s="4" t="n">
-        <v>-46.57</v>
+        <v>-46.56</v>
       </c>
       <c r="N416" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>-42.69</v>
+        <v>-42.68</v>
       </c>
       <c r="P416" s="4" t="n">
         <v>-2.39</v>
@@ -43471,7 +43471,7 @@
         </is>
       </c>
       <c r="I417" s="4" t="n">
-        <v>49.3</v>
+        <v>49.31</v>
       </c>
       <c r="J417" s="4" t="n">
         <v>100</v>
@@ -43485,13 +43485,13 @@
         </is>
       </c>
       <c r="M417" s="4" t="n">
-        <v>36.58</v>
+        <v>36.59</v>
       </c>
       <c r="N417" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O417" s="4" t="n">
-        <v>49.3</v>
+        <v>49.31</v>
       </c>
       <c r="P417" s="4" t="n">
         <v>1.31</v>
@@ -43620,10 +43620,10 @@
         <v>0</v>
       </c>
       <c r="AB418" s="4" t="n">
-        <v>43.87</v>
+        <v>43.88</v>
       </c>
       <c r="AC418" s="4" t="n">
-        <v>56.13</v>
+        <v>56.12</v>
       </c>
       <c r="AD418" s="4" t="n">
         <v>0</v>
@@ -43667,7 +43667,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-12.97</v>
+        <v>-12.96</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>1</v>
@@ -43687,7 +43687,7 @@
         <v>5.38</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-12.97</v>
+        <v>-12.96</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.8100000000000001</v>
@@ -43765,7 +43765,7 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-2.34</v>
+        <v>-2.33</v>
       </c>
       <c r="J420" s="4" t="n">
         <v>29.1</v>
@@ -43785,7 +43785,7 @@
         <v>5.38</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.86</v>
       </c>
       <c r="P420" s="4" t="n">
         <v>-0.82</v>
@@ -43797,10 +43797,10 @@
         <v>-14.97</v>
       </c>
       <c r="S420" s="4" t="n">
-        <v>42.5</v>
+        <v>40</v>
       </c>
       <c r="T420" s="4" t="n">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="U420" t="n">
         <v>1</v>
@@ -43873,7 +43873,7 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-10.9</v>
+        <v>-10.89</v>
       </c>
       <c r="J421" s="4" t="n">
         <v>2.1</v>
@@ -43887,13 +43887,13 @@
         </is>
       </c>
       <c r="M421" s="4" t="n">
-        <v>-11.81</v>
+        <v>-11.8</v>
       </c>
       <c r="N421" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-10.9</v>
+        <v>-10.89</v>
       </c>
       <c r="P421" s="4" t="n">
         <v>0</v>
@@ -43989,7 +43989,7 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-18.04</v>
+        <v>-18.03</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>5.38</v>
@@ -44077,7 +44077,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-22.58</v>
+        <v>-22.57</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.1</v>
@@ -44091,13 +44091,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-19.16</v>
+        <v>-19.15</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-22.58</v>
+        <v>-22.57</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -44128,10 +44128,10 @@
         <v>0</v>
       </c>
       <c r="AB423" s="4" t="n">
-        <v>38.71</v>
+        <v>38.72</v>
       </c>
       <c r="AC423" s="4" t="n">
-        <v>61.29</v>
+        <v>61.28</v>
       </c>
       <c r="AD423" s="4" t="n">
         <v>0</v>
@@ -44179,7 +44179,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-13.85</v>
+        <v>-13.84</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>0.8</v>
@@ -44199,7 +44199,7 @@
         <v>5.38</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-13.85</v>
+        <v>-13.84</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="I426" s="4" t="n">
-        <v>54.09</v>
+        <v>54.1</v>
       </c>
       <c r="J426" s="4" t="n">
         <v>100</v>
@@ -44403,13 +44403,13 @@
         </is>
       </c>
       <c r="M426" s="4" t="n">
-        <v>39.1</v>
+        <v>39.11</v>
       </c>
       <c r="N426" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O426" s="4" t="n">
-        <v>54.09</v>
+        <v>54.1</v>
       </c>
       <c r="P426" s="4" t="n">
         <v>0</v>
@@ -44487,7 +44487,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>61.71</v>
+        <v>61.72</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -44501,13 +44501,13 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>54.81</v>
+        <v>54.82</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>61.71</v>
+        <v>61.72</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>0.21</v>
@@ -44603,13 +44603,13 @@
         </is>
       </c>
       <c r="M428" s="4" t="n">
-        <v>-17.32</v>
+        <v>-17.31</v>
       </c>
       <c r="N428" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O428" s="4" t="n">
-        <v>-18.14</v>
+        <v>-18.13</v>
       </c>
       <c r="P428" s="4" t="n">
         <v>-1.61</v>
@@ -44687,7 +44687,7 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-8.24</v>
+        <v>-8.23</v>
       </c>
       <c r="J429" s="4" t="n">
         <v>8.800000000000001</v>
@@ -44701,13 +44701,13 @@
         </is>
       </c>
       <c r="M429" s="4" t="n">
-        <v>-12.16</v>
+        <v>-12.15</v>
       </c>
       <c r="N429" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-8.24</v>
+        <v>-8.23</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.72</v>
@@ -44785,7 +44785,7 @@
         </is>
       </c>
       <c r="I430" s="4" t="n">
-        <v>46.18</v>
+        <v>46.19</v>
       </c>
       <c r="J430" s="4" t="n">
         <v>100</v>
@@ -44805,7 +44805,7 @@
         <v>5.38</v>
       </c>
       <c r="O430" s="4" t="n">
-        <v>46.18</v>
+        <v>46.19</v>
       </c>
       <c r="P430" s="4" t="n">
         <v>0</v>
@@ -44887,13 +44887,13 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J431" s="4" t="n">
-        <v>92.5</v>
+        <v>92.3</v>
       </c>
       <c r="K431" s="4" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         </is>
       </c>
       <c r="M431" s="4" t="n">
-        <v>-1.58</v>
+        <v>-1.57</v>
       </c>
       <c r="N431" s="4" t="n">
         <v>5.38</v>
@@ -44919,16 +44919,16 @@
         <v>-10.22</v>
       </c>
       <c r="S431" s="4" t="n">
-        <v>41.35</v>
+        <v>40.79</v>
       </c>
       <c r="T431" s="4" t="n">
-        <v>44.18</v>
+        <v>43.36</v>
       </c>
       <c r="U431" t="n">
         <v>2</v>
       </c>
       <c r="V431" s="4" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="W431" s="5" t="n">
         <v>3773915</v>
@@ -44944,10 +44944,10 @@
         <v>0</v>
       </c>
       <c r="AB431" s="4" t="n">
-        <v>54.36</v>
+        <v>54.32</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>45.64</v>
+        <v>45.68</v>
       </c>
       <c r="AD431" s="4" t="n">
         <v>0</v>
@@ -45005,7 +45005,7 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-4.08</v>
+        <v>-4.07</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>5.38</v>
@@ -45042,10 +45042,10 @@
         <v>0</v>
       </c>
       <c r="AB432" s="4" t="n">
-        <v>51.63</v>
+        <v>51.64</v>
       </c>
       <c r="AC432" s="4" t="n">
-        <v>48.37</v>
+        <v>48.36</v>
       </c>
       <c r="AD432" s="4" t="n">
         <v>0</v>
@@ -45093,7 +45093,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-15.9</v>
+        <v>-15.89</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.6</v>
@@ -45107,13 +45107,13 @@
         </is>
       </c>
       <c r="M433" s="4" t="n">
-        <v>-19.19</v>
+        <v>-19.18</v>
       </c>
       <c r="N433" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-15.9</v>
+        <v>-15.89</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>0</v>
@@ -45195,7 +45195,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>71.25</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -45215,7 +45215,7 @@
         <v>5.38</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>71.25</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="P434" s="4" t="n">
         <v>1.49</v>
@@ -45246,10 +45246,10 @@
         <v>0</v>
       </c>
       <c r="AB434" s="4" t="n">
-        <v>85.62</v>
+        <v>85.63</v>
       </c>
       <c r="AC434" s="4" t="n">
-        <v>14.38</v>
+        <v>14.37</v>
       </c>
       <c r="AD434" s="4" t="n">
         <v>0</v>
@@ -45313,7 +45313,7 @@
         <v>5.38</v>
       </c>
       <c r="O435" s="4" t="n">
-        <v>-13.44</v>
+        <v>-13.43</v>
       </c>
       <c r="P435" s="4" t="n">
         <v>-2.01</v>
@@ -45799,17 +45799,17 @@
         </is>
       </c>
       <c r="I440" s="4" t="n">
-        <v>-3.06</v>
+        <v>-3.57</v>
       </c>
       <c r="J440" s="4" t="n">
-        <v>26.3</v>
+        <v>24.3</v>
       </c>
       <c r="K440" s="4" t="n">
-        <v>73.7</v>
+        <v>75.7</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M440" s="4" t="n">
@@ -45831,16 +45831,16 @@
         <v>-5</v>
       </c>
       <c r="S440" s="4" t="n">
-        <v>43.01</v>
+        <v>41.97</v>
       </c>
       <c r="T440" s="4" t="n">
-        <v>44</v>
+        <v>45.92</v>
       </c>
       <c r="U440" t="n">
         <v>2</v>
       </c>
       <c r="V440" s="4" t="n">
-        <v>1.92</v>
+        <v>-1.05</v>
       </c>
       <c r="W440" s="5" t="n">
         <v>2140980</v>
@@ -45856,10 +45856,10 @@
         <v>0</v>
       </c>
       <c r="AB440" s="4" t="n">
-        <v>48.47</v>
+        <v>48.21</v>
       </c>
       <c r="AC440" s="4" t="n">
-        <v>51.53</v>
+        <v>51.79</v>
       </c>
       <c r="AD440" s="4" t="n">
         <v>0</v>
@@ -47251,13 +47251,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>15.1</v>
+        <v>16.6</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47283,16 +47283,16 @@
         <v>-3.4</v>
       </c>
       <c r="S454" s="4" t="n">
-        <v>41.8</v>
+        <v>41.67</v>
       </c>
       <c r="T454" s="4" t="n">
-        <v>42.96</v>
+        <v>42.92</v>
       </c>
       <c r="U454" t="n">
         <v>2</v>
       </c>
       <c r="V454" s="4" t="n">
-        <v>-3.69</v>
+        <v>-4</v>
       </c>
       <c r="W454" s="5" t="n">
         <v>6292683</v>
@@ -47308,10 +47308,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>53.1</v>
+        <v>52.88</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>46.9</v>
+        <v>47.12</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -48075,13 +48075,13 @@
         </is>
       </c>
       <c r="I462" s="4" t="n">
-        <v>-3.91</v>
+        <v>-4.19</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -48089,13 +48089,13 @@
         </is>
       </c>
       <c r="M462" s="4" t="n">
-        <v>-2.78</v>
+        <v>-2.88</v>
       </c>
       <c r="N462" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O462" s="4" t="n">
-        <v>-4.19</v>
+        <v>-4.29</v>
       </c>
       <c r="P462" s="4" t="n">
         <v>-1.48</v>
@@ -48107,16 +48107,16 @@
         <v>-4.58</v>
       </c>
       <c r="S462" s="4" t="n">
-        <v>45.94</v>
+        <v>47.88</v>
       </c>
       <c r="T462" s="4" t="n">
-        <v>46.49</v>
+        <v>49.02</v>
       </c>
       <c r="U462" t="n">
         <v>2</v>
       </c>
       <c r="V462" s="4" t="n">
-        <v>-3.45</v>
+        <v>-4.04</v>
       </c>
       <c r="W462" s="5" t="n">
         <v>712984</v>
@@ -48132,10 +48132,10 @@
         <v>0</v>
       </c>
       <c r="AB462" s="4" t="n">
-        <v>48.04</v>
+        <v>47.9</v>
       </c>
       <c r="AC462" s="4" t="n">
-        <v>51.96</v>
+        <v>52.1</v>
       </c>
       <c r="AD462" s="4" t="n">
         <v>0</v>
@@ -48183,7 +48183,7 @@
         </is>
       </c>
       <c r="I463" s="4" t="n">
-        <v>49.54</v>
+        <v>49.44</v>
       </c>
       <c r="J463" s="4" t="n">
         <v>100</v>
@@ -48197,13 +48197,13 @@
         </is>
       </c>
       <c r="M463" s="4" t="n">
-        <v>42.21</v>
+        <v>42.11</v>
       </c>
       <c r="N463" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O463" s="4" t="n">
-        <v>49.54</v>
+        <v>49.44</v>
       </c>
       <c r="P463" s="4" t="n">
         <v>0</v>
@@ -48234,10 +48234,10 @@
         <v>0</v>
       </c>
       <c r="AB463" s="4" t="n">
-        <v>74.77</v>
+        <v>74.72</v>
       </c>
       <c r="AC463" s="4" t="n">
-        <v>25.23</v>
+        <v>25.28</v>
       </c>
       <c r="AD463" s="4" t="n">
         <v>0</v>
@@ -48285,13 +48285,13 @@
         </is>
       </c>
       <c r="I464" s="4" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="J464" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K464" s="4" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -48299,13 +48299,13 @@
         </is>
       </c>
       <c r="M464" s="4" t="n">
-        <v>-5.61</v>
+        <v>-5.7</v>
       </c>
       <c r="N464" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O464" s="4" t="n">
-        <v>6.23</v>
+        <v>6.14</v>
       </c>
       <c r="P464" s="4" t="n">
         <v>0.1</v>
@@ -48342,10 +48342,10 @@
         <v>0</v>
       </c>
       <c r="AB464" s="4" t="n">
-        <v>52.18</v>
+        <v>52.15</v>
       </c>
       <c r="AC464" s="4" t="n">
-        <v>47.82</v>
+        <v>47.85</v>
       </c>
       <c r="AD464" s="4" t="n">
         <v>0</v>
@@ -48393,7 +48393,7 @@
         </is>
       </c>
       <c r="I465" s="4" t="n">
-        <v>62.95</v>
+        <v>62.85</v>
       </c>
       <c r="J465" s="4" t="n">
         <v>100</v>
@@ -48407,13 +48407,13 @@
         </is>
       </c>
       <c r="M465" s="4" t="n">
-        <v>53.93</v>
+        <v>53.84</v>
       </c>
       <c r="N465" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O465" s="4" t="n">
-        <v>62.95</v>
+        <v>62.85</v>
       </c>
       <c r="P465" s="4" t="n">
         <v>0</v>
@@ -48444,10 +48444,10 @@
         <v>0</v>
       </c>
       <c r="AB465" s="4" t="n">
-        <v>81.47</v>
+        <v>81.42</v>
       </c>
       <c r="AC465" s="4" t="n">
-        <v>18.53</v>
+        <v>18.58</v>
       </c>
       <c r="AD465" s="4" t="n">
         <v>0</v>
@@ -48495,7 +48495,7 @@
         </is>
       </c>
       <c r="I466" s="4" t="n">
-        <v>-24.22</v>
+        <v>-24.32</v>
       </c>
       <c r="J466" s="4" t="n">
         <v>0.1</v>
@@ -48509,13 +48509,13 @@
         </is>
       </c>
       <c r="M466" s="4" t="n">
-        <v>-21.84</v>
+        <v>-21.94</v>
       </c>
       <c r="N466" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O466" s="4" t="n">
-        <v>-24.22</v>
+        <v>-24.32</v>
       </c>
       <c r="P466" s="4" t="n">
         <v>-2.32</v>
@@ -48546,10 +48546,10 @@
         <v>0</v>
       </c>
       <c r="AB466" s="4" t="n">
-        <v>37.89</v>
+        <v>37.84</v>
       </c>
       <c r="AC466" s="4" t="n">
-        <v>62.11</v>
+        <v>62.16</v>
       </c>
       <c r="AD466" s="4" t="n">
         <v>0</v>
@@ -48597,7 +48597,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-17.33</v>
+        <v>-17.41</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.4</v>
@@ -48611,13 +48611,13 @@
         </is>
       </c>
       <c r="M467" s="4" t="n">
-        <v>-15.45</v>
+        <v>-15.55</v>
       </c>
       <c r="N467" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-15.72</v>
+        <v>-15.81</v>
       </c>
       <c r="P467" s="4" t="n">
         <v>0</v>
@@ -48654,10 +48654,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>41.34</v>
+        <v>41.3</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>58.66</v>
+        <v>58.7</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48701,7 +48701,7 @@
         </is>
       </c>
       <c r="I468" s="4" t="n">
-        <v>-17.83</v>
+        <v>-17.93</v>
       </c>
       <c r="J468" s="4" t="n">
         <v>0.4</v>
@@ -48715,13 +48715,13 @@
         </is>
       </c>
       <c r="M468" s="4" t="n">
-        <v>-21.07</v>
+        <v>-21.17</v>
       </c>
       <c r="N468" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O468" s="4" t="n">
-        <v>-17.83</v>
+        <v>-17.93</v>
       </c>
       <c r="P468" s="4" t="n">
         <v>-1.15</v>
@@ -48752,10 +48752,10 @@
         <v>0</v>
       </c>
       <c r="AB468" s="4" t="n">
-        <v>41.08</v>
+        <v>41.04</v>
       </c>
       <c r="AC468" s="4" t="n">
-        <v>58.92</v>
+        <v>58.96</v>
       </c>
       <c r="AD468" s="4" t="n">
         <v>0</v>
@@ -48803,7 +48803,7 @@
         </is>
       </c>
       <c r="I469" s="4" t="n">
-        <v>-14.16</v>
+        <v>-14.26</v>
       </c>
       <c r="J469" s="4" t="n">
         <v>0.8</v>
@@ -48817,13 +48817,13 @@
         </is>
       </c>
       <c r="M469" s="4" t="n">
-        <v>-15.25</v>
+        <v>-15.34</v>
       </c>
       <c r="N469" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O469" s="4" t="n">
-        <v>-14.16</v>
+        <v>-14.26</v>
       </c>
       <c r="P469" s="4" t="n">
         <v>-1.66</v>
@@ -48854,10 +48854,10 @@
         <v>0</v>
       </c>
       <c r="AB469" s="4" t="n">
-        <v>42.92</v>
+        <v>42.87</v>
       </c>
       <c r="AC469" s="4" t="n">
-        <v>57.08</v>
+        <v>57.13</v>
       </c>
       <c r="AD469" s="4" t="n">
         <v>0</v>
@@ -49207,13 +49207,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.43</v>
+        <v>-0.82</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>49</v>
+        <v>47.8</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>51</v>
+        <v>52.2</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49221,13 +49221,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.92</v>
+        <v>-10.85</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.07</v>
+        <v>-2</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.42</v>
@@ -49242,10 +49242,10 @@
         <v>48.47</v>
       </c>
       <c r="T473" s="4" t="n">
-        <v>47.39</v>
+        <v>47.4</v>
       </c>
       <c r="U473" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V473" s="4" t="n">
         <v>0.67</v>
@@ -49264,10 +49264,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.64</v>
+        <v>45.65</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.36</v>
+        <v>46.35</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -49877,7 +49877,7 @@
         <v>42.98</v>
       </c>
       <c r="U479" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V479" s="4" t="n">
         <v>11.11</v>
@@ -49943,13 +49943,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-1.99</v>
+        <v>-1.94</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -49975,16 +49975,16 @@
         <v>-13.45</v>
       </c>
       <c r="S480" s="4" t="n">
-        <v>46.39</v>
+        <v>46.43</v>
       </c>
       <c r="T480" s="4" t="n">
-        <v>47.27</v>
+        <v>47.28</v>
       </c>
       <c r="U480" t="n">
         <v>9</v>
       </c>
       <c r="V480" s="4" t="n">
-        <v>-1.05</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="W480" s="5" t="n">
         <v>6276527</v>
@@ -50000,10 +50000,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.71</v>
+        <v>47.74</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.66</v>
+        <v>49.63</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -50051,7 +50051,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-21.98</v>
+        <v>-21.99</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0.1</v>
@@ -50065,13 +50065,13 @@
         </is>
       </c>
       <c r="M481" s="4" t="n">
-        <v>-30.08</v>
+        <v>-30.1</v>
       </c>
       <c r="N481" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O481" s="4" t="n">
-        <v>-28</v>
+        <v>-28.02</v>
       </c>
       <c r="P481" s="4" t="n">
         <v>-1.14</v>
@@ -50261,17 +50261,17 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-9.73</v>
+        <v>-9.49</v>
       </c>
       <c r="J483" s="4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="K483" s="4" t="n">
-        <v>95.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>Safe R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M483" s="4" t="n">
@@ -50293,16 +50293,16 @@
         <v>-16.41</v>
       </c>
       <c r="S483" s="4" t="n">
-        <v>43.24</v>
+        <v>43.2</v>
       </c>
       <c r="T483" s="4" t="n">
-        <v>47.13</v>
+        <v>47.03</v>
       </c>
       <c r="U483" t="n">
         <v>3</v>
       </c>
       <c r="V483" s="4" t="n">
-        <v>-6.89</v>
+        <v>-6.83</v>
       </c>
       <c r="W483" s="5" t="n">
         <v>4169078</v>
@@ -50318,10 +50318,10 @@
         <v>0</v>
       </c>
       <c r="AB483" s="4" t="n">
-        <v>45.13</v>
+        <v>45.26</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>54.87</v>
+        <v>54.74</v>
       </c>
       <c r="AD483" s="4" t="n">
         <v>0</v>
@@ -50365,7 +50365,7 @@
         </is>
       </c>
       <c r="I484" s="4" t="n">
-        <v>-28.81</v>
+        <v>-28.58</v>
       </c>
       <c r="J484" s="4" t="n">
         <v>0</v>
@@ -50397,16 +50397,16 @@
         <v>-31.03</v>
       </c>
       <c r="S484" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T484" s="4" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="U484" t="n">
         <v>1</v>
       </c>
       <c r="V484" s="4" t="n">
-        <v>-15.5</v>
+        <v>-14</v>
       </c>
       <c r="W484" s="5" t="n">
         <v>1099509</v>
@@ -50422,10 +50422,10 @@
         <v>0</v>
       </c>
       <c r="AB484" s="4" t="n">
-        <v>35.6</v>
+        <v>35.71</v>
       </c>
       <c r="AC484" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="AD484" s="4" t="n">
         <v>0</v>
@@ -50679,13 +50679,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>65.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50711,16 +50711,16 @@
         <v>7.09</v>
       </c>
       <c r="S487" s="4" t="n">
-        <v>48.39</v>
+        <v>48.26</v>
       </c>
       <c r="T487" s="4" t="n">
-        <v>45.64</v>
+        <v>45.65</v>
       </c>
       <c r="U487" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V487" s="4" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="W487" s="5" t="n">
         <v>0</v>
@@ -50783,13 +50783,13 @@
         </is>
       </c>
       <c r="I488" s="4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="J488" s="4" t="n">
-        <v>71.3</v>
+        <v>71.2</v>
       </c>
       <c r="K488" s="4" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="M488" s="4" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="N488" s="4" t="n">
         <v>5.38</v>
@@ -50887,13 +50887,13 @@
         </is>
       </c>
       <c r="I489" s="4" t="n">
-        <v>9.56</v>
+        <v>9.33</v>
       </c>
       <c r="J489" s="4" t="n">
-        <v>94.7</v>
+        <v>94.2</v>
       </c>
       <c r="K489" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
@@ -50919,16 +50919,16 @@
         <v>4.34</v>
       </c>
       <c r="S489" s="4" t="n">
-        <v>49.3</v>
+        <v>49.71</v>
       </c>
       <c r="T489" s="4" t="n">
-        <v>41.8</v>
+        <v>42.88</v>
       </c>
       <c r="U489" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V489" s="4" t="n">
-        <v>6.64</v>
+        <v>4.82</v>
       </c>
       <c r="W489" s="5" t="n">
         <v>6516273</v>
@@ -50944,10 +50944,10 @@
         <v>0</v>
       </c>
       <c r="AB489" s="4" t="n">
-        <v>54.78</v>
+        <v>54.66</v>
       </c>
       <c r="AC489" s="4" t="n">
-        <v>45.22</v>
+        <v>45.34</v>
       </c>
       <c r="AD489" s="4" t="n">
         <v>0</v>
@@ -51103,7 +51103,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.36</v>
+        <v>-27.46</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51135,16 +51135,16 @@
         <v>-20.58</v>
       </c>
       <c r="S491" s="4" t="n">
-        <v>29.68</v>
+        <v>29.54</v>
       </c>
       <c r="T491" s="4" t="n">
-        <v>44.81</v>
+        <v>44.7</v>
       </c>
       <c r="U491" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V491" s="4" t="n">
-        <v>-16.14</v>
+        <v>-16.15</v>
       </c>
       <c r="W491" s="5" t="n">
         <v>58829</v>
@@ -51158,13 +51158,13 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.39</v>
+        <v>14.5</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>27.29</v>
+        <v>27.19</v>
       </c>
       <c r="AC491" s="4" t="n">
         <v>54.65</v>
@@ -51427,13 +51427,13 @@
         </is>
       </c>
       <c r="I494" s="4" t="n">
-        <v>7.32</v>
+        <v>7.3</v>
       </c>
       <c r="J494" s="4" t="n">
-        <v>88.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K494" s="4" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="L494" t="inlineStr">
         <is>
@@ -51441,13 +51441,13 @@
         </is>
       </c>
       <c r="M494" s="4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="N494" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O494" s="4" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="P494" s="4" t="n">
         <v>0.71</v>
@@ -51484,10 +51484,10 @@
         <v>0</v>
       </c>
       <c r="AB494" s="4" t="n">
-        <v>53.66</v>
+        <v>53.65</v>
       </c>
       <c r="AC494" s="4" t="n">
-        <v>46.34</v>
+        <v>46.35</v>
       </c>
       <c r="AD494" s="4" t="n">
         <v>0</v>
@@ -51739,7 +51739,7 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J497" s="4" t="n">
         <v>69</v>
@@ -51771,16 +51771,16 @@
         <v>-11.31</v>
       </c>
       <c r="S497" s="4" t="n">
-        <v>50.57</v>
+        <v>50.65</v>
       </c>
       <c r="T497" s="4" t="n">
-        <v>45.79</v>
+        <v>45.83</v>
       </c>
       <c r="U497" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V497" s="4" t="n">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="W497" s="5" t="n">
         <v>38566234</v>
@@ -52371,7 +52371,7 @@
         </is>
       </c>
       <c r="I503" s="4" t="n">
-        <v>-31.43</v>
+        <v>-31.39</v>
       </c>
       <c r="J503" s="4" t="n">
         <v>0</v>
@@ -52385,13 +52385,13 @@
         </is>
       </c>
       <c r="M503" s="4" t="n">
-        <v>-26.3</v>
+        <v>-26.26</v>
       </c>
       <c r="N503" s="4" t="n">
         <v>5.38</v>
       </c>
       <c r="O503" s="4" t="n">
-        <v>-31.43</v>
+        <v>-31.39</v>
       </c>
       <c r="P503" s="4" t="n">
         <v>-3.72</v>
@@ -52422,10 +52422,10 @@
         <v>0</v>
       </c>
       <c r="AB503" s="4" t="n">
-        <v>34.28</v>
+        <v>34.3</v>
       </c>
       <c r="AC503" s="4" t="n">
-        <v>65.72</v>
+        <v>65.7</v>
       </c>
       <c r="AD503" s="4" t="n">
         <v>0</v>
@@ -52483,7 +52483,7 @@
         </is>
       </c>
       <c r="M504" s="4" t="n">
-        <v>-10.16</v>
+        <v>-10.15</v>
       </c>
       <c r="N504" s="4" t="n">
         <v>5.38</v>
@@ -52507,7 +52507,7 @@
         <v>45.76</v>
       </c>
       <c r="U504" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V504" s="4" t="n">
         <v>1.33</v>
@@ -52526,10 +52526,10 @@
         <v>0</v>
       </c>
       <c r="AB504" s="4" t="n">
-        <v>49.51</v>
+        <v>49.52</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>48.48</v>
+        <v>48.47</v>
       </c>
       <c r="AD504" s="4" t="n">
         <v>2.01</v>
@@ -53363,7 +53363,7 @@
         <v>38</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="K33" t="n">
         <v>21</v>
@@ -55033,7 +55033,7 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>106.5</v>
+        <v>106.3</v>
       </c>
       <c r="K37" t="n">
         <v>106</v>
@@ -55042,7 +55042,7 @@
         <v>93</v>
       </c>
       <c r="M37" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>99.40000000000001</v>
@@ -55091,7 +55091,7 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="K38" t="n">
         <v>35</v>
@@ -55277,7 +55277,7 @@
         <v>79</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -55381,7 +55381,7 @@
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K43" t="n">
         <v>75</v>
@@ -55393,7 +55393,7 @@
         <v>96</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="K47" t="n">
         <v>41</v>
@@ -55622,7 +55622,7 @@
         <v>26</v>
       </c>
       <c r="M47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>7.8</v>
@@ -56019,7 +56019,7 @@
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>210.3</v>
+        <v>210.2</v>
       </c>
       <c r="K54" t="n">
         <v>207</v>
@@ -56089,7 +56089,7 @@
         <v>18</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -57759,10 +57759,10 @@
         </is>
       </c>
       <c r="J84" s="4" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="K84" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L84" t="n">
         <v>37</v>
@@ -57771,15 +57771,15 @@
         <v>64</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -57829,7 +57829,7 @@
         <v>21</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>63.8</v>
+        <v>63.6</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generic ballot D+5.2 · House popular vote D+7.3</t>
+          <t>Generic ballot D+5.2 · House popular vote D+7.2</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="D8" t="n">
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>55.7</v>
+        <v>56.6</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.3</v>
+        <v>232.4</v>
       </c>
       <c r="C9" t="n">
-        <v>202.7</v>
+        <v>202.6</v>
       </c>
       <c r="D9" t="n">
         <v>231</v>
       </c>
       <c r="E9" t="n">
-        <v>80.7</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="C10" t="n">
-        <v>25.5</v>
+        <v>24.6</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>39.3</v>
+        <v>55.5</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -609,7 +609,6 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -912,20 +911,19 @@
           <t>Bernadette Wilson</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-4.21</v>
+        <v>-4.27</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>37.2</v>
+        <v>36.7</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -968,7 +966,6 @@
       <c r="X2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
       <c r="Z2" s="4" t="n">
         <v>0</v>
       </c>
@@ -1016,7 +1013,6 @@
           <t>Tommy Tuberville</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>REP</t>
@@ -1072,7 +1068,6 @@
       <c r="X3" s="5" t="n">
         <v>13792994</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" s="4" t="n">
         <v>0</v>
       </c>
@@ -1180,7 +1175,6 @@
       <c r="X4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
       <c r="Z4" s="4" t="n">
         <v>0</v>
       </c>
@@ -1288,7 +1282,6 @@
       <c r="X5" s="5" t="n">
         <v>2787170</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
       <c r="Z5" s="4" t="n">
         <v>0</v>
       </c>
@@ -1336,7 +1329,6 @@
           <t>Steve Hilton</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -1392,7 +1384,6 @@
       <c r="X6" s="5" t="n">
         <v>17445485</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" s="4" t="n">
         <v>0</v>
       </c>
@@ -1440,7 +1431,6 @@
           <t>Victor Marx</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -1608,7 +1598,6 @@
       <c r="X8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" t="inlineStr"/>
       <c r="Z8" s="4" t="n">
         <v>0</v>
       </c>
@@ -1656,7 +1645,6 @@
           <t>Byron Donalds</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>REP</t>
@@ -1712,7 +1700,6 @@
       <c r="X9" s="5" t="n">
         <v>99442171</v>
       </c>
-      <c r="Y9" t="inlineStr"/>
       <c r="Z9" s="4" t="n">
         <v>0</v>
       </c>
@@ -1760,7 +1747,6 @@
           <t>Rick Jackson</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>REP</t>
@@ -1816,7 +1802,6 @@
       <c r="X10" s="5" t="n">
         <v>118984243</v>
       </c>
-      <c r="Y10" t="inlineStr"/>
       <c r="Z10" s="4" t="n">
         <v>0</v>
       </c>
@@ -1918,7 +1903,6 @@
       <c r="X11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" t="inlineStr"/>
       <c r="Z11" s="4" t="n">
         <v>0</v>
       </c>
@@ -1966,7 +1950,6 @@
           <t>Zach Lahn</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>REP</t>
@@ -2022,7 +2005,6 @@
       <c r="X12" s="5" t="n">
         <v>1218702</v>
       </c>
-      <c r="Y12" t="inlineStr"/>
       <c r="Z12" s="4" t="n">
         <v>0</v>
       </c>
@@ -2130,7 +2112,6 @@
       <c r="X13" s="5" t="n">
         <v>2057743</v>
       </c>
-      <c r="Y13" t="inlineStr"/>
       <c r="Z13" s="4" t="n">
         <v>0</v>
       </c>
@@ -2238,7 +2219,6 @@
       <c r="X14" s="5" t="n">
         <v>2166962</v>
       </c>
-      <c r="Y14" t="inlineStr"/>
       <c r="Z14" s="4" t="n">
         <v>0</v>
       </c>
@@ -2286,7 +2266,6 @@
           <t>Ty Masterson</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -2336,7 +2315,6 @@
       <c r="X15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" t="inlineStr"/>
       <c r="Z15" s="4" t="n">
         <v>0</v>
       </c>
@@ -2444,7 +2422,6 @@
       <c r="X16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y16" t="inlineStr"/>
       <c r="Z16" s="4" t="n">
         <v>0</v>
       </c>
@@ -2552,7 +2529,6 @@
       <c r="X17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y17" t="inlineStr"/>
       <c r="Z17" s="4" t="n">
         <v>0</v>
       </c>
@@ -2600,7 +2576,6 @@
           <t>Robert Charles</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -2708,7 +2683,6 @@
           <t>John James</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -2764,7 +2738,6 @@
       <c r="X19" s="5" t="n">
         <v>4492470</v>
       </c>
-      <c r="Y19" t="inlineStr"/>
       <c r="Z19" s="4" t="n">
         <v>0</v>
       </c>
@@ -2812,7 +2785,6 @@
           <t>Lisa Demuth</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -2868,7 +2840,6 @@
       <c r="X20" s="5" t="n">
         <v>1102119</v>
       </c>
-      <c r="Y20" t="inlineStr"/>
       <c r="Z20" s="4" t="n">
         <v>0</v>
       </c>
@@ -3088,7 +3059,6 @@
       <c r="X22" s="5" t="n">
         <v>3694856</v>
       </c>
-      <c r="Y22" t="inlineStr"/>
       <c r="Z22" s="4" t="n">
         <v>0</v>
       </c>
@@ -3136,7 +3106,6 @@
           <t>Gregg Hull</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -3192,7 +3161,6 @@
       <c r="X23" s="5" t="n">
         <v>987856</v>
       </c>
-      <c r="Y23" t="inlineStr"/>
       <c r="Z23" s="4" t="n">
         <v>0</v>
       </c>
@@ -3300,7 +3268,6 @@
       <c r="X24" s="5" t="n">
         <v>2275075</v>
       </c>
-      <c r="Y24" t="inlineStr"/>
       <c r="Z24" s="4" t="n">
         <v>0</v>
       </c>
@@ -3408,7 +3375,6 @@
       <c r="X25" s="5" t="n">
         <v>13445025</v>
       </c>
-      <c r="Y25" t="inlineStr"/>
       <c r="Z25" s="4" t="n">
         <v>0</v>
       </c>
@@ -3456,7 +3422,6 @@
           <t>Vivek Ramaswamy</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>REP</t>
@@ -3512,7 +3477,6 @@
       <c r="X26" s="5" t="n">
         <v>30306297</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
       <c r="Z26" s="4" t="n">
         <v>0</v>
       </c>
@@ -3560,7 +3524,6 @@
           <t>Gentner Drummond</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>REP</t>
@@ -3610,7 +3573,6 @@
       <c r="X27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
       <c r="Z27" s="4" t="n">
         <v>0</v>
       </c>
@@ -3718,7 +3680,6 @@
       <c r="X28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y28" t="inlineStr"/>
       <c r="Z28" s="4" t="n">
         <v>0</v>
       </c>
@@ -3826,7 +3787,6 @@
       <c r="X29" s="5" t="n">
         <v>2545436</v>
       </c>
-      <c r="Y29" t="inlineStr"/>
       <c r="Z29" s="4" t="n">
         <v>0</v>
       </c>
@@ -3874,7 +3834,6 @@
           <t>Elaine Pelino</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -3930,7 +3889,6 @@
       <c r="X30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y30" t="inlineStr"/>
       <c r="Z30" s="4" t="n">
         <v>0</v>
       </c>
@@ -3978,7 +3936,6 @@
           <t>Alan Wilson</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>REP</t>
@@ -4034,7 +3991,6 @@
       <c r="X31" s="5" t="n">
         <v>62585</v>
       </c>
-      <c r="Y31" t="inlineStr"/>
       <c r="Z31" s="4" t="n">
         <v>0</v>
       </c>
@@ -4136,7 +4092,6 @@
       <c r="X32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y32" t="inlineStr"/>
       <c r="Z32" s="4" t="n">
         <v>0</v>
       </c>
@@ -4184,7 +4139,6 @@
           <t>Marsha Blackburn</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>REP</t>
@@ -4240,7 +4194,6 @@
       <c r="X33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y33" t="inlineStr"/>
       <c r="Z33" s="4" t="n">
         <v>0</v>
       </c>
@@ -4348,7 +4301,6 @@
       <c r="X34" s="5" t="n">
         <v>71434049</v>
       </c>
-      <c r="Y34" t="inlineStr"/>
       <c r="Z34" s="4" t="n">
         <v>0</v>
       </c>
@@ -4456,7 +4408,6 @@
       <c r="X35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y35" t="inlineStr"/>
       <c r="Z35" s="4" t="n">
         <v>0</v>
       </c>
@@ -4504,7 +4455,6 @@
           <t>Tom Tiffany</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -4560,7 +4510,6 @@
       <c r="X36" s="5" t="n">
         <v>15315779</v>
       </c>
-      <c r="Y36" t="inlineStr"/>
       <c r="Z36" s="4" t="n">
         <v>0</v>
       </c>
@@ -4608,7 +4557,6 @@
           <t>Eric Barlow</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>REP</t>
@@ -4658,7 +4606,6 @@
       <c r="X37" s="5" t="n">
         <v>1673103</v>
       </c>
-      <c r="Y37" t="inlineStr"/>
       <c r="Z37" s="4" t="n">
         <v>0</v>
       </c>
@@ -4717,7 +4664,7 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-5.18</v>
+        <v>-5.17</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>18.5</v>
@@ -4737,7 +4684,7 @@
         <v>5.16</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.27</v>
+        <v>-1.26</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.04</v>
@@ -4818,7 +4765,6 @@
           <t>Jerry Carl</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>REP</t>
@@ -4868,7 +4814,6 @@
       <c r="X39" s="5" t="n">
         <v>1162583</v>
       </c>
-      <c r="Y39" t="inlineStr"/>
       <c r="Z39" s="4" t="n">
         <v>0</v>
       </c>
@@ -4976,7 +4921,6 @@
       <c r="X40" s="5" t="n">
         <v>1318574</v>
       </c>
-      <c r="Y40" t="inlineStr"/>
       <c r="Z40" s="4" t="n">
         <v>0</v>
       </c>
@@ -5078,7 +5022,6 @@
       <c r="X41" s="5" t="n">
         <v>2133554</v>
       </c>
-      <c r="Y41" t="inlineStr"/>
       <c r="Z41" s="4" t="n">
         <v>0</v>
       </c>
@@ -5180,7 +5123,6 @@
       <c r="X42" s="5" t="n">
         <v>1022664</v>
       </c>
-      <c r="Y42" t="inlineStr"/>
       <c r="Z42" s="4" t="n">
         <v>0</v>
       </c>
@@ -5282,7 +5224,6 @@
       <c r="X43" s="5" t="n">
         <v>1477819</v>
       </c>
-      <c r="Y43" t="inlineStr"/>
       <c r="Z43" s="4" t="n">
         <v>0</v>
       </c>
@@ -5384,7 +5325,6 @@
       <c r="X44" s="5" t="n">
         <v>1053566</v>
       </c>
-      <c r="Y44" t="inlineStr"/>
       <c r="Z44" s="4" t="n">
         <v>0</v>
       </c>
@@ -5486,7 +5426,6 @@
       <c r="X45" s="5" t="n">
         <v>150730</v>
       </c>
-      <c r="Y45" t="inlineStr"/>
       <c r="Z45" s="4" t="n">
         <v>0</v>
       </c>
@@ -5588,7 +5527,6 @@
       <c r="X46" s="5" t="n">
         <v>944302</v>
       </c>
-      <c r="Y46" t="inlineStr"/>
       <c r="Z46" s="4" t="n">
         <v>0</v>
       </c>
@@ -5696,7 +5634,6 @@
       <c r="X47" s="5" t="n">
         <v>4421510</v>
       </c>
-      <c r="Y47" t="inlineStr"/>
       <c r="Z47" s="4" t="n">
         <v>0</v>
       </c>
@@ -5798,7 +5735,6 @@
       <c r="X48" s="5" t="n">
         <v>1871761</v>
       </c>
-      <c r="Y48" t="inlineStr"/>
       <c r="Z48" s="4" t="n">
         <v>0</v>
       </c>
@@ -5900,7 +5836,6 @@
       <c r="X49" s="5" t="n">
         <v>2562973</v>
       </c>
-      <c r="Y49" t="inlineStr"/>
       <c r="Z49" s="4" t="n">
         <v>0</v>
       </c>
@@ -5948,7 +5883,6 @@
           <t>Jay Feely</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>REP</t>
@@ -6004,7 +5938,6 @@
       <c r="X50" s="5" t="n">
         <v>2528497</v>
       </c>
-      <c r="Y50" t="inlineStr"/>
       <c r="Z50" s="4" t="n">
         <v>0</v>
       </c>
@@ -6112,7 +6045,6 @@
       <c r="X51" s="5" t="n">
         <v>9481428</v>
       </c>
-      <c r="Y51" t="inlineStr"/>
       <c r="Z51" s="4" t="n">
         <v>0</v>
       </c>
@@ -6214,7 +6146,6 @@
       <c r="X52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y52" t="inlineStr"/>
       <c r="Z52" s="4" t="n">
         <v>0</v>
       </c>
@@ -6316,7 +6247,6 @@
       <c r="X53" s="5" t="n">
         <v>564641</v>
       </c>
-      <c r="Y53" t="inlineStr"/>
       <c r="Z53" s="4" t="n">
         <v>0</v>
       </c>
@@ -6364,7 +6294,6 @@
           <t>Daniel Keenan</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>REP</t>
@@ -6414,7 +6343,6 @@
       <c r="X54" s="5" t="n">
         <v>1851302</v>
       </c>
-      <c r="Y54" t="inlineStr"/>
       <c r="Z54" s="4" t="n">
         <v>0</v>
       </c>
@@ -6522,7 +6450,6 @@
       <c r="X55" s="5" t="n">
         <v>6172867</v>
       </c>
-      <c r="Y55" t="inlineStr"/>
       <c r="Z55" s="4" t="n">
         <v>0</v>
       </c>
@@ -6624,7 +6551,6 @@
       <c r="X56" s="5" t="n">
         <v>224367</v>
       </c>
-      <c r="Y56" t="inlineStr"/>
       <c r="Z56" s="4" t="n">
         <v>0</v>
       </c>
@@ -6726,7 +6652,6 @@
       <c r="X57" s="5" t="n">
         <v>1206361</v>
       </c>
-      <c r="Y57" t="inlineStr"/>
       <c r="Z57" s="4" t="n">
         <v>0</v>
       </c>
@@ -6828,7 +6753,6 @@
       <c r="X58" s="5" t="n">
         <v>580042</v>
       </c>
-      <c r="Y58" t="inlineStr"/>
       <c r="Z58" s="4" t="n">
         <v>0</v>
       </c>
@@ -6930,7 +6854,6 @@
       <c r="X59" s="5" t="n">
         <v>1488906</v>
       </c>
-      <c r="Y59" t="inlineStr"/>
       <c r="Z59" s="4" t="n">
         <v>0</v>
       </c>
@@ -7032,7 +6955,6 @@
       <c r="X60" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y60" t="inlineStr"/>
       <c r="Z60" s="4" t="n">
         <v>0</v>
       </c>
@@ -7134,7 +7056,6 @@
       <c r="X61" s="5" t="n">
         <v>258139</v>
       </c>
-      <c r="Y61" t="inlineStr"/>
       <c r="Z61" s="4" t="n">
         <v>0</v>
       </c>
@@ -7236,7 +7157,6 @@
       <c r="X62" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y62" t="inlineStr"/>
       <c r="Z62" s="4" t="n">
         <v>0</v>
       </c>
@@ -7338,7 +7258,6 @@
       <c r="X63" s="5" t="n">
         <v>928788</v>
       </c>
-      <c r="Y63" t="inlineStr"/>
       <c r="Z63" s="4" t="n">
         <v>0</v>
       </c>
@@ -7440,7 +7359,6 @@
       <c r="X64" s="5" t="n">
         <v>2988805</v>
       </c>
-      <c r="Y64" t="inlineStr"/>
       <c r="Z64" s="4" t="n">
         <v>0</v>
       </c>
@@ -7542,7 +7460,6 @@
       <c r="X65" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y65" t="inlineStr"/>
       <c r="Z65" s="4" t="n">
         <v>0</v>
       </c>
@@ -7644,7 +7561,6 @@
       <c r="X66" s="5" t="n">
         <v>8576</v>
       </c>
-      <c r="Y66" t="inlineStr"/>
       <c r="Z66" s="4" t="n">
         <v>0</v>
       </c>
@@ -7746,7 +7662,6 @@
       <c r="X67" s="5" t="n">
         <v>52178</v>
       </c>
-      <c r="Y67" t="inlineStr"/>
       <c r="Z67" s="4" t="n">
         <v>0</v>
       </c>
@@ -7848,7 +7763,6 @@
       <c r="X68" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y68" t="inlineStr"/>
       <c r="Z68" s="4" t="n">
         <v>0</v>
       </c>
@@ -7896,7 +7810,6 @@
           <t>(no Republican — top-two)</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -7946,7 +7859,6 @@
       <c r="X69" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y69" t="inlineStr"/>
       <c r="Z69" s="4" t="n">
         <v>0</v>
       </c>
@@ -8048,7 +7960,6 @@
       <c r="X70" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y70" t="inlineStr"/>
       <c r="Z70" s="4" t="n">
         <v>0</v>
       </c>
@@ -8150,7 +8061,6 @@
       <c r="X71" s="5" t="n">
         <v>2237084</v>
       </c>
-      <c r="Y71" t="inlineStr"/>
       <c r="Z71" s="4" t="n">
         <v>0</v>
       </c>
@@ -8198,7 +8108,6 @@
           <t>(no Republican — top-two)</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -8248,7 +8157,6 @@
       <c r="X72" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y72" t="inlineStr"/>
       <c r="Z72" s="4" t="n">
         <v>0</v>
       </c>
@@ -8350,7 +8258,6 @@
       <c r="X73" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y73" t="inlineStr"/>
       <c r="Z73" s="4" t="n">
         <v>0</v>
       </c>
@@ -8452,7 +8359,6 @@
       <c r="X74" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y74" t="inlineStr"/>
       <c r="Z74" s="4" t="n">
         <v>0</v>
       </c>
@@ -8554,7 +8460,6 @@
       <c r="X75" s="5" t="n">
         <v>37653</v>
       </c>
-      <c r="Y75" t="inlineStr"/>
       <c r="Z75" s="4" t="n">
         <v>0</v>
       </c>
@@ -8656,7 +8561,6 @@
       <c r="X76" s="5" t="n">
         <v>60180</v>
       </c>
-      <c r="Y76" t="inlineStr"/>
       <c r="Z76" s="4" t="n">
         <v>0</v>
       </c>
@@ -8758,7 +8662,6 @@
       <c r="X77" s="5" t="n">
         <v>76324</v>
       </c>
-      <c r="Y77" t="inlineStr"/>
       <c r="Z77" s="4" t="n">
         <v>0</v>
       </c>
@@ -8860,7 +8763,6 @@
       <c r="X78" s="5" t="n">
         <v>1849356</v>
       </c>
-      <c r="Y78" t="inlineStr"/>
       <c r="Z78" s="4" t="n">
         <v>0</v>
       </c>
@@ -8962,7 +8864,6 @@
       <c r="X79" s="5" t="n">
         <v>338971</v>
       </c>
-      <c r="Y79" t="inlineStr"/>
       <c r="Z79" s="4" t="n">
         <v>0</v>
       </c>
@@ -9070,7 +8971,6 @@
       <c r="X80" s="5" t="n">
         <v>4927602</v>
       </c>
-      <c r="Y80" t="inlineStr"/>
       <c r="Z80" s="4" t="n">
         <v>0</v>
       </c>
@@ -9172,7 +9072,6 @@
       <c r="X81" s="5" t="n">
         <v>1455868</v>
       </c>
-      <c r="Y81" t="inlineStr"/>
       <c r="Z81" s="4" t="n">
         <v>0</v>
       </c>
@@ -9274,7 +9173,6 @@
       <c r="X82" s="5" t="n">
         <v>203264</v>
       </c>
-      <c r="Y82" t="inlineStr"/>
       <c r="Z82" s="4" t="n">
         <v>0</v>
       </c>
@@ -9376,7 +9274,6 @@
       <c r="X83" s="5" t="n">
         <v>936496</v>
       </c>
-      <c r="Y83" t="inlineStr"/>
       <c r="Z83" s="4" t="n">
         <v>0</v>
       </c>
@@ -9424,7 +9321,6 @@
           <t>Samuel Gallucci</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -9474,7 +9370,6 @@
       <c r="X84" s="5" t="n">
         <v>377078</v>
       </c>
-      <c r="Y84" t="inlineStr"/>
       <c r="Z84" s="4" t="n">
         <v>0</v>
       </c>
@@ -9576,7 +9471,6 @@
       <c r="X85" s="5" t="n">
         <v>379440</v>
       </c>
-      <c r="Y85" t="inlineStr"/>
       <c r="Z85" s="4" t="n">
         <v>0</v>
       </c>
@@ -9678,7 +9572,6 @@
       <c r="X86" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="Y86" t="inlineStr"/>
       <c r="Z86" s="4" t="n">
         <v>0</v>
       </c>
@@ -9780,7 +9673,6 @@
       <c r="X87" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y87" t="inlineStr"/>
       <c r="Z87" s="4" t="n">
         <v>0</v>
       </c>
@@ -9882,7 +9774,6 @@
       <c r="X88" s="5" t="n">
         <v>58294</v>
       </c>
-      <c r="Y88" t="inlineStr"/>
       <c r="Z88" s="4" t="n">
         <v>0</v>
       </c>
@@ -9984,7 +9875,6 @@
       <c r="X89" s="5" t="n">
         <v>81571</v>
       </c>
-      <c r="Y89" t="inlineStr"/>
       <c r="Z89" s="4" t="n">
         <v>0</v>
       </c>
@@ -10086,7 +9976,6 @@
       <c r="X90" s="5" t="n">
         <v>34316</v>
       </c>
-      <c r="Y90" t="inlineStr"/>
       <c r="Z90" s="4" t="n">
         <v>0</v>
       </c>
@@ -10188,7 +10077,6 @@
       <c r="X91" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y91" t="inlineStr"/>
       <c r="Z91" s="4" t="n">
         <v>0</v>
       </c>
@@ -10290,7 +10178,6 @@
       <c r="X92" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y92" t="inlineStr"/>
       <c r="Z92" s="4" t="n">
         <v>0</v>
       </c>
@@ -10392,7 +10279,6 @@
       <c r="X93" s="5" t="n">
         <v>4759</v>
       </c>
-      <c r="Y93" t="inlineStr"/>
       <c r="Z93" s="4" t="n">
         <v>0</v>
       </c>
@@ -10494,7 +10380,6 @@
       <c r="X94" s="5" t="n">
         <v>5139</v>
       </c>
-      <c r="Y94" t="inlineStr"/>
       <c r="Z94" s="4" t="n">
         <v>0</v>
       </c>
@@ -10596,7 +10481,6 @@
       <c r="X95" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y95" t="inlineStr"/>
       <c r="Z95" s="4" t="n">
         <v>0</v>
       </c>
@@ -10644,7 +10528,6 @@
           <t>Pedro Casas</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -10694,7 +10577,6 @@
       <c r="X96" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y96" t="inlineStr"/>
       <c r="Z96" s="4" t="n">
         <v>0</v>
       </c>
@@ -10796,7 +10678,6 @@
       <c r="X97" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y97" t="inlineStr"/>
       <c r="Z97" s="4" t="n">
         <v>0</v>
       </c>
@@ -10898,7 +10779,6 @@
       <c r="X98" s="5" t="n">
         <v>6142469</v>
       </c>
-      <c r="Y98" t="inlineStr"/>
       <c r="Z98" s="4" t="n">
         <v>0</v>
       </c>
@@ -11000,7 +10880,6 @@
       <c r="X99" s="5" t="n">
         <v>1709</v>
       </c>
-      <c r="Y99" t="inlineStr"/>
       <c r="Z99" s="4" t="n">
         <v>0</v>
       </c>
@@ -11102,7 +10981,6 @@
       <c r="X100" s="5" t="n">
         <v>231371</v>
       </c>
-      <c r="Y100" t="inlineStr"/>
       <c r="Z100" s="4" t="n">
         <v>0</v>
       </c>
@@ -11204,7 +11082,6 @@
       <c r="X101" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y101" t="inlineStr"/>
       <c r="Z101" s="4" t="n">
         <v>0</v>
       </c>
@@ -11306,7 +11183,6 @@
       <c r="X102" s="5" t="n">
         <v>13898</v>
       </c>
-      <c r="Y102" t="inlineStr"/>
       <c r="Z102" s="4" t="n">
         <v>0</v>
       </c>
@@ -11408,7 +11284,6 @@
       <c r="X103" s="5" t="n">
         <v>756510</v>
       </c>
-      <c r="Y103" t="inlineStr"/>
       <c r="Z103" s="4" t="n">
         <v>0</v>
       </c>
@@ -11510,7 +11385,6 @@
       <c r="X104" s="5" t="n">
         <v>80726</v>
       </c>
-      <c r="Y104" t="inlineStr"/>
       <c r="Z104" s="4" t="n">
         <v>0</v>
       </c>
@@ -11612,7 +11486,6 @@
       <c r="X105" s="5" t="n">
         <v>375883</v>
       </c>
-      <c r="Y105" t="inlineStr"/>
       <c r="Z105" s="4" t="n">
         <v>0</v>
       </c>
@@ -11660,7 +11533,6 @@
           <t>Jim Desmond</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -11716,7 +11588,6 @@
       <c r="X106" s="5" t="n">
         <v>2258836</v>
       </c>
-      <c r="Y106" t="inlineStr"/>
       <c r="Z106" s="4" t="n">
         <v>0</v>
       </c>
@@ -11818,7 +11689,6 @@
       <c r="X107" s="5" t="n">
         <v>58784</v>
       </c>
-      <c r="Y107" t="inlineStr"/>
       <c r="Z107" s="4" t="n">
         <v>0</v>
       </c>
@@ -11920,7 +11790,6 @@
       <c r="X108" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y108" t="inlineStr"/>
       <c r="Z108" s="4" t="n">
         <v>0</v>
       </c>
@@ -12022,7 +11891,6 @@
       <c r="X109" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y109" t="inlineStr"/>
       <c r="Z109" s="4" t="n">
         <v>0</v>
       </c>
@@ -12124,7 +11992,6 @@
       <c r="X110" s="5" t="n">
         <v>25498</v>
       </c>
-      <c r="Y110" t="inlineStr"/>
       <c r="Z110" s="4" t="n">
         <v>0</v>
       </c>
@@ -12172,7 +12039,6 @@
           <t>Christy Peterson</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -12222,7 +12088,6 @@
       <c r="X111" s="5" t="n">
         <v>2057</v>
       </c>
-      <c r="Y111" t="inlineStr"/>
       <c r="Z111" s="4" t="n">
         <v>0</v>
       </c>
@@ -12324,7 +12189,6 @@
       <c r="X112" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y112" t="inlineStr"/>
       <c r="Z112" s="4" t="n">
         <v>0</v>
       </c>
@@ -12432,7 +12296,6 @@
       <c r="X113" s="5" t="n">
         <v>3552599</v>
       </c>
-      <c r="Y113" t="inlineStr"/>
       <c r="Z113" s="4" t="n">
         <v>0</v>
       </c>
@@ -12534,7 +12397,6 @@
       <c r="X114" s="5" t="n">
         <v>1010297</v>
       </c>
-      <c r="Y114" t="inlineStr"/>
       <c r="Z114" s="4" t="n">
         <v>0</v>
       </c>
@@ -12642,7 +12504,6 @@
       <c r="X115" s="5" t="n">
         <v>2177288</v>
       </c>
-      <c r="Y115" t="inlineStr"/>
       <c r="Z115" s="4" t="n">
         <v>0</v>
       </c>
@@ -12744,7 +12605,6 @@
       <c r="X116" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y116" t="inlineStr"/>
       <c r="Z116" s="4" t="n">
         <v>0</v>
       </c>
@@ -12846,7 +12706,6 @@
       <c r="X117" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y117" t="inlineStr"/>
       <c r="Z117" s="4" t="n">
         <v>0</v>
       </c>
@@ -12948,7 +12807,6 @@
       <c r="X118" s="5" t="n">
         <v>5393673</v>
       </c>
-      <c r="Y118" t="inlineStr"/>
       <c r="Z118" s="4" t="n">
         <v>0</v>
       </c>
@@ -12996,7 +12854,6 @@
           <t>Amy Chai</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -13046,7 +12903,6 @@
       <c r="X119" s="5" t="n">
         <v>20827</v>
       </c>
-      <c r="Y119" t="inlineStr"/>
       <c r="Z119" s="4" t="n">
         <v>0</v>
       </c>
@@ -13148,7 +13004,6 @@
       <c r="X120" s="5" t="n">
         <v>283997</v>
       </c>
-      <c r="Y120" t="inlineStr"/>
       <c r="Z120" s="4" t="n">
         <v>0</v>
       </c>
@@ -13250,7 +13105,6 @@
       <c r="X121" s="5" t="n">
         <v>14649</v>
       </c>
-      <c r="Y121" t="inlineStr"/>
       <c r="Z121" s="4" t="n">
         <v>0</v>
       </c>
@@ -13352,7 +13206,6 @@
       <c r="X122" s="5" t="n">
         <v>46809</v>
       </c>
-      <c r="Y122" t="inlineStr"/>
       <c r="Z122" s="4" t="n">
         <v>0</v>
       </c>
@@ -13454,7 +13307,6 @@
       <c r="X123" s="5" t="n">
         <v>311676</v>
       </c>
-      <c r="Y123" t="inlineStr"/>
       <c r="Z123" s="4" t="n">
         <v>0</v>
       </c>
@@ -13556,7 +13408,6 @@
       <c r="X124" s="5" t="n">
         <v>769</v>
       </c>
-      <c r="Y124" t="inlineStr"/>
       <c r="Z124" s="4" t="n">
         <v>0</v>
       </c>
@@ -13658,7 +13509,6 @@
       <c r="X125" s="5" t="n">
         <v>3789738</v>
       </c>
-      <c r="Y125" t="inlineStr"/>
       <c r="Z125" s="4" t="n">
         <v>0</v>
       </c>
@@ -13706,7 +13556,6 @@
           <t>Austin Rogers</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>REP</t>
@@ -13756,7 +13605,6 @@
       <c r="X126" s="5" t="n">
         <v>1010277</v>
       </c>
-      <c r="Y126" t="inlineStr"/>
       <c r="Z126" s="4" t="n">
         <v>0</v>
       </c>
@@ -13858,7 +13706,6 @@
       <c r="X127" s="5" t="n">
         <v>2045294</v>
       </c>
-      <c r="Y127" t="inlineStr"/>
       <c r="Z127" s="4" t="n">
         <v>0</v>
       </c>
@@ -13960,7 +13807,6 @@
       <c r="X128" s="5" t="n">
         <v>2163376</v>
       </c>
-      <c r="Y128" t="inlineStr"/>
       <c r="Z128" s="4" t="n">
         <v>0</v>
       </c>
@@ -14062,7 +13908,6 @@
       <c r="X129" s="5" t="n">
         <v>726727</v>
       </c>
-      <c r="Y129" t="inlineStr"/>
       <c r="Z129" s="4" t="n">
         <v>0</v>
       </c>
@@ -14164,7 +14009,6 @@
       <c r="X130" s="5" t="n">
         <v>4286207</v>
       </c>
-      <c r="Y130" t="inlineStr"/>
       <c r="Z130" s="4" t="n">
         <v>0</v>
       </c>
@@ -14212,7 +14056,6 @@
           <t>Ryan Elijah</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>REP</t>
@@ -14262,7 +14105,6 @@
       <c r="X131" s="5" t="n">
         <v>355955</v>
       </c>
-      <c r="Y131" t="inlineStr"/>
       <c r="Z131" s="4" t="n">
         <v>0</v>
       </c>
@@ -14370,7 +14212,6 @@
       <c r="X132" s="5" t="n">
         <v>1824838</v>
       </c>
-      <c r="Y132" t="inlineStr"/>
       <c r="Z132" s="4" t="n">
         <v>0</v>
       </c>
@@ -14472,7 +14313,6 @@
       <c r="X133" s="5" t="n">
         <v>1298516</v>
       </c>
-      <c r="Y133" t="inlineStr"/>
       <c r="Z133" s="4" t="n">
         <v>0</v>
       </c>
@@ -14574,7 +14414,6 @@
       <c r="X134" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y134" t="inlineStr"/>
       <c r="Z134" s="4" t="n">
         <v>0</v>
       </c>
@@ -14622,7 +14461,6 @@
           <t>Joe Strada</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>REP</t>
@@ -14678,7 +14516,6 @@
       <c r="X135" s="5" t="n">
         <v>5248640</v>
       </c>
-      <c r="Y135" t="inlineStr"/>
       <c r="Z135" s="4" t="n">
         <v>0</v>
       </c>
@@ -14780,7 +14617,6 @@
       <c r="X136" s="5" t="n">
         <v>1588538</v>
       </c>
-      <c r="Y136" t="inlineStr"/>
       <c r="Z136" s="4" t="n">
         <v>0</v>
       </c>
@@ -14888,7 +14724,6 @@
       <c r="X137" s="5" t="n">
         <v>3233312</v>
       </c>
-      <c r="Y137" t="inlineStr"/>
       <c r="Z137" s="4" t="n">
         <v>0</v>
       </c>
@@ -14996,7 +14831,6 @@
       <c r="X138" s="5" t="n">
         <v>2116747</v>
       </c>
-      <c r="Y138" t="inlineStr"/>
       <c r="Z138" s="4" t="n">
         <v>0</v>
       </c>
@@ -15098,7 +14932,6 @@
       <c r="X139" s="5" t="n">
         <v>2346664</v>
       </c>
-      <c r="Y139" t="inlineStr"/>
       <c r="Z139" s="4" t="n">
         <v>0</v>
       </c>
@@ -15146,7 +14979,6 @@
           <t>Sydney Gruters</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>REP</t>
@@ -15196,7 +15028,6 @@
       <c r="X140" s="5" t="n">
         <v>1087683</v>
       </c>
-      <c r="Y140" t="inlineStr"/>
       <c r="Z140" s="4" t="n">
         <v>0</v>
       </c>
@@ -15298,7 +15129,6 @@
       <c r="X141" s="5" t="n">
         <v>1337887</v>
       </c>
-      <c r="Y141" t="inlineStr"/>
       <c r="Z141" s="4" t="n">
         <v>0</v>
       </c>
@@ -15400,7 +15230,6 @@
       <c r="X142" s="5" t="n">
         <v>850000</v>
       </c>
-      <c r="Y142" t="inlineStr"/>
       <c r="Z142" s="4" t="n">
         <v>0</v>
       </c>
@@ -15448,7 +15277,6 @@
           <t>Jim Schwartzel</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>REP</t>
@@ -15498,7 +15326,6 @@
       <c r="X143" s="5" t="n">
         <v>2065485</v>
       </c>
-      <c r="Y143" t="inlineStr"/>
       <c r="Z143" s="4" t="n">
         <v>0</v>
       </c>
@@ -15600,7 +15427,6 @@
       <c r="X144" s="5" t="n">
         <v>63849</v>
       </c>
-      <c r="Y144" t="inlineStr"/>
       <c r="Z144" s="4" t="n">
         <v>0</v>
       </c>
@@ -15702,7 +15528,6 @@
       <c r="X145" s="5" t="n">
         <v>4308890</v>
       </c>
-      <c r="Y145" t="inlineStr"/>
       <c r="Z145" s="4" t="n">
         <v>0</v>
       </c>
@@ -15750,7 +15575,6 @@
           <t>Casey Askar</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>REP</t>
@@ -15806,7 +15630,6 @@
       <c r="X146" s="5" t="n">
         <v>2567760</v>
       </c>
-      <c r="Y146" t="inlineStr"/>
       <c r="Z146" s="4" t="n">
         <v>0</v>
       </c>
@@ -15908,7 +15731,6 @@
       <c r="X147" s="5" t="n">
         <v>162515</v>
       </c>
-      <c r="Y147" t="inlineStr"/>
       <c r="Z147" s="4" t="n">
         <v>0</v>
       </c>
@@ -15956,7 +15778,6 @@
           <t>Te Brown</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -16006,7 +15827,6 @@
       <c r="X148" s="5" t="n">
         <v>313318</v>
       </c>
-      <c r="Y148" t="inlineStr"/>
       <c r="Z148" s="4" t="n">
         <v>0</v>
       </c>
@@ -16114,7 +15934,6 @@
       <c r="X149" s="5" t="n">
         <v>2245960</v>
       </c>
-      <c r="Y149" t="inlineStr"/>
       <c r="Z149" s="4" t="n">
         <v>0</v>
       </c>
@@ -16216,7 +16035,6 @@
       <c r="X150" s="5" t="n">
         <v>2060782</v>
       </c>
-      <c r="Y150" t="inlineStr"/>
       <c r="Z150" s="4" t="n">
         <v>0</v>
       </c>
@@ -16324,7 +16142,6 @@
       <c r="X151" s="5" t="n">
         <v>1999399</v>
       </c>
-      <c r="Y151" t="inlineStr"/>
       <c r="Z151" s="4" t="n">
         <v>0</v>
       </c>
@@ -16432,7 +16249,6 @@
       <c r="X152" s="5" t="n">
         <v>601254</v>
       </c>
-      <c r="Y152" t="inlineStr"/>
       <c r="Z152" s="4" t="n">
         <v>0</v>
       </c>
@@ -16480,7 +16296,6 @@
           <t>James Kingston</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>REP</t>
@@ -16530,7 +16345,6 @@
       <c r="X153" s="5" t="n">
         <v>1944528</v>
       </c>
-      <c r="Y153" t="inlineStr"/>
       <c r="Z153" s="4" t="n">
         <v>0</v>
       </c>
@@ -16632,7 +16446,6 @@
       <c r="X154" s="5" t="n">
         <v>142715</v>
       </c>
-      <c r="Y154" t="inlineStr"/>
       <c r="Z154" s="4" t="n">
         <v>0</v>
       </c>
@@ -16734,7 +16547,6 @@
       <c r="X155" s="5" t="n">
         <v>2009763</v>
       </c>
-      <c r="Y155" t="inlineStr"/>
       <c r="Z155" s="4" t="n">
         <v>0</v>
       </c>
@@ -16836,7 +16648,6 @@
       <c r="X156" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y156" t="inlineStr"/>
       <c r="Z156" s="4" t="n">
         <v>0</v>
       </c>
@@ -16938,7 +16749,6 @@
       <c r="X157" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y157" t="inlineStr"/>
       <c r="Z157" s="4" t="n">
         <v>0</v>
       </c>
@@ -17040,7 +16850,6 @@
       <c r="X158" s="5" t="n">
         <v>10320</v>
       </c>
-      <c r="Y158" t="inlineStr"/>
       <c r="Z158" s="4" t="n">
         <v>0</v>
       </c>
@@ -17142,7 +16951,6 @@
       <c r="X159" s="5" t="n">
         <v>1642413</v>
       </c>
-      <c r="Y159" t="inlineStr"/>
       <c r="Z159" s="4" t="n">
         <v>0</v>
       </c>
@@ -17244,7 +17052,6 @@
       <c r="X160" s="5" t="n">
         <v>1124952</v>
       </c>
-      <c r="Y160" t="inlineStr"/>
       <c r="Z160" s="4" t="n">
         <v>0</v>
       </c>
@@ -17346,7 +17153,6 @@
       <c r="X161" s="5" t="n">
         <v>671072</v>
       </c>
-      <c r="Y161" t="inlineStr"/>
       <c r="Z161" s="4" t="n">
         <v>0</v>
       </c>
@@ -17394,7 +17200,6 @@
           <t>Houston Gaines</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
           <t>REP</t>
@@ -17444,7 +17249,6 @@
       <c r="X162" s="5" t="n">
         <v>2303880</v>
       </c>
-      <c r="Y162" t="inlineStr"/>
       <c r="Z162" s="4" t="n">
         <v>0</v>
       </c>
@@ -17492,7 +17296,6 @@
           <t>John Cowan</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>REP</t>
@@ -17542,7 +17345,6 @@
       <c r="X163" s="5" t="n">
         <v>2347796</v>
       </c>
-      <c r="Y163" t="inlineStr"/>
       <c r="Z163" s="4" t="n">
         <v>0</v>
       </c>
@@ -17644,7 +17446,6 @@
       <c r="X164" s="5" t="n">
         <v>993220</v>
       </c>
-      <c r="Y164" t="inlineStr"/>
       <c r="Z164" s="4" t="n">
         <v>0</v>
       </c>
@@ -17692,7 +17493,6 @@
           <t>Jonathan Chavez</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -17742,7 +17542,6 @@
       <c r="X165" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y165" t="inlineStr"/>
       <c r="Z165" s="4" t="n">
         <v>0</v>
       </c>
@@ -17844,7 +17643,6 @@
       <c r="X166" s="5" t="n">
         <v>1846892</v>
       </c>
-      <c r="Y166" t="inlineStr"/>
       <c r="Z166" s="4" t="n">
         <v>0</v>
       </c>
@@ -17946,7 +17744,6 @@
       <c r="X167" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y167" t="inlineStr"/>
       <c r="Z167" s="4" t="n">
         <v>0</v>
       </c>
@@ -18048,7 +17845,6 @@
       <c r="X168" s="5" t="n">
         <v>122615</v>
       </c>
-      <c r="Y168" t="inlineStr"/>
       <c r="Z168" s="4" t="n">
         <v>0</v>
       </c>
@@ -18156,7 +17952,6 @@
       <c r="X169" s="5" t="n">
         <v>7208271</v>
       </c>
-      <c r="Y169" t="inlineStr"/>
       <c r="Z169" s="4" t="n">
         <v>0</v>
       </c>
@@ -18204,7 +17999,6 @@
           <t>Joe Mitchell</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>REP</t>
@@ -18260,7 +18054,6 @@
       <c r="X170" s="5" t="n">
         <v>1938593</v>
       </c>
-      <c r="Y170" t="inlineStr"/>
       <c r="Z170" s="4" t="n">
         <v>0</v>
       </c>
@@ -18368,7 +18161,6 @@
       <c r="X171" s="5" t="n">
         <v>4869249</v>
       </c>
-      <c r="Y171" t="inlineStr"/>
       <c r="Z171" s="4" t="n">
         <v>0</v>
       </c>
@@ -18416,7 +18208,6 @@
           <t>Chris McGowan</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
           <t>REP</t>
@@ -18466,7 +18257,6 @@
       <c r="X172" s="5" t="n">
         <v>679844</v>
       </c>
-      <c r="Y172" t="inlineStr"/>
       <c r="Z172" s="4" t="n">
         <v>0</v>
       </c>
@@ -18574,7 +18364,6 @@
       <c r="X173" s="5" t="n">
         <v>662615</v>
       </c>
-      <c r="Y173" t="inlineStr"/>
       <c r="Z173" s="4" t="n">
         <v>0</v>
       </c>
@@ -18676,7 +18465,6 @@
       <c r="X174" s="5" t="n">
         <v>1118093</v>
       </c>
-      <c r="Y174" t="inlineStr"/>
       <c r="Z174" s="4" t="n">
         <v>0</v>
       </c>
@@ -18778,7 +18566,6 @@
       <c r="X175" s="5" t="n">
         <v>63316</v>
       </c>
-      <c r="Y175" t="inlineStr"/>
       <c r="Z175" s="4" t="n">
         <v>0</v>
       </c>
@@ -18826,7 +18613,6 @@
           <t>Calvin Coleman</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -18876,7 +18662,6 @@
       <c r="X176" s="5" t="n">
         <v>7994</v>
       </c>
-      <c r="Y176" t="inlineStr"/>
       <c r="Z176" s="4" t="n">
         <v>0</v>
       </c>
@@ -18978,7 +18763,6 @@
       <c r="X177" s="5" t="n">
         <v>8080</v>
       </c>
-      <c r="Y177" t="inlineStr"/>
       <c r="Z177" s="4" t="n">
         <v>0</v>
       </c>
@@ -19026,7 +18810,6 @@
           <t>Lupe Castillo</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -19082,7 +18865,6 @@
       <c r="X178" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y178" t="inlineStr"/>
       <c r="Z178" s="4" t="n">
         <v>0</v>
       </c>
@@ -19184,7 +18966,6 @@
       <c r="X179" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y179" t="inlineStr"/>
       <c r="Z179" s="4" t="n">
         <v>0</v>
       </c>
@@ -19286,7 +19067,6 @@
       <c r="X180" s="5" t="n">
         <v>313038</v>
       </c>
-      <c r="Y180" t="inlineStr"/>
       <c r="Z180" s="4" t="n">
         <v>0</v>
       </c>
@@ -19334,7 +19114,6 @@
           <t>Chad Koppie</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -19384,7 +19163,6 @@
       <c r="X181" s="5" t="n">
         <v>55451</v>
       </c>
-      <c r="Y181" t="inlineStr"/>
       <c r="Z181" s="4" t="n">
         <v>0</v>
       </c>
@@ -19432,7 +19210,6 @@
           <t>Jennifer Davis</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -19482,7 +19259,6 @@
       <c r="X182" s="5" t="n">
         <v>1476009</v>
       </c>
-      <c r="Y182" t="inlineStr"/>
       <c r="Z182" s="4" t="n">
         <v>0</v>
       </c>
@@ -19530,7 +19306,6 @@
           <t>John Elleson</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -19580,7 +19355,6 @@
       <c r="X183" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y183" t="inlineStr"/>
       <c r="Z183" s="4" t="n">
         <v>0</v>
       </c>
@@ -19682,7 +19456,6 @@
       <c r="X184" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y184" t="inlineStr"/>
       <c r="Z184" s="4" t="n">
         <v>0</v>
       </c>
@@ -19784,7 +19557,6 @@
       <c r="X185" s="5" t="n">
         <v>311439</v>
       </c>
-      <c r="Y185" t="inlineStr"/>
       <c r="Z185" s="4" t="n">
         <v>0</v>
       </c>
@@ -19886,7 +19658,6 @@
       <c r="X186" s="5" t="n">
         <v>1327225</v>
       </c>
-      <c r="Y186" t="inlineStr"/>
       <c r="Z186" s="4" t="n">
         <v>0</v>
       </c>
@@ -19988,7 +19759,6 @@
       <c r="X187" s="5" t="n">
         <v>348237</v>
       </c>
-      <c r="Y187" t="inlineStr"/>
       <c r="Z187" s="4" t="n">
         <v>0</v>
       </c>
@@ -20090,7 +19860,6 @@
       <c r="X188" s="5" t="n">
         <v>140848</v>
       </c>
-      <c r="Y188" t="inlineStr"/>
       <c r="Z188" s="4" t="n">
         <v>0</v>
       </c>
@@ -20192,7 +19961,6 @@
       <c r="X189" s="5" t="n">
         <v>1331399</v>
       </c>
-      <c r="Y189" t="inlineStr"/>
       <c r="Z189" s="4" t="n">
         <v>0</v>
       </c>
@@ -20294,7 +20062,6 @@
       <c r="X190" s="5" t="n">
         <v>3672739</v>
       </c>
-      <c r="Y190" t="inlineStr"/>
       <c r="Z190" s="4" t="n">
         <v>0</v>
       </c>
@@ -20396,7 +20163,6 @@
       <c r="X191" s="5" t="n">
         <v>308832</v>
       </c>
-      <c r="Y191" t="inlineStr"/>
       <c r="Z191" s="4" t="n">
         <v>0</v>
       </c>
@@ -20498,7 +20264,6 @@
       <c r="X192" s="5" t="n">
         <v>2376256</v>
       </c>
-      <c r="Y192" t="inlineStr"/>
       <c r="Z192" s="4" t="n">
         <v>0</v>
       </c>
@@ -20600,7 +20365,6 @@
       <c r="X193" s="5" t="n">
         <v>5246030</v>
       </c>
-      <c r="Y193" t="inlineStr"/>
       <c r="Z193" s="4" t="n">
         <v>0</v>
       </c>
@@ -20702,7 +20466,6 @@
       <c r="X194" s="5" t="n">
         <v>839565</v>
       </c>
-      <c r="Y194" t="inlineStr"/>
       <c r="Z194" s="4" t="n">
         <v>0</v>
       </c>
@@ -20804,7 +20567,6 @@
       <c r="X195" s="5" t="n">
         <v>358293</v>
       </c>
-      <c r="Y195" t="inlineStr"/>
       <c r="Z195" s="4" t="n">
         <v>0</v>
       </c>
@@ -20912,7 +20674,6 @@
       <c r="X196" s="5" t="n">
         <v>1327228</v>
       </c>
-      <c r="Y196" t="inlineStr"/>
       <c r="Z196" s="4" t="n">
         <v>0</v>
       </c>
@@ -21014,7 +20775,6 @@
       <c r="X197" s="5" t="n">
         <v>2426805</v>
       </c>
-      <c r="Y197" t="inlineStr"/>
       <c r="Z197" s="4" t="n">
         <v>0</v>
       </c>
@@ -21116,7 +20876,6 @@
       <c r="X198" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y198" t="inlineStr"/>
       <c r="Z198" s="4" t="n">
         <v>0</v>
       </c>
@@ -21218,7 +20977,6 @@
       <c r="X199" s="5" t="n">
         <v>1171366</v>
       </c>
-      <c r="Y199" t="inlineStr"/>
       <c r="Z199" s="4" t="n">
         <v>0</v>
       </c>
@@ -21320,7 +21078,6 @@
       <c r="X200" s="5" t="n">
         <v>1856572</v>
       </c>
-      <c r="Y200" t="inlineStr"/>
       <c r="Z200" s="4" t="n">
         <v>0</v>
       </c>
@@ -21422,7 +21179,6 @@
       <c r="X201" s="5" t="n">
         <v>1488465</v>
       </c>
-      <c r="Y201" t="inlineStr"/>
       <c r="Z201" s="4" t="n">
         <v>0</v>
       </c>
@@ -21524,7 +21280,6 @@
       <c r="X202" s="5" t="n">
         <v>1457605</v>
       </c>
-      <c r="Y202" t="inlineStr"/>
       <c r="Z202" s="4" t="n">
         <v>0</v>
       </c>
@@ -21626,7 +21381,6 @@
       <c r="X203" s="5" t="n">
         <v>18916</v>
       </c>
-      <c r="Y203" t="inlineStr"/>
       <c r="Z203" s="4" t="n">
         <v>0</v>
       </c>
@@ -21728,7 +21482,6 @@
       <c r="X204" s="5" t="n">
         <v>1855035</v>
       </c>
-      <c r="Y204" t="inlineStr"/>
       <c r="Z204" s="4" t="n">
         <v>0</v>
       </c>
@@ -21830,7 +21583,6 @@
       <c r="X205" s="5" t="n">
         <v>1899533</v>
       </c>
-      <c r="Y205" t="inlineStr"/>
       <c r="Z205" s="4" t="n">
         <v>0</v>
       </c>
@@ -21932,7 +21684,6 @@
       <c r="X206" s="5" t="n">
         <v>4707593</v>
       </c>
-      <c r="Y206" t="inlineStr"/>
       <c r="Z206" s="4" t="n">
         <v>0</v>
       </c>
@@ -22034,7 +21785,6 @@
       <c r="X207" s="5" t="n">
         <v>38069</v>
       </c>
-      <c r="Y207" t="inlineStr"/>
       <c r="Z207" s="4" t="n">
         <v>0</v>
       </c>
@@ -22082,7 +21832,6 @@
           <t>Ed Gallrein</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>REP</t>
@@ -22132,7 +21881,6 @@
       <c r="X208" s="5" t="n">
         <v>3567324</v>
       </c>
-      <c r="Y208" t="inlineStr"/>
       <c r="Z208" s="4" t="n">
         <v>0</v>
       </c>
@@ -22234,7 +21982,6 @@
       <c r="X209" s="5" t="n">
         <v>849758</v>
       </c>
-      <c r="Y209" t="inlineStr"/>
       <c r="Z209" s="4" t="n">
         <v>0</v>
       </c>
@@ -22282,7 +22029,6 @@
           <t>Ralph Alvarado</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
           <t>REP</t>
@@ -22338,7 +22084,6 @@
       <c r="X210" s="5" t="n">
         <v>1521813</v>
       </c>
-      <c r="Y210" t="inlineStr"/>
       <c r="Z210" s="4" t="n">
         <v>0</v>
       </c>
@@ -22440,7 +22185,6 @@
       <c r="X211" s="5" t="n">
         <v>10638030</v>
       </c>
-      <c r="Y211" t="inlineStr"/>
       <c r="Z211" s="4" t="n">
         <v>0</v>
       </c>
@@ -22542,7 +22286,6 @@
       <c r="X212" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y212" t="inlineStr"/>
       <c r="Z212" s="4" t="n">
         <v>0</v>
       </c>
@@ -22644,7 +22387,6 @@
       <c r="X213" s="5" t="n">
         <v>822841</v>
       </c>
-      <c r="Y213" t="inlineStr"/>
       <c r="Z213" s="4" t="n">
         <v>0</v>
       </c>
@@ -22746,7 +22488,6 @@
       <c r="X214" s="5" t="n">
         <v>20976864</v>
       </c>
-      <c r="Y214" t="inlineStr"/>
       <c r="Z214" s="4" t="n">
         <v>0</v>
       </c>
@@ -22794,7 +22535,6 @@
           <t>Blake Miguez</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
           <t>REP</t>
@@ -22844,7 +22584,6 @@
       <c r="X215" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y215" t="inlineStr"/>
       <c r="Z215" s="4" t="n">
         <v>0</v>
       </c>
@@ -22892,7 +22631,6 @@
           <t>Peter Williams</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -22942,7 +22680,6 @@
       <c r="X216" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y216" t="inlineStr"/>
       <c r="Z216" s="4" t="n">
         <v>0</v>
       </c>
@@ -23044,7 +22781,6 @@
       <c r="X217" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y217" t="inlineStr"/>
       <c r="Z217" s="4" t="n">
         <v>0</v>
       </c>
@@ -23146,7 +22882,6 @@
       <c r="X218" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y218" t="inlineStr"/>
       <c r="Z218" s="4" t="n">
         <v>0</v>
       </c>
@@ -23248,7 +22983,6 @@
       <c r="X219" s="5" t="n">
         <v>7121</v>
       </c>
-      <c r="Y219" t="inlineStr"/>
       <c r="Z219" s="4" t="n">
         <v>0</v>
       </c>
@@ -23350,7 +23084,6 @@
       <c r="X220" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y220" t="inlineStr"/>
       <c r="Z220" s="4" t="n">
         <v>0</v>
       </c>
@@ -23452,7 +23185,6 @@
       <c r="X221" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y221" t="inlineStr"/>
       <c r="Z221" s="4" t="n">
         <v>0</v>
       </c>
@@ -23500,7 +23232,6 @@
           <t>John Field</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -23550,7 +23281,6 @@
       <c r="X222" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y222" t="inlineStr"/>
       <c r="Z222" s="4" t="n">
         <v>0</v>
       </c>
@@ -23652,7 +23382,6 @@
       <c r="X223" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y223" t="inlineStr"/>
       <c r="Z223" s="4" t="n">
         <v>0</v>
       </c>
@@ -23754,7 +23483,6 @@
       <c r="X224" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y224" t="inlineStr"/>
       <c r="Z224" s="4" t="n">
         <v>0</v>
       </c>
@@ -23856,7 +23584,6 @@
       <c r="X225" s="5" t="n">
         <v>175122</v>
       </c>
-      <c r="Y225" t="inlineStr"/>
       <c r="Z225" s="4" t="n">
         <v>0</v>
       </c>
@@ -23958,7 +23685,6 @@
       <c r="X226" s="5" t="n">
         <v>2319668</v>
       </c>
-      <c r="Y226" t="inlineStr"/>
       <c r="Z226" s="4" t="n">
         <v>0</v>
       </c>
@@ -24060,7 +23786,6 @@
       <c r="X227" s="5" t="n">
         <v>20194</v>
       </c>
-      <c r="Y227" t="inlineStr"/>
       <c r="Z227" s="4" t="n">
         <v>0</v>
       </c>
@@ -24162,7 +23887,6 @@
       <c r="X228" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y228" t="inlineStr"/>
       <c r="Z228" s="4" t="n">
         <v>0</v>
       </c>
@@ -24210,7 +23934,6 @@
           <t>Republican candidate (MD-04)</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -24260,7 +23983,6 @@
       <c r="X229" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y229" t="inlineStr"/>
       <c r="Z229" s="4" t="n">
         <v>0</v>
       </c>
@@ -24308,7 +24030,6 @@
           <t>Chris Chaffee</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -24358,7 +24079,6 @@
       <c r="X230" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y230" t="inlineStr"/>
       <c r="Z230" s="4" t="n">
         <v>0</v>
       </c>
@@ -24460,7 +24180,6 @@
       <c r="X231" s="5" t="n">
         <v>403934</v>
       </c>
-      <c r="Y231" t="inlineStr"/>
       <c r="Z231" s="4" t="n">
         <v>0</v>
       </c>
@@ -24562,7 +24281,6 @@
       <c r="X232" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y232" t="inlineStr"/>
       <c r="Z232" s="4" t="n">
         <v>0</v>
       </c>
@@ -24664,7 +24382,6 @@
       <c r="X233" s="5" t="n">
         <v>16590</v>
       </c>
-      <c r="Y233" t="inlineStr"/>
       <c r="Z233" s="4" t="n">
         <v>0</v>
       </c>
@@ -24723,7 +24440,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.31</v>
+        <v>30.2</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24766,7 +24483,6 @@
       <c r="X234" s="5" t="n">
         <v>75680</v>
       </c>
-      <c r="Y234" t="inlineStr"/>
       <c r="Z234" s="4" t="n">
         <v>0</v>
       </c>
@@ -24814,20 +24530,19 @@
           <t>Paul LePage</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.48</v>
+        <v>-4.58</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>36.3</v>
+        <v>35.9</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>63.7</v>
+        <v>64.2</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24870,7 +24585,6 @@
       <c r="X235" s="5" t="n">
         <v>2563901</v>
       </c>
-      <c r="Y235" t="inlineStr"/>
       <c r="Z235" s="4" t="n">
         <v>0</v>
       </c>
@@ -24972,7 +24686,6 @@
       <c r="X236" s="5" t="n">
         <v>1917574</v>
       </c>
-      <c r="Y236" t="inlineStr"/>
       <c r="Z236" s="4" t="n">
         <v>0</v>
       </c>
@@ -25074,7 +24787,6 @@
       <c r="X237" s="5" t="n">
         <v>1652235</v>
       </c>
-      <c r="Y237" t="inlineStr"/>
       <c r="Z237" s="4" t="n">
         <v>0</v>
       </c>
@@ -25176,7 +24888,6 @@
       <c r="X238" s="5" t="n">
         <v>551697</v>
       </c>
-      <c r="Y238" t="inlineStr"/>
       <c r="Z238" s="4" t="n">
         <v>0</v>
       </c>
@@ -25284,7 +24995,6 @@
       <c r="X239" s="5" t="n">
         <v>4093991</v>
       </c>
-      <c r="Y239" t="inlineStr"/>
       <c r="Z239" s="4" t="n">
         <v>0</v>
       </c>
@@ -25386,7 +25096,6 @@
       <c r="X240" s="5" t="n">
         <v>1742399</v>
       </c>
-      <c r="Y240" t="inlineStr"/>
       <c r="Z240" s="4" t="n">
         <v>0</v>
       </c>
@@ -25488,7 +25197,6 @@
       <c r="X241" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y241" t="inlineStr"/>
       <c r="Z241" s="4" t="n">
         <v>0</v>
       </c>
@@ -25596,7 +25304,6 @@
       <c r="X242" s="5" t="n">
         <v>6306828</v>
       </c>
-      <c r="Y242" t="inlineStr"/>
       <c r="Z242" s="4" t="n">
         <v>0</v>
       </c>
@@ -25698,7 +25405,6 @@
       <c r="X243" s="5" t="n">
         <v>224066</v>
       </c>
-      <c r="Y243" t="inlineStr"/>
       <c r="Z243" s="4" t="n">
         <v>0</v>
       </c>
@@ -25800,7 +25506,6 @@
       <c r="X244" s="5" t="n">
         <v>5242309</v>
       </c>
-      <c r="Y244" t="inlineStr"/>
       <c r="Z244" s="4" t="n">
         <v>0</v>
       </c>
@@ -25848,7 +25553,6 @@
           <t>Michael Bouchard Jr.</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>REP</t>
@@ -25904,7 +25608,6 @@
       <c r="X245" s="5" t="n">
         <v>1623745</v>
       </c>
-      <c r="Y245" t="inlineStr"/>
       <c r="Z245" s="4" t="n">
         <v>0</v>
       </c>
@@ -25952,7 +25655,6 @@
           <t>Ethan Baker</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -26002,7 +25704,6 @@
       <c r="X246" s="5" t="n">
         <v>141876</v>
       </c>
-      <c r="Y246" t="inlineStr"/>
       <c r="Z246" s="4" t="n">
         <v>0</v>
       </c>
@@ -26104,7 +25805,6 @@
       <c r="X247" s="5" t="n">
         <v>775</v>
       </c>
-      <c r="Y247" t="inlineStr"/>
       <c r="Z247" s="4" t="n">
         <v>0</v>
       </c>
@@ -26144,7 +25844,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Shri Thanedar</t>
+          <t>Donavan McKinney</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -26152,18 +25852,13 @@
           <t>T.P. Nykoriak</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
       <c r="I248" s="4" t="n">
-        <v>58.25</v>
+        <v>53.14</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>100</v>
@@ -26183,13 +25878,13 @@
         <v>5.16</v>
       </c>
       <c r="O248" s="4" t="n">
-        <v>58.25</v>
+        <v>53.14</v>
       </c>
       <c r="P248" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q248" s="4" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R248" s="4" t="n">
         <v>42.28</v>
@@ -26201,12 +25896,11 @@
       </c>
       <c r="V248" s="4" t="n"/>
       <c r="W248" s="5" t="n">
-        <v>390276</v>
+        <v>1372309</v>
       </c>
       <c r="X248" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y248" t="inlineStr"/>
       <c r="Z248" s="4" t="n">
         <v>0</v>
       </c>
@@ -26214,10 +25908,10 @@
         <v>0</v>
       </c>
       <c r="AB248" s="4" t="n">
-        <v>79.12</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="AC248" s="4" t="n">
-        <v>20.88</v>
+        <v>23.43</v>
       </c>
       <c r="AD248" s="4" t="n">
         <v>0</v>
@@ -26314,7 +26008,6 @@
       <c r="X249" s="5" t="n">
         <v>2030569</v>
       </c>
-      <c r="Y249" t="inlineStr"/>
       <c r="Z249" s="4" t="n">
         <v>0</v>
       </c>
@@ -26362,7 +26055,6 @@
           <t>Eric Pratt</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -26418,7 +26110,6 @@
       <c r="X250" s="5" t="n">
         <v>511213</v>
       </c>
-      <c r="Y250" t="inlineStr"/>
       <c r="Z250" s="4" t="n">
         <v>0</v>
       </c>
@@ -26520,7 +26211,6 @@
       <c r="X251" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y251" t="inlineStr"/>
       <c r="Z251" s="4" t="n">
         <v>0</v>
       </c>
@@ -26622,7 +26312,6 @@
       <c r="X252" s="5" t="n">
         <v>28031</v>
       </c>
-      <c r="Y252" t="inlineStr"/>
       <c r="Z252" s="4" t="n">
         <v>0</v>
       </c>
@@ -26724,7 +26413,6 @@
       <c r="X253" s="5" t="n">
         <v>747046</v>
       </c>
-      <c r="Y253" t="inlineStr"/>
       <c r="Z253" s="4" t="n">
         <v>0</v>
       </c>
@@ -26826,7 +26514,6 @@
       <c r="X254" s="5" t="n">
         <v>9786064</v>
       </c>
-      <c r="Y254" t="inlineStr"/>
       <c r="Z254" s="4" t="n">
         <v>0</v>
       </c>
@@ -26928,7 +26615,6 @@
       <c r="X255" s="5" t="n">
         <v>1286028</v>
       </c>
-      <c r="Y255" t="inlineStr"/>
       <c r="Z255" s="4" t="n">
         <v>0</v>
       </c>
@@ -27030,7 +26716,6 @@
       <c r="X256" s="5" t="n">
         <v>1996898</v>
       </c>
-      <c r="Y256" t="inlineStr"/>
       <c r="Z256" s="4" t="n">
         <v>0</v>
       </c>
@@ -27132,7 +26817,6 @@
       <c r="X257" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y257" t="inlineStr"/>
       <c r="Z257" s="4" t="n">
         <v>0</v>
       </c>
@@ -27240,7 +26924,6 @@
       <c r="X258" s="5" t="n">
         <v>3528095</v>
       </c>
-      <c r="Y258" t="inlineStr"/>
       <c r="Z258" s="4" t="n">
         <v>0</v>
       </c>
@@ -27342,7 +27025,6 @@
       <c r="X259" s="5" t="n">
         <v>950350</v>
       </c>
-      <c r="Y259" t="inlineStr"/>
       <c r="Z259" s="4" t="n">
         <v>0</v>
       </c>
@@ -27444,7 +27126,6 @@
       <c r="X260" s="5" t="n">
         <v>1392968</v>
       </c>
-      <c r="Y260" t="inlineStr"/>
       <c r="Z260" s="4" t="n">
         <v>0</v>
       </c>
@@ -27546,7 +27227,6 @@
       <c r="X261" s="5" t="n">
         <v>331764</v>
       </c>
-      <c r="Y261" t="inlineStr"/>
       <c r="Z261" s="4" t="n">
         <v>0</v>
       </c>
@@ -27594,7 +27274,6 @@
           <t>Chris Stigall</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
           <t>REP</t>
@@ -27644,7 +27323,6 @@
       <c r="X262" s="5" t="n">
         <v>599336</v>
       </c>
-      <c r="Y262" t="inlineStr"/>
       <c r="Z262" s="4" t="n">
         <v>0</v>
       </c>
@@ -27746,7 +27424,6 @@
       <c r="X263" s="5" t="n">
         <v>1460463</v>
       </c>
-      <c r="Y263" t="inlineStr"/>
       <c r="Z263" s="4" t="n">
         <v>0</v>
       </c>
@@ -27848,7 +27525,6 @@
       <c r="X264" s="5" t="n">
         <v>5264183</v>
       </c>
-      <c r="Y264" t="inlineStr"/>
       <c r="Z264" s="4" t="n">
         <v>0</v>
       </c>
@@ -27950,7 +27626,6 @@
       <c r="X265" s="5" t="n">
         <v>1004205</v>
       </c>
-      <c r="Y265" t="inlineStr"/>
       <c r="Z265" s="4" t="n">
         <v>0</v>
       </c>
@@ -28052,7 +27727,6 @@
       <c r="X266" s="5" t="n">
         <v>45390</v>
       </c>
-      <c r="Y266" t="inlineStr"/>
       <c r="Z266" s="4" t="n">
         <v>0</v>
       </c>
@@ -28154,7 +27828,6 @@
       <c r="X267" s="5" t="n">
         <v>822761</v>
       </c>
-      <c r="Y267" t="inlineStr"/>
       <c r="Z267" s="4" t="n">
         <v>0</v>
       </c>
@@ -28256,7 +27929,6 @@
       <c r="X268" s="5" t="n">
         <v>990106</v>
       </c>
-      <c r="Y268" t="inlineStr"/>
       <c r="Z268" s="4" t="n">
         <v>0</v>
       </c>
@@ -28304,20 +27976,19 @@
           <t>Aaron Flint</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-7.39</v>
+        <v>-7.4</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>88.7</v>
+        <v>88.8</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28325,13 +27996,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.7</v>
+        <v>-12.71</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.66</v>
+        <v>-8.68</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28360,7 +28031,6 @@
       <c r="X269" s="5" t="n">
         <v>1303394</v>
       </c>
-      <c r="Y269" t="inlineStr"/>
       <c r="Z269" s="4" t="n">
         <v>0</v>
       </c>
@@ -28419,7 +28089,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-34.4</v>
+        <v>-34.41</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28433,13 +28103,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.66</v>
+        <v>-31.67</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-34.4</v>
+        <v>-34.41</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28462,7 +28132,6 @@
       <c r="X270" s="5" t="n">
         <v>2127927</v>
       </c>
-      <c r="Y270" t="inlineStr"/>
       <c r="Z270" s="4" t="n">
         <v>0</v>
       </c>
@@ -28470,10 +28139,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>32.8</v>
+        <v>32.79</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>67.2</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28570,7 +28239,6 @@
       <c r="X271" s="5" t="n">
         <v>3793077</v>
       </c>
-      <c r="Y271" t="inlineStr"/>
       <c r="Z271" s="4" t="n">
         <v>0</v>
       </c>
@@ -28672,7 +28340,6 @@
       <c r="X272" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y272" t="inlineStr"/>
       <c r="Z272" s="4" t="n">
         <v>0</v>
       </c>
@@ -28774,7 +28441,6 @@
       <c r="X273" s="5" t="n">
         <v>2357956</v>
       </c>
-      <c r="Y273" t="inlineStr"/>
       <c r="Z273" s="4" t="n">
         <v>0</v>
       </c>
@@ -28876,7 +28542,6 @@
       <c r="X274" s="5" t="n">
         <v>11917</v>
       </c>
-      <c r="Y274" t="inlineStr"/>
       <c r="Z274" s="4" t="n">
         <v>0</v>
       </c>
@@ -28978,7 +28643,6 @@
       <c r="X275" s="5" t="n">
         <v>1662604</v>
       </c>
-      <c r="Y275" t="inlineStr"/>
       <c r="Z275" s="4" t="n">
         <v>0</v>
       </c>
@@ -29080,7 +28744,6 @@
       <c r="X276" s="5" t="n">
         <v>1226408</v>
       </c>
-      <c r="Y276" t="inlineStr"/>
       <c r="Z276" s="4" t="n">
         <v>0</v>
       </c>
@@ -29182,7 +28845,6 @@
       <c r="X277" s="5" t="n">
         <v>1990423</v>
       </c>
-      <c r="Y277" t="inlineStr"/>
       <c r="Z277" s="4" t="n">
         <v>0</v>
       </c>
@@ -29284,7 +28946,6 @@
       <c r="X278" s="5" t="n">
         <v>1019134</v>
       </c>
-      <c r="Y278" t="inlineStr"/>
       <c r="Z278" s="4" t="n">
         <v>0</v>
       </c>
@@ -29386,7 +29047,6 @@
       <c r="X279" s="5" t="n">
         <v>3215341</v>
       </c>
-      <c r="Y279" t="inlineStr"/>
       <c r="Z279" s="4" t="n">
         <v>0</v>
       </c>
@@ -29494,7 +29154,6 @@
       <c r="X280" s="5" t="n">
         <v>1081821</v>
       </c>
-      <c r="Y280" t="inlineStr"/>
       <c r="Z280" s="4" t="n">
         <v>0</v>
       </c>
@@ -29542,7 +29201,6 @@
           <t>Jennifer Balkcom</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
           <t>REP</t>
@@ -29592,7 +29250,6 @@
       <c r="X281" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y281" t="inlineStr"/>
       <c r="Z281" s="4" t="n">
         <v>0</v>
       </c>
@@ -29694,7 +29351,6 @@
       <c r="X282" s="5" t="n">
         <v>28704</v>
       </c>
-      <c r="Y282" t="inlineStr"/>
       <c r="Z282" s="4" t="n">
         <v>0</v>
       </c>
@@ -29796,7 +29452,6 @@
       <c r="X283" s="5" t="n">
         <v>1339161</v>
       </c>
-      <c r="Y283" t="inlineStr"/>
       <c r="Z283" s="4" t="n">
         <v>0</v>
       </c>
@@ -29904,7 +29559,6 @@
       <c r="X284" s="5" t="n">
         <v>1538952</v>
       </c>
-      <c r="Y284" t="inlineStr"/>
       <c r="Z284" s="4" t="n">
         <v>0</v>
       </c>
@@ -30006,7 +29660,6 @@
       <c r="X285" s="5" t="n">
         <v>1730663</v>
       </c>
-      <c r="Y285" t="inlineStr"/>
       <c r="Z285" s="4" t="n">
         <v>0</v>
       </c>
@@ -30114,7 +29767,6 @@
       <c r="X286" s="5" t="n">
         <v>2368910</v>
       </c>
-      <c r="Y286" t="inlineStr"/>
       <c r="Z286" s="4" t="n">
         <v>0</v>
       </c>
@@ -30162,7 +29814,6 @@
           <t>Brinker Harding</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
           <t>REP</t>
@@ -30218,7 +29869,6 @@
       <c r="X287" s="5" t="n">
         <v>2034386</v>
       </c>
-      <c r="Y287" t="inlineStr"/>
       <c r="Z287" s="4" t="n">
         <v>0</v>
       </c>
@@ -30320,7 +29970,6 @@
       <c r="X288" s="5" t="n">
         <v>1777414</v>
       </c>
-      <c r="Y288" t="inlineStr"/>
       <c r="Z288" s="4" t="n">
         <v>0</v>
       </c>
@@ -30368,7 +30017,6 @@
           <t>Anthony DiLorenzo</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -30418,7 +30066,6 @@
       <c r="X289" s="5" t="n">
         <v>2326786</v>
       </c>
-      <c r="Y289" t="inlineStr"/>
       <c r="Z289" s="4" t="n">
         <v>0</v>
       </c>
@@ -30526,7 +30173,6 @@
       <c r="X290" s="5" t="n">
         <v>1108535</v>
       </c>
-      <c r="Y290" t="inlineStr"/>
       <c r="Z290" s="4" t="n">
         <v>0</v>
       </c>
@@ -30628,7 +30274,6 @@
       <c r="X291" s="5" t="n">
         <v>11125</v>
       </c>
-      <c r="Y291" t="inlineStr"/>
       <c r="Z291" s="4" t="n">
         <v>0</v>
       </c>
@@ -30736,7 +30381,6 @@
       <c r="X292" s="5" t="n">
         <v>1930058</v>
       </c>
-      <c r="Y292" t="inlineStr"/>
       <c r="Z292" s="4" t="n">
         <v>0</v>
       </c>
@@ -30838,7 +30482,6 @@
       <c r="X293" s="5" t="n">
         <v>79190</v>
       </c>
-      <c r="Y293" t="inlineStr"/>
       <c r="Z293" s="4" t="n">
         <v>0</v>
       </c>
@@ -30940,7 +30583,6 @@
       <c r="X294" s="5" t="n">
         <v>592016</v>
       </c>
-      <c r="Y294" t="inlineStr"/>
       <c r="Z294" s="4" t="n">
         <v>0</v>
       </c>
@@ -31042,7 +30684,6 @@
       <c r="X295" s="5" t="n">
         <v>55656</v>
       </c>
-      <c r="Y295" t="inlineStr"/>
       <c r="Z295" s="4" t="n">
         <v>0</v>
       </c>
@@ -31144,7 +30785,6 @@
       <c r="X296" s="5" t="n">
         <v>7645</v>
       </c>
-      <c r="Y296" t="inlineStr"/>
       <c r="Z296" s="4" t="n">
         <v>0</v>
       </c>
@@ -31252,7 +30892,6 @@
       <c r="X297" s="5" t="n">
         <v>4892807</v>
       </c>
-      <c r="Y297" t="inlineStr"/>
       <c r="Z297" s="4" t="n">
         <v>0</v>
       </c>
@@ -31354,7 +30993,6 @@
       <c r="X298" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y298" t="inlineStr"/>
       <c r="Z298" s="4" t="n">
         <v>0</v>
       </c>
@@ -31456,7 +31094,6 @@
       <c r="X299" s="5" t="n">
         <v>437829</v>
       </c>
-      <c r="Y299" t="inlineStr"/>
       <c r="Z299" s="4" t="n">
         <v>0</v>
       </c>
@@ -31558,7 +31195,6 @@
       <c r="X300" s="5" t="n">
         <v>2270</v>
       </c>
-      <c r="Y300" t="inlineStr"/>
       <c r="Z300" s="4" t="n">
         <v>0</v>
       </c>
@@ -31660,7 +31296,6 @@
       <c r="X301" s="5" t="n">
         <v>657711</v>
       </c>
-      <c r="Y301" t="inlineStr"/>
       <c r="Z301" s="4" t="n">
         <v>0</v>
       </c>
@@ -31708,7 +31343,6 @@
           <t>Gregg Mele</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -31758,7 +31392,6 @@
       <c r="X302" s="5" t="n">
         <v>79425</v>
       </c>
-      <c r="Y302" t="inlineStr"/>
       <c r="Z302" s="4" t="n">
         <v>0</v>
       </c>
@@ -31860,7 +31493,6 @@
       <c r="X303" s="5" t="n">
         <v>100340</v>
       </c>
-      <c r="Y303" t="inlineStr"/>
       <c r="Z303" s="4" t="n">
         <v>0</v>
       </c>
@@ -31968,7 +31600,6 @@
       <c r="X304" s="5" t="n">
         <v>1510080</v>
       </c>
-      <c r="Y304" t="inlineStr"/>
       <c r="Z304" s="4" t="n">
         <v>0</v>
       </c>
@@ -32070,7 +31701,6 @@
       <c r="X305" s="5" t="n">
         <v>440623</v>
       </c>
-      <c r="Y305" t="inlineStr"/>
       <c r="Z305" s="4" t="n">
         <v>0</v>
       </c>
@@ -32172,7 +31802,6 @@
       <c r="X306" s="5" t="n">
         <v>1915058</v>
       </c>
-      <c r="Y306" t="inlineStr"/>
       <c r="Z306" s="4" t="n">
         <v>0</v>
       </c>
@@ -32220,7 +31849,6 @@
           <t>David Flippo</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
         <is>
           <t>REP</t>
@@ -32276,7 +31904,6 @@
       <c r="X307" s="5" t="n">
         <v>2275392</v>
       </c>
-      <c r="Y307" t="inlineStr"/>
       <c r="Z307" s="4" t="n">
         <v>0</v>
       </c>
@@ -32378,7 +32005,6 @@
       <c r="X308" s="5" t="n">
         <v>4055410</v>
       </c>
-      <c r="Y308" t="inlineStr"/>
       <c r="Z308" s="4" t="n">
         <v>0</v>
       </c>
@@ -32480,7 +32106,6 @@
       <c r="X309" s="5" t="n">
         <v>884687</v>
       </c>
-      <c r="Y309" t="inlineStr"/>
       <c r="Z309" s="4" t="n">
         <v>0</v>
       </c>
@@ -32588,7 +32213,6 @@
       <c r="X310" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y310" t="inlineStr"/>
       <c r="Z310" s="4" t="n">
         <v>0</v>
       </c>
@@ -32690,7 +32314,6 @@
       <c r="X311" s="5" t="n">
         <v>3513016</v>
       </c>
-      <c r="Y311" t="inlineStr"/>
       <c r="Z311" s="4" t="n">
         <v>0</v>
       </c>
@@ -32792,7 +32415,6 @@
       <c r="X312" s="5" t="n">
         <v>1666542</v>
       </c>
-      <c r="Y312" t="inlineStr"/>
       <c r="Z312" s="4" t="n">
         <v>0</v>
       </c>
@@ -32900,7 +32522,6 @@
       <c r="X313" s="5" t="n">
         <v>264824</v>
       </c>
-      <c r="Y313" t="inlineStr"/>
       <c r="Z313" s="4" t="n">
         <v>0</v>
       </c>
@@ -33002,7 +32623,6 @@
       <c r="X314" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y314" t="inlineStr"/>
       <c r="Z314" s="4" t="n">
         <v>0</v>
       </c>
@@ -33104,7 +32724,6 @@
       <c r="X315" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y315" t="inlineStr"/>
       <c r="Z315" s="4" t="n">
         <v>0</v>
       </c>
@@ -33152,7 +32771,6 @@
           <t>Melvin Rivera</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -33202,7 +32820,6 @@
       <c r="X316" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y316" t="inlineStr"/>
       <c r="Z316" s="4" t="n">
         <v>0</v>
       </c>
@@ -33304,7 +32921,6 @@
       <c r="X317" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y317" t="inlineStr"/>
       <c r="Z317" s="4" t="n">
         <v>0</v>
       </c>
@@ -33406,7 +33022,6 @@
       <c r="X318" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y318" t="inlineStr"/>
       <c r="Z318" s="4" t="n">
         <v>0</v>
       </c>
@@ -33454,7 +33069,6 @@
           <t>Jennifer Moore</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -33504,7 +33118,6 @@
       <c r="X319" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y319" t="inlineStr"/>
       <c r="Z319" s="4" t="n">
         <v>0</v>
       </c>
@@ -33606,7 +33219,6 @@
       <c r="X320" s="5" t="n">
         <v>2750505</v>
       </c>
-      <c r="Y320" t="inlineStr"/>
       <c r="Z320" s="4" t="n">
         <v>0</v>
       </c>
@@ -33654,7 +33266,6 @@
           <t>Caroline Shinkle</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -33704,7 +33315,6 @@
       <c r="X321" s="5" t="n">
         <v>155145</v>
       </c>
-      <c r="Y321" t="inlineStr"/>
       <c r="Z321" s="4" t="n">
         <v>0</v>
       </c>
@@ -33752,7 +33362,6 @@
           <t>Republican candidate (NY-13)</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -33802,7 +33411,6 @@
       <c r="X322" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y322" t="inlineStr"/>
       <c r="Z322" s="4" t="n">
         <v>0</v>
       </c>
@@ -33904,7 +33512,6 @@
       <c r="X323" s="5" t="n">
         <v>342896</v>
       </c>
-      <c r="Y323" t="inlineStr"/>
       <c r="Z323" s="4" t="n">
         <v>0</v>
       </c>
@@ -34006,7 +33613,6 @@
       <c r="X324" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y324" t="inlineStr"/>
       <c r="Z324" s="4" t="n">
         <v>0</v>
       </c>
@@ -34108,7 +33714,6 @@
       <c r="X325" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y325" t="inlineStr"/>
       <c r="Z325" s="4" t="n">
         <v>0</v>
       </c>
@@ -34216,7 +33821,6 @@
       <c r="X326" s="5" t="n">
         <v>8172046</v>
       </c>
-      <c r="Y326" t="inlineStr"/>
       <c r="Z326" s="4" t="n">
         <v>0</v>
       </c>
@@ -34324,7 +33928,6 @@
       <c r="X327" s="5" t="n">
         <v>89698</v>
       </c>
-      <c r="Y327" t="inlineStr"/>
       <c r="Z327" s="4" t="n">
         <v>0</v>
       </c>
@@ -34426,7 +34029,6 @@
       <c r="X328" s="5" t="n">
         <v>1237179</v>
       </c>
-      <c r="Y328" t="inlineStr"/>
       <c r="Z328" s="4" t="n">
         <v>0</v>
       </c>
@@ -34528,7 +34130,6 @@
       <c r="X329" s="5" t="n">
         <v>29026</v>
       </c>
-      <c r="Y329" t="inlineStr"/>
       <c r="Z329" s="4" t="n">
         <v>0</v>
       </c>
@@ -34576,7 +34177,6 @@
           <t>Anthony Constantino</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
           <t>REP</t>
@@ -34632,7 +34232,6 @@
       <c r="X330" s="5" t="n">
         <v>9460254</v>
       </c>
-      <c r="Y330" t="inlineStr"/>
       <c r="Z330" s="4" t="n">
         <v>0</v>
       </c>
@@ -34734,7 +34333,6 @@
       <c r="X331" s="5" t="n">
         <v>267339</v>
       </c>
-      <c r="Y331" t="inlineStr"/>
       <c r="Z331" s="4" t="n">
         <v>0</v>
       </c>
@@ -34836,7 +34434,6 @@
       <c r="X332" s="5" t="n">
         <v>2326405</v>
       </c>
-      <c r="Y332" t="inlineStr"/>
       <c r="Z332" s="4" t="n">
         <v>0</v>
       </c>
@@ -34938,7 +34535,6 @@
       <c r="X333" s="5" t="n">
         <v>2763139</v>
       </c>
-      <c r="Y333" t="inlineStr"/>
       <c r="Z333" s="4" t="n">
         <v>0</v>
       </c>
@@ -35040,7 +34636,6 @@
       <c r="X334" s="5" t="n">
         <v>32416</v>
       </c>
-      <c r="Y334" t="inlineStr"/>
       <c r="Z334" s="4" t="n">
         <v>0</v>
       </c>
@@ -35142,7 +34737,6 @@
       <c r="X335" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y335" t="inlineStr"/>
       <c r="Z335" s="4" t="n">
         <v>0</v>
       </c>
@@ -35244,7 +34838,6 @@
       <c r="X336" s="5" t="n">
         <v>1513614</v>
       </c>
-      <c r="Y336" t="inlineStr"/>
       <c r="Z336" s="4" t="n">
         <v>0</v>
       </c>
@@ -35346,7 +34939,6 @@
       <c r="X337" s="5" t="n">
         <v>1095248</v>
       </c>
-      <c r="Y337" t="inlineStr"/>
       <c r="Z337" s="4" t="n">
         <v>0</v>
       </c>
@@ -35448,7 +35040,6 @@
       <c r="X338" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y338" t="inlineStr"/>
       <c r="Z338" s="4" t="n">
         <v>0</v>
       </c>
@@ -35550,7 +35141,6 @@
       <c r="X339" s="5" t="n">
         <v>4774322</v>
       </c>
-      <c r="Y339" t="inlineStr"/>
       <c r="Z339" s="4" t="n">
         <v>0</v>
       </c>
@@ -35652,7 +35242,6 @@
       <c r="X340" s="5" t="n">
         <v>1461648</v>
       </c>
-      <c r="Y340" t="inlineStr"/>
       <c r="Z340" s="4" t="n">
         <v>0</v>
       </c>
@@ -35754,7 +35343,6 @@
       <c r="X341" s="5" t="n">
         <v>1112553</v>
       </c>
-      <c r="Y341" t="inlineStr"/>
       <c r="Z341" s="4" t="n">
         <v>0</v>
       </c>
@@ -35862,7 +35450,6 @@
       <c r="X342" s="5" t="n">
         <v>2142562</v>
       </c>
-      <c r="Y342" t="inlineStr"/>
       <c r="Z342" s="4" t="n">
         <v>0</v>
       </c>
@@ -35964,7 +35551,6 @@
       <c r="X343" s="5" t="n">
         <v>661353</v>
       </c>
-      <c r="Y343" t="inlineStr"/>
       <c r="Z343" s="4" t="n">
         <v>0</v>
       </c>
@@ -36072,7 +35658,6 @@
       <c r="X344" s="5" t="n">
         <v>1508953</v>
       </c>
-      <c r="Y344" t="inlineStr"/>
       <c r="Z344" s="4" t="n">
         <v>0</v>
       </c>
@@ -36180,7 +35765,6 @@
       <c r="X345" s="5" t="n">
         <v>894595</v>
       </c>
-      <c r="Y345" t="inlineStr"/>
       <c r="Z345" s="4" t="n">
         <v>0</v>
       </c>
@@ -36282,7 +35866,6 @@
       <c r="X346" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y346" t="inlineStr"/>
       <c r="Z346" s="4" t="n">
         <v>0</v>
       </c>
@@ -36384,7 +35967,6 @@
       <c r="X347" s="5" t="n">
         <v>1743281</v>
       </c>
-      <c r="Y347" t="inlineStr"/>
       <c r="Z347" s="4" t="n">
         <v>0</v>
       </c>
@@ -36486,7 +36068,6 @@
       <c r="X348" s="5" t="n">
         <v>127109</v>
       </c>
-      <c r="Y348" t="inlineStr"/>
       <c r="Z348" s="4" t="n">
         <v>0</v>
       </c>
@@ -36588,7 +36169,6 @@
       <c r="X349" s="5" t="n">
         <v>1410643</v>
       </c>
-      <c r="Y349" t="inlineStr"/>
       <c r="Z349" s="4" t="n">
         <v>0</v>
       </c>
@@ -36696,7 +36276,6 @@
       <c r="X350" s="5" t="n">
         <v>3299678</v>
       </c>
-      <c r="Y350" t="inlineStr"/>
       <c r="Z350" s="4" t="n">
         <v>0</v>
       </c>
@@ -36744,7 +36323,6 @@
           <t>Jackson Lahmeyer</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr">
         <is>
           <t>REP</t>
@@ -36794,7 +36372,6 @@
       <c r="X351" s="5" t="n">
         <v>415914</v>
       </c>
-      <c r="Y351" t="inlineStr"/>
       <c r="Z351" s="4" t="n">
         <v>0</v>
       </c>
@@ -36896,7 +36473,6 @@
       <c r="X352" s="5" t="n">
         <v>218894</v>
       </c>
-      <c r="Y352" t="inlineStr"/>
       <c r="Z352" s="4" t="n">
         <v>0</v>
       </c>
@@ -36998,7 +36574,6 @@
       <c r="X353" s="5" t="n">
         <v>907279</v>
       </c>
-      <c r="Y353" t="inlineStr"/>
       <c r="Z353" s="4" t="n">
         <v>0</v>
       </c>
@@ -37100,7 +36675,6 @@
       <c r="X354" s="5" t="n">
         <v>3827891</v>
       </c>
-      <c r="Y354" t="inlineStr"/>
       <c r="Z354" s="4" t="n">
         <v>0</v>
       </c>
@@ -37202,7 +36776,6 @@
       <c r="X355" s="5" t="n">
         <v>1943507</v>
       </c>
-      <c r="Y355" t="inlineStr"/>
       <c r="Z355" s="4" t="n">
         <v>0</v>
       </c>
@@ -37304,7 +36877,6 @@
       <c r="X356" s="5" t="n">
         <v>4466</v>
       </c>
-      <c r="Y356" t="inlineStr"/>
       <c r="Z356" s="4" t="n">
         <v>0</v>
       </c>
@@ -37406,7 +36978,6 @@
       <c r="X357" s="5" t="n">
         <v>1011413</v>
       </c>
-      <c r="Y357" t="inlineStr"/>
       <c r="Z357" s="4" t="n">
         <v>0</v>
       </c>
@@ -37508,7 +37079,6 @@
       <c r="X358" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y358" t="inlineStr"/>
       <c r="Z358" s="4" t="n">
         <v>0</v>
       </c>
@@ -37610,7 +37180,6 @@
       <c r="X359" s="5" t="n">
         <v>677571</v>
       </c>
-      <c r="Y359" t="inlineStr"/>
       <c r="Z359" s="4" t="n">
         <v>0</v>
       </c>
@@ -37712,7 +37281,6 @@
       <c r="X360" s="5" t="n">
         <v>423922</v>
       </c>
-      <c r="Y360" t="inlineStr"/>
       <c r="Z360" s="4" t="n">
         <v>0</v>
       </c>
@@ -37814,7 +37382,6 @@
       <c r="X361" s="5" t="n">
         <v>12791</v>
       </c>
-      <c r="Y361" t="inlineStr"/>
       <c r="Z361" s="4" t="n">
         <v>0</v>
       </c>
@@ -37922,7 +37489,6 @@
       <c r="X362" s="5" t="n">
         <v>6734931</v>
       </c>
-      <c r="Y362" t="inlineStr"/>
       <c r="Z362" s="4" t="n">
         <v>0</v>
       </c>
@@ -38024,7 +37590,6 @@
       <c r="X363" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y363" t="inlineStr"/>
       <c r="Z363" s="4" t="n">
         <v>0</v>
       </c>
@@ -38072,7 +37637,6 @@
           <t>Alexander Schnell</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -38122,7 +37686,6 @@
       <c r="X364" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="Y364" t="inlineStr"/>
       <c r="Z364" s="4" t="n">
         <v>0</v>
       </c>
@@ -38224,7 +37787,6 @@
       <c r="X365" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y365" t="inlineStr"/>
       <c r="Z365" s="4" t="n">
         <v>0</v>
       </c>
@@ -38326,7 +37888,6 @@
       <c r="X366" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y366" t="inlineStr"/>
       <c r="Z366" s="4" t="n">
         <v>0</v>
       </c>
@@ -38428,7 +37989,6 @@
       <c r="X367" s="5" t="n">
         <v>411270</v>
       </c>
-      <c r="Y367" t="inlineStr"/>
       <c r="Z367" s="4" t="n">
         <v>0</v>
       </c>
@@ -38536,7 +38096,6 @@
       <c r="X368" s="5" t="n">
         <v>4357405</v>
       </c>
-      <c r="Y368" t="inlineStr"/>
       <c r="Z368" s="4" t="n">
         <v>0</v>
       </c>
@@ -38644,7 +38203,6 @@
       <c r="X369" s="5" t="n">
         <v>5234586</v>
       </c>
-      <c r="Y369" t="inlineStr"/>
       <c r="Z369" s="4" t="n">
         <v>0</v>
       </c>
@@ -38746,7 +38304,6 @@
       <c r="X370" s="5" t="n">
         <v>1903078</v>
       </c>
-      <c r="Y370" t="inlineStr"/>
       <c r="Z370" s="4" t="n">
         <v>0</v>
       </c>
@@ -38854,7 +38411,6 @@
       <c r="X371" s="5" t="n">
         <v>5194925</v>
       </c>
-      <c r="Y371" t="inlineStr"/>
       <c r="Z371" s="4" t="n">
         <v>0</v>
       </c>
@@ -38956,7 +38512,6 @@
       <c r="X372" s="5" t="n">
         <v>1524161</v>
       </c>
-      <c r="Y372" t="inlineStr"/>
       <c r="Z372" s="4" t="n">
         <v>0</v>
       </c>
@@ -39058,7 +38613,6 @@
       <c r="X373" s="5" t="n">
         <v>17477</v>
       </c>
-      <c r="Y373" t="inlineStr"/>
       <c r="Z373" s="4" t="n">
         <v>0</v>
       </c>
@@ -39160,7 +38714,6 @@
       <c r="X374" s="5" t="n">
         <v>2418119</v>
       </c>
-      <c r="Y374" t="inlineStr"/>
       <c r="Z374" s="4" t="n">
         <v>0</v>
       </c>
@@ -39262,7 +38815,6 @@
       <c r="X375" s="5" t="n">
         <v>4209644</v>
       </c>
-      <c r="Y375" t="inlineStr"/>
       <c r="Z375" s="4" t="n">
         <v>0</v>
       </c>
@@ -39364,7 +38916,6 @@
       <c r="X376" s="5" t="n">
         <v>1851459</v>
       </c>
-      <c r="Y376" t="inlineStr"/>
       <c r="Z376" s="4" t="n">
         <v>0</v>
       </c>
@@ -39466,7 +39017,6 @@
       <c r="X377" s="5" t="n">
         <v>1168433</v>
       </c>
-      <c r="Y377" t="inlineStr"/>
       <c r="Z377" s="4" t="n">
         <v>0</v>
       </c>
@@ -39568,7 +39118,6 @@
       <c r="X378" s="5" t="n">
         <v>21506</v>
       </c>
-      <c r="Y378" t="inlineStr"/>
       <c r="Z378" s="4" t="n">
         <v>0</v>
       </c>
@@ -39670,7 +39219,6 @@
       <c r="X379" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y379" t="inlineStr"/>
       <c r="Z379" s="4" t="n">
         <v>0</v>
       </c>
@@ -39772,7 +39320,6 @@
       <c r="X380" s="5" t="n">
         <v>2979124</v>
       </c>
-      <c r="Y380" t="inlineStr"/>
       <c r="Z380" s="4" t="n">
         <v>0</v>
       </c>
@@ -39820,7 +39367,6 @@
           <t>Jenny Costa Honeycutt</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr">
         <is>
           <t>REP</t>
@@ -39876,7 +39422,6 @@
       <c r="X381" s="5" t="n">
         <v>556418</v>
       </c>
-      <c r="Y381" t="inlineStr"/>
       <c r="Z381" s="4" t="n">
         <v>0</v>
       </c>
@@ -39978,7 +39523,6 @@
       <c r="X382" s="5" t="n">
         <v>861105</v>
       </c>
-      <c r="Y382" t="inlineStr"/>
       <c r="Z382" s="4" t="n">
         <v>0</v>
       </c>
@@ -40080,7 +39624,6 @@
       <c r="X383" s="5" t="n">
         <v>505333</v>
       </c>
-      <c r="Y383" t="inlineStr"/>
       <c r="Z383" s="4" t="n">
         <v>0</v>
       </c>
@@ -40182,7 +39725,6 @@
       <c r="X384" s="5" t="n">
         <v>1595725</v>
       </c>
-      <c r="Y384" t="inlineStr"/>
       <c r="Z384" s="4" t="n">
         <v>0</v>
       </c>
@@ -40230,7 +39772,6 @@
           <t>Wes Climer</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
           <t>REP</t>
@@ -40280,7 +39821,6 @@
       <c r="X385" s="5" t="n">
         <v>884284</v>
       </c>
-      <c r="Y385" t="inlineStr"/>
       <c r="Z385" s="4" t="n">
         <v>0</v>
       </c>
@@ -40382,7 +39922,6 @@
       <c r="X386" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y386" t="inlineStr"/>
       <c r="Z386" s="4" t="n">
         <v>0</v>
       </c>
@@ -40490,7 +40029,6 @@
       <c r="X387" s="5" t="n">
         <v>1720803</v>
       </c>
-      <c r="Y387" t="inlineStr"/>
       <c r="Z387" s="4" t="n">
         <v>0</v>
       </c>
@@ -40538,7 +40076,6 @@
           <t>Marty Jackley</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
           <t>REP</t>
@@ -40588,7 +40125,6 @@
       <c r="X388" s="5" t="n">
         <v>1438706</v>
       </c>
-      <c r="Y388" t="inlineStr"/>
       <c r="Z388" s="4" t="n">
         <v>0</v>
       </c>
@@ -40690,7 +40226,6 @@
       <c r="X389" s="5" t="n">
         <v>1274194</v>
       </c>
-      <c r="Y389" t="inlineStr"/>
       <c r="Z389" s="4" t="n">
         <v>0</v>
       </c>
@@ -40792,7 +40327,6 @@
       <c r="X390" s="5" t="n">
         <v>2428734</v>
       </c>
-      <c r="Y390" t="inlineStr"/>
       <c r="Z390" s="4" t="n">
         <v>0</v>
       </c>
@@ -40894,7 +40428,6 @@
       <c r="X391" s="5" t="n">
         <v>2330803</v>
       </c>
-      <c r="Y391" t="inlineStr"/>
       <c r="Z391" s="4" t="n">
         <v>0</v>
       </c>
@@ -40996,7 +40529,6 @@
       <c r="X392" s="5" t="n">
         <v>536843</v>
       </c>
-      <c r="Y392" t="inlineStr"/>
       <c r="Z392" s="4" t="n">
         <v>0</v>
       </c>
@@ -41044,7 +40576,6 @@
           <t>Charlie Hatcher</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr">
         <is>
           <t>REP</t>
@@ -41094,7 +40625,6 @@
       <c r="X393" s="5" t="n">
         <v>719503</v>
       </c>
-      <c r="Y393" t="inlineStr"/>
       <c r="Z393" s="4" t="n">
         <v>0</v>
       </c>
@@ -41142,7 +40672,6 @@
           <t>Johnny Garrett</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr">
         <is>
           <t>REP</t>
@@ -41192,7 +40721,6 @@
       <c r="X394" s="5" t="n">
         <v>2380327</v>
       </c>
-      <c r="Y394" t="inlineStr"/>
       <c r="Z394" s="4" t="n">
         <v>0</v>
       </c>
@@ -41294,7 +40822,6 @@
       <c r="X395" s="5" t="n">
         <v>2300690</v>
       </c>
-      <c r="Y395" t="inlineStr"/>
       <c r="Z395" s="4" t="n">
         <v>0</v>
       </c>
@@ -41396,7 +40923,6 @@
       <c r="X396" s="5" t="n">
         <v>2232874</v>
       </c>
-      <c r="Y396" t="inlineStr"/>
       <c r="Z396" s="4" t="n">
         <v>0</v>
       </c>
@@ -41444,7 +40970,6 @@
           <t>Brent Taylor</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr">
         <is>
           <t>REP</t>
@@ -41494,7 +41019,6 @@
       <c r="X397" s="5" t="n">
         <v>1549482</v>
       </c>
-      <c r="Y397" t="inlineStr"/>
       <c r="Z397" s="4" t="n">
         <v>0</v>
       </c>
@@ -41596,7 +41120,6 @@
       <c r="X398" s="5" t="n">
         <v>1797848</v>
       </c>
-      <c r="Y398" t="inlineStr"/>
       <c r="Z398" s="4" t="n">
         <v>0</v>
       </c>
@@ -41644,7 +41167,6 @@
           <t>Steve Toth</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr">
         <is>
           <t>REP</t>
@@ -41694,7 +41216,6 @@
       <c r="X399" s="5" t="n">
         <v>824450</v>
       </c>
-      <c r="Y399" t="inlineStr"/>
       <c r="Z399" s="4" t="n">
         <v>0</v>
       </c>
@@ -41796,7 +41317,6 @@
       <c r="X400" s="5" t="n">
         <v>645503</v>
       </c>
-      <c r="Y400" t="inlineStr"/>
       <c r="Z400" s="4" t="n">
         <v>0</v>
       </c>
@@ -41898,7 +41418,6 @@
       <c r="X401" s="5" t="n">
         <v>790505</v>
       </c>
-      <c r="Y401" t="inlineStr"/>
       <c r="Z401" s="4" t="n">
         <v>0</v>
       </c>
@@ -42000,7 +41519,6 @@
       <c r="X402" s="5" t="n">
         <v>1341647</v>
       </c>
-      <c r="Y402" t="inlineStr"/>
       <c r="Z402" s="4" t="n">
         <v>0</v>
       </c>
@@ -42102,7 +41620,6 @@
       <c r="X403" s="5" t="n">
         <v>4660385</v>
       </c>
-      <c r="Y403" t="inlineStr"/>
       <c r="Z403" s="4" t="n">
         <v>0</v>
       </c>
@@ -42204,7 +41721,6 @@
       <c r="X404" s="5" t="n">
         <v>76578</v>
       </c>
-      <c r="Y404" t="inlineStr"/>
       <c r="Z404" s="4" t="n">
         <v>0</v>
       </c>
@@ -42252,7 +41768,6 @@
           <t>Jessica Steinmann</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr">
         <is>
           <t>REP</t>
@@ -42302,7 +41817,6 @@
       <c r="X405" s="5" t="n">
         <v>2064033</v>
       </c>
-      <c r="Y405" t="inlineStr"/>
       <c r="Z405" s="4" t="n">
         <v>0</v>
       </c>
@@ -42350,7 +41864,6 @@
           <t>Alexandra Mealer</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr">
         <is>
           <t>REP</t>
@@ -42400,7 +41913,6 @@
       <c r="X406" s="5" t="n">
         <v>2080514</v>
       </c>
-      <c r="Y406" t="inlineStr"/>
       <c r="Z406" s="4" t="n">
         <v>0</v>
       </c>
@@ -42448,7 +41960,6 @@
           <t>Chris Gober</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr">
         <is>
           <t>REP</t>
@@ -42498,7 +42009,6 @@
       <c r="X407" s="5" t="n">
         <v>2559185</v>
       </c>
-      <c r="Y407" t="inlineStr"/>
       <c r="Z407" s="4" t="n">
         <v>0</v>
       </c>
@@ -42600,7 +42110,6 @@
       <c r="X408" s="5" t="n">
         <v>3189023</v>
       </c>
-      <c r="Y408" t="inlineStr"/>
       <c r="Z408" s="4" t="n">
         <v>0</v>
       </c>
@@ -42702,7 +42211,6 @@
       <c r="X409" s="5" t="n">
         <v>1756535</v>
       </c>
-      <c r="Y409" t="inlineStr"/>
       <c r="Z409" s="4" t="n">
         <v>0</v>
       </c>
@@ -42804,7 +42312,6 @@
       <c r="X410" s="5" t="n">
         <v>4036265</v>
       </c>
-      <c r="Y410" t="inlineStr"/>
       <c r="Z410" s="4" t="n">
         <v>0</v>
       </c>
@@ -42906,7 +42413,6 @@
       <c r="X411" s="5" t="n">
         <v>972561</v>
       </c>
-      <c r="Y411" t="inlineStr"/>
       <c r="Z411" s="4" t="n">
         <v>0</v>
       </c>
@@ -43014,7 +42520,6 @@
       <c r="X412" s="5" t="n">
         <v>5273960</v>
       </c>
-      <c r="Y412" t="inlineStr"/>
       <c r="Z412" s="4" t="n">
         <v>0</v>
       </c>
@@ -43116,7 +42621,6 @@
       <c r="X413" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y413" t="inlineStr"/>
       <c r="Z413" s="4" t="n">
         <v>0</v>
       </c>
@@ -43218,7 +42722,6 @@
       <c r="X414" s="5" t="n">
         <v>1050237</v>
       </c>
-      <c r="Y414" t="inlineStr"/>
       <c r="Z414" s="4" t="n">
         <v>0</v>
       </c>
@@ -43320,7 +42823,6 @@
       <c r="X415" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y415" t="inlineStr"/>
       <c r="Z415" s="4" t="n">
         <v>0</v>
       </c>
@@ -43368,7 +42870,6 @@
           <t>Tom Sell</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr">
         <is>
           <t>REP</t>
@@ -43418,7 +42919,6 @@
       <c r="X416" s="5" t="n">
         <v>2143025</v>
       </c>
-      <c r="Y416" t="inlineStr"/>
       <c r="Z416" s="4" t="n">
         <v>0</v>
       </c>
@@ -43520,7 +43020,6 @@
       <c r="X417" s="5" t="n">
         <v>48536</v>
       </c>
-      <c r="Y417" t="inlineStr"/>
       <c r="Z417" s="4" t="n">
         <v>0</v>
       </c>
@@ -43568,7 +43067,6 @@
           <t>Mark Teixeira</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr">
         <is>
           <t>REP</t>
@@ -43618,7 +43116,6 @@
       <c r="X418" s="5" t="n">
         <v>4177191</v>
       </c>
-      <c r="Y418" t="inlineStr"/>
       <c r="Z418" s="4" t="n">
         <v>0</v>
       </c>
@@ -43666,7 +43163,6 @@
           <t>Trever Nehls</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr">
         <is>
           <t>REP</t>
@@ -43716,7 +43212,6 @@
       <c r="X419" s="5" t="n">
         <v>206463</v>
       </c>
-      <c r="Y419" t="inlineStr"/>
       <c r="Z419" s="4" t="n">
         <v>0</v>
       </c>
@@ -43764,7 +43259,6 @@
           <t>Brandon Herrera</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr">
         <is>
           <t>REP</t>
@@ -43820,7 +43314,6 @@
       <c r="X420" s="5" t="n">
         <v>1937719</v>
       </c>
-      <c r="Y420" t="inlineStr"/>
       <c r="Z420" s="4" t="n">
         <v>0</v>
       </c>
@@ -43922,7 +43415,6 @@
       <c r="X421" s="5" t="n">
         <v>2540738</v>
       </c>
-      <c r="Y421" t="inlineStr"/>
       <c r="Z421" s="4" t="n">
         <v>0</v>
       </c>
@@ -44024,7 +43516,6 @@
       <c r="X422" s="5" t="n">
         <v>1424050</v>
       </c>
-      <c r="Y422" t="inlineStr"/>
       <c r="Z422" s="4" t="n">
         <v>0</v>
       </c>
@@ -44126,7 +43617,6 @@
       <c r="X423" s="5" t="n">
         <v>4217213</v>
       </c>
-      <c r="Y423" t="inlineStr"/>
       <c r="Z423" s="4" t="n">
         <v>0</v>
       </c>
@@ -44228,7 +43718,6 @@
       <c r="X424" s="5" t="n">
         <v>1062241</v>
       </c>
-      <c r="Y424" t="inlineStr"/>
       <c r="Z424" s="4" t="n">
         <v>0</v>
       </c>
@@ -44336,7 +43825,6 @@
       <c r="X425" s="5" t="n">
         <v>1399881</v>
       </c>
-      <c r="Y425" t="inlineStr"/>
       <c r="Z425" s="4" t="n">
         <v>0</v>
       </c>
@@ -44438,7 +43926,6 @@
       <c r="X426" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y426" t="inlineStr"/>
       <c r="Z426" s="4" t="n">
         <v>0</v>
       </c>
@@ -44486,7 +43973,6 @@
           <t>Sholdon Daniels</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -44536,7 +44022,6 @@
       <c r="X427" s="5" t="n">
         <v>357415</v>
       </c>
-      <c r="Y427" t="inlineStr"/>
       <c r="Z427" s="4" t="n">
         <v>0</v>
       </c>
@@ -44638,7 +44123,6 @@
       <c r="X428" s="5" t="n">
         <v>1419042</v>
       </c>
-      <c r="Y428" t="inlineStr"/>
       <c r="Z428" s="4" t="n">
         <v>0</v>
       </c>
@@ -44686,7 +44170,6 @@
           <t>Jace Yarbrough</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr">
         <is>
           <t>REP</t>
@@ -44736,7 +44219,6 @@
       <c r="X429" s="5" t="n">
         <v>865911</v>
       </c>
-      <c r="Y429" t="inlineStr"/>
       <c r="Z429" s="4" t="n">
         <v>0</v>
       </c>
@@ -44784,7 +44266,6 @@
           <t>Patrick Gillespie</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -44834,7 +44315,6 @@
       <c r="X430" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y430" t="inlineStr"/>
       <c r="Z430" s="4" t="n">
         <v>0</v>
       </c>
@@ -44942,7 +44422,6 @@
       <c r="X431" s="5" t="n">
         <v>2874990</v>
       </c>
-      <c r="Y431" t="inlineStr"/>
       <c r="Z431" s="4" t="n">
         <v>0</v>
       </c>
@@ -44990,7 +44469,6 @@
           <t>Carlos De La Cruz</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr">
         <is>
           <t>REP</t>
@@ -45040,7 +44518,6 @@
       <c r="X432" s="5" t="n">
         <v>1048751</v>
       </c>
-      <c r="Y432" t="inlineStr"/>
       <c r="Z432" s="4" t="n">
         <v>0</v>
       </c>
@@ -45142,7 +44619,6 @@
       <c r="X433" s="5" t="n">
         <v>1006944</v>
       </c>
-      <c r="Y433" t="inlineStr"/>
       <c r="Z433" s="4" t="n">
         <v>0</v>
       </c>
@@ -45244,7 +44720,6 @@
       <c r="X434" s="5" t="n">
         <v>117890</v>
       </c>
-      <c r="Y434" t="inlineStr"/>
       <c r="Z434" s="4" t="n">
         <v>0</v>
       </c>
@@ -45292,7 +44767,6 @@
           <t>Jon Bonck</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
           <t>REP</t>
@@ -45342,7 +44816,6 @@
       <c r="X435" s="5" t="n">
         <v>1644127</v>
       </c>
-      <c r="Y435" t="inlineStr"/>
       <c r="Z435" s="4" t="n">
         <v>0</v>
       </c>
@@ -45390,7 +44863,6 @@
           <t>Riley Owen</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -45440,7 +44912,6 @@
       <c r="X436" s="5" t="n">
         <v>132533</v>
       </c>
-      <c r="Y436" t="inlineStr"/>
       <c r="Z436" s="4" t="n">
         <v>0</v>
       </c>
@@ -45542,7 +45013,6 @@
       <c r="X437" s="5" t="n">
         <v>2536636</v>
       </c>
-      <c r="Y437" t="inlineStr"/>
       <c r="Z437" s="4" t="n">
         <v>0</v>
       </c>
@@ -45644,7 +45114,6 @@
       <c r="X438" s="5" t="n">
         <v>1453861</v>
       </c>
-      <c r="Y438" t="inlineStr"/>
       <c r="Z438" s="4" t="n">
         <v>0</v>
       </c>
@@ -45746,7 +45215,6 @@
       <c r="X439" s="5" t="n">
         <v>971392</v>
       </c>
-      <c r="Y439" t="inlineStr"/>
       <c r="Z439" s="4" t="n">
         <v>0</v>
       </c>
@@ -45854,7 +45322,6 @@
       <c r="X440" s="5" t="n">
         <v>4053142</v>
       </c>
-      <c r="Y440" t="inlineStr"/>
       <c r="Z440" s="4" t="n">
         <v>0</v>
       </c>
@@ -45962,7 +45429,6 @@
       <c r="X441" s="5" t="n">
         <v>5954338</v>
       </c>
-      <c r="Y441" t="inlineStr"/>
       <c r="Z441" s="4" t="n">
         <v>0</v>
       </c>
@@ -46064,7 +45530,6 @@
       <c r="X442" s="5" t="n">
         <v>6555</v>
       </c>
-      <c r="Y442" t="inlineStr"/>
       <c r="Z442" s="4" t="n">
         <v>0</v>
       </c>
@@ -46166,7 +45631,6 @@
       <c r="X443" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y443" t="inlineStr"/>
       <c r="Z443" s="4" t="n">
         <v>0</v>
       </c>
@@ -46274,7 +45738,6 @@
       <c r="X444" s="5" t="n">
         <v>1781840</v>
       </c>
-      <c r="Y444" t="inlineStr"/>
       <c r="Z444" s="4" t="n">
         <v>0</v>
       </c>
@@ -46376,7 +45839,6 @@
       <c r="X445" s="5" t="n">
         <v>1441436</v>
       </c>
-      <c r="Y445" t="inlineStr"/>
       <c r="Z445" s="4" t="n">
         <v>0</v>
       </c>
@@ -46478,7 +45940,6 @@
       <c r="X446" s="5" t="n">
         <v>251134</v>
       </c>
-      <c r="Y446" t="inlineStr"/>
       <c r="Z446" s="4" t="n">
         <v>0</v>
       </c>
@@ -46580,7 +46041,6 @@
       <c r="X447" s="5" t="n">
         <v>21917</v>
       </c>
-      <c r="Y447" t="inlineStr"/>
       <c r="Z447" s="4" t="n">
         <v>0</v>
       </c>
@@ -46682,7 +46142,6 @@
       <c r="X448" s="5" t="n">
         <v>1828839</v>
       </c>
-      <c r="Y448" t="inlineStr"/>
       <c r="Z448" s="4" t="n">
         <v>0</v>
       </c>
@@ -46784,7 +46243,6 @@
       <c r="X449" s="5" t="n">
         <v>107334</v>
       </c>
-      <c r="Y449" t="inlineStr"/>
       <c r="Z449" s="4" t="n">
         <v>0</v>
       </c>
@@ -46886,7 +46344,6 @@
       <c r="X450" s="5" t="n">
         <v>5637</v>
       </c>
-      <c r="Y450" t="inlineStr"/>
       <c r="Z450" s="4" t="n">
         <v>0</v>
       </c>
@@ -46994,7 +46451,6 @@
       <c r="X451" s="5" t="n">
         <v>58280</v>
       </c>
-      <c r="Y451" t="inlineStr"/>
       <c r="Z451" s="4" t="n">
         <v>0</v>
       </c>
@@ -47096,7 +46552,6 @@
       <c r="X452" s="5" t="n">
         <v>3186</v>
       </c>
-      <c r="Y452" t="inlineStr"/>
       <c r="Z452" s="4" t="n">
         <v>0</v>
       </c>
@@ -47198,7 +46653,6 @@
       <c r="X453" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y453" t="inlineStr"/>
       <c r="Z453" s="4" t="n">
         <v>0</v>
       </c>
@@ -47306,7 +46760,6 @@
       <c r="X454" s="5" t="n">
         <v>2214441</v>
       </c>
-      <c r="Y454" t="inlineStr"/>
       <c r="Z454" s="4" t="n">
         <v>0</v>
       </c>
@@ -47354,7 +46807,6 @@
           <t>Amanda McKinney</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr">
         <is>
           <t>REP</t>
@@ -47404,7 +46856,6 @@
       <c r="X455" s="5" t="n">
         <v>981820</v>
       </c>
-      <c r="Y455" t="inlineStr"/>
       <c r="Z455" s="4" t="n">
         <v>0</v>
       </c>
@@ -47512,7 +46963,6 @@
       <c r="X456" s="5" t="n">
         <v>1738226</v>
       </c>
-      <c r="Y456" t="inlineStr"/>
       <c r="Z456" s="4" t="n">
         <v>0</v>
       </c>
@@ -47614,7 +47064,6 @@
       <c r="X457" s="5" t="n">
         <v>27615</v>
       </c>
-      <c r="Y457" t="inlineStr"/>
       <c r="Z457" s="4" t="n">
         <v>0</v>
       </c>
@@ -47716,7 +47165,6 @@
       <c r="X458" s="5" t="n">
         <v>11811</v>
       </c>
-      <c r="Y458" t="inlineStr"/>
       <c r="Z458" s="4" t="n">
         <v>0</v>
       </c>
@@ -47818,7 +47266,6 @@
       <c r="X459" s="5" t="n">
         <v>126517</v>
       </c>
-      <c r="Y459" t="inlineStr"/>
       <c r="Z459" s="4" t="n">
         <v>0</v>
       </c>
@@ -47920,7 +47367,6 @@
       <c r="X460" s="5" t="n">
         <v>99242</v>
       </c>
-      <c r="Y460" t="inlineStr"/>
       <c r="Z460" s="4" t="n">
         <v>0</v>
       </c>
@@ -48022,7 +47468,6 @@
       <c r="X461" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y461" t="inlineStr"/>
       <c r="Z461" s="4" t="n">
         <v>0</v>
       </c>
@@ -48130,7 +47575,6 @@
       <c r="X462" s="5" t="n">
         <v>5467777</v>
       </c>
-      <c r="Y462" t="inlineStr"/>
       <c r="Z462" s="4" t="n">
         <v>0</v>
       </c>
@@ -48232,7 +47676,6 @@
       <c r="X463" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y463" t="inlineStr"/>
       <c r="Z463" s="4" t="n">
         <v>0</v>
       </c>
@@ -48340,7 +47783,6 @@
       <c r="X464" s="5" t="n">
         <v>7526052</v>
       </c>
-      <c r="Y464" t="inlineStr"/>
       <c r="Z464" s="4" t="n">
         <v>0</v>
       </c>
@@ -48442,7 +47884,6 @@
       <c r="X465" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y465" t="inlineStr"/>
       <c r="Z465" s="4" t="n">
         <v>0</v>
       </c>
@@ -48544,7 +47985,6 @@
       <c r="X466" s="5" t="n">
         <v>1376100</v>
       </c>
-      <c r="Y466" t="inlineStr"/>
       <c r="Z466" s="4" t="n">
         <v>0</v>
       </c>
@@ -48652,7 +48092,6 @@
       <c r="X467" s="5" t="n">
         <v>929020</v>
       </c>
-      <c r="Y467" t="inlineStr"/>
       <c r="Z467" s="4" t="n">
         <v>0</v>
       </c>
@@ -48700,7 +48139,6 @@
           <t>Michael Alfonso</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr">
         <is>
           <t>REP</t>
@@ -48750,7 +48188,6 @@
       <c r="X468" s="5" t="n">
         <v>1351546</v>
       </c>
-      <c r="Y468" t="inlineStr"/>
       <c r="Z468" s="4" t="n">
         <v>0</v>
       </c>
@@ -48852,7 +48289,6 @@
       <c r="X469" s="5" t="n">
         <v>1090216</v>
       </c>
-      <c r="Y469" t="inlineStr"/>
       <c r="Z469" s="4" t="n">
         <v>0</v>
       </c>
@@ -48954,7 +48390,6 @@
       <c r="X470" s="5" t="n">
         <v>1746898</v>
       </c>
-      <c r="Y470" t="inlineStr"/>
       <c r="Z470" s="4" t="n">
         <v>0</v>
       </c>
@@ -49056,7 +48491,6 @@
       <c r="X471" s="5" t="n">
         <v>1325162</v>
       </c>
-      <c r="Y471" t="inlineStr"/>
       <c r="Z471" s="4" t="n">
         <v>0</v>
       </c>
@@ -49104,7 +48538,6 @@
           <t>Chuck Gray</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr"/>
       <c r="H472" t="inlineStr">
         <is>
           <t>REP</t>
@@ -49154,7 +48587,6 @@
       <c r="X472" s="5" t="n">
         <v>1621197</v>
       </c>
-      <c r="Y472" t="inlineStr"/>
       <c r="Z472" s="4" t="n">
         <v>0</v>
       </c>
@@ -49213,13 +48645,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>48</v>
+        <v>49.8</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>52</v>
+        <v>50.2</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49227,13 +48659,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.88</v>
+        <v>-10.89</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.16</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.41</v>
@@ -49262,7 +48694,6 @@
       <c r="X473" s="5" t="n">
         <v>9136967</v>
       </c>
-      <c r="Y473" t="inlineStr"/>
       <c r="Z473" s="4" t="n">
         <v>0</v>
       </c>
@@ -49310,7 +48741,6 @@
           <t>Barry Moore</t>
         </is>
       </c>
-      <c r="G474" t="inlineStr"/>
       <c r="H474" t="inlineStr">
         <is>
           <t>REP</t>
@@ -49366,7 +48796,6 @@
       <c r="X474" s="5" t="n">
         <v>3787330</v>
       </c>
-      <c r="Y474" t="inlineStr"/>
       <c r="Z474" s="4" t="n">
         <v>0</v>
       </c>
@@ -49474,7 +48903,6 @@
       <c r="X475" s="5" t="n">
         <v>6233117</v>
       </c>
-      <c r="Y475" t="inlineStr"/>
       <c r="Z475" s="4" t="n">
         <v>0</v>
       </c>
@@ -49576,7 +49004,6 @@
       <c r="X476" s="5" t="n">
         <v>138147</v>
       </c>
-      <c r="Y476" t="inlineStr"/>
       <c r="Z476" s="4" t="n">
         <v>0</v>
       </c>
@@ -49678,7 +49105,6 @@
       <c r="X477" s="5" t="n">
         <v>70152</v>
       </c>
-      <c r="Y477" t="inlineStr"/>
       <c r="Z477" s="4" t="n">
         <v>0</v>
       </c>
@@ -49786,7 +49212,6 @@
       <c r="X478" s="5" t="n">
         <v>11270805</v>
       </c>
-      <c r="Y478" t="inlineStr"/>
       <c r="Z478" s="4" t="n">
         <v>0</v>
       </c>
@@ -49894,7 +49319,6 @@
       <c r="X479" s="5" t="n">
         <v>7409350</v>
       </c>
-      <c r="Y479" t="inlineStr"/>
       <c r="Z479" s="4" t="n">
         <v>0</v>
       </c>
@@ -49942,7 +49366,6 @@
           <t>Ashley Hinson</t>
         </is>
       </c>
-      <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr">
         <is>
           <t>REP</t>
@@ -49998,7 +49421,6 @@
       <c r="X480" s="5" t="n">
         <v>10217845</v>
       </c>
-      <c r="Y480" t="inlineStr"/>
       <c r="Z480" s="4" t="n">
         <v>0</v>
       </c>
@@ -50158,7 +49580,6 @@
           <t>Don Tracy</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -50208,7 +49629,6 @@
       <c r="X482" s="5" t="n">
         <v>2459890</v>
       </c>
-      <c r="Y482" t="inlineStr"/>
       <c r="Z482" s="4" t="n">
         <v>0</v>
       </c>
@@ -50316,7 +49736,6 @@
       <c r="X483" s="5" t="n">
         <v>4009075</v>
       </c>
-      <c r="Y483" t="inlineStr"/>
       <c r="Z483" s="4" t="n">
         <v>0</v>
       </c>
@@ -50364,7 +49783,6 @@
           <t>Andy Barr</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr"/>
       <c r="H484" t="inlineStr">
         <is>
           <t>REP</t>
@@ -50420,7 +49838,6 @@
       <c r="X484" s="5" t="n">
         <v>9981055</v>
       </c>
-      <c r="Y484" t="inlineStr"/>
       <c r="Z484" s="4" t="n">
         <v>0</v>
       </c>
@@ -50468,7 +49885,6 @@
           <t>Julia Letlow</t>
         </is>
       </c>
-      <c r="G485" t="inlineStr"/>
       <c r="H485" t="inlineStr">
         <is>
           <t>REP</t>
@@ -50518,7 +49934,6 @@
       <c r="X485" s="5" t="n">
         <v>6210122</v>
       </c>
-      <c r="Y485" t="inlineStr"/>
       <c r="Z485" s="4" t="n">
         <v>0</v>
       </c>
@@ -50626,7 +50041,6 @@
       <c r="X486" s="5" t="n">
         <v>1561360</v>
       </c>
-      <c r="Y486" t="inlineStr"/>
       <c r="Z486" s="4" t="n">
         <v>0</v>
       </c>
@@ -50734,7 +50148,6 @@
       <c r="X487" s="5" t="n">
         <v>16169827</v>
       </c>
-      <c r="Y487" t="inlineStr"/>
       <c r="Z487" s="4" t="n">
         <v>0</v>
       </c>
@@ -50782,7 +50195,6 @@
           <t>Mike Rogers</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr"/>
       <c r="H488" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -50838,7 +50250,6 @@
       <c r="X488" s="5" t="n">
         <v>10898177</v>
       </c>
-      <c r="Y488" t="inlineStr"/>
       <c r="Z488" s="4" t="n">
         <v>0</v>
       </c>
@@ -50886,7 +50297,6 @@
           <t>Michele Tafoya</t>
         </is>
       </c>
-      <c r="G489" t="inlineStr"/>
       <c r="H489" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -50942,7 +50352,6 @@
       <c r="X489" s="5" t="n">
         <v>5337942</v>
       </c>
-      <c r="Y489" t="inlineStr"/>
       <c r="Z489" s="4" t="n">
         <v>0</v>
       </c>
@@ -51102,14 +50511,13 @@
           <t>Kurt Alme</t>
         </is>
       </c>
-      <c r="G491" t="inlineStr"/>
       <c r="H491" t="inlineStr">
         <is>
           <t>REP</t>
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.52</v>
+        <v>-27.58</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51164,16 +50572,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.44</v>
+        <v>14.51</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>27.19</v>
+        <v>27.12</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>54.71</v>
+        <v>54.7</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51210,7 +50618,6 @@
           <t>Michael Whatley</t>
         </is>
       </c>
-      <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr">
         <is>
           <t>REP</t>
@@ -51266,7 +50673,6 @@
       <c r="X492" s="5" t="n">
         <v>11272504</v>
       </c>
-      <c r="Y492" t="inlineStr"/>
       <c r="Z492" s="4" t="n">
         <v>0</v>
       </c>
@@ -51426,7 +50832,6 @@
           <t>John E. Sununu</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -51482,7 +50887,6 @@
       <c r="X494" s="5" t="n">
         <v>3662252</v>
       </c>
-      <c r="Y494" t="inlineStr"/>
       <c r="Z494" s="4" t="n">
         <v>0</v>
       </c>
@@ -51584,7 +50988,6 @@
       <c r="X495" s="5" t="n">
         <v>27316</v>
       </c>
-      <c r="Y495" t="inlineStr"/>
       <c r="Z495" s="4" t="n">
         <v>0</v>
       </c>
@@ -51686,7 +51089,6 @@
       <c r="X496" s="5" t="n">
         <v>33525</v>
       </c>
-      <c r="Y496" t="inlineStr"/>
       <c r="Z496" s="4" t="n">
         <v>0</v>
       </c>
@@ -51794,7 +51196,6 @@
       <c r="X497" s="5" t="n">
         <v>14360028</v>
       </c>
-      <c r="Y497" t="inlineStr"/>
       <c r="Z497" s="4" t="n">
         <v>0</v>
       </c>
@@ -51842,7 +51243,6 @@
           <t>Kevin Hern</t>
         </is>
       </c>
-      <c r="G498" t="inlineStr"/>
       <c r="H498" t="inlineStr">
         <is>
           <t>REP</t>
@@ -51898,7 +51298,6 @@
       <c r="X498" s="5" t="n">
         <v>9953579</v>
       </c>
-      <c r="Y498" t="inlineStr"/>
       <c r="Z498" s="4" t="n">
         <v>0</v>
       </c>
@@ -52000,7 +51399,6 @@
       <c r="X499" s="5" t="n">
         <v>120760</v>
       </c>
-      <c r="Y499" t="inlineStr"/>
       <c r="Z499" s="4" t="n">
         <v>0</v>
       </c>
@@ -52108,7 +51506,6 @@
       <c r="X500" s="5" t="n">
         <v>163439</v>
       </c>
-      <c r="Y500" t="inlineStr"/>
       <c r="Z500" s="4" t="n">
         <v>0</v>
       </c>
@@ -52156,7 +51553,6 @@
           <t>Generic Republican</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr">
         <is>
           <t>REP</t>
@@ -52212,7 +51608,6 @@
       <c r="X501" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y501" t="inlineStr"/>
       <c r="Z501" s="4" t="n">
         <v>0</v>
       </c>
@@ -52426,7 +51821,6 @@
       <c r="X503" s="5" t="n">
         <v>7162897</v>
       </c>
-      <c r="Y503" t="inlineStr"/>
       <c r="Z503" s="4" t="n">
         <v>0</v>
       </c>
@@ -52474,7 +51868,6 @@
           <t>Ken Paxton</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr">
         <is>
           <t>REP</t>
@@ -52530,7 +51923,6 @@
       <c r="X504" s="5" t="n">
         <v>9248699</v>
       </c>
-      <c r="Y504" t="inlineStr"/>
       <c r="Z504" s="4" t="n">
         <v>0</v>
       </c>
@@ -52632,7 +52024,6 @@
       <c r="X505" s="5" t="n">
         <v>418742</v>
       </c>
-      <c r="Y505" t="inlineStr"/>
       <c r="Z505" s="4" t="n">
         <v>0</v>
       </c>
@@ -52734,7 +52125,6 @@
       <c r="X506" s="5" t="n">
         <v>4624145</v>
       </c>
-      <c r="Y506" t="inlineStr"/>
       <c r="Z506" s="4" t="n">
         <v>0</v>
       </c>
@@ -52782,7 +52172,6 @@
           <t>Harriet Hageman</t>
         </is>
       </c>
-      <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr">
         <is>
           <t>REP</t>
@@ -52832,7 +52221,6 @@
       <c r="X507" s="5" t="n">
         <v>2435023</v>
       </c>
-      <c r="Y507" t="inlineStr"/>
       <c r="Z507" s="4" t="n">
         <v>0</v>
       </c>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generic ballot D+5.2 · House popular vote D+7.3</t>
+          <t>Generic ballot D+5.2 · House popular vote D+7.4</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="C8" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="D8" t="n">
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>56.2</v>
+        <v>51.3</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.6</v>
+        <v>232.9</v>
       </c>
       <c r="C9" t="n">
-        <v>202.4</v>
+        <v>202.1</v>
       </c>
       <c r="D9" t="n">
         <v>232</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="C10" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="D10" t="n">
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>56.6</v>
+        <v>55.8</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -721,7 +721,7 @@
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="17" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
     <col width="9" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="9" customWidth="1" min="28" max="28"/>
@@ -904,7 +904,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tom Begich</t>
+          <t>Jonathan Kreiss-Tomkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-4.36</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>36</v>
+        <v>26.1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -950,18 +950,12 @@
       <c r="R2" s="4" t="n">
         <v>-13.8</v>
       </c>
-      <c r="S2" s="4" t="n">
-        <v>46.99</v>
-      </c>
-      <c r="T2" s="4" t="n">
-        <v>37.94</v>
-      </c>
+      <c r="S2" s="4" t="n"/>
+      <c r="T2" s="4" t="n"/>
       <c r="U2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V2" s="4" t="n">
-        <v>8.06</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="4" t="n"/>
       <c r="W2" s="5" t="n">
         <v>0</v>
       </c>
@@ -976,10 +970,10 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>43.94</v>
+        <v>41.8</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>48.06</v>
+        <v>50.2</v>
       </c>
       <c r="AD2" s="4" t="n">
         <v>8</v>
@@ -2927,13 +2921,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-13.82</v>
+        <v>-17.72</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2976,22 +2970,18 @@
       <c r="X21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Brett Lindstrom</t>
-        </is>
-      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>37.92</v>
+        <v>41.14</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>50.08</v>
+        <v>58.86</v>
       </c>
       <c r="AD21" s="4" t="n">
         <v>0</v>
@@ -3557,7 +3547,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gentner Drummond</t>
+          <t>Mike Mazzei</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3567,7 +3557,7 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-31.06</v>
+        <v>-30.36</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>0</v>
@@ -3587,13 +3577,13 @@
         <v>5.2</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-31.06</v>
+        <v>-30.36</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>-34.95</v>
@@ -3618,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>34.47</v>
+        <v>34.82</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>65.53</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="AD27" s="4" t="n">
         <v>0</v>
@@ -4191,7 +4181,7 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-20.9</v>
+        <v>-20.26</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>0.2</v>
@@ -4240,18 +4230,22 @@
       <c r="X33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Lauren Pinkston</t>
+        </is>
+      </c>
       <c r="Z33" s="4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>39.55</v>
+        <v>39.09</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>60.45</v>
+        <v>58.96</v>
       </c>
       <c r="AD33" s="4" t="n">
         <v>0</v>
@@ -4717,30 +4711,30 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-5.08</v>
+        <v>-6.53</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>18.9</v>
+        <v>33.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.78</v>
+        <v>-9.82</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-1.35</v>
+        <v>-7.35</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>-1.04</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="4" t="n">
         <v>-1.67</v>
@@ -4772,19 +4766,19 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>47.46</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>0</v>
+        <v>40.59</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>52.54</v>
+        <v>48.19</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -5322,7 +5316,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Keith Pilkington</t>
+          <t>Maurice Mercer</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5341,7 +5335,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-28.02</v>
+        <v>-30.28</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5361,10 +5355,10 @@
         <v>5.2</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-28.02</v>
+        <v>-30.28</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0</v>
+        <v>-2.26</v>
       </c>
       <c r="Q44" s="4" t="n">
         <v>-2.19</v>
@@ -5379,7 +5373,7 @@
       </c>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="5" t="n">
-        <v>0</v>
+        <v>6539</v>
       </c>
       <c r="X44" s="5" t="n">
         <v>1053566</v>
@@ -5392,10 +5386,10 @@
         <v>0</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>35.99</v>
+        <v>34.86</v>
       </c>
       <c r="AC44" s="4" t="n">
-        <v>64.01000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="AD44" s="4" t="n">
         <v>0</v>
@@ -6157,7 +6151,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kirt Burgess</t>
+          <t>(no Republican filed)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6356,12 +6350,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Christopher James</t>
+          <t>Elizabeth Lee</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Daniel Keenan</t>
+          <t>Mark Lamb</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6371,13 +6365,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>-12.73</v>
+        <v>-12.42</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -6391,10 +6385,10 @@
         <v>5.2</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>-12.73</v>
+        <v>-12.42</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>-1.75</v>
+        <v>-1.44</v>
       </c>
       <c r="Q54" s="4" t="n">
         <v>0</v>
@@ -6409,10 +6403,10 @@
       </c>
       <c r="V54" s="4" t="n"/>
       <c r="W54" s="5" t="n">
-        <v>134852</v>
+        <v>153111</v>
       </c>
       <c r="X54" s="5" t="n">
-        <v>1851302</v>
+        <v>1222217</v>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" s="4" t="n">
@@ -6422,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>43.63</v>
+        <v>43.79</v>
       </c>
       <c r="AC54" s="4" t="n">
-        <v>56.37</v>
+        <v>56.21</v>
       </c>
       <c r="AD54" s="4" t="n">
         <v>0</v>
@@ -6664,7 +6658,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bernadette Greene Placentia</t>
+          <t>Bernadette Greene-Placentia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6683,13 +6677,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-8.27</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>5.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>94.5</v>
+        <v>91.3</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -6703,10 +6697,10 @@
         <v>5.2</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-8.27</v>
       </c>
       <c r="P57" s="4" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="4" t="n">
         <v>-0.95</v>
@@ -6721,7 +6715,7 @@
       </c>
       <c r="V57" s="4" t="n"/>
       <c r="W57" s="5" t="n">
-        <v>209358</v>
+        <v>0</v>
       </c>
       <c r="X57" s="5" t="n">
         <v>1206361</v>
@@ -6734,10 +6728,10 @@
         <v>0</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>45.27</v>
+        <v>45.86</v>
       </c>
       <c r="AC57" s="4" t="n">
-        <v>54.73</v>
+        <v>54.14</v>
       </c>
       <c r="AD57" s="4" t="n">
         <v>0</v>
@@ -6883,7 +6877,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>DEM</t>
+          <t>REP</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -7480,7 +7474,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Doris Matsui</t>
+          <t>Mai Vang</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7488,11 +7482,7 @@
           <t>(no Republican — top-two)</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>DEM</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -7519,13 +7509,13 @@
         <v>5.2</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>25.26</v>
+        <v>21.74</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R65" s="4" t="n">
         <v>13.26</v>
@@ -7537,7 +7527,7 @@
       </c>
       <c r="V65" s="4" t="n"/>
       <c r="W65" s="5" t="n">
-        <v>3192087</v>
+        <v>1086084</v>
       </c>
       <c r="X65" s="5" t="n">
         <v>0</v>
@@ -8198,7 +8188,11 @@
           <t>(no Republican — top-two)</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DEM</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>DEM</t>
@@ -8225,13 +8219,13 @@
         <v>5.2</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>45.81</v>
+        <v>47.47</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R72" s="4" t="n">
         <v>36.2</v>
@@ -11663,7 +11657,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>DEM</t>
+          <t>REP</t>
         </is>
       </c>
       <c r="I106" s="4" t="n">
@@ -12369,7 +12363,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jeffrey Hurd</t>
+          <t>Jeff Hurd</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -12687,7 +12681,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Khaleb Dammen</t>
+          <t>Jason Clark</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -12789,7 +12783,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amanda Capobianco</t>
+          <t>Tim Bennett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -12803,7 +12797,7 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>26.37</v>
+        <v>28.49</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>100</v>
@@ -12823,10 +12817,10 @@
         <v>5.2</v>
       </c>
       <c r="O117" s="4" t="n">
-        <v>26.37</v>
+        <v>28.49</v>
       </c>
       <c r="P117" s="4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q117" s="4" t="n">
         <v>3.03</v>
@@ -12844,7 +12838,7 @@
         <v>1866765</v>
       </c>
       <c r="X117" s="5" t="n">
-        <v>0</v>
+        <v>63306</v>
       </c>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" s="4" t="n">
@@ -12854,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>63.18</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AC117" s="4" t="n">
-        <v>36.82</v>
+        <v>35.76</v>
       </c>
       <c r="AD117" s="4" t="n">
         <v>0</v>
@@ -12905,7 +12899,7 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>89.7</v>
@@ -12925,7 +12919,7 @@
         <v>5.2</v>
       </c>
       <c r="O118" s="4" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="P118" s="4" t="n">
         <v>0.01</v>
@@ -13188,7 +13182,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rosa Delauro</t>
+          <t>Rosa DeLauro</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -14517,7 +14511,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuart Farber</t>
+          <t>(no Republican filed)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -15953,7 +15947,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Te Brown</t>
+          <t>Mayonna Te Brown</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -16477,7 +16471,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>James Kingston</t>
+          <t>Jim Kingston</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -16779,7 +16773,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Jim Duffie</t>
+          <t>James Duffie</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -16881,7 +16875,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Republican candidate (GA-05)</t>
+          <t>John Salvesen</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -16978,7 +16972,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lucia McBath</t>
+          <t>Lucy McBath</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -17080,7 +17074,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Haiden Moburg</t>
+          <t>Tony Kozycki</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -17099,7 +17093,7 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>-19.89</v>
+        <v>-20.89</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>0.2</v>
@@ -17119,10 +17113,10 @@
         <v>5.2</v>
       </c>
       <c r="O159" s="4" t="n">
-        <v>-19.89</v>
+        <v>-20.89</v>
       </c>
       <c r="P159" s="4" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="Q159" s="4" t="n">
         <v>-6.18</v>
@@ -17137,7 +17131,7 @@
       </c>
       <c r="V159" s="4" t="n"/>
       <c r="W159" s="5" t="n">
-        <v>0</v>
+        <v>392831</v>
       </c>
       <c r="X159" s="5" t="n">
         <v>1642413</v>
@@ -17150,10 +17144,10 @@
         <v>0</v>
       </c>
       <c r="AB159" s="4" t="n">
-        <v>40.06</v>
+        <v>39.55</v>
       </c>
       <c r="AC159" s="4" t="n">
-        <v>59.94</v>
+        <v>60.45</v>
       </c>
       <c r="AD159" s="4" t="n">
         <v>0</v>
@@ -17182,7 +17176,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>James Cooper</t>
+          <t>Kelly Esti</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -17201,7 +17195,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-29.74</v>
+        <v>-29.5</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>0</v>
@@ -17221,10 +17215,10 @@
         <v>5.2</v>
       </c>
       <c r="O160" s="4" t="n">
-        <v>-29.74</v>
+        <v>-29.5</v>
       </c>
       <c r="P160" s="4" t="n">
-        <v>-2.36</v>
+        <v>-2.12</v>
       </c>
       <c r="Q160" s="4" t="n">
         <v>-6.01</v>
@@ -17239,7 +17233,7 @@
       </c>
       <c r="V160" s="4" t="n"/>
       <c r="W160" s="5" t="n">
-        <v>142</v>
+        <v>19343</v>
       </c>
       <c r="X160" s="5" t="n">
         <v>1124952</v>
@@ -17252,10 +17246,10 @@
         <v>0</v>
       </c>
       <c r="AB160" s="4" t="n">
-        <v>35.13</v>
+        <v>35.25</v>
       </c>
       <c r="AC160" s="4" t="n">
-        <v>64.87</v>
+        <v>64.75</v>
       </c>
       <c r="AD160" s="4" t="n">
         <v>0</v>
@@ -17284,7 +17278,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Nicholas Alex</t>
+          <t>Caitlyn Gegen</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -17303,7 +17297,7 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>-30.03</v>
+        <v>-30.57</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>0</v>
@@ -17323,10 +17317,10 @@
         <v>5.2</v>
       </c>
       <c r="O161" s="4" t="n">
-        <v>-30.03</v>
+        <v>-30.57</v>
       </c>
       <c r="P161" s="4" t="n">
-        <v>-0.9</v>
+        <v>-1.43</v>
       </c>
       <c r="Q161" s="4" t="n">
         <v>-3.57</v>
@@ -17341,7 +17335,7 @@
       </c>
       <c r="V161" s="4" t="n"/>
       <c r="W161" s="5" t="n">
-        <v>156067</v>
+        <v>43387</v>
       </c>
       <c r="X161" s="5" t="n">
         <v>671072</v>
@@ -17354,10 +17348,10 @@
         <v>0</v>
       </c>
       <c r="AB161" s="4" t="n">
-        <v>34.98</v>
+        <v>34.72</v>
       </c>
       <c r="AC161" s="4" t="n">
-        <v>65.02</v>
+        <v>65.28</v>
       </c>
       <c r="AD161" s="4" t="n">
         <v>0</v>
@@ -17889,7 +17883,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Maxwell Frazier</t>
+          <t>Adriel Lam</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -18107,13 +18101,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11.27</v>
+        <v>10.72</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -18156,18 +18150,22 @@
       <c r="X169" s="5" t="n">
         <v>7208271</v>
       </c>
-      <c r="Y169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Michael Bridgford</t>
+        </is>
+      </c>
       <c r="Z169" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA169" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB169" s="4" t="n">
-        <v>55.64</v>
+        <v>49.27</v>
       </c>
       <c r="AC169" s="4" t="n">
-        <v>44.36</v>
+        <v>39.73</v>
       </c>
       <c r="AD169" s="4" t="n">
         <v>0</v>
@@ -18823,7 +18821,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Calvin Coleman</t>
+          <t>Michael Noack</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
@@ -18833,7 +18831,7 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>48.17</v>
+        <v>45.02</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>100</v>
@@ -18853,10 +18851,10 @@
         <v>5.2</v>
       </c>
       <c r="O176" s="4" t="n">
-        <v>48.17</v>
+        <v>45.02</v>
       </c>
       <c r="P176" s="4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q176" s="4" t="n">
         <v>0</v>
@@ -18874,7 +18872,7 @@
         <v>2452894</v>
       </c>
       <c r="X176" s="5" t="n">
-        <v>7994</v>
+        <v>0</v>
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" s="4" t="n">
@@ -18884,10 +18882,10 @@
         <v>0</v>
       </c>
       <c r="AB176" s="4" t="n">
-        <v>74.08</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="AC176" s="4" t="n">
-        <v>25.92</v>
+        <v>27.49</v>
       </c>
       <c r="AD176" s="4" t="n">
         <v>0</v>
@@ -19127,7 +19125,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tom Hanson</t>
+          <t>Tommy Hanson</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -19620,12 +19618,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Bradley Schneider</t>
+          <t>Brad Schneider</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Republican candidate (IL-10)</t>
+          <t>Carl Lambrecht</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -19727,7 +19725,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Jeffrey Walter</t>
+          <t>Jeff Walter</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -20742,7 +20740,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Joseph MacKey</t>
+          <t>Drew Cox</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20761,7 +20759,7 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>-30.73</v>
+        <v>-31.25</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>0</v>
@@ -20781,13 +20779,13 @@
         <v>5.2</v>
       </c>
       <c r="O195" s="4" t="n">
-        <v>-30.73</v>
+        <v>-31.25</v>
       </c>
       <c r="P195" s="4" t="n">
-        <v>-1.14</v>
+        <v>-1.09</v>
       </c>
       <c r="Q195" s="4" t="n">
-        <v>-3.91</v>
+        <v>-4.47</v>
       </c>
       <c r="R195" s="4" t="n">
         <v>-29.88</v>
@@ -20799,7 +20797,7 @@
       </c>
       <c r="V195" s="4" t="n"/>
       <c r="W195" s="5" t="n">
-        <v>11234</v>
+        <v>20377</v>
       </c>
       <c r="X195" s="5" t="n">
         <v>358293</v>
@@ -20812,10 +20810,10 @@
         <v>0</v>
       </c>
       <c r="AB195" s="4" t="n">
-        <v>34.63</v>
+        <v>34.38</v>
       </c>
       <c r="AC195" s="4" t="n">
-        <v>65.37</v>
+        <v>65.62</v>
       </c>
       <c r="AD195" s="4" t="n">
         <v>0</v>
@@ -20844,7 +20842,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>James Ford</t>
+          <t>J.D. Ford</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -21059,7 +21057,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Felipe Rios</t>
+          <t>Patrick McAuley</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -21258,7 +21256,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>James Graham</t>
+          <t>Brad Meyer</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21277,7 +21275,7 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>-29.87</v>
+        <v>-29.97</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>0</v>
@@ -21297,10 +21295,10 @@
         <v>5.2</v>
       </c>
       <c r="O200" s="4" t="n">
-        <v>-29.87</v>
+        <v>-29.97</v>
       </c>
       <c r="P200" s="4" t="n">
-        <v>-1.78</v>
+        <v>-1.88</v>
       </c>
       <c r="Q200" s="4" t="n">
         <v>-2.69</v>
@@ -21315,7 +21313,7 @@
       </c>
       <c r="V200" s="4" t="n"/>
       <c r="W200" s="5" t="n">
-        <v>128179</v>
+        <v>105510</v>
       </c>
       <c r="X200" s="5" t="n">
         <v>1856572</v>
@@ -21328,10 +21326,10 @@
         <v>0</v>
       </c>
       <c r="AB200" s="4" t="n">
-        <v>35.07</v>
+        <v>35.02</v>
       </c>
       <c r="AC200" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>64.98</v>
       </c>
       <c r="AD200" s="4" t="n">
         <v>0</v>
@@ -23896,7 +23894,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Daniel Schwartz</t>
+          <t>Dan Schwartz</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -23998,12 +23996,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>John Olszewski</t>
+          <t>Johnny Olszewski</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>David Wallace</t>
+          <t>Dave Wallace</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -24105,7 +24103,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Penny Kennedy</t>
+          <t>Berney Flowers</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -24119,7 +24117,7 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>32.47</v>
+        <v>34.67</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>100</v>
@@ -24139,10 +24137,10 @@
         <v>5.2</v>
       </c>
       <c r="O228" s="4" t="n">
-        <v>32.47</v>
+        <v>34.67</v>
       </c>
       <c r="P228" s="4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q228" s="4" t="n">
         <v>2.59</v>
@@ -24160,7 +24158,7 @@
         <v>1139858</v>
       </c>
       <c r="X228" s="5" t="n">
-        <v>0</v>
+        <v>12708</v>
       </c>
       <c r="Y228" t="inlineStr"/>
       <c r="Z228" s="4" t="n">
@@ -24170,10 +24168,10 @@
         <v>0</v>
       </c>
       <c r="AB228" s="4" t="n">
-        <v>66.23</v>
+        <v>67.34</v>
       </c>
       <c r="AC228" s="4" t="n">
-        <v>33.77</v>
+        <v>32.66</v>
       </c>
       <c r="AD228" s="4" t="n">
         <v>0</v>
@@ -24207,17 +24205,21 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Republican candidate (MD-04)</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr"/>
+          <t>George McDermott</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>DEM</t>
+        </is>
+      </c>
       <c r="H229" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>84.7</v>
+        <v>86.37</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>100</v>
@@ -24237,13 +24239,13 @@
         <v>5.2</v>
       </c>
       <c r="O229" s="4" t="n">
-        <v>84.7</v>
+        <v>86.37</v>
       </c>
       <c r="P229" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q229" s="4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R229" s="4" t="n">
         <v>75.67</v>
@@ -24268,10 +24270,10 @@
         <v>0</v>
       </c>
       <c r="AB229" s="4" t="n">
-        <v>92.34999999999999</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="AC229" s="4" t="n">
-        <v>7.65</v>
+        <v>6.82</v>
       </c>
       <c r="AD229" s="4" t="n">
         <v>0</v>
@@ -24398,7 +24400,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>April Delaney</t>
+          <t>April McClain Delaney</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -24505,7 +24507,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Republican candidate (MD-07)</t>
+          <t>Scott Collier</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -24723,7 +24725,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.03</v>
+        <v>29.84</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24737,13 +24739,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>21.83</v>
+        <v>21.89</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>30.86</v>
+        <v>30.91</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24774,10 +24776,10 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.16</v>
+        <v>62.18</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.84</v>
+        <v>32.82</v>
       </c>
       <c r="AD234" s="4" t="n">
         <v>5</v>
@@ -24821,13 +24823,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-4.45</v>
+        <v>-3.73</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24835,13 +24837,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-9.32</v>
+        <v>-9.26</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.59</v>
+        <v>-5.54</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24878,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>45.28</v>
+        <v>45.3</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>49.72</v>
+        <v>49.7</v>
       </c>
       <c r="AD235" s="4" t="n">
         <v>5</v>
@@ -25329,7 +25331,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Timothy Walberg</t>
+          <t>Tim Walberg</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -26969,7 +26971,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Peter Stauber</t>
+          <t>Pete Stauber</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -28093,7 +28095,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Mike Guest</t>
+          <t>Michael Guest</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -28190,7 +28192,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Jeffrey Hulum</t>
+          <t>Jeffrey Hulum III</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -28307,13 +28309,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-7.36</v>
+        <v>-7.38</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28321,13 +28323,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.64</v>
+        <v>-12.67</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.57</v>
+        <v>-8.6</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28364,10 +28366,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.32</v>
+        <v>46.31</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.68</v>
+        <v>53.69</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28415,7 +28417,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-34.3</v>
+        <v>-34.34</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28429,13 +28431,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.6</v>
+        <v>-31.64</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-34.3</v>
+        <v>-34.34</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28466,10 +28468,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>32.85</v>
+        <v>32.83</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>67.15000000000001</v>
+        <v>67.17</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -28537,10 +28539,10 @@
         <v>5.2</v>
       </c>
       <c r="O271" s="4" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="P271" s="4" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="Q271" s="4" t="n">
         <v>6.36</v>
@@ -28574,10 +28576,10 @@
         <v>0</v>
       </c>
       <c r="AB271" s="4" t="n">
-        <v>51.48</v>
+        <v>51.49</v>
       </c>
       <c r="AC271" s="4" t="n">
-        <v>48.52</v>
+        <v>48.51</v>
       </c>
       <c r="AD271" s="4" t="n">
         <v>0</v>
@@ -28708,7 +28710,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Raymond Smith</t>
+          <t>Raymond Smith Jr.</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -28815,7 +28817,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Mahesh Ganorkar</t>
+          <t>Max Ganorkar</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -29633,7 +29635,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>John Codiga</t>
+          <t>Jack Codiga</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -29832,7 +29834,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Lakesha Womack</t>
+          <t>LaKesha Womack</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -30061,27 +30063,27 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-9.41</v>
+        <v>-10.2</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-8.539999999999999</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-9.84</v>
+        <v>-10.77</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30118,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>45.29</v>
+        <v>44.9</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>54.71</v>
+        <v>55.1</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30165,13 +30167,13 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.85</v>
+        <v>12.06</v>
       </c>
       <c r="J287" s="4" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K287" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -30179,13 +30181,13 @@
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>9.32</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>14.59</v>
+        <v>13.66</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30222,10 +30224,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.42</v>
+        <v>56.03</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.58</v>
+        <v>43.97</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30273,7 +30275,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-52.38</v>
+        <v>-53.31</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30287,13 +30289,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-49.49</v>
+        <v>-50.42</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-52.38</v>
+        <v>-53.31</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30324,10 +30326,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.81</v>
+        <v>23.34</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.19</v>
+        <v>76.66</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -31293,7 +31295,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Republican candidate (NJ-08)</t>
+          <t>(no Republican filed)</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -31307,7 +31309,7 @@
         </is>
       </c>
       <c r="I298" s="4" t="n">
-        <v>45.96</v>
+        <v>46.75</v>
       </c>
       <c r="J298" s="4" t="n">
         <v>100</v>
@@ -31350,18 +31352,22 @@
       <c r="X298" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y298" t="inlineStr"/>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>Aristotle Eliopoulos</t>
+        </is>
+      </c>
       <c r="Z298" s="4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA298" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB298" s="4" t="n">
-        <v>72.98</v>
+        <v>71.59</v>
       </c>
       <c r="AC298" s="4" t="n">
-        <v>27.02</v>
+        <v>25.97</v>
       </c>
       <c r="AD298" s="4" t="n">
         <v>0</v>
@@ -31492,7 +31498,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Lamonica McIver</t>
+          <t>LaMonica McIver</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -32843,7 +32849,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>REP</t>
+          <t>DEM</t>
         </is>
       </c>
       <c r="I313" s="4" t="n">
@@ -33043,7 +33049,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Juan Pagan</t>
+          <t>Joseph Chou</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -33057,7 +33063,7 @@
         </is>
       </c>
       <c r="I315" s="4" t="n">
-        <v>29.13</v>
+        <v>30.61</v>
       </c>
       <c r="J315" s="4" t="n">
         <v>100</v>
@@ -33077,13 +33083,13 @@
         <v>5.2</v>
       </c>
       <c r="O315" s="4" t="n">
-        <v>29.13</v>
+        <v>30.61</v>
       </c>
       <c r="P315" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q315" s="4" t="n">
-        <v>10.25</v>
+        <v>11.74</v>
       </c>
       <c r="R315" s="4" t="n">
         <v>6.53</v>
@@ -33108,10 +33114,10 @@
         <v>0</v>
       </c>
       <c r="AB315" s="4" t="n">
-        <v>64.56</v>
+        <v>65.31</v>
       </c>
       <c r="AC315" s="4" t="n">
-        <v>35.44</v>
+        <v>34.69</v>
       </c>
       <c r="AD315" s="4" t="n">
         <v>0</v>
@@ -33745,7 +33751,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Republican candidate (NY-13)</t>
+          <t>Jomo Williams</t>
         </is>
       </c>
       <c r="G322" t="inlineStr"/>
@@ -33945,7 +33951,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Republican candidate (NY-15)</t>
+          <t>Stylo Sapaskis</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -35197,7 +35203,7 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>12.06</v>
+        <v>12.05</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>98.90000000000001</v>
@@ -35217,7 +35223,7 @@
         <v>5.2</v>
       </c>
       <c r="O336" s="4" t="n">
-        <v>12.06</v>
+        <v>12.05</v>
       </c>
       <c r="P336" s="4" t="n">
         <v>0.77</v>
@@ -35387,7 +35393,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Republican candidate (OH-03)</t>
+          <t>Cleophus Dulaney</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -35401,7 +35407,7 @@
         </is>
       </c>
       <c r="I338" s="4" t="n">
-        <v>53.01</v>
+        <v>53</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>100</v>
@@ -35421,7 +35427,7 @@
         <v>5.2</v>
       </c>
       <c r="O338" s="4" t="n">
-        <v>53.01</v>
+        <v>53</v>
       </c>
       <c r="P338" s="4" t="n">
         <v>0</v>
@@ -35484,7 +35490,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Tamara Wilson</t>
+          <t>Joshua Kolasinski</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -35503,7 +35509,7 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>-38.29</v>
+        <v>-38.91</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>0</v>
@@ -35523,10 +35529,10 @@
         <v>5.2</v>
       </c>
       <c r="O339" s="4" t="n">
-        <v>-38.29</v>
+        <v>-38.39</v>
       </c>
       <c r="P339" s="4" t="n">
-        <v>-3.15</v>
+        <v>-3.26</v>
       </c>
       <c r="Q339" s="4" t="n">
         <v>-1.21</v>
@@ -35541,23 +35547,27 @@
       </c>
       <c r="V339" s="4" t="n"/>
       <c r="W339" s="5" t="n">
-        <v>22050</v>
+        <v>12868</v>
       </c>
       <c r="X339" s="5" t="n">
         <v>4774322</v>
       </c>
-      <c r="Y339" t="inlineStr"/>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>Tamie Wilson</t>
+        </is>
+      </c>
       <c r="Z339" s="4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA339" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB339" s="4" t="n">
-        <v>30.86</v>
+        <v>30.05</v>
       </c>
       <c r="AC339" s="4" t="n">
-        <v>69.14</v>
+        <v>68.34</v>
       </c>
       <c r="AD339" s="4" t="n">
         <v>0</v>
@@ -35586,7 +35596,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Daniel Burket</t>
+          <t>Brian Shaver</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -35605,7 +35615,7 @@
         </is>
       </c>
       <c r="I340" s="4" t="n">
-        <v>-22.08</v>
+        <v>-22.03</v>
       </c>
       <c r="J340" s="4" t="n">
         <v>0.1</v>
@@ -35619,16 +35629,16 @@
         </is>
       </c>
       <c r="M340" s="4" t="n">
-        <v>-18.93</v>
+        <v>-18.94</v>
       </c>
       <c r="N340" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O340" s="4" t="n">
-        <v>-22.08</v>
+        <v>-22.03</v>
       </c>
       <c r="P340" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.4</v>
       </c>
       <c r="Q340" s="4" t="n">
         <v>-5.23</v>
@@ -35643,7 +35653,7 @@
       </c>
       <c r="V340" s="4" t="n"/>
       <c r="W340" s="5" t="n">
-        <v>7551</v>
+        <v>11664</v>
       </c>
       <c r="X340" s="5" t="n">
         <v>1461648</v>
@@ -35656,10 +35666,10 @@
         <v>0</v>
       </c>
       <c r="AB340" s="4" t="n">
-        <v>38.96</v>
+        <v>38.99</v>
       </c>
       <c r="AC340" s="4" t="n">
-        <v>61.04</v>
+        <v>61.01</v>
       </c>
       <c r="AD340" s="4" t="n">
         <v>0</v>
@@ -35688,7 +35698,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Malcolm Ritchie</t>
+          <t>Elizabeth Kirtley</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -35707,7 +35717,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>-28.14</v>
+        <v>-28.37</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>0</v>
@@ -35727,10 +35737,10 @@
         <v>5.2</v>
       </c>
       <c r="O341" s="4" t="n">
-        <v>-28.14</v>
+        <v>-28.37</v>
       </c>
       <c r="P341" s="4" t="n">
-        <v>-2.11</v>
+        <v>-2.34</v>
       </c>
       <c r="Q341" s="4" t="n">
         <v>-1.23</v>
@@ -35745,7 +35755,7 @@
       </c>
       <c r="V341" s="4" t="n"/>
       <c r="W341" s="5" t="n">
-        <v>19728</v>
+        <v>1132</v>
       </c>
       <c r="X341" s="5" t="n">
         <v>1112553</v>
@@ -35758,10 +35768,10 @@
         <v>0</v>
       </c>
       <c r="AB341" s="4" t="n">
-        <v>35.93</v>
+        <v>35.81</v>
       </c>
       <c r="AC341" s="4" t="n">
-        <v>64.06999999999999</v>
+        <v>64.19</v>
       </c>
       <c r="AD341" s="4" t="n">
         <v>0</v>
@@ -35812,10 +35822,10 @@
         <v>1.09</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35968,10 +35978,10 @@
         <v>0</v>
       </c>
       <c r="AB343" s="4" t="n">
-        <v>45.81</v>
+        <v>45.8</v>
       </c>
       <c r="AC343" s="4" t="n">
-        <v>54.19</v>
+        <v>54.2</v>
       </c>
       <c r="AD343" s="4" t="n">
         <v>0</v>
@@ -36033,7 +36043,7 @@
         </is>
       </c>
       <c r="M344" s="4" t="n">
-        <v>-5.28</v>
+        <v>-5.29</v>
       </c>
       <c r="N344" s="4" t="n">
         <v>5.2</v>
@@ -36235,7 +36245,7 @@
         </is>
       </c>
       <c r="I346" s="4" t="n">
-        <v>70.91</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>100</v>
@@ -36249,13 +36259,13 @@
         </is>
       </c>
       <c r="M346" s="4" t="n">
-        <v>60.77</v>
+        <v>60.76</v>
       </c>
       <c r="N346" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O346" s="4" t="n">
-        <v>70.91</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="P346" s="4" t="n">
         <v>0</v>
@@ -36337,7 +36347,7 @@
         </is>
       </c>
       <c r="I347" s="4" t="n">
-        <v>-25.46</v>
+        <v>-25.47</v>
       </c>
       <c r="J347" s="4" t="n">
         <v>0.1</v>
@@ -36357,7 +36367,7 @@
         <v>5.2</v>
       </c>
       <c r="O347" s="4" t="n">
-        <v>-25.46</v>
+        <v>-25.47</v>
       </c>
       <c r="P347" s="4" t="n">
         <v>-1.94</v>
@@ -36453,7 +36463,7 @@
         </is>
       </c>
       <c r="M348" s="4" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="N348" s="4" t="n">
         <v>5.2</v>
@@ -36555,7 +36565,7 @@
         </is>
       </c>
       <c r="M349" s="4" t="n">
-        <v>-15.35</v>
+        <v>-15.36</v>
       </c>
       <c r="N349" s="4" t="n">
         <v>5.2</v>
@@ -36737,7 +36747,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Jackson Lahmeyer</t>
+          <t>Mark Tedford</t>
         </is>
       </c>
       <c r="G351" t="inlineStr"/>
@@ -36747,7 +36757,7 @@
         </is>
       </c>
       <c r="I351" s="4" t="n">
-        <v>-16.98</v>
+        <v>-17.66</v>
       </c>
       <c r="J351" s="4" t="n">
         <v>0.4</v>
@@ -36761,16 +36771,16 @@
         </is>
       </c>
       <c r="M351" s="4" t="n">
-        <v>-20.77</v>
+        <v>-20.61</v>
       </c>
       <c r="N351" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O351" s="4" t="n">
-        <v>-16.98</v>
+        <v>-17.66</v>
       </c>
       <c r="P351" s="4" t="n">
-        <v>-0.85</v>
+        <v>-1.7</v>
       </c>
       <c r="Q351" s="4" t="n">
         <v>0</v>
@@ -36788,7 +36798,7 @@
         <v>141972</v>
       </c>
       <c r="X351" s="5" t="n">
-        <v>415914</v>
+        <v>1763830</v>
       </c>
       <c r="Y351" t="inlineStr"/>
       <c r="Z351" s="4" t="n">
@@ -36798,10 +36808,10 @@
         <v>0</v>
       </c>
       <c r="AB351" s="4" t="n">
-        <v>41.51</v>
+        <v>41.17</v>
       </c>
       <c r="AC351" s="4" t="n">
-        <v>58.49</v>
+        <v>58.83</v>
       </c>
       <c r="AD351" s="4" t="n">
         <v>0</v>
@@ -36830,7 +36840,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Erik Terwey</t>
+          <t>Brandon Wade</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -36849,7 +36859,7 @@
         </is>
       </c>
       <c r="I352" s="4" t="n">
-        <v>-51.52</v>
+        <v>-51.46</v>
       </c>
       <c r="J352" s="4" t="n">
         <v>0</v>
@@ -36863,16 +36873,16 @@
         </is>
       </c>
       <c r="M352" s="4" t="n">
-        <v>-54.03</v>
+        <v>-53.87</v>
       </c>
       <c r="N352" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O352" s="4" t="n">
-        <v>-51.52</v>
+        <v>-51.46</v>
       </c>
       <c r="P352" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="Q352" s="4" t="n">
         <v>-0.28</v>
@@ -36887,7 +36897,7 @@
       </c>
       <c r="V352" s="4" t="n"/>
       <c r="W352" s="5" t="n">
-        <v>11759</v>
+        <v>4290</v>
       </c>
       <c r="X352" s="5" t="n">
         <v>218894</v>
@@ -36900,10 +36910,10 @@
         <v>0</v>
       </c>
       <c r="AB352" s="4" t="n">
-        <v>24.24</v>
+        <v>24.27</v>
       </c>
       <c r="AC352" s="4" t="n">
-        <v>75.76000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="AD352" s="4" t="n">
         <v>0</v>
@@ -36932,7 +36942,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Jules Roberson</t>
+          <t>Suzie Byrd</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -36951,7 +36961,7 @@
         </is>
       </c>
       <c r="I353" s="4" t="n">
-        <v>-45.45</v>
+        <v>-43.09</v>
       </c>
       <c r="J353" s="4" t="n">
         <v>0</v>
@@ -36965,16 +36975,16 @@
         </is>
       </c>
       <c r="M353" s="4" t="n">
-        <v>-43.73</v>
+        <v>-43.57</v>
       </c>
       <c r="N353" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O353" s="4" t="n">
-        <v>-45.45</v>
+        <v>-43.09</v>
       </c>
       <c r="P353" s="4" t="n">
-        <v>-2.2</v>
+        <v>0</v>
       </c>
       <c r="Q353" s="4" t="n">
         <v>-4.46</v>
@@ -36989,7 +36999,7 @@
       </c>
       <c r="V353" s="4" t="n"/>
       <c r="W353" s="5" t="n">
-        <v>945</v>
+        <v>0</v>
       </c>
       <c r="X353" s="5" t="n">
         <v>907279</v>
@@ -37002,10 +37012,10 @@
         <v>0</v>
       </c>
       <c r="AB353" s="4" t="n">
-        <v>27.27</v>
+        <v>28.45</v>
       </c>
       <c r="AC353" s="4" t="n">
-        <v>72.73</v>
+        <v>71.55</v>
       </c>
       <c r="AD353" s="4" t="n">
         <v>0</v>
@@ -37053,7 +37063,7 @@
         </is>
       </c>
       <c r="I354" s="4" t="n">
-        <v>-34.8</v>
+        <v>-34.64</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>0</v>
@@ -37067,13 +37077,13 @@
         </is>
       </c>
       <c r="M354" s="4" t="n">
-        <v>-31.76</v>
+        <v>-31.6</v>
       </c>
       <c r="N354" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O354" s="4" t="n">
-        <v>-34.8</v>
+        <v>-34.64</v>
       </c>
       <c r="P354" s="4" t="n">
         <v>-2.65</v>
@@ -37104,10 +37114,10 @@
         <v>0</v>
       </c>
       <c r="AB354" s="4" t="n">
-        <v>32.6</v>
+        <v>32.68</v>
       </c>
       <c r="AC354" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="AD354" s="4" t="n">
         <v>0</v>
@@ -37155,7 +37165,7 @@
         </is>
       </c>
       <c r="I355" s="4" t="n">
-        <v>-16.84</v>
+        <v>-16.68</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>0.5</v>
@@ -37169,13 +37179,13 @@
         </is>
       </c>
       <c r="M355" s="4" t="n">
-        <v>-17.52</v>
+        <v>-17.36</v>
       </c>
       <c r="N355" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O355" s="4" t="n">
-        <v>-16.84</v>
+        <v>-16.68</v>
       </c>
       <c r="P355" s="4" t="n">
         <v>-1.04</v>
@@ -37206,10 +37216,10 @@
         <v>0</v>
       </c>
       <c r="AB355" s="4" t="n">
-        <v>41.58</v>
+        <v>41.66</v>
       </c>
       <c r="AC355" s="4" t="n">
-        <v>58.42</v>
+        <v>58.34</v>
       </c>
       <c r="AD355" s="4" t="n">
         <v>0</v>
@@ -37544,12 +37554,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Valerie Hoyle</t>
+          <t>Val Hoyle</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Monique Despain</t>
+          <t>Monique DeSpain</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -37661,7 +37671,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>REP</t>
+          <t>DEM</t>
         </is>
       </c>
       <c r="I360" s="4" t="n">
@@ -37850,7 +37860,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Robert Harvie</t>
+          <t>Bob Harvie</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -38065,7 +38075,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Alexander Schnell</t>
+          <t>(no Republican filed)</t>
         </is>
       </c>
       <c r="G364" t="inlineStr"/>
@@ -38075,7 +38085,7 @@
         </is>
       </c>
       <c r="I364" s="4" t="n">
-        <v>92.05</v>
+        <v>89.12</v>
       </c>
       <c r="J364" s="4" t="n">
         <v>100</v>
@@ -38095,10 +38105,10 @@
         <v>5.2</v>
       </c>
       <c r="O364" s="4" t="n">
-        <v>92.05</v>
+        <v>89.19</v>
       </c>
       <c r="P364" s="4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q364" s="4" t="n">
         <v>0</v>
@@ -38116,20 +38126,24 @@
         <v>1329253</v>
       </c>
       <c r="X364" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="Y364" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>Dennis Joseph Mahoney</t>
+        </is>
+      </c>
       <c r="Z364" s="4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA364" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB364" s="4" t="n">
-        <v>96.02</v>
+        <v>93.14</v>
       </c>
       <c r="AC364" s="4" t="n">
-        <v>3.98</v>
+        <v>5.36</v>
       </c>
       <c r="AD364" s="4" t="n">
         <v>0</v>
@@ -38260,12 +38274,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Mary Scanlon</t>
+          <t>Mary Gay Scanlon</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Melvin Johnakin</t>
+          <t>Nicholas Manganaro</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -38279,7 +38293,7 @@
         </is>
       </c>
       <c r="I366" s="4" t="n">
-        <v>42.36</v>
+        <v>44.5</v>
       </c>
       <c r="J366" s="4" t="n">
         <v>100</v>
@@ -38299,10 +38313,10 @@
         <v>5.2</v>
       </c>
       <c r="O366" s="4" t="n">
-        <v>42.36</v>
+        <v>44.5</v>
       </c>
       <c r="P366" s="4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q366" s="4" t="n">
         <v>3.07</v>
@@ -38320,7 +38334,7 @@
         <v>990586</v>
       </c>
       <c r="X366" s="5" t="n">
-        <v>0</v>
+        <v>9296</v>
       </c>
       <c r="Y366" t="inlineStr"/>
       <c r="Z366" s="4" t="n">
@@ -38330,10 +38344,10 @@
         <v>0</v>
       </c>
       <c r="AB366" s="4" t="n">
-        <v>71.18000000000001</v>
+        <v>72.25</v>
       </c>
       <c r="AC366" s="4" t="n">
-        <v>28.82</v>
+        <v>27.75</v>
       </c>
       <c r="AD366" s="4" t="n">
         <v>0</v>
@@ -38367,7 +38381,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Martin Young</t>
+          <t>Marty Young</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -38587,7 +38601,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>DEM</t>
+          <t>REP</t>
         </is>
       </c>
       <c r="I369" s="4" t="n">
@@ -38997,7 +39011,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Leonard Fechter</t>
+          <t>James Hayes</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -39011,7 +39025,7 @@
         </is>
       </c>
       <c r="I373" s="4" t="n">
-        <v>29.81</v>
+        <v>29.59</v>
       </c>
       <c r="J373" s="4" t="n">
         <v>100</v>
@@ -39031,10 +39045,10 @@
         <v>5.2</v>
       </c>
       <c r="O373" s="4" t="n">
-        <v>29.81</v>
+        <v>29.59</v>
       </c>
       <c r="P373" s="4" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="Q373" s="4" t="n">
         <v>-1.29</v>
@@ -39052,7 +39066,7 @@
         <v>1466287</v>
       </c>
       <c r="X373" s="5" t="n">
-        <v>17477</v>
+        <v>40139</v>
       </c>
       <c r="Y373" t="inlineStr"/>
       <c r="Z373" s="4" t="n">
@@ -39062,10 +39076,10 @@
         <v>0</v>
       </c>
       <c r="AB373" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AC373" s="4" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="AD373" s="4" t="n">
         <v>0</v>
@@ -39094,7 +39108,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Elizabeth Farnham</t>
+          <t>Beth Farnham</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -39196,7 +39210,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>David Bradstock</t>
+          <t>Alan Bradstock</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -39298,7 +39312,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Raymond Bilger</t>
+          <t>Ray Bilger</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -39405,7 +39419,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>George Kelly</t>
+          <t>Mike Kelly</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -39507,7 +39521,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Jesse Vodvarka</t>
+          <t>Tony Guy</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -39521,13 +39535,13 @@
         </is>
       </c>
       <c r="I378" s="4" t="n">
-        <v>21.84</v>
+        <v>21.2</v>
       </c>
       <c r="J378" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="K378" s="4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -39541,10 +39555,10 @@
         <v>5.2</v>
       </c>
       <c r="O378" s="4" t="n">
-        <v>21.84</v>
+        <v>21.2</v>
       </c>
       <c r="P378" s="4" t="n">
-        <v>2.76</v>
+        <v>2.12</v>
       </c>
       <c r="Q378" s="4" t="n">
         <v>4.58</v>
@@ -39562,7 +39576,7 @@
         <v>2776943</v>
       </c>
       <c r="X378" s="5" t="n">
-        <v>21506</v>
+        <v>117530</v>
       </c>
       <c r="Y378" t="inlineStr"/>
       <c r="Z378" s="4" t="n">
@@ -39572,10 +39586,10 @@
         <v>0</v>
       </c>
       <c r="AB378" s="4" t="n">
-        <v>60.92</v>
+        <v>60.6</v>
       </c>
       <c r="AC378" s="4" t="n">
-        <v>39.08</v>
+        <v>39.4</v>
       </c>
       <c r="AD378" s="4" t="n">
         <v>0</v>
@@ -39823,27 +39837,27 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-3.47</v>
+        <v>-3.15</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>24.7</v>
+        <v>25.9</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>75.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M381" s="4" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="N381" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O381" s="4" t="n">
-        <v>-3.39</v>
+        <v>-2.92</v>
       </c>
       <c r="P381" s="4" t="n">
         <v>0.72</v>
@@ -39880,10 +39894,10 @@
         <v>0</v>
       </c>
       <c r="AB381" s="4" t="n">
-        <v>47.21</v>
+        <v>47.37</v>
       </c>
       <c r="AC381" s="4" t="n">
-        <v>50.61</v>
+        <v>50.45</v>
       </c>
       <c r="AD381" s="4" t="n">
         <v>2.18</v>
@@ -39931,13 +39945,13 @@
         </is>
       </c>
       <c r="I382" s="4" t="n">
-        <v>-11.64</v>
+        <v>-11.17</v>
       </c>
       <c r="J382" s="4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K382" s="4" t="n">
-        <v>98.8</v>
+        <v>98.5</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -39945,13 +39959,13 @@
         </is>
       </c>
       <c r="M382" s="4" t="n">
-        <v>-10.04</v>
+        <v>-9.57</v>
       </c>
       <c r="N382" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O382" s="4" t="n">
-        <v>-11.64</v>
+        <v>-11.17</v>
       </c>
       <c r="P382" s="4" t="n">
         <v>-2.01</v>
@@ -39982,10 +39996,10 @@
         <v>0</v>
       </c>
       <c r="AB382" s="4" t="n">
-        <v>44.18</v>
+        <v>44.41</v>
       </c>
       <c r="AC382" s="4" t="n">
-        <v>55.82</v>
+        <v>55.59</v>
       </c>
       <c r="AD382" s="4" t="n">
         <v>0</v>
@@ -40033,7 +40047,7 @@
         </is>
       </c>
       <c r="I383" s="4" t="n">
-        <v>-41.64</v>
+        <v>-41.18</v>
       </c>
       <c r="J383" s="4" t="n">
         <v>0</v>
@@ -40047,13 +40061,13 @@
         </is>
       </c>
       <c r="M383" s="4" t="n">
-        <v>-38.5</v>
+        <v>-38.03</v>
       </c>
       <c r="N383" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O383" s="4" t="n">
-        <v>-41.64</v>
+        <v>-41.18</v>
       </c>
       <c r="P383" s="4" t="n">
         <v>-1.36</v>
@@ -40084,10 +40098,10 @@
         <v>0</v>
       </c>
       <c r="AB383" s="4" t="n">
-        <v>29.18</v>
+        <v>29.41</v>
       </c>
       <c r="AC383" s="4" t="n">
-        <v>70.81999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="AD383" s="4" t="n">
         <v>0</v>
@@ -40135,7 +40149,7 @@
         </is>
       </c>
       <c r="I384" s="4" t="n">
-        <v>-18.08</v>
+        <v>-17.61</v>
       </c>
       <c r="J384" s="4" t="n">
         <v>0.4</v>
@@ -40149,13 +40163,13 @@
         </is>
       </c>
       <c r="M384" s="4" t="n">
-        <v>-19.34</v>
+        <v>-18.87</v>
       </c>
       <c r="N384" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O384" s="4" t="n">
-        <v>-18.08</v>
+        <v>-17.61</v>
       </c>
       <c r="P384" s="4" t="n">
         <v>-2.31</v>
@@ -40186,10 +40200,10 @@
         <v>0</v>
       </c>
       <c r="AB384" s="4" t="n">
-        <v>40.96</v>
+        <v>41.19</v>
       </c>
       <c r="AC384" s="4" t="n">
-        <v>59.04</v>
+        <v>58.81</v>
       </c>
       <c r="AD384" s="4" t="n">
         <v>0</v>
@@ -40233,13 +40247,13 @@
         </is>
       </c>
       <c r="I385" s="4" t="n">
-        <v>-14.78</v>
+        <v>-14.31</v>
       </c>
       <c r="J385" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K385" s="4" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -40247,13 +40261,13 @@
         </is>
       </c>
       <c r="M385" s="4" t="n">
-        <v>-18.32</v>
+        <v>-17.85</v>
       </c>
       <c r="N385" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O385" s="4" t="n">
-        <v>-14.78</v>
+        <v>-14.31</v>
       </c>
       <c r="P385" s="4" t="n">
         <v>-1.2</v>
@@ -40284,10 +40298,10 @@
         <v>0</v>
       </c>
       <c r="AB385" s="4" t="n">
-        <v>42.61</v>
+        <v>42.84</v>
       </c>
       <c r="AC385" s="4" t="n">
-        <v>57.39</v>
+        <v>57.16</v>
       </c>
       <c r="AD385" s="4" t="n">
         <v>0</v>
@@ -40335,7 +40349,7 @@
         </is>
       </c>
       <c r="I386" s="4" t="n">
-        <v>36.12</v>
+        <v>36.59</v>
       </c>
       <c r="J386" s="4" t="n">
         <v>100</v>
@@ -40349,13 +40363,13 @@
         </is>
       </c>
       <c r="M386" s="4" t="n">
-        <v>29.41</v>
+        <v>29.88</v>
       </c>
       <c r="N386" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O386" s="4" t="n">
-        <v>36.12</v>
+        <v>36.59</v>
       </c>
       <c r="P386" s="4" t="n">
         <v>0</v>
@@ -40386,10 +40400,10 @@
         <v>0</v>
       </c>
       <c r="AB386" s="4" t="n">
-        <v>68.06</v>
+        <v>68.3</v>
       </c>
       <c r="AC386" s="4" t="n">
-        <v>31.94</v>
+        <v>31.7</v>
       </c>
       <c r="AD386" s="4" t="n">
         <v>0</v>
@@ -40437,7 +40451,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-16.5</v>
+        <v>-16.2</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>0.5</v>
@@ -40451,13 +40465,13 @@
         </is>
       </c>
       <c r="M387" s="4" t="n">
-        <v>-20.91</v>
+        <v>-20.44</v>
       </c>
       <c r="N387" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O387" s="4" t="n">
-        <v>-21.53</v>
+        <v>-21.07</v>
       </c>
       <c r="P387" s="4" t="n">
         <v>-1.22</v>
@@ -40494,10 +40508,10 @@
         <v>0</v>
       </c>
       <c r="AB387" s="4" t="n">
-        <v>41.75</v>
+        <v>41.9</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>58.25</v>
+        <v>58.1</v>
       </c>
       <c r="AD387" s="4" t="n">
         <v>0</v>
@@ -40526,7 +40540,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Nicole Gronli</t>
+          <t>Nikki Gronli</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -40643,7 +40657,7 @@
         </is>
       </c>
       <c r="I389" s="4" t="n">
-        <v>-55.99</v>
+        <v>-55.83</v>
       </c>
       <c r="J389" s="4" t="n">
         <v>0</v>
@@ -40657,13 +40671,13 @@
         </is>
       </c>
       <c r="M389" s="4" t="n">
-        <v>-56.2</v>
+        <v>-56.04</v>
       </c>
       <c r="N389" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O389" s="4" t="n">
-        <v>-55.99</v>
+        <v>-55.83</v>
       </c>
       <c r="P389" s="4" t="n">
         <v>-1.63</v>
@@ -40694,10 +40708,10 @@
         <v>0</v>
       </c>
       <c r="AB389" s="4" t="n">
-        <v>22</v>
+        <v>22.08</v>
       </c>
       <c r="AC389" s="4" t="n">
-        <v>78</v>
+        <v>77.92</v>
       </c>
       <c r="AD389" s="4" t="n">
         <v>0</v>
@@ -40745,7 +40759,7 @@
         </is>
       </c>
       <c r="I390" s="4" t="n">
-        <v>-33.33</v>
+        <v>-33.17</v>
       </c>
       <c r="J390" s="4" t="n">
         <v>0</v>
@@ -40759,13 +40773,13 @@
         </is>
       </c>
       <c r="M390" s="4" t="n">
-        <v>-32.04</v>
+        <v>-31.88</v>
       </c>
       <c r="N390" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O390" s="4" t="n">
-        <v>-33.33</v>
+        <v>-33.17</v>
       </c>
       <c r="P390" s="4" t="n">
         <v>-1.28</v>
@@ -40796,10 +40810,10 @@
         <v>0</v>
       </c>
       <c r="AB390" s="4" t="n">
-        <v>33.34</v>
+        <v>33.42</v>
       </c>
       <c r="AC390" s="4" t="n">
-        <v>66.66</v>
+        <v>66.58</v>
       </c>
       <c r="AD390" s="4" t="n">
         <v>0</v>
@@ -40847,7 +40861,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>-35.11</v>
+        <v>-34.95</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>0</v>
@@ -40861,13 +40875,13 @@
         </is>
       </c>
       <c r="M391" s="4" t="n">
-        <v>-33.85</v>
+        <v>-33.69</v>
       </c>
       <c r="N391" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O391" s="4" t="n">
-        <v>-35.11</v>
+        <v>-34.95</v>
       </c>
       <c r="P391" s="4" t="n">
         <v>-2.34</v>
@@ -40898,10 +40912,10 @@
         <v>0</v>
       </c>
       <c r="AB391" s="4" t="n">
-        <v>32.45</v>
+        <v>32.53</v>
       </c>
       <c r="AC391" s="4" t="n">
-        <v>67.55</v>
+        <v>67.47</v>
       </c>
       <c r="AD391" s="4" t="n">
         <v>0</v>
@@ -40935,7 +40949,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Scott Desjarlais</t>
+          <t>Scott DesJarlais</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -40949,7 +40963,7 @@
         </is>
       </c>
       <c r="I392" s="4" t="n">
-        <v>-17.47</v>
+        <v>-17.31</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>0.4</v>
@@ -40963,13 +40977,13 @@
         </is>
       </c>
       <c r="M392" s="4" t="n">
-        <v>-20.82</v>
+        <v>-20.66</v>
       </c>
       <c r="N392" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O392" s="4" t="n">
-        <v>-17.47</v>
+        <v>-17.31</v>
       </c>
       <c r="P392" s="4" t="n">
         <v>-1.26</v>
@@ -41000,10 +41014,10 @@
         <v>0</v>
       </c>
       <c r="AB392" s="4" t="n">
-        <v>41.26</v>
+        <v>41.34</v>
       </c>
       <c r="AC392" s="4" t="n">
-        <v>58.74</v>
+        <v>58.66</v>
       </c>
       <c r="AD392" s="4" t="n">
         <v>0</v>
@@ -41047,13 +41061,13 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-13.16</v>
+        <v>-13</v>
       </c>
       <c r="J393" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K393" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -41061,13 +41075,13 @@
         </is>
       </c>
       <c r="M393" s="4" t="n">
-        <v>-18.91</v>
+        <v>-18.75</v>
       </c>
       <c r="N393" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>-13.16</v>
+        <v>-13</v>
       </c>
       <c r="P393" s="4" t="n">
         <v>0.96</v>
@@ -41098,10 +41112,10 @@
         <v>0</v>
       </c>
       <c r="AB393" s="4" t="n">
-        <v>43.42</v>
+        <v>43.5</v>
       </c>
       <c r="AC393" s="4" t="n">
-        <v>56.58</v>
+        <v>56.5</v>
       </c>
       <c r="AD393" s="4" t="n">
         <v>0</v>
@@ -41145,7 +41159,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-21.35</v>
+        <v>-21.19</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>0.2</v>
@@ -41159,13 +41173,13 @@
         </is>
       </c>
       <c r="M394" s="4" t="n">
-        <v>-23.86</v>
+        <v>-23.7</v>
       </c>
       <c r="N394" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O394" s="4" t="n">
-        <v>-21.35</v>
+        <v>-21.19</v>
       </c>
       <c r="P394" s="4" t="n">
         <v>-2.06</v>
@@ -41196,10 +41210,10 @@
         <v>0</v>
       </c>
       <c r="AB394" s="4" t="n">
-        <v>39.33</v>
+        <v>39.41</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>60.67</v>
+        <v>60.59</v>
       </c>
       <c r="AD394" s="4" t="n">
         <v>0</v>
@@ -41247,7 +41261,7 @@
         </is>
       </c>
       <c r="I395" s="4" t="n">
-        <v>-17.87</v>
+        <v>-17.71</v>
       </c>
       <c r="J395" s="4" t="n">
         <v>0.4</v>
@@ -41261,13 +41275,13 @@
         </is>
       </c>
       <c r="M395" s="4" t="n">
-        <v>-20.24</v>
+        <v>-20.08</v>
       </c>
       <c r="N395" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O395" s="4" t="n">
-        <v>-17.87</v>
+        <v>-17.71</v>
       </c>
       <c r="P395" s="4" t="n">
         <v>-0.6</v>
@@ -41298,10 +41312,10 @@
         <v>0</v>
       </c>
       <c r="AB395" s="4" t="n">
-        <v>41.07</v>
+        <v>41.15</v>
       </c>
       <c r="AC395" s="4" t="n">
-        <v>58.93</v>
+        <v>58.85</v>
       </c>
       <c r="AD395" s="4" t="n">
         <v>0</v>
@@ -41349,7 +41363,7 @@
         </is>
       </c>
       <c r="I396" s="4" t="n">
-        <v>-21.12</v>
+        <v>-20.96</v>
       </c>
       <c r="J396" s="4" t="n">
         <v>0.2</v>
@@ -41363,13 +41377,13 @@
         </is>
       </c>
       <c r="M396" s="4" t="n">
-        <v>-18.04</v>
+        <v>-17.88</v>
       </c>
       <c r="N396" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O396" s="4" t="n">
-        <v>-21.12</v>
+        <v>-20.96</v>
       </c>
       <c r="P396" s="4" t="n">
         <v>-2.43</v>
@@ -41400,10 +41414,10 @@
         <v>0</v>
       </c>
       <c r="AB396" s="4" t="n">
-        <v>39.44</v>
+        <v>39.52</v>
       </c>
       <c r="AC396" s="4" t="n">
-        <v>60.56</v>
+        <v>60.48</v>
       </c>
       <c r="AD396" s="4" t="n">
         <v>0</v>
@@ -41432,7 +41446,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Justin Pearson</t>
+          <t>Justin J. Pearson</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -41443,11 +41457,11 @@
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr">
         <is>
-          <t>REP</t>
+          <t>DEM</t>
         </is>
       </c>
       <c r="I397" s="4" t="n">
-        <v>-11.75</v>
+        <v>-11.59</v>
       </c>
       <c r="J397" s="4" t="n">
         <v>1.2</v>
@@ -41461,13 +41475,13 @@
         </is>
       </c>
       <c r="M397" s="4" t="n">
-        <v>-16.89</v>
+        <v>-16.73</v>
       </c>
       <c r="N397" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O397" s="4" t="n">
-        <v>-11.75</v>
+        <v>-11.59</v>
       </c>
       <c r="P397" s="4" t="n">
         <v>0.24</v>
@@ -41498,10 +41512,10 @@
         <v>0</v>
       </c>
       <c r="AB397" s="4" t="n">
-        <v>44.12</v>
+        <v>44.2</v>
       </c>
       <c r="AC397" s="4" t="n">
-        <v>55.88</v>
+        <v>55.8</v>
       </c>
       <c r="AD397" s="4" t="n">
         <v>0</v>
@@ -41530,7 +41544,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Democratic candidate (TX-01)</t>
+          <t>Yolanda Prince</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -41549,7 +41563,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-40.72</v>
+        <v>-43.31</v>
       </c>
       <c r="J398" s="4" t="n">
         <v>0</v>
@@ -41569,10 +41583,10 @@
         <v>5.2</v>
       </c>
       <c r="O398" s="4" t="n">
-        <v>-40.72</v>
+        <v>-43.31</v>
       </c>
       <c r="P398" s="4" t="n">
-        <v>0</v>
+        <v>-2.58</v>
       </c>
       <c r="Q398" s="4" t="n">
         <v>-1.67</v>
@@ -41587,7 +41601,7 @@
       </c>
       <c r="V398" s="4" t="n"/>
       <c r="W398" s="5" t="n">
-        <v>0</v>
+        <v>9245</v>
       </c>
       <c r="X398" s="5" t="n">
         <v>1797848</v>
@@ -41600,10 +41614,10 @@
         <v>0</v>
       </c>
       <c r="AB398" s="4" t="n">
-        <v>29.64</v>
+        <v>28.35</v>
       </c>
       <c r="AC398" s="4" t="n">
-        <v>70.36</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="AD398" s="4" t="n">
         <v>0</v>
@@ -41934,7 +41948,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Ruth Torres</t>
+          <t>Chelsey Hockett</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -41953,13 +41967,13 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-13.51</v>
+        <v>-15.24</v>
       </c>
       <c r="J402" s="4" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K402" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
@@ -41973,13 +41987,13 @@
         <v>5.2</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-13.51</v>
+        <v>-15.24</v>
       </c>
       <c r="P402" s="4" t="n">
-        <v>-2.23</v>
+        <v>-2.33</v>
       </c>
       <c r="Q402" s="4" t="n">
-        <v>-0.52</v>
+        <v>-2.16</v>
       </c>
       <c r="R402" s="4" t="n">
         <v>-21.84</v>
@@ -41991,7 +42005,7 @@
       </c>
       <c r="V402" s="4" t="n"/>
       <c r="W402" s="5" t="n">
-        <v>20748</v>
+        <v>12666</v>
       </c>
       <c r="X402" s="5" t="n">
         <v>1341647</v>
@@ -42004,10 +42018,10 @@
         <v>0</v>
       </c>
       <c r="AB402" s="4" t="n">
-        <v>43.25</v>
+        <v>42.38</v>
       </c>
       <c r="AC402" s="4" t="n">
-        <v>56.75</v>
+        <v>57.62</v>
       </c>
       <c r="AD402" s="4" t="n">
         <v>0</v>
@@ -42069,7 +42083,7 @@
         </is>
       </c>
       <c r="M403" s="4" t="n">
-        <v>-18.58</v>
+        <v>-18.59</v>
       </c>
       <c r="N403" s="4" t="n">
         <v>5.2</v>
@@ -42138,7 +42152,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Elizabeth Fletcher</t>
+          <t>Lizzie Fletcher</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -42171,7 +42185,7 @@
         </is>
       </c>
       <c r="M404" s="4" t="n">
-        <v>30.75</v>
+        <v>30.74</v>
       </c>
       <c r="N404" s="4" t="n">
         <v>5.2</v>
@@ -42240,7 +42254,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Keith Coleman</t>
+          <t>Laura Jones</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -42255,7 +42269,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-18.09</v>
+        <v>-17.98</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.4</v>
@@ -42275,10 +42289,10 @@
         <v>5.2</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-18.09</v>
+        <v>-17.98</v>
       </c>
       <c r="P405" s="4" t="n">
-        <v>-2.83</v>
+        <v>-2.72</v>
       </c>
       <c r="Q405" s="4" t="n">
         <v>0</v>
@@ -42293,7 +42307,7 @@
       </c>
       <c r="V405" s="4" t="n"/>
       <c r="W405" s="5" t="n">
-        <v>11974</v>
+        <v>21980</v>
       </c>
       <c r="X405" s="5" t="n">
         <v>2064033</v>
@@ -42306,10 +42320,10 @@
         <v>0</v>
       </c>
       <c r="AB405" s="4" t="n">
-        <v>40.96</v>
+        <v>41.01</v>
       </c>
       <c r="AC405" s="4" t="n">
-        <v>59.04</v>
+        <v>58.99</v>
       </c>
       <c r="AD405" s="4" t="n">
         <v>0</v>
@@ -42343,7 +42357,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Alexandra Mealer</t>
+          <t>Alex Mealer</t>
         </is>
       </c>
       <c r="G406" t="inlineStr"/>
@@ -42367,7 +42381,7 @@
         </is>
       </c>
       <c r="M406" s="4" t="n">
-        <v>-12.26</v>
+        <v>-12.27</v>
       </c>
       <c r="N406" s="4" t="n">
         <v>5.2</v>
@@ -42404,10 +42418,10 @@
         <v>0</v>
       </c>
       <c r="AB406" s="4" t="n">
-        <v>46.6</v>
+        <v>46.59</v>
       </c>
       <c r="AC406" s="4" t="n">
-        <v>53.4</v>
+        <v>53.41</v>
       </c>
       <c r="AD406" s="4" t="n">
         <v>0</v>
@@ -42636,7 +42650,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Heli Rodriguez-Prilliman</t>
+          <t>Heli Rodriguez Prilliman</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -42771,7 +42785,7 @@
         </is>
       </c>
       <c r="M410" s="4" t="n">
-        <v>-42.23</v>
+        <v>-42.24</v>
       </c>
       <c r="N410" s="4" t="n">
         <v>5.2</v>
@@ -42840,7 +42854,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Richard Davis</t>
+          <t>Thurman Bartie</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -42859,7 +42873,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-19.79</v>
+        <v>-19.84</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.2</v>
@@ -42879,10 +42893,10 @@
         <v>5.2</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-19.79</v>
+        <v>-19.84</v>
       </c>
       <c r="P411" s="4" t="n">
-        <v>-1.89</v>
+        <v>-1.94</v>
       </c>
       <c r="Q411" s="4" t="n">
         <v>-3.76</v>
@@ -42897,7 +42911,7 @@
       </c>
       <c r="V411" s="4" t="n"/>
       <c r="W411" s="5" t="n">
-        <v>31761</v>
+        <v>26823</v>
       </c>
       <c r="X411" s="5" t="n">
         <v>972561</v>
@@ -42910,10 +42924,10 @@
         <v>0</v>
       </c>
       <c r="AB411" s="4" t="n">
-        <v>40.11</v>
+        <v>40.08</v>
       </c>
       <c r="AC411" s="4" t="n">
-        <v>59.89</v>
+        <v>59.92</v>
       </c>
       <c r="AD411" s="4" t="n">
         <v>0</v>
@@ -42961,7 +42975,7 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="J412" s="4" t="n">
         <v>66.2</v>
@@ -43055,7 +43069,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Republican candidate (TX-16)</t>
+          <t>Adam Bauman</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -43152,7 +43166,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Democratic candidate (TX-17)</t>
+          <t>Casey Shepard</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -43171,13 +43185,13 @@
         </is>
       </c>
       <c r="I414" s="4" t="n">
-        <v>-14.98</v>
+        <v>-17.17</v>
       </c>
       <c r="J414" s="4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K414" s="4" t="n">
-        <v>99.3</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -43191,10 +43205,10 @@
         <v>5.2</v>
       </c>
       <c r="O414" s="4" t="n">
-        <v>-14.98</v>
+        <v>-17.17</v>
       </c>
       <c r="P414" s="4" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="Q414" s="4" t="n">
         <v>-3.99</v>
@@ -43209,7 +43223,7 @@
       </c>
       <c r="V414" s="4" t="n"/>
       <c r="W414" s="5" t="n">
-        <v>0</v>
+        <v>8801</v>
       </c>
       <c r="X414" s="5" t="n">
         <v>1050237</v>
@@ -43222,10 +43236,10 @@
         <v>0</v>
       </c>
       <c r="AB414" s="4" t="n">
-        <v>42.51</v>
+        <v>41.41</v>
       </c>
       <c r="AC414" s="4" t="n">
-        <v>57.49</v>
+        <v>58.59</v>
       </c>
       <c r="AD414" s="4" t="n">
         <v>0</v>
@@ -43259,7 +43273,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Republican candidate (TX-18)</t>
+          <t>Ronald Whitfield</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -43273,7 +43287,7 @@
         </is>
       </c>
       <c r="I415" s="4" t="n">
-        <v>70.95999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="J415" s="4" t="n">
         <v>100</v>
@@ -43293,7 +43307,7 @@
         <v>5.2</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>70.95999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="P415" s="4" t="n">
         <v>0</v>
@@ -43524,10 +43538,10 @@
         <v>0</v>
       </c>
       <c r="AB417" s="4" t="n">
-        <v>74.55</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="AC417" s="4" t="n">
-        <v>25.45</v>
+        <v>25.46</v>
       </c>
       <c r="AD417" s="4" t="n">
         <v>0</v>
@@ -43571,7 +43585,7 @@
         </is>
       </c>
       <c r="I418" s="4" t="n">
-        <v>-12.46</v>
+        <v>-12.47</v>
       </c>
       <c r="J418" s="4" t="n">
         <v>1.1</v>
@@ -43585,13 +43599,13 @@
         </is>
       </c>
       <c r="M418" s="4" t="n">
-        <v>-16.92</v>
+        <v>-16.93</v>
       </c>
       <c r="N418" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O418" s="4" t="n">
-        <v>-12.46</v>
+        <v>-12.47</v>
       </c>
       <c r="P418" s="4" t="n">
         <v>-2.06</v>
@@ -43683,7 +43697,7 @@
         </is>
       </c>
       <c r="M419" s="4" t="n">
-        <v>-17.5</v>
+        <v>-17.51</v>
       </c>
       <c r="N419" s="4" t="n">
         <v>5.2</v>
@@ -43856,12 +43870,12 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Democratic candidate (TX-24)</t>
+          <t>Kevin Burge</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Elizabeth Van Duyne</t>
+          <t>Beth Van Duyne</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -43875,13 +43889,13 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-11.11</v>
+        <v>-12.84</v>
       </c>
       <c r="J421" s="4" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="K421" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -43895,10 +43909,10 @@
         <v>5.2</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-11.11</v>
+        <v>-12.84</v>
       </c>
       <c r="P421" s="4" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="Q421" s="4" t="n">
         <v>-4.34</v>
@@ -43913,7 +43927,7 @@
       </c>
       <c r="V421" s="4" t="n"/>
       <c r="W421" s="5" t="n">
-        <v>0</v>
+        <v>209860</v>
       </c>
       <c r="X421" s="5" t="n">
         <v>2540738</v>
@@ -43926,10 +43940,10 @@
         <v>0</v>
       </c>
       <c r="AB421" s="4" t="n">
-        <v>44.45</v>
+        <v>43.58</v>
       </c>
       <c r="AC421" s="4" t="n">
-        <v>55.55</v>
+        <v>56.42</v>
       </c>
       <c r="AD421" s="4" t="n">
         <v>0</v>
@@ -44303,7 +44317,7 @@
         <v>5.2</v>
       </c>
       <c r="O425" s="4" t="n">
-        <v>19.98</v>
+        <v>19.97</v>
       </c>
       <c r="P425" s="4" t="n">
         <v>0.34</v>
@@ -44474,12 +44488,12 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Frederick Haynes</t>
+          <t>Frederick Haynes III</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Sholdon Daniels</t>
+          <t>Everett Jackson</t>
         </is>
       </c>
       <c r="G427" t="inlineStr"/>
@@ -44489,7 +44503,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>61.5</v>
+        <v>62.85</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -44509,10 +44523,10 @@
         <v>5.2</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>61.5</v>
+        <v>62.85</v>
       </c>
       <c r="P427" s="4" t="n">
-        <v>0.21</v>
+        <v>1.56</v>
       </c>
       <c r="Q427" s="4" t="n">
         <v>0</v>
@@ -44530,7 +44544,7 @@
         <v>420153</v>
       </c>
       <c r="X427" s="5" t="n">
-        <v>357415</v>
+        <v>17215</v>
       </c>
       <c r="Y427" t="inlineStr"/>
       <c r="Z427" s="4" t="n">
@@ -44540,10 +44554,10 @@
         <v>0</v>
       </c>
       <c r="AB427" s="4" t="n">
-        <v>80.75</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="AC427" s="4" t="n">
-        <v>19.25</v>
+        <v>18.57</v>
       </c>
       <c r="AD427" s="4" t="n">
         <v>0</v>
@@ -44591,7 +44605,7 @@
         </is>
       </c>
       <c r="I428" s="4" t="n">
-        <v>-18.93</v>
+        <v>-18.94</v>
       </c>
       <c r="J428" s="4" t="n">
         <v>0.3</v>
@@ -44801,7 +44815,7 @@
         </is>
       </c>
       <c r="M430" s="4" t="n">
-        <v>40.95</v>
+        <v>40.94</v>
       </c>
       <c r="N430" s="4" t="n">
         <v>5.2</v>
@@ -44838,10 +44852,10 @@
         <v>0</v>
       </c>
       <c r="AB430" s="4" t="n">
-        <v>72.98999999999999</v>
+        <v>72.98</v>
       </c>
       <c r="AC430" s="4" t="n">
-        <v>27.01</v>
+        <v>27.02</v>
       </c>
       <c r="AD430" s="4" t="n">
         <v>0</v>
@@ -44909,7 +44923,7 @@
         <v>5.2</v>
       </c>
       <c r="O431" s="4" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="P431" s="4" t="n">
         <v>0.14</v>
@@ -45183,7 +45197,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Lauren Pena</t>
+          <t>Lauren Peña</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -45197,7 +45211,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>71.04000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -45211,16 +45225,16 @@
         </is>
       </c>
       <c r="M434" s="4" t="n">
-        <v>63.57</v>
+        <v>63.56</v>
       </c>
       <c r="N434" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>71.04000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="P434" s="4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q434" s="4" t="n">
         <v>-0.07000000000000001</v>
@@ -45238,7 +45252,7 @@
         <v>1172881</v>
       </c>
       <c r="X434" s="5" t="n">
-        <v>117890</v>
+        <v>0</v>
       </c>
       <c r="Y434" t="inlineStr"/>
       <c r="Z434" s="4" t="n">
@@ -45248,10 +45262,10 @@
         <v>0</v>
       </c>
       <c r="AB434" s="4" t="n">
-        <v>85.52</v>
+        <v>84.77</v>
       </c>
       <c r="AC434" s="4" t="n">
-        <v>14.48</v>
+        <v>15.23</v>
       </c>
       <c r="AD434" s="4" t="n">
         <v>0</v>
@@ -45389,7 +45403,7 @@
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
-          <t>DEM</t>
+          <t>REP</t>
         </is>
       </c>
       <c r="I436" s="4" t="n">
@@ -45680,7 +45694,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Jonathan Larsen</t>
+          <t>Jonny Larsen</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -46202,7 +46216,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Thomas Perriello</t>
+          <t>Tom Perriello</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -48580,7 +48594,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Democratic candidate (WI-06)</t>
+          <t>Brad Smith</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -48599,13 +48613,13 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-17.34</v>
+        <v>-18.29</v>
       </c>
       <c r="J467" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K467" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="L467" t="inlineStr">
         <is>
@@ -48619,10 +48633,10 @@
         <v>5.2</v>
       </c>
       <c r="O467" s="4" t="n">
-        <v>-15.85</v>
+        <v>-16.99</v>
       </c>
       <c r="P467" s="4" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="Q467" s="4" t="n">
         <v>-4.83</v>
@@ -48643,7 +48657,7 @@
         <v>-25</v>
       </c>
       <c r="W467" s="5" t="n">
-        <v>0</v>
+        <v>166061</v>
       </c>
       <c r="X467" s="5" t="n">
         <v>929020</v>
@@ -48656,10 +48670,10 @@
         <v>0</v>
       </c>
       <c r="AB467" s="4" t="n">
-        <v>41.33</v>
+        <v>40.86</v>
       </c>
       <c r="AC467" s="4" t="n">
-        <v>58.67</v>
+        <v>59.14</v>
       </c>
       <c r="AD467" s="4" t="n">
         <v>0</v>
@@ -48990,7 +49004,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Ahsan Parsi</t>
+          <t>Ace Parsi</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -49209,13 +49223,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.8</v>
+        <v>-1.65</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>48.5</v>
+        <v>44.7</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>51.5</v>
+        <v>55.3</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49223,13 +49237,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.91</v>
+        <v>-12</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-2.26</v>
+        <v>-3.34</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.4</v>
@@ -49266,10 +49280,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.57</v>
+        <v>45.3</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.43</v>
+        <v>46.7</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>8</v>
@@ -50681,17 +50695,17 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>0.71</v>
+        <v>0.99</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>64.5</v>
+        <v>54</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>35.5</v>
+        <v>46</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>Lean D</t>
+          <t>Toss-up</t>
         </is>
       </c>
       <c r="M487" s="4" t="n">
@@ -50738,13 +50752,13 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>50.36</v>
+        <v>47.84</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>49.64</v>
+        <v>47.16</v>
       </c>
       <c r="AD487" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="488">
@@ -51105,7 +51119,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.3</v>
+        <v>-27.43</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51160,16 +51174,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.54</v>
+        <v>14.5</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>27.25</v>
+        <v>27.2</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>54.55</v>
+        <v>54.63</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51321,13 +51335,13 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-4.58</v>
+        <v>-5.33</v>
       </c>
       <c r="J493" s="4" t="n">
-        <v>20.7</v>
+        <v>18</v>
       </c>
       <c r="K493" s="4" t="n">
-        <v>79.3</v>
+        <v>82</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -51335,13 +51349,13 @@
         </is>
       </c>
       <c r="M493" s="4" t="n">
-        <v>-19.16</v>
+        <v>-20.13</v>
       </c>
       <c r="N493" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O493" s="4" t="n">
-        <v>-6.3</v>
+        <v>-7.28</v>
       </c>
       <c r="P493" s="4" t="n">
         <v>-0.5</v>
@@ -51376,16 +51390,16 @@
         </is>
       </c>
       <c r="Z493" s="4" t="n">
-        <v>47.71</v>
+        <v>47.34</v>
       </c>
       <c r="AA493" s="4" t="n">
-        <v>20.7</v>
+        <v>18</v>
       </c>
       <c r="AB493" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC493" s="4" t="n">
-        <v>52.29</v>
+        <v>52.66</v>
       </c>
       <c r="AD493" s="4" t="n">
         <v>0</v>
@@ -51761,7 +51775,7 @@
         <v>5.2</v>
       </c>
       <c r="O497" s="4" t="n">
-        <v>-1.97</v>
+        <v>-1.98</v>
       </c>
       <c r="P497" s="4" t="n">
         <v>0.57</v>
@@ -51845,7 +51859,7 @@
         </is>
       </c>
       <c r="I498" s="4" t="n">
-        <v>-30.8</v>
+        <v>-30.7</v>
       </c>
       <c r="J498" s="4" t="n">
         <v>0</v>
@@ -51859,13 +51873,13 @@
         </is>
       </c>
       <c r="M498" s="4" t="n">
-        <v>-33.89</v>
+        <v>-33.71</v>
       </c>
       <c r="N498" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O498" s="4" t="n">
-        <v>-35.63</v>
+        <v>-35.45</v>
       </c>
       <c r="P498" s="4" t="n">
         <v>-3.46</v>
@@ -51902,10 +51916,10 @@
         <v>0</v>
       </c>
       <c r="AB498" s="4" t="n">
-        <v>34.6</v>
+        <v>34.65</v>
       </c>
       <c r="AC498" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AD498" s="4" t="n">
         <v>0</v>
@@ -52149,7 +52163,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Generic Republican</t>
+          <t>Darline Graham</t>
         </is>
       </c>
       <c r="G501" t="inlineStr"/>
@@ -52159,13 +52173,13 @@
         </is>
       </c>
       <c r="I501" s="4" t="n">
-        <v>-7.56</v>
+        <v>-5.22</v>
       </c>
       <c r="J501" s="4" t="n">
-        <v>10.8</v>
+        <v>18.4</v>
       </c>
       <c r="K501" s="4" t="n">
-        <v>89.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -52179,10 +52193,10 @@
         <v>5.2</v>
       </c>
       <c r="O501" s="4" t="n">
-        <v>-6.64</v>
+        <v>-5.4</v>
       </c>
       <c r="P501" s="4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q501" s="4" t="n">
         <v>3.25</v>
@@ -52191,22 +52205,22 @@
         <v>-18.12</v>
       </c>
       <c r="S501" s="4" t="n">
-        <v>39</v>
+        <v>44.73</v>
       </c>
       <c r="T501" s="4" t="n">
-        <v>47</v>
+        <v>47.89</v>
       </c>
       <c r="U501" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V501" s="4" t="n">
-        <v>-11</v>
+        <v>-6.16</v>
       </c>
       <c r="W501" s="5" t="n">
         <v>10804040</v>
       </c>
       <c r="X501" s="5" t="n">
-        <v>0</v>
+        <v>346783</v>
       </c>
       <c r="Y501" t="inlineStr"/>
       <c r="Z501" s="4" t="n">
@@ -52216,10 +52230,10 @@
         <v>0</v>
       </c>
       <c r="AB501" s="4" t="n">
-        <v>45.35</v>
+        <v>46.5</v>
       </c>
       <c r="AC501" s="4" t="n">
-        <v>52.78</v>
+        <v>51.63</v>
       </c>
       <c r="AD501" s="4" t="n">
         <v>1.87</v>
@@ -52379,7 +52393,7 @@
         </is>
       </c>
       <c r="I503" s="4" t="n">
-        <v>-31.61</v>
+        <v>-31.45</v>
       </c>
       <c r="J503" s="4" t="n">
         <v>0</v>
@@ -52393,13 +52407,13 @@
         </is>
       </c>
       <c r="M503" s="4" t="n">
-        <v>-26.29</v>
+        <v>-26.13</v>
       </c>
       <c r="N503" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="O503" s="4" t="n">
-        <v>-31.61</v>
+        <v>-31.45</v>
       </c>
       <c r="P503" s="4" t="n">
         <v>-3.72</v>
@@ -52430,10 +52444,10 @@
         <v>0</v>
       </c>
       <c r="AB503" s="4" t="n">
-        <v>34.2</v>
+        <v>34.28</v>
       </c>
       <c r="AC503" s="4" t="n">
-        <v>65.8</v>
+        <v>65.72</v>
       </c>
       <c r="AD503" s="4" t="n">
         <v>0</v>
@@ -52477,7 +52491,7 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="J504" s="4" t="n">
         <v>66.2</v>
@@ -52497,10 +52511,10 @@
         <v>5.2</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>-0.43</v>
+        <v>-0.47</v>
       </c>
       <c r="P504" s="4" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q504" s="4" t="n">
         <v>2.05</v>
@@ -52534,10 +52548,10 @@
         <v>0</v>
       </c>
       <c r="AB504" s="4" t="n">
-        <v>49.55</v>
+        <v>49.54</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>48.44</v>
+        <v>48.45</v>
       </c>
       <c r="AD504" s="4" t="n">
         <v>2.01</v>
@@ -53001,19 +53015,19 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="K2" t="n">
         <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -53076,7 +53090,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -55169,7 +55183,7 @@
         <v>112</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -55691,7 +55705,7 @@
         <v>23</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -55969,7 +55983,7 @@
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="K53" t="n">
         <v>18</v>
@@ -55981,7 +55995,7 @@
         <v>22</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -56616,7 +56630,7 @@
         <v>7</v>
       </c>
       <c r="M64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0</v>
@@ -57013,10 +57027,10 @@
         </is>
       </c>
       <c r="J71" s="4" t="n">
-        <v>42.4</v>
+        <v>42.8</v>
       </c>
       <c r="K71" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L71" t="n">
         <v>30</v>
@@ -57025,7 +57039,7 @@
         <v>63</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generic ballot D+5.2 · House popular vote D+7.4</t>
+          <t>Generic ballot D+5.2 · House popular vote D+7.3</t>
         </is>
       </c>
     </row>
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="C8" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="D8" t="n">
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>52.2</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="C10" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="D10" t="n">
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-8.98</v>
+        <v>-2.85</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>24.8</v>
+        <v>25.9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>75.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -970,13 +970,13 @@
         <v>0</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>41.81</v>
+        <v>45.45</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>50.19</v>
+        <v>54.55</v>
       </c>
       <c r="AD2" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21.46</v>
+        <v>20.56</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.8</v>
@@ -3920,18 +3920,22 @@
       <c r="X30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Ken Block</t>
+        </is>
+      </c>
       <c r="Z30" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>60.73</v>
+        <v>49.43</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>39.27</v>
+        <v>32.57</v>
       </c>
       <c r="AD30" s="4" t="n">
         <v>0</v>
@@ -4711,13 +4715,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-6.6</v>
+        <v>-5.63</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>31.9</v>
+        <v>25</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4725,16 +4729,16 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-9.84</v>
+        <v>-2.46</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-7.34</v>
+        <v>-1</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="Q38" s="4" t="n">
         <v>-1.67</v>
@@ -4743,16 +4747,16 @@
         <v>-13.8</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>39.51</v>
+        <v>36.81</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>46.77</v>
+        <v>48.68</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>-10.25</v>
+        <v>-13.29</v>
       </c>
       <c r="W38" s="5" t="n">
         <v>0</v>
@@ -4766,19 +4770,19 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>9.220000000000001</v>
+        <v>43.61</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>40.6</v>
+        <v>6.5</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>48.18</v>
+        <v>49.89</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -24725,7 +24729,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>30.61</v>
+        <v>30.89</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>100</v>
@@ -24739,13 +24743,13 @@
         </is>
       </c>
       <c r="M234" s="4" t="n">
-        <v>21.81</v>
+        <v>21.83</v>
       </c>
       <c r="N234" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O234" s="4" t="n">
-        <v>30.87</v>
+        <v>30.89</v>
       </c>
       <c r="P234" s="4" t="n">
         <v>1</v>
@@ -24776,13 +24780,13 @@
         <v>0</v>
       </c>
       <c r="AB234" s="4" t="n">
-        <v>62.16</v>
+        <v>65.44</v>
       </c>
       <c r="AC234" s="4" t="n">
-        <v>32.84</v>
+        <v>34.56</v>
       </c>
       <c r="AD234" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -24823,27 +24827,27 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>-3.78</v>
+        <v>-4.66</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>39.1</v>
+        <v>20.2</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>60.9</v>
+        <v>79.8</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-9.33</v>
+        <v>-9.32</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.58</v>
+        <v>-5.56</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.48</v>
@@ -24880,13 +24884,13 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>45.28</v>
+        <v>47.67</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>49.72</v>
+        <v>52.33</v>
       </c>
       <c r="AD235" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -28309,13 +28313,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-7.35</v>
+        <v>-7.42</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28323,13 +28327,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.64</v>
+        <v>-12.73</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28366,10 +28370,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.32</v>
+        <v>46.29</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.68</v>
+        <v>53.71</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28417,7 +28421,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-34.27</v>
+        <v>-34.36</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28431,13 +28435,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.6</v>
+        <v>-31.69</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-34.27</v>
+        <v>-34.36</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28468,10 +28472,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>32.86</v>
+        <v>32.82</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>67.14</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -39643,7 +39647,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>40.99</v>
+        <v>40.79</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>100</v>
@@ -39657,13 +39661,13 @@
         </is>
       </c>
       <c r="M379" s="4" t="n">
-        <v>27.61</v>
+        <v>27.41</v>
       </c>
       <c r="N379" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O379" s="4" t="n">
-        <v>40.99</v>
+        <v>40.79</v>
       </c>
       <c r="P379" s="4" t="n">
         <v>0</v>
@@ -39694,10 +39698,10 @@
         <v>0</v>
       </c>
       <c r="AB379" s="4" t="n">
-        <v>70.5</v>
+        <v>70.39</v>
       </c>
       <c r="AC379" s="4" t="n">
-        <v>29.5</v>
+        <v>29.61</v>
       </c>
       <c r="AD379" s="4" t="n">
         <v>0</v>
@@ -39745,7 +39749,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>17.69</v>
+        <v>17.48</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39759,13 +39763,13 @@
         </is>
       </c>
       <c r="M380" s="4" t="n">
-        <v>11.75</v>
+        <v>11.55</v>
       </c>
       <c r="N380" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>17.69</v>
+        <v>17.48</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.63</v>
@@ -39796,10 +39800,10 @@
         <v>0</v>
       </c>
       <c r="AB380" s="4" t="n">
-        <v>58.84</v>
+        <v>58.74</v>
       </c>
       <c r="AC380" s="4" t="n">
-        <v>41.16</v>
+        <v>41.26</v>
       </c>
       <c r="AD380" s="4" t="n">
         <v>0</v>
@@ -49229,27 +49233,27 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-1.45</v>
+        <v>-0.7</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>46.4</v>
+        <v>35.6</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>53.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-12.07</v>
+        <v>-10.53</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-3.37</v>
+        <v>-1.84</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.42</v>
@@ -49286,13 +49290,13 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>45.29</v>
+        <v>48.4</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>46.71</v>
+        <v>49.1</v>
       </c>
       <c r="AD473" s="4" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="474">
@@ -50701,17 +50705,17 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>51.1</v>
+        <v>64.5</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>48.9</v>
+        <v>35.5</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>Toss-up</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M487" s="4" t="n">
@@ -50758,13 +50762,13 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>47.83</v>
+        <v>50.35</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>47.17</v>
+        <v>49.65</v>
       </c>
       <c r="AD487" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -51125,13 +51129,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.3</v>
+        <v>-27.66</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51180,16 +51184,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>14.52</v>
+        <v>22.37</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>27.26</v>
+        <v>23.16</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>54.56</v>
+        <v>50.82</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -52075,7 +52079,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>23.46</v>
+        <v>23.33</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -52089,13 +52093,13 @@
         </is>
       </c>
       <c r="M500" s="4" t="n">
-        <v>17.58</v>
+        <v>17.35</v>
       </c>
       <c r="N500" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O500" s="4" t="n">
-        <v>26.3</v>
+        <v>26.07</v>
       </c>
       <c r="P500" s="4" t="n">
         <v>2.03</v>
@@ -52132,10 +52136,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.73</v>
+        <v>61.67</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.27</v>
+        <v>38.33</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -53021,19 +53025,19 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
         <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -53096,7 +53100,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -55177,13 +55181,13 @@
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K39" t="n">
         <v>83</v>
       </c>
       <c r="L39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M39" t="n">
         <v>110</v>
@@ -55247,7 +55251,7 @@
         <v>29</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>87.2</v>
+        <v>87.3</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -55653,7 +55657,7 @@
         <v>52</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -55699,7 +55703,7 @@
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="K48" t="n">
         <v>19</v>
@@ -56917,7 +56921,7 @@
         </is>
       </c>
       <c r="J69" s="4" t="n">
-        <v>62.1</v>
+        <v>61.9</v>
       </c>
       <c r="K69" t="n">
         <v>64</v>
@@ -56929,7 +56933,7 @@
         <v>74</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -56975,7 +56979,7 @@
         </is>
       </c>
       <c r="J70" s="4" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="K70" t="n">
         <v>33</v>
@@ -56987,7 +56991,7 @@
         <v>38</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="C8" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="D8" t="n">
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>54.3</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="C10" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="D10" t="n">
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>54.9</v>
+        <v>54.3</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -922,10 +922,10 @@
         <v>-2.85</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>74.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4718,10 +4718,10 @@
         <v>-5.63</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43.61</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>6.5</v>
@@ -18527,7 +18527,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-27.74</v>
+        <v>-29.97</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18541,13 +18541,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-41.19</v>
+        <v>-44.8</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-38.65</v>
+        <v>-42.26</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18584,10 +18584,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>36.13</v>
+        <v>35.02</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>63.87</v>
+        <v>64.98</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18635,13 +18635,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-25.29</v>
+        <v>-28.9</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -18649,13 +18649,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-23.37</v>
+        <v>-26.98</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-25.29</v>
+        <v>-28.9</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -18686,10 +18686,10 @@
         <v>0</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>37.36</v>
+        <v>35.55</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>62.64</v>
+        <v>64.45</v>
       </c>
       <c r="AD174" s="4" t="n">
         <v>0</v>
@@ -24830,10 +24830,10 @@
         <v>-4.66</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>79.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -28313,13 +28313,13 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>-7.42</v>
+        <v>-6.08</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>11.2</v>
+        <v>15.5</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>88.8</v>
+        <v>84.5</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28327,13 +28327,13 @@
         </is>
       </c>
       <c r="M269" s="4" t="n">
-        <v>-12.73</v>
+        <v>-10.96</v>
       </c>
       <c r="N269" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O269" s="4" t="n">
-        <v>-8.630000000000001</v>
+        <v>-6.86</v>
       </c>
       <c r="P269" s="4" t="n">
         <v>-0.14</v>
@@ -28370,10 +28370,10 @@
         <v>0</v>
       </c>
       <c r="AB269" s="4" t="n">
-        <v>46.29</v>
+        <v>46.96</v>
       </c>
       <c r="AC269" s="4" t="n">
-        <v>53.71</v>
+        <v>53.04</v>
       </c>
       <c r="AD269" s="4" t="n">
         <v>0</v>
@@ -28421,7 +28421,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>-34.36</v>
+        <v>-32.59</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>0</v>
@@ -28435,13 +28435,13 @@
         </is>
       </c>
       <c r="M270" s="4" t="n">
-        <v>-31.69</v>
+        <v>-29.92</v>
       </c>
       <c r="N270" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O270" s="4" t="n">
-        <v>-34.36</v>
+        <v>-32.59</v>
       </c>
       <c r="P270" s="4" t="n">
         <v>-2.59</v>
@@ -28472,10 +28472,10 @@
         <v>0</v>
       </c>
       <c r="AB270" s="4" t="n">
-        <v>32.82</v>
+        <v>33.7</v>
       </c>
       <c r="AC270" s="4" t="n">
-        <v>67.18000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="AD270" s="4" t="n">
         <v>0</v>
@@ -30067,13 +30067,13 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>-10.22</v>
+        <v>-12.68</v>
       </c>
       <c r="J286" s="4" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="K286" s="4" t="n">
-        <v>96.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="M286" s="4" t="n">
-        <v>-9.529999999999999</v>
+        <v>-12.41</v>
       </c>
       <c r="N286" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O286" s="4" t="n">
-        <v>-10.79</v>
+        <v>-13.68</v>
       </c>
       <c r="P286" s="4" t="n">
         <v>-0.99</v>
@@ -30124,10 +30124,10 @@
         <v>0</v>
       </c>
       <c r="AB286" s="4" t="n">
-        <v>44.89</v>
+        <v>43.66</v>
       </c>
       <c r="AC286" s="4" t="n">
-        <v>55.11</v>
+        <v>56.34</v>
       </c>
       <c r="AD286" s="4" t="n">
         <v>0</v>
@@ -30171,27 +30171,27 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>12.04</v>
+        <v>9.58</v>
       </c>
       <c r="J287" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="K287" s="4" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>Safe D</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="M287" s="4" t="n">
-        <v>8.33</v>
+        <v>5.45</v>
       </c>
       <c r="N287" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O287" s="4" t="n">
-        <v>13.63</v>
+        <v>10.74</v>
       </c>
       <c r="P287" s="4" t="n">
         <v>0.43</v>
@@ -30228,10 +30228,10 @@
         <v>0</v>
       </c>
       <c r="AB287" s="4" t="n">
-        <v>56.02</v>
+        <v>54.79</v>
       </c>
       <c r="AC287" s="4" t="n">
-        <v>43.98</v>
+        <v>45.21</v>
       </c>
       <c r="AD287" s="4" t="n">
         <v>0</v>
@@ -30279,7 +30279,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>-53.34</v>
+        <v>-56.22</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>0</v>
@@ -30293,13 +30293,13 @@
         </is>
       </c>
       <c r="M288" s="4" t="n">
-        <v>-50.48</v>
+        <v>-53.36</v>
       </c>
       <c r="N288" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O288" s="4" t="n">
-        <v>-53.34</v>
+        <v>-56.22</v>
       </c>
       <c r="P288" s="4" t="n">
         <v>-2.18</v>
@@ -30330,10 +30330,10 @@
         <v>0</v>
       </c>
       <c r="AB288" s="4" t="n">
-        <v>23.33</v>
+        <v>21.89</v>
       </c>
       <c r="AC288" s="4" t="n">
-        <v>76.67</v>
+        <v>78.11</v>
       </c>
       <c r="AD288" s="4" t="n">
         <v>0</v>
@@ -40565,7 +40565,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>-23.81</v>
+        <v>-25.36</v>
       </c>
       <c r="J388" s="4" t="n">
         <v>0.1</v>
@@ -40579,13 +40579,13 @@
         </is>
       </c>
       <c r="M388" s="4" t="n">
-        <v>-26.82</v>
+        <v>-28.37</v>
       </c>
       <c r="N388" s="4" t="n">
         <v>5.23</v>
       </c>
       <c r="O388" s="4" t="n">
-        <v>-23.81</v>
+        <v>-25.36</v>
       </c>
       <c r="P388" s="4" t="n">
         <v>-1.2</v>
@@ -40616,10 +40616,10 @@
         <v>0</v>
       </c>
       <c r="AB388" s="4" t="n">
-        <v>38.1</v>
+        <v>37.32</v>
       </c>
       <c r="AC388" s="4" t="n">
-        <v>61.9</v>
+        <v>62.68</v>
       </c>
       <c r="AD388" s="4" t="n">
         <v>0</v>
@@ -49236,10 +49236,10 @@
         <v>-0.7</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>35.6</v>
+        <v>36.5</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -51129,13 +51129,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.66</v>
+        <v>-27.74</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51184,16 +51184,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>22.37</v>
+        <v>22.38</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>23.16</v>
+        <v>23.11</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>50.82</v>
+        <v>50.85</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="C8" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>54.9</v>
+        <v>60.7</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233.1</v>
+        <v>233</v>
       </c>
       <c r="C9" t="n">
-        <v>201.9</v>
+        <v>202</v>
       </c>
       <c r="D9" t="n">
         <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25.5</v>
+        <v>26.1</v>
       </c>
       <c r="C10" t="n">
-        <v>24.5</v>
+        <v>23.9</v>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>54.9</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-2.84</v>
+        <v>6.53</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>25.9</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>74.09999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-5.78</v>
+        <v>-5.12</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>75</v>
+        <v>74.3</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-2.46</v>
+        <v>-0.2</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-0.98</v>
+        <v>1.28</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.03</v>
@@ -4753,16 +4753,16 @@
         <v>-13.8</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>37.92</v>
+        <v>36.81</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>49.61</v>
+        <v>48.68</v>
       </c>
       <c r="U38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>-12.42</v>
+        <v>-13.29</v>
       </c>
       <c r="W38" s="5" t="n">
         <v>0</v>
@@ -4776,16 +4776,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>43.54</v>
+        <v>45.54</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>49.96</v>
+        <v>50.66</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -24842,10 +24842,10 @@
         <v>-4.6</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>20.2</v>
+        <v>20.9</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>79.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -49263,27 +49263,27 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.71</v>
+        <v>1.24</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>35.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>33.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-10.53</v>
+        <v>-8.19</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-1.84</v>
+        <v>0.5</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.4</v>
@@ -49320,10 +49320,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>48.4</v>
+        <v>49.03</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>49.1</v>
+        <v>48.47</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>2.5</v>
@@ -50738,10 +50738,10 @@
         <v>1.16</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.9</v>
+        <v>33.6</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.84</v>
+        <v>-27.63</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51214,16 +51214,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>22.34</v>
+        <v>22.33</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>23.08</v>
+        <v>23.19</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>50.92</v>
+        <v>50.82</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -53055,7 +53055,7 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="K2" t="n">
         <v>17</v>
@@ -53067,7 +53067,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>41</v>
       </c>
       <c r="L47" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M47" t="n">
         <v>52</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
         <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>60.7</v>
+        <v>62.5</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>232.7</v>
       </c>
       <c r="C9" t="n">
-        <v>202</v>
+        <v>202.3</v>
       </c>
       <c r="D9" t="n">
         <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="C10" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D10" t="n">
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>67.2</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,17 +919,17 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>6.53</v>
+        <v>22.83</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>13.9</v>
+        <v>0.8</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Likely D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="M2" s="4" t="n">
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-5.12</v>
+        <v>-1.19</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>25.7</v>
+        <v>33.5</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>74.3</v>
+        <v>66.5</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-0.2</v>
+        <v>1.86</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>1.28</v>
+        <v>3.34</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.03</v>
@@ -4776,16 +4776,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>45.54</v>
+        <v>45.22</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>25.7</v>
+        <v>33.5</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>50.66</v>
+        <v>49.18</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -24842,10 +24842,10 @@
         <v>-4.6</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>33.1</v>
+        <v>27.9</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-8.19</v>
+        <v>-5.92</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>0.5</v>
+        <v>2.77</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.4</v>
@@ -49320,10 +49320,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>49.03</v>
+        <v>49.64</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>48.47</v>
+        <v>47.86</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>2.5</v>
@@ -50738,10 +50738,10 @@
         <v>1.16</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.63</v>
+        <v>-27.69</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51214,16 +51214,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>22.33</v>
+        <v>22.29</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>23.19</v>
+        <v>23.18</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>50.82</v>
+        <v>50.87</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>62.5</v>
+        <v>62.1</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.7</v>
+        <v>233</v>
       </c>
       <c r="C9" t="n">
-        <v>202.3</v>
+        <v>202</v>
       </c>
       <c r="D9" t="n">
         <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>81.2</v>
+        <v>82</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>22.83</v>
+        <v>11.7</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>99.2</v>
+        <v>98.7</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-1.19</v>
+        <v>-1.65</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>66.5</v>
+        <v>68.5</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>1.86</v>
+        <v>0.98</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>3.34</v>
+        <v>2.46</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.03</v>
@@ -4776,16 +4776,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>45.22</v>
+        <v>44.99</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>49.18</v>
+        <v>49.41</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>0</v>
@@ -49263,13 +49263,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>2.47</v>
+        <v>1.94</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49277,13 +49277,13 @@
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-5.92</v>
+        <v>-6.9</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>2.77</v>
+        <v>1.79</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.4</v>
@@ -49320,10 +49320,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>49.64</v>
+        <v>49.38</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>47.86</v>
+        <v>48.12</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>2.5</v>
@@ -50738,10 +50738,10 @@
         <v>1.16</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.69</v>
+        <v>-27.7</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51214,16 +51214,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>22.29</v>
+        <v>22.27</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>23.18</v>
+        <v>23.19</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>50.87</v>
+        <v>50.88</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="D8" t="n">
         <v>51</v>
       </c>
-      <c r="C8" t="n">
-        <v>49</v>
-      </c>
-      <c r="D8" t="n">
-        <v>52</v>
-      </c>
       <c r="E8" t="n">
-        <v>62.1</v>
+        <v>55.4</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>232.6</v>
       </c>
       <c r="C9" t="n">
-        <v>202</v>
+        <v>202.4</v>
       </c>
       <c r="D9" t="n">
         <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="C10" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="D10" t="n">
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>67.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4721,27 +4721,27 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-1.65</v>
+        <v>-5.1</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>31.5</v>
+        <v>17.8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>68.5</v>
+        <v>82.2</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.98</v>
+        <v>-3.88</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>2.46</v>
+        <v>-2.4</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>-1.03</v>
@@ -4776,19 +4776,19 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>44.99</v>
+        <v>44.02</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>31.5</v>
+        <v>17.8</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>49.41</v>
+        <v>50.98</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="39">
@@ -24842,10 +24842,10 @@
         <v>-4.6</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>79.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -49263,27 +49263,27 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>1.94</v>
+        <v>-0.73</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>70.7</v>
+        <v>36.9</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>29.3</v>
+        <v>63.1</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>Lean D</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M473" s="4" t="n">
-        <v>-6.9</v>
+        <v>-12.1</v>
       </c>
       <c r="N473" s="4" t="n">
         <v>5.24</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>1.79</v>
+        <v>-3.41</v>
       </c>
       <c r="P473" s="4" t="n">
         <v>0.4</v>
@@ -49320,10 +49320,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>49.38</v>
+        <v>47.97</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>48.12</v>
+        <v>49.53</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>2.5</v>
@@ -50738,10 +50738,10 @@
         <v>1.16</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.7</v>
+        <v>-27.75</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51214,16 +51214,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>22.27</v>
+        <v>22.35</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>23.19</v>
+        <v>23.12</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>50.88</v>
+        <v>50.87</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -53055,19 +53055,19 @@
         </is>
       </c>
       <c r="J2" s="4" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="K2" t="n">
         <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>21</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="K3" t="n">
         <v>9</v>
@@ -53130,7 +53130,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -550,7 +550,7 @@
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>54.9</v>
+        <v>55.7</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.6</v>
+        <v>232.3</v>
       </c>
       <c r="C9" t="n">
-        <v>202.4</v>
+        <v>202.7</v>
       </c>
       <c r="D9" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>81.3</v>
+        <v>80.7</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>66.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -4724,10 +4724,10 @@
         <v>-4.89</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44.12</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>3.8</v>
@@ -14433,17 +14433,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>0.36</v>
+        <v>-1.47</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>63.2</v>
+        <v>32.5</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>36.8</v>
+        <v>67.5</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Lean D</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="M133" s="4" t="n">
@@ -14464,12 +14464,18 @@
       <c r="R133" s="4" t="n">
         <v>-17.93</v>
       </c>
-      <c r="S133" s="4" t="n"/>
-      <c r="T133" s="4" t="n"/>
+      <c r="S133" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="T133" s="4" t="n">
+        <v>41</v>
+      </c>
       <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V133" s="4" t="n">
+        <v>-3</v>
+      </c>
       <c r="W133" s="5" t="n">
         <v>2157834</v>
       </c>
@@ -14484,10 +14490,10 @@
         <v>0</v>
       </c>
       <c r="AB133" s="4" t="n">
-        <v>50.18</v>
+        <v>49.26</v>
       </c>
       <c r="AC133" s="4" t="n">
-        <v>49.82</v>
+        <v>50.74</v>
       </c>
       <c r="AD133" s="4" t="n">
         <v>0</v>
@@ -15157,13 +15163,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>-5.02</v>
+        <v>-3.4</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>19.1</v>
+        <v>25</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>80.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -15188,12 +15194,18 @@
       <c r="R140" s="4" t="n">
         <v>-13.81</v>
       </c>
-      <c r="S140" s="4" t="n"/>
-      <c r="T140" s="4" t="n"/>
+      <c r="S140" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="T140" s="4" t="n">
+        <v>39</v>
+      </c>
       <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="V140" s="4" t="n">
+        <v>-2</v>
+      </c>
       <c r="W140" s="5" t="n">
         <v>296507</v>
       </c>
@@ -15208,10 +15220,10 @@
         <v>0</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>47.49</v>
+        <v>48.3</v>
       </c>
       <c r="AC140" s="4" t="n">
-        <v>52.51</v>
+        <v>51.7</v>
       </c>
       <c r="AD140" s="4" t="n">
         <v>0</v>
@@ -24842,10 +24854,10 @@
         <v>-4.59</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -49272,10 +49284,10 @@
         <v>-0.54</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>63.2</v>
+        <v>63.5</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -50744,10 +50756,10 @@
         <v>1.1</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.5</v>
+        <v>33.9</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -51165,13 +51177,13 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.84</v>
+        <v>-27.91</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K491" s="4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -51220,16 +51232,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>22.27</v>
+        <v>22.29</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>23.12</v>
+        <v>23.07</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>50.96</v>
+        <v>50.98</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>

--- a/output/nowcast.xlsx
+++ b/output/nowcast.xlsx
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data as of 2026-09-04 · evaluated at 0 days to election (actual: 60 days out)</t>
+          <t>Data as of 2026-09-05 · evaluated at 0 days to election (actual: 59 days out)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>230</v>
       </c>
       <c r="E9" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="F9" t="n">
         <v>218</v>
@@ -600,7 +600,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>66.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -922,10 +922,10 @@
         <v>11.74</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-18.29</v>
+        <v>-18.32</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.3</v>
@@ -1074,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>40.85</v>
+        <v>40.84</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>59.15</v>
+        <v>59.16</v>
       </c>
       <c r="AD3" s="4" t="n">
         <v>0</v>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-17.71</v>
+        <v>-17.85</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0.4</v>
@@ -1182,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>41.14</v>
+        <v>41.07</v>
       </c>
       <c r="AC4" s="4" t="n">
-        <v>58.86</v>
+        <v>58.93</v>
       </c>
       <c r="AD4" s="4" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>93</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26.18</v>
+        <v>26.21</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>100</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>63.09</v>
+        <v>63.1</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>36.91</v>
+        <v>36.9</v>
       </c>
       <c r="AD6" s="4" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>18.48</v>
+        <v>18.5</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>99.7</v>
@@ -1610,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>59.24</v>
+        <v>59.25</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>40.76</v>
+        <v>40.75</v>
       </c>
       <c r="AD8" s="4" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>80.2</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-38.94</v>
+        <v>-39.05</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>30.53</v>
+        <v>30.48</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>69.47</v>
+        <v>69.52</v>
       </c>
       <c r="AD13" s="4" t="n">
         <v>0</v>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.53</v>
+        <v>-7.6</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
         <v>0</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>46.23</v>
+        <v>46.2</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>53.77</v>
+        <v>53.8</v>
       </c>
       <c r="AD15" s="4" t="n">
         <v>0</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>28.29</v>
+        <v>28.32</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>100</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>64.14</v>
+        <v>64.16</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>35.86</v>
+        <v>35.84</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>33.92</v>
+        <v>34</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>100</v>
@@ -2560,10 +2560,10 @@
         <v>0</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>66.95999999999999</v>
+        <v>67</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>33.04</v>
+        <v>33</v>
       </c>
       <c r="AD17" s="4" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>97.40000000000001</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.46</v>
+        <v>12.45</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>98.90000000000001</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-11.42</v>
+        <v>-11.48</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>1.3</v>
@@ -3055,10 +3055,10 @@
         <v>5.28</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-13.05</v>
+        <v>-13.13</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.31</v>
+        <v>-1.39</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>-19.79</v>
@@ -3079,10 +3079,10 @@
         <v>-9.5</v>
       </c>
       <c r="W22" s="5" t="n">
-        <v>606192</v>
+        <v>908163</v>
       </c>
       <c r="X22" s="5" t="n">
-        <v>3694856</v>
+        <v>6079166</v>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" s="4" t="n">
@@ -3092,10 +3092,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>44.29</v>
+        <v>44.26</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>55.71</v>
+        <v>55.74</v>
       </c>
       <c r="AD22" s="4" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>95.7</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3304,10 +3304,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>50.38</v>
+        <v>50.39</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>49.62</v>
+        <v>49.61</v>
       </c>
       <c r="AD24" s="4" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.63</v>
+        <v>-3.64</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>24.1</v>
@@ -3516,10 +3516,10 @@
         <v>0</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>48.19</v>
+        <v>48.18</v>
       </c>
       <c r="AC26" s="4" t="n">
-        <v>51.81</v>
+        <v>51.82</v>
       </c>
       <c r="AD26" s="4" t="n">
         <v>0</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>80.7</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>20.5</v>
+        <v>20.49</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>99.8</v>
@@ -3938,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>49.41</v>
+        <v>49.4</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>32.59</v>
+        <v>32.6</v>
       </c>
       <c r="AD30" s="4" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-16.26</v>
+        <v>-16.28</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>0.5</v>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.99</v>
+        <v>-7.01</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>12.5</v>
@@ -4360,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>46.5</v>
+        <v>46.49</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>53.5</v>
+        <v>53.51</v>
       </c>
       <c r="AD34" s="4" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-21.09</v>
+        <v>-21.13</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>0.2</v>
@@ -4468,10 +4468,10 @@
         <v>0</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>39.46</v>
+        <v>39.44</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>60.54</v>
+        <v>60.56</v>
       </c>
       <c r="AD35" s="4" t="n">
         <v>0</v>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>-4.89</v>
+        <v>-4.85</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -4776,16 +4776,16 @@
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>44.12</v>
+        <v>44.14</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="AB38" s="4" t="n">
         <v>3.8</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>50.88</v>
+        <v>50.86</v>
       </c>
       <c r="AD38" s="4" t="n">
         <v>1.2</v>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-27.52</v>
+        <v>-27.53</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>0</v>
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-30.5</v>
+        <v>-30.51</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-27.52</v>
+        <v>-27.53</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>-1.75</v>
@@ -4880,10 +4880,10 @@
         <v>0</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>36.24</v>
+        <v>36.23</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>63.76</v>
+        <v>63.77</v>
       </c>
       <c r="AD39" s="4" t="n">
         <v>0</v>
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-8.710000000000001</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-1.68</v>
+        <v>-1.69</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>-0.45</v>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>-40.49</v>
+        <v>-40.5</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>0</v>
@@ -5053,13 +5053,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-41.26</v>
+        <v>-41.27</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-40.49</v>
+        <v>-40.5</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>-2.23</v>
@@ -5090,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>29.76</v>
+        <v>29.75</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>70.23999999999999</v>
+        <v>70.25</v>
       </c>
       <c r="AD41" s="4" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>-60.67</v>
+        <v>-60.68</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>0</v>
@@ -5155,13 +5155,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-61.51</v>
+        <v>-61.52</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-60.67</v>
+        <v>-60.68</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>-2.1</v>
@@ -5192,10 +5192,10 @@
         <v>0</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>19.67</v>
+        <v>19.66</v>
       </c>
       <c r="AC42" s="4" t="n">
-        <v>80.33</v>
+        <v>80.34</v>
       </c>
       <c r="AD42" s="4" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-22.59</v>
+        <v>-22.6</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>0.1</v>
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-25.06</v>
+        <v>-25.07</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-22.59</v>
+        <v>-22.6</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>-0.59</v>
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>-30.29</v>
+        <v>-30.3</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>0</v>
@@ -5359,13 +5359,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-30.58</v>
+        <v>-30.59</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-30.29</v>
+        <v>-30.3</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>-2.26</v>
@@ -5396,10 +5396,10 @@
         <v>0</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>34.86</v>
+        <v>34.85</v>
       </c>
       <c r="AC44" s="4" t="n">
-        <v>65.14</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="AD44" s="4" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>34.86</v>
+        <v>34.85</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>100</v>
@@ -5461,13 +5461,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>23.66</v>
+        <v>23.65</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>34.86</v>
+        <v>34.85</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>1.73</v>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>-40.48</v>
+        <v>-40.53</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>0</v>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>-39.18</v>
+        <v>-39.23</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>-40.48</v>
+        <v>-40.53</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>-1.62</v>
@@ -5600,10 +5600,10 @@
         <v>0</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>29.76</v>
+        <v>29.74</v>
       </c>
       <c r="AC46" s="4" t="n">
-        <v>70.23999999999999</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="AD46" s="4" t="n">
         <v>0</v>
@@ -5651,13 +5651,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>-4.1</v>
+        <v>-4.16</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -5665,13 +5665,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-9.98</v>
+        <v>-10.03</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>-7.33</v>
+        <v>-7.38</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>-0.99</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>47.95</v>
+        <v>47.92</v>
       </c>
       <c r="AC47" s="4" t="n">
-        <v>52.05</v>
+        <v>52.08</v>
       </c>
       <c r="AD47" s="4" t="n">
         <v>0</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>-23.34</v>
+        <v>-23.39</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>0.1</v>
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>-20.17</v>
+        <v>-20.22</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-23.34</v>
+        <v>-23.39</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>-1.82</v>
@@ -5810,10 +5810,10 @@
         <v>0</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>38.33</v>
+        <v>38.31</v>
       </c>
       <c r="AC48" s="4" t="n">
-        <v>61.67</v>
+        <v>61.69</v>
       </c>
       <c r="AD48" s="4" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>-36.6</v>
+        <v>-36.64</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>0</v>
@@ -5875,13 +5875,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>-33.54</v>
+        <v>-33.59</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>-36.6</v>
+        <v>-36.64</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>-2.88</v>
@@ -5912,10 +5912,10 @@
         <v>0</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>31.7</v>
+        <v>31.68</v>
       </c>
       <c r="AC49" s="4" t="n">
-        <v>68.3</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="AD49" s="4" t="n">
         <v>0</v>
@@ -5973,13 +5973,13 @@
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>-0.49</v>
@@ -6067,13 +6067,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.87</v>
+        <v>-0.84</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6124,10 +6124,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>49.56</v>
+        <v>49.58</v>
       </c>
       <c r="AC51" s="4" t="n">
-        <v>50.44</v>
+        <v>50.42</v>
       </c>
       <c r="AD51" s="4" t="n">
         <v>0</v>
@@ -6426,10 +6426,10 @@
         <v>0</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>43.83</v>
+        <v>43.82</v>
       </c>
       <c r="AC54" s="4" t="n">
-        <v>56.17</v>
+        <v>56.18</v>
       </c>
       <c r="AD54" s="4" t="n">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>-12.48</v>
+        <v>-12.49</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>5.28</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>-22.51</v>
+        <v>-22.52</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>0.1</v>
@@ -6809,7 +6809,7 @@
         <v>5.28</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>-22.51</v>
+        <v>-22.52</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>-0.33</v>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>5.28</v>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>33.31</v>
+        <v>33.32</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>100</v>
@@ -7007,13 +7007,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>27.68</v>
+        <v>27.69</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33.31</v>
+        <v>33.32</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>21.12</v>
+        <v>21.13</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>99.8</v>
@@ -7115,7 +7115,7 @@
         <v>5.28</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>21.12</v>
+        <v>21.13</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>1.08</v>
@@ -7211,13 +7211,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>18.13</v>
+        <v>18.14</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>26.54</v>
+        <v>26.55</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>-18.24</v>
+        <v>-18.23</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0.3</v>
@@ -7319,7 +7319,7 @@
         <v>5.28</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>-18.24</v>
+        <v>-18.23</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>-0.65</v>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12.39</v>
+        <v>12.4</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>98.90000000000001</v>
@@ -7415,13 +7415,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>11.1</v>
+        <v>11.11</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>12.39</v>
+        <v>12.4</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>-0.35</v>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>39.03</v>
+        <v>39.04</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>5.28</v>
@@ -7652,10 +7652,10 @@
         <v>0</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>74.48</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AC66" s="4" t="n">
-        <v>25.52</v>
+        <v>25.51</v>
       </c>
       <c r="AD66" s="4" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>30.7</v>
+        <v>30.71</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>100</v>
@@ -7723,7 +7723,7 @@
         <v>5.28</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>30.7</v>
+        <v>30.71</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>2.78</v>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>42.87</v>
+        <v>42.88</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>100</v>
@@ -7825,7 +7825,7 @@
         <v>5.28</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>42.87</v>
+        <v>42.88</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
@@ -7917,13 +7917,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>73.89</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>78.86</v>
+        <v>78.87</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21.59</v>
+        <v>21.6</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>99.8</v>
@@ -8127,7 +8127,7 @@
         <v>5.28</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>21.59</v>
+        <v>21.6</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0.46</v>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>40.56</v>
+        <v>40.57</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>5.28</v>
@@ -8362,10 +8362,10 @@
         <v>0</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.11</v>
       </c>
       <c r="AC73" s="4" t="n">
-        <v>20.9</v>
+        <v>20.89</v>
       </c>
       <c r="AD73" s="4" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="M74" s="4" t="n">
-        <v>52.77</v>
+        <v>52.78</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>5.28</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>48.97</v>
+        <v>48.98</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>100</v>
@@ -8535,7 +8535,7 @@
         <v>5.28</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>48.97</v>
+        <v>48.98</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>3.69</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>43.91</v>
+        <v>43.92</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>100</v>
@@ -8637,7 +8637,7 @@
         <v>5.28</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>43.91</v>
+        <v>43.92</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>2.1</v>
@@ -8733,13 +8733,13 @@
         </is>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.5</v>
+        <v>38.51</v>
       </c>
       <c r="N77" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>50.18</v>
+        <v>50.19</v>
       </c>
       <c r="P77" s="4" t="n">
         <v>2.46</v>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-28.63</v>
+        <v>-28.62</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>0</v>
@@ -8835,13 +8835,13 @@
         </is>
       </c>
       <c r="M78" s="4" t="n">
-        <v>-30.47</v>
+        <v>-30.46</v>
       </c>
       <c r="N78" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>-28.63</v>
+        <v>-28.62</v>
       </c>
       <c r="P78" s="4" t="n">
         <v>-2.51</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="M79" s="4" t="n">
-        <v>11.64</v>
+        <v>11.65</v>
       </c>
       <c r="N79" s="4" t="n">
         <v>5.28</v>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>84.3</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="M80" s="4" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="N80" s="4" t="n">
         <v>5.28</v>
@@ -9082,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>53</v>
+        <v>53.01</v>
       </c>
       <c r="AC80" s="4" t="n">
-        <v>47</v>
+        <v>46.99</v>
       </c>
       <c r="AD80" s="4" t="n">
         <v>0</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="M82" s="4" t="n">
-        <v>28.05</v>
+        <v>28.06</v>
       </c>
       <c r="N82" s="4" t="n">
         <v>5.28</v>
@@ -9286,10 +9286,10 @@
         <v>0</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>68.31</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="AC82" s="4" t="n">
-        <v>31.69</v>
+        <v>31.68</v>
       </c>
       <c r="AD82" s="4" t="n">
         <v>0</v>
@@ -9388,10 +9388,10 @@
         <v>0</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>59.86</v>
+        <v>59.87</v>
       </c>
       <c r="AC83" s="4" t="n">
-        <v>40.14</v>
+        <v>40.13</v>
       </c>
       <c r="AD83" s="4" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25.79</v>
+        <v>25.8</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>100</v>
@@ -9455,7 +9455,7 @@
         <v>5.28</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>25.79</v>
+        <v>25.8</v>
       </c>
       <c r="P84" s="4" t="n">
         <v>0.63</v>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>39.75</v>
+        <v>39.76</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>100</v>
@@ -9653,13 +9653,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="n">
-        <v>29.64</v>
+        <v>29.65</v>
       </c>
       <c r="N86" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>39.75</v>
+        <v>39.76</v>
       </c>
       <c r="P86" s="4" t="n">
         <v>2.23</v>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>41.2</v>
+        <v>41.21</v>
       </c>
       <c r="N87" s="4" t="n">
         <v>5.28</v>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>51.65</v>
+        <v>51.66</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>100</v>
@@ -9857,13 +9857,13 @@
         </is>
       </c>
       <c r="M88" s="4" t="n">
-        <v>44.65</v>
+        <v>44.66</v>
       </c>
       <c r="N88" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>51.65</v>
+        <v>51.66</v>
       </c>
       <c r="P88" s="4" t="n">
         <v>1.57</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>58.01</v>
+        <v>58.02</v>
       </c>
       <c r="AC89" s="4" t="n">
-        <v>41.99</v>
+        <v>41.98</v>
       </c>
       <c r="AD89" s="4" t="n">
         <v>0</v>
@@ -10061,7 +10061,7 @@
         </is>
       </c>
       <c r="M90" s="4" t="n">
-        <v>29.76</v>
+        <v>29.77</v>
       </c>
       <c r="N90" s="4" t="n">
         <v>5.28</v>
@@ -10098,10 +10098,10 @@
         <v>0</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>69.75</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="AC90" s="4" t="n">
-        <v>30.25</v>
+        <v>30.24</v>
       </c>
       <c r="AD90" s="4" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28.34</v>
+        <v>28.35</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>100</v>
@@ -10163,13 +10163,13 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>16.11</v>
+        <v>16.12</v>
       </c>
       <c r="N91" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28.34</v>
+        <v>28.35</v>
       </c>
       <c r="P91" s="4" t="n">
         <v>0</v>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="M92" s="4" t="n">
-        <v>58.67</v>
+        <v>58.68</v>
       </c>
       <c r="N92" s="4" t="n">
         <v>5.28</v>
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26.25</v>
+        <v>26.26</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>100</v>
@@ -10373,7 +10373,7 @@
         <v>5.28</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>26.25</v>
+        <v>26.26</v>
       </c>
       <c r="P93" s="4" t="n">
         <v>2.03</v>
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>51.03</v>
+        <v>51.04</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>100</v>
@@ -10469,13 +10469,13 @@
         </is>
       </c>
       <c r="M94" s="4" t="n">
-        <v>43.26</v>
+        <v>43.27</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>51.03</v>
+        <v>51.04</v>
       </c>
       <c r="P94" s="4" t="n">
         <v>2.66</v>
@@ -10577,7 +10577,7 @@
         <v>5.28</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>76.52</v>
+        <v>76.53</v>
       </c>
       <c r="P95" s="4" t="n">
         <v>0</v>
@@ -10706,10 +10706,10 @@
         <v>0</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>62.98</v>
+        <v>62.99</v>
       </c>
       <c r="AC96" s="4" t="n">
-        <v>37.02</v>
+        <v>37.01</v>
       </c>
       <c r="AD96" s="4" t="n">
         <v>0</v>
@@ -10961,7 +10961,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>31.1</v>
+        <v>31.11</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>100</v>
@@ -10981,7 +10981,7 @@
         <v>5.28</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>31.1</v>
+        <v>31.11</v>
       </c>
       <c r="P99" s="4" t="n">
         <v>2.64</v>
@@ -11063,7 +11063,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26.2</v>
+        <v>26.21</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>100</v>
@@ -11083,7 +11083,7 @@
         <v>5.28</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>26.2</v>
+        <v>26.21</v>
       </c>
       <c r="P100" s="4" t="n">
         <v>1.69</v>
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>100</v>
@@ -11281,13 +11281,13 @@
         </is>
       </c>
       <c r="M102" s="4" t="n">
-        <v>43.35</v>
+        <v>43.36</v>
       </c>
       <c r="N102" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>58.85</v>
+        <v>58.86</v>
       </c>
       <c r="P102" s="4" t="n">
         <v>1.93</v>
@@ -11471,7 +11471,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>39.35</v>
+        <v>39.36</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>100</v>
@@ -11485,13 +11485,13 @@
         </is>
       </c>
       <c r="M104" s="4" t="n">
-        <v>21.81</v>
+        <v>21.82</v>
       </c>
       <c r="N104" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>39.35</v>
+        <v>39.36</v>
       </c>
       <c r="P104" s="4" t="n">
         <v>1.73</v>
@@ -11593,7 +11593,7 @@
         <v>5.28</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>22.44</v>
+        <v>22.45</v>
       </c>
       <c r="P105" s="4" t="n">
         <v>1.61</v>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>7.47</v>
+        <v>7.53</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -11685,13 +11685,13 @@
         </is>
       </c>
       <c r="M106" s="4" t="n">
-        <v>5.43</v>
+        <v>5.44</v>
       </c>
       <c r="N106" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
       <c r="P106" s="4" t="n">
         <v>0.13</v>
@@ -11728,10 +11728,10 @@
         <v>0</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>53.73</v>
+        <v>53.77</v>
       </c>
       <c r="AC106" s="4" t="n">
-        <v>46.27</v>
+        <v>46.23</v>
       </c>
       <c r="AD106" s="4" t="n">
         <v>0</v>
@@ -11881,7 +11881,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>26.17</v>
+        <v>26.18</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>100</v>
@@ -11895,13 +11895,13 @@
         </is>
       </c>
       <c r="M108" s="4" t="n">
-        <v>20.59</v>
+        <v>20.6</v>
       </c>
       <c r="N108" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>26.17</v>
+        <v>26.18</v>
       </c>
       <c r="P108" s="4" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27.4</v>
+        <v>27.41</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>100</v>
@@ -11997,13 +11997,13 @@
         </is>
       </c>
       <c r="M109" s="4" t="n">
-        <v>21.24</v>
+        <v>21.25</v>
       </c>
       <c r="N109" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O109" s="4" t="n">
-        <v>27.4</v>
+        <v>27.41</v>
       </c>
       <c r="P109" s="4" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>39.65</v>
+        <v>39.66</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>100</v>
@@ -12105,7 +12105,7 @@
         <v>5.28</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>39.65</v>
+        <v>39.66</v>
       </c>
       <c r="P110" s="4" t="n">
         <v>1.58</v>
@@ -12387,13 +12387,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>-2.29</v>
+        <v>-2.28</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -12444,10 +12444,10 @@
         <v>0</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>48.85</v>
+        <v>48.86</v>
       </c>
       <c r="AC113" s="4" t="n">
-        <v>51.15</v>
+        <v>51.14</v>
       </c>
       <c r="AD113" s="4" t="n">
         <v>0</v>
@@ -12654,10 +12654,10 @@
         <v>0</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>46.79</v>
+        <v>46.78</v>
       </c>
       <c r="AC115" s="4" t="n">
-        <v>53.21</v>
+        <v>53.22</v>
       </c>
       <c r="AD115" s="4" t="n">
         <v>0</v>
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M119" s="4" t="n">
-        <v>25.37</v>
+        <v>25.38</v>
       </c>
       <c r="N119" s="4" t="n">
         <v>5.28</v>
@@ -13058,10 +13058,10 @@
         <v>0</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>66.12</v>
+        <v>66.13</v>
       </c>
       <c r="AC119" s="4" t="n">
-        <v>33.88</v>
+        <v>33.87</v>
       </c>
       <c r="AD119" s="4" t="n">
         <v>0</v>
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="M120" s="4" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
       <c r="N120" s="4" t="n">
         <v>5.28</v>
@@ -13160,10 +13160,10 @@
         <v>0</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>61.27</v>
+        <v>61.28</v>
       </c>
       <c r="AC120" s="4" t="n">
-        <v>38.73</v>
+        <v>38.72</v>
       </c>
       <c r="AD120" s="4" t="n">
         <v>0</v>
@@ -13211,7 +13211,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>28.57</v>
+        <v>28.58</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>100</v>
@@ -13225,13 +13225,13 @@
         </is>
       </c>
       <c r="M121" s="4" t="n">
-        <v>16.44</v>
+        <v>16.45</v>
       </c>
       <c r="N121" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O121" s="4" t="n">
-        <v>28.57</v>
+        <v>28.58</v>
       </c>
       <c r="P121" s="4" t="n">
         <v>2.19</v>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>35.03</v>
+        <v>35.04</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>100</v>
@@ -13327,13 +13327,13 @@
         </is>
       </c>
       <c r="M122" s="4" t="n">
-        <v>26.35</v>
+        <v>26.36</v>
       </c>
       <c r="N122" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>35.03</v>
+        <v>35.04</v>
       </c>
       <c r="P122" s="4" t="n">
         <v>2.02</v>
@@ -13466,10 +13466,10 @@
         <v>0</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>57.28</v>
+        <v>57.29</v>
       </c>
       <c r="AC123" s="4" t="n">
-        <v>42.72</v>
+        <v>42.71</v>
       </c>
       <c r="AD123" s="4" t="n">
         <v>0</v>
@@ -13768,10 +13768,10 @@
         <v>0</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>45.05</v>
+        <v>45.04</v>
       </c>
       <c r="AC126" s="4" t="n">
-        <v>54.95</v>
+        <v>54.96</v>
       </c>
       <c r="AD126" s="4" t="n">
         <v>0</v>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>-17.54</v>
+        <v>-17.55</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>0.4</v>
@@ -13839,7 +13839,7 @@
         <v>5.28</v>
       </c>
       <c r="O127" s="4" t="n">
-        <v>-17.54</v>
+        <v>-17.55</v>
       </c>
       <c r="P127" s="4" t="n">
         <v>-2.38</v>
@@ -13972,10 +13972,10 @@
         <v>0</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>45.58</v>
+        <v>45.57</v>
       </c>
       <c r="AC128" s="4" t="n">
-        <v>54.42</v>
+        <v>54.43</v>
       </c>
       <c r="AD128" s="4" t="n">
         <v>0</v>
@@ -14074,10 +14074,10 @@
         <v>0</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>41.02</v>
+        <v>41.01</v>
       </c>
       <c r="AC129" s="4" t="n">
-        <v>58.98</v>
+        <v>58.99</v>
       </c>
       <c r="AD129" s="4" t="n">
         <v>0</v>
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M131" s="4" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="N131" s="4" t="n">
         <v>5.28</v>
@@ -14325,7 +14325,7 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-10.24</v>
+        <v>-10.23</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>3.6</v>
@@ -14345,7 +14345,7 @@
         <v>5.28</v>
       </c>
       <c r="O132" s="4" t="n">
-        <v>-9.6</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="P132" s="4" t="n">
         <v>-0.66</v>
@@ -14433,13 +14433,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>-1.47</v>
+        <v>-1.44</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -14490,10 +14490,10 @@
         <v>0</v>
       </c>
       <c r="AB133" s="4" t="n">
-        <v>49.26</v>
+        <v>49.28</v>
       </c>
       <c r="AC133" s="4" t="n">
-        <v>50.74</v>
+        <v>50.72</v>
       </c>
       <c r="AD133" s="4" t="n">
         <v>0</v>
@@ -14639,13 +14639,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>-7.07</v>
+        <v>-7.1</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -14696,10 +14696,10 @@
         <v>0</v>
       </c>
       <c r="AB135" s="4" t="n">
-        <v>46.46</v>
+        <v>46.45</v>
       </c>
       <c r="AC135" s="4" t="n">
-        <v>53.54</v>
+        <v>53.55</v>
       </c>
       <c r="AD135" s="4" t="n">
         <v>0</v>
@@ -14849,7 +14849,7 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>-5.18</v>
+        <v>-5.19</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>18.5</v>
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>85</v>
@@ -14971,13 +14971,13 @@
         </is>
       </c>
       <c r="M138" s="4" t="n">
-        <v>-6.05</v>
+        <v>-6.06</v>
       </c>
       <c r="N138" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O138" s="4" t="n">
-        <v>5.38</v>
+        <v>5.37</v>
       </c>
       <c r="P138" s="4" t="n">
         <v>0.09</v>
@@ -15014,10 +15014,10 @@
         <v>0</v>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>53.11</v>
+        <v>53.1</v>
       </c>
       <c r="AC138" s="4" t="n">
-        <v>46.89</v>
+        <v>46.9</v>
       </c>
       <c r="AD138" s="4" t="n">
         <v>0</v>
@@ -15163,13 +15163,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>-3.4</v>
+        <v>-3.43</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -15220,10 +15220,10 @@
         <v>0</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>48.3</v>
+        <v>48.28</v>
       </c>
       <c r="AC140" s="4" t="n">
-        <v>51.7</v>
+        <v>51.72</v>
       </c>
       <c r="AD140" s="4" t="n">
         <v>0</v>
@@ -15271,7 +15271,7 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>-18.6</v>
+        <v>-18.61</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>0.3</v>
@@ -15285,13 +15285,13 @@
         </is>
       </c>
       <c r="M141" s="4" t="n">
-        <v>-17.43</v>
+        <v>-17.44</v>
       </c>
       <c r="N141" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O141" s="4" t="n">
-        <v>-18.6</v>
+        <v>-18.61</v>
       </c>
       <c r="P141" s="4" t="n">
         <v>-1.69</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>44.31</v>
+        <v>44.3</v>
       </c>
       <c r="AC142" s="4" t="n">
-        <v>55.69</v>
+        <v>55.7</v>
       </c>
       <c r="AD142" s="4" t="n">
         <v>0</v>
@@ -15471,7 +15471,7 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>-22.56</v>
+        <v>-22.57</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>0.1</v>
@@ -15491,7 +15491,7 @@
         <v>5.28</v>
       </c>
       <c r="O143" s="4" t="n">
-        <v>-22.56</v>
+        <v>-22.57</v>
       </c>
       <c r="P143" s="4" t="n">
         <v>-2.21</v>
@@ -15624,10 +15624,10 @@
         <v>0</v>
       </c>
       <c r="AB144" s="4" t="n">
-        <v>76.81999999999999</v>
+        <v>76.81</v>
       </c>
       <c r="AC144" s="4" t="n">
-        <v>23.18</v>
+        <v>23.19</v>
       </c>
       <c r="AD144" s="4" t="n">
         <v>0</v>
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -15830,10 +15830,10 @@
         <v>0</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>50.02</v>
+        <v>50.03</v>
       </c>
       <c r="AC146" s="4" t="n">
-        <v>49.98</v>
+        <v>49.97</v>
       </c>
       <c r="AD146" s="4" t="n">
         <v>0</v>
@@ -15881,7 +15881,7 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>31.5</v>
+        <v>31.49</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>100</v>
@@ -15901,7 +15901,7 @@
         <v>5.28</v>
       </c>
       <c r="O147" s="4" t="n">
-        <v>31.5</v>
+        <v>31.49</v>
       </c>
       <c r="P147" s="4" t="n">
         <v>1.81</v>
@@ -16192,10 +16192,10 @@
         <v>-10.78</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>-8.48</v>
+        <v>-8.49</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>8.1</v>
@@ -16517,13 +16517,13 @@
         </is>
       </c>
       <c r="M153" s="4" t="n">
-        <v>-11.55</v>
+        <v>-11.56</v>
       </c>
       <c r="N153" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>-8.48</v>
+        <v>-8.49</v>
       </c>
       <c r="P153" s="4" t="n">
         <v>-1.91</v>
@@ -16605,7 +16605,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>24.37</v>
+        <v>24.15</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>99.90000000000001</v>
@@ -16625,10 +16625,10 @@
         <v>5.28</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>24.37</v>
+        <v>24.15</v>
       </c>
       <c r="P154" s="4" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Q154" s="4" t="n">
         <v>5.49</v>
@@ -16646,7 +16646,7 @@
         <v>1126530</v>
       </c>
       <c r="X154" s="5" t="n">
-        <v>142715</v>
+        <v>206344</v>
       </c>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" s="4" t="n">
@@ -16656,10 +16656,10 @@
         <v>0</v>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>62.18</v>
+        <v>62.07</v>
       </c>
       <c r="AC154" s="4" t="n">
-        <v>37.82</v>
+        <v>37.93</v>
       </c>
       <c r="AD154" s="4" t="n">
         <v>0</v>
@@ -16809,7 +16809,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>65.47</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>100</v>
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="M156" s="4" t="n">
-        <v>58.3</v>
+        <v>58.29</v>
       </c>
       <c r="N156" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>65.47</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="P156" s="4" t="n">
         <v>0</v>
@@ -16911,7 +16911,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>83.92</v>
+        <v>83.91</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>100</v>
@@ -16925,13 +16925,13 @@
         </is>
       </c>
       <c r="M157" s="4" t="n">
-        <v>76.70999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="N157" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O157" s="4" t="n">
-        <v>83.92</v>
+        <v>83.91</v>
       </c>
       <c r="P157" s="4" t="n">
         <v>0</v>
@@ -17013,7 +17013,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>63.22</v>
+        <v>63.21</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>100</v>
@@ -17033,7 +17033,7 @@
         <v>5.28</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>63.22</v>
+        <v>63.21</v>
       </c>
       <c r="P158" s="4" t="n">
         <v>2.07</v>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="M159" s="4" t="n">
-        <v>-18.44</v>
+        <v>-18.45</v>
       </c>
       <c r="N159" s="4" t="n">
         <v>5.28</v>
@@ -17217,7 +17217,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-29.42</v>
+        <v>-29.43</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>0</v>
@@ -17231,13 +17231,13 @@
         </is>
       </c>
       <c r="M160" s="4" t="n">
-        <v>-26.27</v>
+        <v>-26.28</v>
       </c>
       <c r="N160" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O160" s="4" t="n">
-        <v>-29.42</v>
+        <v>-29.43</v>
       </c>
       <c r="P160" s="4" t="n">
         <v>-2.12</v>
@@ -17319,7 +17319,7 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>-30.49</v>
+        <v>-30.5</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>0</v>
@@ -17333,13 +17333,13 @@
         </is>
       </c>
       <c r="M161" s="4" t="n">
-        <v>-30.59</v>
+        <v>-30.6</v>
       </c>
       <c r="N161" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O161" s="4" t="n">
-        <v>-30.49</v>
+        <v>-30.5</v>
       </c>
       <c r="P161" s="4" t="n">
         <v>-1.43</v>
@@ -17468,10 +17468,10 @@
         <v>0</v>
       </c>
       <c r="AB162" s="4" t="n">
-        <v>41.94</v>
+        <v>41.93</v>
       </c>
       <c r="AC162" s="4" t="n">
-        <v>58.06</v>
+        <v>58.07</v>
       </c>
       <c r="AD162" s="4" t="n">
         <v>0</v>
@@ -17529,7 +17529,7 @@
         </is>
       </c>
       <c r="M163" s="4" t="n">
-        <v>-19.96</v>
+        <v>-19.97</v>
       </c>
       <c r="N163" s="4" t="n">
         <v>5.28</v>
@@ -17566,10 +17566,10 @@
         <v>0</v>
       </c>
       <c r="AB163" s="4" t="n">
-        <v>41.39</v>
+        <v>41.38</v>
       </c>
       <c r="AC163" s="4" t="n">
-        <v>58.61</v>
+        <v>58.62</v>
       </c>
       <c r="AD163" s="4" t="n">
         <v>0</v>
@@ -17617,7 +17617,7 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-11.56</v>
+        <v>-11.57</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>1.2</v>
@@ -17637,7 +17637,7 @@
         <v>5.28</v>
       </c>
       <c r="O164" s="4" t="n">
-        <v>-11.56</v>
+        <v>-11.57</v>
       </c>
       <c r="P164" s="4" t="n">
         <v>-1.96</v>
@@ -17715,7 +17715,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>51.01</v>
+        <v>51</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>100</v>
@@ -17729,13 +17729,13 @@
         </is>
       </c>
       <c r="M165" s="4" t="n">
-        <v>45.46</v>
+        <v>45.45</v>
       </c>
       <c r="N165" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>51.01</v>
+        <v>51</v>
       </c>
       <c r="P165" s="4" t="n">
         <v>0</v>
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="M166" s="4" t="n">
-        <v>-33.88</v>
+        <v>-33.89</v>
       </c>
       <c r="N166" s="4" t="n">
         <v>5.28</v>
@@ -18123,7 +18123,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>97.90000000000001</v>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M169" s="4" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="N169" s="4" t="n">
         <v>5.28</v>
@@ -18146,7 +18146,7 @@
         <v>13.53</v>
       </c>
       <c r="P169" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Q169" s="4" t="n">
         <v>10.1</v>
@@ -18231,7 +18231,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>67</v>
@@ -18245,13 +18245,13 @@
         </is>
       </c>
       <c r="M170" s="4" t="n">
-        <v>-2.65</v>
+        <v>-2.66</v>
       </c>
       <c r="N170" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O170" s="4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="P170" s="4" t="n">
         <v>0.19</v>
@@ -18339,13 +18339,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -18353,13 +18353,13 @@
         </is>
       </c>
       <c r="M171" s="4" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="N171" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O171" s="4" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="P171" s="4" t="n">
         <v>0.06</v>
@@ -18443,7 +18443,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-21.06</v>
+        <v>-21.07</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>0.2</v>
@@ -18457,13 +18457,13 @@
         </is>
       </c>
       <c r="M172" s="4" t="n">
-        <v>-24.63</v>
+        <v>-24.64</v>
       </c>
       <c r="N172" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O172" s="4" t="n">
-        <v>-21.06</v>
+        <v>-21.07</v>
       </c>
       <c r="P172" s="4" t="n">
         <v>-1.08</v>
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>-31.1</v>
+        <v>-31.25</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>0</v>
@@ -18559,13 +18559,13 @@
         </is>
       </c>
       <c r="M173" s="4" t="n">
-        <v>-44.99</v>
+        <v>-45.02</v>
       </c>
       <c r="N173" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O173" s="4" t="n">
-        <v>-42.41</v>
+        <v>-42.43</v>
       </c>
       <c r="P173" s="4" t="n">
         <v>-0.84</v>
@@ -18602,10 +18602,10 @@
         <v>0</v>
       </c>
       <c r="AB173" s="4" t="n">
-        <v>34.45</v>
+        <v>34.37</v>
       </c>
       <c r="AC173" s="4" t="n">
-        <v>65.55</v>
+        <v>65.63</v>
       </c>
       <c r="AD173" s="4" t="n">
         <v>0</v>
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-29.04</v>
+        <v>-29.07</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>0</v>
@@ -18667,13 +18667,13 @@
         </is>
       </c>
       <c r="M174" s="4" t="n">
-        <v>-27.18</v>
+        <v>-27.2</v>
       </c>
       <c r="N174" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>-29.04</v>
+        <v>-29.07</v>
       </c>
       <c r="P174" s="4" t="n">
         <v>-1.51</v>
@@ -18704,10 +18704,10 @@
         <v>0</v>
       </c>
       <c r="AB174" s="4" t="n">
-        <v>35.48</v>
+        <v>35.47</v>
       </c>
       <c r="AC174" s="4" t="n">
-        <v>64.52</v>
+        <v>64.53</v>
       </c>
       <c r="AD174" s="4" t="n">
         <v>0</v>
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>36.39</v>
+        <v>36.53</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>100</v>
@@ -19110,10 +19110,10 @@
         <v>0</v>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>68.19</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="AC178" s="4" t="n">
-        <v>31.81</v>
+        <v>31.74</v>
       </c>
       <c r="AD178" s="4" t="n">
         <v>0</v>
@@ -20883,7 +20883,7 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-12.62</v>
+        <v>-12.66</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>1</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AB196" s="4" t="n">
-        <v>43.69</v>
+        <v>43.67</v>
       </c>
       <c r="AC196" s="4" t="n">
-        <v>56.31</v>
+        <v>56.33</v>
       </c>
       <c r="AD196" s="4" t="n">
         <v>0</v>
@@ -21399,7 +21399,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>-30.69</v>
+        <v>-30.71</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>0</v>
@@ -21413,13 +21413,13 @@
         </is>
       </c>
       <c r="M201" s="4" t="n">
-        <v>-28.16</v>
+        <v>-28.18</v>
       </c>
       <c r="N201" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O201" s="4" t="n">
-        <v>-30.69</v>
+        <v>-30.71</v>
       </c>
       <c r="P201" s="4" t="n">
         <v>-2.06</v>
@@ -21450,10 +21450,10 @@
         <v>0</v>
       </c>
       <c r="AB201" s="4" t="n">
-        <v>34.65</v>
+        <v>34.64</v>
       </c>
       <c r="AC201" s="4" t="n">
-        <v>65.34999999999999</v>
+        <v>65.36</v>
       </c>
       <c r="AD201" s="4" t="n">
         <v>0</v>
@@ -21501,7 +21501,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-16.51</v>
+        <v>-16.53</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>0.5</v>
@@ -21515,13 +21515,13 @@
         </is>
       </c>
       <c r="M202" s="4" t="n">
-        <v>-15.73</v>
+        <v>-15.75</v>
       </c>
       <c r="N202" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O202" s="4" t="n">
-        <v>-16.51</v>
+        <v>-16.53</v>
       </c>
       <c r="P202" s="4" t="n">
         <v>-0.47</v>
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>22.26</v>
+        <v>22.24</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>99.90000000000001</v>
@@ -21617,13 +21617,13 @@
         </is>
       </c>
       <c r="M203" s="4" t="n">
-        <v>7.24</v>
+        <v>7.22</v>
       </c>
       <c r="N203" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O203" s="4" t="n">
-        <v>22.26</v>
+        <v>22.24</v>
       </c>
       <c r="P203" s="4" t="n">
         <v>3</v>
@@ -21654,10 +21654,10 @@
         <v>0</v>
       </c>
       <c r="AB203" s="4" t="n">
-        <v>61.13</v>
+        <v>61.12</v>
       </c>
       <c r="AC203" s="4" t="n">
-        <v>38.87</v>
+        <v>38.88</v>
       </c>
       <c r="AD203" s="4" t="n">
         <v>0</v>
@@ -21705,7 +21705,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-21.97</v>
+        <v>-21.99</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>0.1</v>
@@ -21719,13 +21719,13 @@
         </is>
       </c>
       <c r="M204" s="4" t="n">
-        <v>-20.12</v>
+        <v>-20.14</v>
       </c>
       <c r="N204" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O204" s="4" t="n">
-        <v>-21.97</v>
+        <v>-21.99</v>
       </c>
       <c r="P204" s="4" t="n">
         <v>-1.43</v>
@@ -22309,7 +22309,7 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>-6.67</v>
+        <v>-6.69</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>13.5</v>
@@ -22366,10 +22366,10 @@
         <v>0</v>
       </c>
       <c r="AB210" s="4" t="n">
-        <v>46.67</v>
+        <v>46.65</v>
       </c>
       <c r="AC210" s="4" t="n">
-        <v>53.33</v>
+        <v>53.35</v>
       </c>
       <c r="AD210" s="4" t="n">
         <v>0</v>
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>23.78</v>
+        <v>23.79</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23035,13 +23035,13 @@
         </is>
       </c>
       <c r="M217" s="4" t="n">
-        <v>16.96</v>
+        <v>16.97</v>
       </c>
       <c r="N217" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O217" s="4" t="n">
-        <v>23.78</v>
+        <v>23.79</v>
       </c>
       <c r="P217" s="4" t="n">
         <v>0</v>
@@ -23072,10 +23072,10 @@
         <v>0</v>
       </c>
       <c r="AB217" s="4" t="n">
-        <v>61.89</v>
+        <v>61.9</v>
       </c>
       <c r="AC217" s="4" t="n">
-        <v>38.11</v>
+        <v>38.1</v>
       </c>
       <c r="AD217" s="4" t="n">
         <v>0</v>
@@ -23123,7 +23123,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>33.4</v>
+        <v>33.41</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>100</v>
@@ -23137,13 +23137,13 @@
         </is>
       </c>
       <c r="M218" s="4" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="N218" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O218" s="4" t="n">
-        <v>33.4</v>
+        <v>33.41</v>
       </c>
       <c r="P218" s="4" t="n">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="AB218" s="4" t="n">
-        <v>66.7</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="AC218" s="4" t="n">
-        <v>33.3</v>
+        <v>33.29</v>
       </c>
       <c r="AD218" s="4" t="n">
         <v>0</v>
@@ -23225,7 +23225,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>31.98</v>
+        <v>31.99</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>100</v>
@@ -23239,13 +23239,13 @@
         </is>
       </c>
       <c r="M219" s="4" t="n">
-        <v>22.41</v>
+        <v>22.42</v>
       </c>
       <c r="N219" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O219" s="4" t="n">
-        <v>31.98</v>
+        <v>31.99</v>
       </c>
       <c r="P219" s="4" t="n">
         <v>2.54</v>
@@ -23327,7 +23327,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>29.46</v>
+        <v>29.47</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>100</v>
@@ -23341,13 +23341,13 @@
         </is>
       </c>
       <c r="M220" s="4" t="n">
-        <v>23.23</v>
+        <v>23.24</v>
       </c>
       <c r="N220" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O220" s="4" t="n">
-        <v>29.46</v>
+        <v>29.47</v>
       </c>
       <c r="P220" s="4" t="n">
         <v>0</v>
@@ -23429,7 +23429,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>55.08</v>
+        <v>55.09</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>100</v>
@@ -23443,13 +23443,13 @@
         </is>
       </c>
       <c r="M221" s="4" t="n">
-        <v>48.59</v>
+        <v>48.6</v>
       </c>
       <c r="N221" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O221" s="4" t="n">
-        <v>55.08</v>
+        <v>55.09</v>
       </c>
       <c r="P221" s="4" t="n">
         <v>0</v>
@@ -23527,7 +23527,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>28.22</v>
+        <v>28.23</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>100</v>
@@ -23541,13 +23541,13 @@
         </is>
       </c>
       <c r="M222" s="4" t="n">
-        <v>23.44</v>
+        <v>23.45</v>
       </c>
       <c r="N222" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O222" s="4" t="n">
-        <v>28.22</v>
+        <v>28.23</v>
       </c>
       <c r="P222" s="4" t="n">
         <v>0</v>
@@ -23629,7 +23629,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>75.87</v>
+        <v>75.88</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>100</v>
@@ -23643,13 +23643,13 @@
         </is>
       </c>
       <c r="M223" s="4" t="n">
-        <v>68.59999999999999</v>
+        <v>68.61</v>
       </c>
       <c r="N223" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O223" s="4" t="n">
-        <v>75.87</v>
+        <v>75.88</v>
       </c>
       <c r="P223" s="4" t="n">
         <v>0</v>
@@ -23680,10 +23680,10 @@
         <v>0</v>
       </c>
       <c r="AB223" s="4" t="n">
-        <v>87.93000000000001</v>
+        <v>87.94</v>
       </c>
       <c r="AC223" s="4" t="n">
-        <v>12.07</v>
+        <v>12.06</v>
       </c>
       <c r="AD223" s="4" t="n">
         <v>0</v>
@@ -23731,7 +23731,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>100</v>
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="M224" s="4" t="n">
-        <v>30</v>
+        <v>30.01</v>
       </c>
       <c r="N224" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O224" s="4" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="P224" s="4" t="n">
         <v>0</v>
@@ -23782,10 +23782,10 @@
         <v>0</v>
       </c>
       <c r="AB224" s="4" t="n">
-        <v>72.59</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AC224" s="4" t="n">
-        <v>27.41</v>
+        <v>27.4</v>
       </c>
       <c r="AD224" s="4" t="n">
         <v>0</v>
@@ -23833,7 +23833,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>22.25</v>
+        <v>22.26</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>99.90000000000001</v>
@@ -23847,13 +23847,13 @@
         </is>
       </c>
       <c r="M225" s="4" t="n">
-        <v>13.48</v>
+        <v>13.49</v>
       </c>
       <c r="N225" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O225" s="4" t="n">
-        <v>22.25</v>
+        <v>22.26</v>
       </c>
       <c r="P225" s="4" t="n">
         <v>0.5600000000000001</v>
@@ -23884,10 +23884,10 @@
         <v>0</v>
       </c>
       <c r="AB225" s="4" t="n">
-        <v>61.12</v>
+        <v>61.13</v>
       </c>
       <c r="AC225" s="4" t="n">
-        <v>38.88</v>
+        <v>38.87</v>
       </c>
       <c r="AD225" s="4" t="n">
         <v>0</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>-15.93</v>
+        <v>-15.91</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>0.6</v>
@@ -23949,13 +23949,13 @@
         </is>
       </c>
       <c r="M226" s="4" t="n">
-        <v>-16.13</v>
+        <v>-16.11</v>
       </c>
       <c r="N226" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O226" s="4" t="n">
-        <v>-15.9</v>
+        <v>-15.88</v>
       </c>
       <c r="P226" s="4" t="n">
         <v>-0.86</v>
@@ -24043,7 +24043,7 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>31.21</v>
+        <v>31.23</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>100</v>
@@ -24057,13 +24057,13 @@
         </is>
       </c>
       <c r="M227" s="4" t="n">
-        <v>20.09</v>
+        <v>20.11</v>
       </c>
       <c r="N227" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O227" s="4" t="n">
-        <v>31.21</v>
+        <v>31.23</v>
       </c>
       <c r="P227" s="4" t="n">
         <v>2.06</v>
@@ -24094,10 +24094,10 @@
         <v>0</v>
       </c>
       <c r="AB227" s="4" t="n">
-        <v>65.61</v>
+        <v>65.62</v>
       </c>
       <c r="AC227" s="4" t="n">
-        <v>34.39</v>
+        <v>34.38</v>
       </c>
       <c r="AD227" s="4" t="n">
         <v>0</v>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>34.97</v>
+        <v>34.99</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>100</v>
@@ -24159,13 +24159,13 @@
         </is>
       </c>
       <c r="M228" s="4" t="n">
-        <v>25.31</v>
+        <v>25.33</v>
       </c>
       <c r="N228" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O228" s="4" t="n">
-        <v>34.97</v>
+        <v>34.99</v>
       </c>
       <c r="P228" s="4" t="n">
         <v>2.21</v>
@@ -24196,10 +24196,10 @@
         <v>0</v>
       </c>
       <c r="AB228" s="4" t="n">
-        <v>67.48999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="AC228" s="4" t="n">
-        <v>32.51</v>
+        <v>32.5</v>
       </c>
       <c r="AD228" s="4" t="n">
         <v>0</v>
@@ -24247,7 +24247,7 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>86.67</v>
+        <v>86.69</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>100</v>
@@ -24261,13 +24261,13 @@
         </is>
       </c>
       <c r="M229" s="4" t="n">
-        <v>78.79000000000001</v>
+        <v>78.81</v>
       </c>
       <c r="N229" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O229" s="4" t="n">
-        <v>86.67</v>
+        <v>86.69</v>
       </c>
       <c r="P229" s="4" t="n">
         <v>0</v>
@@ -24298,10 +24298,10 @@
         <v>0</v>
       </c>
       <c r="AB229" s="4" t="n">
-        <v>93.33</v>
+        <v>93.34</v>
       </c>
       <c r="AC229" s="4" t="n">
-        <v>6.67</v>
+        <v>6.66</v>
       </c>
       <c r="AD229" s="4" t="n">
         <v>0</v>
@@ -24345,7 +24345,7 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>39.9</v>
+        <v>39.92</v>
       </c>
       <c r="J230" s="4" t="n">
         <v>100</v>
@@ -24359,13 +24359,13 @@
         </is>
       </c>
       <c r="M230" s="4" t="n">
-        <v>35.2</v>
+        <v>35.22</v>
       </c>
       <c r="N230" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O230" s="4" t="n">
-        <v>39.9</v>
+        <v>39.92</v>
       </c>
       <c r="P230" s="4" t="n">
         <v>0</v>
@@ -24396,10 +24396,10 @@
         <v>0</v>
       </c>
       <c r="AB230" s="4" t="n">
-        <v>69.95</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="AC230" s="4" t="n">
-        <v>30.05</v>
+        <v>30.04</v>
       </c>
       <c r="AD230" s="4" t="n">
         <v>0</v>
@@ -24447,7 +24447,7 @@
         </is>
       </c>
       <c r="I231" s="4" t="n">
-        <v>19.23</v>
+        <v>19.25</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>99.7</v>
@@ -24461,13 +24461,13 @@
         </is>
       </c>
       <c r="M231" s="4" t="n">
-        <v>7.58</v>
+        <v>7.6</v>
       </c>
       <c r="N231" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O231" s="4" t="n">
-        <v>19.23</v>
+        <v>19.25</v>
       </c>
       <c r="P231" s="4" t="n">
         <v>2.47</v>
@@ -24498,10 +24498,10 @@
         <v>0</v>
       </c>
       <c r="AB231" s="4" t="n">
-        <v>59.62</v>
+        <v>59.63</v>
       </c>
       <c r="AC231" s="4" t="n">
-        <v>40.38</v>
+        <v>40.37</v>
       </c>
       <c r="AD231" s="4" t="n">
         <v>0</v>
@@ -24549,7 +24549,7 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>71.97</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>100</v>
@@ -24563,13 +24563,13 @@
         </is>
       </c>
       <c r="M232" s="4" t="n">
-        <v>62.67</v>
+        <v>62.69</v>
       </c>
       <c r="N232" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O232" s="4" t="n">
-        <v>71.97</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="P232" s="4" t="n">
         <v>0</v>
@@ -24600,10 +24600,10 @@
         <v>0</v>
       </c>
       <c r="AB232" s="4" t="n">
-        <v>85.98999999999999</v>
+        <v>86</v>
       </c>
       <c r="AC232" s="4" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="AD232" s="4" t="n">
         <v>0</v>
@@ -24651,7 +24651,7 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>69.45999999999999</v>
+        <v>69.48</v>
       </c>
       <c r="J233" s="4" t="n">
         <v>100</v>
@@ -24665,13 +24665,13 @@
         </is>
       </c>
       <c r="M233" s="4" t="n">
-        <v>60.52</v>
+        <v>60.54</v>
       </c>
       <c r="N233" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O233" s="4" t="n">
-        <v>69.45999999999999</v>
+        <v>69.48</v>
       </c>
       <c r="P233" s="4" t="n">
         <v>3.54</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="AB233" s="4" t="n">
-        <v>84.73</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="AC233" s="4" t="n">
-        <v>15.27</v>
+        <v>15.26</v>
       </c>
       <c r="AD233" s="4" t="n">
         <v>0</v>
@@ -24854,10 +24854,10 @@
         <v>-4.59</v>
       </c>
       <c r="J235" s="4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>79.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -24865,13 +24865,13 @@
         </is>
       </c>
       <c r="M235" s="4" t="n">
-        <v>-9.23</v>
+        <v>-9.24</v>
       </c>
       <c r="N235" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O235" s="4" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="P235" s="4" t="n">
         <v>-0.46</v>
@@ -24908,10 +24908,10 @@
         <v>0</v>
       </c>
       <c r="AB235" s="4" t="n">
-        <v>47.71</v>
+        <v>47.7</v>
       </c>
       <c r="AC235" s="4" t="n">
-        <v>52.29</v>
+        <v>52.3</v>
       </c>
       <c r="AD235" s="4" t="n">
         <v>0</v>
@@ -25163,7 +25163,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>21.09</v>
+        <v>21.1</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>99.8</v>
@@ -25183,7 +25183,7 @@
         <v>5.28</v>
       </c>
       <c r="O238" s="4" t="n">
-        <v>21.09</v>
+        <v>21.1</v>
       </c>
       <c r="P238" s="4" t="n">
         <v>0.83</v>
@@ -25285,7 +25285,7 @@
         <v>5.28</v>
       </c>
       <c r="O239" s="4" t="n">
-        <v>-2.46</v>
+        <v>-2.45</v>
       </c>
       <c r="P239" s="4" t="n">
         <v>-0.26</v>
@@ -25373,7 +25373,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>-25.95</v>
+        <v>-25.94</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>0</v>
@@ -25393,7 +25393,7 @@
         <v>5.28</v>
       </c>
       <c r="O240" s="4" t="n">
-        <v>-25.95</v>
+        <v>-25.94</v>
       </c>
       <c r="P240" s="4" t="n">
         <v>-2.12</v>
@@ -25489,7 +25489,7 @@
         </is>
       </c>
       <c r="M241" s="4" t="n">
-        <v>27.95</v>
+        <v>27.96</v>
       </c>
       <c r="N241" s="4" t="n">
         <v>5.28</v>
@@ -25597,10 +25597,10 @@
         <v>5.28</v>
       </c>
       <c r="O242" s="4" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="P242" s="4" t="n">
-        <v>-1.12</v>
+        <v>-1.14</v>
       </c>
       <c r="Q242" s="4" t="n">
         <v>-3.8</v>
@@ -25699,7 +25699,7 @@
         </is>
       </c>
       <c r="M243" s="4" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="N243" s="4" t="n">
         <v>5.28</v>
@@ -25736,10 +25736,10 @@
         <v>0</v>
       </c>
       <c r="AB243" s="4" t="n">
-        <v>59.66</v>
+        <v>59.67</v>
       </c>
       <c r="AC243" s="4" t="n">
-        <v>40.34</v>
+        <v>40.33</v>
       </c>
       <c r="AD243" s="4" t="n">
         <v>0</v>
@@ -25838,10 +25838,10 @@
         <v>0</v>
       </c>
       <c r="AB244" s="4" t="n">
-        <v>33.52</v>
+        <v>33.53</v>
       </c>
       <c r="AC244" s="4" t="n">
-        <v>66.48</v>
+        <v>66.47</v>
       </c>
       <c r="AD244" s="4" t="n">
         <v>0</v>
@@ -25885,13 +25885,13 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="J245" s="4" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K245" s="4" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -25899,13 +25899,13 @@
         </is>
       </c>
       <c r="M245" s="4" t="n">
-        <v>-1.97</v>
+        <v>-1.96</v>
       </c>
       <c r="N245" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O245" s="4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="P245" s="4" t="n">
         <v>-0.15</v>
@@ -25942,10 +25942,10 @@
         <v>0</v>
       </c>
       <c r="AB245" s="4" t="n">
-        <v>50.35</v>
+        <v>50.36</v>
       </c>
       <c r="AC245" s="4" t="n">
-        <v>49.65</v>
+        <v>49.64</v>
       </c>
       <c r="AD245" s="4" t="n">
         <v>0</v>
@@ -26003,7 +26003,7 @@
         </is>
       </c>
       <c r="M246" s="4" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="N246" s="4" t="n">
         <v>5.28</v>
@@ -26091,7 +26091,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>58.84</v>
+        <v>58.85</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>100</v>
@@ -26111,7 +26111,7 @@
         <v>5.28</v>
       </c>
       <c r="O247" s="4" t="n">
-        <v>58.84</v>
+        <v>58.85</v>
       </c>
       <c r="P247" s="4" t="n">
         <v>2.96</v>
@@ -26395,13 +26395,13 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>12.52</v>
+        <v>12.53</v>
       </c>
       <c r="J250" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="K250" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -27217,13 +27217,13 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>-10.86</v>
+        <v>-10.87</v>
       </c>
       <c r="J258" s="4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="K258" s="4" t="n">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         <v>0</v>
       </c>
       <c r="AB258" s="4" t="n">
-        <v>44.57</v>
+        <v>44.56</v>
       </c>
       <c r="AC258" s="4" t="n">
-        <v>55.43</v>
+        <v>55.44</v>
       </c>
       <c r="AD258" s="4" t="n">
         <v>0</v>
@@ -27947,7 +27947,7 @@
         </is>
       </c>
       <c r="M265" s="4" t="n">
-        <v>-33.48</v>
+        <v>-33.49</v>
       </c>
       <c r="N265" s="4" t="n">
         <v>5.28</v>
@@ -27984,10 +27984,10 @@
         <v>0</v>
       </c>
       <c r="AB265" s="4" t="n">
-        <v>33.95</v>
+        <v>33.94</v>
       </c>
       <c r="AC265" s="4" t="n">
-        <v>66.05</v>
+        <v>66.06</v>
       </c>
       <c r="AD265" s="4" t="n">
         <v>0</v>
@@ -28086,10 +28086,10 @@
         <v>0</v>
       </c>
       <c r="AB266" s="4" t="n">
-        <v>67.92</v>
+        <v>67.91</v>
       </c>
       <c r="AC266" s="4" t="n">
-        <v>32.08</v>
+        <v>32.09</v>
       </c>
       <c r="AD266" s="4" t="n">
         <v>0</v>
@@ -28151,7 +28151,7 @@
         </is>
       </c>
       <c r="M267" s="4" t="n">
-        <v>-25.66</v>
+        <v>-25.67</v>
       </c>
       <c r="N267" s="4" t="n">
         <v>5.28</v>
@@ -28188,10 +28188,10 @@
         <v>0</v>
       </c>
       <c r="AB267" s="4" t="n">
-        <v>38.2</v>
+        <v>38.19</v>
       </c>
       <c r="AC267" s="4" t="n">
-        <v>61.8</v>
+        <v>61.81</v>
       </c>
       <c r="AD267" s="4" t="n">
         <v>0</v>
@@ -28290,10 +28290,10 @@
         <v>0</v>
       </c>
       <c r="AB268" s="4" t="n">
-        <v>29.4</v>
+        <v>29.39</v>
       </c>
       <c r="AC268" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>70.61</v>
       </c>
       <c r="AD268" s="4" t="n">
         <v>0</v>
@@ -28340,10 +28340,10 @@
         <v>-6.08</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>5.28</v>
       </c>
       <c r="O271" s="4" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="P271" s="4" t="n">
         <v>0.09</v>
@@ -28655,7 +28655,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>45.57</v>
+        <v>45.56</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>100</v>
@@ -28669,13 +28669,13 @@
         </is>
       </c>
       <c r="M272" s="4" t="n">
-        <v>37.09</v>
+        <v>37.08</v>
       </c>
       <c r="N272" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O272" s="4" t="n">
-        <v>45.57</v>
+        <v>45.56</v>
       </c>
       <c r="P272" s="4" t="n">
         <v>0</v>
@@ -28757,7 +28757,7 @@
         </is>
       </c>
       <c r="I273" s="4" t="n">
-        <v>-7.03</v>
+        <v>-7.05</v>
       </c>
       <c r="J273" s="4" t="n">
         <v>12.4</v>
@@ -28771,13 +28771,13 @@
         </is>
       </c>
       <c r="M273" s="4" t="n">
-        <v>-9.73</v>
+        <v>-9.74</v>
       </c>
       <c r="N273" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O273" s="4" t="n">
-        <v>-7.55</v>
+        <v>-7.56</v>
       </c>
       <c r="P273" s="4" t="n">
         <v>-1.35</v>
@@ -28865,7 +28865,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>59.08</v>
+        <v>59.07</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>100</v>
@@ -28879,13 +28879,13 @@
         </is>
       </c>
       <c r="M274" s="4" t="n">
-        <v>48.78</v>
+        <v>48.77</v>
       </c>
       <c r="N274" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O274" s="4" t="n">
-        <v>59.08</v>
+        <v>59.07</v>
       </c>
       <c r="P274" s="4" t="n">
         <v>1.88</v>
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>-9.619999999999999</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>5.1</v>
@@ -29185,7 +29185,7 @@
         </is>
       </c>
       <c r="M277" s="4" t="n">
-        <v>-10.77</v>
+        <v>-10.78</v>
       </c>
       <c r="N277" s="4" t="n">
         <v>5.28</v>
@@ -29228,10 +29228,10 @@
         <v>0</v>
       </c>
       <c r="AB277" s="4" t="n">
-        <v>44.46</v>
+        <v>44.45</v>
       </c>
       <c r="AC277" s="4" t="n">
-        <v>53.92</v>
+        <v>53.93</v>
       </c>
       <c r="AD277" s="4" t="n">
         <v>1.62</v>
@@ -29279,7 +29279,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>-16.78</v>
+        <v>-16.79</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>0.5</v>
@@ -29293,13 +29293,13 @@
         </is>
       </c>
       <c r="M278" s="4" t="n">
-        <v>-16.81</v>
+        <v>-16.82</v>
       </c>
       <c r="N278" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O278" s="4" t="n">
-        <v>-16.78</v>
+        <v>-16.79</v>
       </c>
       <c r="P278" s="4" t="n">
         <v>-1.86</v>
@@ -29330,10 +29330,10 @@
         <v>0</v>
       </c>
       <c r="AB278" s="4" t="n">
-        <v>41.61</v>
+        <v>41.6</v>
       </c>
       <c r="AC278" s="4" t="n">
-        <v>58.39</v>
+        <v>58.4</v>
       </c>
       <c r="AD278" s="4" t="n">
         <v>0</v>
@@ -29381,7 +29381,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>-11.28</v>
+        <v>-11.29</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>1.3</v>
@@ -29395,13 +29395,13 @@
         </is>
       </c>
       <c r="M279" s="4" t="n">
-        <v>-13.1</v>
+        <v>-13.11</v>
       </c>
       <c r="N279" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O279" s="4" t="n">
-        <v>-11.28</v>
+        <v>-11.29</v>
       </c>
       <c r="P279" s="4" t="n">
         <v>-0.22</v>
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>-15.58</v>
+        <v>-15.59</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>0.6</v>
@@ -29503,7 +29503,7 @@
         <v>5.28</v>
       </c>
       <c r="O280" s="4" t="n">
-        <v>-16.21</v>
+        <v>-16.22</v>
       </c>
       <c r="P280" s="4" t="n">
         <v>-1.6</v>
@@ -29587,7 +29587,7 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>-3.19</v>
+        <v>-3.2</v>
       </c>
       <c r="J281" s="4" t="n">
         <v>25.8</v>
@@ -29601,13 +29601,13 @@
         </is>
       </c>
       <c r="M281" s="4" t="n">
-        <v>-7.75</v>
+        <v>-7.76</v>
       </c>
       <c r="N281" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O281" s="4" t="n">
-        <v>-3.19</v>
+        <v>-3.2</v>
       </c>
       <c r="P281" s="4" t="n">
         <v>0</v>
@@ -29638,10 +29638,10 @@
         <v>0</v>
       </c>
       <c r="AB281" s="4" t="n">
-        <v>48.41</v>
+        <v>48.4</v>
       </c>
       <c r="AC281" s="4" t="n">
-        <v>51.59</v>
+        <v>51.6</v>
       </c>
       <c r="AD281" s="4" t="n">
         <v>0</v>
@@ -29791,7 +29791,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>-13.3</v>
+        <v>-13.31</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>0.9</v>
@@ -29805,13 +29805,13 @@
         </is>
       </c>
       <c r="M283" s="4" t="n">
-        <v>-14.47</v>
+        <v>-14.48</v>
       </c>
       <c r="N283" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O283" s="4" t="n">
-        <v>-12.84</v>
+        <v>-12.85</v>
       </c>
       <c r="P283" s="4" t="n">
         <v>-0.19</v>
@@ -29842,10 +29842,10 @@
         <v>0</v>
       </c>
       <c r="AB283" s="4" t="n">
-        <v>42.55</v>
+        <v>42.54</v>
       </c>
       <c r="AC283" s="4" t="n">
-        <v>55.6</v>
+        <v>55.61</v>
       </c>
       <c r="AD283" s="4" t="n">
         <v>1.85</v>
@@ -29893,7 +29893,7 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>-12.76</v>
+        <v>-12.77</v>
       </c>
       <c r="J284" s="4" t="n">
         <v>1</v>
@@ -29907,7 +29907,7 @@
         </is>
       </c>
       <c r="M284" s="4" t="n">
-        <v>-13.27</v>
+        <v>-13.28</v>
       </c>
       <c r="N284" s="4" t="n">
         <v>5.28</v>
@@ -29950,10 +29950,10 @@
         <v>0</v>
       </c>
       <c r="AB284" s="4" t="n">
-        <v>43.62</v>
+        <v>43.61</v>
       </c>
       <c r="AC284" s="4" t="n">
-        <v>56.38</v>
+        <v>56.39</v>
       </c>
       <c r="AD284" s="4" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="J289" s="4" t="n">
         <v>80.90000000000001</v>
@@ -30433,10 +30433,10 @@
         <v>5.28</v>
       </c>
       <c r="O289" s="4" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="P289" s="4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q289" s="4" t="n">
         <v>0</v>
@@ -30464,10 +30464,10 @@
         <v>0</v>
       </c>
       <c r="AB289" s="4" t="n">
-        <v>52.51</v>
+        <v>52.5</v>
       </c>
       <c r="AC289" s="4" t="n">
-        <v>47.49</v>
+        <v>47.5</v>
       </c>
       <c r="AD289" s="4" t="n">
         <v>0</v>
@@ -30515,7 +30515,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>15.14</v>
+        <v>15.13</v>
       </c>
       <c r="J290" s="4" t="n">
         <v>99.40000000000001</v>
@@ -30535,7 +30535,7 @@
         <v>5.28</v>
       </c>
       <c r="O290" s="4" t="n">
-        <v>14.72</v>
+        <v>14.71</v>
       </c>
       <c r="P290" s="4" t="n">
         <v>0.92</v>
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>16.14</v>
+        <v>16.15</v>
       </c>
       <c r="J306" s="4" t="n">
         <v>99.5</v>
@@ -32191,7 +32191,7 @@
         <v>5.28</v>
       </c>
       <c r="O306" s="4" t="n">
-        <v>16.14</v>
+        <v>16.15</v>
       </c>
       <c r="P306" s="4" t="n">
         <v>-0.16</v>
@@ -32269,13 +32269,13 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>-6.07</v>
+        <v>-6.1</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="K307" s="4" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         </is>
       </c>
       <c r="M307" s="4" t="n">
-        <v>-12.62</v>
+        <v>-12.61</v>
       </c>
       <c r="N307" s="4" t="n">
         <v>5.28</v>
@@ -32326,10 +32326,10 @@
         <v>0</v>
       </c>
       <c r="AB307" s="4" t="n">
-        <v>46.96</v>
+        <v>46.95</v>
       </c>
       <c r="AC307" s="4" t="n">
-        <v>53.04</v>
+        <v>53.05</v>
       </c>
       <c r="AD307" s="4" t="n">
         <v>0</v>
@@ -32377,7 +32377,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="J308" s="4" t="n">
         <v>98.8</v>
@@ -32391,13 +32391,13 @@
         </is>
       </c>
       <c r="M308" s="4" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="N308" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O308" s="4" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="P308" s="4" t="n">
         <v>0.06</v>
@@ -32479,7 +32479,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>17.4</v>
+        <v>17.41</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>99.59999999999999</v>
@@ -32493,13 +32493,13 @@
         </is>
       </c>
       <c r="M309" s="4" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="N309" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O309" s="4" t="n">
-        <v>17.4</v>
+        <v>17.41</v>
       </c>
       <c r="P309" s="4" t="n">
         <v>0.97</v>
@@ -34209,7 +34209,7 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="J326" s="4" t="n">
         <v>72.40000000000001</v>
@@ -34317,7 +34317,7 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>18.15</v>
+        <v>18.19</v>
       </c>
       <c r="J327" s="4" t="n">
         <v>99.7</v>
@@ -34374,10 +34374,10 @@
         <v>0</v>
       </c>
       <c r="AB327" s="4" t="n">
-        <v>59.07</v>
+        <v>59.1</v>
       </c>
       <c r="AC327" s="4" t="n">
-        <v>40.93</v>
+        <v>40.9</v>
       </c>
       <c r="AD327" s="4" t="n">
         <v>0</v>
@@ -34625,13 +34625,13 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>-9.960000000000001</v>
+        <v>-10.03</v>
       </c>
       <c r="J330" s="4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K330" s="4" t="n">
-        <v>95.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -34682,10 +34682,10 @@
         <v>0</v>
       </c>
       <c r="AB330" s="4" t="n">
-        <v>45.02</v>
+        <v>44.99</v>
       </c>
       <c r="AC330" s="4" t="n">
-        <v>54.98</v>
+        <v>55.01</v>
       </c>
       <c r="AD330" s="4" t="n">
         <v>0</v>
@@ -35243,13 +35243,13 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>9.32</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="J336" s="4" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="K336" s="4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -35300,10 +35300,10 @@
         <v>0</v>
       </c>
       <c r="AB336" s="4" t="n">
-        <v>54.66</v>
+        <v>54.68</v>
       </c>
       <c r="AC336" s="4" t="n">
-        <v>45.34</v>
+        <v>45.32</v>
       </c>
       <c r="AD336" s="4" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="I337" s="4" t="n">
-        <v>-35.75</v>
+        <v>-35.76</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>0</v>
@@ -35365,13 +35365,13 @@
         </is>
       </c>
       <c r="M337" s="4" t="n">
-        <v>-37.43</v>
+        <v>-37.44</v>
       </c>
       <c r="N337" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O337" s="4" t="n">
-        <v>-35.75</v>
+        <v>-35.76</v>
       </c>
       <c r="P337" s="4" t="n">
         <v>0</v>
@@ -35467,7 +35467,7 @@
         </is>
       </c>
       <c r="M338" s="4" t="n">
-        <v>45.65</v>
+        <v>45.64</v>
       </c>
       <c r="N338" s="4" t="n">
         <v>5.28</v>
@@ -35555,7 +35555,7 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>-38.77</v>
+        <v>-38.78</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>0</v>
@@ -35569,13 +35569,13 @@
         </is>
       </c>
       <c r="M339" s="4" t="n">
-        <v>-38.19</v>
+        <v>-38.2</v>
       </c>
       <c r="N339" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O339" s="4" t="n">
-        <v>-38.25</v>
+        <v>-38.26</v>
       </c>
       <c r="P339" s="4" t="n">
         <v>-3.26</v>
@@ -35661,7 +35661,7 @@
         </is>
       </c>
       <c r="I340" s="4" t="n">
-        <v>-21.89</v>
+        <v>-21.9</v>
       </c>
       <c r="J340" s="4" t="n">
         <v>0.1</v>
@@ -35681,7 +35681,7 @@
         <v>5.28</v>
       </c>
       <c r="O340" s="4" t="n">
-        <v>-21.89</v>
+        <v>-21.9</v>
       </c>
       <c r="P340" s="4" t="n">
         <v>-2.4</v>
@@ -35712,10 +35712,10 @@
         <v>0</v>
       </c>
       <c r="AB340" s="4" t="n">
-        <v>39.06</v>
+        <v>39.05</v>
       </c>
       <c r="AC340" s="4" t="n">
-        <v>60.94</v>
+        <v>60.95</v>
       </c>
       <c r="AD340" s="4" t="n">
         <v>0</v>
@@ -35763,7 +35763,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>-28.23</v>
+        <v>-28.24</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>0</v>
@@ -35777,13 +35777,13 @@
         </is>
       </c>
       <c r="M341" s="4" t="n">
-        <v>-29.1</v>
+        <v>-29.11</v>
       </c>
       <c r="N341" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O341" s="4" t="n">
-        <v>-28.23</v>
+        <v>-28.24</v>
       </c>
       <c r="P341" s="4" t="n">
         <v>-2.34</v>
@@ -35865,13 +35865,13 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="J342" s="4" t="n">
-        <v>64.2</v>
+        <v>64</v>
       </c>
       <c r="K342" s="4" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35879,16 +35879,16 @@
         </is>
       </c>
       <c r="M342" s="4" t="n">
-        <v>-6.63</v>
+        <v>-6.64</v>
       </c>
       <c r="N342" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O342" s="4" t="n">
-        <v>-4.64</v>
+        <v>-4.65</v>
       </c>
       <c r="P342" s="4" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="Q342" s="4" t="n">
         <v>-2</v>
@@ -35922,10 +35922,10 @@
         <v>0</v>
       </c>
       <c r="AB342" s="4" t="n">
-        <v>50.32</v>
+        <v>50.29</v>
       </c>
       <c r="AC342" s="4" t="n">
-        <v>49.68</v>
+        <v>49.71</v>
       </c>
       <c r="AD342" s="4" t="n">
         <v>0</v>
@@ -35973,13 +35973,13 @@
         </is>
       </c>
       <c r="I343" s="4" t="n">
-        <v>-8.25</v>
+        <v>-8.26</v>
       </c>
       <c r="J343" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K343" s="4" t="n">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -35987,13 +35987,13 @@
         </is>
       </c>
       <c r="M343" s="4" t="n">
-        <v>-11.63</v>
+        <v>-11.64</v>
       </c>
       <c r="N343" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O343" s="4" t="n">
-        <v>-8.25</v>
+        <v>-8.26</v>
       </c>
       <c r="P343" s="4" t="n">
         <v>0</v>
@@ -36075,17 +36075,17 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>9.66</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J344" s="4" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="K344" s="4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>Safe D</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="M344" s="4" t="n">
@@ -36095,10 +36095,10 @@
         <v>5.28</v>
       </c>
       <c r="O344" s="4" t="n">
-        <v>11.54</v>
+        <v>11.51</v>
       </c>
       <c r="P344" s="4" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q344" s="4" t="n">
         <v>11.37</v>
@@ -36132,10 +36132,10 @@
         <v>0</v>
       </c>
       <c r="AB344" s="4" t="n">
-        <v>54.83</v>
+        <v>54.82</v>
       </c>
       <c r="AC344" s="4" t="n">
-        <v>45.17</v>
+        <v>45.18</v>
       </c>
       <c r="AD344" s="4" t="n">
         <v>0</v>
@@ -36183,7 +36183,7 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>-9.140000000000001</v>
+        <v>-9.15</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>6.3</v>
@@ -36197,13 +36197,13 @@
         </is>
       </c>
       <c r="M345" s="4" t="n">
-        <v>-3.23</v>
+        <v>-3.24</v>
       </c>
       <c r="N345" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O345" s="4" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="P345" s="4" t="n">
         <v>-0.62</v>
@@ -36444,10 +36444,10 @@
         <v>0</v>
       </c>
       <c r="AB347" s="4" t="n">
-        <v>37.34</v>
+        <v>37.33</v>
       </c>
       <c r="AC347" s="4" t="n">
-        <v>62.66</v>
+        <v>62.67</v>
       </c>
       <c r="AD347" s="4" t="n">
         <v>0</v>
@@ -36546,10 +36546,10 @@
         <v>0</v>
       </c>
       <c r="AB348" s="4" t="n">
-        <v>59.59</v>
+        <v>59.58</v>
       </c>
       <c r="AC348" s="4" t="n">
-        <v>40.41</v>
+        <v>40.42</v>
       </c>
       <c r="AD348" s="4" t="n">
         <v>0</v>
@@ -36597,7 +36597,7 @@
         </is>
       </c>
       <c r="I349" s="4" t="n">
-        <v>-19.46</v>
+        <v>-19.47</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>0.3</v>
@@ -36617,7 +36617,7 @@
         <v>5.28</v>
       </c>
       <c r="O349" s="4" t="n">
-        <v>-19.46</v>
+        <v>-19.47</v>
       </c>
       <c r="P349" s="4" t="n">
         <v>-1.93</v>
@@ -36699,13 +36699,13 @@
         </is>
       </c>
       <c r="I350" s="4" t="n">
-        <v>-6</v>
+        <v>-5.99</v>
       </c>
       <c r="J350" s="4" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="K350" s="4" t="n">
-        <v>84.3</v>
+        <v>84.2</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -36713,13 +36713,13 @@
         </is>
       </c>
       <c r="M350" s="4" t="n">
-        <v>-5.35</v>
+        <v>-5.36</v>
       </c>
       <c r="N350" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O350" s="4" t="n">
-        <v>-5.29</v>
+        <v>-5.3</v>
       </c>
       <c r="P350" s="4" t="n">
         <v>-1.22</v>
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="I351" s="4" t="n">
-        <v>-17.69</v>
+        <v>-17.7</v>
       </c>
       <c r="J351" s="4" t="n">
         <v>0.4</v>
@@ -36817,13 +36817,13 @@
         </is>
       </c>
       <c r="M351" s="4" t="n">
-        <v>-20.71</v>
+        <v>-20.73</v>
       </c>
       <c r="N351" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O351" s="4" t="n">
-        <v>-17.69</v>
+        <v>-17.7</v>
       </c>
       <c r="P351" s="4" t="n">
         <v>-1.7</v>
@@ -36905,7 +36905,7 @@
         </is>
       </c>
       <c r="I352" s="4" t="n">
-        <v>-51.49</v>
+        <v>-51.5</v>
       </c>
       <c r="J352" s="4" t="n">
         <v>0</v>
@@ -36919,13 +36919,13 @@
         </is>
       </c>
       <c r="M352" s="4" t="n">
-        <v>-53.98</v>
+        <v>-53.99</v>
       </c>
       <c r="N352" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O352" s="4" t="n">
-        <v>-51.49</v>
+        <v>-51.5</v>
       </c>
       <c r="P352" s="4" t="n">
         <v>-1.2</v>
@@ -36956,10 +36956,10 @@
         <v>0</v>
       </c>
       <c r="AB352" s="4" t="n">
-        <v>24.26</v>
+        <v>24.25</v>
       </c>
       <c r="AC352" s="4" t="n">
-        <v>75.73999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="AD352" s="4" t="n">
         <v>0</v>
@@ -37007,7 +37007,7 @@
         </is>
       </c>
       <c r="I353" s="4" t="n">
-        <v>-43.12</v>
+        <v>-43.13</v>
       </c>
       <c r="J353" s="4" t="n">
         <v>0</v>
@@ -37021,13 +37021,13 @@
         </is>
       </c>
       <c r="M353" s="4" t="n">
-        <v>-43.68</v>
+        <v>-43.69</v>
       </c>
       <c r="N353" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O353" s="4" t="n">
-        <v>-43.12</v>
+        <v>-43.13</v>
       </c>
       <c r="P353" s="4" t="n">
         <v>0</v>
@@ -37058,10 +37058,10 @@
         <v>0</v>
       </c>
       <c r="AB353" s="4" t="n">
-        <v>28.44</v>
+        <v>28.43</v>
       </c>
       <c r="AC353" s="4" t="n">
-        <v>71.56</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="AD353" s="4" t="n">
         <v>0</v>
@@ -37109,7 +37109,7 @@
         </is>
       </c>
       <c r="I354" s="4" t="n">
-        <v>-34.66</v>
+        <v>-34.68</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>0</v>
@@ -37123,13 +37123,13 @@
         </is>
       </c>
       <c r="M354" s="4" t="n">
-        <v>-31.71</v>
+        <v>-31.72</v>
       </c>
       <c r="N354" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O354" s="4" t="n">
-        <v>-34.66</v>
+        <v>-34.68</v>
       </c>
       <c r="P354" s="4" t="n">
         <v>-2.65</v>
@@ -37160,10 +37160,10 @@
         <v>0</v>
       </c>
       <c r="AB354" s="4" t="n">
-        <v>32.67</v>
+        <v>32.66</v>
       </c>
       <c r="AC354" s="4" t="n">
-        <v>67.33</v>
+        <v>67.34</v>
       </c>
       <c r="AD354" s="4" t="n">
         <v>0</v>
@@ -37211,7 +37211,7 @@
         </is>
       </c>
       <c r="I355" s="4" t="n">
-        <v>-16.71</v>
+        <v>-16.72</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>0.5</v>
@@ -37225,13 +37225,13 @@
         </is>
       </c>
       <c r="M355" s="4" t="n">
-        <v>-17.47</v>
+        <v>-17.48</v>
       </c>
       <c r="N355" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O355" s="4" t="n">
-        <v>-16.71</v>
+        <v>-16.72</v>
       </c>
       <c r="P355" s="4" t="n">
         <v>-1.04</v>
@@ -37415,7 +37415,7 @@
         </is>
       </c>
       <c r="I357" s="4" t="n">
-        <v>-28.9</v>
+        <v>-28.89</v>
       </c>
       <c r="J357" s="4" t="n">
         <v>0</v>
@@ -37435,7 +37435,7 @@
         <v>5.28</v>
       </c>
       <c r="O357" s="4" t="n">
-        <v>-28.9</v>
+        <v>-28.89</v>
       </c>
       <c r="P357" s="4" t="n">
         <v>-1.49</v>
@@ -37823,7 +37823,7 @@
         </is>
       </c>
       <c r="I361" s="4" t="n">
-        <v>18.11</v>
+        <v>18.12</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>99.7</v>
@@ -37843,7 +37843,7 @@
         <v>5.28</v>
       </c>
       <c r="O361" s="4" t="n">
-        <v>18.11</v>
+        <v>18.12</v>
       </c>
       <c r="P361" s="4" t="n">
         <v>2.46</v>
@@ -37925,13 +37925,13 @@
         </is>
       </c>
       <c r="I362" s="4" t="n">
-        <v>-2.58</v>
+        <v>-2.56</v>
       </c>
       <c r="J362" s="4" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="K362" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -37982,10 +37982,10 @@
         <v>0</v>
       </c>
       <c r="AB362" s="4" t="n">
-        <v>48.71</v>
+        <v>48.72</v>
       </c>
       <c r="AC362" s="4" t="n">
-        <v>51.29</v>
+        <v>51.28</v>
       </c>
       <c r="AD362" s="4" t="n">
         <v>0</v>
@@ -38543,7 +38543,7 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="J368" s="4" t="n">
         <v>73.5</v>
@@ -38600,10 +38600,10 @@
         <v>0</v>
       </c>
       <c r="AB368" s="4" t="n">
-        <v>51.5</v>
+        <v>51.51</v>
       </c>
       <c r="AC368" s="4" t="n">
-        <v>48.5</v>
+        <v>48.49</v>
       </c>
       <c r="AD368" s="4" t="n">
         <v>0</v>
@@ -38651,7 +38651,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>64</v>
@@ -38864,10 +38864,10 @@
         <v>9.130000000000001</v>
       </c>
       <c r="J371" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="K371" s="4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>17.62</v>
+        <v>17.63</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>99.59999999999999</v>
@@ -39805,7 +39805,7 @@
         <v>5.28</v>
       </c>
       <c r="O380" s="4" t="n">
-        <v>17.62</v>
+        <v>17.63</v>
       </c>
       <c r="P380" s="4" t="n">
         <v>-0.57</v>
@@ -39883,7 +39883,7 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>-2.91</v>
+        <v>-2.9</v>
       </c>
       <c r="J381" s="4" t="n">
         <v>26.9</v>
@@ -40497,7 +40497,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>-16.71</v>
+        <v>-16.77</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>0.5</v>
@@ -40554,10 +40554,10 @@
         <v>0</v>
       </c>
       <c r="AB387" s="4" t="n">
-        <v>41.65</v>
+        <v>41.61</v>
       </c>
       <c r="AC387" s="4" t="n">
-        <v>58.35</v>
+        <v>58.39</v>
       </c>
       <c r="AD387" s="4" t="n">
         <v>0</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="I389" s="4" t="n">
-        <v>-53.9</v>
+        <v>-53.92</v>
       </c>
       <c r="J389" s="4" t="n">
         <v>0</v>
@@ -40717,13 +40717,13 @@
         </is>
       </c>
       <c r="M389" s="4" t="n">
-        <v>-54.19</v>
+        <v>-54.21</v>
       </c>
       <c r="N389" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O389" s="4" t="n">
-        <v>-53.9</v>
+        <v>-53.92</v>
       </c>
       <c r="P389" s="4" t="n">
         <v>-1.63</v>
@@ -40754,10 +40754,10 @@
         <v>0</v>
       </c>
       <c r="AB389" s="4" t="n">
-        <v>23.05</v>
+        <v>23.04</v>
       </c>
       <c r="AC389" s="4" t="n">
-        <v>76.95</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="AD389" s="4" t="n">
         <v>0</v>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="I390" s="4" t="n">
-        <v>-31.23</v>
+        <v>-31.25</v>
       </c>
       <c r="J390" s="4" t="n">
         <v>0</v>
@@ -40819,13 +40819,13 @@
         </is>
       </c>
       <c r="M390" s="4" t="n">
-        <v>-30.03</v>
+        <v>-30.05</v>
       </c>
       <c r="N390" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O390" s="4" t="n">
-        <v>-31.23</v>
+        <v>-31.25</v>
       </c>
       <c r="P390" s="4" t="n">
         <v>-1.28</v>
@@ -40856,10 +40856,10 @@
         <v>0</v>
       </c>
       <c r="AB390" s="4" t="n">
-        <v>34.38</v>
+        <v>34.37</v>
       </c>
       <c r="AC390" s="4" t="n">
-        <v>65.62</v>
+        <v>65.63</v>
       </c>
       <c r="AD390" s="4" t="n">
         <v>0</v>
@@ -40907,7 +40907,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>-33.01</v>
+        <v>-33.03</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>0</v>
@@ -40921,13 +40921,13 @@
         </is>
       </c>
       <c r="M391" s="4" t="n">
-        <v>-31.84</v>
+        <v>-31.86</v>
       </c>
       <c r="N391" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O391" s="4" t="n">
-        <v>-33.01</v>
+        <v>-33.03</v>
       </c>
       <c r="P391" s="4" t="n">
         <v>-2.34</v>
@@ -40958,10 +40958,10 @@
         <v>0</v>
       </c>
       <c r="AB391" s="4" t="n">
-        <v>33.49</v>
+        <v>33.48</v>
       </c>
       <c r="AC391" s="4" t="n">
-        <v>66.51000000000001</v>
+        <v>66.52</v>
       </c>
       <c r="AD391" s="4" t="n">
         <v>0</v>
@@ -41009,7 +41009,7 @@
         </is>
       </c>
       <c r="I392" s="4" t="n">
-        <v>-15.38</v>
+        <v>-15.4</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>0.6</v>
@@ -41023,13 +41023,13 @@
         </is>
       </c>
       <c r="M392" s="4" t="n">
-        <v>-18.81</v>
+        <v>-18.83</v>
       </c>
       <c r="N392" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O392" s="4" t="n">
-        <v>-15.38</v>
+        <v>-15.4</v>
       </c>
       <c r="P392" s="4" t="n">
         <v>-1.26</v>
@@ -41060,10 +41060,10 @@
         <v>0</v>
       </c>
       <c r="AB392" s="4" t="n">
-        <v>42.31</v>
+        <v>42.3</v>
       </c>
       <c r="AC392" s="4" t="n">
-        <v>57.69</v>
+        <v>57.7</v>
       </c>
       <c r="AD392" s="4" t="n">
         <v>0</v>
@@ -41107,7 +41107,7 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>-11.03</v>
+        <v>-11.05</v>
       </c>
       <c r="J393" s="4" t="n">
         <v>1.8</v>
@@ -41121,13 +41121,13 @@
         </is>
       </c>
       <c r="M393" s="4" t="n">
-        <v>-16.89</v>
+        <v>-16.91</v>
       </c>
       <c r="N393" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>-11.07</v>
+        <v>-11.09</v>
       </c>
       <c r="P393" s="4" t="n">
         <v>0.96</v>
@@ -41211,7 +41211,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>-19.25</v>
+        <v>-19.27</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>0.3</v>
@@ -41225,13 +41225,13 @@
         </is>
       </c>
       <c r="M394" s="4" t="n">
-        <v>-21.85</v>
+        <v>-21.87</v>
       </c>
       <c r="N394" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O394" s="4" t="n">
-        <v>-19.25</v>
+        <v>-19.27</v>
       </c>
       <c r="P394" s="4" t="n">
         <v>-2.06</v>
@@ -41262,10 +41262,10 @@
         <v>0</v>
       </c>
       <c r="AB394" s="4" t="n">
-        <v>40.37</v>
+        <v>40.36</v>
       </c>
       <c r="AC394" s="4" t="n">
-        <v>59.63</v>
+        <v>59.64</v>
       </c>
       <c r="AD394" s="4" t="n">
         <v>0</v>
@@ -41313,7 +41313,7 @@
         </is>
       </c>
       <c r="I395" s="4" t="n">
-        <v>-15.77</v>
+        <v>-15.79</v>
       </c>
       <c r="J395" s="4" t="n">
         <v>0.6</v>
@@ -41327,13 +41327,13 @@
         </is>
       </c>
       <c r="M395" s="4" t="n">
-        <v>-18.23</v>
+        <v>-18.25</v>
       </c>
       <c r="N395" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O395" s="4" t="n">
-        <v>-15.77</v>
+        <v>-15.79</v>
       </c>
       <c r="P395" s="4" t="n">
         <v>-0.6</v>
@@ -41364,10 +41364,10 @@
         <v>0</v>
       </c>
       <c r="AB395" s="4" t="n">
-        <v>42.11</v>
+        <v>42.1</v>
       </c>
       <c r="AC395" s="4" t="n">
-        <v>57.89</v>
+        <v>57.9</v>
       </c>
       <c r="AD395" s="4" t="n">
         <v>0</v>
@@ -41415,7 +41415,7 @@
         </is>
       </c>
       <c r="I396" s="4" t="n">
-        <v>-19.02</v>
+        <v>-19.04</v>
       </c>
       <c r="J396" s="4" t="n">
         <v>0.3</v>
@@ -41429,13 +41429,13 @@
         </is>
       </c>
       <c r="M396" s="4" t="n">
-        <v>-16.02</v>
+        <v>-16.04</v>
       </c>
       <c r="N396" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O396" s="4" t="n">
-        <v>-19.02</v>
+        <v>-19.04</v>
       </c>
       <c r="P396" s="4" t="n">
         <v>-2.43</v>
@@ -41466,10 +41466,10 @@
         <v>0</v>
       </c>
       <c r="AB396" s="4" t="n">
-        <v>40.49</v>
+        <v>40.48</v>
       </c>
       <c r="AC396" s="4" t="n">
-        <v>59.51</v>
+        <v>59.52</v>
       </c>
       <c r="AD396" s="4" t="n">
         <v>0</v>
@@ -41513,7 +41513,7 @@
         </is>
       </c>
       <c r="I397" s="4" t="n">
-        <v>-9.66</v>
+        <v>-9.68</v>
       </c>
       <c r="J397" s="4" t="n">
         <v>5</v>
@@ -41523,17 +41523,17 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="M397" s="4" t="n">
-        <v>-14.88</v>
+        <v>-14.9</v>
       </c>
       <c r="N397" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O397" s="4" t="n">
-        <v>-9.66</v>
+        <v>-9.68</v>
       </c>
       <c r="P397" s="4" t="n">
         <v>0.24</v>
@@ -41564,10 +41564,10 @@
         <v>0</v>
       </c>
       <c r="AB397" s="4" t="n">
-        <v>45.17</v>
+        <v>45.16</v>
       </c>
       <c r="AC397" s="4" t="n">
-        <v>54.83</v>
+        <v>54.84</v>
       </c>
       <c r="AD397" s="4" t="n">
         <v>0</v>
@@ -41615,7 +41615,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>-43.21</v>
+        <v>-43.22</v>
       </c>
       <c r="J398" s="4" t="n">
         <v>0</v>
@@ -41629,13 +41629,13 @@
         </is>
       </c>
       <c r="M398" s="4" t="n">
-        <v>-44.2</v>
+        <v>-44.21</v>
       </c>
       <c r="N398" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O398" s="4" t="n">
-        <v>-43.21</v>
+        <v>-43.22</v>
       </c>
       <c r="P398" s="4" t="n">
         <v>-2.58</v>
@@ -41666,10 +41666,10 @@
         <v>0</v>
       </c>
       <c r="AB398" s="4" t="n">
-        <v>28.4</v>
+        <v>28.39</v>
       </c>
       <c r="AC398" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>71.61</v>
       </c>
       <c r="AD398" s="4" t="n">
         <v>0</v>
@@ -41764,10 +41764,10 @@
         <v>0</v>
       </c>
       <c r="AB399" s="4" t="n">
-        <v>43.82</v>
+        <v>43.81</v>
       </c>
       <c r="AC399" s="4" t="n">
-        <v>56.18</v>
+        <v>56.19</v>
       </c>
       <c r="AD399" s="4" t="n">
         <v>0</v>
@@ -41815,7 +41815,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>-15.45</v>
+        <v>-15.46</v>
       </c>
       <c r="J400" s="4" t="n">
         <v>0.6</v>
@@ -41829,13 +41829,13 @@
         </is>
       </c>
       <c r="M400" s="4" t="n">
-        <v>-18.8</v>
+        <v>-18.81</v>
       </c>
       <c r="N400" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O400" s="4" t="n">
-        <v>-15.45</v>
+        <v>-15.46</v>
       </c>
       <c r="P400" s="4" t="n">
         <v>-0.25</v>
@@ -41866,10 +41866,10 @@
         <v>0</v>
       </c>
       <c r="AB400" s="4" t="n">
-        <v>42.28</v>
+        <v>42.27</v>
       </c>
       <c r="AC400" s="4" t="n">
-        <v>57.72</v>
+        <v>57.73</v>
       </c>
       <c r="AD400" s="4" t="n">
         <v>0</v>
@@ -41917,7 +41917,7 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>-20.88</v>
+        <v>-20.89</v>
       </c>
       <c r="J401" s="4" t="n">
         <v>0.2</v>
@@ -41937,7 +41937,7 @@
         <v>5.28</v>
       </c>
       <c r="O401" s="4" t="n">
-        <v>-20.88</v>
+        <v>-20.89</v>
       </c>
       <c r="P401" s="4" t="n">
         <v>-1.91</v>
@@ -41968,10 +41968,10 @@
         <v>0</v>
       </c>
       <c r="AB401" s="4" t="n">
-        <v>39.56</v>
+        <v>39.55</v>
       </c>
       <c r="AC401" s="4" t="n">
-        <v>60.44</v>
+        <v>60.45</v>
       </c>
       <c r="AD401" s="4" t="n">
         <v>0</v>
@@ -42019,7 +42019,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>-15.14</v>
+        <v>-15.15</v>
       </c>
       <c r="J402" s="4" t="n">
         <v>0.6</v>
@@ -42039,7 +42039,7 @@
         <v>5.28</v>
       </c>
       <c r="O402" s="4" t="n">
-        <v>-15.14</v>
+        <v>-15.15</v>
       </c>
       <c r="P402" s="4" t="n">
         <v>-2.33</v>
@@ -42121,7 +42121,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>-18.79</v>
+        <v>-18.8</v>
       </c>
       <c r="J403" s="4" t="n">
         <v>0.3</v>
@@ -42135,13 +42135,13 @@
         </is>
       </c>
       <c r="M403" s="4" t="n">
-        <v>-18.57</v>
+        <v>-18.58</v>
       </c>
       <c r="N403" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O403" s="4" t="n">
-        <v>-18.79</v>
+        <v>-18.8</v>
       </c>
       <c r="P403" s="4" t="n">
         <v>-2.94</v>
@@ -42223,7 +42223,7 @@
         </is>
       </c>
       <c r="I404" s="4" t="n">
-        <v>40.97</v>
+        <v>40.96</v>
       </c>
       <c r="J404" s="4" t="n">
         <v>100</v>
@@ -42237,13 +42237,13 @@
         </is>
       </c>
       <c r="M404" s="4" t="n">
-        <v>30.76</v>
+        <v>30.75</v>
       </c>
       <c r="N404" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O404" s="4" t="n">
-        <v>40.97</v>
+        <v>40.96</v>
       </c>
       <c r="P404" s="4" t="n">
         <v>1.84</v>
@@ -42274,10 +42274,10 @@
         <v>0</v>
       </c>
       <c r="AB404" s="4" t="n">
-        <v>70.48999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="AC404" s="4" t="n">
-        <v>29.51</v>
+        <v>29.52</v>
       </c>
       <c r="AD404" s="4" t="n">
         <v>0</v>
@@ -42321,7 +42321,7 @@
         </is>
       </c>
       <c r="I405" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.89</v>
       </c>
       <c r="J405" s="4" t="n">
         <v>0.4</v>
@@ -42335,13 +42335,13 @@
         </is>
       </c>
       <c r="M405" s="4" t="n">
-        <v>-21.27</v>
+        <v>-21.28</v>
       </c>
       <c r="N405" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O405" s="4" t="n">
-        <v>-17.88</v>
+        <v>-17.89</v>
       </c>
       <c r="P405" s="4" t="n">
         <v>-2.72</v>
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="I406" s="4" t="n">
-        <v>-6.71</v>
+        <v>-6.72</v>
       </c>
       <c r="J406" s="4" t="n">
         <v>13.4</v>
@@ -42433,13 +42433,13 @@
         </is>
       </c>
       <c r="M406" s="4" t="n">
-        <v>-12.25</v>
+        <v>-12.26</v>
       </c>
       <c r="N406" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O406" s="4" t="n">
-        <v>-6.71</v>
+        <v>-6.72</v>
       </c>
       <c r="P406" s="4" t="n">
         <v>-1.92</v>
@@ -42517,7 +42517,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="n">
-        <v>-13.1</v>
+        <v>-13.11</v>
       </c>
       <c r="J407" s="4" t="n">
         <v>0.9</v>
@@ -42531,13 +42531,13 @@
         </is>
       </c>
       <c r="M407" s="4" t="n">
-        <v>-16.93</v>
+        <v>-16.94</v>
       </c>
       <c r="N407" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O407" s="4" t="n">
-        <v>-13.1</v>
+        <v>-13.11</v>
       </c>
       <c r="P407" s="4" t="n">
         <v>-1.52</v>
@@ -42619,7 +42619,7 @@
         </is>
       </c>
       <c r="I408" s="4" t="n">
-        <v>-27.46</v>
+        <v>-27.47</v>
       </c>
       <c r="J408" s="4" t="n">
         <v>0</v>
@@ -42633,13 +42633,13 @@
         </is>
       </c>
       <c r="M408" s="4" t="n">
-        <v>-29.62</v>
+        <v>-29.63</v>
       </c>
       <c r="N408" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O408" s="4" t="n">
-        <v>-27.46</v>
+        <v>-27.47</v>
       </c>
       <c r="P408" s="4" t="n">
         <v>-2.36</v>
@@ -42721,7 +42721,7 @@
         </is>
       </c>
       <c r="I409" s="4" t="n">
-        <v>-18.81</v>
+        <v>-18.82</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>0.3</v>
@@ -42735,13 +42735,13 @@
         </is>
       </c>
       <c r="M409" s="4" t="n">
-        <v>-18.57</v>
+        <v>-18.58</v>
       </c>
       <c r="N409" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O409" s="4" t="n">
-        <v>-18.81</v>
+        <v>-18.82</v>
       </c>
       <c r="P409" s="4" t="n">
         <v>0</v>
@@ -42823,7 +42823,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="n">
-        <v>-40.76</v>
+        <v>-40.77</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>0</v>
@@ -42837,13 +42837,13 @@
         </is>
       </c>
       <c r="M410" s="4" t="n">
-        <v>-42.22</v>
+        <v>-42.23</v>
       </c>
       <c r="N410" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O410" s="4" t="n">
-        <v>-40.76</v>
+        <v>-40.77</v>
       </c>
       <c r="P410" s="4" t="n">
         <v>-2.49</v>
@@ -42874,10 +42874,10 @@
         <v>0</v>
       </c>
       <c r="AB410" s="4" t="n">
-        <v>29.62</v>
+        <v>29.61</v>
       </c>
       <c r="AC410" s="4" t="n">
-        <v>70.38</v>
+        <v>70.39</v>
       </c>
       <c r="AD410" s="4" t="n">
         <v>0</v>
@@ -42925,7 +42925,7 @@
         </is>
       </c>
       <c r="I411" s="4" t="n">
-        <v>-19.74</v>
+        <v>-19.75</v>
       </c>
       <c r="J411" s="4" t="n">
         <v>0.2</v>
@@ -42945,7 +42945,7 @@
         <v>5.28</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>-19.74</v>
+        <v>-19.75</v>
       </c>
       <c r="P411" s="4" t="n">
         <v>-1.94</v>
@@ -43027,13 +43027,13 @@
         </is>
       </c>
       <c r="I412" s="4" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J412" s="4" t="n">
-        <v>65.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K412" s="4" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -43041,13 +43041,13 @@
         </is>
       </c>
       <c r="M412" s="4" t="n">
-        <v>-8.31</v>
+        <v>-8.32</v>
       </c>
       <c r="N412" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>-1.59</v>
+        <v>-1.6</v>
       </c>
       <c r="P412" s="4" t="n">
         <v>-0.3</v>
@@ -43084,10 +43084,10 @@
         <v>0</v>
       </c>
       <c r="AB412" s="4" t="n">
-        <v>50.48</v>
+        <v>50.47</v>
       </c>
       <c r="AC412" s="4" t="n">
-        <v>49.52</v>
+        <v>49.53</v>
       </c>
       <c r="AD412" s="4" t="n">
         <v>0</v>
@@ -43135,7 +43135,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="n">
-        <v>36.52</v>
+        <v>36.51</v>
       </c>
       <c r="J413" s="4" t="n">
         <v>100</v>
@@ -43149,13 +43149,13 @@
         </is>
       </c>
       <c r="M413" s="4" t="n">
-        <v>26.73</v>
+        <v>26.72</v>
       </c>
       <c r="N413" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O413" s="4" t="n">
-        <v>36.52</v>
+        <v>36.51</v>
       </c>
       <c r="P413" s="4" t="n">
         <v>0</v>
@@ -43186,10 +43186,10 @@
         <v>0</v>
       </c>
       <c r="AB413" s="4" t="n">
-        <v>68.26000000000001</v>
+        <v>68.25</v>
       </c>
       <c r="AC413" s="4" t="n">
-        <v>31.74</v>
+        <v>31.75</v>
       </c>
       <c r="AD413" s="4" t="n">
         <v>0</v>
@@ -43251,7 +43251,7 @@
         </is>
       </c>
       <c r="M414" s="4" t="n">
-        <v>-16.4</v>
+        <v>-16.41</v>
       </c>
       <c r="N414" s="4" t="n">
         <v>5.28</v>
@@ -43339,7 +43339,7 @@
         </is>
       </c>
       <c r="I415" s="4" t="n">
-        <v>71.05</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="J415" s="4" t="n">
         <v>100</v>
@@ -43359,7 +43359,7 @@
         <v>5.28</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>71.05</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="P415" s="4" t="n">
         <v>0</v>
@@ -43390,10 +43390,10 @@
         <v>0</v>
       </c>
       <c r="AB415" s="4" t="n">
-        <v>85.53</v>
+        <v>85.52</v>
       </c>
       <c r="AC415" s="4" t="n">
-        <v>14.47</v>
+        <v>14.48</v>
       </c>
       <c r="AD415" s="4" t="n">
         <v>0</v>
@@ -43437,7 +43437,7 @@
         </is>
       </c>
       <c r="I416" s="4" t="n">
-        <v>-42.8</v>
+        <v>-42.81</v>
       </c>
       <c r="J416" s="4" t="n">
         <v>0</v>
@@ -43451,13 +43451,13 @@
         </is>
       </c>
       <c r="M416" s="4" t="n">
-        <v>-46.58</v>
+        <v>-46.59</v>
       </c>
       <c r="N416" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>-42.8</v>
+        <v>-42.81</v>
       </c>
       <c r="P416" s="4" t="n">
         <v>-2.39</v>
@@ -43488,10 +43488,10 @@
         <v>0</v>
       </c>
       <c r="AB416" s="4" t="n">
-        <v>28.6</v>
+        <v>28.59</v>
       </c>
       <c r="AC416" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>71.41</v>
       </c>
       <c r="AD416" s="4" t="n">
         <v>0</v>
@@ -43539,7 +43539,7 @@
         </is>
       </c>
       <c r="I417" s="4" t="n">
-        <v>49.19</v>
+        <v>49.18</v>
       </c>
       <c r="J417" s="4" t="n">
         <v>100</v>
@@ -43553,13 +43553,13 @@
         </is>
       </c>
       <c r="M417" s="4" t="n">
-        <v>36.57</v>
+        <v>36.56</v>
       </c>
       <c r="N417" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O417" s="4" t="n">
-        <v>49.19</v>
+        <v>49.18</v>
       </c>
       <c r="P417" s="4" t="n">
         <v>1.31</v>
@@ -43637,7 +43637,7 @@
         </is>
       </c>
       <c r="I418" s="4" t="n">
-        <v>-12.37</v>
+        <v>-12.38</v>
       </c>
       <c r="J418" s="4" t="n">
         <v>1.1</v>
@@ -43651,13 +43651,13 @@
         </is>
       </c>
       <c r="M418" s="4" t="n">
-        <v>-16.91</v>
+        <v>-16.92</v>
       </c>
       <c r="N418" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O418" s="4" t="n">
-        <v>-12.37</v>
+        <v>-12.38</v>
       </c>
       <c r="P418" s="4" t="n">
         <v>-2.06</v>
@@ -43688,10 +43688,10 @@
         <v>0</v>
       </c>
       <c r="AB418" s="4" t="n">
-        <v>43.82</v>
+        <v>43.81</v>
       </c>
       <c r="AC418" s="4" t="n">
-        <v>56.18</v>
+        <v>56.19</v>
       </c>
       <c r="AD418" s="4" t="n">
         <v>0</v>
@@ -43735,7 +43735,7 @@
         </is>
       </c>
       <c r="I419" s="4" t="n">
-        <v>-13.08</v>
+        <v>-13.09</v>
       </c>
       <c r="J419" s="4" t="n">
         <v>1</v>
@@ -43749,13 +43749,13 @@
         </is>
       </c>
       <c r="M419" s="4" t="n">
-        <v>-17.49</v>
+        <v>-17.5</v>
       </c>
       <c r="N419" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O419" s="4" t="n">
-        <v>-13.08</v>
+        <v>-13.09</v>
       </c>
       <c r="P419" s="4" t="n">
         <v>-0.8100000000000001</v>
@@ -43786,10 +43786,10 @@
         <v>0</v>
       </c>
       <c r="AB419" s="4" t="n">
-        <v>43.46</v>
+        <v>43.45</v>
       </c>
       <c r="AC419" s="4" t="n">
-        <v>56.54</v>
+        <v>56.55</v>
       </c>
       <c r="AD419" s="4" t="n">
         <v>0</v>
@@ -43833,7 +43833,7 @@
         </is>
       </c>
       <c r="I420" s="4" t="n">
-        <v>-2.37</v>
+        <v>-2.38</v>
       </c>
       <c r="J420" s="4" t="n">
         <v>28.9</v>
@@ -43853,7 +43853,7 @@
         <v>5.28</v>
       </c>
       <c r="O420" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.92</v>
       </c>
       <c r="P420" s="4" t="n">
         <v>-0.75</v>
@@ -43941,7 +43941,7 @@
         </is>
       </c>
       <c r="I421" s="4" t="n">
-        <v>-12.74</v>
+        <v>-12.75</v>
       </c>
       <c r="J421" s="4" t="n">
         <v>1</v>
@@ -43955,13 +43955,13 @@
         </is>
       </c>
       <c r="M421" s="4" t="n">
-        <v>-11.82</v>
+        <v>-11.83</v>
       </c>
       <c r="N421" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O421" s="4" t="n">
-        <v>-12.74</v>
+        <v>-12.75</v>
       </c>
       <c r="P421" s="4" t="n">
         <v>-1.72</v>
@@ -44057,7 +44057,7 @@
         </is>
       </c>
       <c r="M422" s="4" t="n">
-        <v>-18.05</v>
+        <v>-18.06</v>
       </c>
       <c r="N422" s="4" t="n">
         <v>5.28</v>
@@ -44145,7 +44145,7 @@
         </is>
       </c>
       <c r="I423" s="4" t="n">
-        <v>-22.69</v>
+        <v>-22.7</v>
       </c>
       <c r="J423" s="4" t="n">
         <v>0.1</v>
@@ -44159,13 +44159,13 @@
         </is>
       </c>
       <c r="M423" s="4" t="n">
-        <v>-19.17</v>
+        <v>-19.18</v>
       </c>
       <c r="N423" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O423" s="4" t="n">
-        <v>-22.69</v>
+        <v>-22.7</v>
       </c>
       <c r="P423" s="4" t="n">
         <v>-3.11</v>
@@ -44196,10 +44196,10 @@
         <v>0</v>
       </c>
       <c r="AB423" s="4" t="n">
-        <v>38.66</v>
+        <v>38.65</v>
       </c>
       <c r="AC423" s="4" t="n">
-        <v>61.34</v>
+        <v>61.35</v>
       </c>
       <c r="AD423" s="4" t="n">
         <v>0</v>
@@ -44247,7 +44247,7 @@
         </is>
       </c>
       <c r="I424" s="4" t="n">
-        <v>-13.96</v>
+        <v>-13.97</v>
       </c>
       <c r="J424" s="4" t="n">
         <v>0.8</v>
@@ -44267,7 +44267,7 @@
         <v>5.28</v>
       </c>
       <c r="O424" s="4" t="n">
-        <v>-13.96</v>
+        <v>-13.97</v>
       </c>
       <c r="P424" s="4" t="n">
         <v>-1.33</v>
@@ -44349,7 +44349,7 @@
         </is>
       </c>
       <c r="I425" s="4" t="n">
-        <v>16.16</v>
+        <v>16.2</v>
       </c>
       <c r="J425" s="4" t="n">
         <v>99.5</v>
@@ -44369,7 +44369,7 @@
         <v>5.28</v>
       </c>
       <c r="O425" s="4" t="n">
-        <v>20.07</v>
+        <v>20.06</v>
       </c>
       <c r="P425" s="4" t="n">
         <v>0.34</v>
@@ -44406,10 +44406,10 @@
         <v>0</v>
       </c>
       <c r="AB425" s="4" t="n">
-        <v>58.08</v>
+        <v>58.1</v>
       </c>
       <c r="AC425" s="4" t="n">
-        <v>41.92</v>
+        <v>41.9</v>
       </c>
       <c r="AD425" s="4" t="n">
         <v>0</v>
@@ -44457,7 +44457,7 @@
         </is>
       </c>
       <c r="I426" s="4" t="n">
-        <v>53.98</v>
+        <v>53.97</v>
       </c>
       <c r="J426" s="4" t="n">
         <v>100</v>
@@ -44471,13 +44471,13 @@
         </is>
       </c>
       <c r="M426" s="4" t="n">
-        <v>39.09</v>
+        <v>39.08</v>
       </c>
       <c r="N426" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O426" s="4" t="n">
-        <v>53.98</v>
+        <v>53.97</v>
       </c>
       <c r="P426" s="4" t="n">
         <v>0</v>
@@ -44555,7 +44555,7 @@
         </is>
       </c>
       <c r="I427" s="4" t="n">
-        <v>62.95</v>
+        <v>62.94</v>
       </c>
       <c r="J427" s="4" t="n">
         <v>100</v>
@@ -44569,13 +44569,13 @@
         </is>
       </c>
       <c r="M427" s="4" t="n">
-        <v>54.8</v>
+        <v>54.79</v>
       </c>
       <c r="N427" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O427" s="4" t="n">
-        <v>62.95</v>
+        <v>62.94</v>
       </c>
       <c r="P427" s="4" t="n">
         <v>1.56</v>
@@ -44657,7 +44657,7 @@
         </is>
       </c>
       <c r="I428" s="4" t="n">
-        <v>-18.84</v>
+        <v>-18.85</v>
       </c>
       <c r="J428" s="4" t="n">
         <v>0.3</v>
@@ -44671,13 +44671,13 @@
         </is>
       </c>
       <c r="M428" s="4" t="n">
-        <v>-17.33</v>
+        <v>-17.34</v>
       </c>
       <c r="N428" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O428" s="4" t="n">
-        <v>-18.25</v>
+        <v>-18.26</v>
       </c>
       <c r="P428" s="4" t="n">
         <v>-1.61</v>
@@ -44755,7 +44755,7 @@
         </is>
       </c>
       <c r="I429" s="4" t="n">
-        <v>-8.34</v>
+        <v>-8.35</v>
       </c>
       <c r="J429" s="4" t="n">
         <v>8.5</v>
@@ -44769,13 +44769,13 @@
         </is>
       </c>
       <c r="M429" s="4" t="n">
-        <v>-12.17</v>
+        <v>-12.18</v>
       </c>
       <c r="N429" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O429" s="4" t="n">
-        <v>-8.34</v>
+        <v>-8.35</v>
       </c>
       <c r="P429" s="4" t="n">
         <v>-1.71</v>
@@ -44853,7 +44853,7 @@
         </is>
       </c>
       <c r="I430" s="4" t="n">
-        <v>46.07</v>
+        <v>46.06</v>
       </c>
       <c r="J430" s="4" t="n">
         <v>100</v>
@@ -44867,13 +44867,13 @@
         </is>
       </c>
       <c r="M430" s="4" t="n">
-        <v>40.96</v>
+        <v>40.95</v>
       </c>
       <c r="N430" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O430" s="4" t="n">
-        <v>46.07</v>
+        <v>46.06</v>
       </c>
       <c r="P430" s="4" t="n">
         <v>0</v>
@@ -44955,13 +44955,13 @@
         </is>
       </c>
       <c r="I431" s="4" t="n">
-        <v>8.039999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="J431" s="4" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="K431" s="4" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -44969,13 +44969,13 @@
         </is>
       </c>
       <c r="M431" s="4" t="n">
-        <v>-1.59</v>
+        <v>-1.6</v>
       </c>
       <c r="N431" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O431" s="4" t="n">
-        <v>11.14</v>
+        <v>11.13</v>
       </c>
       <c r="P431" s="4" t="n">
         <v>0.14</v>
@@ -45012,10 +45012,10 @@
         <v>0</v>
       </c>
       <c r="AB431" s="4" t="n">
-        <v>54.02</v>
+        <v>54.03</v>
       </c>
       <c r="AC431" s="4" t="n">
-        <v>45.98</v>
+        <v>45.97</v>
       </c>
       <c r="AD431" s="4" t="n">
         <v>0</v>
@@ -45059,13 +45059,13 @@
         </is>
       </c>
       <c r="I432" s="4" t="n">
-        <v>-0.82</v>
+        <v>-0.75</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>35</v>
+        <v>35.3</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>65</v>
+        <v>64.7</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         </is>
       </c>
       <c r="M432" s="4" t="n">
-        <v>-4.09</v>
+        <v>-4.1</v>
       </c>
       <c r="N432" s="4" t="n">
         <v>5.28</v>
@@ -45116,10 +45116,10 @@
         <v>0</v>
       </c>
       <c r="AB432" s="4" t="n">
-        <v>49.59</v>
+        <v>49.62</v>
       </c>
       <c r="AC432" s="4" t="n">
-        <v>50.41</v>
+        <v>50.38</v>
       </c>
       <c r="AD432" s="4" t="n">
         <v>0</v>
@@ -45167,7 +45167,7 @@
         </is>
       </c>
       <c r="I433" s="4" t="n">
-        <v>-16.01</v>
+        <v>-16.02</v>
       </c>
       <c r="J433" s="4" t="n">
         <v>0.5</v>
@@ -45181,13 +45181,13 @@
         </is>
       </c>
       <c r="M433" s="4" t="n">
-        <v>-19.2</v>
+        <v>-19.21</v>
       </c>
       <c r="N433" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O433" s="4" t="n">
-        <v>-16.01</v>
+        <v>-16.02</v>
       </c>
       <c r="P433" s="4" t="n">
         <v>0</v>
@@ -45269,7 +45269,7 @@
         </is>
       </c>
       <c r="I434" s="4" t="n">
-        <v>69.65000000000001</v>
+        <v>69.64</v>
       </c>
       <c r="J434" s="4" t="n">
         <v>100</v>
@@ -45283,13 +45283,13 @@
         </is>
       </c>
       <c r="M434" s="4" t="n">
-        <v>63.58</v>
+        <v>63.57</v>
       </c>
       <c r="N434" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O434" s="4" t="n">
-        <v>69.65000000000001</v>
+        <v>69.64</v>
       </c>
       <c r="P434" s="4" t="n">
         <v>0</v>
@@ -45387,7 +45387,7 @@
         <v>5.28</v>
       </c>
       <c r="O435" s="4" t="n">
-        <v>-13.55</v>
+        <v>-13.56</v>
       </c>
       <c r="P435" s="4" t="n">
         <v>-2.01</v>
@@ -45418,10 +45418,10 @@
         <v>0</v>
       </c>
       <c r="AB435" s="4" t="n">
-        <v>42.02</v>
+        <v>42.01</v>
       </c>
       <c r="AC435" s="4" t="n">
-        <v>55.8</v>
+        <v>55.81</v>
       </c>
       <c r="AD435" s="4" t="n">
         <v>2.18</v>
@@ -45873,7 +45873,7 @@
         </is>
       </c>
       <c r="I440" s="4" t="n">
-        <v>-3.57</v>
+        <v>-3.58</v>
       </c>
       <c r="J440" s="4" t="n">
         <v>24.3</v>
@@ -45981,13 +45981,13 @@
         </is>
       </c>
       <c r="I441" s="4" t="n">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="J441" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="K441" s="4" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -46038,10 +46038,10 @@
         <v>0</v>
       </c>
       <c r="AB441" s="4" t="n">
-        <v>51.84</v>
+        <v>51.86</v>
       </c>
       <c r="AC441" s="4" t="n">
-        <v>48.16</v>
+        <v>48.14</v>
       </c>
       <c r="AD441" s="4" t="n">
         <v>0</v>
@@ -46293,7 +46293,7 @@
         </is>
       </c>
       <c r="I444" s="4" t="n">
-        <v>-5.53</v>
+        <v>-5.52</v>
       </c>
       <c r="J444" s="4" t="n">
         <v>17.3</v>
@@ -46313,7 +46313,7 @@
         <v>5.28</v>
       </c>
       <c r="O444" s="4" t="n">
-        <v>-5.3</v>
+        <v>-5.29</v>
       </c>
       <c r="P444" s="4" t="n">
         <v>0.2</v>
@@ -47013,7 +47013,7 @@
         </is>
       </c>
       <c r="I451" s="4" t="n">
-        <v>35.67</v>
+        <v>35.66</v>
       </c>
       <c r="J451" s="4" t="n">
         <v>100</v>
@@ -47027,13 +47027,13 @@
         </is>
       </c>
       <c r="M451" s="4" t="n">
-        <v>19.97</v>
+        <v>19.96</v>
       </c>
       <c r="N451" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O451" s="4" t="n">
-        <v>35.69</v>
+        <v>35.68</v>
       </c>
       <c r="P451" s="4" t="n">
         <v>1.67</v>
@@ -47325,13 +47325,13 @@
         </is>
       </c>
       <c r="I454" s="4" t="n">
-        <v>6.13</v>
+        <v>6.15</v>
       </c>
       <c r="J454" s="4" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K454" s="4" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -47382,10 +47382,10 @@
         <v>0</v>
       </c>
       <c r="AB454" s="4" t="n">
-        <v>53.06</v>
+        <v>53.08</v>
       </c>
       <c r="AC454" s="4" t="n">
-        <v>46.94</v>
+        <v>46.92</v>
       </c>
       <c r="AD454" s="4" t="n">
         <v>0</v>
@@ -48671,7 +48671,7 @@
         </is>
       </c>
       <c r="I467" s="4" t="n">
-        <v>-18.29</v>
+        <v>-18.28</v>
       </c>
       <c r="J467" s="4" t="n">
         <v>0.3</v>
@@ -49281,13 +49281,13 @@
         </is>
       </c>
       <c r="I473" s="4" t="n">
-        <v>-0.54</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J473" s="4" t="n">
-        <v>36.5</v>
+        <v>37.7</v>
       </c>
       <c r="K473" s="4" t="n">
-        <v>63.5</v>
+        <v>62.3</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -49301,10 +49301,10 @@
         <v>5.28</v>
       </c>
       <c r="O473" s="4" t="n">
-        <v>-3.38</v>
+        <v>-3.39</v>
       </c>
       <c r="P473" s="4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="Q473" s="4" t="n">
         <v>4.11</v>
@@ -49338,10 +49338,10 @@
         <v>0</v>
       </c>
       <c r="AB473" s="4" t="n">
-        <v>48.07</v>
+        <v>48.06</v>
       </c>
       <c r="AC473" s="4" t="n">
-        <v>49.43</v>
+        <v>49.44</v>
       </c>
       <c r="AD473" s="4" t="n">
         <v>2.5</v>
@@ -49385,7 +49385,7 @@
         </is>
       </c>
       <c r="I474" s="4" t="n">
-        <v>-21.83</v>
+        <v>-21.86</v>
       </c>
       <c r="J474" s="4" t="n">
         <v>0.1</v>
@@ -49399,7 +49399,7 @@
         </is>
       </c>
       <c r="M474" s="4" t="n">
-        <v>-26.51</v>
+        <v>-26.52</v>
       </c>
       <c r="N474" s="4" t="n">
         <v>5.28</v>
@@ -49442,10 +49442,10 @@
         <v>0</v>
       </c>
       <c r="AB474" s="4" t="n">
-        <v>39.09</v>
+        <v>39.07</v>
       </c>
       <c r="AC474" s="4" t="n">
-        <v>60.91</v>
+        <v>60.93</v>
       </c>
       <c r="AD474" s="4" t="n">
         <v>0</v>
@@ -49493,7 +49493,7 @@
         </is>
       </c>
       <c r="I475" s="4" t="n">
-        <v>-17.59</v>
+        <v>-17.68</v>
       </c>
       <c r="J475" s="4" t="n">
         <v>0.4</v>
@@ -49507,13 +49507,13 @@
         </is>
       </c>
       <c r="M475" s="4" t="n">
-        <v>-27.15</v>
+        <v>-27.19</v>
       </c>
       <c r="N475" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O475" s="4" t="n">
-        <v>-24.92</v>
+        <v>-24.95</v>
       </c>
       <c r="P475" s="4" t="n">
         <v>-0.87</v>
@@ -49550,10 +49550,10 @@
         <v>0</v>
       </c>
       <c r="AB475" s="4" t="n">
-        <v>41.21</v>
+        <v>41.16</v>
       </c>
       <c r="AC475" s="4" t="n">
-        <v>58.79</v>
+        <v>58.84</v>
       </c>
       <c r="AD475" s="4" t="n">
         <v>0</v>
@@ -49825,7 +49825,7 @@
         <v>5.28</v>
       </c>
       <c r="O478" s="4" t="n">
-        <v>-6.28</v>
+        <v>-6.29</v>
       </c>
       <c r="P478" s="4" t="n">
         <v>-1.8</v>
@@ -49913,7 +49913,7 @@
         </is>
       </c>
       <c r="I479" s="4" t="n">
-        <v>12.18</v>
+        <v>12.16</v>
       </c>
       <c r="J479" s="4" t="n">
         <v>98.90000000000001</v>
@@ -49933,10 +49933,10 @@
         <v>5.28</v>
       </c>
       <c r="O479" s="4" t="n">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="P479" s="4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q479" s="4" t="n">
         <v>6.73</v>
@@ -49970,10 +49970,10 @@
         <v>0</v>
       </c>
       <c r="AB479" s="4" t="n">
-        <v>56.09</v>
+        <v>56.08</v>
       </c>
       <c r="AC479" s="4" t="n">
-        <v>43.91</v>
+        <v>43.92</v>
       </c>
       <c r="AD479" s="4" t="n">
         <v>0</v>
@@ -50017,13 +50017,13 @@
         </is>
       </c>
       <c r="I480" s="4" t="n">
-        <v>-2.09</v>
+        <v>-2.14</v>
       </c>
       <c r="J480" s="4" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="K480" s="4" t="n">
-        <v>70</v>
+        <v>70.2</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -50037,10 +50037,10 @@
         <v>5.28</v>
       </c>
       <c r="O480" s="4" t="n">
-        <v>-4.02</v>
+        <v>-4.11</v>
       </c>
       <c r="P480" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.18</v>
       </c>
       <c r="Q480" s="4" t="n">
         <v>-0.93</v>
@@ -50074,10 +50074,10 @@
         <v>0</v>
       </c>
       <c r="AB480" s="4" t="n">
-        <v>47.67</v>
+        <v>47.64</v>
       </c>
       <c r="AC480" s="4" t="n">
-        <v>49.7</v>
+        <v>49.73</v>
       </c>
       <c r="AD480" s="4" t="n">
         <v>2.63</v>
@@ -50125,7 +50125,7 @@
         </is>
       </c>
       <c r="I481" s="4" t="n">
-        <v>-20.28</v>
+        <v>-20.37</v>
       </c>
       <c r="J481" s="4" t="n">
         <v>0.2</v>
@@ -50139,13 +50139,13 @@
         </is>
       </c>
       <c r="M481" s="4" t="n">
-        <v>-30.63</v>
+        <v>-30.65</v>
       </c>
       <c r="N481" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O481" s="4" t="n">
-        <v>-28.65</v>
+        <v>-28.67</v>
       </c>
       <c r="P481" s="4" t="n">
         <v>-1.14</v>
@@ -50180,7 +50180,7 @@
         </is>
       </c>
       <c r="Z481" s="4" t="n">
-        <v>39.86</v>
+        <v>39.81</v>
       </c>
       <c r="AA481" s="4" t="n">
         <v>0.2</v>
@@ -50189,7 +50189,7 @@
         <v>0</v>
       </c>
       <c r="AC481" s="4" t="n">
-        <v>60.14</v>
+        <v>60.19</v>
       </c>
       <c r="AD481" s="4" t="n">
         <v>0</v>
@@ -50335,7 +50335,7 @@
         </is>
       </c>
       <c r="I483" s="4" t="n">
-        <v>-7.41</v>
+        <v>-7.43</v>
       </c>
       <c r="J483" s="4" t="n">
         <v>11.2</v>
@@ -50349,16 +50349,16 @@
         </is>
       </c>
       <c r="M483" s="4" t="n">
-        <v>-14.2</v>
+        <v>-14.22</v>
       </c>
       <c r="N483" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O483" s="4" t="n">
-        <v>-10.54</v>
+        <v>-10.52</v>
       </c>
       <c r="P483" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="Q483" s="4" t="n">
         <v>-1.09</v>
@@ -50392,10 +50392,10 @@
         <v>0</v>
       </c>
       <c r="AB483" s="4" t="n">
-        <v>46.3</v>
+        <v>46.28</v>
       </c>
       <c r="AC483" s="4" t="n">
-        <v>53.7</v>
+        <v>53.72</v>
       </c>
       <c r="AD483" s="4" t="n">
         <v>0</v>
@@ -50645,7 +50645,7 @@
         </is>
       </c>
       <c r="I486" s="4" t="n">
-        <v>28.81</v>
+        <v>28.84</v>
       </c>
       <c r="J486" s="4" t="n">
         <v>100</v>
@@ -50659,13 +50659,13 @@
         </is>
       </c>
       <c r="M486" s="4" t="n">
-        <v>28.39</v>
+        <v>28.4</v>
       </c>
       <c r="N486" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O486" s="4" t="n">
-        <v>35.51</v>
+        <v>35.52</v>
       </c>
       <c r="P486" s="4" t="n">
         <v>0.52</v>
@@ -50702,10 +50702,10 @@
         <v>0</v>
       </c>
       <c r="AB486" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>64.42</v>
       </c>
       <c r="AC486" s="4" t="n">
-        <v>35.6</v>
+        <v>35.58</v>
       </c>
       <c r="AD486" s="4" t="n">
         <v>0</v>
@@ -50753,13 +50753,13 @@
         </is>
       </c>
       <c r="I487" s="4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="J487" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="K487" s="4" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -50810,10 +50810,10 @@
         <v>0</v>
       </c>
       <c r="AB487" s="4" t="n">
-        <v>50.55</v>
+        <v>50.54</v>
       </c>
       <c r="AC487" s="4" t="n">
-        <v>49.45</v>
+        <v>49.46</v>
       </c>
       <c r="AD487" s="4" t="n">
         <v>0</v>
@@ -50877,10 +50877,10 @@
         <v>5.28</v>
       </c>
       <c r="O488" s="4" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="P488" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.36</v>
       </c>
       <c r="Q488" s="4" t="n">
         <v>0.44</v>
@@ -50914,10 +50914,10 @@
         <v>0</v>
       </c>
       <c r="AB488" s="4" t="n">
-        <v>51.89</v>
+        <v>51.9</v>
       </c>
       <c r="AC488" s="4" t="n">
-        <v>48.11</v>
+        <v>48.1</v>
       </c>
       <c r="AD488" s="4" t="n">
         <v>0</v>
@@ -50961,7 +50961,7 @@
         </is>
       </c>
       <c r="I489" s="4" t="n">
-        <v>9.08</v>
+        <v>9.09</v>
       </c>
       <c r="J489" s="4" t="n">
         <v>93.5</v>
@@ -51018,10 +51018,10 @@
         <v>0</v>
       </c>
       <c r="AB489" s="4" t="n">
-        <v>54.54</v>
+        <v>54.55</v>
       </c>
       <c r="AC489" s="4" t="n">
-        <v>45.46</v>
+        <v>45.45</v>
       </c>
       <c r="AD489" s="4" t="n">
         <v>0</v>
@@ -51069,7 +51069,7 @@
         </is>
       </c>
       <c r="I490" s="4" t="n">
-        <v>-12.31</v>
+        <v>-12.34</v>
       </c>
       <c r="J490" s="4" t="n">
         <v>1.1</v>
@@ -51130,10 +51130,10 @@
         <v>0</v>
       </c>
       <c r="AB490" s="4" t="n">
-        <v>42.29</v>
+        <v>42.28</v>
       </c>
       <c r="AC490" s="4" t="n">
-        <v>54.17</v>
+        <v>54.18</v>
       </c>
       <c r="AD490" s="4" t="n">
         <v>0</v>
@@ -51177,7 +51177,7 @@
         </is>
       </c>
       <c r="I491" s="4" t="n">
-        <v>-27.91</v>
+        <v>-27.81</v>
       </c>
       <c r="J491" s="4" t="n">
         <v>0</v>
@@ -51232,16 +51232,16 @@
         </is>
       </c>
       <c r="Z491" s="4" t="n">
-        <v>22.29</v>
+        <v>22.25</v>
       </c>
       <c r="AA491" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AB491" s="4" t="n">
-        <v>23.07</v>
+        <v>23.14</v>
       </c>
       <c r="AC491" s="4" t="n">
-        <v>50.98</v>
+        <v>50.95</v>
       </c>
       <c r="AD491" s="4" t="n">
         <v>3.66</v>
@@ -51285,13 +51285,13 @@
         </is>
       </c>
       <c r="I492" s="4" t="n">
-        <v>6.71</v>
+        <v>6.69</v>
       </c>
       <c r="J492" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="K492" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -51305,10 +51305,10 @@
         <v>5.28</v>
       </c>
       <c r="O492" s="4" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="P492" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Q492" s="4" t="n">
         <v>1.9</v>
@@ -51342,10 +51342,10 @@
         <v>0</v>
       </c>
       <c r="AB492" s="4" t="n">
-        <v>52.36</v>
+        <v>52.35</v>
       </c>
       <c r="AC492" s="4" t="n">
-        <v>45.77</v>
+        <v>45.78</v>
       </c>
       <c r="AD492" s="4" t="n">
         <v>1.87</v>
@@ -51393,7 +51393,7 @@
         </is>
       </c>
       <c r="I493" s="4" t="n">
-        <v>-5.65</v>
+        <v>-5.66</v>
       </c>
       <c r="J493" s="4" t="n">
         <v>16.9</v>
@@ -51515,16 +51515,16 @@
         </is>
       </c>
       <c r="M494" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="N494" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O494" s="4" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="P494" s="4" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="Q494" s="4" t="n">
         <v>4.2</v>
@@ -51813,13 +51813,13 @@
         </is>
       </c>
       <c r="I497" s="4" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="J497" s="4" t="n">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
       <c r="K497" s="4" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -51833,10 +51833,10 @@
         <v>5.28</v>
       </c>
       <c r="O497" s="4" t="n">
-        <v>-1.93</v>
+        <v>-1.97</v>
       </c>
       <c r="P497" s="4" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="Q497" s="4" t="n">
         <v>1.39</v>
@@ -51870,10 +51870,10 @@
         <v>0</v>
       </c>
       <c r="AB497" s="4" t="n">
-        <v>50.18</v>
+        <v>50.16</v>
       </c>
       <c r="AC497" s="4" t="n">
-        <v>48.25</v>
+        <v>48.27</v>
       </c>
       <c r="AD497" s="4" t="n">
         <v>1.57</v>
@@ -51917,7 +51917,7 @@
         </is>
       </c>
       <c r="I498" s="4" t="n">
-        <v>-31.31</v>
+        <v>-31.38</v>
       </c>
       <c r="J498" s="4" t="n">
         <v>0</v>
@@ -51974,10 +51974,10 @@
         <v>0</v>
       </c>
       <c r="AB498" s="4" t="n">
-        <v>34.34</v>
+        <v>34.31</v>
       </c>
       <c r="AC498" s="4" t="n">
-        <v>65.66</v>
+        <v>65.69</v>
       </c>
       <c r="AD498" s="4" t="n">
         <v>0</v>
@@ -52127,7 +52127,7 @@
         </is>
       </c>
       <c r="I500" s="4" t="n">
-        <v>23.55</v>
+        <v>23.57</v>
       </c>
       <c r="J500" s="4" t="n">
         <v>99.90000000000001</v>
@@ -52141,7 +52141,7 @@
         </is>
       </c>
       <c r="M500" s="4" t="n">
-        <v>17.34</v>
+        <v>17.33</v>
       </c>
       <c r="N500" s="4" t="n">
         <v>5.28</v>
@@ -52184,10 +52184,10 @@
         <v>0</v>
       </c>
       <c r="AB500" s="4" t="n">
-        <v>61.77</v>
+        <v>61.79</v>
       </c>
       <c r="AC500" s="4" t="n">
-        <v>38.23</v>
+        <v>38.21</v>
       </c>
       <c r="AD500" s="4" t="n">
         <v>0</v>
@@ -52339,7 +52339,7 @@
         </is>
       </c>
       <c r="I502" s="4" t="n">
-        <v>-17.62</v>
+        <v>-17.65</v>
       </c>
       <c r="J502" s="4" t="n">
         <v>0.4</v>
@@ -52394,7 +52394,7 @@
         </is>
       </c>
       <c r="Z502" s="4" t="n">
-        <v>41.19</v>
+        <v>41.17</v>
       </c>
       <c r="AA502" s="4" t="n">
         <v>0.4</v>
@@ -52403,7 +52403,7 @@
         <v>0</v>
       </c>
       <c r="AC502" s="4" t="n">
-        <v>58.81</v>
+        <v>58.83</v>
       </c>
       <c r="AD502" s="4" t="n">
         <v>0</v>
@@ -52451,7 +52451,7 @@
         </is>
       </c>
       <c r="I503" s="4" t="n">
-        <v>-26.18</v>
+        <v>-26.26</v>
       </c>
       <c r="J503" s="4" t="n">
         <v>0</v>
@@ -52465,13 +52465,13 @@
         </is>
       </c>
       <c r="M503" s="4" t="n">
-        <v>-25.13</v>
+        <v>-25.14</v>
       </c>
       <c r="N503" s="4" t="n">
         <v>5.28</v>
       </c>
       <c r="O503" s="4" t="n">
-        <v>-30.37</v>
+        <v>-30.38</v>
       </c>
       <c r="P503" s="4" t="n">
         <v>-3.72</v>
@@ -52508,10 +52508,10 @@
         <v>0</v>
       </c>
       <c r="AB503" s="4" t="n">
-        <v>36.91</v>
+        <v>36.87</v>
       </c>
       <c r="AC503" s="4" t="n">
-        <v>63.09</v>
+        <v>63.13</v>
       </c>
       <c r="AD503" s="4" t="n">
         <v>0</v>
@@ -52555,13 +52555,13 @@
         </is>
       </c>
       <c r="I504" s="4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="J504" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K504" s="4" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -52575,10 +52575,10 @@
         <v>5.28</v>
       </c>
       <c r="O504" s="4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.59</v>
       </c>
       <c r="P504" s="4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Q504" s="4" t="n">
         <v>2.05</v>
@@ -52612,10 +52612,10 @@
         <v>0</v>
       </c>
       <c r="AB504" s="4" t="n">
-        <v>49.57</v>
+        <v>49.56</v>
       </c>
       <c r="AC504" s="4" t="n">
-        <v>48.42</v>
+        <v>48.43</v>
       </c>
       <c r="AD504" s="4" t="n">
         <v>2.01</v>
@@ -54029,7 +54029,7 @@
         <v>76</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -54841,7 +54841,7 @@
         <v>67</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>31</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>57</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         </is>
       </c>
       <c r="J74" s="4" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="K74" t="n">
         <v>26</v>
